--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\모듈러사업2실\★ 300. 제1공장_마감관리팀\350. 마감진행현황\BH(수정)\2026년 10월 BH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54112F76-B35B-435A-9BA3-9F912DEBC116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73527249-2650-4CF2-9293-F618004AEEE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="788" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3880,13 +3880,6 @@
     <phoneticPr fontId="24" type="noConversion"/>
   </si>
   <si>
-    <t>402-7-1/
-26SB73
-36B(B-1)
-2026-10-1</t>
-    <phoneticPr fontId="24" type="noConversion"/>
-  </si>
-  <si>
     <t>402-5-9/
 36SB05
 36A(B-1)
@@ -4316,6 +4309,13 @@
     <t>402-3-3/
 36SB43
 2026-10-13</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>403-7-1/
+26SB73
+36B(B-1)
+2026-10-1</t>
     <phoneticPr fontId="24" type="noConversion"/>
   </si>
 </sst>
@@ -6825,13 +6825,487 @@
     <xf numFmtId="0" fontId="55" fillId="26" borderId="9" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="13" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="19" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="56" fillId="20" borderId="8" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="56" fillId="20" borderId="0" xfId="18" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="20" borderId="3" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="6" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="7" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="16" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="13" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="14" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="6" borderId="16" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="6" borderId="13" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="6" borderId="14" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="16" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="14" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="16" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="16" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="16" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="6" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="11" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="8" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="3" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="12" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="4" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="5" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="7" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="8" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="8" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="8" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="8" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="8" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="8" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="13" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="13" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="6" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="11" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="12" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="4" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="18" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="17" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="49" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="18" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="15" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="8" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="8" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="8" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="8" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="8" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="8" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="16" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="14" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="16" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="14" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="5" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="5" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="5" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="5" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="5" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="5" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="5" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="5" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="5" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="8" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="3" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="12" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="4" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="14" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="10" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="16" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="14" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="18" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="17" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="8" borderId="20" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6852,12 +7326,6 @@
     <xf numFmtId="0" fontId="21" fillId="8" borderId="24" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="16" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="14" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="14" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6912,42 +7380,15 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="18" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="15" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="37" fillId="8" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="8" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="8" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="37" fillId="8" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="8" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="8" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="37" fillId="8" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="8" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="8" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6981,448 +7422,7 @@
     <xf numFmtId="0" fontId="45" fillId="0" borderId="14" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="16" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="14" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="10" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="10" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="18" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="17" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="5" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="5" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="5" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="5" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="5" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="5" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="5" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="5" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="5" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="8" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="3" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="12" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="4" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="14" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="16" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="14" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="8" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="3" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="12" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="7" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="4" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="49" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="13" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="13" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="6" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="11" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="12" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="4" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="18" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="17" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="8" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="8" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="8" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="8" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="8" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="8" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="6" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="7" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="16" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="13" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="14" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="18" fillId="6" borderId="16" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="18" fillId="6" borderId="13" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="18" fillId="6" borderId="14" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="16" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="13" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="14" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="16" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="16" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="16" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="6" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="11" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="5" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="20" borderId="8" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="20" borderId="0" xfId="18" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="20" borderId="3" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -7766,31 +7766,31 @@
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
-      <c r="E1" s="546"/>
-      <c r="F1" s="547"/>
-      <c r="G1" s="546"/>
-      <c r="H1" s="550"/>
-      <c r="I1" s="547"/>
-      <c r="J1" s="546"/>
-      <c r="K1" s="550"/>
-      <c r="L1" s="550"/>
-      <c r="M1" s="550"/>
-      <c r="N1" s="550"/>
-      <c r="O1" s="550"/>
-      <c r="P1" s="547"/>
+      <c r="E1" s="402"/>
+      <c r="F1" s="403"/>
+      <c r="G1" s="402"/>
+      <c r="H1" s="406"/>
+      <c r="I1" s="403"/>
+      <c r="J1" s="402"/>
+      <c r="K1" s="406"/>
+      <c r="L1" s="406"/>
+      <c r="M1" s="406"/>
+      <c r="N1" s="406"/>
+      <c r="O1" s="406"/>
+      <c r="P1" s="403"/>
       <c r="Q1" s="3"/>
-      <c r="R1" s="552"/>
-      <c r="S1" s="484"/>
-      <c r="T1" s="553" t="s">
+      <c r="R1" s="408"/>
+      <c r="S1" s="400"/>
+      <c r="T1" s="409" t="s">
         <v>16</v>
       </c>
-      <c r="U1" s="554"/>
-      <c r="V1" s="554"/>
-      <c r="W1" s="554"/>
-      <c r="X1" s="554"/>
-      <c r="Y1" s="554"/>
-      <c r="Z1" s="554"/>
-      <c r="AA1" s="555"/>
+      <c r="U1" s="410"/>
+      <c r="V1" s="410"/>
+      <c r="W1" s="410"/>
+      <c r="X1" s="410"/>
+      <c r="Y1" s="410"/>
+      <c r="Z1" s="410"/>
+      <c r="AA1" s="411"/>
       <c r="AB1" s="4"/>
       <c r="AC1" s="5"/>
       <c r="AI1" s="7"/>
@@ -7812,7 +7812,7 @@
       <c r="AY1" s="16"/>
       <c r="AZ1" s="16"/>
       <c r="BA1" s="16"/>
-      <c r="BB1" s="559" t="s">
+      <c r="BB1" s="415" t="s">
         <v>4</v>
       </c>
       <c r="BC1" s="17"/>
@@ -7831,32 +7831,32 @@
       <c r="B2" s="23"/>
       <c r="C2" s="23"/>
       <c r="D2" s="23"/>
-      <c r="E2" s="548"/>
-      <c r="F2" s="549"/>
-      <c r="G2" s="548"/>
-      <c r="H2" s="551"/>
-      <c r="I2" s="549"/>
-      <c r="J2" s="548"/>
-      <c r="K2" s="551"/>
-      <c r="L2" s="551"/>
-      <c r="M2" s="551"/>
-      <c r="N2" s="551"/>
-      <c r="O2" s="551"/>
-      <c r="P2" s="549"/>
+      <c r="E2" s="404"/>
+      <c r="F2" s="405"/>
+      <c r="G2" s="404"/>
+      <c r="H2" s="407"/>
+      <c r="I2" s="405"/>
+      <c r="J2" s="404"/>
+      <c r="K2" s="407"/>
+      <c r="L2" s="407"/>
+      <c r="M2" s="407"/>
+      <c r="N2" s="407"/>
+      <c r="O2" s="407"/>
+      <c r="P2" s="405"/>
       <c r="Q2" s="3"/>
-      <c r="R2" s="484"/>
-      <c r="S2" s="484"/>
-      <c r="T2" s="556"/>
-      <c r="U2" s="557"/>
-      <c r="V2" s="557"/>
-      <c r="W2" s="557"/>
-      <c r="X2" s="557"/>
-      <c r="Y2" s="557"/>
-      <c r="Z2" s="557"/>
-      <c r="AA2" s="558"/>
+      <c r="R2" s="400"/>
+      <c r="S2" s="400"/>
+      <c r="T2" s="412"/>
+      <c r="U2" s="413"/>
+      <c r="V2" s="413"/>
+      <c r="W2" s="413"/>
+      <c r="X2" s="413"/>
+      <c r="Y2" s="413"/>
+      <c r="Z2" s="413"/>
+      <c r="AA2" s="414"/>
       <c r="AB2" s="24"/>
       <c r="AC2" s="5"/>
-      <c r="AI2" s="561" t="s">
+      <c r="AI2" s="417" t="s">
         <v>17</v>
       </c>
       <c r="AJ2" s="25"/>
@@ -7877,7 +7877,7 @@
       <c r="AY2" s="32"/>
       <c r="AZ2" s="32"/>
       <c r="BA2" s="32"/>
-      <c r="BB2" s="560"/>
+      <c r="BB2" s="416"/>
       <c r="BC2" s="33"/>
       <c r="BD2" s="33"/>
       <c r="BE2" s="34"/>
@@ -7916,21 +7916,21 @@
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
       <c r="S3" s="5"/>
-      <c r="T3" s="564" t="s">
+      <c r="T3" s="420" t="s">
         <v>18</v>
       </c>
-      <c r="U3" s="565"/>
-      <c r="V3" s="566"/>
+      <c r="U3" s="421"/>
+      <c r="V3" s="422"/>
       <c r="W3" s="41"/>
       <c r="X3" s="41"/>
-      <c r="Y3" s="567" t="s">
+      <c r="Y3" s="423" t="s">
         <v>18</v>
       </c>
-      <c r="Z3" s="568"/>
-      <c r="AA3" s="568"/>
-      <c r="AB3" s="569"/>
+      <c r="Z3" s="424"/>
+      <c r="AA3" s="424"/>
+      <c r="AB3" s="425"/>
       <c r="AC3" s="42"/>
-      <c r="AI3" s="562"/>
+      <c r="AI3" s="418"/>
       <c r="AJ3" s="43"/>
       <c r="AK3" s="26"/>
       <c r="AL3" s="26"/>
@@ -7975,7 +7975,7 @@
       <c r="AA4" s="50"/>
       <c r="AB4" s="41"/>
       <c r="AC4" s="42"/>
-      <c r="AI4" s="562"/>
+      <c r="AI4" s="418"/>
       <c r="AJ4" s="43"/>
       <c r="AK4" s="26"/>
       <c r="AL4" s="26"/>
@@ -8021,7 +8021,7 @@
       <c r="AA5" s="50"/>
       <c r="AB5" s="41"/>
       <c r="AC5" s="53"/>
-      <c r="AI5" s="563"/>
+      <c r="AI5" s="419"/>
       <c r="AJ5" s="54"/>
       <c r="AK5" s="55"/>
       <c r="AL5" s="55"/>
@@ -8403,52 +8403,52 @@
       <c r="AH10" s="59"/>
       <c r="AI10" s="44"/>
       <c r="AJ10" s="354"/>
-      <c r="AK10" s="570" t="s">
+      <c r="AK10" s="426" t="s">
         <v>7</v>
       </c>
-      <c r="AL10" s="571"/>
-      <c r="AM10" s="571"/>
-      <c r="AN10" s="571"/>
-      <c r="AO10" s="571"/>
-      <c r="AP10" s="571"/>
-      <c r="AQ10" s="571"/>
-      <c r="AR10" s="572"/>
+      <c r="AL10" s="393"/>
+      <c r="AM10" s="393"/>
+      <c r="AN10" s="393"/>
+      <c r="AO10" s="393"/>
+      <c r="AP10" s="393"/>
+      <c r="AQ10" s="393"/>
+      <c r="AR10" s="427"/>
       <c r="AS10" s="3"/>
       <c r="AT10" s="354"/>
       <c r="AU10" s="324"/>
       <c r="AV10" s="325"/>
       <c r="AW10" s="325"/>
-      <c r="AX10" s="571" t="s">
+      <c r="AX10" s="393" t="s">
         <v>8</v>
       </c>
-      <c r="AY10" s="571"/>
+      <c r="AY10" s="393"/>
       <c r="AZ10" s="325"/>
       <c r="BA10" s="325"/>
       <c r="BB10" s="326"/>
       <c r="BC10" s="3"/>
       <c r="BD10" s="350"/>
-      <c r="BE10" s="573" t="s">
+      <c r="BE10" s="428" t="s">
         <v>9</v>
       </c>
-      <c r="BF10" s="574"/>
-      <c r="BG10" s="574"/>
-      <c r="BH10" s="574"/>
-      <c r="BI10" s="574"/>
-      <c r="BJ10" s="574"/>
-      <c r="BK10" s="574"/>
-      <c r="BL10" s="575"/>
+      <c r="BF10" s="429"/>
+      <c r="BG10" s="429"/>
+      <c r="BH10" s="429"/>
+      <c r="BI10" s="429"/>
+      <c r="BJ10" s="429"/>
+      <c r="BK10" s="429"/>
+      <c r="BL10" s="430"/>
       <c r="BM10" s="314"/>
       <c r="BN10" s="344"/>
-      <c r="BO10" s="573" t="s">
+      <c r="BO10" s="428" t="s">
         <v>10</v>
       </c>
-      <c r="BP10" s="574"/>
-      <c r="BQ10" s="574"/>
-      <c r="BR10" s="574"/>
-      <c r="BS10" s="574"/>
-      <c r="BT10" s="574"/>
-      <c r="BU10" s="574"/>
-      <c r="BV10" s="575"/>
+      <c r="BP10" s="429"/>
+      <c r="BQ10" s="429"/>
+      <c r="BR10" s="429"/>
+      <c r="BS10" s="429"/>
+      <c r="BT10" s="429"/>
+      <c r="BU10" s="429"/>
+      <c r="BV10" s="430"/>
       <c r="BX10" s="348"/>
     </row>
     <row r="11" spans="1:76" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -8461,28 +8461,28 @@
       </c>
       <c r="F11" s="72"/>
       <c r="G11" s="72"/>
-      <c r="H11" s="576" t="s">
+      <c r="H11" s="431" t="s">
         <v>21</v>
       </c>
-      <c r="I11" s="577"/>
-      <c r="J11" s="576" t="s">
+      <c r="I11" s="432"/>
+      <c r="J11" s="431" t="s">
         <v>22</v>
       </c>
-      <c r="K11" s="577"/>
-      <c r="L11" s="578" t="s">
+      <c r="K11" s="432"/>
+      <c r="L11" s="438" t="s">
         <v>23</v>
       </c>
-      <c r="M11" s="578"/>
+      <c r="M11" s="438"/>
       <c r="N11" s="73"/>
-      <c r="O11" s="579" t="s">
+      <c r="O11" s="440" t="s">
         <v>24</v>
       </c>
-      <c r="P11" s="580"/>
-      <c r="Q11" s="580"/>
-      <c r="R11" s="580"/>
-      <c r="S11" s="580"/>
-      <c r="T11" s="580"/>
-      <c r="U11" s="580"/>
+      <c r="P11" s="441"/>
+      <c r="Q11" s="441"/>
+      <c r="R11" s="441"/>
+      <c r="S11" s="441"/>
+      <c r="T11" s="441"/>
+      <c r="U11" s="441"/>
       <c r="V11" s="74"/>
       <c r="W11" s="75"/>
       <c r="X11" s="75"/>
@@ -8501,16 +8501,16 @@
         <v>300</v>
       </c>
       <c r="AK11" s="391" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AL11" s="391" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="AM11" s="312"/>
       <c r="AN11" s="312"/>
       <c r="AO11" s="312"/>
       <c r="AP11" s="371" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="AQ11" s="312"/>
       <c r="AR11" s="312"/>
@@ -8567,20 +8567,20 @@
       <c r="E12" s="78"/>
       <c r="F12" s="79"/>
       <c r="G12" s="79"/>
-      <c r="H12" s="478"/>
-      <c r="I12" s="480"/>
-      <c r="J12" s="478"/>
-      <c r="K12" s="480"/>
-      <c r="L12" s="479"/>
-      <c r="M12" s="479"/>
+      <c r="H12" s="433"/>
+      <c r="I12" s="434"/>
+      <c r="J12" s="433"/>
+      <c r="K12" s="434"/>
+      <c r="L12" s="435"/>
+      <c r="M12" s="435"/>
       <c r="N12" s="81"/>
-      <c r="O12" s="581"/>
-      <c r="P12" s="582"/>
-      <c r="Q12" s="582"/>
-      <c r="R12" s="582"/>
-      <c r="S12" s="582"/>
-      <c r="T12" s="582"/>
-      <c r="U12" s="582"/>
+      <c r="O12" s="442"/>
+      <c r="P12" s="443"/>
+      <c r="Q12" s="443"/>
+      <c r="R12" s="443"/>
+      <c r="S12" s="443"/>
+      <c r="T12" s="443"/>
+      <c r="U12" s="443"/>
       <c r="V12" s="82"/>
       <c r="W12" s="53"/>
       <c r="X12" s="53"/>
@@ -8606,7 +8606,7 @@
       <c r="AN12" s="313"/>
       <c r="AO12" s="313"/>
       <c r="AP12" s="359" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="AQ12" s="359" t="s">
         <v>575</v>
@@ -8657,20 +8657,20 @@
       <c r="E13" s="78"/>
       <c r="F13" s="79"/>
       <c r="G13" s="79"/>
-      <c r="H13" s="478"/>
-      <c r="I13" s="480"/>
-      <c r="J13" s="478"/>
-      <c r="K13" s="480"/>
-      <c r="L13" s="479"/>
-      <c r="M13" s="479"/>
+      <c r="H13" s="433"/>
+      <c r="I13" s="434"/>
+      <c r="J13" s="433"/>
+      <c r="K13" s="434"/>
+      <c r="L13" s="435"/>
+      <c r="M13" s="435"/>
       <c r="N13" s="81"/>
-      <c r="O13" s="581"/>
-      <c r="P13" s="582"/>
-      <c r="Q13" s="582"/>
-      <c r="R13" s="582"/>
-      <c r="S13" s="582"/>
-      <c r="T13" s="582"/>
-      <c r="U13" s="582"/>
+      <c r="O13" s="442"/>
+      <c r="P13" s="443"/>
+      <c r="Q13" s="443"/>
+      <c r="R13" s="443"/>
+      <c r="S13" s="443"/>
+      <c r="T13" s="443"/>
+      <c r="U13" s="443"/>
       <c r="V13" s="82"/>
       <c r="W13" s="53"/>
       <c r="X13" s="53"/>
@@ -8689,20 +8689,20 @@
         <v>300</v>
       </c>
       <c r="AK13" s="391" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="AL13" s="391" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AM13" s="328"/>
       <c r="AN13" s="328"/>
       <c r="AO13" s="328"/>
       <c r="AP13" s="371" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="AQ13" s="328"/>
       <c r="AR13" s="328"/>
-      <c r="AS13" s="393" t="s">
+      <c r="AS13" s="395" t="s">
         <v>534</v>
       </c>
       <c r="AT13" s="352" t="s">
@@ -8716,7 +8716,7 @@
       <c r="AZ13" s="328"/>
       <c r="BA13" s="328"/>
       <c r="BB13" s="328"/>
-      <c r="BC13" s="393" t="s">
+      <c r="BC13" s="395" t="s">
         <v>356</v>
       </c>
       <c r="BD13" s="352" t="s">
@@ -8730,7 +8730,7 @@
       <c r="BJ13" s="328"/>
       <c r="BK13" s="328"/>
       <c r="BL13" s="328"/>
-      <c r="BM13" s="393" t="s">
+      <c r="BM13" s="395" t="s">
         <v>330</v>
       </c>
       <c r="BN13" s="346" t="s">
@@ -8744,7 +8744,7 @@
       <c r="BT13" s="328"/>
       <c r="BU13" s="328"/>
       <c r="BV13" s="328"/>
-      <c r="BW13" s="393" t="s">
+      <c r="BW13" s="395" t="s">
         <v>302</v>
       </c>
       <c r="BX13" s="348"/>
@@ -8755,20 +8755,20 @@
       <c r="E14" s="78"/>
       <c r="F14" s="79"/>
       <c r="G14" s="79"/>
-      <c r="H14" s="478"/>
-      <c r="I14" s="480"/>
-      <c r="J14" s="478"/>
-      <c r="K14" s="480"/>
-      <c r="L14" s="479"/>
-      <c r="M14" s="479"/>
+      <c r="H14" s="433"/>
+      <c r="I14" s="434"/>
+      <c r="J14" s="433"/>
+      <c r="K14" s="434"/>
+      <c r="L14" s="435"/>
+      <c r="M14" s="435"/>
       <c r="N14" s="81"/>
-      <c r="O14" s="581"/>
-      <c r="P14" s="582"/>
-      <c r="Q14" s="582"/>
-      <c r="R14" s="582"/>
-      <c r="S14" s="582"/>
-      <c r="T14" s="582"/>
-      <c r="U14" s="582"/>
+      <c r="O14" s="442"/>
+      <c r="P14" s="443"/>
+      <c r="Q14" s="443"/>
+      <c r="R14" s="443"/>
+      <c r="S14" s="443"/>
+      <c r="T14" s="443"/>
+      <c r="U14" s="443"/>
       <c r="V14" s="82"/>
       <c r="W14" s="53"/>
       <c r="X14" s="53"/>
@@ -8785,28 +8785,28 @@
       <c r="AI14" s="84"/>
       <c r="AJ14" s="352"/>
       <c r="AK14" s="369" t="s">
+        <v>606</v>
+      </c>
+      <c r="AL14" s="361" t="s">
         <v>607</v>
       </c>
-      <c r="AL14" s="361" t="s">
-        <v>608</v>
-      </c>
       <c r="AM14" s="333" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="AN14" s="327"/>
       <c r="AO14" s="368" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AP14" s="359" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="AQ14" s="359" t="s">
+        <v>608</v>
+      </c>
+      <c r="AR14" s="359" t="s">
         <v>609</v>
       </c>
-      <c r="AR14" s="359" t="s">
-        <v>610</v>
-      </c>
-      <c r="AS14" s="393"/>
+      <c r="AS14" s="395"/>
       <c r="AT14" s="352"/>
       <c r="AU14" s="327"/>
       <c r="AV14" s="327"/>
@@ -8816,7 +8816,7 @@
       <c r="AZ14" s="327"/>
       <c r="BA14" s="327"/>
       <c r="BB14" s="327"/>
-      <c r="BC14" s="393"/>
+      <c r="BC14" s="395"/>
       <c r="BD14" s="352"/>
       <c r="BE14" s="327"/>
       <c r="BF14" s="327"/>
@@ -8826,7 +8826,7 @@
       <c r="BJ14" s="327"/>
       <c r="BK14" s="327"/>
       <c r="BL14" s="327"/>
-      <c r="BM14" s="393"/>
+      <c r="BM14" s="395"/>
       <c r="BN14" s="346"/>
       <c r="BO14" s="335" t="s">
         <v>434</v>
@@ -8840,7 +8840,7 @@
       <c r="BT14" s="327"/>
       <c r="BU14" s="327"/>
       <c r="BV14" s="327"/>
-      <c r="BW14" s="393"/>
+      <c r="BW14" s="395"/>
       <c r="BX14" s="348"/>
     </row>
     <row r="15" spans="1:76" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -8852,20 +8852,20 @@
       <c r="E15" s="78"/>
       <c r="F15" s="79"/>
       <c r="G15" s="79"/>
-      <c r="H15" s="478"/>
-      <c r="I15" s="480"/>
-      <c r="J15" s="478"/>
-      <c r="K15" s="480"/>
-      <c r="L15" s="479"/>
-      <c r="M15" s="479"/>
+      <c r="H15" s="433"/>
+      <c r="I15" s="434"/>
+      <c r="J15" s="433"/>
+      <c r="K15" s="434"/>
+      <c r="L15" s="435"/>
+      <c r="M15" s="435"/>
       <c r="N15" s="81"/>
-      <c r="O15" s="583"/>
-      <c r="P15" s="584"/>
-      <c r="Q15" s="584"/>
-      <c r="R15" s="584"/>
-      <c r="S15" s="584"/>
-      <c r="T15" s="584"/>
-      <c r="U15" s="584"/>
+      <c r="O15" s="444"/>
+      <c r="P15" s="445"/>
+      <c r="Q15" s="445"/>
+      <c r="R15" s="445"/>
+      <c r="S15" s="445"/>
+      <c r="T15" s="445"/>
+      <c r="U15" s="445"/>
       <c r="V15" s="82"/>
       <c r="W15" s="53"/>
       <c r="X15" s="53"/>
@@ -8884,10 +8884,10 @@
         <v>300</v>
       </c>
       <c r="AK15" s="391" t="s">
+        <v>640</v>
+      </c>
+      <c r="AL15" s="391" t="s">
         <v>641</v>
-      </c>
-      <c r="AL15" s="391" t="s">
-        <v>642</v>
       </c>
       <c r="AM15" s="312"/>
       <c r="AN15" s="312"/>
@@ -8948,22 +8948,22 @@
       <c r="E16" s="78"/>
       <c r="F16" s="79"/>
       <c r="G16" s="79"/>
-      <c r="H16" s="478"/>
-      <c r="I16" s="480"/>
-      <c r="J16" s="478"/>
-      <c r="K16" s="480"/>
-      <c r="L16" s="479"/>
-      <c r="M16" s="479"/>
+      <c r="H16" s="433"/>
+      <c r="I16" s="434"/>
+      <c r="J16" s="433"/>
+      <c r="K16" s="434"/>
+      <c r="L16" s="435"/>
+      <c r="M16" s="435"/>
       <c r="N16" s="81"/>
-      <c r="O16" s="579" t="s">
+      <c r="O16" s="440" t="s">
         <v>25</v>
       </c>
-      <c r="P16" s="580"/>
-      <c r="Q16" s="580"/>
-      <c r="R16" s="580"/>
-      <c r="S16" s="580"/>
-      <c r="T16" s="580"/>
-      <c r="U16" s="580"/>
+      <c r="P16" s="441"/>
+      <c r="Q16" s="441"/>
+      <c r="R16" s="441"/>
+      <c r="S16" s="441"/>
+      <c r="T16" s="441"/>
+      <c r="U16" s="441"/>
       <c r="V16" s="82"/>
       <c r="W16" s="53"/>
       <c r="X16" s="53"/>
@@ -8980,28 +8980,28 @@
       <c r="AI16" s="42"/>
       <c r="AJ16" s="351"/>
       <c r="AK16" s="369" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AL16" s="369" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="AM16" s="369" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="AN16" s="369" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="AO16" s="359" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AP16" s="320" t="s">
         <v>276</v>
       </c>
       <c r="AQ16" s="359" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="AR16" s="333" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="AS16" s="394"/>
       <c r="AT16" s="351"/>
@@ -9047,20 +9047,20 @@
       <c r="E17" s="78"/>
       <c r="F17" s="79"/>
       <c r="G17" s="79"/>
-      <c r="H17" s="478"/>
-      <c r="I17" s="480"/>
-      <c r="J17" s="478"/>
-      <c r="K17" s="480"/>
-      <c r="L17" s="479"/>
-      <c r="M17" s="479"/>
+      <c r="H17" s="433"/>
+      <c r="I17" s="434"/>
+      <c r="J17" s="433"/>
+      <c r="K17" s="434"/>
+      <c r="L17" s="435"/>
+      <c r="M17" s="435"/>
       <c r="N17" s="81"/>
-      <c r="O17" s="581"/>
-      <c r="P17" s="582"/>
-      <c r="Q17" s="582"/>
-      <c r="R17" s="582"/>
-      <c r="S17" s="582"/>
-      <c r="T17" s="582"/>
-      <c r="U17" s="582"/>
+      <c r="O17" s="442"/>
+      <c r="P17" s="443"/>
+      <c r="Q17" s="443"/>
+      <c r="R17" s="443"/>
+      <c r="S17" s="443"/>
+      <c r="T17" s="443"/>
+      <c r="U17" s="443"/>
       <c r="V17" s="82"/>
       <c r="W17" s="53"/>
       <c r="X17" s="53"/>
@@ -9079,10 +9079,10 @@
         <v>300</v>
       </c>
       <c r="AK17" s="370" t="s">
+        <v>621</v>
+      </c>
+      <c r="AL17" s="391" t="s">
         <v>622</v>
-      </c>
-      <c r="AL17" s="391" t="s">
-        <v>623</v>
       </c>
       <c r="AM17" s="328"/>
       <c r="AN17" s="328"/>
@@ -9090,7 +9090,7 @@
       <c r="AP17" s="328"/>
       <c r="AQ17" s="328"/>
       <c r="AR17" s="328"/>
-      <c r="AS17" s="393" t="s">
+      <c r="AS17" s="395" t="s">
         <v>536</v>
       </c>
       <c r="AT17" s="352" t="s">
@@ -9104,7 +9104,7 @@
       <c r="AZ17" s="328"/>
       <c r="BA17" s="328"/>
       <c r="BB17" s="328"/>
-      <c r="BC17" s="393" t="s">
+      <c r="BC17" s="395" t="s">
         <v>358</v>
       </c>
       <c r="BD17" s="352" t="s">
@@ -9124,7 +9124,7 @@
       <c r="BL17" s="362" t="s">
         <v>107</v>
       </c>
-      <c r="BM17" s="393" t="s">
+      <c r="BM17" s="395" t="s">
         <v>332</v>
       </c>
       <c r="BN17" s="346" t="s">
@@ -9140,7 +9140,7 @@
       <c r="BT17" s="328"/>
       <c r="BU17" s="328"/>
       <c r="BV17" s="328"/>
-      <c r="BW17" s="589" t="s">
+      <c r="BW17" s="399" t="s">
         <v>304</v>
       </c>
       <c r="BX17" s="348"/>
@@ -9151,24 +9151,24 @@
       </c>
       <c r="B18" s="61"/>
       <c r="E18" s="78"/>
-      <c r="F18" s="486" t="s">
+      <c r="F18" s="455" t="s">
         <v>26</v>
       </c>
-      <c r="G18" s="488"/>
-      <c r="H18" s="479"/>
-      <c r="I18" s="480"/>
-      <c r="J18" s="478"/>
-      <c r="K18" s="480"/>
-      <c r="L18" s="479"/>
-      <c r="M18" s="479"/>
+      <c r="G18" s="456"/>
+      <c r="H18" s="435"/>
+      <c r="I18" s="434"/>
+      <c r="J18" s="433"/>
+      <c r="K18" s="434"/>
+      <c r="L18" s="435"/>
+      <c r="M18" s="435"/>
       <c r="N18" s="81"/>
-      <c r="O18" s="581"/>
-      <c r="P18" s="582"/>
-      <c r="Q18" s="582"/>
-      <c r="R18" s="582"/>
-      <c r="S18" s="582"/>
-      <c r="T18" s="582"/>
-      <c r="U18" s="582"/>
+      <c r="O18" s="442"/>
+      <c r="P18" s="443"/>
+      <c r="Q18" s="443"/>
+      <c r="R18" s="443"/>
+      <c r="S18" s="443"/>
+      <c r="T18" s="443"/>
+      <c r="U18" s="443"/>
       <c r="V18" s="82"/>
       <c r="W18" s="53"/>
       <c r="X18" s="53"/>
@@ -9185,26 +9185,26 @@
       <c r="AI18" s="42"/>
       <c r="AJ18" s="352"/>
       <c r="AK18" s="369" t="s">
+        <v>623</v>
+      </c>
+      <c r="AL18" s="369" t="s">
         <v>624</v>
       </c>
-      <c r="AL18" s="369" t="s">
+      <c r="AM18" s="369" t="s">
         <v>625</v>
       </c>
-      <c r="AM18" s="369" t="s">
+      <c r="AN18" s="369" t="s">
         <v>626</v>
       </c>
-      <c r="AN18" s="369" t="s">
+      <c r="AO18" s="359" t="s">
         <v>627</v>
       </c>
-      <c r="AO18" s="359" t="s">
+      <c r="AP18" s="359" t="s">
         <v>628</v>
-      </c>
-      <c r="AP18" s="359" t="s">
-        <v>629</v>
       </c>
       <c r="AQ18" s="327"/>
       <c r="AR18" s="327"/>
-      <c r="AS18" s="393"/>
+      <c r="AS18" s="395"/>
       <c r="AT18" s="352"/>
       <c r="AU18" s="327"/>
       <c r="AV18" s="327"/>
@@ -9214,7 +9214,7 @@
       <c r="AZ18" s="327"/>
       <c r="BA18" s="327"/>
       <c r="BB18" s="327"/>
-      <c r="BC18" s="393"/>
+      <c r="BC18" s="395"/>
       <c r="BD18" s="352"/>
       <c r="BE18" s="374"/>
       <c r="BF18" s="320" t="s">
@@ -9234,7 +9234,7 @@
       <c r="BL18" s="362" t="s">
         <v>109</v>
       </c>
-      <c r="BM18" s="393"/>
+      <c r="BM18" s="395"/>
       <c r="BN18" s="346"/>
       <c r="BO18" s="362" t="s">
         <v>179</v>
@@ -9254,31 +9254,31 @@
       <c r="BV18" s="362" t="s">
         <v>182</v>
       </c>
-      <c r="BW18" s="589"/>
+      <c r="BW18" s="399"/>
       <c r="BX18" s="348"/>
     </row>
     <row r="19" spans="1:76" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="22"/>
       <c r="B19" s="63"/>
       <c r="E19" s="78"/>
-      <c r="F19" s="585"/>
-      <c r="G19" s="586"/>
-      <c r="H19" s="479"/>
-      <c r="I19" s="480"/>
-      <c r="J19" s="478"/>
-      <c r="K19" s="480"/>
-      <c r="L19" s="479"/>
-      <c r="M19" s="479"/>
+      <c r="F19" s="457"/>
+      <c r="G19" s="458"/>
+      <c r="H19" s="435"/>
+      <c r="I19" s="434"/>
+      <c r="J19" s="433"/>
+      <c r="K19" s="434"/>
+      <c r="L19" s="435"/>
+      <c r="M19" s="435"/>
       <c r="N19" s="81"/>
-      <c r="O19" s="506" t="s">
+      <c r="O19" s="461" t="s">
         <v>27</v>
       </c>
-      <c r="P19" s="507"/>
-      <c r="Q19" s="507"/>
-      <c r="R19" s="507"/>
-      <c r="S19" s="507"/>
-      <c r="T19" s="507"/>
-      <c r="U19" s="508"/>
+      <c r="P19" s="462"/>
+      <c r="Q19" s="462"/>
+      <c r="R19" s="462"/>
+      <c r="S19" s="462"/>
+      <c r="T19" s="462"/>
+      <c r="U19" s="463"/>
       <c r="V19" s="82"/>
       <c r="W19" s="53"/>
       <c r="X19" s="53"/>
@@ -9298,7 +9298,7 @@
       </c>
       <c r="AK19" s="312"/>
       <c r="AL19" s="391" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="AM19" s="312"/>
       <c r="AN19" s="312"/>
@@ -9357,33 +9357,33 @@
       <c r="BT19" s="312"/>
       <c r="BU19" s="312"/>
       <c r="BV19" s="312"/>
-      <c r="BW19" s="484" t="s">
+      <c r="BW19" s="400" t="s">
         <v>305</v>
       </c>
       <c r="BX19" s="348"/>
     </row>
     <row r="20" spans="1:76" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="515" t="s">
+      <c r="A20" s="470" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="516"/>
+      <c r="B20" s="471"/>
       <c r="E20" s="103"/>
-      <c r="F20" s="587"/>
-      <c r="G20" s="588"/>
-      <c r="H20" s="479"/>
-      <c r="I20" s="480"/>
-      <c r="J20" s="478"/>
-      <c r="K20" s="480"/>
-      <c r="L20" s="479"/>
-      <c r="M20" s="479"/>
+      <c r="F20" s="459"/>
+      <c r="G20" s="460"/>
+      <c r="H20" s="435"/>
+      <c r="I20" s="434"/>
+      <c r="J20" s="433"/>
+      <c r="K20" s="434"/>
+      <c r="L20" s="435"/>
+      <c r="M20" s="435"/>
       <c r="N20" s="81"/>
-      <c r="O20" s="509"/>
-      <c r="P20" s="510"/>
-      <c r="Q20" s="510"/>
-      <c r="R20" s="510"/>
-      <c r="S20" s="510"/>
-      <c r="T20" s="510"/>
-      <c r="U20" s="511"/>
+      <c r="O20" s="464"/>
+      <c r="P20" s="465"/>
+      <c r="Q20" s="465"/>
+      <c r="R20" s="465"/>
+      <c r="S20" s="465"/>
+      <c r="T20" s="465"/>
+      <c r="U20" s="466"/>
       <c r="V20" s="82"/>
       <c r="W20" s="53"/>
       <c r="X20" s="53"/>
@@ -9401,7 +9401,7 @@
       <c r="AJ20" s="351"/>
       <c r="AK20" s="313"/>
       <c r="AL20" s="369" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="AM20" s="313"/>
       <c r="AN20" s="313"/>
@@ -9422,7 +9422,7 @@
       <c r="BC20" s="394"/>
       <c r="BD20" s="351"/>
       <c r="BE20" s="369" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="BF20" s="335" t="s">
         <v>578</v>
@@ -9451,7 +9451,7 @@
       <c r="BQ20" s="313"/>
       <c r="BR20" s="313"/>
       <c r="BS20" s="335" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="BT20" s="320" t="s">
         <v>95</v>
@@ -9462,29 +9462,29 @@
       <c r="BV20" s="362" t="s">
         <v>191</v>
       </c>
-      <c r="BW20" s="484"/>
+      <c r="BW20" s="400"/>
       <c r="BX20" s="348"/>
     </row>
     <row r="21" spans="1:76" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="460"/>
-      <c r="B21" s="517"/>
+      <c r="A21" s="472"/>
+      <c r="B21" s="473"/>
       <c r="E21" s="106"/>
       <c r="F21" s="107"/>
       <c r="G21" s="107"/>
-      <c r="H21" s="478"/>
-      <c r="I21" s="480"/>
-      <c r="J21" s="478"/>
-      <c r="K21" s="480"/>
-      <c r="L21" s="479"/>
-      <c r="M21" s="479"/>
+      <c r="H21" s="433"/>
+      <c r="I21" s="434"/>
+      <c r="J21" s="433"/>
+      <c r="K21" s="434"/>
+      <c r="L21" s="435"/>
+      <c r="M21" s="435"/>
       <c r="N21" s="81"/>
-      <c r="O21" s="509"/>
-      <c r="P21" s="510"/>
-      <c r="Q21" s="510"/>
-      <c r="R21" s="510"/>
-      <c r="S21" s="510"/>
-      <c r="T21" s="510"/>
-      <c r="U21" s="511"/>
+      <c r="O21" s="464"/>
+      <c r="P21" s="465"/>
+      <c r="Q21" s="465"/>
+      <c r="R21" s="465"/>
+      <c r="S21" s="465"/>
+      <c r="T21" s="465"/>
+      <c r="U21" s="466"/>
       <c r="V21" s="82"/>
       <c r="W21" s="53"/>
       <c r="X21" s="53"/>
@@ -9510,7 +9510,7 @@
       <c r="AP21" s="328"/>
       <c r="AQ21" s="328"/>
       <c r="AR21" s="328"/>
-      <c r="AS21" s="393" t="s">
+      <c r="AS21" s="395" t="s">
         <v>538</v>
       </c>
       <c r="AT21" s="352" t="s">
@@ -9524,7 +9524,7 @@
       <c r="AZ21" s="328"/>
       <c r="BA21" s="328"/>
       <c r="BB21" s="328"/>
-      <c r="BC21" s="393" t="s">
+      <c r="BC21" s="395" t="s">
         <v>360</v>
       </c>
       <c r="BD21" s="352" t="s">
@@ -9543,7 +9543,7 @@
       <c r="BL21" s="320" t="s">
         <v>125</v>
       </c>
-      <c r="BM21" s="393" t="s">
+      <c r="BM21" s="395" t="s">
         <v>334</v>
       </c>
       <c r="BN21" s="346" t="s">
@@ -9557,35 +9557,35 @@
       <c r="BT21" s="328"/>
       <c r="BU21" s="328"/>
       <c r="BV21" s="328"/>
-      <c r="BW21" s="545" t="s">
+      <c r="BW21" s="401" t="s">
         <v>306</v>
       </c>
       <c r="BX21" s="348"/>
     </row>
     <row r="22" spans="1:76" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="467"/>
-      <c r="B22" s="518"/>
+      <c r="A22" s="474"/>
+      <c r="B22" s="475"/>
       <c r="C22" s="109"/>
       <c r="D22" s="93"/>
-      <c r="E22" s="519" t="s">
+      <c r="E22" s="453" t="s">
         <v>29</v>
       </c>
-      <c r="F22" s="519"/>
-      <c r="G22" s="520"/>
-      <c r="H22" s="478"/>
-      <c r="I22" s="480"/>
-      <c r="J22" s="478"/>
-      <c r="K22" s="480"/>
-      <c r="L22" s="479"/>
-      <c r="M22" s="479"/>
+      <c r="F22" s="453"/>
+      <c r="G22" s="454"/>
+      <c r="H22" s="433"/>
+      <c r="I22" s="434"/>
+      <c r="J22" s="433"/>
+      <c r="K22" s="434"/>
+      <c r="L22" s="435"/>
+      <c r="M22" s="435"/>
       <c r="N22" s="81"/>
-      <c r="O22" s="512"/>
-      <c r="P22" s="513"/>
-      <c r="Q22" s="513"/>
-      <c r="R22" s="513"/>
-      <c r="S22" s="513"/>
-      <c r="T22" s="513"/>
-      <c r="U22" s="514"/>
+      <c r="O22" s="467"/>
+      <c r="P22" s="468"/>
+      <c r="Q22" s="468"/>
+      <c r="R22" s="468"/>
+      <c r="S22" s="468"/>
+      <c r="T22" s="468"/>
+      <c r="U22" s="469"/>
       <c r="V22" s="82"/>
       <c r="W22" s="53"/>
       <c r="X22" s="53"/>
@@ -9606,12 +9606,12 @@
       <c r="AM22" s="327"/>
       <c r="AN22" s="327"/>
       <c r="AO22" s="359" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="AP22" s="327"/>
       <c r="AQ22" s="327"/>
       <c r="AR22" s="327"/>
-      <c r="AS22" s="393"/>
+      <c r="AS22" s="395"/>
       <c r="AT22" s="352"/>
       <c r="AU22" s="327"/>
       <c r="AV22" s="327"/>
@@ -9621,7 +9621,7 @@
       <c r="AZ22" s="327"/>
       <c r="BA22" s="327"/>
       <c r="BB22" s="327"/>
-      <c r="BC22" s="393"/>
+      <c r="BC22" s="395"/>
       <c r="BD22" s="352"/>
       <c r="BE22" s="320" t="s">
         <v>186</v>
@@ -9643,7 +9643,7 @@
       <c r="BL22" s="320" t="s">
         <v>113</v>
       </c>
-      <c r="BM22" s="393"/>
+      <c r="BM22" s="395"/>
       <c r="BN22" s="346"/>
       <c r="BO22" s="320" t="s">
         <v>193</v>
@@ -9667,33 +9667,33 @@
       <c r="BV22" s="320" t="s">
         <v>195</v>
       </c>
-      <c r="BW22" s="545"/>
+      <c r="BW22" s="401"/>
       <c r="BX22" s="348"/>
     </row>
     <row r="23" spans="1:76" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="515" t="s">
+      <c r="A23" s="470" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="523"/>
+      <c r="B23" s="476"/>
       <c r="C23" s="109"/>
       <c r="D23" s="112"/>
-      <c r="E23" s="521"/>
-      <c r="F23" s="521"/>
-      <c r="G23" s="522"/>
-      <c r="H23" s="478"/>
-      <c r="I23" s="480"/>
-      <c r="J23" s="478"/>
-      <c r="K23" s="480"/>
-      <c r="L23" s="479"/>
-      <c r="M23" s="479"/>
+      <c r="E23" s="450"/>
+      <c r="F23" s="450"/>
+      <c r="G23" s="451"/>
+      <c r="H23" s="433"/>
+      <c r="I23" s="434"/>
+      <c r="J23" s="433"/>
+      <c r="K23" s="434"/>
+      <c r="L23" s="435"/>
+      <c r="M23" s="435"/>
       <c r="N23" s="81"/>
-      <c r="O23" s="525"/>
-      <c r="P23" s="526"/>
-      <c r="Q23" s="526"/>
-      <c r="R23" s="526"/>
-      <c r="S23" s="526"/>
-      <c r="T23" s="526"/>
-      <c r="U23" s="527"/>
+      <c r="O23" s="478"/>
+      <c r="P23" s="479"/>
+      <c r="Q23" s="479"/>
+      <c r="R23" s="479"/>
+      <c r="S23" s="479"/>
+      <c r="T23" s="479"/>
+      <c r="U23" s="480"/>
       <c r="V23" s="74"/>
       <c r="W23" s="75"/>
       <c r="X23" s="75"/>
@@ -9768,35 +9768,35 @@
       <c r="BS23" s="312"/>
       <c r="BU23" s="312"/>
       <c r="BV23" s="312"/>
-      <c r="BW23" s="484" t="s">
+      <c r="BW23" s="400" t="s">
         <v>307</v>
       </c>
       <c r="BX23" s="348"/>
     </row>
     <row r="24" spans="1:76" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="460"/>
-      <c r="B24" s="524"/>
+      <c r="A24" s="472"/>
+      <c r="B24" s="477"/>
       <c r="C24" s="113"/>
       <c r="D24" s="112"/>
-      <c r="E24" s="519" t="s">
+      <c r="E24" s="453" t="s">
         <v>29</v>
       </c>
-      <c r="F24" s="519"/>
-      <c r="G24" s="520"/>
-      <c r="H24" s="478"/>
-      <c r="I24" s="480"/>
-      <c r="J24" s="478"/>
-      <c r="K24" s="480"/>
-      <c r="L24" s="479"/>
-      <c r="M24" s="479"/>
+      <c r="F24" s="453"/>
+      <c r="G24" s="454"/>
+      <c r="H24" s="433"/>
+      <c r="I24" s="434"/>
+      <c r="J24" s="433"/>
+      <c r="K24" s="434"/>
+      <c r="L24" s="435"/>
+      <c r="M24" s="435"/>
       <c r="N24" s="81"/>
-      <c r="O24" s="528"/>
-      <c r="P24" s="529"/>
-      <c r="Q24" s="529"/>
-      <c r="R24" s="529"/>
-      <c r="S24" s="529"/>
-      <c r="T24" s="529"/>
-      <c r="U24" s="530"/>
+      <c r="O24" s="481"/>
+      <c r="P24" s="482"/>
+      <c r="Q24" s="482"/>
+      <c r="R24" s="482"/>
+      <c r="S24" s="482"/>
+      <c r="T24" s="482"/>
+      <c r="U24" s="483"/>
       <c r="V24" s="82"/>
       <c r="W24" s="53"/>
       <c r="X24" s="90"/>
@@ -9849,7 +9849,7 @@
         <v>117</v>
       </c>
       <c r="BK24" s="369" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="BL24" s="359" t="s">
         <v>119</v>
@@ -9878,31 +9878,31 @@
       <c r="BV24" s="320" t="s">
         <v>200</v>
       </c>
-      <c r="BW24" s="484"/>
+      <c r="BW24" s="400"/>
       <c r="BX24" s="348"/>
     </row>
     <row r="25" spans="1:76" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="467"/>
-      <c r="B25" s="518"/>
+      <c r="A25" s="474"/>
+      <c r="B25" s="475"/>
       <c r="C25" s="109"/>
       <c r="D25" s="115"/>
-      <c r="E25" s="534"/>
-      <c r="F25" s="534"/>
-      <c r="G25" s="535"/>
-      <c r="H25" s="478"/>
-      <c r="I25" s="480"/>
-      <c r="J25" s="478"/>
-      <c r="K25" s="480"/>
-      <c r="L25" s="479"/>
-      <c r="M25" s="479"/>
+      <c r="E25" s="447"/>
+      <c r="F25" s="447"/>
+      <c r="G25" s="448"/>
+      <c r="H25" s="433"/>
+      <c r="I25" s="434"/>
+      <c r="J25" s="433"/>
+      <c r="K25" s="434"/>
+      <c r="L25" s="435"/>
+      <c r="M25" s="435"/>
       <c r="N25" s="81"/>
-      <c r="O25" s="528"/>
-      <c r="P25" s="529"/>
-      <c r="Q25" s="529"/>
-      <c r="R25" s="529"/>
-      <c r="S25" s="529"/>
-      <c r="T25" s="529"/>
-      <c r="U25" s="530"/>
+      <c r="O25" s="481"/>
+      <c r="P25" s="482"/>
+      <c r="Q25" s="482"/>
+      <c r="R25" s="482"/>
+      <c r="S25" s="482"/>
+      <c r="T25" s="482"/>
+      <c r="U25" s="483"/>
       <c r="V25" s="104"/>
       <c r="W25" s="97"/>
       <c r="X25" s="97"/>
@@ -9928,7 +9928,7 @@
       <c r="AP25" s="328"/>
       <c r="AQ25" s="328"/>
       <c r="AR25" s="328"/>
-      <c r="AS25" s="393" t="s">
+      <c r="AS25" s="395" t="s">
         <v>540</v>
       </c>
       <c r="AT25" s="352" t="s">
@@ -9942,7 +9942,7 @@
       <c r="AZ25" s="328"/>
       <c r="BA25" s="328"/>
       <c r="BB25" s="328"/>
-      <c r="BC25" s="393" t="s">
+      <c r="BC25" s="395" t="s">
         <v>362</v>
       </c>
       <c r="BD25" s="352" t="s">
@@ -9960,7 +9960,7 @@
         <v>204</v>
       </c>
       <c r="BL25" s="328"/>
-      <c r="BM25" s="393" t="s">
+      <c r="BM25" s="395" t="s">
         <v>336</v>
       </c>
       <c r="BN25" s="346" t="s">
@@ -9978,35 +9978,35 @@
         <v>199</v>
       </c>
       <c r="BV25" s="328"/>
-      <c r="BW25" s="545" t="s">
+      <c r="BW25" s="401" t="s">
         <v>308</v>
       </c>
       <c r="BX25" s="348"/>
     </row>
     <row r="26" spans="1:76" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="515" t="s">
+      <c r="A26" s="470" t="s">
         <v>31</v>
       </c>
-      <c r="B26" s="516"/>
+      <c r="B26" s="471"/>
       <c r="C26" s="65"/>
       <c r="D26" s="65"/>
-      <c r="E26" s="536"/>
-      <c r="F26" s="534"/>
-      <c r="G26" s="535"/>
-      <c r="H26" s="478"/>
-      <c r="I26" s="480"/>
-      <c r="J26" s="478"/>
-      <c r="K26" s="480"/>
-      <c r="L26" s="479"/>
-      <c r="M26" s="479"/>
+      <c r="E26" s="446"/>
+      <c r="F26" s="447"/>
+      <c r="G26" s="448"/>
+      <c r="H26" s="433"/>
+      <c r="I26" s="434"/>
+      <c r="J26" s="433"/>
+      <c r="K26" s="434"/>
+      <c r="L26" s="435"/>
+      <c r="M26" s="435"/>
       <c r="N26" s="81"/>
-      <c r="O26" s="531"/>
-      <c r="P26" s="532"/>
-      <c r="Q26" s="532"/>
-      <c r="R26" s="532"/>
-      <c r="S26" s="532"/>
-      <c r="T26" s="532"/>
-      <c r="U26" s="533"/>
+      <c r="O26" s="484"/>
+      <c r="P26" s="485"/>
+      <c r="Q26" s="485"/>
+      <c r="R26" s="485"/>
+      <c r="S26" s="485"/>
+      <c r="T26" s="485"/>
+      <c r="U26" s="486"/>
       <c r="V26" s="104"/>
       <c r="Z26" s="93"/>
       <c r="AA26" s="101"/>
@@ -10021,7 +10021,7 @@
       <c r="AJ26" s="352"/>
       <c r="AK26" s="327"/>
       <c r="AL26" s="333" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="AM26" s="327"/>
       <c r="AN26" s="327"/>
@@ -10029,7 +10029,7 @@
       <c r="AP26" s="327"/>
       <c r="AQ26" s="327"/>
       <c r="AR26" s="327"/>
-      <c r="AS26" s="393"/>
+      <c r="AS26" s="395"/>
       <c r="AT26" s="352"/>
       <c r="AU26" s="327"/>
       <c r="AV26" s="327"/>
@@ -10039,7 +10039,7 @@
       <c r="AZ26" s="327"/>
       <c r="BA26" s="327"/>
       <c r="BB26" s="327"/>
-      <c r="BC26" s="393"/>
+      <c r="BC26" s="395"/>
       <c r="BD26" s="352"/>
       <c r="BE26" s="335" t="s">
         <v>201</v>
@@ -10063,7 +10063,7 @@
       <c r="BL26" s="359" t="s">
         <v>120</v>
       </c>
-      <c r="BM26" s="393"/>
+      <c r="BM26" s="395"/>
       <c r="BN26" s="346"/>
       <c r="BO26" s="359" t="s">
         <v>431</v>
@@ -10085,33 +10085,33 @@
         <v>64</v>
       </c>
       <c r="BV26" s="327"/>
-      <c r="BW26" s="545"/>
+      <c r="BW26" s="401"/>
       <c r="BX26" s="348"/>
     </row>
     <row r="27" spans="1:76" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="460"/>
-      <c r="B27" s="517"/>
+      <c r="A27" s="472"/>
+      <c r="B27" s="473"/>
       <c r="C27" s="65"/>
       <c r="D27" s="117"/>
       <c r="E27" s="118"/>
       <c r="F27" s="119"/>
       <c r="G27" s="119"/>
-      <c r="H27" s="478"/>
-      <c r="I27" s="480"/>
-      <c r="J27" s="478"/>
-      <c r="K27" s="480"/>
-      <c r="L27" s="479"/>
-      <c r="M27" s="479"/>
+      <c r="H27" s="433"/>
+      <c r="I27" s="434"/>
+      <c r="J27" s="433"/>
+      <c r="K27" s="434"/>
+      <c r="L27" s="435"/>
+      <c r="M27" s="435"/>
       <c r="N27" s="81"/>
-      <c r="O27" s="537" t="s">
+      <c r="O27" s="488" t="s">
         <v>32</v>
       </c>
-      <c r="P27" s="538"/>
-      <c r="Q27" s="538"/>
-      <c r="R27" s="538"/>
-      <c r="S27" s="538"/>
-      <c r="T27" s="538"/>
-      <c r="U27" s="539"/>
+      <c r="P27" s="489"/>
+      <c r="Q27" s="489"/>
+      <c r="R27" s="489"/>
+      <c r="S27" s="489"/>
+      <c r="T27" s="489"/>
+      <c r="U27" s="490"/>
       <c r="Z27" s="93"/>
       <c r="AA27" s="101"/>
       <c r="AB27" s="101"/>
@@ -10183,33 +10183,33 @@
         <v>70</v>
       </c>
       <c r="BV27" s="312"/>
-      <c r="BW27" s="484" t="s">
+      <c r="BW27" s="400" t="s">
         <v>309</v>
       </c>
       <c r="BX27" s="348"/>
     </row>
     <row r="28" spans="1:76" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="467"/>
-      <c r="B28" s="468"/>
-      <c r="E28" s="543" t="s">
+      <c r="A28" s="474"/>
+      <c r="B28" s="487"/>
+      <c r="E28" s="452" t="s">
         <v>33</v>
       </c>
-      <c r="F28" s="519"/>
-      <c r="G28" s="520"/>
-      <c r="H28" s="478"/>
-      <c r="I28" s="480"/>
-      <c r="J28" s="478"/>
-      <c r="K28" s="480"/>
-      <c r="L28" s="479"/>
-      <c r="M28" s="479"/>
+      <c r="F28" s="453"/>
+      <c r="G28" s="454"/>
+      <c r="H28" s="433"/>
+      <c r="I28" s="434"/>
+      <c r="J28" s="433"/>
+      <c r="K28" s="434"/>
+      <c r="L28" s="435"/>
+      <c r="M28" s="435"/>
       <c r="N28" s="81"/>
-      <c r="O28" s="540"/>
-      <c r="P28" s="541"/>
-      <c r="Q28" s="541"/>
-      <c r="R28" s="541"/>
-      <c r="S28" s="541"/>
-      <c r="T28" s="541"/>
-      <c r="U28" s="542"/>
+      <c r="O28" s="491"/>
+      <c r="P28" s="492"/>
+      <c r="Q28" s="492"/>
+      <c r="R28" s="492"/>
+      <c r="S28" s="492"/>
+      <c r="T28" s="492"/>
+      <c r="U28" s="493"/>
       <c r="V28" s="120"/>
       <c r="X28" s="92"/>
       <c r="Z28" s="93"/>
@@ -10224,7 +10224,7 @@
       <c r="AJ28" s="351"/>
       <c r="AK28" s="313"/>
       <c r="AL28" s="333" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="AM28" s="313"/>
       <c r="AN28" s="313"/>
@@ -10276,13 +10276,13 @@
       </c>
       <c r="BQ28" s="313"/>
       <c r="BR28" s="333" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="BS28" s="320" t="s">
         <v>66</v>
       </c>
       <c r="BT28" s="359" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="BU28" s="362" t="s">
         <v>210</v>
@@ -10290,29 +10290,29 @@
       <c r="BV28" s="362" t="s">
         <v>67</v>
       </c>
-      <c r="BW28" s="484"/>
+      <c r="BW28" s="400"/>
       <c r="BX28" s="348"/>
     </row>
     <row r="29" spans="1:76" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="90"/>
       <c r="B29" s="90"/>
-      <c r="E29" s="536"/>
-      <c r="F29" s="534"/>
-      <c r="G29" s="535"/>
-      <c r="H29" s="478"/>
-      <c r="I29" s="480"/>
-      <c r="J29" s="478"/>
-      <c r="K29" s="480"/>
-      <c r="L29" s="479"/>
-      <c r="M29" s="479"/>
+      <c r="E29" s="446"/>
+      <c r="F29" s="447"/>
+      <c r="G29" s="448"/>
+      <c r="H29" s="433"/>
+      <c r="I29" s="434"/>
+      <c r="J29" s="433"/>
+      <c r="K29" s="434"/>
+      <c r="L29" s="435"/>
+      <c r="M29" s="435"/>
       <c r="N29" s="81"/>
-      <c r="O29" s="540"/>
-      <c r="P29" s="541"/>
-      <c r="Q29" s="541"/>
-      <c r="R29" s="541"/>
-      <c r="S29" s="541"/>
-      <c r="T29" s="541"/>
-      <c r="U29" s="542"/>
+      <c r="O29" s="491"/>
+      <c r="P29" s="492"/>
+      <c r="Q29" s="492"/>
+      <c r="R29" s="492"/>
+      <c r="S29" s="492"/>
+      <c r="T29" s="492"/>
+      <c r="U29" s="493"/>
       <c r="V29" s="86"/>
       <c r="W29" s="121"/>
       <c r="X29" s="92"/>
@@ -10336,7 +10336,7 @@
       <c r="AP29" s="328"/>
       <c r="AQ29" s="328"/>
       <c r="AR29" s="328"/>
-      <c r="AS29" s="393" t="s">
+      <c r="AS29" s="395" t="s">
         <v>542</v>
       </c>
       <c r="AT29" s="352" t="s">
@@ -10350,7 +10350,7 @@
       <c r="AZ29" s="328"/>
       <c r="BA29" s="328"/>
       <c r="BB29" s="328"/>
-      <c r="BC29" s="393" t="s">
+      <c r="BC29" s="395" t="s">
         <v>364</v>
       </c>
       <c r="BD29" s="352" t="s">
@@ -10368,7 +10368,7 @@
       <c r="BJ29" s="328"/>
       <c r="BK29" s="328"/>
       <c r="BL29" s="328"/>
-      <c r="BM29" s="393" t="s">
+      <c r="BM29" s="395" t="s">
         <v>338</v>
       </c>
       <c r="BN29" s="346" t="s">
@@ -10382,7 +10382,7 @@
       <c r="BT29" s="328"/>
       <c r="BU29" s="328"/>
       <c r="BV29" s="328"/>
-      <c r="BW29" s="545" t="s">
+      <c r="BW29" s="401" t="s">
         <v>310</v>
       </c>
       <c r="BX29" s="348"/>
@@ -10390,23 +10390,23 @@
     <row r="30" spans="1:76" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="90"/>
       <c r="B30" s="90"/>
-      <c r="E30" s="536"/>
-      <c r="F30" s="534"/>
-      <c r="G30" s="535"/>
-      <c r="H30" s="478"/>
-      <c r="I30" s="480"/>
-      <c r="J30" s="478"/>
-      <c r="K30" s="480"/>
-      <c r="L30" s="479"/>
-      <c r="M30" s="479"/>
+      <c r="E30" s="446"/>
+      <c r="F30" s="447"/>
+      <c r="G30" s="448"/>
+      <c r="H30" s="433"/>
+      <c r="I30" s="434"/>
+      <c r="J30" s="433"/>
+      <c r="K30" s="434"/>
+      <c r="L30" s="435"/>
+      <c r="M30" s="435"/>
       <c r="N30" s="81"/>
-      <c r="O30" s="540"/>
-      <c r="P30" s="541"/>
-      <c r="Q30" s="541"/>
-      <c r="R30" s="541"/>
-      <c r="S30" s="541"/>
-      <c r="T30" s="541"/>
-      <c r="U30" s="542"/>
+      <c r="O30" s="491"/>
+      <c r="P30" s="492"/>
+      <c r="Q30" s="492"/>
+      <c r="R30" s="492"/>
+      <c r="S30" s="492"/>
+      <c r="T30" s="492"/>
+      <c r="U30" s="493"/>
       <c r="V30" s="99"/>
       <c r="X30" s="42"/>
       <c r="Y30" s="70"/>
@@ -10429,7 +10429,7 @@
       <c r="AP30" s="327"/>
       <c r="AQ30" s="327"/>
       <c r="AR30" s="327"/>
-      <c r="AS30" s="393"/>
+      <c r="AS30" s="395"/>
       <c r="AT30" s="352"/>
       <c r="AU30" s="327"/>
       <c r="AV30" s="327"/>
@@ -10439,13 +10439,13 @@
       <c r="AZ30" s="327"/>
       <c r="BA30" s="327"/>
       <c r="BB30" s="327"/>
-      <c r="BC30" s="393"/>
+      <c r="BC30" s="395"/>
       <c r="BD30" s="352"/>
       <c r="BE30" s="359" t="s">
         <v>425</v>
       </c>
       <c r="BF30" s="369" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="BG30" s="327"/>
       <c r="BH30" s="320" t="s">
@@ -10461,9 +10461,9 @@
         <v>585</v>
       </c>
       <c r="BL30" s="369" t="s">
-        <v>669</v>
-      </c>
-      <c r="BM30" s="393"/>
+        <v>668</v>
+      </c>
+      <c r="BM30" s="395"/>
       <c r="BN30" s="346"/>
       <c r="BO30" s="320" t="s">
         <v>68</v>
@@ -10473,7 +10473,7 @@
       </c>
       <c r="BQ30" s="327"/>
       <c r="BR30" s="333" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="BS30" s="320" t="s">
         <v>69</v>
@@ -10487,29 +10487,29 @@
       <c r="BV30" s="320" t="s">
         <v>214</v>
       </c>
-      <c r="BW30" s="545"/>
+      <c r="BW30" s="401"/>
       <c r="BX30" s="348"/>
     </row>
     <row r="31" spans="1:76" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="90"/>
       <c r="B31" s="90"/>
-      <c r="E31" s="536"/>
-      <c r="F31" s="534"/>
-      <c r="G31" s="535"/>
-      <c r="H31" s="478"/>
-      <c r="I31" s="480"/>
-      <c r="J31" s="478"/>
-      <c r="K31" s="480"/>
-      <c r="L31" s="479"/>
-      <c r="M31" s="479"/>
+      <c r="E31" s="446"/>
+      <c r="F31" s="447"/>
+      <c r="G31" s="448"/>
+      <c r="H31" s="433"/>
+      <c r="I31" s="434"/>
+      <c r="J31" s="433"/>
+      <c r="K31" s="434"/>
+      <c r="L31" s="435"/>
+      <c r="M31" s="435"/>
       <c r="N31" s="81"/>
-      <c r="O31" s="540"/>
-      <c r="P31" s="541"/>
-      <c r="Q31" s="541"/>
-      <c r="R31" s="541"/>
-      <c r="S31" s="541"/>
-      <c r="T31" s="541"/>
-      <c r="U31" s="542"/>
+      <c r="O31" s="491"/>
+      <c r="P31" s="492"/>
+      <c r="Q31" s="492"/>
+      <c r="R31" s="492"/>
+      <c r="S31" s="492"/>
+      <c r="T31" s="492"/>
+      <c r="U31" s="493"/>
       <c r="V31" s="123"/>
       <c r="Z31" s="93"/>
       <c r="AA31" s="124"/>
@@ -10581,7 +10581,7 @@
       <c r="BT31" s="312"/>
       <c r="BU31" s="312"/>
       <c r="BV31" s="312"/>
-      <c r="BW31" s="484" t="s">
+      <c r="BW31" s="400" t="s">
         <v>311</v>
       </c>
       <c r="BX31" s="348"/>
@@ -10589,23 +10589,23 @@
     <row r="32" spans="1:76" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="90"/>
       <c r="B32" s="90"/>
-      <c r="E32" s="544"/>
-      <c r="F32" s="521"/>
-      <c r="G32" s="522"/>
-      <c r="H32" s="478"/>
-      <c r="I32" s="480"/>
-      <c r="J32" s="478"/>
-      <c r="K32" s="480"/>
-      <c r="L32" s="479"/>
-      <c r="M32" s="479"/>
+      <c r="E32" s="449"/>
+      <c r="F32" s="450"/>
+      <c r="G32" s="451"/>
+      <c r="H32" s="433"/>
+      <c r="I32" s="434"/>
+      <c r="J32" s="433"/>
+      <c r="K32" s="434"/>
+      <c r="L32" s="435"/>
+      <c r="M32" s="435"/>
       <c r="N32" s="81"/>
-      <c r="O32" s="540"/>
-      <c r="P32" s="541"/>
-      <c r="Q32" s="541"/>
-      <c r="R32" s="541"/>
-      <c r="S32" s="541"/>
-      <c r="T32" s="541"/>
-      <c r="U32" s="542"/>
+      <c r="O32" s="491"/>
+      <c r="P32" s="492"/>
+      <c r="Q32" s="492"/>
+      <c r="R32" s="492"/>
+      <c r="S32" s="492"/>
+      <c r="T32" s="492"/>
+      <c r="U32" s="493"/>
       <c r="V32" s="123"/>
       <c r="Z32" s="93"/>
       <c r="AA32" s="124"/>
@@ -10669,7 +10669,7 @@
       </c>
       <c r="BQ32" s="313"/>
       <c r="BR32" s="333" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="BS32" s="320" t="s">
         <v>73</v>
@@ -10678,34 +10678,34 @@
         <v>74</v>
       </c>
       <c r="BU32" s="333" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="BV32" s="313"/>
-      <c r="BW32" s="484"/>
+      <c r="BW32" s="400"/>
       <c r="BX32" s="348"/>
     </row>
     <row r="33" spans="1:79" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="90"/>
       <c r="B33" s="90"/>
-      <c r="E33" s="536" t="s">
+      <c r="E33" s="446" t="s">
         <v>34</v>
       </c>
-      <c r="F33" s="534"/>
-      <c r="G33" s="535"/>
-      <c r="H33" s="478"/>
-      <c r="I33" s="480"/>
-      <c r="J33" s="478"/>
-      <c r="K33" s="480"/>
-      <c r="L33" s="479"/>
-      <c r="M33" s="479"/>
+      <c r="F33" s="447"/>
+      <c r="G33" s="448"/>
+      <c r="H33" s="433"/>
+      <c r="I33" s="434"/>
+      <c r="J33" s="433"/>
+      <c r="K33" s="434"/>
+      <c r="L33" s="435"/>
+      <c r="M33" s="435"/>
       <c r="N33" s="81"/>
-      <c r="O33" s="540"/>
-      <c r="P33" s="541"/>
-      <c r="Q33" s="541"/>
-      <c r="R33" s="541"/>
-      <c r="S33" s="541"/>
-      <c r="T33" s="541"/>
-      <c r="U33" s="542"/>
+      <c r="O33" s="491"/>
+      <c r="P33" s="492"/>
+      <c r="Q33" s="492"/>
+      <c r="R33" s="492"/>
+      <c r="S33" s="492"/>
+      <c r="T33" s="492"/>
+      <c r="U33" s="493"/>
       <c r="V33" s="123"/>
       <c r="W33" s="87"/>
       <c r="X33" s="42"/>
@@ -10729,7 +10729,7 @@
       <c r="AP33" s="328"/>
       <c r="AQ33" s="328"/>
       <c r="AR33" s="328"/>
-      <c r="AS33" s="393" t="s">
+      <c r="AS33" s="395" t="s">
         <v>544</v>
       </c>
       <c r="AT33" s="352" t="s">
@@ -10743,7 +10743,7 @@
       <c r="AZ33" s="328"/>
       <c r="BA33" s="328"/>
       <c r="BB33" s="328"/>
-      <c r="BC33" s="393" t="s">
+      <c r="BC33" s="395" t="s">
         <v>366</v>
       </c>
       <c r="BD33" s="352" t="s">
@@ -10760,7 +10760,7 @@
       <c r="BL33" s="360" t="s">
         <v>407</v>
       </c>
-      <c r="BM33" s="393" t="s">
+      <c r="BM33" s="395" t="s">
         <v>340</v>
       </c>
       <c r="BN33" s="346" t="s">
@@ -10774,7 +10774,7 @@
       <c r="BT33" s="328"/>
       <c r="BU33" s="328"/>
       <c r="BV33" s="328"/>
-      <c r="BW33" s="545" t="s">
+      <c r="BW33" s="401" t="s">
         <v>312</v>
       </c>
       <c r="BX33" s="348"/>
@@ -10782,23 +10782,23 @@
     <row r="34" spans="1:79" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="90"/>
       <c r="B34" s="90"/>
-      <c r="E34" s="536"/>
-      <c r="F34" s="534"/>
-      <c r="G34" s="535"/>
-      <c r="H34" s="478"/>
-      <c r="I34" s="480"/>
-      <c r="J34" s="478"/>
-      <c r="K34" s="480"/>
-      <c r="L34" s="479"/>
-      <c r="M34" s="479"/>
+      <c r="E34" s="446"/>
+      <c r="F34" s="447"/>
+      <c r="G34" s="448"/>
+      <c r="H34" s="433"/>
+      <c r="I34" s="434"/>
+      <c r="J34" s="433"/>
+      <c r="K34" s="434"/>
+      <c r="L34" s="435"/>
+      <c r="M34" s="435"/>
       <c r="N34" s="81"/>
-      <c r="O34" s="540"/>
-      <c r="P34" s="541"/>
-      <c r="Q34" s="541"/>
-      <c r="R34" s="541"/>
-      <c r="S34" s="541"/>
-      <c r="T34" s="541"/>
-      <c r="U34" s="542"/>
+      <c r="O34" s="491"/>
+      <c r="P34" s="492"/>
+      <c r="Q34" s="492"/>
+      <c r="R34" s="492"/>
+      <c r="S34" s="492"/>
+      <c r="T34" s="492"/>
+      <c r="U34" s="493"/>
       <c r="V34" s="127"/>
       <c r="W34" s="87"/>
       <c r="X34" s="42"/>
@@ -10817,7 +10817,7 @@
       <c r="AP34" s="327"/>
       <c r="AQ34" s="327"/>
       <c r="AR34" s="327"/>
-      <c r="AS34" s="393"/>
+      <c r="AS34" s="395"/>
       <c r="AT34" s="352"/>
       <c r="AU34" s="327"/>
       <c r="AV34" s="327"/>
@@ -10829,7 +10829,7 @@
       <c r="BB34" s="335" t="s">
         <v>493</v>
       </c>
-      <c r="BC34" s="393"/>
+      <c r="BC34" s="395"/>
       <c r="BD34" s="352"/>
       <c r="BE34" s="335" t="s">
         <v>448</v>
@@ -10853,7 +10853,7 @@
       <c r="BL34" s="359" t="s">
         <v>130</v>
       </c>
-      <c r="BM34" s="393"/>
+      <c r="BM34" s="395"/>
       <c r="BN34" s="346"/>
       <c r="BO34" s="320" t="s">
         <v>75</v>
@@ -10863,7 +10863,7 @@
       </c>
       <c r="BQ34" s="327"/>
       <c r="BR34" s="333" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="BS34" s="362" t="s">
         <v>220</v>
@@ -10877,29 +10877,29 @@
       <c r="BV34" s="362" t="s">
         <v>221</v>
       </c>
-      <c r="BW34" s="545"/>
+      <c r="BW34" s="401"/>
       <c r="BX34" s="348"/>
     </row>
     <row r="35" spans="1:79" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="90"/>
       <c r="B35" s="90"/>
-      <c r="E35" s="536"/>
-      <c r="F35" s="534"/>
-      <c r="G35" s="535"/>
-      <c r="H35" s="478"/>
-      <c r="I35" s="480"/>
-      <c r="J35" s="478"/>
-      <c r="K35" s="480"/>
-      <c r="L35" s="479"/>
-      <c r="M35" s="479"/>
+      <c r="E35" s="446"/>
+      <c r="F35" s="447"/>
+      <c r="G35" s="448"/>
+      <c r="H35" s="433"/>
+      <c r="I35" s="434"/>
+      <c r="J35" s="433"/>
+      <c r="K35" s="434"/>
+      <c r="L35" s="435"/>
+      <c r="M35" s="435"/>
       <c r="N35" s="81"/>
-      <c r="O35" s="540"/>
-      <c r="P35" s="541"/>
-      <c r="Q35" s="541"/>
-      <c r="R35" s="541"/>
-      <c r="S35" s="541"/>
-      <c r="T35" s="541"/>
-      <c r="U35" s="542"/>
+      <c r="O35" s="491"/>
+      <c r="P35" s="492"/>
+      <c r="Q35" s="492"/>
+      <c r="R35" s="492"/>
+      <c r="S35" s="492"/>
+      <c r="T35" s="492"/>
+      <c r="U35" s="493"/>
       <c r="V35" s="127"/>
       <c r="W35" s="87"/>
       <c r="X35" s="42"/>
@@ -10965,7 +10965,7 @@
       <c r="BT35" s="312"/>
       <c r="BU35" s="312"/>
       <c r="BV35" s="312"/>
-      <c r="BW35" s="484" t="s">
+      <c r="BW35" s="400" t="s">
         <v>313</v>
       </c>
       <c r="BX35" s="348"/>
@@ -10973,23 +10973,23 @@
     <row r="36" spans="1:79" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="42"/>
       <c r="B36" s="97"/>
-      <c r="E36" s="536"/>
-      <c r="F36" s="534"/>
-      <c r="G36" s="535"/>
-      <c r="H36" s="478"/>
-      <c r="I36" s="480"/>
-      <c r="J36" s="478"/>
-      <c r="K36" s="480"/>
-      <c r="L36" s="479"/>
-      <c r="M36" s="479"/>
+      <c r="E36" s="446"/>
+      <c r="F36" s="447"/>
+      <c r="G36" s="448"/>
+      <c r="H36" s="433"/>
+      <c r="I36" s="434"/>
+      <c r="J36" s="433"/>
+      <c r="K36" s="434"/>
+      <c r="L36" s="435"/>
+      <c r="M36" s="435"/>
       <c r="N36" s="81"/>
-      <c r="O36" s="540"/>
-      <c r="P36" s="541"/>
-      <c r="Q36" s="541"/>
-      <c r="R36" s="541"/>
-      <c r="S36" s="541"/>
-      <c r="T36" s="541"/>
-      <c r="U36" s="542"/>
+      <c r="O36" s="491"/>
+      <c r="P36" s="492"/>
+      <c r="Q36" s="492"/>
+      <c r="R36" s="492"/>
+      <c r="S36" s="492"/>
+      <c r="T36" s="492"/>
+      <c r="U36" s="493"/>
       <c r="V36" s="127"/>
       <c r="W36" s="86"/>
       <c r="X36" s="86"/>
@@ -11071,7 +11071,7 @@
       <c r="BV36" s="362" t="s">
         <v>80</v>
       </c>
-      <c r="BW36" s="484"/>
+      <c r="BW36" s="400"/>
       <c r="BX36" s="348"/>
       <c r="CA36" s="6" t="s">
         <v>14</v>
@@ -11080,23 +11080,23 @@
     <row r="37" spans="1:79" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="42"/>
       <c r="B37" s="97"/>
-      <c r="E37" s="536"/>
-      <c r="F37" s="534"/>
-      <c r="G37" s="535"/>
-      <c r="H37" s="478"/>
-      <c r="I37" s="480"/>
-      <c r="J37" s="478"/>
-      <c r="K37" s="480"/>
-      <c r="L37" s="479"/>
-      <c r="M37" s="479"/>
+      <c r="E37" s="446"/>
+      <c r="F37" s="447"/>
+      <c r="G37" s="448"/>
+      <c r="H37" s="433"/>
+      <c r="I37" s="434"/>
+      <c r="J37" s="433"/>
+      <c r="K37" s="434"/>
+      <c r="L37" s="435"/>
+      <c r="M37" s="435"/>
       <c r="N37" s="81"/>
-      <c r="O37" s="540"/>
-      <c r="P37" s="541"/>
-      <c r="Q37" s="541"/>
-      <c r="R37" s="541"/>
-      <c r="S37" s="541"/>
-      <c r="T37" s="541"/>
-      <c r="U37" s="542"/>
+      <c r="O37" s="491"/>
+      <c r="P37" s="492"/>
+      <c r="Q37" s="492"/>
+      <c r="R37" s="492"/>
+      <c r="S37" s="492"/>
+      <c r="T37" s="492"/>
+      <c r="U37" s="493"/>
       <c r="V37" s="97"/>
       <c r="W37" s="86"/>
       <c r="X37" s="86"/>
@@ -11139,30 +11139,30 @@
         <v>368</v>
       </c>
       <c r="BD37" s="353"/>
-      <c r="BE37" s="590" t="s">
+      <c r="BE37" s="396" t="s">
         <v>57</v>
       </c>
-      <c r="BF37" s="591"/>
-      <c r="BG37" s="591"/>
-      <c r="BH37" s="591"/>
-      <c r="BI37" s="591"/>
-      <c r="BJ37" s="591"/>
-      <c r="BK37" s="591"/>
-      <c r="BL37" s="592"/>
+      <c r="BF37" s="397"/>
+      <c r="BG37" s="397"/>
+      <c r="BH37" s="397"/>
+      <c r="BI37" s="397"/>
+      <c r="BJ37" s="397"/>
+      <c r="BK37" s="397"/>
+      <c r="BL37" s="398"/>
       <c r="BM37" s="332" t="s">
         <v>342</v>
       </c>
       <c r="BN37" s="347"/>
-      <c r="BO37" s="590" t="s">
+      <c r="BO37" s="396" t="s">
         <v>58</v>
       </c>
-      <c r="BP37" s="591"/>
-      <c r="BQ37" s="591"/>
-      <c r="BR37" s="591"/>
-      <c r="BS37" s="591"/>
-      <c r="BT37" s="591"/>
-      <c r="BU37" s="591"/>
-      <c r="BV37" s="592"/>
+      <c r="BP37" s="397"/>
+      <c r="BQ37" s="397"/>
+      <c r="BR37" s="397"/>
+      <c r="BS37" s="397"/>
+      <c r="BT37" s="397"/>
+      <c r="BU37" s="397"/>
+      <c r="BV37" s="398"/>
       <c r="BW37" s="343" t="s">
         <v>314</v>
       </c>
@@ -11171,23 +11171,23 @@
     <row r="38" spans="1:79" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="42"/>
       <c r="B38" s="97"/>
-      <c r="E38" s="544"/>
-      <c r="F38" s="521"/>
-      <c r="G38" s="522"/>
-      <c r="H38" s="478"/>
-      <c r="I38" s="480"/>
-      <c r="J38" s="478"/>
-      <c r="K38" s="480"/>
-      <c r="L38" s="479"/>
-      <c r="M38" s="479"/>
+      <c r="E38" s="449"/>
+      <c r="F38" s="450"/>
+      <c r="G38" s="451"/>
+      <c r="H38" s="433"/>
+      <c r="I38" s="434"/>
+      <c r="J38" s="433"/>
+      <c r="K38" s="434"/>
+      <c r="L38" s="435"/>
+      <c r="M38" s="435"/>
       <c r="N38" s="81"/>
-      <c r="O38" s="540"/>
-      <c r="P38" s="541"/>
-      <c r="Q38" s="541"/>
-      <c r="R38" s="541"/>
-      <c r="S38" s="541"/>
-      <c r="T38" s="541"/>
-      <c r="U38" s="542"/>
+      <c r="O38" s="491"/>
+      <c r="P38" s="492"/>
+      <c r="Q38" s="492"/>
+      <c r="R38" s="492"/>
+      <c r="S38" s="492"/>
+      <c r="T38" s="492"/>
+      <c r="U38" s="493"/>
       <c r="V38" s="97"/>
       <c r="W38" s="86"/>
       <c r="X38" s="86"/>
@@ -11259,7 +11259,7 @@
       <c r="BT38" s="312"/>
       <c r="BU38" s="312"/>
       <c r="BV38" s="312"/>
-      <c r="BW38" s="484" t="s">
+      <c r="BW38" s="400" t="s">
         <v>315</v>
       </c>
       <c r="BX38" s="348"/>
@@ -11267,25 +11267,25 @@
     <row r="39" spans="1:79" ht="279.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="42"/>
       <c r="B39" s="97"/>
-      <c r="E39" s="543" t="s">
+      <c r="E39" s="452" t="s">
         <v>35</v>
       </c>
-      <c r="F39" s="519"/>
-      <c r="G39" s="520"/>
-      <c r="H39" s="478"/>
-      <c r="I39" s="480"/>
-      <c r="J39" s="478"/>
-      <c r="K39" s="480"/>
-      <c r="L39" s="479"/>
-      <c r="M39" s="479"/>
+      <c r="F39" s="453"/>
+      <c r="G39" s="454"/>
+      <c r="H39" s="433"/>
+      <c r="I39" s="434"/>
+      <c r="J39" s="433"/>
+      <c r="K39" s="434"/>
+      <c r="L39" s="435"/>
+      <c r="M39" s="435"/>
       <c r="N39" s="133"/>
-      <c r="O39" s="540"/>
-      <c r="P39" s="541"/>
-      <c r="Q39" s="541"/>
-      <c r="R39" s="541"/>
-      <c r="S39" s="541"/>
-      <c r="T39" s="541"/>
-      <c r="U39" s="542"/>
+      <c r="O39" s="491"/>
+      <c r="P39" s="492"/>
+      <c r="Q39" s="492"/>
+      <c r="R39" s="492"/>
+      <c r="S39" s="492"/>
+      <c r="T39" s="492"/>
+      <c r="U39" s="493"/>
       <c r="V39" s="97"/>
       <c r="W39" s="86"/>
       <c r="X39" s="86"/>
@@ -11313,14 +11313,14 @@
       <c r="AT39" s="351"/>
       <c r="AU39" s="313"/>
       <c r="AV39" s="335" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="AW39" s="313"/>
       <c r="AX39" s="313"/>
       <c r="AY39" s="313"/>
       <c r="AZ39" s="313"/>
       <c r="BA39" s="335" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="BB39" s="313"/>
       <c r="BC39" s="394"/>
@@ -11357,13 +11357,13 @@
       </c>
       <c r="BQ39" s="313"/>
       <c r="BR39" s="368" t="s">
+        <v>648</v>
+      </c>
+      <c r="BS39" s="335" t="s">
         <v>649</v>
       </c>
-      <c r="BS39" s="335" t="s">
+      <c r="BT39" s="368" t="s">
         <v>650</v>
-      </c>
-      <c r="BT39" s="368" t="s">
-        <v>651</v>
       </c>
       <c r="BU39" s="320" t="s">
         <v>82</v>
@@ -11371,29 +11371,29 @@
       <c r="BV39" s="320" t="s">
         <v>232</v>
       </c>
-      <c r="BW39" s="484"/>
+      <c r="BW39" s="400"/>
       <c r="BX39" s="348"/>
     </row>
     <row r="40" spans="1:79" ht="279.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A40" s="42"/>
       <c r="B40" s="97"/>
-      <c r="E40" s="536"/>
-      <c r="F40" s="534"/>
-      <c r="G40" s="535"/>
-      <c r="H40" s="478"/>
-      <c r="I40" s="480"/>
-      <c r="J40" s="478"/>
-      <c r="K40" s="480"/>
-      <c r="L40" s="479"/>
-      <c r="M40" s="479"/>
+      <c r="E40" s="446"/>
+      <c r="F40" s="447"/>
+      <c r="G40" s="448"/>
+      <c r="H40" s="433"/>
+      <c r="I40" s="434"/>
+      <c r="J40" s="433"/>
+      <c r="K40" s="434"/>
+      <c r="L40" s="435"/>
+      <c r="M40" s="435"/>
       <c r="N40" s="81"/>
-      <c r="O40" s="540"/>
-      <c r="P40" s="541"/>
-      <c r="Q40" s="541"/>
-      <c r="R40" s="541"/>
-      <c r="S40" s="541"/>
-      <c r="T40" s="541"/>
-      <c r="U40" s="542"/>
+      <c r="O40" s="491"/>
+      <c r="P40" s="492"/>
+      <c r="Q40" s="492"/>
+      <c r="R40" s="492"/>
+      <c r="S40" s="492"/>
+      <c r="T40" s="492"/>
+      <c r="U40" s="493"/>
       <c r="W40" s="86"/>
       <c r="X40" s="86"/>
       <c r="Y40" s="132"/>
@@ -11414,7 +11414,7 @@
       <c r="AP40" s="328"/>
       <c r="AQ40" s="328"/>
       <c r="AR40" s="328"/>
-      <c r="AS40" s="393" t="s">
+      <c r="AS40" s="395" t="s">
         <v>556</v>
       </c>
       <c r="AT40" s="352" t="s">
@@ -11428,7 +11428,7 @@
       <c r="AZ40" s="328"/>
       <c r="BA40" s="328"/>
       <c r="BB40" s="328"/>
-      <c r="BC40" s="393" t="s">
+      <c r="BC40" s="395" t="s">
         <v>370</v>
       </c>
       <c r="BD40" s="352" t="s">
@@ -11444,7 +11444,7 @@
       <c r="BJ40" s="328"/>
       <c r="BK40" s="328"/>
       <c r="BL40" s="328"/>
-      <c r="BM40" s="393" t="s">
+      <c r="BM40" s="395" t="s">
         <v>344</v>
       </c>
       <c r="BN40" s="346" t="s">
@@ -11460,7 +11460,7 @@
       <c r="BT40" s="328"/>
       <c r="BU40" s="328"/>
       <c r="BV40" s="328"/>
-      <c r="BW40" s="545" t="s">
+      <c r="BW40" s="401" t="s">
         <v>316</v>
       </c>
       <c r="BX40" s="348"/>
@@ -11468,23 +11468,23 @@
     <row r="41" spans="1:79" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="42"/>
       <c r="B41" s="97"/>
-      <c r="E41" s="544"/>
-      <c r="F41" s="521"/>
-      <c r="G41" s="522"/>
-      <c r="H41" s="478"/>
-      <c r="I41" s="480"/>
-      <c r="J41" s="478"/>
-      <c r="K41" s="480"/>
-      <c r="L41" s="479"/>
-      <c r="M41" s="479"/>
+      <c r="E41" s="449"/>
+      <c r="F41" s="450"/>
+      <c r="G41" s="451"/>
+      <c r="H41" s="433"/>
+      <c r="I41" s="434"/>
+      <c r="J41" s="433"/>
+      <c r="K41" s="434"/>
+      <c r="L41" s="435"/>
+      <c r="M41" s="435"/>
       <c r="N41" s="81"/>
-      <c r="O41" s="540"/>
-      <c r="P41" s="541"/>
-      <c r="Q41" s="541"/>
-      <c r="R41" s="541"/>
-      <c r="S41" s="541"/>
-      <c r="T41" s="541"/>
-      <c r="U41" s="542"/>
+      <c r="O41" s="491"/>
+      <c r="P41" s="492"/>
+      <c r="Q41" s="492"/>
+      <c r="R41" s="492"/>
+      <c r="S41" s="492"/>
+      <c r="T41" s="492"/>
+      <c r="U41" s="493"/>
       <c r="W41" s="86"/>
       <c r="X41" s="86"/>
       <c r="Z41" s="135"/>
@@ -11501,7 +11501,7 @@
       <c r="AP41" s="327"/>
       <c r="AQ41" s="327"/>
       <c r="AR41" s="327"/>
-      <c r="AS41" s="393"/>
+      <c r="AS41" s="395"/>
       <c r="AT41" s="352"/>
       <c r="AU41" s="333" t="s">
         <v>494</v>
@@ -11525,7 +11525,7 @@
       <c r="BB41" s="361" t="s">
         <v>458</v>
       </c>
-      <c r="BC41" s="393"/>
+      <c r="BC41" s="395"/>
       <c r="BD41" s="352"/>
       <c r="BE41" s="359" t="s">
         <v>465</v>
@@ -11549,7 +11549,7 @@
       <c r="BL41" s="335" t="s">
         <v>233</v>
       </c>
-      <c r="BM41" s="393"/>
+      <c r="BM41" s="395"/>
       <c r="BN41" s="346"/>
       <c r="BO41" s="320" t="s">
         <v>574</v>
@@ -11559,7 +11559,7 @@
       </c>
       <c r="BQ41" s="327"/>
       <c r="BR41" s="368" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="BS41" s="359" t="s">
         <v>230</v>
@@ -11568,36 +11568,36 @@
         <v>590</v>
       </c>
       <c r="BU41" s="335" t="s">
+        <v>651</v>
+      </c>
+      <c r="BV41" s="368" t="s">
         <v>652</v>
       </c>
-      <c r="BV41" s="368" t="s">
-        <v>653</v>
-      </c>
-      <c r="BW41" s="545"/>
+      <c r="BW41" s="401"/>
       <c r="BX41" s="348"/>
     </row>
     <row r="42" spans="1:79" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="42"/>
       <c r="B42" s="97"/>
-      <c r="E42" s="543" t="s">
+      <c r="E42" s="452" t="s">
         <v>36</v>
       </c>
-      <c r="F42" s="519"/>
-      <c r="G42" s="520"/>
-      <c r="H42" s="478"/>
-      <c r="I42" s="480"/>
-      <c r="J42" s="478"/>
-      <c r="K42" s="480"/>
-      <c r="L42" s="479"/>
-      <c r="M42" s="479"/>
+      <c r="F42" s="453"/>
+      <c r="G42" s="454"/>
+      <c r="H42" s="433"/>
+      <c r="I42" s="434"/>
+      <c r="J42" s="433"/>
+      <c r="K42" s="434"/>
+      <c r="L42" s="435"/>
+      <c r="M42" s="435"/>
       <c r="N42" s="81"/>
-      <c r="O42" s="540"/>
-      <c r="P42" s="541"/>
-      <c r="Q42" s="541"/>
-      <c r="R42" s="541"/>
-      <c r="S42" s="541"/>
-      <c r="T42" s="541"/>
-      <c r="U42" s="542"/>
+      <c r="O42" s="491"/>
+      <c r="P42" s="492"/>
+      <c r="Q42" s="492"/>
+      <c r="R42" s="492"/>
+      <c r="S42" s="492"/>
+      <c r="T42" s="492"/>
+      <c r="U42" s="493"/>
       <c r="V42" s="92"/>
       <c r="W42" s="86"/>
       <c r="X42" s="86"/>
@@ -11665,7 +11665,7 @@
       <c r="BT42" s="312"/>
       <c r="BU42" s="312"/>
       <c r="BV42" s="312"/>
-      <c r="BW42" s="484" t="s">
+      <c r="BW42" s="400" t="s">
         <v>317</v>
       </c>
       <c r="BX42" s="348"/>
@@ -11675,23 +11675,23 @@
       <c r="B43" s="97"/>
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
-      <c r="E43" s="544"/>
-      <c r="F43" s="521"/>
-      <c r="G43" s="522"/>
-      <c r="H43" s="478"/>
-      <c r="I43" s="480"/>
-      <c r="J43" s="478"/>
-      <c r="K43" s="480"/>
-      <c r="L43" s="479"/>
-      <c r="M43" s="479"/>
+      <c r="E43" s="449"/>
+      <c r="F43" s="450"/>
+      <c r="G43" s="451"/>
+      <c r="H43" s="433"/>
+      <c r="I43" s="434"/>
+      <c r="J43" s="433"/>
+      <c r="K43" s="434"/>
+      <c r="L43" s="435"/>
+      <c r="M43" s="435"/>
       <c r="N43" s="81"/>
-      <c r="O43" s="540"/>
-      <c r="P43" s="541"/>
-      <c r="Q43" s="541"/>
-      <c r="R43" s="541"/>
-      <c r="S43" s="541"/>
-      <c r="T43" s="541"/>
-      <c r="U43" s="542"/>
+      <c r="O43" s="491"/>
+      <c r="P43" s="492"/>
+      <c r="Q43" s="492"/>
+      <c r="R43" s="492"/>
+      <c r="S43" s="492"/>
+      <c r="T43" s="492"/>
+      <c r="U43" s="493"/>
       <c r="V43" s="138"/>
       <c r="W43" s="86"/>
       <c r="X43" s="86"/>
@@ -11773,7 +11773,7 @@
       </c>
       <c r="BQ43" s="313"/>
       <c r="BR43" s="368" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="BS43" s="384" t="s">
         <v>591</v>
@@ -11787,7 +11787,7 @@
       <c r="BV43" s="368" t="s">
         <v>592</v>
       </c>
-      <c r="BW43" s="484"/>
+      <c r="BW43" s="400"/>
       <c r="BX43" s="349"/>
     </row>
     <row r="44" spans="1:79" s="143" customFormat="1" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -11795,25 +11795,25 @@
       <c r="B44" s="90"/>
       <c r="C44" s="6"/>
       <c r="D44" s="6"/>
-      <c r="E44" s="544" t="s">
+      <c r="E44" s="449" t="s">
         <v>37</v>
       </c>
-      <c r="F44" s="521"/>
-      <c r="G44" s="522"/>
-      <c r="H44" s="481"/>
-      <c r="I44" s="483"/>
-      <c r="J44" s="481"/>
-      <c r="K44" s="483"/>
-      <c r="L44" s="482"/>
-      <c r="M44" s="482"/>
+      <c r="F44" s="450"/>
+      <c r="G44" s="451"/>
+      <c r="H44" s="436"/>
+      <c r="I44" s="437"/>
+      <c r="J44" s="436"/>
+      <c r="K44" s="437"/>
+      <c r="L44" s="439"/>
+      <c r="M44" s="439"/>
       <c r="N44" s="81"/>
-      <c r="O44" s="540"/>
-      <c r="P44" s="541"/>
-      <c r="Q44" s="541"/>
-      <c r="R44" s="541"/>
-      <c r="S44" s="541"/>
-      <c r="T44" s="541"/>
-      <c r="U44" s="542"/>
+      <c r="O44" s="491"/>
+      <c r="P44" s="492"/>
+      <c r="Q44" s="492"/>
+      <c r="R44" s="492"/>
+      <c r="S44" s="492"/>
+      <c r="T44" s="492"/>
+      <c r="U44" s="493"/>
       <c r="V44" s="42"/>
       <c r="W44" s="6"/>
       <c r="X44" s="139"/>
@@ -11839,7 +11839,7 @@
       <c r="AP44" s="328"/>
       <c r="AQ44" s="328"/>
       <c r="AR44" s="328"/>
-      <c r="AS44" s="393" t="s">
+      <c r="AS44" s="395" t="s">
         <v>558</v>
       </c>
       <c r="AT44" s="352" t="s">
@@ -11853,7 +11853,7 @@
       <c r="AZ44" s="328"/>
       <c r="BA44" s="328"/>
       <c r="BB44" s="328"/>
-      <c r="BC44" s="393" t="s">
+      <c r="BC44" s="395" t="s">
         <v>372</v>
       </c>
       <c r="BD44" s="352" t="s">
@@ -11867,7 +11867,7 @@
       <c r="BJ44" s="328"/>
       <c r="BK44" s="328"/>
       <c r="BL44" s="328"/>
-      <c r="BM44" s="393" t="s">
+      <c r="BM44" s="395" t="s">
         <v>346</v>
       </c>
       <c r="BN44" s="346" t="s">
@@ -11881,7 +11881,7 @@
       <c r="BT44" s="328"/>
       <c r="BU44" s="328"/>
       <c r="BV44" s="328"/>
-      <c r="BW44" s="545" t="s">
+      <c r="BW44" s="401" t="s">
         <v>318</v>
       </c>
       <c r="BX44" s="349"/>
@@ -11889,38 +11889,38 @@
     <row r="45" spans="1:79" s="143" customFormat="1" ht="279.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="42"/>
       <c r="B45" s="90"/>
-      <c r="E45" s="493" t="s">
+      <c r="E45" s="494" t="s">
         <v>38</v>
       </c>
-      <c r="F45" s="493"/>
-      <c r="G45" s="493"/>
-      <c r="H45" s="493"/>
-      <c r="I45" s="493"/>
-      <c r="J45" s="493"/>
-      <c r="K45" s="493"/>
-      <c r="L45" s="493"/>
-      <c r="M45" s="493"/>
+      <c r="F45" s="494"/>
+      <c r="G45" s="494"/>
+      <c r="H45" s="494"/>
+      <c r="I45" s="494"/>
+      <c r="J45" s="494"/>
+      <c r="K45" s="494"/>
+      <c r="L45" s="494"/>
+      <c r="M45" s="494"/>
       <c r="N45" s="145"/>
-      <c r="O45" s="494" t="s">
+      <c r="O45" s="495" t="s">
         <v>38</v>
       </c>
-      <c r="P45" s="495"/>
-      <c r="Q45" s="495"/>
-      <c r="R45" s="495"/>
-      <c r="S45" s="495"/>
-      <c r="T45" s="495"/>
-      <c r="U45" s="495"/>
+      <c r="P45" s="496"/>
+      <c r="Q45" s="496"/>
+      <c r="R45" s="496"/>
+      <c r="S45" s="496"/>
+      <c r="T45" s="496"/>
+      <c r="U45" s="496"/>
       <c r="V45" s="146"/>
       <c r="W45" s="147"/>
       <c r="X45" s="147"/>
       <c r="Y45" s="147"/>
       <c r="Z45" s="148"/>
-      <c r="AA45" s="496"/>
-      <c r="AB45" s="497"/>
-      <c r="AC45" s="497"/>
-      <c r="AD45" s="498"/>
-      <c r="AE45" s="498"/>
-      <c r="AF45" s="498"/>
+      <c r="AA45" s="497"/>
+      <c r="AB45" s="498"/>
+      <c r="AC45" s="498"/>
+      <c r="AD45" s="499"/>
+      <c r="AE45" s="499"/>
+      <c r="AF45" s="499"/>
       <c r="AG45" s="149"/>
       <c r="AH45" s="149"/>
       <c r="AI45" s="150"/>
@@ -11933,7 +11933,7 @@
       <c r="AP45" s="327"/>
       <c r="AQ45" s="327"/>
       <c r="AR45" s="327"/>
-      <c r="AS45" s="393"/>
+      <c r="AS45" s="395"/>
       <c r="AT45" s="352"/>
       <c r="AU45" s="333" t="s">
         <v>506</v>
@@ -11957,7 +11957,7 @@
       <c r="BB45" s="333" t="s">
         <v>512</v>
       </c>
-      <c r="BC45" s="393"/>
+      <c r="BC45" s="395"/>
       <c r="BD45" s="352"/>
       <c r="BE45" s="335" t="s">
         <v>238</v>
@@ -11981,7 +11981,7 @@
       <c r="BL45" s="335" t="s">
         <v>147</v>
       </c>
-      <c r="BM45" s="393"/>
+      <c r="BM45" s="395"/>
       <c r="BN45" s="346"/>
       <c r="BO45" s="335" t="s">
         <v>474</v>
@@ -11991,7 +11991,7 @@
       </c>
       <c r="BQ45" s="327"/>
       <c r="BR45" s="335" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="BS45" s="359" t="s">
         <v>237</v>
@@ -12003,7 +12003,7 @@
         <v>593</v>
       </c>
       <c r="BV45" s="375"/>
-      <c r="BW45" s="545"/>
+      <c r="BW45" s="401"/>
       <c r="BX45" s="349"/>
     </row>
     <row r="46" spans="1:79" s="143" customFormat="1" ht="279.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
@@ -12026,7 +12026,7 @@
       </c>
       <c r="M46" s="72"/>
       <c r="N46" s="154"/>
-      <c r="O46" s="499"/>
+      <c r="O46" s="500"/>
       <c r="P46" s="53"/>
       <c r="Q46" s="53"/>
       <c r="R46" s="53"/>
@@ -12104,7 +12104,7 @@
       <c r="BV46" s="371" t="s">
         <v>403</v>
       </c>
-      <c r="BW46" s="484" t="s">
+      <c r="BW46" s="400" t="s">
         <v>319</v>
       </c>
       <c r="BX46" s="349"/>
@@ -12123,7 +12123,7 @@
       <c r="L47" s="79"/>
       <c r="M47" s="79"/>
       <c r="N47" s="154"/>
-      <c r="O47" s="395"/>
+      <c r="O47" s="501"/>
       <c r="P47" s="53"/>
       <c r="Q47" s="53"/>
       <c r="R47" s="53"/>
@@ -12207,7 +12207,7 @@
       </c>
       <c r="BQ47" s="313"/>
       <c r="BR47" s="335" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="BS47" s="335" t="s">
         <v>473</v>
@@ -12221,7 +12221,7 @@
       <c r="BV47" s="359" t="s">
         <v>290</v>
       </c>
-      <c r="BW47" s="484"/>
+      <c r="BW47" s="400"/>
       <c r="BX47" s="349"/>
     </row>
     <row r="48" spans="1:79" s="143" customFormat="1" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -12268,7 +12268,7 @@
       <c r="AP48" s="328"/>
       <c r="AQ48" s="328"/>
       <c r="AR48" s="328"/>
-      <c r="AS48" s="393" t="s">
+      <c r="AS48" s="395" t="s">
         <v>560</v>
       </c>
       <c r="AT48" s="352" t="s">
@@ -12282,7 +12282,7 @@
       <c r="AZ48" s="328"/>
       <c r="BA48" s="328"/>
       <c r="BB48" s="328"/>
-      <c r="BC48" s="393" t="s">
+      <c r="BC48" s="395" t="s">
         <v>374</v>
       </c>
       <c r="BD48" s="352" t="s">
@@ -12298,7 +12298,7 @@
       </c>
       <c r="BK48" s="328"/>
       <c r="BL48" s="328"/>
-      <c r="BM48" s="393" t="s">
+      <c r="BM48" s="395" t="s">
         <v>348</v>
       </c>
       <c r="BN48" s="346" t="s">
@@ -12318,7 +12318,7 @@
       <c r="BV48" s="321" t="s">
         <v>244</v>
       </c>
-      <c r="BW48" s="545" t="s">
+      <c r="BW48" s="401" t="s">
         <v>320</v>
       </c>
       <c r="BX48" s="349"/>
@@ -12364,7 +12364,7 @@
       <c r="AP49" s="327"/>
       <c r="AQ49" s="327"/>
       <c r="AR49" s="327"/>
-      <c r="AS49" s="393"/>
+      <c r="AS49" s="395"/>
       <c r="AT49" s="352"/>
       <c r="AU49" s="361" t="s">
         <v>518</v>
@@ -12383,10 +12383,10 @@
         <v>522</v>
       </c>
       <c r="BA49" s="361" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="BB49" s="327"/>
-      <c r="BC49" s="393"/>
+      <c r="BC49" s="395"/>
       <c r="BD49" s="352"/>
       <c r="BE49" s="335" t="s">
         <v>478</v>
@@ -12410,7 +12410,7 @@
       <c r="BL49" s="359" t="s">
         <v>451</v>
       </c>
-      <c r="BM49" s="393"/>
+      <c r="BM49" s="395"/>
       <c r="BN49" s="346"/>
       <c r="BO49" s="335" t="s">
         <v>479</v>
@@ -12434,7 +12434,7 @@
       <c r="BV49" s="320" t="s">
         <v>288</v>
       </c>
-      <c r="BW49" s="545"/>
+      <c r="BW49" s="401"/>
       <c r="BX49" s="349"/>
     </row>
     <row r="50" spans="1:86" s="143" customFormat="1" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -12450,8 +12450,8 @@
       <c r="L50" s="79"/>
       <c r="M50" s="79"/>
       <c r="N50" s="154"/>
-      <c r="O50" s="492"/>
-      <c r="P50" s="395"/>
+      <c r="O50" s="511"/>
+      <c r="P50" s="501"/>
       <c r="Q50" s="172"/>
       <c r="R50" s="172"/>
       <c r="S50" s="172"/>
@@ -12528,7 +12528,7 @@
       <c r="BV50" s="321" t="s">
         <v>101</v>
       </c>
-      <c r="BW50" s="484" t="s">
+      <c r="BW50" s="400" t="s">
         <v>321</v>
       </c>
       <c r="BX50" s="349"/>
@@ -12546,8 +12546,8 @@
       <c r="L51" s="79"/>
       <c r="M51" s="79"/>
       <c r="N51" s="154"/>
-      <c r="O51" s="492"/>
-      <c r="P51" s="395"/>
+      <c r="O51" s="511"/>
+      <c r="P51" s="501"/>
       <c r="Q51" s="172"/>
       <c r="R51" s="172"/>
       <c r="S51" s="172"/>
@@ -12580,12 +12580,12 @@
       <c r="AV51" s="361" t="s">
         <v>603</v>
       </c>
-      <c r="AW51" s="361" t="s">
-        <v>604</v>
+      <c r="AW51" s="368" t="s">
+        <v>675</v>
       </c>
       <c r="AX51" s="313"/>
       <c r="AY51" s="361" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="AZ51" s="361" t="s">
         <v>523</v>
@@ -12606,7 +12606,7 @@
       </c>
       <c r="BG51" s="313"/>
       <c r="BH51" s="369" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="BI51" s="320" t="s">
         <v>236</v>
@@ -12644,17 +12644,17 @@
       <c r="BV51" s="320" t="s">
         <v>93</v>
       </c>
-      <c r="BW51" s="484"/>
+      <c r="BW51" s="400"/>
       <c r="BX51" s="349"/>
     </row>
     <row r="52" spans="1:86" s="143" customFormat="1" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="151"/>
       <c r="B52" s="151"/>
-      <c r="E52" s="500" t="s">
+      <c r="E52" s="502" t="s">
         <v>42</v>
       </c>
-      <c r="F52" s="501"/>
-      <c r="G52" s="504" t="s">
+      <c r="F52" s="503"/>
+      <c r="G52" s="506" t="s">
         <v>43</v>
       </c>
       <c r="H52" s="79"/>
@@ -12664,8 +12664,8 @@
       <c r="L52" s="79"/>
       <c r="M52" s="79"/>
       <c r="N52" s="154"/>
-      <c r="O52" s="492"/>
-      <c r="P52" s="395"/>
+      <c r="O52" s="511"/>
+      <c r="P52" s="501"/>
       <c r="Q52" s="172"/>
       <c r="R52" s="172"/>
       <c r="S52" s="172"/>
@@ -12691,7 +12691,7 @@
       <c r="AP52" s="328"/>
       <c r="AQ52" s="328"/>
       <c r="AR52" s="328"/>
-      <c r="AS52" s="393" t="s">
+      <c r="AS52" s="395" t="s">
         <v>562</v>
       </c>
       <c r="AT52" s="352" t="s">
@@ -12705,7 +12705,7 @@
       <c r="AZ52" s="328"/>
       <c r="BA52" s="328"/>
       <c r="BB52" s="328"/>
-      <c r="BC52" s="393" t="s">
+      <c r="BC52" s="395" t="s">
         <v>376</v>
       </c>
       <c r="BD52" s="352" t="s">
@@ -12725,7 +12725,7 @@
       <c r="BL52" s="321" t="s">
         <v>530</v>
       </c>
-      <c r="BM52" s="393" t="s">
+      <c r="BM52" s="395" t="s">
         <v>350</v>
       </c>
       <c r="BN52" s="346" t="s">
@@ -12747,7 +12747,7 @@
       <c r="BV52" s="321" t="s">
         <v>415</v>
       </c>
-      <c r="BW52" s="545" t="s">
+      <c r="BW52" s="401" t="s">
         <v>322</v>
       </c>
       <c r="BX52" s="349"/>
@@ -12755,9 +12755,9 @@
     <row r="53" spans="1:86" s="143" customFormat="1" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="151"/>
       <c r="B53" s="151"/>
-      <c r="E53" s="502"/>
-      <c r="F53" s="503"/>
-      <c r="G53" s="505"/>
+      <c r="E53" s="504"/>
+      <c r="F53" s="505"/>
+      <c r="G53" s="507"/>
       <c r="H53" s="79"/>
       <c r="I53" s="79"/>
       <c r="J53" s="78"/>
@@ -12789,7 +12789,7 @@
       <c r="AP53" s="327"/>
       <c r="AQ53" s="327"/>
       <c r="AR53" s="327"/>
-      <c r="AS53" s="393"/>
+      <c r="AS53" s="395"/>
       <c r="AT53" s="352"/>
       <c r="AU53" s="361" t="s">
         <v>599</v>
@@ -12802,7 +12802,7 @@
       </c>
       <c r="AX53" s="327"/>
       <c r="AY53" s="333" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AZ53" s="361" t="s">
         <v>526</v>
@@ -12811,7 +12811,7 @@
         <v>527</v>
       </c>
       <c r="BB53" s="327"/>
-      <c r="BC53" s="393"/>
+      <c r="BC53" s="395"/>
       <c r="BD53" s="352"/>
       <c r="BE53" s="335" t="s">
         <v>594</v>
@@ -12831,7 +12831,7 @@
       <c r="BL53" s="320" t="s">
         <v>251</v>
       </c>
-      <c r="BM53" s="393"/>
+      <c r="BM53" s="395"/>
       <c r="BN53" s="346"/>
       <c r="BO53" s="368" t="s">
         <v>490</v>
@@ -12855,7 +12855,7 @@
       <c r="BV53" s="320" t="s">
         <v>414</v>
       </c>
-      <c r="BW53" s="545"/>
+      <c r="BW53" s="401"/>
       <c r="BX53" s="349"/>
     </row>
     <row r="54" spans="1:86" s="143" customFormat="1" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -12946,7 +12946,7 @@
       </c>
       <c r="BU54" s="312"/>
       <c r="BV54" s="312"/>
-      <c r="BW54" s="484" t="s">
+      <c r="BW54" s="400" t="s">
         <v>323</v>
       </c>
       <c r="BX54" s="349"/>
@@ -13054,7 +13054,7 @@
       <c r="BV55" s="362" t="s">
         <v>285</v>
       </c>
-      <c r="BW55" s="484"/>
+      <c r="BW55" s="400"/>
       <c r="BX55" s="348"/>
     </row>
     <row r="56" spans="1:86" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -13072,15 +13072,15 @@
       <c r="L56" s="79"/>
       <c r="M56" s="79"/>
       <c r="N56" s="154"/>
-      <c r="O56" s="426" t="s">
+      <c r="O56" s="516" t="s">
         <v>44</v>
       </c>
-      <c r="P56" s="426"/>
-      <c r="Q56" s="426"/>
-      <c r="R56" s="426"/>
-      <c r="S56" s="426"/>
-      <c r="T56" s="426"/>
-      <c r="U56" s="427"/>
+      <c r="P56" s="516"/>
+      <c r="Q56" s="516"/>
+      <c r="R56" s="516"/>
+      <c r="S56" s="516"/>
+      <c r="T56" s="516"/>
+      <c r="U56" s="517"/>
       <c r="V56" s="85"/>
       <c r="W56" s="111"/>
       <c r="X56" s="53"/>
@@ -13106,7 +13106,7 @@
       <c r="AP56" s="328"/>
       <c r="AQ56" s="328"/>
       <c r="AR56" s="328"/>
-      <c r="AS56" s="393" t="s">
+      <c r="AS56" s="395" t="s">
         <v>564</v>
       </c>
       <c r="AT56" s="352" t="s">
@@ -13120,7 +13120,7 @@
       <c r="AZ56" s="328"/>
       <c r="BA56" s="328"/>
       <c r="BB56" s="328"/>
-      <c r="BC56" s="393" t="s">
+      <c r="BC56" s="395" t="s">
         <v>378</v>
       </c>
       <c r="BD56" s="352" t="s">
@@ -13140,7 +13140,7 @@
         <v>257</v>
       </c>
       <c r="BL56" s="328"/>
-      <c r="BM56" s="393" t="s">
+      <c r="BM56" s="395" t="s">
         <v>352</v>
       </c>
       <c r="BN56" s="346" t="s">
@@ -13158,7 +13158,7 @@
       <c r="BV56" s="321" t="s">
         <v>412</v>
       </c>
-      <c r="BW56" s="545" t="s">
+      <c r="BW56" s="401" t="s">
         <v>324</v>
       </c>
       <c r="BX56" s="348"/>
@@ -13176,13 +13176,13 @@
       <c r="L57" s="79"/>
       <c r="M57" s="79"/>
       <c r="N57" s="81"/>
-      <c r="O57" s="429"/>
-      <c r="P57" s="429"/>
-      <c r="Q57" s="429"/>
-      <c r="R57" s="429"/>
-      <c r="S57" s="429"/>
-      <c r="T57" s="429"/>
-      <c r="U57" s="430"/>
+      <c r="O57" s="518"/>
+      <c r="P57" s="518"/>
+      <c r="Q57" s="518"/>
+      <c r="R57" s="518"/>
+      <c r="S57" s="518"/>
+      <c r="T57" s="518"/>
+      <c r="U57" s="519"/>
       <c r="V57" s="85"/>
       <c r="W57" s="53"/>
       <c r="X57" s="53"/>
@@ -13206,7 +13206,7 @@
       <c r="AP57" s="327"/>
       <c r="AQ57" s="327"/>
       <c r="AR57" s="327"/>
-      <c r="AS57" s="393"/>
+      <c r="AS57" s="395"/>
       <c r="AT57" s="352"/>
       <c r="AU57" s="327"/>
       <c r="AV57" s="361" t="s">
@@ -13218,7 +13218,7 @@
       <c r="AZ57" s="327"/>
       <c r="BA57" s="327"/>
       <c r="BB57" s="327"/>
-      <c r="BC57" s="393"/>
+      <c r="BC57" s="395"/>
       <c r="BD57" s="352"/>
       <c r="BE57" s="320" t="s">
         <v>532</v>
@@ -13242,20 +13242,20 @@
       <c r="BL57" s="320" t="s">
         <v>262</v>
       </c>
-      <c r="BM57" s="393"/>
+      <c r="BM57" s="395"/>
       <c r="BN57" s="346"/>
       <c r="BO57" s="368" t="s">
+        <v>666</v>
+      </c>
+      <c r="BP57" s="368" t="s">
         <v>667</v>
-      </c>
-      <c r="BP57" s="368" t="s">
-        <v>668</v>
       </c>
       <c r="BQ57" s="327"/>
       <c r="BR57" s="335" t="s">
         <v>271</v>
       </c>
       <c r="BS57" s="369" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="BT57" s="320" t="s">
         <v>98</v>
@@ -13266,17 +13266,17 @@
       <c r="BV57" s="362" t="s">
         <v>284</v>
       </c>
-      <c r="BW57" s="545"/>
+      <c r="BW57" s="401"/>
       <c r="BX57" s="348"/>
     </row>
     <row r="58" spans="1:86" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="152"/>
       <c r="B58" s="152"/>
-      <c r="E58" s="478" t="s">
+      <c r="E58" s="433" t="s">
         <v>45</v>
       </c>
-      <c r="F58" s="479"/>
-      <c r="G58" s="480"/>
+      <c r="F58" s="435"/>
+      <c r="G58" s="434"/>
       <c r="H58" s="79"/>
       <c r="I58" s="79"/>
       <c r="J58" s="78"/>
@@ -13284,13 +13284,13 @@
       <c r="L58" s="79"/>
       <c r="M58" s="79"/>
       <c r="N58" s="81"/>
-      <c r="O58" s="429"/>
-      <c r="P58" s="429"/>
-      <c r="Q58" s="429"/>
-      <c r="R58" s="429"/>
-      <c r="S58" s="429"/>
-      <c r="T58" s="429"/>
-      <c r="U58" s="430"/>
+      <c r="O58" s="518"/>
+      <c r="P58" s="518"/>
+      <c r="Q58" s="518"/>
+      <c r="R58" s="518"/>
+      <c r="S58" s="518"/>
+      <c r="T58" s="518"/>
+      <c r="U58" s="519"/>
       <c r="V58" s="85"/>
       <c r="W58" s="53"/>
       <c r="X58" s="53"/>
@@ -13340,7 +13340,7 @@
       <c r="BA58" s="312"/>
       <c r="BB58" s="312"/>
       <c r="BC58" s="394" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="BD58" s="351" t="s">
         <v>300</v>
@@ -13373,7 +13373,7 @@
         <v>102</v>
       </c>
       <c r="BV58" s="312"/>
-      <c r="BW58" s="484" t="s">
+      <c r="BW58" s="400" t="s">
         <v>325</v>
       </c>
       <c r="BX58" s="348"/>
@@ -13381,9 +13381,9 @@
     <row r="59" spans="1:86" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="152"/>
       <c r="B59" s="152"/>
-      <c r="E59" s="478"/>
-      <c r="F59" s="479"/>
-      <c r="G59" s="480"/>
+      <c r="E59" s="433"/>
+      <c r="F59" s="435"/>
+      <c r="G59" s="434"/>
       <c r="H59" s="79"/>
       <c r="I59" s="79"/>
       <c r="J59" s="78"/>
@@ -13391,13 +13391,13 @@
       <c r="L59" s="79"/>
       <c r="M59" s="79"/>
       <c r="N59" s="81"/>
-      <c r="O59" s="429"/>
-      <c r="P59" s="429"/>
-      <c r="Q59" s="429"/>
-      <c r="R59" s="429"/>
-      <c r="S59" s="429"/>
-      <c r="T59" s="429"/>
-      <c r="U59" s="430"/>
+      <c r="O59" s="518"/>
+      <c r="P59" s="518"/>
+      <c r="Q59" s="518"/>
+      <c r="R59" s="518"/>
+      <c r="S59" s="518"/>
+      <c r="T59" s="518"/>
+      <c r="U59" s="519"/>
       <c r="V59" s="189"/>
       <c r="W59" s="53"/>
       <c r="X59" s="53"/>
@@ -13439,16 +13439,16 @@
         <v>411</v>
       </c>
       <c r="AS59" s="366" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AT59" s="351"/>
       <c r="AU59" s="313"/>
       <c r="AV59" s="313"/>
       <c r="AW59" s="335" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="AX59" s="333" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AY59" s="313"/>
       <c r="AZ59" s="313"/>
@@ -13467,7 +13467,7 @@
         <v>169</v>
       </c>
       <c r="BI59" s="335" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="BJ59" s="320" t="s">
         <v>170</v>
@@ -13504,15 +13504,15 @@
       <c r="BV59" s="320" t="s">
         <v>283</v>
       </c>
-      <c r="BW59" s="484"/>
+      <c r="BW59" s="400"/>
       <c r="BX59" s="348"/>
     </row>
     <row r="60" spans="1:86" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="152"/>
       <c r="B60" s="152"/>
-      <c r="E60" s="478"/>
-      <c r="F60" s="479"/>
-      <c r="G60" s="480"/>
+      <c r="E60" s="433"/>
+      <c r="F60" s="435"/>
+      <c r="G60" s="434"/>
       <c r="H60" s="79"/>
       <c r="I60" s="79"/>
       <c r="J60" s="78"/>
@@ -13520,13 +13520,13 @@
       <c r="L60" s="79"/>
       <c r="M60" s="79"/>
       <c r="N60" s="81"/>
-      <c r="O60" s="429"/>
-      <c r="P60" s="429"/>
-      <c r="Q60" s="429"/>
-      <c r="R60" s="429"/>
-      <c r="S60" s="429"/>
-      <c r="T60" s="429"/>
-      <c r="U60" s="430"/>
+      <c r="O60" s="518"/>
+      <c r="P60" s="518"/>
+      <c r="Q60" s="518"/>
+      <c r="R60" s="518"/>
+      <c r="S60" s="518"/>
+      <c r="T60" s="518"/>
+      <c r="U60" s="519"/>
       <c r="V60" s="85"/>
       <c r="W60" s="53"/>
       <c r="X60" s="53"/>
@@ -13571,11 +13571,11 @@
       </c>
       <c r="AQ60" s="379">
         <f>COUNTIF( $BE$11:$BL$61,"*402*") + COUNTIF($AK$11:$BB$59,"*402*")+ COUNTIF($BE$63:$BM$63,"*402*") +COUNTIF($BO$11:$BV$65,"*402*") -1</f>
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AR60" s="378">
         <f>COUNTIF( $BE$11:$BL$61,"*403*") + COUNTIF($AK$11:$BB$59,"*403*")+ COUNTIF($BE$63:$BM$63,"*403*") +COUNTIF($BO$11:$BV$65,"*403*") -1</f>
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AS60" s="367">
         <f>14*6-2</f>
@@ -13616,7 +13616,7 @@
       <c r="BJ60" s="328"/>
       <c r="BK60" s="328"/>
       <c r="BL60" s="328"/>
-      <c r="BM60" s="393" t="s">
+      <c r="BM60" s="395" t="s">
         <v>354</v>
       </c>
       <c r="BN60" s="346" t="s">
@@ -13630,7 +13630,7 @@
       <c r="BT60" s="328"/>
       <c r="BU60" s="328"/>
       <c r="BV60" s="328"/>
-      <c r="BW60" s="545" t="s">
+      <c r="BW60" s="401" t="s">
         <v>326</v>
       </c>
       <c r="BX60" s="348"/>
@@ -13638,9 +13638,9 @@
     <row r="61" spans="1:86" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="191"/>
       <c r="B61" s="191"/>
-      <c r="E61" s="478"/>
-      <c r="F61" s="479"/>
-      <c r="G61" s="480"/>
+      <c r="E61" s="433"/>
+      <c r="F61" s="435"/>
+      <c r="G61" s="434"/>
       <c r="H61" s="79"/>
       <c r="I61" s="79"/>
       <c r="J61" s="78"/>
@@ -13648,13 +13648,13 @@
       <c r="L61" s="79"/>
       <c r="M61" s="79"/>
       <c r="N61" s="81"/>
-      <c r="O61" s="429"/>
-      <c r="P61" s="429"/>
-      <c r="Q61" s="429"/>
-      <c r="R61" s="429"/>
-      <c r="S61" s="429"/>
-      <c r="T61" s="429"/>
-      <c r="U61" s="430"/>
+      <c r="O61" s="518"/>
+      <c r="P61" s="518"/>
+      <c r="Q61" s="518"/>
+      <c r="R61" s="518"/>
+      <c r="S61" s="518"/>
+      <c r="T61" s="518"/>
+      <c r="U61" s="519"/>
       <c r="V61" s="85"/>
       <c r="W61" s="53"/>
       <c r="X61" s="53"/>
@@ -13684,7 +13684,7 @@
       <c r="BL61" s="320" t="s">
         <v>269</v>
       </c>
-      <c r="BM61" s="393"/>
+      <c r="BM61" s="395"/>
       <c r="BN61" s="346"/>
       <c r="BO61" s="335" t="s">
         <v>487</v>
@@ -13708,15 +13708,15 @@
       <c r="BV61" s="320" t="s">
         <v>104</v>
       </c>
-      <c r="BW61" s="545"/>
+      <c r="BW61" s="401"/>
       <c r="BX61" s="348"/>
     </row>
     <row r="62" spans="1:86" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="191"/>
       <c r="B62" s="191"/>
-      <c r="E62" s="478"/>
-      <c r="F62" s="479"/>
-      <c r="G62" s="480"/>
+      <c r="E62" s="433"/>
+      <c r="F62" s="435"/>
+      <c r="G62" s="434"/>
       <c r="H62" s="79"/>
       <c r="I62" s="79"/>
       <c r="J62" s="78"/>
@@ -13724,13 +13724,13 @@
       <c r="L62" s="79"/>
       <c r="M62" s="79"/>
       <c r="N62" s="81"/>
-      <c r="O62" s="429"/>
-      <c r="P62" s="429"/>
-      <c r="Q62" s="429"/>
-      <c r="R62" s="429"/>
-      <c r="S62" s="429"/>
-      <c r="T62" s="429"/>
-      <c r="U62" s="430"/>
+      <c r="O62" s="518"/>
+      <c r="P62" s="518"/>
+      <c r="Q62" s="518"/>
+      <c r="R62" s="518"/>
+      <c r="S62" s="518"/>
+      <c r="T62" s="518"/>
+      <c r="U62" s="519"/>
       <c r="V62" s="85"/>
       <c r="W62" s="53"/>
       <c r="X62" s="53"/>
@@ -13791,7 +13791,7 @@
       <c r="BT62" s="312"/>
       <c r="BU62" s="312"/>
       <c r="BV62" s="312"/>
-      <c r="BW62" s="484" t="s">
+      <c r="BW62" s="400" t="s">
         <v>327</v>
       </c>
       <c r="BX62" s="349"/>
@@ -13809,9 +13809,9 @@
     <row r="63" spans="1:86" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="191"/>
       <c r="B63" s="191"/>
-      <c r="E63" s="478"/>
-      <c r="F63" s="479"/>
-      <c r="G63" s="480"/>
+      <c r="E63" s="433"/>
+      <c r="F63" s="435"/>
+      <c r="G63" s="434"/>
       <c r="H63" s="79"/>
       <c r="I63" s="79"/>
       <c r="J63" s="78"/>
@@ -13819,13 +13819,13 @@
       <c r="L63" s="79"/>
       <c r="M63" s="79"/>
       <c r="N63" s="81"/>
-      <c r="O63" s="429"/>
-      <c r="P63" s="429"/>
-      <c r="Q63" s="429"/>
-      <c r="R63" s="429"/>
-      <c r="S63" s="429"/>
-      <c r="T63" s="429"/>
-      <c r="U63" s="430"/>
+      <c r="O63" s="518"/>
+      <c r="P63" s="518"/>
+      <c r="Q63" s="518"/>
+      <c r="R63" s="518"/>
+      <c r="S63" s="518"/>
+      <c r="T63" s="518"/>
+      <c r="U63" s="519"/>
       <c r="V63" s="85"/>
       <c r="W63" s="53"/>
       <c r="X63" s="53"/>
@@ -13848,7 +13848,7 @@
         <v>299</v>
       </c>
       <c r="BE63" s="386" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="BF63" s="377" t="s">
         <v>278</v>
@@ -13877,15 +13877,15 @@
       <c r="BT63" s="313"/>
       <c r="BU63" s="313"/>
       <c r="BV63" s="313"/>
-      <c r="BW63" s="484"/>
+      <c r="BW63" s="400"/>
       <c r="BX63" s="348"/>
     </row>
     <row r="64" spans="1:86" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="191"/>
       <c r="B64" s="191"/>
-      <c r="E64" s="478"/>
-      <c r="F64" s="479"/>
-      <c r="G64" s="480"/>
+      <c r="E64" s="433"/>
+      <c r="F64" s="435"/>
+      <c r="G64" s="434"/>
       <c r="H64" s="79"/>
       <c r="I64" s="79"/>
       <c r="J64" s="78"/>
@@ -13893,13 +13893,13 @@
       <c r="L64" s="79"/>
       <c r="M64" s="79"/>
       <c r="N64" s="81"/>
-      <c r="O64" s="429"/>
-      <c r="P64" s="429"/>
-      <c r="Q64" s="429"/>
-      <c r="R64" s="429"/>
-      <c r="S64" s="429"/>
-      <c r="T64" s="429"/>
-      <c r="U64" s="430"/>
+      <c r="O64" s="518"/>
+      <c r="P64" s="518"/>
+      <c r="Q64" s="518"/>
+      <c r="R64" s="518"/>
+      <c r="S64" s="518"/>
+      <c r="T64" s="518"/>
+      <c r="U64" s="519"/>
       <c r="V64" s="85"/>
       <c r="W64" s="53"/>
       <c r="X64" s="53"/>
@@ -13927,7 +13927,7 @@
       <c r="BT64" s="328"/>
       <c r="BU64" s="328"/>
       <c r="BV64" s="328"/>
-      <c r="BW64" s="485" t="s">
+      <c r="BW64" s="512" t="s">
         <v>328</v>
       </c>
       <c r="BX64" s="348"/>
@@ -13935,9 +13935,9 @@
     <row r="65" spans="1:85" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="191"/>
       <c r="B65" s="191"/>
-      <c r="E65" s="481"/>
-      <c r="F65" s="482"/>
-      <c r="G65" s="483"/>
+      <c r="E65" s="436"/>
+      <c r="F65" s="439"/>
+      <c r="G65" s="437"/>
       <c r="H65" s="79"/>
       <c r="I65" s="79"/>
       <c r="J65" s="78"/>
@@ -13945,13 +13945,13 @@
       <c r="L65" s="79"/>
       <c r="M65" s="79"/>
       <c r="N65" s="81"/>
-      <c r="O65" s="432"/>
-      <c r="P65" s="432"/>
-      <c r="Q65" s="432"/>
-      <c r="R65" s="432"/>
-      <c r="S65" s="432"/>
-      <c r="T65" s="432"/>
-      <c r="U65" s="433"/>
+      <c r="O65" s="520"/>
+      <c r="P65" s="520"/>
+      <c r="Q65" s="520"/>
+      <c r="R65" s="520"/>
+      <c r="S65" s="520"/>
+      <c r="T65" s="520"/>
+      <c r="U65" s="521"/>
       <c r="V65" s="85"/>
       <c r="W65" s="53"/>
       <c r="X65" s="53"/>
@@ -13977,7 +13977,7 @@
       <c r="BT65" s="327"/>
       <c r="BU65" s="327"/>
       <c r="BV65" s="327"/>
-      <c r="BW65" s="485"/>
+      <c r="BW65" s="512"/>
       <c r="BX65" s="348"/>
     </row>
     <row r="66" spans="1:85" ht="279.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -13995,15 +13995,15 @@
       <c r="L66" s="79"/>
       <c r="M66" s="79"/>
       <c r="N66" s="81"/>
-      <c r="O66" s="425" t="s">
+      <c r="O66" s="578" t="s">
         <v>47</v>
       </c>
-      <c r="P66" s="426"/>
-      <c r="Q66" s="426"/>
-      <c r="R66" s="426"/>
-      <c r="S66" s="426"/>
-      <c r="T66" s="426"/>
-      <c r="U66" s="427"/>
+      <c r="P66" s="516"/>
+      <c r="Q66" s="516"/>
+      <c r="R66" s="516"/>
+      <c r="S66" s="516"/>
+      <c r="T66" s="516"/>
+      <c r="U66" s="517"/>
       <c r="V66" s="85"/>
       <c r="W66" s="53"/>
       <c r="X66" s="53"/>
@@ -14027,12 +14027,12 @@
       <c r="AQ66" s="86"/>
       <c r="AR66" s="209"/>
       <c r="AS66" s="209"/>
-      <c r="AT66" s="486" t="s">
+      <c r="AT66" s="455" t="s">
         <v>11</v>
       </c>
-      <c r="AU66" s="487"/>
-      <c r="AV66" s="487"/>
-      <c r="AW66" s="488"/>
+      <c r="AU66" s="522"/>
+      <c r="AV66" s="522"/>
+      <c r="AW66" s="456"/>
       <c r="AX66" s="210"/>
       <c r="AY66" s="210"/>
       <c r="AZ66" s="210"/>
@@ -14075,23 +14075,23 @@
       <c r="L67" s="79"/>
       <c r="M67" s="79"/>
       <c r="N67" s="81"/>
-      <c r="O67" s="428"/>
-      <c r="P67" s="429"/>
-      <c r="Q67" s="429"/>
-      <c r="R67" s="429"/>
-      <c r="S67" s="429"/>
-      <c r="T67" s="429"/>
-      <c r="U67" s="430"/>
+      <c r="O67" s="579"/>
+      <c r="P67" s="518"/>
+      <c r="Q67" s="518"/>
+      <c r="R67" s="518"/>
+      <c r="S67" s="518"/>
+      <c r="T67" s="518"/>
+      <c r="U67" s="519"/>
       <c r="V67" s="85"/>
       <c r="W67" s="53"/>
       <c r="X67" s="53"/>
       <c r="Y67" s="53"/>
       <c r="Z67" s="83"/>
-      <c r="AA67" s="434" t="s">
+      <c r="AA67" s="581" t="s">
         <v>48</v>
       </c>
-      <c r="AB67" s="435"/>
-      <c r="AC67" s="436"/>
+      <c r="AB67" s="582"/>
+      <c r="AC67" s="583"/>
       <c r="AD67" s="95"/>
       <c r="AE67" s="95"/>
       <c r="AF67" s="95"/>
@@ -14201,21 +14201,21 @@
       <c r="L68" s="79"/>
       <c r="M68" s="79"/>
       <c r="N68" s="81"/>
-      <c r="O68" s="428"/>
-      <c r="P68" s="429"/>
-      <c r="Q68" s="429"/>
-      <c r="R68" s="429"/>
-      <c r="S68" s="429"/>
-      <c r="T68" s="429"/>
-      <c r="U68" s="430"/>
+      <c r="O68" s="579"/>
+      <c r="P68" s="518"/>
+      <c r="Q68" s="518"/>
+      <c r="R68" s="518"/>
+      <c r="S68" s="518"/>
+      <c r="T68" s="518"/>
+      <c r="U68" s="519"/>
       <c r="V68" s="85"/>
       <c r="W68" s="53"/>
       <c r="X68" s="53"/>
       <c r="Y68" s="53"/>
       <c r="Z68" s="83"/>
-      <c r="AA68" s="437"/>
-      <c r="AB68" s="438"/>
-      <c r="AC68" s="439"/>
+      <c r="AA68" s="584"/>
+      <c r="AB68" s="585"/>
+      <c r="AC68" s="586"/>
       <c r="AD68" s="95"/>
       <c r="AE68" s="95"/>
       <c r="AF68" s="95"/>
@@ -14346,21 +14346,21 @@
       <c r="L69" s="79"/>
       <c r="M69" s="79"/>
       <c r="N69" s="81"/>
-      <c r="O69" s="428"/>
-      <c r="P69" s="429"/>
-      <c r="Q69" s="429"/>
-      <c r="R69" s="429"/>
-      <c r="S69" s="429"/>
-      <c r="T69" s="429"/>
-      <c r="U69" s="430"/>
+      <c r="O69" s="579"/>
+      <c r="P69" s="518"/>
+      <c r="Q69" s="518"/>
+      <c r="R69" s="518"/>
+      <c r="S69" s="518"/>
+      <c r="T69" s="518"/>
+      <c r="U69" s="519"/>
       <c r="V69" s="85"/>
       <c r="W69" s="53"/>
       <c r="X69" s="53"/>
       <c r="Y69" s="53"/>
       <c r="Z69" s="83"/>
-      <c r="AA69" s="437"/>
-      <c r="AB69" s="438"/>
-      <c r="AC69" s="439"/>
+      <c r="AA69" s="584"/>
+      <c r="AB69" s="585"/>
+      <c r="AC69" s="586"/>
       <c r="AD69" s="95"/>
       <c r="AE69" s="95"/>
       <c r="AF69" s="95"/>
@@ -14375,12 +14375,12 @@
       <c r="AQ69" s="198"/>
       <c r="AR69" s="213"/>
       <c r="AS69" s="271"/>
-      <c r="AT69" s="404" t="s">
+      <c r="AT69" s="560" t="s">
         <v>12</v>
       </c>
-      <c r="AU69" s="405"/>
-      <c r="AV69" s="405"/>
-      <c r="AW69" s="406"/>
+      <c r="AU69" s="561"/>
+      <c r="AV69" s="561"/>
+      <c r="AW69" s="562"/>
       <c r="AX69" s="210"/>
       <c r="AY69" s="210"/>
       <c r="AZ69" s="306">
@@ -14412,7 +14412,7 @@
       </c>
       <c r="BG69" s="337">
         <f>COUNTIF($AK$11:$BL$63,"*402-7-*") + COUNTIF($BO$11:$BV$65,"*402-7-*")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BH69" s="337">
         <f>COUNTIF($AK$11:$BL$63,"*402-8-*") + COUNTIF($BO$11:$BV$65,"*402-8-*")</f>
@@ -14476,7 +14476,7 @@
       </c>
       <c r="BW69" s="310">
         <f>SUM(BA69:BV69)/(14*22)</f>
-        <v>0.27597402597402598</v>
+        <v>0.27272727272727271</v>
       </c>
     </row>
     <row r="70" spans="1:85" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -14492,21 +14492,21 @@
       <c r="L70" s="79"/>
       <c r="M70" s="79"/>
       <c r="N70" s="81"/>
-      <c r="O70" s="428"/>
-      <c r="P70" s="429"/>
-      <c r="Q70" s="429"/>
-      <c r="R70" s="429"/>
-      <c r="S70" s="429"/>
-      <c r="T70" s="429"/>
-      <c r="U70" s="430"/>
+      <c r="O70" s="579"/>
+      <c r="P70" s="518"/>
+      <c r="Q70" s="518"/>
+      <c r="R70" s="518"/>
+      <c r="S70" s="518"/>
+      <c r="T70" s="518"/>
+      <c r="U70" s="519"/>
       <c r="V70" s="189"/>
       <c r="W70" s="53"/>
       <c r="X70" s="53"/>
       <c r="Y70" s="53"/>
       <c r="Z70" s="83"/>
-      <c r="AA70" s="437"/>
-      <c r="AB70" s="438"/>
-      <c r="AC70" s="439"/>
+      <c r="AA70" s="584"/>
+      <c r="AB70" s="585"/>
+      <c r="AC70" s="586"/>
       <c r="AD70" s="95"/>
       <c r="AE70" s="95"/>
       <c r="AF70" s="95"/>
@@ -14517,10 +14517,10 @@
       <c r="AQ70" s="198"/>
       <c r="AR70" s="213"/>
       <c r="AS70" s="271"/>
-      <c r="AT70" s="407"/>
-      <c r="AU70" s="408"/>
-      <c r="AV70" s="408"/>
-      <c r="AW70" s="409"/>
+      <c r="AT70" s="563"/>
+      <c r="AU70" s="564"/>
+      <c r="AV70" s="564"/>
+      <c r="AW70" s="565"/>
       <c r="AX70" s="210"/>
       <c r="AY70" s="210"/>
       <c r="AZ70" s="307">
@@ -14552,7 +14552,7 @@
       </c>
       <c r="BG70" s="336">
         <f>COUNTIF($AK$11:$BL$63,"*403-7-*") + COUNTIF($BO$11:$BV$65,"*403-7-*")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BH70" s="336">
         <f>COUNTIF($AK$11:$BL$63,"*403-8-*") + COUNTIF($BO$11:$BV$65,"*403-8-*")</f>
@@ -14616,7 +14616,7 @@
       </c>
       <c r="BW70" s="310">
         <f>SUM(BA70:BV70)/(14*16)</f>
-        <v>0.9508928571428571</v>
+        <v>0.9553571428571429</v>
       </c>
     </row>
     <row r="71" spans="1:85" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -14632,21 +14632,21 @@
       <c r="L71" s="79"/>
       <c r="M71" s="79"/>
       <c r="N71" s="81"/>
-      <c r="O71" s="428"/>
-      <c r="P71" s="429"/>
-      <c r="Q71" s="429"/>
-      <c r="R71" s="429"/>
-      <c r="S71" s="429"/>
-      <c r="T71" s="429"/>
-      <c r="U71" s="430"/>
+      <c r="O71" s="579"/>
+      <c r="P71" s="518"/>
+      <c r="Q71" s="518"/>
+      <c r="R71" s="518"/>
+      <c r="S71" s="518"/>
+      <c r="T71" s="518"/>
+      <c r="U71" s="519"/>
       <c r="V71" s="189"/>
       <c r="W71" s="53"/>
       <c r="X71" s="53"/>
       <c r="Y71" s="53"/>
       <c r="Z71" s="83"/>
-      <c r="AA71" s="440"/>
-      <c r="AB71" s="441"/>
-      <c r="AC71" s="442"/>
+      <c r="AA71" s="587"/>
+      <c r="AB71" s="588"/>
+      <c r="AC71" s="589"/>
       <c r="AD71" s="95"/>
       <c r="AE71" s="95"/>
       <c r="AF71" s="95"/>
@@ -14657,10 +14657,10 @@
       <c r="AQ71" s="198"/>
       <c r="AR71" s="213"/>
       <c r="AS71" s="271"/>
-      <c r="AT71" s="410"/>
-      <c r="AU71" s="411"/>
-      <c r="AV71" s="411"/>
-      <c r="AW71" s="412"/>
+      <c r="AT71" s="566"/>
+      <c r="AU71" s="567"/>
+      <c r="AV71" s="567"/>
+      <c r="AW71" s="568"/>
       <c r="AX71" s="210"/>
       <c r="AY71" s="210"/>
       <c r="AZ71" s="210"/>
@@ -14681,13 +14681,13 @@
       <c r="L72" s="79"/>
       <c r="M72" s="79"/>
       <c r="N72" s="81"/>
-      <c r="O72" s="428"/>
-      <c r="P72" s="429"/>
-      <c r="Q72" s="429"/>
-      <c r="R72" s="429"/>
-      <c r="S72" s="429"/>
-      <c r="T72" s="429"/>
-      <c r="U72" s="430"/>
+      <c r="O72" s="579"/>
+      <c r="P72" s="518"/>
+      <c r="Q72" s="518"/>
+      <c r="R72" s="518"/>
+      <c r="S72" s="518"/>
+      <c r="T72" s="518"/>
+      <c r="U72" s="519"/>
       <c r="V72" s="189"/>
       <c r="W72" s="53"/>
       <c r="X72" s="53"/>
@@ -14744,13 +14744,13 @@
       <c r="L73" s="79"/>
       <c r="M73" s="79"/>
       <c r="N73" s="81"/>
-      <c r="O73" s="428"/>
-      <c r="P73" s="429"/>
-      <c r="Q73" s="429"/>
-      <c r="R73" s="429"/>
-      <c r="S73" s="429"/>
-      <c r="T73" s="429"/>
-      <c r="U73" s="430"/>
+      <c r="O73" s="579"/>
+      <c r="P73" s="518"/>
+      <c r="Q73" s="518"/>
+      <c r="R73" s="518"/>
+      <c r="S73" s="518"/>
+      <c r="T73" s="518"/>
+      <c r="U73" s="519"/>
       <c r="V73" s="189"/>
       <c r="W73" s="53"/>
       <c r="X73" s="53"/>
@@ -14807,22 +14807,22 @@
       <c r="L74" s="79"/>
       <c r="M74" s="79"/>
       <c r="N74" s="81"/>
-      <c r="O74" s="428"/>
-      <c r="P74" s="429"/>
-      <c r="Q74" s="429"/>
-      <c r="R74" s="429"/>
-      <c r="S74" s="429"/>
-      <c r="T74" s="429"/>
-      <c r="U74" s="430"/>
+      <c r="O74" s="579"/>
+      <c r="P74" s="518"/>
+      <c r="Q74" s="518"/>
+      <c r="R74" s="518"/>
+      <c r="S74" s="518"/>
+      <c r="T74" s="518"/>
+      <c r="U74" s="519"/>
       <c r="V74" s="207"/>
       <c r="W74" s="208"/>
       <c r="X74" s="53"/>
       <c r="Y74" s="53"/>
       <c r="Z74" s="53"/>
-      <c r="AB74" s="490" t="s">
+      <c r="AB74" s="509" t="s">
         <v>49</v>
       </c>
-      <c r="AC74" s="491"/>
+      <c r="AC74" s="510"/>
       <c r="AG74" s="90"/>
       <c r="AH74" s="121"/>
       <c r="AI74" s="90"/>
@@ -14831,21 +14831,21 @@
       <c r="AQ74" s="198"/>
       <c r="AR74" s="198"/>
       <c r="AS74" s="198"/>
-      <c r="AT74" s="413" t="s">
+      <c r="AT74" s="569" t="s">
         <v>13</v>
       </c>
-      <c r="AU74" s="414"/>
-      <c r="AV74" s="414"/>
-      <c r="AW74" s="414"/>
-      <c r="AX74" s="414"/>
-      <c r="AY74" s="415"/>
+      <c r="AU74" s="570"/>
+      <c r="AV74" s="570"/>
+      <c r="AW74" s="570"/>
+      <c r="AX74" s="570"/>
+      <c r="AY74" s="571"/>
       <c r="AZ74" s="210"/>
       <c r="BA74" s="90"/>
-      <c r="BB74" s="422" t="s">
+      <c r="BB74" s="513" t="s">
         <v>0</v>
       </c>
       <c r="BC74" s="297"/>
-      <c r="BD74" s="422" t="s">
+      <c r="BD74" s="513" t="s">
         <v>1</v>
       </c>
       <c r="BF74" s="294"/>
@@ -14879,19 +14879,19 @@
       <c r="L75" s="79"/>
       <c r="M75" s="79"/>
       <c r="N75" s="81"/>
-      <c r="O75" s="428"/>
-      <c r="P75" s="429"/>
-      <c r="Q75" s="429"/>
-      <c r="R75" s="429"/>
-      <c r="S75" s="429"/>
-      <c r="T75" s="429"/>
-      <c r="U75" s="430"/>
+      <c r="O75" s="579"/>
+      <c r="P75" s="518"/>
+      <c r="Q75" s="518"/>
+      <c r="R75" s="518"/>
+      <c r="S75" s="518"/>
+      <c r="T75" s="518"/>
+      <c r="U75" s="519"/>
       <c r="V75" s="189"/>
       <c r="W75" s="208"/>
       <c r="X75" s="53"/>
       <c r="Z75" s="53"/>
-      <c r="AB75" s="490"/>
-      <c r="AC75" s="491"/>
+      <c r="AB75" s="509"/>
+      <c r="AC75" s="510"/>
       <c r="AD75" s="92"/>
       <c r="AE75" s="92"/>
       <c r="AG75" s="90"/>
@@ -14902,17 +14902,17 @@
       <c r="AQ75" s="42"/>
       <c r="AR75" s="198"/>
       <c r="AS75" s="198"/>
-      <c r="AT75" s="416"/>
-      <c r="AU75" s="417"/>
-      <c r="AV75" s="417"/>
-      <c r="AW75" s="417"/>
-      <c r="AX75" s="417"/>
-      <c r="AY75" s="418"/>
+      <c r="AT75" s="572"/>
+      <c r="AU75" s="573"/>
+      <c r="AV75" s="573"/>
+      <c r="AW75" s="573"/>
+      <c r="AX75" s="573"/>
+      <c r="AY75" s="574"/>
       <c r="AZ75" s="97"/>
       <c r="BA75" s="97"/>
-      <c r="BB75" s="423"/>
+      <c r="BB75" s="514"/>
       <c r="BC75" s="298"/>
-      <c r="BD75" s="423"/>
+      <c r="BD75" s="514"/>
       <c r="BL75" s="88"/>
       <c r="BN75" s="6"/>
       <c r="BO75" s="6"/>
@@ -14937,13 +14937,13 @@
       <c r="L76" s="79"/>
       <c r="M76" s="79"/>
       <c r="N76" s="81"/>
-      <c r="O76" s="428"/>
-      <c r="P76" s="429"/>
-      <c r="Q76" s="429"/>
-      <c r="R76" s="429"/>
-      <c r="S76" s="429"/>
-      <c r="T76" s="429"/>
-      <c r="U76" s="430"/>
+      <c r="O76" s="579"/>
+      <c r="P76" s="518"/>
+      <c r="Q76" s="518"/>
+      <c r="R76" s="518"/>
+      <c r="S76" s="518"/>
+      <c r="T76" s="518"/>
+      <c r="U76" s="519"/>
       <c r="V76" s="189"/>
       <c r="W76" s="208"/>
       <c r="X76" s="53"/>
@@ -14966,17 +14966,17 @@
       <c r="AQ76" s="234"/>
       <c r="AR76" s="206"/>
       <c r="AS76" s="206"/>
-      <c r="AT76" s="419"/>
-      <c r="AU76" s="420"/>
-      <c r="AV76" s="420"/>
-      <c r="AW76" s="420"/>
-      <c r="AX76" s="420"/>
-      <c r="AY76" s="421"/>
+      <c r="AT76" s="575"/>
+      <c r="AU76" s="576"/>
+      <c r="AV76" s="576"/>
+      <c r="AW76" s="576"/>
+      <c r="AX76" s="576"/>
+      <c r="AY76" s="577"/>
       <c r="AZ76" s="206"/>
       <c r="BA76" s="206"/>
-      <c r="BB76" s="424"/>
+      <c r="BB76" s="515"/>
       <c r="BC76" s="299"/>
-      <c r="BD76" s="424"/>
+      <c r="BD76" s="515"/>
       <c r="BE76" s="235"/>
       <c r="BF76" s="235"/>
       <c r="BG76" s="235"/>
@@ -14998,13 +14998,13 @@
       <c r="L77" s="79"/>
       <c r="M77" s="79"/>
       <c r="N77" s="81"/>
-      <c r="O77" s="428"/>
-      <c r="P77" s="429"/>
-      <c r="Q77" s="429"/>
-      <c r="R77" s="429"/>
-      <c r="S77" s="429"/>
-      <c r="T77" s="429"/>
-      <c r="U77" s="430"/>
+      <c r="O77" s="579"/>
+      <c r="P77" s="518"/>
+      <c r="Q77" s="518"/>
+      <c r="R77" s="518"/>
+      <c r="S77" s="518"/>
+      <c r="T77" s="518"/>
+      <c r="U77" s="519"/>
       <c r="V77" s="189"/>
       <c r="W77" s="208"/>
       <c r="X77" s="53"/>
@@ -15019,13 +15019,13 @@
       <c r="AJ77" s="186"/>
       <c r="AK77" s="226"/>
       <c r="AL77" s="226"/>
-      <c r="AM77" s="396" t="s">
+      <c r="AM77" s="554" t="s">
         <v>3</v>
       </c>
-      <c r="AN77" s="397"/>
-      <c r="AO77" s="397"/>
-      <c r="AP77" s="397"/>
-      <c r="AQ77" s="398"/>
+      <c r="AN77" s="555"/>
+      <c r="AO77" s="555"/>
+      <c r="AP77" s="555"/>
+      <c r="AQ77" s="556"/>
       <c r="AR77" s="240"/>
       <c r="BI77" s="241"/>
     </row>
@@ -15042,13 +15042,13 @@
       <c r="L78" s="107"/>
       <c r="M78" s="107"/>
       <c r="N78" s="215"/>
-      <c r="O78" s="431"/>
-      <c r="P78" s="432"/>
-      <c r="Q78" s="432"/>
-      <c r="R78" s="432"/>
-      <c r="S78" s="432"/>
-      <c r="T78" s="432"/>
-      <c r="U78" s="433"/>
+      <c r="O78" s="580"/>
+      <c r="P78" s="520"/>
+      <c r="Q78" s="520"/>
+      <c r="R78" s="520"/>
+      <c r="S78" s="520"/>
+      <c r="T78" s="520"/>
+      <c r="U78" s="521"/>
       <c r="V78" s="189"/>
       <c r="W78" s="208"/>
       <c r="X78" s="53"/>
@@ -15060,11 +15060,11 @@
       <c r="AH78" s="92"/>
       <c r="AK78" s="226"/>
       <c r="AL78" s="226"/>
-      <c r="AM78" s="399"/>
-      <c r="AN78" s="400"/>
-      <c r="AO78" s="400"/>
-      <c r="AP78" s="400"/>
-      <c r="AQ78" s="401"/>
+      <c r="AM78" s="557"/>
+      <c r="AN78" s="558"/>
+      <c r="AO78" s="558"/>
+      <c r="AP78" s="558"/>
+      <c r="AQ78" s="559"/>
       <c r="AU78" s="248"/>
       <c r="AV78" s="248"/>
       <c r="AW78" s="248"/>
@@ -15339,13 +15339,13 @@
       <c r="H83" s="229"/>
       <c r="I83" s="230"/>
       <c r="J83" s="231"/>
-      <c r="K83" s="451" t="s">
+      <c r="K83" s="527" t="s">
         <v>50</v>
       </c>
-      <c r="L83" s="452"/>
-      <c r="M83" s="452"/>
-      <c r="N83" s="452"/>
-      <c r="O83" s="453"/>
+      <c r="L83" s="528"/>
+      <c r="M83" s="528"/>
+      <c r="N83" s="528"/>
+      <c r="O83" s="529"/>
       <c r="P83" s="224"/>
       <c r="Q83" s="224"/>
       <c r="R83" s="224"/>
@@ -15402,28 +15402,28 @@
     </row>
     <row r="84" spans="1:74" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="42"/>
-      <c r="B84" s="460" t="s">
+      <c r="B84" s="472" t="s">
         <v>51</v>
       </c>
-      <c r="C84" s="461"/>
-      <c r="D84" s="462"/>
-      <c r="E84" s="402" t="s">
+      <c r="C84" s="536"/>
+      <c r="D84" s="537"/>
+      <c r="E84" s="525" t="s">
         <v>52</v>
       </c>
-      <c r="F84" s="403"/>
-      <c r="G84" s="467" t="s">
+      <c r="F84" s="526"/>
+      <c r="G84" s="474" t="s">
         <v>52</v>
       </c>
-      <c r="H84" s="468"/>
-      <c r="I84" s="469" t="s">
+      <c r="H84" s="487"/>
+      <c r="I84" s="542" t="s">
         <v>53</v>
       </c>
-      <c r="J84" s="470"/>
-      <c r="K84" s="454"/>
-      <c r="L84" s="455"/>
-      <c r="M84" s="455"/>
-      <c r="N84" s="455"/>
-      <c r="O84" s="456"/>
+      <c r="J84" s="543"/>
+      <c r="K84" s="530"/>
+      <c r="L84" s="531"/>
+      <c r="M84" s="531"/>
+      <c r="N84" s="531"/>
+      <c r="O84" s="532"/>
       <c r="P84" s="224"/>
       <c r="Q84" s="224"/>
       <c r="R84" s="224"/>
@@ -15477,27 +15477,27 @@
       <c r="BS84" s="259"/>
       <c r="BT84" s="259"/>
       <c r="BU84" s="259"/>
-      <c r="BV84" s="489"/>
+      <c r="BV84" s="508"/>
     </row>
     <row r="85" spans="1:74" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="463"/>
-      <c r="C85" s="461"/>
-      <c r="D85" s="462"/>
-      <c r="E85" s="402" t="s">
+      <c r="B85" s="538"/>
+      <c r="C85" s="536"/>
+      <c r="D85" s="537"/>
+      <c r="E85" s="525" t="s">
         <v>52</v>
       </c>
-      <c r="F85" s="473"/>
-      <c r="G85" s="402" t="s">
+      <c r="F85" s="546"/>
+      <c r="G85" s="525" t="s">
         <v>52</v>
       </c>
-      <c r="H85" s="473"/>
-      <c r="I85" s="469"/>
-      <c r="J85" s="470"/>
-      <c r="K85" s="454"/>
-      <c r="L85" s="455"/>
-      <c r="M85" s="455"/>
-      <c r="N85" s="455"/>
-      <c r="O85" s="456"/>
+      <c r="H85" s="546"/>
+      <c r="I85" s="542"/>
+      <c r="J85" s="543"/>
+      <c r="K85" s="530"/>
+      <c r="L85" s="531"/>
+      <c r="M85" s="531"/>
+      <c r="N85" s="531"/>
+      <c r="O85" s="532"/>
       <c r="P85" s="224"/>
       <c r="Q85" s="224"/>
       <c r="R85" s="224"/>
@@ -15551,28 +15551,28 @@
       <c r="BS85" s="259"/>
       <c r="BT85" s="259"/>
       <c r="BU85" s="259"/>
-      <c r="BV85" s="489"/>
+      <c r="BV85" s="508"/>
     </row>
     <row r="86" spans="1:74" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="42"/>
-      <c r="B86" s="464"/>
-      <c r="C86" s="465"/>
-      <c r="D86" s="466"/>
-      <c r="E86" s="402" t="s">
+      <c r="B86" s="539"/>
+      <c r="C86" s="540"/>
+      <c r="D86" s="541"/>
+      <c r="E86" s="525" t="s">
         <v>54</v>
       </c>
-      <c r="F86" s="403"/>
-      <c r="G86" s="402" t="s">
+      <c r="F86" s="526"/>
+      <c r="G86" s="525" t="s">
         <v>55</v>
       </c>
-      <c r="H86" s="403"/>
-      <c r="I86" s="471"/>
-      <c r="J86" s="472"/>
-      <c r="K86" s="457"/>
-      <c r="L86" s="458"/>
-      <c r="M86" s="458"/>
-      <c r="N86" s="458"/>
-      <c r="O86" s="459"/>
+      <c r="H86" s="526"/>
+      <c r="I86" s="544"/>
+      <c r="J86" s="545"/>
+      <c r="K86" s="533"/>
+      <c r="L86" s="534"/>
+      <c r="M86" s="534"/>
+      <c r="N86" s="534"/>
+      <c r="O86" s="535"/>
       <c r="P86" s="242"/>
       <c r="Q86" s="242"/>
       <c r="R86" s="242"/>
@@ -15626,7 +15626,7 @@
       <c r="BS86" s="259"/>
       <c r="BT86" s="259"/>
       <c r="BU86" s="259"/>
-      <c r="BV86" s="489"/>
+      <c r="BV86" s="508"/>
     </row>
     <row r="87" spans="1:74" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="249"/>
@@ -15698,7 +15698,7 @@
       <c r="BU87" s="259"/>
     </row>
     <row r="88" spans="1:74" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="395"/>
+      <c r="A88" s="501"/>
       <c r="B88" s="42"/>
       <c r="C88" s="42"/>
       <c r="D88" s="42"/>
@@ -15706,20 +15706,20 @@
       <c r="F88" s="42"/>
       <c r="G88" s="96"/>
       <c r="K88" s="92"/>
-      <c r="R88" s="449"/>
-      <c r="S88" s="449"/>
-      <c r="T88" s="449"/>
-      <c r="U88" s="449"/>
-      <c r="V88" s="449"/>
-      <c r="W88" s="449"/>
-      <c r="X88" s="449"/>
-      <c r="Y88" s="449"/>
-      <c r="Z88" s="449"/>
-      <c r="AA88" s="449"/>
-      <c r="AB88" s="449"/>
-      <c r="AC88" s="449"/>
-      <c r="AD88" s="443"/>
-      <c r="AE88" s="444"/>
+      <c r="R88" s="552"/>
+      <c r="S88" s="552"/>
+      <c r="T88" s="552"/>
+      <c r="U88" s="552"/>
+      <c r="V88" s="552"/>
+      <c r="W88" s="552"/>
+      <c r="X88" s="552"/>
+      <c r="Y88" s="552"/>
+      <c r="Z88" s="552"/>
+      <c r="AA88" s="552"/>
+      <c r="AB88" s="552"/>
+      <c r="AC88" s="552"/>
+      <c r="AD88" s="590"/>
+      <c r="AE88" s="591"/>
       <c r="AG88" s="260"/>
       <c r="AK88" s="206"/>
       <c r="AL88" s="206"/>
@@ -15756,7 +15756,7 @@
       <c r="BU88" s="259"/>
     </row>
     <row r="89" spans="1:74" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="395"/>
+      <c r="A89" s="501"/>
       <c r="B89" s="42"/>
       <c r="C89" s="42"/>
       <c r="D89" s="42"/>
@@ -15764,20 +15764,20 @@
       <c r="F89" s="42"/>
       <c r="G89" s="96"/>
       <c r="K89" s="92"/>
-      <c r="R89" s="450"/>
-      <c r="S89" s="450"/>
-      <c r="T89" s="450"/>
-      <c r="U89" s="450"/>
-      <c r="V89" s="450"/>
-      <c r="W89" s="450"/>
-      <c r="X89" s="450"/>
-      <c r="Y89" s="450"/>
-      <c r="Z89" s="450"/>
-      <c r="AA89" s="450"/>
-      <c r="AB89" s="450"/>
-      <c r="AC89" s="450"/>
-      <c r="AD89" s="443"/>
-      <c r="AE89" s="444"/>
+      <c r="R89" s="553"/>
+      <c r="S89" s="553"/>
+      <c r="T89" s="553"/>
+      <c r="U89" s="553"/>
+      <c r="V89" s="553"/>
+      <c r="W89" s="553"/>
+      <c r="X89" s="553"/>
+      <c r="Y89" s="553"/>
+      <c r="Z89" s="553"/>
+      <c r="AA89" s="553"/>
+      <c r="AB89" s="553"/>
+      <c r="AC89" s="553"/>
+      <c r="AD89" s="590"/>
+      <c r="AE89" s="591"/>
       <c r="AG89" s="264"/>
       <c r="AK89" s="285"/>
       <c r="AL89" s="281"/>
@@ -15818,18 +15818,18 @@
       <c r="BU89" s="259"/>
     </row>
     <row r="90" spans="1:74" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="395"/>
+      <c r="A90" s="501"/>
       <c r="H90" s="265"/>
       <c r="I90" s="265"/>
       <c r="J90" s="265"/>
       <c r="K90" s="179"/>
       <c r="L90" s="179"/>
-      <c r="R90" s="474"/>
-      <c r="S90" s="475"/>
-      <c r="T90" s="476"/>
-      <c r="U90" s="477"/>
-      <c r="V90" s="476"/>
-      <c r="W90" s="477"/>
+      <c r="R90" s="548"/>
+      <c r="S90" s="549"/>
+      <c r="T90" s="550"/>
+      <c r="U90" s="551"/>
+      <c r="V90" s="550"/>
+      <c r="W90" s="551"/>
       <c r="AD90" s="70"/>
       <c r="AE90" s="70"/>
       <c r="AF90" s="70"/>
@@ -15885,12 +15885,12 @@
       <c r="J91" s="179"/>
       <c r="K91" s="70"/>
       <c r="L91" s="70"/>
-      <c r="R91" s="445"/>
-      <c r="S91" s="446"/>
-      <c r="T91" s="445"/>
-      <c r="U91" s="446"/>
-      <c r="V91" s="447"/>
-      <c r="W91" s="448"/>
+      <c r="R91" s="523"/>
+      <c r="S91" s="524"/>
+      <c r="T91" s="523"/>
+      <c r="U91" s="524"/>
+      <c r="V91" s="547"/>
+      <c r="W91" s="592"/>
       <c r="X91" s="5"/>
       <c r="AB91" s="267"/>
       <c r="AC91" s="5"/>
@@ -15900,7 +15900,7 @@
       <c r="AH91" s="70"/>
     </row>
     <row r="92" spans="1:74" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="395"/>
+      <c r="A92" s="501"/>
       <c r="B92" s="179"/>
       <c r="C92" s="179"/>
       <c r="D92" s="179"/>
@@ -15917,15 +15917,15 @@
       <c r="O92" s="269"/>
       <c r="P92" s="224"/>
       <c r="Q92" s="70"/>
-      <c r="R92" s="445"/>
-      <c r="S92" s="446"/>
-      <c r="T92" s="445"/>
-      <c r="U92" s="446"/>
-      <c r="V92" s="445"/>
-      <c r="W92" s="446"/>
+      <c r="R92" s="523"/>
+      <c r="S92" s="524"/>
+      <c r="T92" s="523"/>
+      <c r="U92" s="524"/>
+      <c r="V92" s="523"/>
+      <c r="W92" s="524"/>
       <c r="X92" s="46"/>
-      <c r="Y92" s="445"/>
-      <c r="Z92" s="446"/>
+      <c r="Y92" s="523"/>
+      <c r="Z92" s="524"/>
       <c r="AA92" s="270"/>
       <c r="AB92" s="271"/>
       <c r="AC92" s="5"/>
@@ -15935,7 +15935,7 @@
       <c r="AH92" s="70"/>
     </row>
     <row r="93" spans="1:74" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="395"/>
+      <c r="A93" s="501"/>
       <c r="B93" s="97"/>
       <c r="C93" s="97"/>
       <c r="D93" s="97"/>
@@ -15953,13 +15953,13 @@
       <c r="P93" s="70"/>
       <c r="Q93" s="70"/>
       <c r="R93" s="272"/>
-      <c r="S93" s="445"/>
-      <c r="T93" s="446"/>
+      <c r="S93" s="523"/>
+      <c r="T93" s="524"/>
       <c r="U93" s="273"/>
-      <c r="V93" s="447"/>
-      <c r="W93" s="447"/>
-      <c r="X93" s="447"/>
-      <c r="Y93" s="447"/>
+      <c r="V93" s="547"/>
+      <c r="W93" s="547"/>
+      <c r="X93" s="547"/>
+      <c r="Y93" s="547"/>
       <c r="Z93" s="274"/>
       <c r="AA93" s="275"/>
       <c r="AB93" s="267"/>
@@ -15971,7 +15971,7 @@
       <c r="AH93" s="70"/>
     </row>
     <row r="94" spans="1:74" ht="186" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="395"/>
+      <c r="A94" s="501"/>
       <c r="B94" s="97"/>
       <c r="C94" s="97"/>
       <c r="D94" s="97"/>
@@ -16023,11 +16023,11 @@
       <c r="W95" s="199"/>
     </row>
     <row r="96" spans="1:74" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E96" s="395"/>
+      <c r="E96" s="501"/>
       <c r="F96" s="159"/>
-      <c r="G96" s="395"/>
-      <c r="H96" s="395"/>
-      <c r="I96" s="395"/>
+      <c r="G96" s="501"/>
+      <c r="H96" s="501"/>
+      <c r="I96" s="501"/>
       <c r="J96" s="199"/>
       <c r="K96" s="199"/>
       <c r="L96" s="199"/>
@@ -16044,11 +16044,11 @@
       <c r="W96" s="199"/>
     </row>
     <row r="97" spans="5:36" ht="186" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E97" s="395"/>
+      <c r="E97" s="501"/>
       <c r="F97" s="159"/>
-      <c r="G97" s="395"/>
-      <c r="H97" s="395"/>
-      <c r="I97" s="395"/>
+      <c r="G97" s="501"/>
+      <c r="H97" s="501"/>
+      <c r="I97" s="501"/>
       <c r="J97" s="199"/>
       <c r="K97" s="199"/>
       <c r="L97" s="199"/>
@@ -16078,11 +16078,11 @@
       <c r="AJ97" s="284"/>
     </row>
     <row r="98" spans="5:36" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E98" s="395"/>
+      <c r="E98" s="501"/>
       <c r="F98" s="159"/>
-      <c r="G98" s="395"/>
-      <c r="H98" s="395"/>
-      <c r="I98" s="395"/>
+      <c r="G98" s="501"/>
+      <c r="H98" s="501"/>
+      <c r="I98" s="501"/>
       <c r="J98" s="199"/>
       <c r="K98" s="199"/>
       <c r="L98" s="199"/>
@@ -16121,69 +16121,116 @@
     </row>
   </sheetData>
   <mergeCells count="197">
-    <mergeCell ref="AX10:AY10"/>
-    <mergeCell ref="BC27:BC28"/>
-    <mergeCell ref="BC29:BC30"/>
-    <mergeCell ref="BC31:BC32"/>
-    <mergeCell ref="BC33:BC34"/>
-    <mergeCell ref="BC35:BC36"/>
-    <mergeCell ref="BC38:BC39"/>
-    <mergeCell ref="BC40:BC41"/>
-    <mergeCell ref="BC11:BC12"/>
-    <mergeCell ref="BC13:BC14"/>
-    <mergeCell ref="BC15:BC16"/>
-    <mergeCell ref="BC17:BC18"/>
-    <mergeCell ref="BC19:BC20"/>
-    <mergeCell ref="BC21:BC22"/>
-    <mergeCell ref="BC23:BC24"/>
-    <mergeCell ref="BC25:BC26"/>
-    <mergeCell ref="BC42:BC43"/>
-    <mergeCell ref="BC44:BC45"/>
-    <mergeCell ref="BC46:BC47"/>
-    <mergeCell ref="BC48:BC49"/>
-    <mergeCell ref="BM40:BM41"/>
-    <mergeCell ref="BM42:BM43"/>
-    <mergeCell ref="BM44:BM45"/>
-    <mergeCell ref="BM46:BM47"/>
-    <mergeCell ref="BO37:BV37"/>
-    <mergeCell ref="BE37:BL37"/>
-    <mergeCell ref="BM48:BM49"/>
-    <mergeCell ref="BM21:BM22"/>
-    <mergeCell ref="BM23:BM24"/>
-    <mergeCell ref="BM25:BM26"/>
-    <mergeCell ref="BM27:BM28"/>
-    <mergeCell ref="BM29:BM30"/>
-    <mergeCell ref="BM31:BM32"/>
-    <mergeCell ref="BM33:BM34"/>
-    <mergeCell ref="BM35:BM36"/>
-    <mergeCell ref="BM38:BM39"/>
-    <mergeCell ref="BW11:BW12"/>
-    <mergeCell ref="BW13:BW14"/>
-    <mergeCell ref="BW15:BW16"/>
-    <mergeCell ref="BW17:BW18"/>
-    <mergeCell ref="BM11:BM12"/>
-    <mergeCell ref="BM13:BM14"/>
-    <mergeCell ref="BM15:BM16"/>
-    <mergeCell ref="BM17:BM18"/>
-    <mergeCell ref="BM19:BM20"/>
-    <mergeCell ref="BW19:BW20"/>
-    <mergeCell ref="BW25:BW26"/>
-    <mergeCell ref="BW27:BW28"/>
-    <mergeCell ref="BW48:BW49"/>
-    <mergeCell ref="BW50:BW51"/>
-    <mergeCell ref="BW52:BW53"/>
-    <mergeCell ref="BW54:BW55"/>
-    <mergeCell ref="BW60:BW61"/>
-    <mergeCell ref="BW29:BW30"/>
-    <mergeCell ref="BW31:BW32"/>
-    <mergeCell ref="BW33:BW34"/>
-    <mergeCell ref="BW35:BW36"/>
-    <mergeCell ref="BW38:BW39"/>
-    <mergeCell ref="BW40:BW41"/>
-    <mergeCell ref="BW42:BW43"/>
-    <mergeCell ref="BW44:BW45"/>
-    <mergeCell ref="BW46:BW47"/>
-    <mergeCell ref="BW56:BW57"/>
+    <mergeCell ref="AS29:AS30"/>
+    <mergeCell ref="AS31:AS32"/>
+    <mergeCell ref="AS33:AS34"/>
+    <mergeCell ref="AS35:AS36"/>
+    <mergeCell ref="AS38:AS39"/>
+    <mergeCell ref="AS40:AS41"/>
+    <mergeCell ref="AS42:AS43"/>
+    <mergeCell ref="AS44:AS45"/>
+    <mergeCell ref="AS46:AS47"/>
+    <mergeCell ref="AS11:AS12"/>
+    <mergeCell ref="AS13:AS14"/>
+    <mergeCell ref="AS15:AS16"/>
+    <mergeCell ref="AS17:AS18"/>
+    <mergeCell ref="AS19:AS20"/>
+    <mergeCell ref="AS21:AS22"/>
+    <mergeCell ref="AS23:AS24"/>
+    <mergeCell ref="AS25:AS26"/>
+    <mergeCell ref="AS27:AS28"/>
+    <mergeCell ref="E96:E98"/>
+    <mergeCell ref="G96:G98"/>
+    <mergeCell ref="H96:H98"/>
+    <mergeCell ref="I96:I98"/>
+    <mergeCell ref="AM77:AQ78"/>
+    <mergeCell ref="G86:H86"/>
+    <mergeCell ref="AT69:AW71"/>
+    <mergeCell ref="AT74:AY76"/>
+    <mergeCell ref="BB74:BB76"/>
+    <mergeCell ref="O66:U78"/>
+    <mergeCell ref="AA67:AC71"/>
+    <mergeCell ref="AD88:AE88"/>
+    <mergeCell ref="AD89:AE89"/>
+    <mergeCell ref="R91:S91"/>
+    <mergeCell ref="T91:U91"/>
+    <mergeCell ref="V91:W91"/>
+    <mergeCell ref="X88:X89"/>
+    <mergeCell ref="Y88:Y89"/>
+    <mergeCell ref="Z88:Z89"/>
+    <mergeCell ref="AA88:AA89"/>
+    <mergeCell ref="AB88:AB89"/>
+    <mergeCell ref="AC88:AC89"/>
+    <mergeCell ref="R88:R89"/>
+    <mergeCell ref="S88:S89"/>
+    <mergeCell ref="A92:A94"/>
+    <mergeCell ref="R92:S92"/>
+    <mergeCell ref="T92:U92"/>
+    <mergeCell ref="V92:W92"/>
+    <mergeCell ref="Y92:Z92"/>
+    <mergeCell ref="E86:F86"/>
+    <mergeCell ref="A88:A90"/>
+    <mergeCell ref="K83:O86"/>
+    <mergeCell ref="B84:D86"/>
+    <mergeCell ref="E84:F84"/>
+    <mergeCell ref="G84:H84"/>
+    <mergeCell ref="I84:J86"/>
+    <mergeCell ref="E85:F85"/>
+    <mergeCell ref="G85:H85"/>
+    <mergeCell ref="S93:T93"/>
+    <mergeCell ref="V93:W93"/>
+    <mergeCell ref="X93:Y93"/>
+    <mergeCell ref="R90:S90"/>
+    <mergeCell ref="T90:U90"/>
+    <mergeCell ref="V90:W90"/>
+    <mergeCell ref="T88:T89"/>
+    <mergeCell ref="U88:U89"/>
+    <mergeCell ref="V88:V89"/>
+    <mergeCell ref="W88:W89"/>
+    <mergeCell ref="E58:G65"/>
+    <mergeCell ref="BW58:BW59"/>
+    <mergeCell ref="BW62:BW63"/>
+    <mergeCell ref="BW64:BW65"/>
+    <mergeCell ref="BD74:BD76"/>
+    <mergeCell ref="BC58:BC59"/>
+    <mergeCell ref="O56:U65"/>
+    <mergeCell ref="BC56:BC57"/>
+    <mergeCell ref="AT66:AW66"/>
+    <mergeCell ref="BV84:BV86"/>
+    <mergeCell ref="AB74:AC75"/>
+    <mergeCell ref="O50:P50"/>
+    <mergeCell ref="O51:P51"/>
+    <mergeCell ref="BM50:BM51"/>
+    <mergeCell ref="BM52:BM53"/>
+    <mergeCell ref="BC50:BC51"/>
+    <mergeCell ref="BC52:BC53"/>
+    <mergeCell ref="BC54:BC55"/>
+    <mergeCell ref="BM54:BM55"/>
+    <mergeCell ref="BM56:BM57"/>
+    <mergeCell ref="BM58:BM59"/>
+    <mergeCell ref="BM60:BM61"/>
+    <mergeCell ref="O52:P52"/>
+    <mergeCell ref="AS48:AS49"/>
+    <mergeCell ref="AS50:AS51"/>
+    <mergeCell ref="AS52:AS53"/>
+    <mergeCell ref="AS54:AS55"/>
+    <mergeCell ref="AS56:AS57"/>
+    <mergeCell ref="E45:M45"/>
+    <mergeCell ref="O45:U45"/>
+    <mergeCell ref="AA45:AC45"/>
+    <mergeCell ref="AD45:AF45"/>
+    <mergeCell ref="O46:O47"/>
+    <mergeCell ref="E52:F53"/>
+    <mergeCell ref="G52:G53"/>
+    <mergeCell ref="O19:U22"/>
+    <mergeCell ref="A20:B22"/>
+    <mergeCell ref="E22:G23"/>
+    <mergeCell ref="A23:B25"/>
+    <mergeCell ref="O23:U26"/>
+    <mergeCell ref="E24:G26"/>
+    <mergeCell ref="A26:B28"/>
+    <mergeCell ref="O27:U44"/>
+    <mergeCell ref="E28:G32"/>
     <mergeCell ref="BW21:BW22"/>
     <mergeCell ref="E1:F2"/>
     <mergeCell ref="G1:I2"/>
@@ -16208,116 +16255,69 @@
     <mergeCell ref="E42:G43"/>
     <mergeCell ref="E44:G44"/>
     <mergeCell ref="F18:G20"/>
-    <mergeCell ref="O19:U22"/>
-    <mergeCell ref="A20:B22"/>
-    <mergeCell ref="E22:G23"/>
-    <mergeCell ref="A23:B25"/>
-    <mergeCell ref="O23:U26"/>
-    <mergeCell ref="E24:G26"/>
-    <mergeCell ref="A26:B28"/>
-    <mergeCell ref="O27:U44"/>
-    <mergeCell ref="E28:G32"/>
-    <mergeCell ref="AS48:AS49"/>
-    <mergeCell ref="AS50:AS51"/>
-    <mergeCell ref="AS52:AS53"/>
-    <mergeCell ref="AS54:AS55"/>
-    <mergeCell ref="AS56:AS57"/>
-    <mergeCell ref="E45:M45"/>
-    <mergeCell ref="O45:U45"/>
-    <mergeCell ref="AA45:AC45"/>
-    <mergeCell ref="AD45:AF45"/>
-    <mergeCell ref="O46:O47"/>
-    <mergeCell ref="E52:F53"/>
-    <mergeCell ref="G52:G53"/>
-    <mergeCell ref="BV84:BV86"/>
-    <mergeCell ref="AB74:AC75"/>
-    <mergeCell ref="O50:P50"/>
-    <mergeCell ref="O51:P51"/>
-    <mergeCell ref="BM50:BM51"/>
-    <mergeCell ref="BM52:BM53"/>
-    <mergeCell ref="BC50:BC51"/>
-    <mergeCell ref="BC52:BC53"/>
-    <mergeCell ref="BC54:BC55"/>
-    <mergeCell ref="BM54:BM55"/>
-    <mergeCell ref="BM56:BM57"/>
-    <mergeCell ref="BM58:BM59"/>
-    <mergeCell ref="BM60:BM61"/>
-    <mergeCell ref="O52:P52"/>
-    <mergeCell ref="E58:G65"/>
-    <mergeCell ref="BW58:BW59"/>
-    <mergeCell ref="BW62:BW63"/>
-    <mergeCell ref="BW64:BW65"/>
-    <mergeCell ref="BD74:BD76"/>
-    <mergeCell ref="BC58:BC59"/>
-    <mergeCell ref="O56:U65"/>
-    <mergeCell ref="BC56:BC57"/>
-    <mergeCell ref="AT66:AW66"/>
-    <mergeCell ref="A92:A94"/>
-    <mergeCell ref="R92:S92"/>
-    <mergeCell ref="T92:U92"/>
-    <mergeCell ref="V92:W92"/>
-    <mergeCell ref="Y92:Z92"/>
-    <mergeCell ref="E86:F86"/>
-    <mergeCell ref="A88:A90"/>
-    <mergeCell ref="K83:O86"/>
-    <mergeCell ref="B84:D86"/>
-    <mergeCell ref="E84:F84"/>
-    <mergeCell ref="G84:H84"/>
-    <mergeCell ref="I84:J86"/>
-    <mergeCell ref="E85:F85"/>
-    <mergeCell ref="G85:H85"/>
-    <mergeCell ref="S93:T93"/>
-    <mergeCell ref="V93:W93"/>
-    <mergeCell ref="X93:Y93"/>
-    <mergeCell ref="R90:S90"/>
-    <mergeCell ref="T90:U90"/>
-    <mergeCell ref="V90:W90"/>
-    <mergeCell ref="T88:T89"/>
-    <mergeCell ref="U88:U89"/>
-    <mergeCell ref="V88:V89"/>
-    <mergeCell ref="W88:W89"/>
-    <mergeCell ref="E96:E98"/>
-    <mergeCell ref="G96:G98"/>
-    <mergeCell ref="H96:H98"/>
-    <mergeCell ref="I96:I98"/>
-    <mergeCell ref="AM77:AQ78"/>
-    <mergeCell ref="G86:H86"/>
-    <mergeCell ref="AT69:AW71"/>
-    <mergeCell ref="AT74:AY76"/>
-    <mergeCell ref="BB74:BB76"/>
-    <mergeCell ref="O66:U78"/>
-    <mergeCell ref="AA67:AC71"/>
-    <mergeCell ref="AD88:AE88"/>
-    <mergeCell ref="AD89:AE89"/>
-    <mergeCell ref="R91:S91"/>
-    <mergeCell ref="T91:U91"/>
-    <mergeCell ref="V91:W91"/>
-    <mergeCell ref="X88:X89"/>
-    <mergeCell ref="Y88:Y89"/>
-    <mergeCell ref="Z88:Z89"/>
-    <mergeCell ref="AA88:AA89"/>
-    <mergeCell ref="AB88:AB89"/>
-    <mergeCell ref="AC88:AC89"/>
-    <mergeCell ref="R88:R89"/>
-    <mergeCell ref="S88:S89"/>
-    <mergeCell ref="AS11:AS12"/>
-    <mergeCell ref="AS13:AS14"/>
-    <mergeCell ref="AS15:AS16"/>
-    <mergeCell ref="AS17:AS18"/>
-    <mergeCell ref="AS19:AS20"/>
-    <mergeCell ref="AS21:AS22"/>
-    <mergeCell ref="AS23:AS24"/>
-    <mergeCell ref="AS25:AS26"/>
-    <mergeCell ref="AS27:AS28"/>
-    <mergeCell ref="AS29:AS30"/>
-    <mergeCell ref="AS31:AS32"/>
-    <mergeCell ref="AS33:AS34"/>
-    <mergeCell ref="AS35:AS36"/>
-    <mergeCell ref="AS38:AS39"/>
-    <mergeCell ref="AS40:AS41"/>
-    <mergeCell ref="AS42:AS43"/>
-    <mergeCell ref="AS44:AS45"/>
-    <mergeCell ref="AS46:AS47"/>
+    <mergeCell ref="BW25:BW26"/>
+    <mergeCell ref="BW27:BW28"/>
+    <mergeCell ref="BW48:BW49"/>
+    <mergeCell ref="BW50:BW51"/>
+    <mergeCell ref="BW52:BW53"/>
+    <mergeCell ref="BW54:BW55"/>
+    <mergeCell ref="BW60:BW61"/>
+    <mergeCell ref="BW29:BW30"/>
+    <mergeCell ref="BW31:BW32"/>
+    <mergeCell ref="BW33:BW34"/>
+    <mergeCell ref="BW35:BW36"/>
+    <mergeCell ref="BW38:BW39"/>
+    <mergeCell ref="BW40:BW41"/>
+    <mergeCell ref="BW42:BW43"/>
+    <mergeCell ref="BW44:BW45"/>
+    <mergeCell ref="BW46:BW47"/>
+    <mergeCell ref="BW56:BW57"/>
+    <mergeCell ref="BW11:BW12"/>
+    <mergeCell ref="BW13:BW14"/>
+    <mergeCell ref="BW15:BW16"/>
+    <mergeCell ref="BW17:BW18"/>
+    <mergeCell ref="BM11:BM12"/>
+    <mergeCell ref="BM13:BM14"/>
+    <mergeCell ref="BM15:BM16"/>
+    <mergeCell ref="BM17:BM18"/>
+    <mergeCell ref="BM19:BM20"/>
+    <mergeCell ref="BW19:BW20"/>
+    <mergeCell ref="BM21:BM22"/>
+    <mergeCell ref="BM23:BM24"/>
+    <mergeCell ref="BM25:BM26"/>
+    <mergeCell ref="BM27:BM28"/>
+    <mergeCell ref="BM29:BM30"/>
+    <mergeCell ref="BM31:BM32"/>
+    <mergeCell ref="BM33:BM34"/>
+    <mergeCell ref="BM35:BM36"/>
+    <mergeCell ref="BM38:BM39"/>
+    <mergeCell ref="BC42:BC43"/>
+    <mergeCell ref="BC44:BC45"/>
+    <mergeCell ref="BC46:BC47"/>
+    <mergeCell ref="BC48:BC49"/>
+    <mergeCell ref="BM40:BM41"/>
+    <mergeCell ref="BM42:BM43"/>
+    <mergeCell ref="BM44:BM45"/>
+    <mergeCell ref="BM46:BM47"/>
+    <mergeCell ref="BO37:BV37"/>
+    <mergeCell ref="BE37:BL37"/>
+    <mergeCell ref="BM48:BM49"/>
+    <mergeCell ref="AX10:AY10"/>
+    <mergeCell ref="BC27:BC28"/>
+    <mergeCell ref="BC29:BC30"/>
+    <mergeCell ref="BC31:BC32"/>
+    <mergeCell ref="BC33:BC34"/>
+    <mergeCell ref="BC35:BC36"/>
+    <mergeCell ref="BC38:BC39"/>
+    <mergeCell ref="BC40:BC41"/>
+    <mergeCell ref="BC11:BC12"/>
+    <mergeCell ref="BC13:BC14"/>
+    <mergeCell ref="BC15:BC16"/>
+    <mergeCell ref="BC17:BC18"/>
+    <mergeCell ref="BC19:BC20"/>
+    <mergeCell ref="BC21:BC22"/>
+    <mergeCell ref="BC23:BC24"/>
+    <mergeCell ref="BC25:BC26"/>
   </mergeCells>
   <phoneticPr fontId="24" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\모듈러사업2실\★ 300. 제1공장_마감관리팀\350. 마감진행현황\BH(수정)\2026년 10월 BH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73527249-2650-4CF2-9293-F618004AEEE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3881910D-7BA8-4F9E-AE18-32F5448F198D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="788" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="676">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="675">
   <si>
     <t>공업화 주택 샘플</t>
   </si>
@@ -512,13 +512,6 @@
     <phoneticPr fontId="24" type="noConversion"/>
   </si>
   <si>
-    <t>401-7-9/
-26SA01
-NONE
-2026-6-18</t>
-    <phoneticPr fontId="24" type="noConversion"/>
-  </si>
-  <si>
     <t>401-15-2/
 46SB42
 NONE
@@ -967,13 +960,6 @@
     <phoneticPr fontId="24" type="noConversion"/>
   </si>
   <si>
-    <t>401-6-13/
-26SA03
-NONE
-2026-4-27</t>
-    <phoneticPr fontId="24" type="noConversion"/>
-  </si>
-  <si>
     <t>401-7-13/
 26SA03
 NONE
@@ -1037,13 +1023,6 @@
     <phoneticPr fontId="24" type="noConversion"/>
   </si>
   <si>
-    <t>401-12-13/
-26SA03
-NONE
-2026-6-1</t>
-    <phoneticPr fontId="24" type="noConversion"/>
-  </si>
-  <si>
     <t>401-10-13/
 26SA03
 NONE
@@ -1055,13 +1034,6 @@
 26SA03
 NONE
 2026-5-26</t>
-    <phoneticPr fontId="24" type="noConversion"/>
-  </si>
-  <si>
-    <t>401-7-7/
-26SA01
-NONE
-2026-6-4</t>
     <phoneticPr fontId="24" type="noConversion"/>
   </si>
   <si>
@@ -1709,13 +1681,6 @@
     <phoneticPr fontId="24" type="noConversion"/>
   </si>
   <si>
-    <t>401-6-14/
-26SA74
-26A(B-1)
-2026-5-26</t>
-    <phoneticPr fontId="24" type="noConversion"/>
-  </si>
-  <si>
     <t>401-8-14/
 26SA74
 26A(B-1)
@@ -1804,13 +1769,6 @@
 26SA04
 26A(B-1)
 2026-4-22</t>
-    <phoneticPr fontId="24" type="noConversion"/>
-  </si>
-  <si>
-    <t>401-16-13/
-26SA03
-NONE
-2026-5-28</t>
     <phoneticPr fontId="24" type="noConversion"/>
   </si>
   <si>
@@ -4316,6 +4274,38 @@
 26SB73
 36B(B-1)
 2026-10-1</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>401-12-13/
+26SA03
+NONE
+2026-5-28</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>401-16-13/
+26SA03
+NONE
+2026-6-1</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>402-1-4/
+36SB42
+2026-10-15</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>402-12-8/
+26SB62
+2026-10-15</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>403-16-5
+26SB61
+2026-10-15</t>
     <phoneticPr fontId="24" type="noConversion"/>
   </si>
 </sst>
@@ -5645,7 +5635,7 @@
     </xf>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="593">
+  <cellXfs count="596">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6735,9 +6725,6 @@
     <xf numFmtId="0" fontId="55" fillId="24" borderId="9" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="24" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="55" fillId="12" borderId="2" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -6823,6 +6810,18 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="55" fillId="26" borderId="9" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="25" borderId="2" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="25" borderId="9" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="25" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="26" borderId="2" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="16" borderId="13" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7766,31 +7765,31 @@
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
-      <c r="E1" s="402"/>
-      <c r="F1" s="403"/>
-      <c r="G1" s="402"/>
-      <c r="H1" s="406"/>
-      <c r="I1" s="403"/>
-      <c r="J1" s="402"/>
-      <c r="K1" s="406"/>
-      <c r="L1" s="406"/>
-      <c r="M1" s="406"/>
-      <c r="N1" s="406"/>
-      <c r="O1" s="406"/>
-      <c r="P1" s="403"/>
+      <c r="E1" s="405"/>
+      <c r="F1" s="406"/>
+      <c r="G1" s="405"/>
+      <c r="H1" s="409"/>
+      <c r="I1" s="406"/>
+      <c r="J1" s="405"/>
+      <c r="K1" s="409"/>
+      <c r="L1" s="409"/>
+      <c r="M1" s="409"/>
+      <c r="N1" s="409"/>
+      <c r="O1" s="409"/>
+      <c r="P1" s="406"/>
       <c r="Q1" s="3"/>
-      <c r="R1" s="408"/>
-      <c r="S1" s="400"/>
-      <c r="T1" s="409" t="s">
+      <c r="R1" s="411"/>
+      <c r="S1" s="403"/>
+      <c r="T1" s="412" t="s">
         <v>16</v>
       </c>
-      <c r="U1" s="410"/>
-      <c r="V1" s="410"/>
-      <c r="W1" s="410"/>
-      <c r="X1" s="410"/>
-      <c r="Y1" s="410"/>
-      <c r="Z1" s="410"/>
-      <c r="AA1" s="411"/>
+      <c r="U1" s="413"/>
+      <c r="V1" s="413"/>
+      <c r="W1" s="413"/>
+      <c r="X1" s="413"/>
+      <c r="Y1" s="413"/>
+      <c r="Z1" s="413"/>
+      <c r="AA1" s="414"/>
       <c r="AB1" s="4"/>
       <c r="AC1" s="5"/>
       <c r="AI1" s="7"/>
@@ -7812,7 +7811,7 @@
       <c r="AY1" s="16"/>
       <c r="AZ1" s="16"/>
       <c r="BA1" s="16"/>
-      <c r="BB1" s="415" t="s">
+      <c r="BB1" s="418" t="s">
         <v>4</v>
       </c>
       <c r="BC1" s="17"/>
@@ -7831,32 +7830,32 @@
       <c r="B2" s="23"/>
       <c r="C2" s="23"/>
       <c r="D2" s="23"/>
-      <c r="E2" s="404"/>
-      <c r="F2" s="405"/>
-      <c r="G2" s="404"/>
-      <c r="H2" s="407"/>
-      <c r="I2" s="405"/>
-      <c r="J2" s="404"/>
-      <c r="K2" s="407"/>
-      <c r="L2" s="407"/>
-      <c r="M2" s="407"/>
-      <c r="N2" s="407"/>
-      <c r="O2" s="407"/>
-      <c r="P2" s="405"/>
+      <c r="E2" s="407"/>
+      <c r="F2" s="408"/>
+      <c r="G2" s="407"/>
+      <c r="H2" s="410"/>
+      <c r="I2" s="408"/>
+      <c r="J2" s="407"/>
+      <c r="K2" s="410"/>
+      <c r="L2" s="410"/>
+      <c r="M2" s="410"/>
+      <c r="N2" s="410"/>
+      <c r="O2" s="410"/>
+      <c r="P2" s="408"/>
       <c r="Q2" s="3"/>
-      <c r="R2" s="400"/>
-      <c r="S2" s="400"/>
-      <c r="T2" s="412"/>
-      <c r="U2" s="413"/>
-      <c r="V2" s="413"/>
-      <c r="W2" s="413"/>
-      <c r="X2" s="413"/>
-      <c r="Y2" s="413"/>
-      <c r="Z2" s="413"/>
-      <c r="AA2" s="414"/>
+      <c r="R2" s="403"/>
+      <c r="S2" s="403"/>
+      <c r="T2" s="415"/>
+      <c r="U2" s="416"/>
+      <c r="V2" s="416"/>
+      <c r="W2" s="416"/>
+      <c r="X2" s="416"/>
+      <c r="Y2" s="416"/>
+      <c r="Z2" s="416"/>
+      <c r="AA2" s="417"/>
       <c r="AB2" s="24"/>
       <c r="AC2" s="5"/>
-      <c r="AI2" s="417" t="s">
+      <c r="AI2" s="420" t="s">
         <v>17</v>
       </c>
       <c r="AJ2" s="25"/>
@@ -7877,7 +7876,7 @@
       <c r="AY2" s="32"/>
       <c r="AZ2" s="32"/>
       <c r="BA2" s="32"/>
-      <c r="BB2" s="416"/>
+      <c r="BB2" s="419"/>
       <c r="BC2" s="33"/>
       <c r="BD2" s="33"/>
       <c r="BE2" s="34"/>
@@ -7916,21 +7915,21 @@
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
       <c r="S3" s="5"/>
-      <c r="T3" s="420" t="s">
+      <c r="T3" s="423" t="s">
         <v>18</v>
       </c>
-      <c r="U3" s="421"/>
-      <c r="V3" s="422"/>
+      <c r="U3" s="424"/>
+      <c r="V3" s="425"/>
       <c r="W3" s="41"/>
       <c r="X3" s="41"/>
-      <c r="Y3" s="423" t="s">
+      <c r="Y3" s="426" t="s">
         <v>18</v>
       </c>
-      <c r="Z3" s="424"/>
-      <c r="AA3" s="424"/>
-      <c r="AB3" s="425"/>
+      <c r="Z3" s="427"/>
+      <c r="AA3" s="427"/>
+      <c r="AB3" s="428"/>
       <c r="AC3" s="42"/>
-      <c r="AI3" s="418"/>
+      <c r="AI3" s="421"/>
       <c r="AJ3" s="43"/>
       <c r="AK3" s="26"/>
       <c r="AL3" s="26"/>
@@ -7975,7 +7974,7 @@
       <c r="AA4" s="50"/>
       <c r="AB4" s="41"/>
       <c r="AC4" s="42"/>
-      <c r="AI4" s="418"/>
+      <c r="AI4" s="421"/>
       <c r="AJ4" s="43"/>
       <c r="AK4" s="26"/>
       <c r="AL4" s="26"/>
@@ -8021,7 +8020,7 @@
       <c r="AA5" s="50"/>
       <c r="AB5" s="41"/>
       <c r="AC5" s="53"/>
-      <c r="AI5" s="419"/>
+      <c r="AI5" s="422"/>
       <c r="AJ5" s="54"/>
       <c r="AK5" s="55"/>
       <c r="AL5" s="55"/>
@@ -8274,102 +8273,102 @@
       <c r="AI9" s="44"/>
       <c r="AJ9" s="44"/>
       <c r="AK9" s="21" t="s">
+        <v>541</v>
+      </c>
+      <c r="AL9" s="21" t="s">
+        <v>542</v>
+      </c>
+      <c r="AM9" s="21" t="s">
+        <v>543</v>
+      </c>
+      <c r="AN9" s="21" t="s">
+        <v>544</v>
+      </c>
+      <c r="AO9" s="21" t="s">
+        <v>545</v>
+      </c>
+      <c r="AP9" s="21" t="s">
+        <v>548</v>
+      </c>
+      <c r="AQ9" s="21" t="s">
+        <v>546</v>
+      </c>
+      <c r="AR9" s="21" t="s">
         <v>547</v>
-      </c>
-      <c r="AL9" s="21" t="s">
-        <v>548</v>
-      </c>
-      <c r="AM9" s="21" t="s">
-        <v>549</v>
-      </c>
-      <c r="AN9" s="21" t="s">
-        <v>550</v>
-      </c>
-      <c r="AO9" s="21" t="s">
-        <v>551</v>
-      </c>
-      <c r="AP9" s="21" t="s">
-        <v>554</v>
-      </c>
-      <c r="AQ9" s="21" t="s">
-        <v>552</v>
-      </c>
-      <c r="AR9" s="21" t="s">
-        <v>553</v>
       </c>
       <c r="AS9" s="62"/>
       <c r="AT9" s="44"/>
       <c r="AU9" s="21" t="s">
+        <v>389</v>
+      </c>
+      <c r="AV9" s="21" t="s">
+        <v>390</v>
+      </c>
+      <c r="AW9" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="AX9" s="21" t="s">
+        <v>392</v>
+      </c>
+      <c r="AY9" s="21" t="s">
+        <v>393</v>
+      </c>
+      <c r="AZ9" s="21" t="s">
+        <v>394</v>
+      </c>
+      <c r="BA9" s="21" t="s">
         <v>395</v>
       </c>
-      <c r="AV9" s="21" t="s">
+      <c r="BB9" s="21" t="s">
         <v>396</v>
       </c>
-      <c r="AW9" s="21" t="s">
-        <v>397</v>
-      </c>
-      <c r="AX9" s="21" t="s">
-        <v>398</v>
-      </c>
-      <c r="AY9" s="21" t="s">
-        <v>399</v>
-      </c>
-      <c r="AZ9" s="21" t="s">
-        <v>400</v>
-      </c>
-      <c r="BA9" s="21" t="s">
-        <v>401</v>
-      </c>
-      <c r="BB9" s="21" t="s">
-        <v>402</v>
-      </c>
       <c r="BE9" s="21" t="s">
+        <v>381</v>
+      </c>
+      <c r="BF9" s="21" t="s">
+        <v>382</v>
+      </c>
+      <c r="BG9" s="21" t="s">
+        <v>383</v>
+      </c>
+      <c r="BH9" s="21" t="s">
+        <v>384</v>
+      </c>
+      <c r="BI9" s="21" t="s">
+        <v>385</v>
+      </c>
+      <c r="BJ9" s="21" t="s">
+        <v>386</v>
+      </c>
+      <c r="BK9" s="21" t="s">
         <v>387</v>
       </c>
-      <c r="BF9" s="21" t="s">
+      <c r="BL9" s="21" t="s">
         <v>388</v>
       </c>
-      <c r="BG9" s="21" t="s">
-        <v>389</v>
-      </c>
-      <c r="BH9" s="21" t="s">
-        <v>390</v>
-      </c>
-      <c r="BI9" s="21" t="s">
-        <v>391</v>
-      </c>
-      <c r="BJ9" s="21" t="s">
-        <v>392</v>
-      </c>
-      <c r="BK9" s="21" t="s">
-        <v>393</v>
-      </c>
-      <c r="BL9" s="21" t="s">
-        <v>394</v>
-      </c>
       <c r="BO9" s="21" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="BP9" s="21" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="BQ9" s="21" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="BR9" s="21" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="BS9" s="21" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="BT9" s="21" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="BU9" s="21" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="BV9" s="21" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
     </row>
     <row r="10" spans="1:76" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -8403,52 +8402,52 @@
       <c r="AH10" s="59"/>
       <c r="AI10" s="44"/>
       <c r="AJ10" s="354"/>
-      <c r="AK10" s="426" t="s">
+      <c r="AK10" s="429" t="s">
         <v>7</v>
       </c>
-      <c r="AL10" s="393"/>
-      <c r="AM10" s="393"/>
-      <c r="AN10" s="393"/>
-      <c r="AO10" s="393"/>
-      <c r="AP10" s="393"/>
-      <c r="AQ10" s="393"/>
-      <c r="AR10" s="427"/>
+      <c r="AL10" s="396"/>
+      <c r="AM10" s="396"/>
+      <c r="AN10" s="396"/>
+      <c r="AO10" s="396"/>
+      <c r="AP10" s="396"/>
+      <c r="AQ10" s="396"/>
+      <c r="AR10" s="430"/>
       <c r="AS10" s="3"/>
       <c r="AT10" s="354"/>
       <c r="AU10" s="324"/>
       <c r="AV10" s="325"/>
       <c r="AW10" s="325"/>
-      <c r="AX10" s="393" t="s">
+      <c r="AX10" s="396" t="s">
         <v>8</v>
       </c>
-      <c r="AY10" s="393"/>
+      <c r="AY10" s="396"/>
       <c r="AZ10" s="325"/>
       <c r="BA10" s="325"/>
       <c r="BB10" s="326"/>
       <c r="BC10" s="3"/>
       <c r="BD10" s="350"/>
-      <c r="BE10" s="428" t="s">
+      <c r="BE10" s="431" t="s">
         <v>9</v>
       </c>
-      <c r="BF10" s="429"/>
-      <c r="BG10" s="429"/>
-      <c r="BH10" s="429"/>
-      <c r="BI10" s="429"/>
-      <c r="BJ10" s="429"/>
-      <c r="BK10" s="429"/>
-      <c r="BL10" s="430"/>
+      <c r="BF10" s="432"/>
+      <c r="BG10" s="432"/>
+      <c r="BH10" s="432"/>
+      <c r="BI10" s="432"/>
+      <c r="BJ10" s="432"/>
+      <c r="BK10" s="432"/>
+      <c r="BL10" s="433"/>
       <c r="BM10" s="314"/>
       <c r="BN10" s="344"/>
-      <c r="BO10" s="428" t="s">
+      <c r="BO10" s="431" t="s">
         <v>10</v>
       </c>
-      <c r="BP10" s="429"/>
-      <c r="BQ10" s="429"/>
-      <c r="BR10" s="429"/>
-      <c r="BS10" s="429"/>
-      <c r="BT10" s="429"/>
-      <c r="BU10" s="429"/>
-      <c r="BV10" s="430"/>
+      <c r="BP10" s="432"/>
+      <c r="BQ10" s="432"/>
+      <c r="BR10" s="432"/>
+      <c r="BS10" s="432"/>
+      <c r="BT10" s="432"/>
+      <c r="BU10" s="432"/>
+      <c r="BV10" s="433"/>
       <c r="BX10" s="348"/>
     </row>
     <row r="11" spans="1:76" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -8461,28 +8460,28 @@
       </c>
       <c r="F11" s="72"/>
       <c r="G11" s="72"/>
-      <c r="H11" s="431" t="s">
+      <c r="H11" s="434" t="s">
         <v>21</v>
       </c>
-      <c r="I11" s="432"/>
-      <c r="J11" s="431" t="s">
+      <c r="I11" s="435"/>
+      <c r="J11" s="434" t="s">
         <v>22</v>
       </c>
-      <c r="K11" s="432"/>
-      <c r="L11" s="438" t="s">
+      <c r="K11" s="435"/>
+      <c r="L11" s="441" t="s">
         <v>23</v>
       </c>
-      <c r="M11" s="438"/>
+      <c r="M11" s="441"/>
       <c r="N11" s="73"/>
-      <c r="O11" s="440" t="s">
+      <c r="O11" s="443" t="s">
         <v>24</v>
       </c>
-      <c r="P11" s="441"/>
-      <c r="Q11" s="441"/>
-      <c r="R11" s="441"/>
-      <c r="S11" s="441"/>
-      <c r="T11" s="441"/>
-      <c r="U11" s="441"/>
+      <c r="P11" s="444"/>
+      <c r="Q11" s="444"/>
+      <c r="R11" s="444"/>
+      <c r="S11" s="444"/>
+      <c r="T11" s="444"/>
+      <c r="U11" s="444"/>
       <c r="V11" s="74"/>
       <c r="W11" s="75"/>
       <c r="X11" s="75"/>
@@ -8498,27 +8497,27 @@
       <c r="AH11" s="59"/>
       <c r="AI11" s="44"/>
       <c r="AJ11" s="351" t="s">
-        <v>300</v>
-      </c>
-      <c r="AK11" s="391" t="s">
-        <v>612</v>
-      </c>
-      <c r="AL11" s="391" t="s">
-        <v>632</v>
+        <v>294</v>
+      </c>
+      <c r="AK11" s="390" t="s">
+        <v>606</v>
+      </c>
+      <c r="AL11" s="390" t="s">
+        <v>626</v>
       </c>
       <c r="AM11" s="312"/>
       <c r="AN11" s="312"/>
       <c r="AO11" s="312"/>
-      <c r="AP11" s="371" t="s">
-        <v>636</v>
+      <c r="AP11" s="370" t="s">
+        <v>630</v>
       </c>
       <c r="AQ11" s="312"/>
       <c r="AR11" s="312"/>
-      <c r="AS11" s="394" t="s">
-        <v>533</v>
+      <c r="AS11" s="397" t="s">
+        <v>527</v>
       </c>
       <c r="AT11" s="351" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AU11" s="312"/>
       <c r="AV11" s="312"/>
@@ -8528,11 +8527,11 @@
       <c r="AZ11" s="312"/>
       <c r="BA11" s="312"/>
       <c r="BB11" s="312"/>
-      <c r="BC11" s="394" t="s">
-        <v>355</v>
+      <c r="BC11" s="397" t="s">
+        <v>349</v>
       </c>
       <c r="BD11" s="351" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="BE11" s="312"/>
       <c r="BF11" s="312"/>
@@ -8542,11 +8541,11 @@
       <c r="BJ11" s="312"/>
       <c r="BK11" s="312"/>
       <c r="BL11" s="312"/>
-      <c r="BM11" s="394" t="s">
-        <v>329</v>
+      <c r="BM11" s="397" t="s">
+        <v>323</v>
       </c>
       <c r="BN11" s="345" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="BO11" s="312"/>
       <c r="BP11" s="312"/>
@@ -8556,8 +8555,8 @@
       <c r="BT11" s="312"/>
       <c r="BU11" s="312"/>
       <c r="BV11" s="312"/>
-      <c r="BW11" s="394" t="s">
-        <v>301</v>
+      <c r="BW11" s="397" t="s">
+        <v>295</v>
       </c>
       <c r="BX11" s="348"/>
     </row>
@@ -8567,20 +8566,20 @@
       <c r="E12" s="78"/>
       <c r="F12" s="79"/>
       <c r="G12" s="79"/>
-      <c r="H12" s="433"/>
-      <c r="I12" s="434"/>
-      <c r="J12" s="433"/>
-      <c r="K12" s="434"/>
-      <c r="L12" s="435"/>
-      <c r="M12" s="435"/>
+      <c r="H12" s="436"/>
+      <c r="I12" s="437"/>
+      <c r="J12" s="436"/>
+      <c r="K12" s="437"/>
+      <c r="L12" s="438"/>
+      <c r="M12" s="438"/>
       <c r="N12" s="81"/>
-      <c r="O12" s="442"/>
-      <c r="P12" s="443"/>
-      <c r="Q12" s="443"/>
-      <c r="R12" s="443"/>
-      <c r="S12" s="443"/>
-      <c r="T12" s="443"/>
-      <c r="U12" s="443"/>
+      <c r="O12" s="445"/>
+      <c r="P12" s="446"/>
+      <c r="Q12" s="446"/>
+      <c r="R12" s="446"/>
+      <c r="S12" s="446"/>
+      <c r="T12" s="446"/>
+      <c r="U12" s="446"/>
       <c r="V12" s="82"/>
       <c r="W12" s="53"/>
       <c r="X12" s="53"/>
@@ -8597,24 +8596,24 @@
       <c r="AI12" s="44"/>
       <c r="AJ12" s="351"/>
       <c r="AK12" s="361" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="AL12" s="361" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="AM12" s="313"/>
       <c r="AN12" s="313"/>
       <c r="AO12" s="313"/>
       <c r="AP12" s="359" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="AQ12" s="359" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="AR12" s="359" t="s">
-        <v>566</v>
-      </c>
-      <c r="AS12" s="394"/>
+        <v>560</v>
+      </c>
+      <c r="AS12" s="397"/>
       <c r="AT12" s="351"/>
       <c r="AU12" s="313"/>
       <c r="AV12" s="313"/>
@@ -8624,7 +8623,7 @@
       <c r="AZ12" s="313"/>
       <c r="BA12" s="313"/>
       <c r="BB12" s="313"/>
-      <c r="BC12" s="394"/>
+      <c r="BC12" s="397"/>
       <c r="BD12" s="351"/>
       <c r="BE12" s="313"/>
       <c r="BF12" s="313"/>
@@ -8634,13 +8633,13 @@
       <c r="BJ12" s="313"/>
       <c r="BK12" s="313"/>
       <c r="BL12" s="313"/>
-      <c r="BM12" s="394"/>
+      <c r="BM12" s="397"/>
       <c r="BN12" s="345"/>
       <c r="BO12" s="362" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="BP12" s="320" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="BQ12" s="313"/>
       <c r="BR12" s="313"/>
@@ -8648,7 +8647,7 @@
       <c r="BT12" s="313"/>
       <c r="BU12" s="313"/>
       <c r="BV12" s="313"/>
-      <c r="BW12" s="394"/>
+      <c r="BW12" s="397"/>
       <c r="BX12" s="348"/>
     </row>
     <row r="13" spans="1:76" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -8657,20 +8656,20 @@
       <c r="E13" s="78"/>
       <c r="F13" s="79"/>
       <c r="G13" s="79"/>
-      <c r="H13" s="433"/>
-      <c r="I13" s="434"/>
-      <c r="J13" s="433"/>
-      <c r="K13" s="434"/>
-      <c r="L13" s="435"/>
-      <c r="M13" s="435"/>
+      <c r="H13" s="436"/>
+      <c r="I13" s="437"/>
+      <c r="J13" s="436"/>
+      <c r="K13" s="437"/>
+      <c r="L13" s="438"/>
+      <c r="M13" s="438"/>
       <c r="N13" s="81"/>
-      <c r="O13" s="442"/>
-      <c r="P13" s="443"/>
-      <c r="Q13" s="443"/>
-      <c r="R13" s="443"/>
-      <c r="S13" s="443"/>
-      <c r="T13" s="443"/>
-      <c r="U13" s="443"/>
+      <c r="O13" s="445"/>
+      <c r="P13" s="446"/>
+      <c r="Q13" s="446"/>
+      <c r="R13" s="446"/>
+      <c r="S13" s="446"/>
+      <c r="T13" s="446"/>
+      <c r="U13" s="446"/>
       <c r="V13" s="82"/>
       <c r="W13" s="53"/>
       <c r="X13" s="53"/>
@@ -8686,27 +8685,27 @@
       <c r="AH13" s="84"/>
       <c r="AI13" s="84"/>
       <c r="AJ13" s="352" t="s">
-        <v>300</v>
-      </c>
-      <c r="AK13" s="391" t="s">
+        <v>294</v>
+      </c>
+      <c r="AK13" s="390" t="s">
+        <v>627</v>
+      </c>
+      <c r="AL13" s="390" t="s">
         <v>633</v>
-      </c>
-      <c r="AL13" s="391" t="s">
-        <v>639</v>
       </c>
       <c r="AM13" s="328"/>
       <c r="AN13" s="328"/>
       <c r="AO13" s="328"/>
-      <c r="AP13" s="371" t="s">
-        <v>637</v>
+      <c r="AP13" s="370" t="s">
+        <v>631</v>
       </c>
       <c r="AQ13" s="328"/>
       <c r="AR13" s="328"/>
-      <c r="AS13" s="395" t="s">
-        <v>534</v>
+      <c r="AS13" s="398" t="s">
+        <v>528</v>
       </c>
       <c r="AT13" s="352" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AU13" s="328"/>
       <c r="AV13" s="328"/>
@@ -8716,11 +8715,11 @@
       <c r="AZ13" s="328"/>
       <c r="BA13" s="328"/>
       <c r="BB13" s="328"/>
-      <c r="BC13" s="395" t="s">
-        <v>356</v>
+      <c r="BC13" s="398" t="s">
+        <v>350</v>
       </c>
       <c r="BD13" s="352" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="BE13" s="328"/>
       <c r="BF13" s="328"/>
@@ -8730,11 +8729,11 @@
       <c r="BJ13" s="328"/>
       <c r="BK13" s="328"/>
       <c r="BL13" s="328"/>
-      <c r="BM13" s="395" t="s">
-        <v>330</v>
+      <c r="BM13" s="398" t="s">
+        <v>324</v>
       </c>
       <c r="BN13" s="346" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="BO13" s="328"/>
       <c r="BP13" s="328"/>
@@ -8744,8 +8743,8 @@
       <c r="BT13" s="328"/>
       <c r="BU13" s="328"/>
       <c r="BV13" s="328"/>
-      <c r="BW13" s="395" t="s">
-        <v>302</v>
+      <c r="BW13" s="398" t="s">
+        <v>296</v>
       </c>
       <c r="BX13" s="348"/>
     </row>
@@ -8755,20 +8754,20 @@
       <c r="E14" s="78"/>
       <c r="F14" s="79"/>
       <c r="G14" s="79"/>
-      <c r="H14" s="433"/>
-      <c r="I14" s="434"/>
-      <c r="J14" s="433"/>
-      <c r="K14" s="434"/>
-      <c r="L14" s="435"/>
-      <c r="M14" s="435"/>
+      <c r="H14" s="436"/>
+      <c r="I14" s="437"/>
+      <c r="J14" s="436"/>
+      <c r="K14" s="437"/>
+      <c r="L14" s="438"/>
+      <c r="M14" s="438"/>
       <c r="N14" s="81"/>
-      <c r="O14" s="442"/>
-      <c r="P14" s="443"/>
-      <c r="Q14" s="443"/>
-      <c r="R14" s="443"/>
-      <c r="S14" s="443"/>
-      <c r="T14" s="443"/>
-      <c r="U14" s="443"/>
+      <c r="O14" s="445"/>
+      <c r="P14" s="446"/>
+      <c r="Q14" s="446"/>
+      <c r="R14" s="446"/>
+      <c r="S14" s="446"/>
+      <c r="T14" s="446"/>
+      <c r="U14" s="446"/>
       <c r="V14" s="82"/>
       <c r="W14" s="53"/>
       <c r="X14" s="53"/>
@@ -8784,29 +8783,29 @@
       <c r="AH14" s="84"/>
       <c r="AI14" s="84"/>
       <c r="AJ14" s="352"/>
-      <c r="AK14" s="369" t="s">
-        <v>606</v>
+      <c r="AK14" s="368" t="s">
+        <v>600</v>
       </c>
       <c r="AL14" s="361" t="s">
+        <v>601</v>
+      </c>
+      <c r="AM14" s="333" t="s">
         <v>607</v>
       </c>
-      <c r="AM14" s="333" t="s">
-        <v>613</v>
-      </c>
       <c r="AN14" s="327"/>
-      <c r="AO14" s="368" t="s">
-        <v>614</v>
+      <c r="AO14" s="367" t="s">
+        <v>608</v>
       </c>
       <c r="AP14" s="359" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="AQ14" s="359" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="AR14" s="359" t="s">
-        <v>609</v>
-      </c>
-      <c r="AS14" s="395"/>
+        <v>603</v>
+      </c>
+      <c r="AS14" s="398"/>
       <c r="AT14" s="352"/>
       <c r="AU14" s="327"/>
       <c r="AV14" s="327"/>
@@ -8816,7 +8815,7 @@
       <c r="AZ14" s="327"/>
       <c r="BA14" s="327"/>
       <c r="BB14" s="327"/>
-      <c r="BC14" s="395"/>
+      <c r="BC14" s="398"/>
       <c r="BD14" s="352"/>
       <c r="BE14" s="327"/>
       <c r="BF14" s="327"/>
@@ -8826,13 +8825,13 @@
       <c r="BJ14" s="327"/>
       <c r="BK14" s="327"/>
       <c r="BL14" s="327"/>
-      <c r="BM14" s="395"/>
+      <c r="BM14" s="398"/>
       <c r="BN14" s="346"/>
       <c r="BO14" s="335" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="BP14" s="320" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="BQ14" s="327"/>
       <c r="BR14" s="327"/>
@@ -8840,7 +8839,7 @@
       <c r="BT14" s="327"/>
       <c r="BU14" s="327"/>
       <c r="BV14" s="327"/>
-      <c r="BW14" s="395"/>
+      <c r="BW14" s="398"/>
       <c r="BX14" s="348"/>
     </row>
     <row r="15" spans="1:76" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -8852,20 +8851,20 @@
       <c r="E15" s="78"/>
       <c r="F15" s="79"/>
       <c r="G15" s="79"/>
-      <c r="H15" s="433"/>
-      <c r="I15" s="434"/>
-      <c r="J15" s="433"/>
-      <c r="K15" s="434"/>
-      <c r="L15" s="435"/>
-      <c r="M15" s="435"/>
+      <c r="H15" s="436"/>
+      <c r="I15" s="437"/>
+      <c r="J15" s="436"/>
+      <c r="K15" s="437"/>
+      <c r="L15" s="438"/>
+      <c r="M15" s="438"/>
       <c r="N15" s="81"/>
-      <c r="O15" s="444"/>
-      <c r="P15" s="445"/>
-      <c r="Q15" s="445"/>
-      <c r="R15" s="445"/>
-      <c r="S15" s="445"/>
-      <c r="T15" s="445"/>
-      <c r="U15" s="445"/>
+      <c r="O15" s="447"/>
+      <c r="P15" s="448"/>
+      <c r="Q15" s="448"/>
+      <c r="R15" s="448"/>
+      <c r="S15" s="448"/>
+      <c r="T15" s="448"/>
+      <c r="U15" s="448"/>
       <c r="V15" s="82"/>
       <c r="W15" s="53"/>
       <c r="X15" s="53"/>
@@ -8881,13 +8880,13 @@
       <c r="AH15" s="42"/>
       <c r="AI15" s="42"/>
       <c r="AJ15" s="351" t="s">
-        <v>300</v>
-      </c>
-      <c r="AK15" s="391" t="s">
-        <v>640</v>
-      </c>
-      <c r="AL15" s="391" t="s">
-        <v>641</v>
+        <v>294</v>
+      </c>
+      <c r="AK15" s="390" t="s">
+        <v>634</v>
+      </c>
+      <c r="AL15" s="390" t="s">
+        <v>635</v>
       </c>
       <c r="AM15" s="312"/>
       <c r="AN15" s="312"/>
@@ -8895,11 +8894,11 @@
       <c r="AP15" s="312"/>
       <c r="AQ15" s="312"/>
       <c r="AR15" s="312"/>
-      <c r="AS15" s="394" t="s">
-        <v>535</v>
+      <c r="AS15" s="397" t="s">
+        <v>529</v>
       </c>
       <c r="AT15" s="351" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AU15" s="312"/>
       <c r="AV15" s="312"/>
@@ -8909,11 +8908,11 @@
       <c r="AZ15" s="312"/>
       <c r="BA15" s="312"/>
       <c r="BB15" s="312"/>
-      <c r="BC15" s="394" t="s">
-        <v>357</v>
+      <c r="BC15" s="397" t="s">
+        <v>351</v>
       </c>
       <c r="BD15" s="351" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="BE15" s="312"/>
       <c r="BF15" s="312"/>
@@ -8923,11 +8922,11 @@
       <c r="BJ15" s="312"/>
       <c r="BK15" s="312"/>
       <c r="BL15" s="312"/>
-      <c r="BM15" s="394" t="s">
-        <v>331</v>
+      <c r="BM15" s="397" t="s">
+        <v>325</v>
       </c>
       <c r="BN15" s="345" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="BO15" s="312"/>
       <c r="BP15" s="312"/>
@@ -8937,8 +8936,8 @@
       <c r="BT15" s="312"/>
       <c r="BU15" s="312"/>
       <c r="BV15" s="312"/>
-      <c r="BW15" s="394" t="s">
-        <v>303</v>
+      <c r="BW15" s="397" t="s">
+        <v>297</v>
       </c>
       <c r="BX15" s="348"/>
     </row>
@@ -8948,22 +8947,22 @@
       <c r="E16" s="78"/>
       <c r="F16" s="79"/>
       <c r="G16" s="79"/>
-      <c r="H16" s="433"/>
-      <c r="I16" s="434"/>
-      <c r="J16" s="433"/>
-      <c r="K16" s="434"/>
-      <c r="L16" s="435"/>
-      <c r="M16" s="435"/>
+      <c r="H16" s="436"/>
+      <c r="I16" s="437"/>
+      <c r="J16" s="436"/>
+      <c r="K16" s="437"/>
+      <c r="L16" s="438"/>
+      <c r="M16" s="438"/>
       <c r="N16" s="81"/>
-      <c r="O16" s="440" t="s">
+      <c r="O16" s="443" t="s">
         <v>25</v>
       </c>
-      <c r="P16" s="441"/>
-      <c r="Q16" s="441"/>
-      <c r="R16" s="441"/>
-      <c r="S16" s="441"/>
-      <c r="T16" s="441"/>
-      <c r="U16" s="441"/>
+      <c r="P16" s="444"/>
+      <c r="Q16" s="444"/>
+      <c r="R16" s="444"/>
+      <c r="S16" s="444"/>
+      <c r="T16" s="444"/>
+      <c r="U16" s="444"/>
       <c r="V16" s="82"/>
       <c r="W16" s="53"/>
       <c r="X16" s="53"/>
@@ -8979,31 +8978,31 @@
       <c r="AH16" s="42"/>
       <c r="AI16" s="42"/>
       <c r="AJ16" s="351"/>
-      <c r="AK16" s="369" t="s">
-        <v>620</v>
-      </c>
-      <c r="AL16" s="369" t="s">
-        <v>619</v>
-      </c>
-      <c r="AM16" s="369" t="s">
-        <v>618</v>
-      </c>
-      <c r="AN16" s="369" t="s">
-        <v>617</v>
+      <c r="AK16" s="368" t="s">
+        <v>614</v>
+      </c>
+      <c r="AL16" s="368" t="s">
+        <v>613</v>
+      </c>
+      <c r="AM16" s="368" t="s">
+        <v>612</v>
+      </c>
+      <c r="AN16" s="368" t="s">
+        <v>611</v>
       </c>
       <c r="AO16" s="359" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="AP16" s="320" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="AQ16" s="359" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="AR16" s="333" t="s">
-        <v>638</v>
-      </c>
-      <c r="AS16" s="394"/>
+        <v>632</v>
+      </c>
+      <c r="AS16" s="397"/>
       <c r="AT16" s="351"/>
       <c r="AU16" s="313"/>
       <c r="AV16" s="313"/>
@@ -9013,7 +9012,7 @@
       <c r="AZ16" s="313"/>
       <c r="BA16" s="313"/>
       <c r="BB16" s="313"/>
-      <c r="BC16" s="394"/>
+      <c r="BC16" s="397"/>
       <c r="BD16" s="351"/>
       <c r="BE16" s="313"/>
       <c r="BF16" s="313"/>
@@ -9023,13 +9022,13 @@
       <c r="BJ16" s="313"/>
       <c r="BK16" s="313"/>
       <c r="BL16" s="313"/>
-      <c r="BM16" s="394"/>
+      <c r="BM16" s="397"/>
       <c r="BN16" s="345"/>
       <c r="BO16" s="362" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="BP16" s="320" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="BQ16" s="313"/>
       <c r="BR16" s="313"/>
@@ -9037,7 +9036,7 @@
       <c r="BT16" s="313"/>
       <c r="BU16" s="313"/>
       <c r="BV16" s="313"/>
-      <c r="BW16" s="394"/>
+      <c r="BW16" s="397"/>
       <c r="BX16" s="348"/>
     </row>
     <row r="17" spans="1:76" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9047,20 +9046,20 @@
       <c r="E17" s="78"/>
       <c r="F17" s="79"/>
       <c r="G17" s="79"/>
-      <c r="H17" s="433"/>
-      <c r="I17" s="434"/>
-      <c r="J17" s="433"/>
-      <c r="K17" s="434"/>
-      <c r="L17" s="435"/>
-      <c r="M17" s="435"/>
+      <c r="H17" s="436"/>
+      <c r="I17" s="437"/>
+      <c r="J17" s="436"/>
+      <c r="K17" s="437"/>
+      <c r="L17" s="438"/>
+      <c r="M17" s="438"/>
       <c r="N17" s="81"/>
-      <c r="O17" s="442"/>
-      <c r="P17" s="443"/>
-      <c r="Q17" s="443"/>
-      <c r="R17" s="443"/>
-      <c r="S17" s="443"/>
-      <c r="T17" s="443"/>
-      <c r="U17" s="443"/>
+      <c r="O17" s="445"/>
+      <c r="P17" s="446"/>
+      <c r="Q17" s="446"/>
+      <c r="R17" s="446"/>
+      <c r="S17" s="446"/>
+      <c r="T17" s="446"/>
+      <c r="U17" s="446"/>
       <c r="V17" s="82"/>
       <c r="W17" s="53"/>
       <c r="X17" s="53"/>
@@ -9076,13 +9075,13 @@
       <c r="AH17" s="42"/>
       <c r="AI17" s="42"/>
       <c r="AJ17" s="352" t="s">
-        <v>300</v>
-      </c>
-      <c r="AK17" s="370" t="s">
-        <v>621</v>
-      </c>
-      <c r="AL17" s="391" t="s">
-        <v>622</v>
+        <v>294</v>
+      </c>
+      <c r="AK17" s="369" t="s">
+        <v>615</v>
+      </c>
+      <c r="AL17" s="390" t="s">
+        <v>616</v>
       </c>
       <c r="AM17" s="328"/>
       <c r="AN17" s="328"/>
@@ -9090,11 +9089,11 @@
       <c r="AP17" s="328"/>
       <c r="AQ17" s="328"/>
       <c r="AR17" s="328"/>
-      <c r="AS17" s="395" t="s">
-        <v>536</v>
+      <c r="AS17" s="398" t="s">
+        <v>530</v>
       </c>
       <c r="AT17" s="352" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AU17" s="328"/>
       <c r="AV17" s="328"/>
@@ -9104,34 +9103,32 @@
       <c r="AZ17" s="328"/>
       <c r="BA17" s="328"/>
       <c r="BB17" s="328"/>
-      <c r="BC17" s="395" t="s">
-        <v>358</v>
+      <c r="BC17" s="398" t="s">
+        <v>352</v>
       </c>
       <c r="BD17" s="352" t="s">
-        <v>300</v>
-      </c>
-      <c r="BE17" s="334" t="s">
-        <v>576</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="BE17" s="328"/>
       <c r="BF17" s="328"/>
       <c r="BG17" s="328"/>
       <c r="BH17" s="328"/>
       <c r="BI17" s="328"/>
-      <c r="BJ17" s="328"/>
+      <c r="BJ17" s="372"/>
       <c r="BK17" s="321" t="s">
+        <v>105</v>
+      </c>
+      <c r="BL17" s="392" t="s">
         <v>106</v>
       </c>
-      <c r="BL17" s="362" t="s">
-        <v>107</v>
-      </c>
-      <c r="BM17" s="395" t="s">
-        <v>332</v>
+      <c r="BM17" s="398" t="s">
+        <v>326</v>
       </c>
       <c r="BN17" s="346" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="BO17" s="321" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="BP17" s="328"/>
       <c r="BQ17" s="328"/>
@@ -9140,8 +9137,8 @@
       <c r="BT17" s="328"/>
       <c r="BU17" s="328"/>
       <c r="BV17" s="328"/>
-      <c r="BW17" s="399" t="s">
-        <v>304</v>
+      <c r="BW17" s="402" t="s">
+        <v>298</v>
       </c>
       <c r="BX17" s="348"/>
     </row>
@@ -9151,24 +9148,24 @@
       </c>
       <c r="B18" s="61"/>
       <c r="E18" s="78"/>
-      <c r="F18" s="455" t="s">
+      <c r="F18" s="458" t="s">
         <v>26</v>
       </c>
-      <c r="G18" s="456"/>
-      <c r="H18" s="435"/>
-      <c r="I18" s="434"/>
-      <c r="J18" s="433"/>
-      <c r="K18" s="434"/>
-      <c r="L18" s="435"/>
-      <c r="M18" s="435"/>
+      <c r="G18" s="459"/>
+      <c r="H18" s="438"/>
+      <c r="I18" s="437"/>
+      <c r="J18" s="436"/>
+      <c r="K18" s="437"/>
+      <c r="L18" s="438"/>
+      <c r="M18" s="438"/>
       <c r="N18" s="81"/>
-      <c r="O18" s="442"/>
-      <c r="P18" s="443"/>
-      <c r="Q18" s="443"/>
-      <c r="R18" s="443"/>
-      <c r="S18" s="443"/>
-      <c r="T18" s="443"/>
-      <c r="U18" s="443"/>
+      <c r="O18" s="445"/>
+      <c r="P18" s="446"/>
+      <c r="Q18" s="446"/>
+      <c r="R18" s="446"/>
+      <c r="S18" s="446"/>
+      <c r="T18" s="446"/>
+      <c r="U18" s="446"/>
       <c r="V18" s="82"/>
       <c r="W18" s="53"/>
       <c r="X18" s="53"/>
@@ -9184,27 +9181,27 @@
       <c r="AH18" s="42"/>
       <c r="AI18" s="42"/>
       <c r="AJ18" s="352"/>
-      <c r="AK18" s="369" t="s">
-        <v>623</v>
-      </c>
-      <c r="AL18" s="369" t="s">
-        <v>624</v>
-      </c>
-      <c r="AM18" s="369" t="s">
-        <v>625</v>
-      </c>
-      <c r="AN18" s="369" t="s">
-        <v>626</v>
+      <c r="AK18" s="368" t="s">
+        <v>617</v>
+      </c>
+      <c r="AL18" s="368" t="s">
+        <v>618</v>
+      </c>
+      <c r="AM18" s="368" t="s">
+        <v>619</v>
+      </c>
+      <c r="AN18" s="368" t="s">
+        <v>620</v>
       </c>
       <c r="AO18" s="359" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="AP18" s="359" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="AQ18" s="327"/>
       <c r="AR18" s="327"/>
-      <c r="AS18" s="395"/>
+      <c r="AS18" s="398"/>
       <c r="AT18" s="352"/>
       <c r="AU18" s="327"/>
       <c r="AV18" s="327"/>
@@ -9214,71 +9211,71 @@
       <c r="AZ18" s="327"/>
       <c r="BA18" s="327"/>
       <c r="BB18" s="327"/>
-      <c r="BC18" s="395"/>
+      <c r="BC18" s="398"/>
       <c r="BD18" s="352"/>
-      <c r="BE18" s="374"/>
+      <c r="BE18" s="373"/>
       <c r="BF18" s="320" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="BG18" s="327"/>
       <c r="BH18" s="327"/>
       <c r="BI18" s="359" t="s">
-        <v>416</v>
-      </c>
-      <c r="BJ18" s="334" t="s">
-        <v>577</v>
+        <v>410</v>
+      </c>
+      <c r="BJ18" s="335" t="s">
+        <v>571</v>
       </c>
       <c r="BK18" s="320" t="s">
+        <v>107</v>
+      </c>
+      <c r="BL18" s="393" t="s">
         <v>108</v>
       </c>
-      <c r="BL18" s="362" t="s">
-        <v>109</v>
-      </c>
-      <c r="BM18" s="395"/>
+      <c r="BM18" s="398"/>
       <c r="BN18" s="346"/>
       <c r="BO18" s="362" t="s">
-        <v>179</v>
-      </c>
-      <c r="BP18" s="368" t="s">
-        <v>453</v>
+        <v>175</v>
+      </c>
+      <c r="BP18" s="367" t="s">
+        <v>447</v>
       </c>
       <c r="BQ18" s="327"/>
       <c r="BR18" s="327"/>
       <c r="BS18" s="327"/>
       <c r="BT18" s="359" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="BU18" s="320" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="BV18" s="362" t="s">
-        <v>182</v>
-      </c>
-      <c r="BW18" s="399"/>
+        <v>178</v>
+      </c>
+      <c r="BW18" s="402"/>
       <c r="BX18" s="348"/>
     </row>
     <row r="19" spans="1:76" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="22"/>
       <c r="B19" s="63"/>
       <c r="E19" s="78"/>
-      <c r="F19" s="457"/>
-      <c r="G19" s="458"/>
-      <c r="H19" s="435"/>
-      <c r="I19" s="434"/>
-      <c r="J19" s="433"/>
-      <c r="K19" s="434"/>
-      <c r="L19" s="435"/>
-      <c r="M19" s="435"/>
+      <c r="F19" s="460"/>
+      <c r="G19" s="461"/>
+      <c r="H19" s="438"/>
+      <c r="I19" s="437"/>
+      <c r="J19" s="436"/>
+      <c r="K19" s="437"/>
+      <c r="L19" s="438"/>
+      <c r="M19" s="438"/>
       <c r="N19" s="81"/>
-      <c r="O19" s="461" t="s">
+      <c r="O19" s="464" t="s">
         <v>27</v>
       </c>
-      <c r="P19" s="462"/>
-      <c r="Q19" s="462"/>
-      <c r="R19" s="462"/>
-      <c r="S19" s="462"/>
-      <c r="T19" s="462"/>
-      <c r="U19" s="463"/>
+      <c r="P19" s="465"/>
+      <c r="Q19" s="465"/>
+      <c r="R19" s="465"/>
+      <c r="S19" s="465"/>
+      <c r="T19" s="465"/>
+      <c r="U19" s="466"/>
       <c r="V19" s="82"/>
       <c r="W19" s="53"/>
       <c r="X19" s="53"/>
@@ -9294,11 +9291,11 @@
       <c r="AH19" s="86"/>
       <c r="AI19" s="86"/>
       <c r="AJ19" s="351" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AK19" s="312"/>
-      <c r="AL19" s="391" t="s">
-        <v>653</v>
+      <c r="AL19" s="390" t="s">
+        <v>647</v>
       </c>
       <c r="AM19" s="312"/>
       <c r="AN19" s="312"/>
@@ -9306,11 +9303,11 @@
       <c r="AP19" s="312"/>
       <c r="AQ19" s="312"/>
       <c r="AR19" s="312"/>
-      <c r="AS19" s="394" t="s">
-        <v>537</v>
+      <c r="AS19" s="397" t="s">
+        <v>531</v>
       </c>
       <c r="AT19" s="351" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AU19" s="312"/>
       <c r="AV19" s="312"/>
@@ -9320,35 +9317,35 @@
       <c r="AZ19" s="312"/>
       <c r="BA19" s="312"/>
       <c r="BB19" s="312"/>
-      <c r="BC19" s="394" t="s">
-        <v>359</v>
+      <c r="BC19" s="397" t="s">
+        <v>353</v>
       </c>
       <c r="BD19" s="351" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="BE19" s="312"/>
       <c r="BG19" s="312"/>
       <c r="BH19" s="312"/>
       <c r="BI19" s="321" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BJ19" s="321" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="BK19" s="321" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="BL19" s="321" t="s">
-        <v>185</v>
-      </c>
-      <c r="BM19" s="394" t="s">
-        <v>333</v>
+        <v>181</v>
+      </c>
+      <c r="BM19" s="397" t="s">
+        <v>327</v>
       </c>
       <c r="BN19" s="345" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="BO19" s="321" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="BP19" s="312"/>
       <c r="BQ19" s="312"/>
@@ -9357,33 +9354,33 @@
       <c r="BT19" s="312"/>
       <c r="BU19" s="312"/>
       <c r="BV19" s="312"/>
-      <c r="BW19" s="400" t="s">
-        <v>305</v>
+      <c r="BW19" s="403" t="s">
+        <v>299</v>
       </c>
       <c r="BX19" s="348"/>
     </row>
     <row r="20" spans="1:76" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="470" t="s">
+      <c r="A20" s="473" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="471"/>
+      <c r="B20" s="474"/>
       <c r="E20" s="103"/>
-      <c r="F20" s="459"/>
-      <c r="G20" s="460"/>
-      <c r="H20" s="435"/>
-      <c r="I20" s="434"/>
-      <c r="J20" s="433"/>
-      <c r="K20" s="434"/>
-      <c r="L20" s="435"/>
-      <c r="M20" s="435"/>
+      <c r="F20" s="462"/>
+      <c r="G20" s="463"/>
+      <c r="H20" s="438"/>
+      <c r="I20" s="437"/>
+      <c r="J20" s="436"/>
+      <c r="K20" s="437"/>
+      <c r="L20" s="438"/>
+      <c r="M20" s="438"/>
       <c r="N20" s="81"/>
-      <c r="O20" s="464"/>
-      <c r="P20" s="465"/>
-      <c r="Q20" s="465"/>
-      <c r="R20" s="465"/>
-      <c r="S20" s="465"/>
-      <c r="T20" s="465"/>
-      <c r="U20" s="466"/>
+      <c r="O20" s="467"/>
+      <c r="P20" s="468"/>
+      <c r="Q20" s="468"/>
+      <c r="R20" s="468"/>
+      <c r="S20" s="468"/>
+      <c r="T20" s="468"/>
+      <c r="U20" s="469"/>
       <c r="V20" s="82"/>
       <c r="W20" s="53"/>
       <c r="X20" s="53"/>
@@ -9400,8 +9397,8 @@
       <c r="AI20" s="102"/>
       <c r="AJ20" s="351"/>
       <c r="AK20" s="313"/>
-      <c r="AL20" s="369" t="s">
-        <v>629</v>
+      <c r="AL20" s="368" t="s">
+        <v>623</v>
       </c>
       <c r="AM20" s="313"/>
       <c r="AN20" s="313"/>
@@ -9409,7 +9406,7 @@
       <c r="AP20" s="313"/>
       <c r="AQ20" s="313"/>
       <c r="AR20" s="313"/>
-      <c r="AS20" s="394"/>
+      <c r="AS20" s="397"/>
       <c r="AT20" s="351"/>
       <c r="AU20" s="313"/>
       <c r="AV20" s="313"/>
@@ -9419,72 +9416,74 @@
       <c r="AZ20" s="313"/>
       <c r="BA20" s="313"/>
       <c r="BB20" s="313"/>
-      <c r="BC20" s="394"/>
+      <c r="BC20" s="397"/>
       <c r="BD20" s="351"/>
-      <c r="BE20" s="369" t="s">
-        <v>674</v>
+      <c r="BE20" s="368" t="s">
+        <v>668</v>
       </c>
       <c r="BF20" s="335" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="BG20" s="313"/>
       <c r="BI20" s="320" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="BJ20" s="362" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="BK20" s="362" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="BL20" s="320" t="s">
-        <v>189</v>
-      </c>
-      <c r="BM20" s="394"/>
+        <v>185</v>
+      </c>
+      <c r="BM20" s="397"/>
       <c r="BN20" s="345"/>
       <c r="BO20" s="362" t="s">
         <v>59</v>
       </c>
       <c r="BP20" s="335" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="BQ20" s="313"/>
-      <c r="BR20" s="313"/>
+      <c r="BR20" s="391" t="s">
+        <v>194</v>
+      </c>
       <c r="BS20" s="335" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
       <c r="BT20" s="320" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="BU20" s="362" t="s">
         <v>60</v>
       </c>
       <c r="BV20" s="362" t="s">
-        <v>191</v>
-      </c>
-      <c r="BW20" s="400"/>
+        <v>187</v>
+      </c>
+      <c r="BW20" s="403"/>
       <c r="BX20" s="348"/>
     </row>
     <row r="21" spans="1:76" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="472"/>
-      <c r="B21" s="473"/>
+      <c r="A21" s="475"/>
+      <c r="B21" s="476"/>
       <c r="E21" s="106"/>
       <c r="F21" s="107"/>
       <c r="G21" s="107"/>
-      <c r="H21" s="433"/>
-      <c r="I21" s="434"/>
-      <c r="J21" s="433"/>
-      <c r="K21" s="434"/>
-      <c r="L21" s="435"/>
-      <c r="M21" s="435"/>
+      <c r="H21" s="436"/>
+      <c r="I21" s="437"/>
+      <c r="J21" s="436"/>
+      <c r="K21" s="437"/>
+      <c r="L21" s="438"/>
+      <c r="M21" s="438"/>
       <c r="N21" s="81"/>
-      <c r="O21" s="464"/>
-      <c r="P21" s="465"/>
-      <c r="Q21" s="465"/>
-      <c r="R21" s="465"/>
-      <c r="S21" s="465"/>
-      <c r="T21" s="465"/>
-      <c r="U21" s="466"/>
+      <c r="O21" s="467"/>
+      <c r="P21" s="468"/>
+      <c r="Q21" s="468"/>
+      <c r="R21" s="468"/>
+      <c r="S21" s="468"/>
+      <c r="T21" s="468"/>
+      <c r="U21" s="469"/>
       <c r="V21" s="82"/>
       <c r="W21" s="53"/>
       <c r="X21" s="53"/>
@@ -9500,7 +9499,7 @@
       <c r="AH21" s="102"/>
       <c r="AI21" s="102"/>
       <c r="AJ21" s="352" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AK21" s="328"/>
       <c r="AL21" s="328"/>
@@ -9510,11 +9509,11 @@
       <c r="AP21" s="328"/>
       <c r="AQ21" s="328"/>
       <c r="AR21" s="328"/>
-      <c r="AS21" s="395" t="s">
-        <v>538</v>
+      <c r="AS21" s="398" t="s">
+        <v>532</v>
       </c>
       <c r="AT21" s="352" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AU21" s="328"/>
       <c r="AV21" s="328"/>
@@ -9524,30 +9523,31 @@
       <c r="AZ21" s="328"/>
       <c r="BA21" s="328"/>
       <c r="BB21" s="328"/>
-      <c r="BC21" s="395" t="s">
-        <v>360</v>
+      <c r="BC21" s="398" t="s">
+        <v>354</v>
       </c>
       <c r="BD21" s="352" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="BE21" s="328"/>
+      <c r="BF21" s="372"/>
       <c r="BG21" s="328"/>
-      <c r="BH21" s="321" t="s">
-        <v>112</v>
+      <c r="BH21" s="395" t="s">
+        <v>111</v>
       </c>
       <c r="BI21" s="328"/>
       <c r="BJ21" s="321" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="BK21" s="328"/>
-      <c r="BL21" s="320" t="s">
-        <v>125</v>
-      </c>
-      <c r="BM21" s="395" t="s">
-        <v>334</v>
+      <c r="BL21" s="321" t="s">
+        <v>124</v>
+      </c>
+      <c r="BM21" s="398" t="s">
+        <v>328</v>
       </c>
       <c r="BN21" s="346" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="BO21" s="328"/>
       <c r="BP21" s="328"/>
@@ -9557,35 +9557,35 @@
       <c r="BT21" s="328"/>
       <c r="BU21" s="328"/>
       <c r="BV21" s="328"/>
-      <c r="BW21" s="401" t="s">
-        <v>306</v>
+      <c r="BW21" s="404" t="s">
+        <v>300</v>
       </c>
       <c r="BX21" s="348"/>
     </row>
     <row r="22" spans="1:76" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="474"/>
-      <c r="B22" s="475"/>
+      <c r="A22" s="477"/>
+      <c r="B22" s="478"/>
       <c r="C22" s="109"/>
       <c r="D22" s="93"/>
-      <c r="E22" s="453" t="s">
+      <c r="E22" s="456" t="s">
         <v>29</v>
       </c>
-      <c r="F22" s="453"/>
-      <c r="G22" s="454"/>
-      <c r="H22" s="433"/>
-      <c r="I22" s="434"/>
-      <c r="J22" s="433"/>
-      <c r="K22" s="434"/>
-      <c r="L22" s="435"/>
-      <c r="M22" s="435"/>
+      <c r="F22" s="456"/>
+      <c r="G22" s="457"/>
+      <c r="H22" s="436"/>
+      <c r="I22" s="437"/>
+      <c r="J22" s="436"/>
+      <c r="K22" s="437"/>
+      <c r="L22" s="438"/>
+      <c r="M22" s="438"/>
       <c r="N22" s="81"/>
-      <c r="O22" s="467"/>
-      <c r="P22" s="468"/>
-      <c r="Q22" s="468"/>
-      <c r="R22" s="468"/>
-      <c r="S22" s="468"/>
-      <c r="T22" s="468"/>
-      <c r="U22" s="469"/>
+      <c r="O22" s="470"/>
+      <c r="P22" s="471"/>
+      <c r="Q22" s="471"/>
+      <c r="R22" s="471"/>
+      <c r="S22" s="471"/>
+      <c r="T22" s="471"/>
+      <c r="U22" s="472"/>
       <c r="V22" s="82"/>
       <c r="W22" s="53"/>
       <c r="X22" s="53"/>
@@ -9606,12 +9606,12 @@
       <c r="AM22" s="327"/>
       <c r="AN22" s="327"/>
       <c r="AO22" s="359" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="AP22" s="327"/>
       <c r="AQ22" s="327"/>
       <c r="AR22" s="327"/>
-      <c r="AS22" s="395"/>
+      <c r="AS22" s="398"/>
       <c r="AT22" s="352"/>
       <c r="AU22" s="327"/>
       <c r="AV22" s="327"/>
@@ -9621,79 +9621,79 @@
       <c r="AZ22" s="327"/>
       <c r="BA22" s="327"/>
       <c r="BB22" s="327"/>
-      <c r="BC22" s="395"/>
+      <c r="BC22" s="398"/>
       <c r="BD22" s="352"/>
       <c r="BE22" s="320" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="BF22" s="335" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="BG22" s="327"/>
       <c r="BH22" s="362" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="BI22" s="320" t="s">
-        <v>192</v>
-      </c>
-      <c r="BJ22" s="320" t="s">
-        <v>118</v>
-      </c>
-      <c r="BK22" s="375"/>
+        <v>188</v>
+      </c>
+      <c r="BJ22" s="391" t="s">
+        <v>117</v>
+      </c>
+      <c r="BK22" s="374"/>
       <c r="BL22" s="320" t="s">
-        <v>113</v>
-      </c>
-      <c r="BM22" s="395"/>
+        <v>112</v>
+      </c>
+      <c r="BM22" s="398"/>
       <c r="BN22" s="346"/>
       <c r="BO22" s="320" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="BP22" s="362" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="BQ22" s="327"/>
       <c r="BR22" s="359" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="BS22" s="320" t="s">
         <v>61</v>
       </c>
       <c r="BT22" s="359" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="BU22" s="359" t="s">
-        <v>420</v>
-      </c>
-      <c r="BV22" s="320" t="s">
-        <v>195</v>
-      </c>
-      <c r="BW22" s="401"/>
+        <v>414</v>
+      </c>
+      <c r="BV22" s="391" t="s">
+        <v>191</v>
+      </c>
+      <c r="BW22" s="404"/>
       <c r="BX22" s="348"/>
     </row>
     <row r="23" spans="1:76" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="470" t="s">
+      <c r="A23" s="473" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="476"/>
+      <c r="B23" s="479"/>
       <c r="C23" s="109"/>
       <c r="D23" s="112"/>
-      <c r="E23" s="450"/>
-      <c r="F23" s="450"/>
-      <c r="G23" s="451"/>
-      <c r="H23" s="433"/>
-      <c r="I23" s="434"/>
-      <c r="J23" s="433"/>
-      <c r="K23" s="434"/>
-      <c r="L23" s="435"/>
-      <c r="M23" s="435"/>
+      <c r="E23" s="453"/>
+      <c r="F23" s="453"/>
+      <c r="G23" s="454"/>
+      <c r="H23" s="436"/>
+      <c r="I23" s="437"/>
+      <c r="J23" s="436"/>
+      <c r="K23" s="437"/>
+      <c r="L23" s="438"/>
+      <c r="M23" s="438"/>
       <c r="N23" s="81"/>
-      <c r="O23" s="478"/>
-      <c r="P23" s="479"/>
-      <c r="Q23" s="479"/>
-      <c r="R23" s="479"/>
-      <c r="S23" s="479"/>
-      <c r="T23" s="479"/>
-      <c r="U23" s="480"/>
+      <c r="O23" s="481"/>
+      <c r="P23" s="482"/>
+      <c r="Q23" s="482"/>
+      <c r="R23" s="482"/>
+      <c r="S23" s="482"/>
+      <c r="T23" s="482"/>
+      <c r="U23" s="483"/>
       <c r="V23" s="74"/>
       <c r="W23" s="75"/>
       <c r="X23" s="75"/>
@@ -9709,7 +9709,7 @@
       <c r="AH23" s="95"/>
       <c r="AI23" s="86"/>
       <c r="AJ23" s="351" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AK23" s="312"/>
       <c r="AL23" s="312"/>
@@ -9719,11 +9719,11 @@
       <c r="AP23" s="312"/>
       <c r="AQ23" s="312"/>
       <c r="AR23" s="312"/>
-      <c r="AS23" s="394" t="s">
-        <v>539</v>
+      <c r="AS23" s="397" t="s">
+        <v>533</v>
       </c>
       <c r="AT23" s="351" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AU23" s="312"/>
       <c r="AV23" s="312"/>
@@ -9733,33 +9733,32 @@
       <c r="AZ23" s="312"/>
       <c r="BA23" s="312"/>
       <c r="BB23" s="312"/>
-      <c r="BC23" s="394" t="s">
-        <v>361</v>
+      <c r="BC23" s="397" t="s">
+        <v>355</v>
       </c>
       <c r="BD23" s="351" t="s">
-        <v>300</v>
-      </c>
-      <c r="BE23" s="334" t="s">
-        <v>581</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="BE23" s="312"/>
       <c r="BF23" s="334" t="s">
-        <v>582</v>
-      </c>
-      <c r="BG23" s="312"/>
+        <v>576</v>
+      </c>
       <c r="BH23" s="334" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="BI23" s="312"/>
       <c r="BJ23" s="360" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="BK23" s="312"/>
-      <c r="BL23" s="312"/>
-      <c r="BM23" s="394" t="s">
-        <v>335</v>
+      <c r="BL23" s="334" t="s">
+        <v>197</v>
+      </c>
+      <c r="BM23" s="397" t="s">
+        <v>329</v>
       </c>
       <c r="BN23" s="345" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="BO23" s="312"/>
       <c r="BP23" s="312"/>
@@ -9768,35 +9767,35 @@
       <c r="BS23" s="312"/>
       <c r="BU23" s="312"/>
       <c r="BV23" s="312"/>
-      <c r="BW23" s="400" t="s">
-        <v>307</v>
+      <c r="BW23" s="403" t="s">
+        <v>301</v>
       </c>
       <c r="BX23" s="348"/>
     </row>
     <row r="24" spans="1:76" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="472"/>
-      <c r="B24" s="477"/>
+      <c r="A24" s="475"/>
+      <c r="B24" s="480"/>
       <c r="C24" s="113"/>
       <c r="D24" s="112"/>
-      <c r="E24" s="453" t="s">
+      <c r="E24" s="456" t="s">
         <v>29</v>
       </c>
-      <c r="F24" s="453"/>
-      <c r="G24" s="454"/>
-      <c r="H24" s="433"/>
-      <c r="I24" s="434"/>
-      <c r="J24" s="433"/>
-      <c r="K24" s="434"/>
-      <c r="L24" s="435"/>
-      <c r="M24" s="435"/>
+      <c r="F24" s="456"/>
+      <c r="G24" s="457"/>
+      <c r="H24" s="436"/>
+      <c r="I24" s="437"/>
+      <c r="J24" s="436"/>
+      <c r="K24" s="437"/>
+      <c r="L24" s="438"/>
+      <c r="M24" s="438"/>
       <c r="N24" s="81"/>
-      <c r="O24" s="481"/>
-      <c r="P24" s="482"/>
-      <c r="Q24" s="482"/>
-      <c r="R24" s="482"/>
-      <c r="S24" s="482"/>
-      <c r="T24" s="482"/>
-      <c r="U24" s="483"/>
+      <c r="O24" s="484"/>
+      <c r="P24" s="485"/>
+      <c r="Q24" s="485"/>
+      <c r="R24" s="485"/>
+      <c r="S24" s="485"/>
+      <c r="T24" s="485"/>
+      <c r="U24" s="486"/>
       <c r="V24" s="82"/>
       <c r="W24" s="53"/>
       <c r="X24" s="90"/>
@@ -9820,7 +9819,7 @@
       <c r="AP24" s="313"/>
       <c r="AQ24" s="313"/>
       <c r="AR24" s="313"/>
-      <c r="AS24" s="394"/>
+      <c r="AS24" s="397"/>
       <c r="AT24" s="351"/>
       <c r="AU24" s="313"/>
       <c r="AV24" s="313"/>
@@ -9830,79 +9829,77 @@
       <c r="AZ24" s="313"/>
       <c r="BA24" s="313"/>
       <c r="BB24" s="313"/>
-      <c r="BC24" s="394"/>
+      <c r="BC24" s="397"/>
       <c r="BD24" s="351"/>
       <c r="BE24" s="359" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="BF24" s="359" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="BG24" s="313"/>
       <c r="BH24" s="335" t="s">
+        <v>115</v>
+      </c>
+      <c r="BI24" s="367" t="s">
+        <v>420</v>
+      </c>
+      <c r="BJ24" s="335" t="s">
         <v>116</v>
       </c>
-      <c r="BI24" s="368" t="s">
-        <v>426</v>
-      </c>
-      <c r="BJ24" s="335" t="s">
-        <v>117</v>
-      </c>
-      <c r="BK24" s="369" t="s">
-        <v>669</v>
+      <c r="BK24" s="368" t="s">
+        <v>663</v>
       </c>
       <c r="BL24" s="359" t="s">
-        <v>119</v>
-      </c>
-      <c r="BM24" s="394"/>
+        <v>118</v>
+      </c>
+      <c r="BM24" s="397"/>
       <c r="BN24" s="345"/>
       <c r="BO24" s="320" t="s">
         <v>62</v>
       </c>
-      <c r="BP24" s="320" t="s">
-        <v>198</v>
-      </c>
+      <c r="BP24" s="313"/>
       <c r="BQ24" s="313"/>
       <c r="BR24" s="359" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="BS24" s="359" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="BT24" s="359" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="BU24" s="359" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="BV24" s="320" t="s">
-        <v>200</v>
-      </c>
-      <c r="BW24" s="400"/>
+        <v>196</v>
+      </c>
+      <c r="BW24" s="403"/>
       <c r="BX24" s="348"/>
     </row>
     <row r="25" spans="1:76" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="474"/>
-      <c r="B25" s="475"/>
+      <c r="A25" s="477"/>
+      <c r="B25" s="478"/>
       <c r="C25" s="109"/>
       <c r="D25" s="115"/>
-      <c r="E25" s="447"/>
-      <c r="F25" s="447"/>
-      <c r="G25" s="448"/>
-      <c r="H25" s="433"/>
-      <c r="I25" s="434"/>
-      <c r="J25" s="433"/>
-      <c r="K25" s="434"/>
-      <c r="L25" s="435"/>
-      <c r="M25" s="435"/>
+      <c r="E25" s="450"/>
+      <c r="F25" s="450"/>
+      <c r="G25" s="451"/>
+      <c r="H25" s="436"/>
+      <c r="I25" s="437"/>
+      <c r="J25" s="436"/>
+      <c r="K25" s="437"/>
+      <c r="L25" s="438"/>
+      <c r="M25" s="438"/>
       <c r="N25" s="81"/>
-      <c r="O25" s="481"/>
-      <c r="P25" s="482"/>
-      <c r="Q25" s="482"/>
-      <c r="R25" s="482"/>
-      <c r="S25" s="482"/>
-      <c r="T25" s="482"/>
-      <c r="U25" s="483"/>
+      <c r="O25" s="484"/>
+      <c r="P25" s="485"/>
+      <c r="Q25" s="485"/>
+      <c r="R25" s="485"/>
+      <c r="S25" s="485"/>
+      <c r="T25" s="485"/>
+      <c r="U25" s="486"/>
       <c r="V25" s="104"/>
       <c r="W25" s="97"/>
       <c r="X25" s="97"/>
@@ -9918,7 +9915,7 @@
       <c r="AH25" s="116"/>
       <c r="AI25" s="116"/>
       <c r="AJ25" s="352" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AK25" s="328"/>
       <c r="AL25" s="328"/>
@@ -9928,11 +9925,11 @@
       <c r="AP25" s="328"/>
       <c r="AQ25" s="328"/>
       <c r="AR25" s="328"/>
-      <c r="AS25" s="395" t="s">
-        <v>540</v>
+      <c r="AS25" s="398" t="s">
+        <v>534</v>
       </c>
       <c r="AT25" s="352" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AU25" s="328"/>
       <c r="AV25" s="328"/>
@@ -9942,29 +9939,31 @@
       <c r="AZ25" s="328"/>
       <c r="BA25" s="328"/>
       <c r="BB25" s="328"/>
-      <c r="BC25" s="395" t="s">
-        <v>362</v>
+      <c r="BC25" s="398" t="s">
+        <v>356</v>
       </c>
       <c r="BD25" s="352" t="s">
-        <v>300</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="BE25" s="372"/>
       <c r="BF25" s="321" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="BG25" s="328"/>
-      <c r="BH25" s="373"/>
-      <c r="BI25" s="371" t="s">
-        <v>121</v>
-      </c>
-      <c r="BJ25" s="359" t="s">
-        <v>204</v>
-      </c>
+      <c r="BH25" s="372"/>
+      <c r="BI25" s="370" t="s">
+        <v>120</v>
+      </c>
+      <c r="BJ25" s="370" t="s">
+        <v>200</v>
+      </c>
+      <c r="BK25" s="372"/>
       <c r="BL25" s="328"/>
-      <c r="BM25" s="395" t="s">
-        <v>336</v>
+      <c r="BM25" s="398" t="s">
+        <v>330</v>
       </c>
       <c r="BN25" s="346" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="BO25" s="328"/>
       <c r="BP25" s="328"/>
@@ -9972,41 +9971,41 @@
       <c r="BR25" s="328"/>
       <c r="BS25" s="328"/>
       <c r="BT25" s="321" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="BU25" s="321" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="BV25" s="328"/>
-      <c r="BW25" s="401" t="s">
-        <v>308</v>
+      <c r="BW25" s="404" t="s">
+        <v>302</v>
       </c>
       <c r="BX25" s="348"/>
     </row>
     <row r="26" spans="1:76" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="470" t="s">
+      <c r="A26" s="473" t="s">
         <v>31</v>
       </c>
-      <c r="B26" s="471"/>
+      <c r="B26" s="474"/>
       <c r="C26" s="65"/>
       <c r="D26" s="65"/>
-      <c r="E26" s="446"/>
-      <c r="F26" s="447"/>
-      <c r="G26" s="448"/>
-      <c r="H26" s="433"/>
-      <c r="I26" s="434"/>
-      <c r="J26" s="433"/>
-      <c r="K26" s="434"/>
-      <c r="L26" s="435"/>
-      <c r="M26" s="435"/>
+      <c r="E26" s="449"/>
+      <c r="F26" s="450"/>
+      <c r="G26" s="451"/>
+      <c r="H26" s="436"/>
+      <c r="I26" s="437"/>
+      <c r="J26" s="436"/>
+      <c r="K26" s="437"/>
+      <c r="L26" s="438"/>
+      <c r="M26" s="438"/>
       <c r="N26" s="81"/>
-      <c r="O26" s="484"/>
-      <c r="P26" s="485"/>
-      <c r="Q26" s="485"/>
-      <c r="R26" s="485"/>
-      <c r="S26" s="485"/>
-      <c r="T26" s="485"/>
-      <c r="U26" s="486"/>
+      <c r="O26" s="487"/>
+      <c r="P26" s="488"/>
+      <c r="Q26" s="488"/>
+      <c r="R26" s="488"/>
+      <c r="S26" s="488"/>
+      <c r="T26" s="488"/>
+      <c r="U26" s="489"/>
       <c r="V26" s="104"/>
       <c r="Z26" s="93"/>
       <c r="AA26" s="101"/>
@@ -10021,7 +10020,7 @@
       <c r="AJ26" s="352"/>
       <c r="AK26" s="327"/>
       <c r="AL26" s="333" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="AM26" s="327"/>
       <c r="AN26" s="327"/>
@@ -10029,7 +10028,7 @@
       <c r="AP26" s="327"/>
       <c r="AQ26" s="327"/>
       <c r="AR26" s="327"/>
-      <c r="AS26" s="395"/>
+      <c r="AS26" s="398"/>
       <c r="AT26" s="352"/>
       <c r="AU26" s="327"/>
       <c r="AV26" s="327"/>
@@ -10039,44 +10038,44 @@
       <c r="AZ26" s="327"/>
       <c r="BA26" s="327"/>
       <c r="BB26" s="327"/>
-      <c r="BC26" s="395"/>
+      <c r="BC26" s="398"/>
       <c r="BD26" s="352"/>
       <c r="BE26" s="335" t="s">
-        <v>201</v>
+        <v>575</v>
       </c>
       <c r="BF26" s="320" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="BG26" s="327"/>
       <c r="BH26" s="359" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="BI26" s="359" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="BJ26" s="359" t="s">
-        <v>203</v>
-      </c>
-      <c r="BK26" s="334" t="s">
-        <v>579</v>
+        <v>199</v>
+      </c>
+      <c r="BK26" s="335" t="s">
+        <v>573</v>
       </c>
       <c r="BL26" s="359" t="s">
-        <v>120</v>
-      </c>
-      <c r="BM26" s="395"/>
+        <v>119</v>
+      </c>
+      <c r="BM26" s="398"/>
       <c r="BN26" s="346"/>
       <c r="BO26" s="359" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="BP26" s="359" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="BQ26" s="327"/>
       <c r="BR26" s="359" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="BS26" s="359" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="BT26" s="320" t="s">
         <v>63</v>
@@ -10085,33 +10084,33 @@
         <v>64</v>
       </c>
       <c r="BV26" s="327"/>
-      <c r="BW26" s="401"/>
+      <c r="BW26" s="404"/>
       <c r="BX26" s="348"/>
     </row>
     <row r="27" spans="1:76" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="472"/>
-      <c r="B27" s="473"/>
+      <c r="A27" s="475"/>
+      <c r="B27" s="476"/>
       <c r="C27" s="65"/>
       <c r="D27" s="117"/>
       <c r="E27" s="118"/>
       <c r="F27" s="119"/>
       <c r="G27" s="119"/>
-      <c r="H27" s="433"/>
-      <c r="I27" s="434"/>
-      <c r="J27" s="433"/>
-      <c r="K27" s="434"/>
-      <c r="L27" s="435"/>
-      <c r="M27" s="435"/>
+      <c r="H27" s="436"/>
+      <c r="I27" s="437"/>
+      <c r="J27" s="436"/>
+      <c r="K27" s="437"/>
+      <c r="L27" s="438"/>
+      <c r="M27" s="438"/>
       <c r="N27" s="81"/>
-      <c r="O27" s="488" t="s">
+      <c r="O27" s="491" t="s">
         <v>32</v>
       </c>
-      <c r="P27" s="489"/>
-      <c r="Q27" s="489"/>
-      <c r="R27" s="489"/>
-      <c r="S27" s="489"/>
-      <c r="T27" s="489"/>
-      <c r="U27" s="490"/>
+      <c r="P27" s="492"/>
+      <c r="Q27" s="492"/>
+      <c r="R27" s="492"/>
+      <c r="S27" s="492"/>
+      <c r="T27" s="492"/>
+      <c r="U27" s="493"/>
       <c r="Z27" s="93"/>
       <c r="AA27" s="101"/>
       <c r="AB27" s="101"/>
@@ -10123,7 +10122,7 @@
       <c r="AH27" s="114"/>
       <c r="AI27" s="108"/>
       <c r="AJ27" s="351" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AK27" s="312"/>
       <c r="AL27" s="312"/>
@@ -10133,11 +10132,11 @@
       <c r="AP27" s="312"/>
       <c r="AQ27" s="312"/>
       <c r="AR27" s="312"/>
-      <c r="AS27" s="394" t="s">
-        <v>541</v>
+      <c r="AS27" s="397" t="s">
+        <v>535</v>
       </c>
       <c r="AT27" s="351" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AU27" s="312"/>
       <c r="AV27" s="312"/>
@@ -10147,35 +10146,35 @@
       <c r="AZ27" s="312"/>
       <c r="BA27" s="312"/>
       <c r="BB27" s="312"/>
-      <c r="BC27" s="394" t="s">
-        <v>363</v>
+      <c r="BC27" s="397" t="s">
+        <v>357</v>
       </c>
       <c r="BD27" s="351" t="s">
-        <v>300</v>
-      </c>
-      <c r="BE27" s="371" t="s">
-        <v>207</v>
-      </c>
-      <c r="BF27" s="371" t="s">
-        <v>124</v>
+        <v>294</v>
+      </c>
+      <c r="BE27" s="370" t="s">
+        <v>203</v>
+      </c>
+      <c r="BF27" s="370" t="s">
+        <v>123</v>
       </c>
       <c r="BG27" s="312"/>
       <c r="BH27" s="312"/>
       <c r="BI27" s="312"/>
       <c r="BJ27" s="312"/>
-      <c r="BK27" s="371" t="s">
-        <v>291</v>
-      </c>
-      <c r="BL27" s="371" t="s">
-        <v>208</v>
-      </c>
-      <c r="BM27" s="394" t="s">
-        <v>337</v>
+      <c r="BK27" s="370" t="s">
+        <v>285</v>
+      </c>
+      <c r="BL27" s="370" t="s">
+        <v>204</v>
+      </c>
+      <c r="BM27" s="397" t="s">
+        <v>331</v>
       </c>
       <c r="BN27" s="345" t="s">
-        <v>300</v>
-      </c>
-      <c r="BO27" s="364"/>
+        <v>294</v>
+      </c>
+      <c r="BO27" s="363"/>
       <c r="BQ27" s="312"/>
       <c r="BR27" s="312"/>
       <c r="BS27" s="312"/>
@@ -10183,33 +10182,33 @@
         <v>70</v>
       </c>
       <c r="BV27" s="312"/>
-      <c r="BW27" s="400" t="s">
-        <v>309</v>
+      <c r="BW27" s="403" t="s">
+        <v>303</v>
       </c>
       <c r="BX27" s="348"/>
     </row>
     <row r="28" spans="1:76" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="474"/>
-      <c r="B28" s="487"/>
-      <c r="E28" s="452" t="s">
+      <c r="A28" s="477"/>
+      <c r="B28" s="490"/>
+      <c r="E28" s="455" t="s">
         <v>33</v>
       </c>
-      <c r="F28" s="453"/>
-      <c r="G28" s="454"/>
-      <c r="H28" s="433"/>
-      <c r="I28" s="434"/>
-      <c r="J28" s="433"/>
-      <c r="K28" s="434"/>
-      <c r="L28" s="435"/>
-      <c r="M28" s="435"/>
+      <c r="F28" s="456"/>
+      <c r="G28" s="457"/>
+      <c r="H28" s="436"/>
+      <c r="I28" s="437"/>
+      <c r="J28" s="436"/>
+      <c r="K28" s="437"/>
+      <c r="L28" s="438"/>
+      <c r="M28" s="438"/>
       <c r="N28" s="81"/>
-      <c r="O28" s="491"/>
-      <c r="P28" s="492"/>
-      <c r="Q28" s="492"/>
-      <c r="R28" s="492"/>
-      <c r="S28" s="492"/>
-      <c r="T28" s="492"/>
-      <c r="U28" s="493"/>
+      <c r="O28" s="494"/>
+      <c r="P28" s="495"/>
+      <c r="Q28" s="495"/>
+      <c r="R28" s="495"/>
+      <c r="S28" s="495"/>
+      <c r="T28" s="495"/>
+      <c r="U28" s="496"/>
       <c r="V28" s="120"/>
       <c r="X28" s="92"/>
       <c r="Z28" s="93"/>
@@ -10224,7 +10223,7 @@
       <c r="AJ28" s="351"/>
       <c r="AK28" s="313"/>
       <c r="AL28" s="333" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="AM28" s="313"/>
       <c r="AN28" s="313"/>
@@ -10232,7 +10231,7 @@
       <c r="AP28" s="313"/>
       <c r="AQ28" s="313"/>
       <c r="AR28" s="313"/>
-      <c r="AS28" s="394"/>
+      <c r="AS28" s="397"/>
       <c r="AT28" s="351"/>
       <c r="AU28" s="313"/>
       <c r="AV28" s="313"/>
@@ -10242,77 +10241,77 @@
       <c r="AZ28" s="313"/>
       <c r="BA28" s="313"/>
       <c r="BB28" s="313"/>
-      <c r="BC28" s="394"/>
+      <c r="BC28" s="397"/>
       <c r="BD28" s="351"/>
       <c r="BE28" s="359" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="BF28" s="359" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="BG28" s="313"/>
       <c r="BH28" s="335" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="BI28" s="359" t="s">
-        <v>427</v>
-      </c>
-      <c r="BJ28" s="360" t="s">
-        <v>428</v>
+        <v>421</v>
+      </c>
+      <c r="BJ28" s="359" t="s">
+        <v>422</v>
       </c>
       <c r="BK28" s="359" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BL28" s="359" t="s">
-        <v>209</v>
-      </c>
-      <c r="BM28" s="394"/>
+        <v>205</v>
+      </c>
+      <c r="BM28" s="397"/>
       <c r="BN28" s="345"/>
       <c r="BO28" s="320" t="s">
         <v>65</v>
       </c>
       <c r="BP28" s="359" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="BQ28" s="313"/>
       <c r="BR28" s="333" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="BS28" s="320" t="s">
         <v>66</v>
       </c>
       <c r="BT28" s="359" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="BU28" s="362" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="BV28" s="362" t="s">
         <v>67</v>
       </c>
-      <c r="BW28" s="400"/>
+      <c r="BW28" s="403"/>
       <c r="BX28" s="348"/>
     </row>
     <row r="29" spans="1:76" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="90"/>
       <c r="B29" s="90"/>
-      <c r="E29" s="446"/>
-      <c r="F29" s="447"/>
-      <c r="G29" s="448"/>
-      <c r="H29" s="433"/>
-      <c r="I29" s="434"/>
-      <c r="J29" s="433"/>
-      <c r="K29" s="434"/>
-      <c r="L29" s="435"/>
-      <c r="M29" s="435"/>
+      <c r="E29" s="449"/>
+      <c r="F29" s="450"/>
+      <c r="G29" s="451"/>
+      <c r="H29" s="436"/>
+      <c r="I29" s="437"/>
+      <c r="J29" s="436"/>
+      <c r="K29" s="437"/>
+      <c r="L29" s="438"/>
+      <c r="M29" s="438"/>
       <c r="N29" s="81"/>
-      <c r="O29" s="491"/>
-      <c r="P29" s="492"/>
-      <c r="Q29" s="492"/>
-      <c r="R29" s="492"/>
-      <c r="S29" s="492"/>
-      <c r="T29" s="492"/>
-      <c r="U29" s="493"/>
+      <c r="O29" s="494"/>
+      <c r="P29" s="495"/>
+      <c r="Q29" s="495"/>
+      <c r="R29" s="495"/>
+      <c r="S29" s="495"/>
+      <c r="T29" s="495"/>
+      <c r="U29" s="496"/>
       <c r="V29" s="86"/>
       <c r="W29" s="121"/>
       <c r="X29" s="92"/>
@@ -10326,7 +10325,7 @@
       <c r="AH29" s="108"/>
       <c r="AI29" s="108"/>
       <c r="AJ29" s="352" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AK29" s="328"/>
       <c r="AL29" s="328"/>
@@ -10336,11 +10335,11 @@
       <c r="AP29" s="328"/>
       <c r="AQ29" s="328"/>
       <c r="AR29" s="328"/>
-      <c r="AS29" s="395" t="s">
-        <v>542</v>
+      <c r="AS29" s="398" t="s">
+        <v>536</v>
       </c>
       <c r="AT29" s="352" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AU29" s="328"/>
       <c r="AV29" s="328"/>
@@ -10350,29 +10349,29 @@
       <c r="AZ29" s="328"/>
       <c r="BA29" s="328"/>
       <c r="BB29" s="328"/>
-      <c r="BC29" s="395" t="s">
-        <v>364</v>
+      <c r="BC29" s="398" t="s">
+        <v>358</v>
       </c>
       <c r="BD29" s="352" t="s">
-        <v>300</v>
-      </c>
-      <c r="BE29" s="371" t="s">
-        <v>128</v>
+        <v>294</v>
+      </c>
+      <c r="BE29" s="370" t="s">
+        <v>127</v>
       </c>
       <c r="BF29" s="328"/>
       <c r="BG29" s="328"/>
-      <c r="BH29" s="320" t="s">
-        <v>213</v>
+      <c r="BH29" s="391" t="s">
+        <v>209</v>
       </c>
       <c r="BI29" s="328"/>
       <c r="BJ29" s="328"/>
       <c r="BK29" s="328"/>
       <c r="BL29" s="328"/>
-      <c r="BM29" s="395" t="s">
-        <v>338</v>
+      <c r="BM29" s="398" t="s">
+        <v>332</v>
       </c>
       <c r="BN29" s="346" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="BO29" s="328"/>
       <c r="BP29" s="328"/>
@@ -10382,31 +10381,31 @@
       <c r="BT29" s="328"/>
       <c r="BU29" s="328"/>
       <c r="BV29" s="328"/>
-      <c r="BW29" s="401" t="s">
-        <v>310</v>
+      <c r="BW29" s="404" t="s">
+        <v>304</v>
       </c>
       <c r="BX29" s="348"/>
     </row>
     <row r="30" spans="1:76" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="90"/>
       <c r="B30" s="90"/>
-      <c r="E30" s="446"/>
-      <c r="F30" s="447"/>
-      <c r="G30" s="448"/>
-      <c r="H30" s="433"/>
-      <c r="I30" s="434"/>
-      <c r="J30" s="433"/>
-      <c r="K30" s="434"/>
-      <c r="L30" s="435"/>
-      <c r="M30" s="435"/>
+      <c r="E30" s="449"/>
+      <c r="F30" s="450"/>
+      <c r="G30" s="451"/>
+      <c r="H30" s="436"/>
+      <c r="I30" s="437"/>
+      <c r="J30" s="436"/>
+      <c r="K30" s="437"/>
+      <c r="L30" s="438"/>
+      <c r="M30" s="438"/>
       <c r="N30" s="81"/>
-      <c r="O30" s="491"/>
-      <c r="P30" s="492"/>
-      <c r="Q30" s="492"/>
-      <c r="R30" s="492"/>
-      <c r="S30" s="492"/>
-      <c r="T30" s="492"/>
-      <c r="U30" s="493"/>
+      <c r="O30" s="494"/>
+      <c r="P30" s="495"/>
+      <c r="Q30" s="495"/>
+      <c r="R30" s="495"/>
+      <c r="S30" s="495"/>
+      <c r="T30" s="495"/>
+      <c r="U30" s="496"/>
       <c r="V30" s="99"/>
       <c r="X30" s="42"/>
       <c r="Y30" s="70"/>
@@ -10429,7 +10428,7 @@
       <c r="AP30" s="327"/>
       <c r="AQ30" s="327"/>
       <c r="AR30" s="327"/>
-      <c r="AS30" s="395"/>
+      <c r="AS30" s="398"/>
       <c r="AT30" s="352"/>
       <c r="AU30" s="327"/>
       <c r="AV30" s="327"/>
@@ -10439,77 +10438,77 @@
       <c r="AZ30" s="327"/>
       <c r="BA30" s="327"/>
       <c r="BB30" s="327"/>
-      <c r="BC30" s="395"/>
+      <c r="BC30" s="398"/>
       <c r="BD30" s="352"/>
       <c r="BE30" s="359" t="s">
-        <v>425</v>
-      </c>
-      <c r="BF30" s="369" t="s">
-        <v>670</v>
+        <v>419</v>
+      </c>
+      <c r="BF30" s="368" t="s">
+        <v>664</v>
       </c>
       <c r="BG30" s="327"/>
       <c r="BH30" s="320" t="s">
-        <v>211</v>
-      </c>
-      <c r="BI30" s="360" t="s">
-        <v>445</v>
+        <v>207</v>
+      </c>
+      <c r="BI30" s="359" t="s">
+        <v>439</v>
       </c>
       <c r="BJ30" s="335" t="s">
-        <v>433</v>
-      </c>
-      <c r="BK30" s="360" t="s">
-        <v>585</v>
-      </c>
-      <c r="BL30" s="369" t="s">
-        <v>668</v>
-      </c>
-      <c r="BM30" s="395"/>
+        <v>427</v>
+      </c>
+      <c r="BK30" s="359" t="s">
+        <v>579</v>
+      </c>
+      <c r="BL30" s="368" t="s">
+        <v>662</v>
+      </c>
+      <c r="BM30" s="398"/>
       <c r="BN30" s="346"/>
       <c r="BO30" s="320" t="s">
         <v>68</v>
       </c>
       <c r="BP30" s="359" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="BQ30" s="327"/>
       <c r="BR30" s="333" t="s">
-        <v>643</v>
-      </c>
-      <c r="BS30" s="320" t="s">
+        <v>637</v>
+      </c>
+      <c r="BS30" s="391" t="s">
         <v>69</v>
       </c>
       <c r="BT30" s="320" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="BU30" s="359" t="s">
         <v>71</v>
       </c>
       <c r="BV30" s="320" t="s">
-        <v>214</v>
-      </c>
-      <c r="BW30" s="401"/>
+        <v>210</v>
+      </c>
+      <c r="BW30" s="404"/>
       <c r="BX30" s="348"/>
     </row>
     <row r="31" spans="1:76" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="90"/>
       <c r="B31" s="90"/>
-      <c r="E31" s="446"/>
-      <c r="F31" s="447"/>
-      <c r="G31" s="448"/>
-      <c r="H31" s="433"/>
-      <c r="I31" s="434"/>
-      <c r="J31" s="433"/>
-      <c r="K31" s="434"/>
-      <c r="L31" s="435"/>
-      <c r="M31" s="435"/>
+      <c r="E31" s="449"/>
+      <c r="F31" s="450"/>
+      <c r="G31" s="451"/>
+      <c r="H31" s="436"/>
+      <c r="I31" s="437"/>
+      <c r="J31" s="436"/>
+      <c r="K31" s="437"/>
+      <c r="L31" s="438"/>
+      <c r="M31" s="438"/>
       <c r="N31" s="81"/>
-      <c r="O31" s="491"/>
-      <c r="P31" s="492"/>
-      <c r="Q31" s="492"/>
-      <c r="R31" s="492"/>
-      <c r="S31" s="492"/>
-      <c r="T31" s="492"/>
-      <c r="U31" s="493"/>
+      <c r="O31" s="494"/>
+      <c r="P31" s="495"/>
+      <c r="Q31" s="495"/>
+      <c r="R31" s="495"/>
+      <c r="S31" s="495"/>
+      <c r="T31" s="495"/>
+      <c r="U31" s="496"/>
       <c r="V31" s="123"/>
       <c r="Z31" s="93"/>
       <c r="AA31" s="124"/>
@@ -10522,7 +10521,7 @@
       <c r="AH31" s="108"/>
       <c r="AI31" s="42"/>
       <c r="AJ31" s="351" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AK31" s="312"/>
       <c r="AL31" s="312"/>
@@ -10532,11 +10531,11 @@
       <c r="AP31" s="312"/>
       <c r="AQ31" s="312"/>
       <c r="AR31" s="312"/>
-      <c r="AS31" s="394" t="s">
-        <v>543</v>
+      <c r="AS31" s="397" t="s">
+        <v>537</v>
       </c>
       <c r="AT31" s="351" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AU31" s="312"/>
       <c r="AV31" s="312"/>
@@ -10546,33 +10545,33 @@
       <c r="AZ31" s="312"/>
       <c r="BA31" s="312"/>
       <c r="BB31" s="312"/>
-      <c r="BC31" s="394" t="s">
-        <v>365</v>
+      <c r="BC31" s="397" t="s">
+        <v>359</v>
       </c>
       <c r="BD31" s="351" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="BE31" s="312"/>
-      <c r="BF31" s="371" t="s">
-        <v>212</v>
+      <c r="BF31" s="370" t="s">
+        <v>208</v>
       </c>
       <c r="BG31" s="312"/>
       <c r="BH31" s="334" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="BI31" s="312"/>
       <c r="BJ31" s="321" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="BK31" s="312"/>
       <c r="BL31" s="334" t="s">
-        <v>129</v>
-      </c>
-      <c r="BM31" s="394" t="s">
-        <v>339</v>
+        <v>128</v>
+      </c>
+      <c r="BM31" s="397" t="s">
+        <v>333</v>
       </c>
       <c r="BN31" s="345" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="BO31" s="312"/>
       <c r="BQ31" s="312"/>
@@ -10581,31 +10580,31 @@
       <c r="BT31" s="312"/>
       <c r="BU31" s="312"/>
       <c r="BV31" s="312"/>
-      <c r="BW31" s="400" t="s">
-        <v>311</v>
+      <c r="BW31" s="403" t="s">
+        <v>305</v>
       </c>
       <c r="BX31" s="348"/>
     </row>
     <row r="32" spans="1:76" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="90"/>
       <c r="B32" s="90"/>
-      <c r="E32" s="449"/>
-      <c r="F32" s="450"/>
-      <c r="G32" s="451"/>
-      <c r="H32" s="433"/>
-      <c r="I32" s="434"/>
-      <c r="J32" s="433"/>
-      <c r="K32" s="434"/>
-      <c r="L32" s="435"/>
-      <c r="M32" s="435"/>
+      <c r="E32" s="452"/>
+      <c r="F32" s="453"/>
+      <c r="G32" s="454"/>
+      <c r="H32" s="436"/>
+      <c r="I32" s="437"/>
+      <c r="J32" s="436"/>
+      <c r="K32" s="437"/>
+      <c r="L32" s="438"/>
+      <c r="M32" s="438"/>
       <c r="N32" s="81"/>
-      <c r="O32" s="491"/>
-      <c r="P32" s="492"/>
-      <c r="Q32" s="492"/>
-      <c r="R32" s="492"/>
-      <c r="S32" s="492"/>
-      <c r="T32" s="492"/>
-      <c r="U32" s="493"/>
+      <c r="O32" s="494"/>
+      <c r="P32" s="495"/>
+      <c r="Q32" s="495"/>
+      <c r="R32" s="495"/>
+      <c r="S32" s="495"/>
+      <c r="T32" s="495"/>
+      <c r="U32" s="496"/>
       <c r="V32" s="123"/>
       <c r="Z32" s="93"/>
       <c r="AA32" s="124"/>
@@ -10625,7 +10624,7 @@
       <c r="AP32" s="313"/>
       <c r="AQ32" s="313"/>
       <c r="AR32" s="313"/>
-      <c r="AS32" s="394"/>
+      <c r="AS32" s="397"/>
       <c r="AT32" s="351"/>
       <c r="AU32" s="313"/>
       <c r="AV32" s="313"/>
@@ -10635,41 +10634,41 @@
       <c r="AZ32" s="313"/>
       <c r="BA32" s="313"/>
       <c r="BB32" s="313"/>
-      <c r="BC32" s="394"/>
+      <c r="BC32" s="397"/>
       <c r="BD32" s="351"/>
       <c r="BE32" s="362" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="BF32" s="359" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="BG32" s="313"/>
-      <c r="BH32" s="376" t="s">
-        <v>436</v>
-      </c>
-      <c r="BI32" s="368" t="s">
-        <v>444</v>
+      <c r="BH32" s="375" t="s">
+        <v>430</v>
+      </c>
+      <c r="BI32" s="367" t="s">
+        <v>438</v>
       </c>
       <c r="BJ32" s="362" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="BK32" s="335" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="BL32" s="359" t="s">
-        <v>437</v>
-      </c>
-      <c r="BM32" s="394"/>
+        <v>431</v>
+      </c>
+      <c r="BM32" s="397"/>
       <c r="BN32" s="345"/>
       <c r="BO32" s="320" t="s">
         <v>72</v>
       </c>
       <c r="BP32" s="359" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="BQ32" s="313"/>
       <c r="BR32" s="333" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="BS32" s="320" t="s">
         <v>73</v>
@@ -10678,34 +10677,36 @@
         <v>74</v>
       </c>
       <c r="BU32" s="333" t="s">
-        <v>645</v>
-      </c>
-      <c r="BV32" s="313"/>
-      <c r="BW32" s="400"/>
+        <v>639</v>
+      </c>
+      <c r="BV32" s="368" t="s">
+        <v>672</v>
+      </c>
+      <c r="BW32" s="403"/>
       <c r="BX32" s="348"/>
     </row>
     <row r="33" spans="1:79" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="90"/>
       <c r="B33" s="90"/>
-      <c r="E33" s="446" t="s">
+      <c r="E33" s="449" t="s">
         <v>34</v>
       </c>
-      <c r="F33" s="447"/>
-      <c r="G33" s="448"/>
-      <c r="H33" s="433"/>
-      <c r="I33" s="434"/>
-      <c r="J33" s="433"/>
-      <c r="K33" s="434"/>
-      <c r="L33" s="435"/>
-      <c r="M33" s="435"/>
+      <c r="F33" s="450"/>
+      <c r="G33" s="451"/>
+      <c r="H33" s="436"/>
+      <c r="I33" s="437"/>
+      <c r="J33" s="436"/>
+      <c r="K33" s="437"/>
+      <c r="L33" s="438"/>
+      <c r="M33" s="438"/>
       <c r="N33" s="81"/>
-      <c r="O33" s="491"/>
-      <c r="P33" s="492"/>
-      <c r="Q33" s="492"/>
-      <c r="R33" s="492"/>
-      <c r="S33" s="492"/>
-      <c r="T33" s="492"/>
-      <c r="U33" s="493"/>
+      <c r="O33" s="494"/>
+      <c r="P33" s="495"/>
+      <c r="Q33" s="495"/>
+      <c r="R33" s="495"/>
+      <c r="S33" s="495"/>
+      <c r="T33" s="495"/>
+      <c r="U33" s="496"/>
       <c r="V33" s="123"/>
       <c r="W33" s="87"/>
       <c r="X33" s="42"/>
@@ -10719,7 +10720,7 @@
       <c r="AF33" s="116"/>
       <c r="AG33" s="116"/>
       <c r="AJ33" s="352" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AK33" s="328"/>
       <c r="AL33" s="328"/>
@@ -10729,11 +10730,11 @@
       <c r="AP33" s="328"/>
       <c r="AQ33" s="328"/>
       <c r="AR33" s="328"/>
-      <c r="AS33" s="395" t="s">
-        <v>544</v>
+      <c r="AS33" s="398" t="s">
+        <v>538</v>
       </c>
       <c r="AT33" s="352" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AU33" s="328"/>
       <c r="AV33" s="328"/>
@@ -10743,28 +10744,29 @@
       <c r="AZ33" s="328"/>
       <c r="BA33" s="328"/>
       <c r="BB33" s="328"/>
-      <c r="BC33" s="395" t="s">
-        <v>366</v>
+      <c r="BC33" s="398" t="s">
+        <v>360</v>
       </c>
       <c r="BD33" s="352" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="BE33" s="334" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="BF33" s="328"/>
       <c r="BG33" s="328"/>
       <c r="BH33" s="328"/>
+      <c r="BI33" s="372"/>
       <c r="BJ33" s="328"/>
       <c r="BK33" s="328"/>
       <c r="BL33" s="360" t="s">
-        <v>407</v>
-      </c>
-      <c r="BM33" s="395" t="s">
-        <v>340</v>
+        <v>401</v>
+      </c>
+      <c r="BM33" s="398" t="s">
+        <v>334</v>
       </c>
       <c r="BN33" s="346" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="BO33" s="328"/>
       <c r="BP33" s="328"/>
@@ -10774,31 +10776,31 @@
       <c r="BT33" s="328"/>
       <c r="BU33" s="328"/>
       <c r="BV33" s="328"/>
-      <c r="BW33" s="401" t="s">
-        <v>312</v>
+      <c r="BW33" s="404" t="s">
+        <v>306</v>
       </c>
       <c r="BX33" s="348"/>
     </row>
     <row r="34" spans="1:79" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="90"/>
       <c r="B34" s="90"/>
-      <c r="E34" s="446"/>
-      <c r="F34" s="447"/>
-      <c r="G34" s="448"/>
-      <c r="H34" s="433"/>
-      <c r="I34" s="434"/>
-      <c r="J34" s="433"/>
-      <c r="K34" s="434"/>
-      <c r="L34" s="435"/>
-      <c r="M34" s="435"/>
+      <c r="E34" s="449"/>
+      <c r="F34" s="450"/>
+      <c r="G34" s="451"/>
+      <c r="H34" s="436"/>
+      <c r="I34" s="437"/>
+      <c r="J34" s="436"/>
+      <c r="K34" s="437"/>
+      <c r="L34" s="438"/>
+      <c r="M34" s="438"/>
       <c r="N34" s="81"/>
-      <c r="O34" s="491"/>
-      <c r="P34" s="492"/>
-      <c r="Q34" s="492"/>
-      <c r="R34" s="492"/>
-      <c r="S34" s="492"/>
-      <c r="T34" s="492"/>
-      <c r="U34" s="493"/>
+      <c r="O34" s="494"/>
+      <c r="P34" s="495"/>
+      <c r="Q34" s="495"/>
+      <c r="R34" s="495"/>
+      <c r="S34" s="495"/>
+      <c r="T34" s="495"/>
+      <c r="U34" s="496"/>
       <c r="V34" s="127"/>
       <c r="W34" s="87"/>
       <c r="X34" s="42"/>
@@ -10817,7 +10819,7 @@
       <c r="AP34" s="327"/>
       <c r="AQ34" s="327"/>
       <c r="AR34" s="327"/>
-      <c r="AS34" s="395"/>
+      <c r="AS34" s="398"/>
       <c r="AT34" s="352"/>
       <c r="AU34" s="327"/>
       <c r="AV34" s="327"/>
@@ -10827,46 +10829,46 @@
       <c r="AZ34" s="327"/>
       <c r="BA34" s="327"/>
       <c r="BB34" s="335" t="s">
-        <v>493</v>
-      </c>
-      <c r="BC34" s="395"/>
+        <v>487</v>
+      </c>
+      <c r="BC34" s="398"/>
       <c r="BD34" s="352"/>
       <c r="BE34" s="335" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="BF34" s="359" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="BG34" s="327"/>
       <c r="BH34" s="359" t="s">
+        <v>435</v>
+      </c>
+      <c r="BI34" s="359" t="s">
+        <v>214</v>
+      </c>
+      <c r="BJ34" s="359" t="s">
         <v>441</v>
       </c>
-      <c r="BI34" s="359" t="s">
-        <v>218</v>
-      </c>
-      <c r="BJ34" s="359" t="s">
-        <v>447</v>
-      </c>
       <c r="BK34" s="359" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="BL34" s="359" t="s">
-        <v>130</v>
-      </c>
-      <c r="BM34" s="395"/>
+        <v>129</v>
+      </c>
+      <c r="BM34" s="398"/>
       <c r="BN34" s="346"/>
       <c r="BO34" s="320" t="s">
         <v>75</v>
       </c>
       <c r="BP34" s="335" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="BQ34" s="327"/>
       <c r="BR34" s="333" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="BS34" s="362" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="BT34" s="320" t="s">
         <v>76</v>
@@ -10875,31 +10877,31 @@
         <v>77</v>
       </c>
       <c r="BV34" s="362" t="s">
-        <v>221</v>
-      </c>
-      <c r="BW34" s="401"/>
+        <v>217</v>
+      </c>
+      <c r="BW34" s="404"/>
       <c r="BX34" s="348"/>
     </row>
     <row r="35" spans="1:79" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="90"/>
       <c r="B35" s="90"/>
-      <c r="E35" s="446"/>
-      <c r="F35" s="447"/>
-      <c r="G35" s="448"/>
-      <c r="H35" s="433"/>
-      <c r="I35" s="434"/>
-      <c r="J35" s="433"/>
-      <c r="K35" s="434"/>
-      <c r="L35" s="435"/>
-      <c r="M35" s="435"/>
+      <c r="E35" s="449"/>
+      <c r="F35" s="450"/>
+      <c r="G35" s="451"/>
+      <c r="H35" s="436"/>
+      <c r="I35" s="437"/>
+      <c r="J35" s="436"/>
+      <c r="K35" s="437"/>
+      <c r="L35" s="438"/>
+      <c r="M35" s="438"/>
       <c r="N35" s="81"/>
-      <c r="O35" s="491"/>
-      <c r="P35" s="492"/>
-      <c r="Q35" s="492"/>
-      <c r="R35" s="492"/>
-      <c r="S35" s="492"/>
-      <c r="T35" s="492"/>
-      <c r="U35" s="493"/>
+      <c r="O35" s="494"/>
+      <c r="P35" s="495"/>
+      <c r="Q35" s="495"/>
+      <c r="R35" s="495"/>
+      <c r="S35" s="495"/>
+      <c r="T35" s="495"/>
+      <c r="U35" s="496"/>
       <c r="V35" s="127"/>
       <c r="W35" s="87"/>
       <c r="X35" s="42"/>
@@ -10911,7 +10913,7 @@
       <c r="AD35" s="42"/>
       <c r="AI35" s="42"/>
       <c r="AJ35" s="351" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AK35" s="312"/>
       <c r="AL35" s="312"/>
@@ -10921,11 +10923,11 @@
       <c r="AP35" s="312"/>
       <c r="AQ35" s="312"/>
       <c r="AR35" s="312"/>
-      <c r="AS35" s="394" t="s">
-        <v>545</v>
+      <c r="AS35" s="397" t="s">
+        <v>539</v>
       </c>
       <c r="AT35" s="351" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AU35" s="312"/>
       <c r="AV35" s="312"/>
@@ -10935,27 +10937,29 @@
       <c r="AZ35" s="312"/>
       <c r="BA35" s="312"/>
       <c r="BB35" s="312"/>
-      <c r="BC35" s="394" t="s">
-        <v>367</v>
+      <c r="BC35" s="397" t="s">
+        <v>361</v>
       </c>
       <c r="BD35" s="351" t="s">
-        <v>300</v>
-      </c>
-      <c r="BE35" s="371" t="s">
-        <v>132</v>
+        <v>294</v>
+      </c>
+      <c r="BE35" s="370" t="s">
+        <v>131</v>
       </c>
       <c r="BF35" s="360" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="BG35" s="312"/>
       <c r="BH35" s="312"/>
-      <c r="BJ35" s="312"/>
+      <c r="BJ35" s="334" t="s">
+        <v>135</v>
+      </c>
       <c r="BL35" s="312"/>
-      <c r="BM35" s="394" t="s">
-        <v>341</v>
+      <c r="BM35" s="397" t="s">
+        <v>335</v>
       </c>
       <c r="BN35" s="345" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="BO35" s="312"/>
       <c r="BP35" s="312"/>
@@ -10965,31 +10969,31 @@
       <c r="BT35" s="312"/>
       <c r="BU35" s="312"/>
       <c r="BV35" s="312"/>
-      <c r="BW35" s="400" t="s">
-        <v>313</v>
+      <c r="BW35" s="403" t="s">
+        <v>307</v>
       </c>
       <c r="BX35" s="348"/>
     </row>
     <row r="36" spans="1:79" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="42"/>
       <c r="B36" s="97"/>
-      <c r="E36" s="446"/>
-      <c r="F36" s="447"/>
-      <c r="G36" s="448"/>
-      <c r="H36" s="433"/>
-      <c r="I36" s="434"/>
-      <c r="J36" s="433"/>
-      <c r="K36" s="434"/>
-      <c r="L36" s="435"/>
-      <c r="M36" s="435"/>
+      <c r="E36" s="449"/>
+      <c r="F36" s="450"/>
+      <c r="G36" s="451"/>
+      <c r="H36" s="436"/>
+      <c r="I36" s="437"/>
+      <c r="J36" s="436"/>
+      <c r="K36" s="437"/>
+      <c r="L36" s="438"/>
+      <c r="M36" s="438"/>
       <c r="N36" s="81"/>
-      <c r="O36" s="491"/>
-      <c r="P36" s="492"/>
-      <c r="Q36" s="492"/>
-      <c r="R36" s="492"/>
-      <c r="S36" s="492"/>
-      <c r="T36" s="492"/>
-      <c r="U36" s="493"/>
+      <c r="O36" s="494"/>
+      <c r="P36" s="495"/>
+      <c r="Q36" s="495"/>
+      <c r="R36" s="495"/>
+      <c r="S36" s="495"/>
+      <c r="T36" s="495"/>
+      <c r="U36" s="496"/>
       <c r="V36" s="127"/>
       <c r="W36" s="86"/>
       <c r="X36" s="86"/>
@@ -11012,7 +11016,7 @@
       <c r="AP36" s="313"/>
       <c r="AQ36" s="313"/>
       <c r="AR36" s="313"/>
-      <c r="AS36" s="394"/>
+      <c r="AS36" s="397"/>
       <c r="AT36" s="351"/>
       <c r="AU36" s="313"/>
       <c r="AV36" s="313"/>
@@ -11022,56 +11026,56 @@
       <c r="AZ36" s="313"/>
       <c r="BA36" s="313"/>
       <c r="BB36" s="335" t="s">
-        <v>454</v>
-      </c>
-      <c r="BC36" s="394"/>
+        <v>448</v>
+      </c>
+      <c r="BC36" s="397"/>
       <c r="BD36" s="351"/>
       <c r="BE36" s="359" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="BF36" s="335" t="s">
+        <v>133</v>
+      </c>
+      <c r="BH36" s="359" t="s">
         <v>134</v>
       </c>
-      <c r="BH36" s="359" t="s">
-        <v>135</v>
-      </c>
       <c r="BI36" s="335" t="s">
+        <v>570</v>
+      </c>
+      <c r="BJ36" s="359" t="s">
+        <v>222</v>
+      </c>
+      <c r="BK36" s="335" t="s">
         <v>136</v>
       </c>
-      <c r="BJ36" s="359" t="s">
-        <v>226</v>
-      </c>
-      <c r="BK36" s="335" t="s">
+      <c r="BL36" s="320" t="s">
         <v>137</v>
       </c>
-      <c r="BL36" s="320" t="s">
-        <v>138</v>
-      </c>
-      <c r="BM36" s="394"/>
+      <c r="BM36" s="397"/>
       <c r="BN36" s="345"/>
       <c r="BO36" s="362" t="s">
         <v>78</v>
       </c>
       <c r="BP36" s="359" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="BQ36" s="313"/>
       <c r="BR36" s="359" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="BS36" s="320" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="BT36" s="362" t="s">
         <v>79</v>
       </c>
       <c r="BU36" s="362" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="BV36" s="362" t="s">
         <v>80</v>
       </c>
-      <c r="BW36" s="400"/>
+      <c r="BW36" s="403"/>
       <c r="BX36" s="348"/>
       <c r="CA36" s="6" t="s">
         <v>14</v>
@@ -11080,23 +11084,23 @@
     <row r="37" spans="1:79" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="42"/>
       <c r="B37" s="97"/>
-      <c r="E37" s="446"/>
-      <c r="F37" s="447"/>
-      <c r="G37" s="448"/>
-      <c r="H37" s="433"/>
-      <c r="I37" s="434"/>
-      <c r="J37" s="433"/>
-      <c r="K37" s="434"/>
-      <c r="L37" s="435"/>
-      <c r="M37" s="435"/>
+      <c r="E37" s="449"/>
+      <c r="F37" s="450"/>
+      <c r="G37" s="451"/>
+      <c r="H37" s="436"/>
+      <c r="I37" s="437"/>
+      <c r="J37" s="436"/>
+      <c r="K37" s="437"/>
+      <c r="L37" s="438"/>
+      <c r="M37" s="438"/>
       <c r="N37" s="81"/>
-      <c r="O37" s="491"/>
-      <c r="P37" s="492"/>
-      <c r="Q37" s="492"/>
-      <c r="R37" s="492"/>
-      <c r="S37" s="492"/>
-      <c r="T37" s="492"/>
-      <c r="U37" s="493"/>
+      <c r="O37" s="494"/>
+      <c r="P37" s="495"/>
+      <c r="Q37" s="495"/>
+      <c r="R37" s="495"/>
+      <c r="S37" s="495"/>
+      <c r="T37" s="495"/>
+      <c r="U37" s="496"/>
       <c r="V37" s="97"/>
       <c r="W37" s="86"/>
       <c r="X37" s="86"/>
@@ -11122,7 +11126,7 @@
       <c r="AQ37" s="339"/>
       <c r="AR37" s="340"/>
       <c r="AS37" s="341" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="AT37" s="353"/>
       <c r="AU37" s="329" t="s">
@@ -11136,58 +11140,58 @@
       <c r="BA37" s="330"/>
       <c r="BB37" s="331"/>
       <c r="BC37" s="332" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="BD37" s="353"/>
-      <c r="BE37" s="396" t="s">
+      <c r="BE37" s="399" t="s">
         <v>57</v>
       </c>
-      <c r="BF37" s="397"/>
-      <c r="BG37" s="397"/>
-      <c r="BH37" s="397"/>
-      <c r="BI37" s="397"/>
-      <c r="BJ37" s="397"/>
-      <c r="BK37" s="397"/>
-      <c r="BL37" s="398"/>
+      <c r="BF37" s="400"/>
+      <c r="BG37" s="400"/>
+      <c r="BH37" s="400"/>
+      <c r="BI37" s="400"/>
+      <c r="BJ37" s="400"/>
+      <c r="BK37" s="400"/>
+      <c r="BL37" s="401"/>
       <c r="BM37" s="332" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="BN37" s="347"/>
-      <c r="BO37" s="396" t="s">
+      <c r="BO37" s="399" t="s">
         <v>58</v>
       </c>
-      <c r="BP37" s="397"/>
-      <c r="BQ37" s="397"/>
-      <c r="BR37" s="397"/>
-      <c r="BS37" s="397"/>
-      <c r="BT37" s="397"/>
-      <c r="BU37" s="397"/>
-      <c r="BV37" s="398"/>
+      <c r="BP37" s="400"/>
+      <c r="BQ37" s="400"/>
+      <c r="BR37" s="400"/>
+      <c r="BS37" s="400"/>
+      <c r="BT37" s="400"/>
+      <c r="BU37" s="400"/>
+      <c r="BV37" s="401"/>
       <c r="BW37" s="343" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="BX37" s="348"/>
     </row>
     <row r="38" spans="1:79" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="42"/>
       <c r="B38" s="97"/>
-      <c r="E38" s="449"/>
-      <c r="F38" s="450"/>
-      <c r="G38" s="451"/>
-      <c r="H38" s="433"/>
-      <c r="I38" s="434"/>
-      <c r="J38" s="433"/>
-      <c r="K38" s="434"/>
-      <c r="L38" s="435"/>
-      <c r="M38" s="435"/>
+      <c r="E38" s="452"/>
+      <c r="F38" s="453"/>
+      <c r="G38" s="454"/>
+      <c r="H38" s="436"/>
+      <c r="I38" s="437"/>
+      <c r="J38" s="436"/>
+      <c r="K38" s="437"/>
+      <c r="L38" s="438"/>
+      <c r="M38" s="438"/>
       <c r="N38" s="81"/>
-      <c r="O38" s="491"/>
-      <c r="P38" s="492"/>
-      <c r="Q38" s="492"/>
-      <c r="R38" s="492"/>
-      <c r="S38" s="492"/>
-      <c r="T38" s="492"/>
-      <c r="U38" s="493"/>
+      <c r="O38" s="494"/>
+      <c r="P38" s="495"/>
+      <c r="Q38" s="495"/>
+      <c r="R38" s="495"/>
+      <c r="S38" s="495"/>
+      <c r="T38" s="495"/>
+      <c r="U38" s="496"/>
       <c r="V38" s="97"/>
       <c r="W38" s="86"/>
       <c r="X38" s="86"/>
@@ -11203,7 +11207,7 @@
       <c r="AH38" s="87"/>
       <c r="AI38" s="100"/>
       <c r="AJ38" s="351" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AK38" s="312"/>
       <c r="AL38" s="312"/>
@@ -11213,11 +11217,11 @@
       <c r="AP38" s="312"/>
       <c r="AQ38" s="312"/>
       <c r="AR38" s="312"/>
-      <c r="AS38" s="394" t="s">
-        <v>555</v>
+      <c r="AS38" s="397" t="s">
+        <v>549</v>
       </c>
       <c r="AT38" s="351" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AU38" s="312"/>
       <c r="AV38" s="312"/>
@@ -11227,29 +11231,29 @@
       <c r="AZ38" s="312"/>
       <c r="BA38" s="312"/>
       <c r="BB38" s="312"/>
-      <c r="BC38" s="394" t="s">
-        <v>369</v>
+      <c r="BC38" s="397" t="s">
+        <v>363</v>
       </c>
       <c r="BD38" s="351" t="s">
-        <v>300</v>
-      </c>
-      <c r="BE38" s="371" t="s">
-        <v>131</v>
+        <v>294</v>
+      </c>
+      <c r="BE38" s="370" t="s">
+        <v>130</v>
       </c>
       <c r="BF38" s="312"/>
       <c r="BG38" s="312"/>
       <c r="BH38" s="312"/>
       <c r="BI38" s="312"/>
-      <c r="BJ38" s="371" t="s">
-        <v>225</v>
+      <c r="BJ38" s="370" t="s">
+        <v>221</v>
       </c>
       <c r="BK38" s="312"/>
       <c r="BL38" s="312"/>
-      <c r="BM38" s="394" t="s">
-        <v>343</v>
+      <c r="BM38" s="397" t="s">
+        <v>337</v>
       </c>
       <c r="BN38" s="345" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="BO38" s="312"/>
       <c r="BP38" s="312"/>
@@ -11259,33 +11263,33 @@
       <c r="BT38" s="312"/>
       <c r="BU38" s="312"/>
       <c r="BV38" s="312"/>
-      <c r="BW38" s="400" t="s">
-        <v>315</v>
+      <c r="BW38" s="403" t="s">
+        <v>309</v>
       </c>
       <c r="BX38" s="348"/>
     </row>
     <row r="39" spans="1:79" ht="279.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="42"/>
       <c r="B39" s="97"/>
-      <c r="E39" s="452" t="s">
+      <c r="E39" s="455" t="s">
         <v>35</v>
       </c>
-      <c r="F39" s="453"/>
-      <c r="G39" s="454"/>
-      <c r="H39" s="433"/>
-      <c r="I39" s="434"/>
-      <c r="J39" s="433"/>
-      <c r="K39" s="434"/>
-      <c r="L39" s="435"/>
-      <c r="M39" s="435"/>
+      <c r="F39" s="456"/>
+      <c r="G39" s="457"/>
+      <c r="H39" s="436"/>
+      <c r="I39" s="437"/>
+      <c r="J39" s="436"/>
+      <c r="K39" s="437"/>
+      <c r="L39" s="438"/>
+      <c r="M39" s="438"/>
       <c r="N39" s="133"/>
-      <c r="O39" s="491"/>
-      <c r="P39" s="492"/>
-      <c r="Q39" s="492"/>
-      <c r="R39" s="492"/>
-      <c r="S39" s="492"/>
-      <c r="T39" s="492"/>
-      <c r="U39" s="493"/>
+      <c r="O39" s="494"/>
+      <c r="P39" s="495"/>
+      <c r="Q39" s="495"/>
+      <c r="R39" s="495"/>
+      <c r="S39" s="495"/>
+      <c r="T39" s="495"/>
+      <c r="U39" s="496"/>
       <c r="V39" s="97"/>
       <c r="W39" s="86"/>
       <c r="X39" s="86"/>
@@ -11309,91 +11313,89 @@
       <c r="AP39" s="313"/>
       <c r="AQ39" s="313"/>
       <c r="AR39" s="313"/>
-      <c r="AS39" s="394"/>
+      <c r="AS39" s="397"/>
       <c r="AT39" s="351"/>
       <c r="AU39" s="313"/>
       <c r="AV39" s="335" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="AW39" s="313"/>
       <c r="AX39" s="313"/>
       <c r="AY39" s="313"/>
       <c r="AZ39" s="313"/>
       <c r="BA39" s="335" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="BB39" s="313"/>
-      <c r="BC39" s="394"/>
+      <c r="BC39" s="397"/>
       <c r="BD39" s="351"/>
       <c r="BE39" s="335" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="BF39" s="335" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="BG39" s="313"/>
       <c r="BH39" s="335" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="BI39" s="335" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="BJ39" s="335" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="BK39" s="335" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="BL39" s="335" t="s">
-        <v>463</v>
-      </c>
-      <c r="BM39" s="394"/>
+        <v>457</v>
+      </c>
+      <c r="BM39" s="397"/>
       <c r="BN39" s="345"/>
       <c r="BO39" s="320" t="s">
         <v>83</v>
       </c>
       <c r="BP39" s="320" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="BQ39" s="313"/>
-      <c r="BR39" s="368" t="s">
-        <v>648</v>
-      </c>
+      <c r="BR39" s="313"/>
       <c r="BS39" s="335" t="s">
-        <v>649</v>
-      </c>
-      <c r="BT39" s="368" t="s">
-        <v>650</v>
+        <v>643</v>
+      </c>
+      <c r="BT39" s="367" t="s">
+        <v>644</v>
       </c>
       <c r="BU39" s="320" t="s">
         <v>82</v>
       </c>
-      <c r="BV39" s="320" t="s">
-        <v>232</v>
-      </c>
-      <c r="BW39" s="400"/>
+      <c r="BV39" s="391" t="s">
+        <v>228</v>
+      </c>
+      <c r="BW39" s="403"/>
       <c r="BX39" s="348"/>
     </row>
     <row r="40" spans="1:79" ht="279.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A40" s="42"/>
       <c r="B40" s="97"/>
-      <c r="E40" s="446"/>
-      <c r="F40" s="447"/>
-      <c r="G40" s="448"/>
-      <c r="H40" s="433"/>
-      <c r="I40" s="434"/>
-      <c r="J40" s="433"/>
-      <c r="K40" s="434"/>
-      <c r="L40" s="435"/>
-      <c r="M40" s="435"/>
+      <c r="E40" s="449"/>
+      <c r="F40" s="450"/>
+      <c r="G40" s="451"/>
+      <c r="H40" s="436"/>
+      <c r="I40" s="437"/>
+      <c r="J40" s="436"/>
+      <c r="K40" s="437"/>
+      <c r="L40" s="438"/>
+      <c r="M40" s="438"/>
       <c r="N40" s="81"/>
-      <c r="O40" s="491"/>
-      <c r="P40" s="492"/>
-      <c r="Q40" s="492"/>
-      <c r="R40" s="492"/>
-      <c r="S40" s="492"/>
-      <c r="T40" s="492"/>
-      <c r="U40" s="493"/>
+      <c r="O40" s="494"/>
+      <c r="P40" s="495"/>
+      <c r="Q40" s="495"/>
+      <c r="R40" s="495"/>
+      <c r="S40" s="495"/>
+      <c r="T40" s="495"/>
+      <c r="U40" s="496"/>
       <c r="W40" s="86"/>
       <c r="X40" s="86"/>
       <c r="Y40" s="132"/>
@@ -11404,7 +11406,7 @@
       <c r="AH40" s="42"/>
       <c r="AI40" s="42"/>
       <c r="AJ40" s="352" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AK40" s="328"/>
       <c r="AL40" s="328"/>
@@ -11414,11 +11416,11 @@
       <c r="AP40" s="328"/>
       <c r="AQ40" s="328"/>
       <c r="AR40" s="328"/>
-      <c r="AS40" s="395" t="s">
-        <v>556</v>
+      <c r="AS40" s="398" t="s">
+        <v>550</v>
       </c>
       <c r="AT40" s="352" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AU40" s="328"/>
       <c r="AV40" s="328"/>
@@ -11428,14 +11430,14 @@
       <c r="AZ40" s="328"/>
       <c r="BA40" s="328"/>
       <c r="BB40" s="328"/>
-      <c r="BC40" s="395" t="s">
-        <v>370</v>
+      <c r="BC40" s="398" t="s">
+        <v>364</v>
       </c>
       <c r="BD40" s="352" t="s">
-        <v>300</v>
-      </c>
-      <c r="BE40" s="371" t="s">
-        <v>250</v>
+        <v>294</v>
+      </c>
+      <c r="BE40" s="370" t="s">
+        <v>246</v>
       </c>
       <c r="BF40" s="328"/>
       <c r="BG40" s="328"/>
@@ -11444,11 +11446,11 @@
       <c r="BJ40" s="328"/>
       <c r="BK40" s="328"/>
       <c r="BL40" s="328"/>
-      <c r="BM40" s="395" t="s">
-        <v>344</v>
+      <c r="BM40" s="398" t="s">
+        <v>338</v>
       </c>
       <c r="BN40" s="346" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="BO40" s="321" t="s">
         <v>84</v>
@@ -11460,31 +11462,31 @@
       <c r="BT40" s="328"/>
       <c r="BU40" s="328"/>
       <c r="BV40" s="328"/>
-      <c r="BW40" s="401" t="s">
-        <v>316</v>
+      <c r="BW40" s="404" t="s">
+        <v>310</v>
       </c>
       <c r="BX40" s="348"/>
     </row>
     <row r="41" spans="1:79" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="42"/>
       <c r="B41" s="97"/>
-      <c r="E41" s="449"/>
-      <c r="F41" s="450"/>
-      <c r="G41" s="451"/>
-      <c r="H41" s="433"/>
-      <c r="I41" s="434"/>
-      <c r="J41" s="433"/>
-      <c r="K41" s="434"/>
-      <c r="L41" s="435"/>
-      <c r="M41" s="435"/>
+      <c r="E41" s="452"/>
+      <c r="F41" s="453"/>
+      <c r="G41" s="454"/>
+      <c r="H41" s="436"/>
+      <c r="I41" s="437"/>
+      <c r="J41" s="436"/>
+      <c r="K41" s="437"/>
+      <c r="L41" s="438"/>
+      <c r="M41" s="438"/>
       <c r="N41" s="81"/>
-      <c r="O41" s="491"/>
-      <c r="P41" s="492"/>
-      <c r="Q41" s="492"/>
-      <c r="R41" s="492"/>
-      <c r="S41" s="492"/>
-      <c r="T41" s="492"/>
-      <c r="U41" s="493"/>
+      <c r="O41" s="494"/>
+      <c r="P41" s="495"/>
+      <c r="Q41" s="495"/>
+      <c r="R41" s="495"/>
+      <c r="S41" s="495"/>
+      <c r="T41" s="495"/>
+      <c r="U41" s="496"/>
       <c r="W41" s="86"/>
       <c r="X41" s="86"/>
       <c r="Z41" s="135"/>
@@ -11501,103 +11503,103 @@
       <c r="AP41" s="327"/>
       <c r="AQ41" s="327"/>
       <c r="AR41" s="327"/>
-      <c r="AS41" s="395"/>
+      <c r="AS41" s="398"/>
       <c r="AT41" s="352"/>
       <c r="AU41" s="333" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="AV41" s="333" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="AW41" s="361" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="AX41" s="327"/>
       <c r="AY41" s="361" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="AZ41" s="361" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="BA41" s="361" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="BB41" s="361" t="s">
-        <v>458</v>
-      </c>
-      <c r="BC41" s="395"/>
+        <v>452</v>
+      </c>
+      <c r="BC41" s="398"/>
       <c r="BD41" s="352"/>
       <c r="BE41" s="359" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="BF41" s="359" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="BG41" s="327"/>
       <c r="BH41" s="359" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="BI41" s="359" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="BJ41" s="359" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="BK41" s="359" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="BL41" s="335" t="s">
-        <v>233</v>
-      </c>
-      <c r="BM41" s="395"/>
+        <v>229</v>
+      </c>
+      <c r="BM41" s="398"/>
       <c r="BN41" s="346"/>
       <c r="BO41" s="320" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="BP41" s="320" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="BQ41" s="327"/>
-      <c r="BR41" s="368" t="s">
-        <v>665</v>
+      <c r="BR41" s="367" t="s">
+        <v>642</v>
       </c>
       <c r="BS41" s="359" t="s">
-        <v>230</v>
-      </c>
-      <c r="BT41" s="387" t="s">
-        <v>590</v>
+        <v>226</v>
+      </c>
+      <c r="BT41" s="386" t="s">
+        <v>584</v>
       </c>
       <c r="BU41" s="335" t="s">
-        <v>651</v>
-      </c>
-      <c r="BV41" s="368" t="s">
-        <v>652</v>
-      </c>
-      <c r="BW41" s="401"/>
+        <v>645</v>
+      </c>
+      <c r="BV41" s="367" t="s">
+        <v>646</v>
+      </c>
+      <c r="BW41" s="404"/>
       <c r="BX41" s="348"/>
     </row>
     <row r="42" spans="1:79" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="42"/>
       <c r="B42" s="97"/>
-      <c r="E42" s="452" t="s">
+      <c r="E42" s="455" t="s">
         <v>36</v>
       </c>
-      <c r="F42" s="453"/>
-      <c r="G42" s="454"/>
-      <c r="H42" s="433"/>
-      <c r="I42" s="434"/>
-      <c r="J42" s="433"/>
-      <c r="K42" s="434"/>
-      <c r="L42" s="435"/>
-      <c r="M42" s="435"/>
+      <c r="F42" s="456"/>
+      <c r="G42" s="457"/>
+      <c r="H42" s="436"/>
+      <c r="I42" s="437"/>
+      <c r="J42" s="436"/>
+      <c r="K42" s="437"/>
+      <c r="L42" s="438"/>
+      <c r="M42" s="438"/>
       <c r="N42" s="81"/>
-      <c r="O42" s="491"/>
-      <c r="P42" s="492"/>
-      <c r="Q42" s="492"/>
-      <c r="R42" s="492"/>
-      <c r="S42" s="492"/>
-      <c r="T42" s="492"/>
-      <c r="U42" s="493"/>
+      <c r="O42" s="494"/>
+      <c r="P42" s="495"/>
+      <c r="Q42" s="495"/>
+      <c r="R42" s="495"/>
+      <c r="S42" s="495"/>
+      <c r="T42" s="495"/>
+      <c r="U42" s="496"/>
       <c r="V42" s="92"/>
       <c r="W42" s="86"/>
       <c r="X42" s="86"/>
@@ -11609,7 +11611,7 @@
       <c r="AG42" s="108"/>
       <c r="AH42" s="108"/>
       <c r="AJ42" s="351" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AK42" s="312"/>
       <c r="AL42" s="312"/>
@@ -11619,11 +11621,11 @@
       <c r="AP42" s="312"/>
       <c r="AQ42" s="312"/>
       <c r="AR42" s="312"/>
-      <c r="AS42" s="394" t="s">
-        <v>557</v>
+      <c r="AS42" s="397" t="s">
+        <v>551</v>
       </c>
       <c r="AT42" s="351" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AU42" s="312"/>
       <c r="AV42" s="312"/>
@@ -11633,11 +11635,11 @@
       <c r="AZ42" s="312"/>
       <c r="BA42" s="312"/>
       <c r="BB42" s="312"/>
-      <c r="BC42" s="394" t="s">
-        <v>371</v>
+      <c r="BC42" s="397" t="s">
+        <v>365</v>
       </c>
       <c r="BD42" s="351" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="BE42" s="312"/>
       <c r="BF42" s="312"/>
@@ -11646,14 +11648,14 @@
       <c r="BI42" s="312"/>
       <c r="BJ42" s="312"/>
       <c r="BK42" s="334" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="BL42" s="312"/>
-      <c r="BM42" s="394" t="s">
-        <v>345</v>
+      <c r="BM42" s="397" t="s">
+        <v>339</v>
       </c>
       <c r="BN42" s="345" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="BO42" s="312"/>
       <c r="BP42" s="321" t="s">
@@ -11665,8 +11667,8 @@
       <c r="BT42" s="312"/>
       <c r="BU42" s="312"/>
       <c r="BV42" s="312"/>
-      <c r="BW42" s="400" t="s">
-        <v>317</v>
+      <c r="BW42" s="403" t="s">
+        <v>311</v>
       </c>
       <c r="BX42" s="348"/>
     </row>
@@ -11675,23 +11677,23 @@
       <c r="B43" s="97"/>
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
-      <c r="E43" s="449"/>
-      <c r="F43" s="450"/>
-      <c r="G43" s="451"/>
-      <c r="H43" s="433"/>
-      <c r="I43" s="434"/>
-      <c r="J43" s="433"/>
-      <c r="K43" s="434"/>
-      <c r="L43" s="435"/>
-      <c r="M43" s="435"/>
+      <c r="E43" s="452"/>
+      <c r="F43" s="453"/>
+      <c r="G43" s="454"/>
+      <c r="H43" s="436"/>
+      <c r="I43" s="437"/>
+      <c r="J43" s="436"/>
+      <c r="K43" s="437"/>
+      <c r="L43" s="438"/>
+      <c r="M43" s="438"/>
       <c r="N43" s="81"/>
-      <c r="O43" s="491"/>
-      <c r="P43" s="492"/>
-      <c r="Q43" s="492"/>
-      <c r="R43" s="492"/>
-      <c r="S43" s="492"/>
-      <c r="T43" s="492"/>
-      <c r="U43" s="493"/>
+      <c r="O43" s="494"/>
+      <c r="P43" s="495"/>
+      <c r="Q43" s="495"/>
+      <c r="R43" s="495"/>
+      <c r="S43" s="495"/>
+      <c r="T43" s="495"/>
+      <c r="U43" s="496"/>
       <c r="V43" s="138"/>
       <c r="W43" s="86"/>
       <c r="X43" s="86"/>
@@ -11715,55 +11717,55 @@
       <c r="AP43" s="313"/>
       <c r="AQ43" s="313"/>
       <c r="AR43" s="313"/>
-      <c r="AS43" s="394"/>
+      <c r="AS43" s="397"/>
       <c r="AT43" s="351"/>
       <c r="AU43" s="333" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="AV43" s="333" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="AW43" s="333" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="AX43" s="313"/>
       <c r="AY43" s="361" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="AZ43" s="335" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="BA43" s="361" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="BB43" s="361" t="s">
-        <v>505</v>
-      </c>
-      <c r="BC43" s="394"/>
+        <v>499</v>
+      </c>
+      <c r="BC43" s="397"/>
       <c r="BD43" s="351"/>
       <c r="BE43" s="359" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="BF43" s="335" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="BG43" s="313"/>
       <c r="BH43" s="335" t="s">
+        <v>143</v>
+      </c>
+      <c r="BI43" s="335" t="s">
         <v>144</v>
       </c>
-      <c r="BI43" s="335" t="s">
-        <v>145</v>
-      </c>
       <c r="BJ43" s="335" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BK43" s="335" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="BL43" s="335" t="s">
-        <v>159</v>
-      </c>
-      <c r="BM43" s="394"/>
+        <v>157</v>
+      </c>
+      <c r="BM43" s="397"/>
       <c r="BN43" s="345"/>
       <c r="BO43" s="320" t="s">
         <v>86</v>
@@ -11772,22 +11774,22 @@
         <v>88</v>
       </c>
       <c r="BQ43" s="313"/>
-      <c r="BR43" s="368" t="s">
-        <v>647</v>
-      </c>
-      <c r="BS43" s="384" t="s">
-        <v>591</v>
+      <c r="BR43" s="367" t="s">
+        <v>659</v>
+      </c>
+      <c r="BS43" s="383" t="s">
+        <v>585</v>
       </c>
       <c r="BT43" s="359" t="s">
-        <v>234</v>
-      </c>
-      <c r="BU43" s="368" t="s">
-        <v>464</v>
-      </c>
-      <c r="BV43" s="368" t="s">
-        <v>592</v>
-      </c>
-      <c r="BW43" s="400"/>
+        <v>230</v>
+      </c>
+      <c r="BU43" s="367" t="s">
+        <v>458</v>
+      </c>
+      <c r="BV43" s="367" t="s">
+        <v>586</v>
+      </c>
+      <c r="BW43" s="403"/>
       <c r="BX43" s="349"/>
     </row>
     <row r="44" spans="1:79" s="143" customFormat="1" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -11795,25 +11797,25 @@
       <c r="B44" s="90"/>
       <c r="C44" s="6"/>
       <c r="D44" s="6"/>
-      <c r="E44" s="449" t="s">
+      <c r="E44" s="452" t="s">
         <v>37</v>
       </c>
-      <c r="F44" s="450"/>
-      <c r="G44" s="451"/>
-      <c r="H44" s="436"/>
-      <c r="I44" s="437"/>
-      <c r="J44" s="436"/>
-      <c r="K44" s="437"/>
-      <c r="L44" s="439"/>
-      <c r="M44" s="439"/>
+      <c r="F44" s="453"/>
+      <c r="G44" s="454"/>
+      <c r="H44" s="439"/>
+      <c r="I44" s="440"/>
+      <c r="J44" s="439"/>
+      <c r="K44" s="440"/>
+      <c r="L44" s="442"/>
+      <c r="M44" s="442"/>
       <c r="N44" s="81"/>
-      <c r="O44" s="491"/>
-      <c r="P44" s="492"/>
-      <c r="Q44" s="492"/>
-      <c r="R44" s="492"/>
-      <c r="S44" s="492"/>
-      <c r="T44" s="492"/>
-      <c r="U44" s="493"/>
+      <c r="O44" s="494"/>
+      <c r="P44" s="495"/>
+      <c r="Q44" s="495"/>
+      <c r="R44" s="495"/>
+      <c r="S44" s="495"/>
+      <c r="T44" s="495"/>
+      <c r="U44" s="496"/>
       <c r="V44" s="42"/>
       <c r="W44" s="6"/>
       <c r="X44" s="139"/>
@@ -11829,7 +11831,7 @@
       <c r="AH44" s="108"/>
       <c r="AI44" s="42"/>
       <c r="AJ44" s="352" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AK44" s="328"/>
       <c r="AL44" s="328"/>
@@ -11839,11 +11841,11 @@
       <c r="AP44" s="328"/>
       <c r="AQ44" s="328"/>
       <c r="AR44" s="328"/>
-      <c r="AS44" s="395" t="s">
-        <v>558</v>
+      <c r="AS44" s="398" t="s">
+        <v>552</v>
       </c>
       <c r="AT44" s="352" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AU44" s="328"/>
       <c r="AV44" s="328"/>
@@ -11853,11 +11855,11 @@
       <c r="AZ44" s="328"/>
       <c r="BA44" s="328"/>
       <c r="BB44" s="328"/>
-      <c r="BC44" s="395" t="s">
-        <v>372</v>
+      <c r="BC44" s="398" t="s">
+        <v>366</v>
       </c>
       <c r="BD44" s="352" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="BE44" s="328"/>
       <c r="BF44" s="328"/>
@@ -11867,11 +11869,11 @@
       <c r="BJ44" s="328"/>
       <c r="BK44" s="328"/>
       <c r="BL44" s="328"/>
-      <c r="BM44" s="395" t="s">
-        <v>346</v>
+      <c r="BM44" s="398" t="s">
+        <v>340</v>
       </c>
       <c r="BN44" s="346" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="BO44" s="328"/>
       <c r="BP44" s="328"/>
@@ -11881,46 +11883,46 @@
       <c r="BT44" s="328"/>
       <c r="BU44" s="328"/>
       <c r="BV44" s="328"/>
-      <c r="BW44" s="401" t="s">
-        <v>318</v>
+      <c r="BW44" s="404" t="s">
+        <v>312</v>
       </c>
       <c r="BX44" s="349"/>
     </row>
     <row r="45" spans="1:79" s="143" customFormat="1" ht="279.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="42"/>
       <c r="B45" s="90"/>
-      <c r="E45" s="494" t="s">
+      <c r="E45" s="497" t="s">
         <v>38</v>
       </c>
-      <c r="F45" s="494"/>
-      <c r="G45" s="494"/>
-      <c r="H45" s="494"/>
-      <c r="I45" s="494"/>
-      <c r="J45" s="494"/>
-      <c r="K45" s="494"/>
-      <c r="L45" s="494"/>
-      <c r="M45" s="494"/>
+      <c r="F45" s="497"/>
+      <c r="G45" s="497"/>
+      <c r="H45" s="497"/>
+      <c r="I45" s="497"/>
+      <c r="J45" s="497"/>
+      <c r="K45" s="497"/>
+      <c r="L45" s="497"/>
+      <c r="M45" s="497"/>
       <c r="N45" s="145"/>
-      <c r="O45" s="495" t="s">
+      <c r="O45" s="498" t="s">
         <v>38</v>
       </c>
-      <c r="P45" s="496"/>
-      <c r="Q45" s="496"/>
-      <c r="R45" s="496"/>
-      <c r="S45" s="496"/>
-      <c r="T45" s="496"/>
-      <c r="U45" s="496"/>
+      <c r="P45" s="499"/>
+      <c r="Q45" s="499"/>
+      <c r="R45" s="499"/>
+      <c r="S45" s="499"/>
+      <c r="T45" s="499"/>
+      <c r="U45" s="499"/>
       <c r="V45" s="146"/>
       <c r="W45" s="147"/>
       <c r="X45" s="147"/>
       <c r="Y45" s="147"/>
       <c r="Z45" s="148"/>
-      <c r="AA45" s="497"/>
-      <c r="AB45" s="498"/>
-      <c r="AC45" s="498"/>
-      <c r="AD45" s="499"/>
-      <c r="AE45" s="499"/>
-      <c r="AF45" s="499"/>
+      <c r="AA45" s="500"/>
+      <c r="AB45" s="501"/>
+      <c r="AC45" s="501"/>
+      <c r="AD45" s="502"/>
+      <c r="AE45" s="502"/>
+      <c r="AF45" s="502"/>
       <c r="AG45" s="149"/>
       <c r="AH45" s="149"/>
       <c r="AI45" s="150"/>
@@ -11933,77 +11935,77 @@
       <c r="AP45" s="327"/>
       <c r="AQ45" s="327"/>
       <c r="AR45" s="327"/>
-      <c r="AS45" s="395"/>
+      <c r="AS45" s="398"/>
       <c r="AT45" s="352"/>
       <c r="AU45" s="333" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="AV45" s="333" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="AW45" s="361" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="AX45" s="327"/>
       <c r="AY45" s="361" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="AZ45" s="333" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="BA45" s="361" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="BB45" s="333" t="s">
-        <v>512</v>
-      </c>
-      <c r="BC45" s="395"/>
+        <v>506</v>
+      </c>
+      <c r="BC45" s="398"/>
       <c r="BD45" s="352"/>
       <c r="BE45" s="335" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="BF45" s="335" t="s">
+        <v>145</v>
+      </c>
+      <c r="BG45" s="384"/>
+      <c r="BH45" s="335" t="s">
+        <v>141</v>
+      </c>
+      <c r="BI45" s="335" t="s">
+        <v>150</v>
+      </c>
+      <c r="BJ45" s="335" t="s">
+        <v>161</v>
+      </c>
+      <c r="BK45" s="335" t="s">
+        <v>155</v>
+      </c>
+      <c r="BL45" s="335" t="s">
         <v>146</v>
       </c>
-      <c r="BG45" s="385"/>
-      <c r="BH45" s="335" t="s">
-        <v>142</v>
-      </c>
-      <c r="BI45" s="335" t="s">
-        <v>151</v>
-      </c>
-      <c r="BJ45" s="335" t="s">
-        <v>163</v>
-      </c>
-      <c r="BK45" s="335" t="s">
-        <v>156</v>
-      </c>
-      <c r="BL45" s="335" t="s">
-        <v>147</v>
-      </c>
-      <c r="BM45" s="395"/>
+      <c r="BM45" s="398"/>
       <c r="BN45" s="346"/>
       <c r="BO45" s="335" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="BP45" s="320" t="s">
         <v>87</v>
       </c>
       <c r="BQ45" s="327"/>
-      <c r="BR45" s="335" t="s">
-        <v>631</v>
+      <c r="BR45" s="367" t="s">
+        <v>641</v>
       </c>
       <c r="BS45" s="359" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="BT45" s="335" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="BU45" s="335" t="s">
-        <v>593</v>
-      </c>
-      <c r="BV45" s="375"/>
-      <c r="BW45" s="401"/>
+        <v>587</v>
+      </c>
+      <c r="BV45" s="374"/>
+      <c r="BW45" s="404"/>
       <c r="BX45" s="349"/>
     </row>
     <row r="46" spans="1:79" s="143" customFormat="1" ht="279.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
@@ -12026,7 +12028,7 @@
       </c>
       <c r="M46" s="72"/>
       <c r="N46" s="154"/>
-      <c r="O46" s="500"/>
+      <c r="O46" s="503"/>
       <c r="P46" s="53"/>
       <c r="Q46" s="53"/>
       <c r="R46" s="53"/>
@@ -12046,7 +12048,7 @@
       <c r="AH46" s="108"/>
       <c r="AI46" s="111"/>
       <c r="AJ46" s="351" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AK46" s="312"/>
       <c r="AL46" s="312"/>
@@ -12056,11 +12058,11 @@
       <c r="AP46" s="312"/>
       <c r="AQ46" s="312"/>
       <c r="AR46" s="312"/>
-      <c r="AS46" s="394" t="s">
-        <v>559</v>
+      <c r="AS46" s="397" t="s">
+        <v>553</v>
       </c>
       <c r="AT46" s="351" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AU46" s="312"/>
       <c r="AV46" s="312"/>
@@ -12070,11 +12072,11 @@
       <c r="AZ46" s="312"/>
       <c r="BA46" s="312"/>
       <c r="BB46" s="312"/>
-      <c r="BC46" s="394" t="s">
-        <v>373</v>
+      <c r="BC46" s="397" t="s">
+        <v>367</v>
       </c>
       <c r="BD46" s="351" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="BE46" s="312"/>
       <c r="BF46" s="312"/>
@@ -12084,13 +12086,13 @@
       <c r="BJ46" s="312"/>
       <c r="BK46" s="312"/>
       <c r="BL46" s="321" t="s">
-        <v>528</v>
-      </c>
-      <c r="BM46" s="394" t="s">
-        <v>347</v>
+        <v>522</v>
+      </c>
+      <c r="BM46" s="397" t="s">
+        <v>341</v>
       </c>
       <c r="BN46" s="345" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="BO46" s="312"/>
       <c r="BP46" s="312"/>
@@ -12099,13 +12101,13 @@
       <c r="BS46" s="312"/>
       <c r="BT46" s="312"/>
       <c r="BU46" s="334" t="s">
-        <v>482</v>
-      </c>
-      <c r="BV46" s="371" t="s">
-        <v>403</v>
-      </c>
-      <c r="BW46" s="400" t="s">
-        <v>319</v>
+        <v>476</v>
+      </c>
+      <c r="BV46" s="370" t="s">
+        <v>397</v>
+      </c>
+      <c r="BW46" s="403" t="s">
+        <v>313</v>
       </c>
       <c r="BX46" s="349"/>
     </row>
@@ -12123,7 +12125,7 @@
       <c r="L47" s="79"/>
       <c r="M47" s="79"/>
       <c r="N47" s="154"/>
-      <c r="O47" s="501"/>
+      <c r="O47" s="504"/>
       <c r="P47" s="53"/>
       <c r="Q47" s="53"/>
       <c r="R47" s="53"/>
@@ -12152,76 +12154,76 @@
       <c r="AP47" s="313"/>
       <c r="AQ47" s="313"/>
       <c r="AR47" s="313"/>
-      <c r="AS47" s="394"/>
+      <c r="AS47" s="397"/>
       <c r="AT47" s="351"/>
       <c r="AU47" s="320" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="AV47" s="320" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AW47" s="361" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="AX47" s="313"/>
       <c r="AY47" s="361" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="AZ47" s="333" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="BA47" s="333" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="BB47" s="333" t="s">
-        <v>517</v>
-      </c>
-      <c r="BC47" s="394"/>
+        <v>511</v>
+      </c>
+      <c r="BC47" s="397"/>
       <c r="BD47" s="351"/>
       <c r="BE47" s="335" t="s">
+        <v>148</v>
+      </c>
+      <c r="BF47" s="335" t="s">
         <v>149</v>
       </c>
-      <c r="BF47" s="335" t="s">
-        <v>150</v>
-      </c>
       <c r="BH47" s="359" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="BI47" s="335" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="BJ47" s="335" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="BK47" s="313"/>
       <c r="BL47" s="320" t="s">
-        <v>242</v>
-      </c>
-      <c r="BM47" s="394"/>
+        <v>238</v>
+      </c>
+      <c r="BM47" s="397"/>
       <c r="BN47" s="345"/>
       <c r="BO47" s="335" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="BP47" s="335" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="BQ47" s="313"/>
       <c r="BR47" s="335" t="s">
-        <v>664</v>
+        <v>625</v>
       </c>
       <c r="BS47" s="335" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="BT47" s="335" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="BU47" s="335" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="BV47" s="359" t="s">
-        <v>290</v>
-      </c>
-      <c r="BW47" s="400"/>
+        <v>284</v>
+      </c>
+      <c r="BW47" s="403"/>
       <c r="BX47" s="349"/>
     </row>
     <row r="48" spans="1:79" s="143" customFormat="1" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -12258,7 +12260,7 @@
       <c r="AH48" s="167"/>
       <c r="AI48" s="167"/>
       <c r="AJ48" s="352" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AK48" s="328"/>
       <c r="AL48" s="328"/>
@@ -12268,11 +12270,11 @@
       <c r="AP48" s="328"/>
       <c r="AQ48" s="328"/>
       <c r="AR48" s="328"/>
-      <c r="AS48" s="395" t="s">
-        <v>560</v>
+      <c r="AS48" s="398" t="s">
+        <v>554</v>
       </c>
       <c r="AT48" s="352" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AU48" s="328"/>
       <c r="AV48" s="328"/>
@@ -12282,11 +12284,11 @@
       <c r="AZ48" s="328"/>
       <c r="BA48" s="328"/>
       <c r="BB48" s="328"/>
-      <c r="BC48" s="395" t="s">
-        <v>374</v>
+      <c r="BC48" s="398" t="s">
+        <v>368</v>
       </c>
       <c r="BD48" s="352" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="BE48" s="328"/>
       <c r="BF48" s="328"/>
@@ -12294,15 +12296,15 @@
       <c r="BH48" s="328"/>
       <c r="BI48" s="328"/>
       <c r="BJ48" s="321" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="BK48" s="328"/>
       <c r="BL48" s="328"/>
-      <c r="BM48" s="395" t="s">
-        <v>348</v>
+      <c r="BM48" s="398" t="s">
+        <v>342</v>
       </c>
       <c r="BN48" s="346" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="BO48" s="328"/>
       <c r="BP48" s="328"/>
@@ -12310,16 +12312,16 @@
       <c r="BR48" s="328"/>
       <c r="BS48" s="328"/>
       <c r="BT48" s="321" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="BU48" s="321" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="BV48" s="321" t="s">
-        <v>244</v>
-      </c>
-      <c r="BW48" s="401" t="s">
-        <v>320</v>
+        <v>240</v>
+      </c>
+      <c r="BW48" s="404" t="s">
+        <v>314</v>
       </c>
       <c r="BX48" s="349"/>
     </row>
@@ -12364,77 +12366,77 @@
       <c r="AP49" s="327"/>
       <c r="AQ49" s="327"/>
       <c r="AR49" s="327"/>
-      <c r="AS49" s="395"/>
+      <c r="AS49" s="398"/>
       <c r="AT49" s="352"/>
       <c r="AU49" s="361" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="AV49" s="361" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="AW49" s="361" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="AX49" s="327"/>
       <c r="AY49" s="361" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="AZ49" s="361" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="BA49" s="361" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="BB49" s="327"/>
-      <c r="BC49" s="395"/>
+      <c r="BC49" s="398"/>
       <c r="BD49" s="352"/>
       <c r="BE49" s="335" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="BF49" s="335" t="s">
-        <v>245</v>
-      </c>
-      <c r="BG49" s="372"/>
+        <v>241</v>
+      </c>
+      <c r="BG49" s="371"/>
       <c r="BH49" s="320" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="BI49" s="320" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="BJ49" s="320" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="BK49" s="320" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="BL49" s="359" t="s">
-        <v>451</v>
-      </c>
-      <c r="BM49" s="395"/>
+        <v>445</v>
+      </c>
+      <c r="BM49" s="398"/>
       <c r="BN49" s="346"/>
       <c r="BO49" s="335" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="BP49" s="335" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="BQ49" s="327"/>
       <c r="BR49" s="335" t="s">
-        <v>596</v>
+        <v>658</v>
       </c>
       <c r="BS49" s="320" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="BT49" s="320" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="BU49" s="320" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="BV49" s="320" t="s">
-        <v>288</v>
-      </c>
-      <c r="BW49" s="401"/>
+        <v>282</v>
+      </c>
+      <c r="BW49" s="404"/>
       <c r="BX49" s="349"/>
     </row>
     <row r="50" spans="1:86" s="143" customFormat="1" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -12450,8 +12452,8 @@
       <c r="L50" s="79"/>
       <c r="M50" s="79"/>
       <c r="N50" s="154"/>
-      <c r="O50" s="511"/>
-      <c r="P50" s="501"/>
+      <c r="O50" s="514"/>
+      <c r="P50" s="504"/>
       <c r="Q50" s="172"/>
       <c r="R50" s="172"/>
       <c r="S50" s="172"/>
@@ -12470,7 +12472,7 @@
       <c r="AH50" s="167"/>
       <c r="AI50" s="167"/>
       <c r="AJ50" s="351" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AK50" s="312"/>
       <c r="AL50" s="312"/>
@@ -12480,11 +12482,11 @@
       <c r="AP50" s="312"/>
       <c r="AQ50" s="312"/>
       <c r="AR50" s="312"/>
-      <c r="AS50" s="394" t="s">
-        <v>561</v>
+      <c r="AS50" s="397" t="s">
+        <v>555</v>
       </c>
       <c r="AT50" s="351" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AU50" s="312"/>
       <c r="AV50" s="312"/>
@@ -12494,14 +12496,14 @@
       <c r="AZ50" s="312"/>
       <c r="BA50" s="312"/>
       <c r="BB50" s="312"/>
-      <c r="BC50" s="394" t="s">
-        <v>375</v>
+      <c r="BC50" s="397" t="s">
+        <v>369</v>
       </c>
       <c r="BD50" s="351" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="BE50" s="334" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="BF50" s="312"/>
       <c r="BG50" s="312"/>
@@ -12509,14 +12511,14 @@
       <c r="BI50" s="312"/>
       <c r="BJ50" s="312"/>
       <c r="BK50" s="321" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="BL50" s="312"/>
-      <c r="BM50" s="394" t="s">
-        <v>349</v>
+      <c r="BM50" s="397" t="s">
+        <v>343</v>
       </c>
       <c r="BN50" s="345" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="BO50" s="312"/>
       <c r="BP50" s="312"/>
@@ -12526,10 +12528,10 @@
       <c r="BT50" s="312"/>
       <c r="BU50" s="312"/>
       <c r="BV50" s="321" t="s">
-        <v>101</v>
-      </c>
-      <c r="BW50" s="400" t="s">
-        <v>321</v>
+        <v>100</v>
+      </c>
+      <c r="BW50" s="403" t="s">
+        <v>315</v>
       </c>
       <c r="BX50" s="349"/>
     </row>
@@ -12546,8 +12548,8 @@
       <c r="L51" s="79"/>
       <c r="M51" s="79"/>
       <c r="N51" s="154"/>
-      <c r="O51" s="511"/>
-      <c r="P51" s="501"/>
+      <c r="O51" s="514"/>
+      <c r="P51" s="504"/>
       <c r="Q51" s="172"/>
       <c r="R51" s="172"/>
       <c r="S51" s="172"/>
@@ -12572,89 +12574,87 @@
       <c r="AP51" s="313"/>
       <c r="AQ51" s="313"/>
       <c r="AR51" s="313"/>
-      <c r="AS51" s="394"/>
+      <c r="AS51" s="397"/>
       <c r="AT51" s="351"/>
       <c r="AU51" s="361" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="AV51" s="361" t="s">
-        <v>603</v>
-      </c>
-      <c r="AW51" s="368" t="s">
-        <v>675</v>
+        <v>597</v>
+      </c>
+      <c r="AW51" s="367" t="s">
+        <v>669</v>
       </c>
       <c r="AX51" s="313"/>
       <c r="AY51" s="361" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="AZ51" s="361" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="BA51" s="361" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="BB51" s="361" t="s">
-        <v>525</v>
-      </c>
-      <c r="BC51" s="394"/>
+        <v>519</v>
+      </c>
+      <c r="BC51" s="397"/>
       <c r="BD51" s="351"/>
       <c r="BE51" s="335" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="BF51" s="335" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="BG51" s="313"/>
-      <c r="BH51" s="369" t="s">
-        <v>663</v>
+      <c r="BH51" s="368" t="s">
+        <v>657</v>
       </c>
       <c r="BI51" s="320" t="s">
-        <v>236</v>
-      </c>
-      <c r="BJ51" s="392" t="s">
-        <v>157</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="BJ51" s="313"/>
       <c r="BK51" s="320" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="BL51" s="320" t="s">
-        <v>158</v>
-      </c>
-      <c r="BM51" s="394"/>
+        <v>156</v>
+      </c>
+      <c r="BM51" s="397"/>
       <c r="BN51" s="345"/>
       <c r="BO51" s="335" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="BP51" s="335" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="BQ51" s="313"/>
       <c r="BR51" s="335" t="s">
-        <v>483</v>
+        <v>590</v>
       </c>
       <c r="BS51" s="320" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="BT51" s="320" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="BU51" s="320" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="BV51" s="320" t="s">
-        <v>93</v>
-      </c>
-      <c r="BW51" s="400"/>
+        <v>92</v>
+      </c>
+      <c r="BW51" s="403"/>
       <c r="BX51" s="349"/>
     </row>
     <row r="52" spans="1:86" s="143" customFormat="1" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="151"/>
       <c r="B52" s="151"/>
-      <c r="E52" s="502" t="s">
+      <c r="E52" s="505" t="s">
         <v>42</v>
       </c>
-      <c r="F52" s="503"/>
-      <c r="G52" s="506" t="s">
+      <c r="F52" s="506"/>
+      <c r="G52" s="509" t="s">
         <v>43</v>
       </c>
       <c r="H52" s="79"/>
@@ -12664,8 +12664,8 @@
       <c r="L52" s="79"/>
       <c r="M52" s="79"/>
       <c r="N52" s="154"/>
-      <c r="O52" s="511"/>
-      <c r="P52" s="501"/>
+      <c r="O52" s="514"/>
+      <c r="P52" s="504"/>
       <c r="Q52" s="172"/>
       <c r="R52" s="172"/>
       <c r="S52" s="172"/>
@@ -12681,7 +12681,7 @@
       <c r="AH52" s="175"/>
       <c r="AI52" s="175"/>
       <c r="AJ52" s="352" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AK52" s="328"/>
       <c r="AL52" s="328"/>
@@ -12691,11 +12691,11 @@
       <c r="AP52" s="328"/>
       <c r="AQ52" s="328"/>
       <c r="AR52" s="328"/>
-      <c r="AS52" s="395" t="s">
-        <v>562</v>
+      <c r="AS52" s="398" t="s">
+        <v>556</v>
       </c>
       <c r="AT52" s="352" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AU52" s="328"/>
       <c r="AV52" s="328"/>
@@ -12705,31 +12705,31 @@
       <c r="AZ52" s="328"/>
       <c r="BA52" s="328"/>
       <c r="BB52" s="328"/>
-      <c r="BC52" s="395" t="s">
-        <v>376</v>
+      <c r="BC52" s="398" t="s">
+        <v>370</v>
       </c>
       <c r="BD52" s="352" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="BE52" s="334" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="BF52" s="328"/>
       <c r="BG52" s="328"/>
       <c r="BH52" s="328"/>
       <c r="BI52" s="328"/>
       <c r="BJ52" s="321" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="BK52" s="328"/>
       <c r="BL52" s="321" t="s">
-        <v>530</v>
-      </c>
-      <c r="BM52" s="395" t="s">
-        <v>350</v>
+        <v>524</v>
+      </c>
+      <c r="BM52" s="398" t="s">
+        <v>344</v>
       </c>
       <c r="BN52" s="346" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="BO52" s="328"/>
       <c r="BP52" s="328"/>
@@ -12739,25 +12739,25 @@
         <v>81</v>
       </c>
       <c r="BT52" s="321" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="BU52" s="321" t="s">
         <v>90</v>
       </c>
       <c r="BV52" s="321" t="s">
-        <v>415</v>
-      </c>
-      <c r="BW52" s="401" t="s">
-        <v>322</v>
+        <v>409</v>
+      </c>
+      <c r="BW52" s="404" t="s">
+        <v>316</v>
       </c>
       <c r="BX52" s="349"/>
     </row>
     <row r="53" spans="1:86" s="143" customFormat="1" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="151"/>
       <c r="B53" s="151"/>
-      <c r="E53" s="504"/>
-      <c r="F53" s="505"/>
-      <c r="G53" s="507"/>
+      <c r="E53" s="507"/>
+      <c r="F53" s="508"/>
+      <c r="G53" s="510"/>
       <c r="H53" s="79"/>
       <c r="I53" s="79"/>
       <c r="J53" s="78"/>
@@ -12789,73 +12789,73 @@
       <c r="AP53" s="327"/>
       <c r="AQ53" s="327"/>
       <c r="AR53" s="327"/>
-      <c r="AS53" s="395"/>
+      <c r="AS53" s="398"/>
       <c r="AT53" s="352"/>
       <c r="AU53" s="361" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="AV53" s="361" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="AW53" s="333" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="AX53" s="327"/>
       <c r="AY53" s="333" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="AZ53" s="361" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="BA53" s="361" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="BB53" s="327"/>
-      <c r="BC53" s="395"/>
+      <c r="BC53" s="398"/>
       <c r="BD53" s="352"/>
       <c r="BE53" s="335" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="BF53" s="335" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="BG53" s="327"/>
       <c r="BH53" s="320" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="BI53" s="327"/>
       <c r="BJ53" s="320" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="BK53" s="327"/>
       <c r="BL53" s="320" t="s">
-        <v>251</v>
-      </c>
-      <c r="BM53" s="395"/>
+        <v>247</v>
+      </c>
+      <c r="BM53" s="398"/>
       <c r="BN53" s="346"/>
-      <c r="BO53" s="368" t="s">
-        <v>490</v>
-      </c>
-      <c r="BP53" s="368" t="s">
-        <v>489</v>
+      <c r="BO53" s="367" t="s">
+        <v>484</v>
+      </c>
+      <c r="BP53" s="367" t="s">
+        <v>483</v>
       </c>
       <c r="BQ53" s="327"/>
       <c r="BR53" s="335" t="s">
-        <v>105</v>
+        <v>477</v>
       </c>
       <c r="BS53" s="320" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="BT53" s="362" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="BU53" s="320" t="s">
         <v>89</v>
       </c>
       <c r="BV53" s="320" t="s">
-        <v>414</v>
-      </c>
-      <c r="BW53" s="401"/>
+        <v>408</v>
+      </c>
+      <c r="BW53" s="404"/>
       <c r="BX53" s="349"/>
     </row>
     <row r="54" spans="1:86" s="143" customFormat="1" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -12889,7 +12889,7 @@
       <c r="AH54" s="165"/>
       <c r="AI54" s="178"/>
       <c r="AJ54" s="351" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AK54" s="312"/>
       <c r="AL54" s="312"/>
@@ -12899,11 +12899,11 @@
       <c r="AP54" s="312"/>
       <c r="AQ54" s="312"/>
       <c r="AR54" s="312"/>
-      <c r="AS54" s="394" t="s">
-        <v>563</v>
+      <c r="AS54" s="397" t="s">
+        <v>557</v>
       </c>
       <c r="AT54" s="351" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AU54" s="312"/>
       <c r="AV54" s="312"/>
@@ -12913,41 +12913,39 @@
       <c r="AZ54" s="312"/>
       <c r="BA54" s="312"/>
       <c r="BB54" s="312"/>
-      <c r="BC54" s="394" t="s">
-        <v>377</v>
+      <c r="BC54" s="397" t="s">
+        <v>371</v>
       </c>
       <c r="BD54" s="351" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="BE54" s="312"/>
       <c r="BF54" s="312"/>
       <c r="BG54" s="312"/>
       <c r="BH54" s="312"/>
       <c r="BI54" s="321" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BJ54" s="312"/>
       <c r="BK54" s="312"/>
       <c r="BL54" s="321" t="s">
-        <v>162</v>
-      </c>
-      <c r="BM54" s="394" t="s">
-        <v>351</v>
+        <v>160</v>
+      </c>
+      <c r="BM54" s="397" t="s">
+        <v>345</v>
       </c>
       <c r="BN54" s="345" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="BO54" s="312"/>
       <c r="BQ54" s="312"/>
       <c r="BR54" s="312"/>
       <c r="BS54" s="312"/>
-      <c r="BT54" s="321" t="s">
-        <v>92</v>
-      </c>
+      <c r="BT54" s="312"/>
       <c r="BU54" s="312"/>
       <c r="BV54" s="312"/>
-      <c r="BW54" s="400" t="s">
-        <v>323</v>
+      <c r="BW54" s="403" t="s">
+        <v>317</v>
       </c>
       <c r="BX54" s="349"/>
     </row>
@@ -12996,11 +12994,11 @@
       <c r="AP55" s="313"/>
       <c r="AQ55" s="313"/>
       <c r="AR55" s="313"/>
-      <c r="AS55" s="394"/>
+      <c r="AS55" s="397"/>
       <c r="AT55" s="351"/>
       <c r="AU55" s="313"/>
       <c r="AV55" s="361" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="AW55" s="313"/>
       <c r="AX55" s="313"/>
@@ -13008,53 +13006,53 @@
       <c r="AZ55" s="313"/>
       <c r="BA55" s="313"/>
       <c r="BB55" s="313"/>
-      <c r="BC55" s="394"/>
+      <c r="BC55" s="397"/>
       <c r="BD55" s="351"/>
       <c r="BE55" s="313"/>
       <c r="BF55" s="335" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="BG55" s="313"/>
       <c r="BH55" s="335" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="BI55" s="320" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="BJ55" s="320" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="BK55" s="335" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="BL55" s="320" t="s">
-        <v>165</v>
-      </c>
-      <c r="BM55" s="394"/>
+        <v>163</v>
+      </c>
+      <c r="BM55" s="397"/>
       <c r="BN55" s="345"/>
       <c r="BO55" s="335" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="BP55" s="335" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="BQ55" s="313"/>
       <c r="BR55" s="335" t="s">
-        <v>273</v>
+        <v>104</v>
       </c>
       <c r="BS55" s="362" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="BT55" s="323" t="s">
         <v>91</v>
       </c>
       <c r="BU55" s="362" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="BV55" s="362" t="s">
-        <v>285</v>
-      </c>
-      <c r="BW55" s="400"/>
+        <v>279</v>
+      </c>
+      <c r="BW55" s="403"/>
       <c r="BX55" s="348"/>
     </row>
     <row r="56" spans="1:86" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -13072,15 +13070,15 @@
       <c r="L56" s="79"/>
       <c r="M56" s="79"/>
       <c r="N56" s="154"/>
-      <c r="O56" s="516" t="s">
+      <c r="O56" s="519" t="s">
         <v>44</v>
       </c>
-      <c r="P56" s="516"/>
-      <c r="Q56" s="516"/>
-      <c r="R56" s="516"/>
-      <c r="S56" s="516"/>
-      <c r="T56" s="516"/>
-      <c r="U56" s="517"/>
+      <c r="P56" s="519"/>
+      <c r="Q56" s="519"/>
+      <c r="R56" s="519"/>
+      <c r="S56" s="519"/>
+      <c r="T56" s="519"/>
+      <c r="U56" s="520"/>
       <c r="V56" s="85"/>
       <c r="W56" s="111"/>
       <c r="X56" s="53"/>
@@ -13096,7 +13094,7 @@
       <c r="AH56" s="165"/>
       <c r="AI56" s="178"/>
       <c r="AJ56" s="352" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AK56" s="328"/>
       <c r="AL56" s="328"/>
@@ -13106,11 +13104,11 @@
       <c r="AP56" s="328"/>
       <c r="AQ56" s="328"/>
       <c r="AR56" s="328"/>
-      <c r="AS56" s="395" t="s">
-        <v>564</v>
+      <c r="AS56" s="398" t="s">
+        <v>558</v>
       </c>
       <c r="AT56" s="352" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AU56" s="328"/>
       <c r="AV56" s="328"/>
@@ -13120,31 +13118,31 @@
       <c r="AZ56" s="328"/>
       <c r="BA56" s="328"/>
       <c r="BB56" s="328"/>
-      <c r="BC56" s="395" t="s">
-        <v>378</v>
+      <c r="BC56" s="398" t="s">
+        <v>372</v>
       </c>
       <c r="BD56" s="352" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="BE56" s="321" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="BF56" s="321" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="BG56" s="328"/>
       <c r="BH56" s="328"/>
       <c r="BI56" s="328"/>
       <c r="BJ56" s="328"/>
       <c r="BK56" s="321" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="BL56" s="328"/>
-      <c r="BM56" s="395" t="s">
-        <v>352</v>
+      <c r="BM56" s="398" t="s">
+        <v>346</v>
       </c>
       <c r="BN56" s="346" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="BO56" s="328"/>
       <c r="BP56" s="328"/>
@@ -13153,13 +13151,13 @@
       <c r="BS56" s="328"/>
       <c r="BT56" s="328"/>
       <c r="BU56" s="321" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="BV56" s="321" t="s">
-        <v>412</v>
-      </c>
-      <c r="BW56" s="401" t="s">
-        <v>324</v>
+        <v>406</v>
+      </c>
+      <c r="BW56" s="404" t="s">
+        <v>318</v>
       </c>
       <c r="BX56" s="348"/>
     </row>
@@ -13176,13 +13174,13 @@
       <c r="L57" s="79"/>
       <c r="M57" s="79"/>
       <c r="N57" s="81"/>
-      <c r="O57" s="518"/>
-      <c r="P57" s="518"/>
-      <c r="Q57" s="518"/>
-      <c r="R57" s="518"/>
-      <c r="S57" s="518"/>
-      <c r="T57" s="518"/>
-      <c r="U57" s="519"/>
+      <c r="O57" s="521"/>
+      <c r="P57" s="521"/>
+      <c r="Q57" s="521"/>
+      <c r="R57" s="521"/>
+      <c r="S57" s="521"/>
+      <c r="T57" s="521"/>
+      <c r="U57" s="522"/>
       <c r="V57" s="85"/>
       <c r="W57" s="53"/>
       <c r="X57" s="53"/>
@@ -13206,11 +13204,11 @@
       <c r="AP57" s="327"/>
       <c r="AQ57" s="327"/>
       <c r="AR57" s="327"/>
-      <c r="AS57" s="395"/>
+      <c r="AS57" s="398"/>
       <c r="AT57" s="352"/>
       <c r="AU57" s="327"/>
       <c r="AV57" s="361" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="AW57" s="327"/>
       <c r="AX57" s="327"/>
@@ -13218,65 +13216,65 @@
       <c r="AZ57" s="327"/>
       <c r="BA57" s="327"/>
       <c r="BB57" s="327"/>
-      <c r="BC57" s="395"/>
+      <c r="BC57" s="398"/>
       <c r="BD57" s="352"/>
       <c r="BE57" s="320" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="BF57" s="320" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="BG57" s="327"/>
       <c r="BH57" s="335" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="BI57" s="320" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="BJ57" s="320" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="BK57" s="320" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="BL57" s="320" t="s">
-        <v>262</v>
-      </c>
-      <c r="BM57" s="395"/>
+        <v>258</v>
+      </c>
+      <c r="BM57" s="398"/>
       <c r="BN57" s="346"/>
-      <c r="BO57" s="368" t="s">
-        <v>666</v>
-      </c>
-      <c r="BP57" s="368" t="s">
-        <v>667</v>
+      <c r="BO57" s="367" t="s">
+        <v>660</v>
+      </c>
+      <c r="BP57" s="367" t="s">
+        <v>661</v>
       </c>
       <c r="BQ57" s="327"/>
       <c r="BR57" s="335" t="s">
-        <v>271</v>
-      </c>
-      <c r="BS57" s="369" t="s">
-        <v>673</v>
+        <v>268</v>
+      </c>
+      <c r="BS57" s="368" t="s">
+        <v>667</v>
       </c>
       <c r="BT57" s="320" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="BU57" s="320" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="BV57" s="362" t="s">
-        <v>284</v>
-      </c>
-      <c r="BW57" s="401"/>
+        <v>278</v>
+      </c>
+      <c r="BW57" s="404"/>
       <c r="BX57" s="348"/>
     </row>
     <row r="58" spans="1:86" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="152"/>
       <c r="B58" s="152"/>
-      <c r="E58" s="433" t="s">
+      <c r="E58" s="436" t="s">
         <v>45</v>
       </c>
-      <c r="F58" s="435"/>
-      <c r="G58" s="434"/>
+      <c r="F58" s="438"/>
+      <c r="G58" s="437"/>
       <c r="H58" s="79"/>
       <c r="I58" s="79"/>
       <c r="J58" s="78"/>
@@ -13284,13 +13282,13 @@
       <c r="L58" s="79"/>
       <c r="M58" s="79"/>
       <c r="N58" s="81"/>
-      <c r="O58" s="518"/>
-      <c r="P58" s="518"/>
-      <c r="Q58" s="518"/>
-      <c r="R58" s="518"/>
-      <c r="S58" s="518"/>
-      <c r="T58" s="518"/>
-      <c r="U58" s="519"/>
+      <c r="O58" s="521"/>
+      <c r="P58" s="521"/>
+      <c r="Q58" s="521"/>
+      <c r="R58" s="521"/>
+      <c r="S58" s="521"/>
+      <c r="T58" s="521"/>
+      <c r="U58" s="522"/>
       <c r="V58" s="85"/>
       <c r="W58" s="53"/>
       <c r="X58" s="53"/>
@@ -13304,32 +13302,32 @@
       <c r="AI58" s="102"/>
       <c r="AJ58" s="44"/>
       <c r="AK58" s="21" t="s">
+        <v>541</v>
+      </c>
+      <c r="AL58" s="21" t="s">
+        <v>542</v>
+      </c>
+      <c r="AM58" s="21" t="s">
+        <v>543</v>
+      </c>
+      <c r="AN58" s="21" t="s">
+        <v>544</v>
+      </c>
+      <c r="AO58" s="21" t="s">
+        <v>545</v>
+      </c>
+      <c r="AP58" s="21" t="s">
+        <v>548</v>
+      </c>
+      <c r="AQ58" s="21" t="s">
+        <v>546</v>
+      </c>
+      <c r="AR58" s="21" t="s">
         <v>547</v>
-      </c>
-      <c r="AL58" s="21" t="s">
-        <v>548</v>
-      </c>
-      <c r="AM58" s="21" t="s">
-        <v>549</v>
-      </c>
-      <c r="AN58" s="21" t="s">
-        <v>550</v>
-      </c>
-      <c r="AO58" s="21" t="s">
-        <v>551</v>
-      </c>
-      <c r="AP58" s="21" t="s">
-        <v>554</v>
-      </c>
-      <c r="AQ58" s="21" t="s">
-        <v>552</v>
-      </c>
-      <c r="AR58" s="21" t="s">
-        <v>553</v>
       </c>
       <c r="AS58" s="62"/>
       <c r="AT58" s="351" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AU58" s="312"/>
       <c r="AV58" s="312"/>
@@ -13339,29 +13337,29 @@
       <c r="AZ58" s="312"/>
       <c r="BA58" s="312"/>
       <c r="BB58" s="312"/>
-      <c r="BC58" s="394" t="s">
-        <v>655</v>
+      <c r="BC58" s="397" t="s">
+        <v>649</v>
       </c>
       <c r="BD58" s="351" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="BE58" s="312"/>
       <c r="BF58" s="312"/>
       <c r="BG58" s="312"/>
       <c r="BH58" s="321" t="s">
-        <v>167</v>
+        <v>671</v>
       </c>
       <c r="BI58" s="312"/>
       <c r="BJ58" s="312"/>
       <c r="BK58" s="321" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="BL58" s="312"/>
-      <c r="BM58" s="394" t="s">
-        <v>353</v>
+      <c r="BM58" s="397" t="s">
+        <v>347</v>
       </c>
       <c r="BN58" s="345" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="BO58" s="312"/>
       <c r="BP58" s="312"/>
@@ -13370,20 +13368,20 @@
       <c r="BS58" s="312"/>
       <c r="BT58" s="312"/>
       <c r="BU58" s="321" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BV58" s="312"/>
-      <c r="BW58" s="400" t="s">
-        <v>325</v>
+      <c r="BW58" s="403" t="s">
+        <v>319</v>
       </c>
       <c r="BX58" s="348"/>
     </row>
     <row r="59" spans="1:86" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="152"/>
       <c r="B59" s="152"/>
-      <c r="E59" s="433"/>
-      <c r="F59" s="435"/>
-      <c r="G59" s="434"/>
+      <c r="E59" s="436"/>
+      <c r="F59" s="438"/>
+      <c r="G59" s="437"/>
       <c r="H59" s="79"/>
       <c r="I59" s="79"/>
       <c r="J59" s="78"/>
@@ -13391,13 +13389,13 @@
       <c r="L59" s="79"/>
       <c r="M59" s="79"/>
       <c r="N59" s="81"/>
-      <c r="O59" s="518"/>
-      <c r="P59" s="518"/>
-      <c r="Q59" s="518"/>
-      <c r="R59" s="518"/>
-      <c r="S59" s="518"/>
-      <c r="T59" s="518"/>
-      <c r="U59" s="519"/>
+      <c r="O59" s="521"/>
+      <c r="P59" s="521"/>
+      <c r="Q59" s="521"/>
+      <c r="R59" s="521"/>
+      <c r="S59" s="521"/>
+      <c r="T59" s="521"/>
+      <c r="U59" s="522"/>
       <c r="V59" s="189"/>
       <c r="W59" s="53"/>
       <c r="X59" s="53"/>
@@ -13411,108 +13409,102 @@
       <c r="AG59" s="102"/>
       <c r="AH59" s="111"/>
       <c r="AI59" s="114"/>
-      <c r="AJ59" s="388" t="s">
-        <v>295</v>
+      <c r="AJ59" s="387" t="s">
+        <v>289</v>
       </c>
       <c r="AK59" s="322" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="AL59" s="322" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="AM59" s="322" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="AN59" s="322" t="s">
-        <v>298</v>
-      </c>
-      <c r="AO59" s="389" t="s">
-        <v>294</v>
-      </c>
-      <c r="AP59" s="381" t="s">
-        <v>409</v>
-      </c>
-      <c r="AQ59" s="382" t="s">
-        <v>410</v>
-      </c>
-      <c r="AR59" s="383" t="s">
-        <v>411</v>
-      </c>
-      <c r="AS59" s="366" t="s">
-        <v>611</v>
+        <v>292</v>
+      </c>
+      <c r="AO59" s="388" t="s">
+        <v>288</v>
+      </c>
+      <c r="AP59" s="380" t="s">
+        <v>403</v>
+      </c>
+      <c r="AQ59" s="381" t="s">
+        <v>404</v>
+      </c>
+      <c r="AR59" s="382" t="s">
+        <v>405</v>
+      </c>
+      <c r="AS59" s="365" t="s">
+        <v>605</v>
       </c>
       <c r="AT59" s="351"/>
       <c r="AU59" s="313"/>
       <c r="AV59" s="313"/>
       <c r="AW59" s="335" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="AX59" s="333" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="AY59" s="313"/>
       <c r="AZ59" s="313"/>
       <c r="BA59" s="313"/>
       <c r="BB59" s="313"/>
-      <c r="BC59" s="394"/>
-      <c r="BD59" s="365"/>
+      <c r="BC59" s="397"/>
+      <c r="BD59" s="364"/>
       <c r="BE59" s="320" t="s">
-        <v>256</v>
-      </c>
-      <c r="BF59" s="392" t="s">
-        <v>263</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="BF59" s="313"/>
       <c r="BG59" s="313"/>
       <c r="BH59" s="320" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="BI59" s="335" t="s">
-        <v>661</v>
-      </c>
-      <c r="BJ59" s="320" t="s">
-        <v>170</v>
-      </c>
+        <v>655</v>
+      </c>
+      <c r="BJ59" s="313"/>
       <c r="BK59" s="320" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="BL59" s="320" t="s">
-        <v>264</v>
-      </c>
-      <c r="BM59" s="394"/>
+        <v>259</v>
+      </c>
+      <c r="BM59" s="397"/>
       <c r="BN59" s="345"/>
-      <c r="BO59" s="335" t="s">
-        <v>265</v>
-      </c>
-      <c r="BP59" s="335" t="s">
+      <c r="BO59" s="368" t="s">
+        <v>673</v>
+      </c>
+      <c r="BP59" s="367" t="s">
+        <v>674</v>
+      </c>
+      <c r="BQ59" s="313"/>
+      <c r="BR59" s="335" t="s">
         <v>266</v>
       </c>
-      <c r="BQ59" s="335" t="s">
-        <v>267</v>
-      </c>
-      <c r="BR59" s="335" t="s">
-        <v>270</v>
-      </c>
       <c r="BS59" s="335" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="BT59" s="320" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="BU59" s="362" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="BV59" s="320" t="s">
-        <v>283</v>
-      </c>
-      <c r="BW59" s="400"/>
+        <v>277</v>
+      </c>
+      <c r="BW59" s="403"/>
       <c r="BX59" s="348"/>
     </row>
     <row r="60" spans="1:86" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="152"/>
       <c r="B60" s="152"/>
-      <c r="E60" s="433"/>
-      <c r="F60" s="435"/>
-      <c r="G60" s="434"/>
+      <c r="E60" s="436"/>
+      <c r="F60" s="438"/>
+      <c r="G60" s="437"/>
       <c r="H60" s="79"/>
       <c r="I60" s="79"/>
       <c r="J60" s="78"/>
@@ -13520,13 +13512,13 @@
       <c r="L60" s="79"/>
       <c r="M60" s="79"/>
       <c r="N60" s="81"/>
-      <c r="O60" s="518"/>
-      <c r="P60" s="518"/>
-      <c r="Q60" s="518"/>
-      <c r="R60" s="518"/>
-      <c r="S60" s="518"/>
-      <c r="T60" s="518"/>
-      <c r="U60" s="519"/>
+      <c r="O60" s="521"/>
+      <c r="P60" s="521"/>
+      <c r="Q60" s="521"/>
+      <c r="R60" s="521"/>
+      <c r="S60" s="521"/>
+      <c r="T60" s="521"/>
+      <c r="U60" s="522"/>
       <c r="V60" s="85"/>
       <c r="W60" s="53"/>
       <c r="X60" s="53"/>
@@ -13541,7 +13533,7 @@
       <c r="AG60" s="114"/>
       <c r="AH60" s="114"/>
       <c r="AI60" s="114"/>
-      <c r="AJ60" s="390">
+      <c r="AJ60" s="389">
         <f>COUNTA(BE63:BN63)</f>
         <v>3</v>
       </c>
@@ -13555,58 +13547,58 @@
       </c>
       <c r="AM60" s="319">
         <f>COUNTA(BE38:BL61,BE11:BL36)</f>
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="AN60" s="319">
         <f>COUNTA(BO38:BV65,BO11:BV36)</f>
-        <v>179</v>
-      </c>
-      <c r="AO60" s="367">
+        <v>181</v>
+      </c>
+      <c r="AO60" s="366">
         <f>SUM(AJ60:AN60)+AS60</f>
-        <v>550</v>
-      </c>
-      <c r="AP60" s="380">
+        <v>553</v>
+      </c>
+      <c r="AP60" s="379">
         <f>COUNTIF( $BE$11:$BL$61,"*401*") + COUNTIF($AK$11:$BB$59,"*401*")+ COUNTIF($BE$63:$BM$63,"*401*") +COUNTIF($BO$11:$BV$65,"*401*") -1</f>
-        <v>170</v>
-      </c>
-      <c r="AQ60" s="379">
+        <v>166</v>
+      </c>
+      <c r="AQ60" s="378">
         <f>COUNTIF( $BE$11:$BL$61,"*402*") + COUNTIF($AK$11:$BB$59,"*402*")+ COUNTIF($BE$63:$BM$63,"*402*") +COUNTIF($BO$11:$BV$65,"*402*") -1</f>
-        <v>84</v>
-      </c>
-      <c r="AR60" s="378">
+        <v>86</v>
+      </c>
+      <c r="AR60" s="377">
         <f>COUNTIF( $BE$11:$BL$61,"*403*") + COUNTIF($AK$11:$BB$59,"*403*")+ COUNTIF($BE$63:$BM$63,"*403*") +COUNTIF($BO$11:$BV$65,"*403*") -1</f>
-        <v>214</v>
-      </c>
-      <c r="AS60" s="367">
-        <f>14*6-2</f>
-        <v>82</v>
+        <v>215</v>
+      </c>
+      <c r="AS60" s="366">
+        <f>14*7-12</f>
+        <v>86</v>
       </c>
       <c r="AU60" s="21" t="s">
+        <v>389</v>
+      </c>
+      <c r="AV60" s="21" t="s">
+        <v>390</v>
+      </c>
+      <c r="AW60" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="AX60" s="21" t="s">
+        <v>392</v>
+      </c>
+      <c r="AY60" s="21" t="s">
+        <v>393</v>
+      </c>
+      <c r="AZ60" s="21" t="s">
+        <v>394</v>
+      </c>
+      <c r="BA60" s="21" t="s">
         <v>395</v>
       </c>
-      <c r="AV60" s="21" t="s">
+      <c r="BB60" s="21" t="s">
         <v>396</v>
       </c>
-      <c r="AW60" s="21" t="s">
-        <v>397</v>
-      </c>
-      <c r="AX60" s="21" t="s">
-        <v>398</v>
-      </c>
-      <c r="AY60" s="21" t="s">
-        <v>399</v>
-      </c>
-      <c r="AZ60" s="21" t="s">
-        <v>400</v>
-      </c>
-      <c r="BA60" s="21" t="s">
-        <v>401</v>
-      </c>
-      <c r="BB60" s="21" t="s">
-        <v>402</v>
-      </c>
       <c r="BD60" s="358" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="BE60" s="328"/>
       <c r="BF60" s="328"/>
@@ -13616,11 +13608,11 @@
       <c r="BJ60" s="328"/>
       <c r="BK60" s="328"/>
       <c r="BL60" s="328"/>
-      <c r="BM60" s="395" t="s">
-        <v>354</v>
+      <c r="BM60" s="398" t="s">
+        <v>348</v>
       </c>
       <c r="BN60" s="346" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="BO60" s="328"/>
       <c r="BP60" s="328"/>
@@ -13630,17 +13622,17 @@
       <c r="BT60" s="328"/>
       <c r="BU60" s="328"/>
       <c r="BV60" s="328"/>
-      <c r="BW60" s="401" t="s">
-        <v>326</v>
+      <c r="BW60" s="404" t="s">
+        <v>320</v>
       </c>
       <c r="BX60" s="348"/>
     </row>
     <row r="61" spans="1:86" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="191"/>
       <c r="B61" s="191"/>
-      <c r="E61" s="433"/>
-      <c r="F61" s="435"/>
-      <c r="G61" s="434"/>
+      <c r="E61" s="436"/>
+      <c r="F61" s="438"/>
+      <c r="G61" s="437"/>
       <c r="H61" s="79"/>
       <c r="I61" s="79"/>
       <c r="J61" s="78"/>
@@ -13648,13 +13640,13 @@
       <c r="L61" s="79"/>
       <c r="M61" s="79"/>
       <c r="N61" s="81"/>
-      <c r="O61" s="518"/>
-      <c r="P61" s="518"/>
-      <c r="Q61" s="518"/>
-      <c r="R61" s="518"/>
-      <c r="S61" s="518"/>
-      <c r="T61" s="518"/>
-      <c r="U61" s="519"/>
+      <c r="O61" s="521"/>
+      <c r="P61" s="521"/>
+      <c r="Q61" s="521"/>
+      <c r="R61" s="521"/>
+      <c r="S61" s="521"/>
+      <c r="T61" s="521"/>
+      <c r="U61" s="522"/>
       <c r="V61" s="85"/>
       <c r="W61" s="53"/>
       <c r="X61" s="53"/>
@@ -13678,45 +13670,47 @@
       <c r="BH61" s="327"/>
       <c r="BI61" s="327"/>
       <c r="BJ61" s="320" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="BK61" s="327"/>
       <c r="BL61" s="320" t="s">
-        <v>269</v>
-      </c>
-      <c r="BM61" s="395"/>
+        <v>264</v>
+      </c>
+      <c r="BM61" s="398"/>
       <c r="BN61" s="346"/>
       <c r="BO61" s="335" t="s">
-        <v>487</v>
+        <v>260</v>
       </c>
       <c r="BP61" s="335" t="s">
-        <v>488</v>
+        <v>261</v>
       </c>
       <c r="BQ61" s="335" t="s">
-        <v>272</v>
-      </c>
-      <c r="BR61" s="327"/>
+        <v>262</v>
+      </c>
+      <c r="BR61" s="335" t="s">
+        <v>265</v>
+      </c>
       <c r="BS61" s="320" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="BT61" s="335" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="BU61" s="320" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="BV61" s="320" t="s">
-        <v>104</v>
-      </c>
-      <c r="BW61" s="401"/>
+        <v>103</v>
+      </c>
+      <c r="BW61" s="404"/>
       <c r="BX61" s="348"/>
     </row>
     <row r="62" spans="1:86" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="191"/>
       <c r="B62" s="191"/>
-      <c r="E62" s="433"/>
-      <c r="F62" s="435"/>
-      <c r="G62" s="434"/>
+      <c r="E62" s="436"/>
+      <c r="F62" s="438"/>
+      <c r="G62" s="437"/>
       <c r="H62" s="79"/>
       <c r="I62" s="79"/>
       <c r="J62" s="78"/>
@@ -13724,13 +13718,13 @@
       <c r="L62" s="79"/>
       <c r="M62" s="79"/>
       <c r="N62" s="81"/>
-      <c r="O62" s="518"/>
-      <c r="P62" s="518"/>
-      <c r="Q62" s="518"/>
-      <c r="R62" s="518"/>
-      <c r="S62" s="518"/>
-      <c r="T62" s="518"/>
-      <c r="U62" s="519"/>
+      <c r="O62" s="521"/>
+      <c r="P62" s="521"/>
+      <c r="Q62" s="521"/>
+      <c r="R62" s="521"/>
+      <c r="S62" s="521"/>
+      <c r="T62" s="521"/>
+      <c r="U62" s="522"/>
       <c r="V62" s="85"/>
       <c r="W62" s="53"/>
       <c r="X62" s="53"/>
@@ -13756,28 +13750,28 @@
       <c r="BC62" s="357"/>
       <c r="BD62" s="315"/>
       <c r="BE62" s="21" t="s">
+        <v>381</v>
+      </c>
+      <c r="BF62" s="21" t="s">
+        <v>382</v>
+      </c>
+      <c r="BG62" s="21" t="s">
+        <v>383</v>
+      </c>
+      <c r="BH62" s="21" t="s">
+        <v>384</v>
+      </c>
+      <c r="BI62" s="21" t="s">
+        <v>385</v>
+      </c>
+      <c r="BJ62" s="21" t="s">
+        <v>386</v>
+      </c>
+      <c r="BK62" s="21" t="s">
         <v>387</v>
       </c>
-      <c r="BF62" s="21" t="s">
+      <c r="BL62" s="21" t="s">
         <v>388</v>
-      </c>
-      <c r="BG62" s="21" t="s">
-        <v>389</v>
-      </c>
-      <c r="BH62" s="21" t="s">
-        <v>390</v>
-      </c>
-      <c r="BI62" s="21" t="s">
-        <v>391</v>
-      </c>
-      <c r="BJ62" s="21" t="s">
-        <v>392</v>
-      </c>
-      <c r="BK62" s="21" t="s">
-        <v>393</v>
-      </c>
-      <c r="BL62" s="21" t="s">
-        <v>394</v>
       </c>
       <c r="BM62" s="342"/>
       <c r="BN62" s="345" t="s">
@@ -13791,8 +13785,8 @@
       <c r="BT62" s="312"/>
       <c r="BU62" s="312"/>
       <c r="BV62" s="312"/>
-      <c r="BW62" s="400" t="s">
-        <v>327</v>
+      <c r="BW62" s="403" t="s">
+        <v>321</v>
       </c>
       <c r="BX62" s="349"/>
       <c r="BY62" s="143"/>
@@ -13809,9 +13803,9 @@
     <row r="63" spans="1:86" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="191"/>
       <c r="B63" s="191"/>
-      <c r="E63" s="433"/>
-      <c r="F63" s="435"/>
-      <c r="G63" s="434"/>
+      <c r="E63" s="436"/>
+      <c r="F63" s="438"/>
+      <c r="G63" s="437"/>
       <c r="H63" s="79"/>
       <c r="I63" s="79"/>
       <c r="J63" s="78"/>
@@ -13819,13 +13813,13 @@
       <c r="L63" s="79"/>
       <c r="M63" s="79"/>
       <c r="N63" s="81"/>
-      <c r="O63" s="518"/>
-      <c r="P63" s="518"/>
-      <c r="Q63" s="518"/>
-      <c r="R63" s="518"/>
-      <c r="S63" s="518"/>
-      <c r="T63" s="518"/>
-      <c r="U63" s="519"/>
+      <c r="O63" s="521"/>
+      <c r="P63" s="521"/>
+      <c r="Q63" s="521"/>
+      <c r="R63" s="521"/>
+      <c r="S63" s="521"/>
+      <c r="T63" s="521"/>
+      <c r="U63" s="522"/>
       <c r="V63" s="85"/>
       <c r="W63" s="53"/>
       <c r="X63" s="53"/>
@@ -13845,16 +13839,16 @@
       <c r="BB63" s="6"/>
       <c r="BC63" s="314"/>
       <c r="BD63" s="316" t="s">
-        <v>299</v>
-      </c>
-      <c r="BE63" s="386" t="s">
-        <v>654</v>
-      </c>
-      <c r="BF63" s="377" t="s">
-        <v>278</v>
-      </c>
-      <c r="BG63" s="363" t="s">
-        <v>277</v>
+        <v>293</v>
+      </c>
+      <c r="BE63" s="385" t="s">
+        <v>648</v>
+      </c>
+      <c r="BF63" s="376" t="s">
+        <v>272</v>
+      </c>
+      <c r="BG63" s="394" t="s">
+        <v>670</v>
       </c>
       <c r="BH63" s="317"/>
       <c r="BI63" s="317"/>
@@ -13864,28 +13858,28 @@
       <c r="BM63" s="6"/>
       <c r="BN63" s="345"/>
       <c r="BO63" s="335" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="BP63" s="335" t="s">
-        <v>274</v>
+        <v>482</v>
       </c>
       <c r="BQ63" s="335" t="s">
-        <v>492</v>
+        <v>267</v>
       </c>
       <c r="BR63" s="313"/>
       <c r="BS63" s="313"/>
       <c r="BT63" s="313"/>
       <c r="BU63" s="313"/>
       <c r="BV63" s="313"/>
-      <c r="BW63" s="400"/>
+      <c r="BW63" s="403"/>
       <c r="BX63" s="348"/>
     </row>
     <row r="64" spans="1:86" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="191"/>
       <c r="B64" s="191"/>
-      <c r="E64" s="433"/>
-      <c r="F64" s="435"/>
-      <c r="G64" s="434"/>
+      <c r="E64" s="436"/>
+      <c r="F64" s="438"/>
+      <c r="G64" s="437"/>
       <c r="H64" s="79"/>
       <c r="I64" s="79"/>
       <c r="J64" s="78"/>
@@ -13893,13 +13887,13 @@
       <c r="L64" s="79"/>
       <c r="M64" s="79"/>
       <c r="N64" s="81"/>
-      <c r="O64" s="518"/>
-      <c r="P64" s="518"/>
-      <c r="Q64" s="518"/>
-      <c r="R64" s="518"/>
-      <c r="S64" s="518"/>
-      <c r="T64" s="518"/>
-      <c r="U64" s="519"/>
+      <c r="O64" s="521"/>
+      <c r="P64" s="521"/>
+      <c r="Q64" s="521"/>
+      <c r="R64" s="521"/>
+      <c r="S64" s="521"/>
+      <c r="T64" s="521"/>
+      <c r="U64" s="522"/>
       <c r="V64" s="85"/>
       <c r="W64" s="53"/>
       <c r="X64" s="53"/>
@@ -13927,17 +13921,17 @@
       <c r="BT64" s="328"/>
       <c r="BU64" s="328"/>
       <c r="BV64" s="328"/>
-      <c r="BW64" s="512" t="s">
-        <v>328</v>
+      <c r="BW64" s="515" t="s">
+        <v>322</v>
       </c>
       <c r="BX64" s="348"/>
     </row>
     <row r="65" spans="1:85" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="191"/>
       <c r="B65" s="191"/>
-      <c r="E65" s="436"/>
-      <c r="F65" s="439"/>
-      <c r="G65" s="437"/>
+      <c r="E65" s="439"/>
+      <c r="F65" s="442"/>
+      <c r="G65" s="440"/>
       <c r="H65" s="79"/>
       <c r="I65" s="79"/>
       <c r="J65" s="78"/>
@@ -13945,13 +13939,13 @@
       <c r="L65" s="79"/>
       <c r="M65" s="79"/>
       <c r="N65" s="81"/>
-      <c r="O65" s="520"/>
-      <c r="P65" s="520"/>
-      <c r="Q65" s="520"/>
-      <c r="R65" s="520"/>
-      <c r="S65" s="520"/>
-      <c r="T65" s="520"/>
-      <c r="U65" s="521"/>
+      <c r="O65" s="523"/>
+      <c r="P65" s="523"/>
+      <c r="Q65" s="523"/>
+      <c r="R65" s="523"/>
+      <c r="S65" s="523"/>
+      <c r="T65" s="523"/>
+      <c r="U65" s="524"/>
       <c r="V65" s="85"/>
       <c r="W65" s="53"/>
       <c r="X65" s="53"/>
@@ -13969,15 +13963,21 @@
       <c r="BB65" s="6"/>
       <c r="BC65" s="314"/>
       <c r="BN65" s="346"/>
-      <c r="BO65" s="327"/>
-      <c r="BP65" s="327"/>
-      <c r="BQ65" s="327"/>
+      <c r="BO65" s="335" t="s">
+        <v>485</v>
+      </c>
+      <c r="BP65" s="335" t="s">
+        <v>269</v>
+      </c>
+      <c r="BQ65" s="335" t="s">
+        <v>486</v>
+      </c>
       <c r="BR65" s="327"/>
       <c r="BS65" s="327"/>
       <c r="BT65" s="327"/>
       <c r="BU65" s="327"/>
       <c r="BV65" s="327"/>
-      <c r="BW65" s="512"/>
+      <c r="BW65" s="515"/>
       <c r="BX65" s="348"/>
     </row>
     <row r="66" spans="1:85" ht="279.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -13995,15 +13995,15 @@
       <c r="L66" s="79"/>
       <c r="M66" s="79"/>
       <c r="N66" s="81"/>
-      <c r="O66" s="578" t="s">
+      <c r="O66" s="581" t="s">
         <v>47</v>
       </c>
-      <c r="P66" s="516"/>
-      <c r="Q66" s="516"/>
-      <c r="R66" s="516"/>
-      <c r="S66" s="516"/>
-      <c r="T66" s="516"/>
-      <c r="U66" s="517"/>
+      <c r="P66" s="519"/>
+      <c r="Q66" s="519"/>
+      <c r="R66" s="519"/>
+      <c r="S66" s="519"/>
+      <c r="T66" s="519"/>
+      <c r="U66" s="520"/>
       <c r="V66" s="85"/>
       <c r="W66" s="53"/>
       <c r="X66" s="53"/>
@@ -14027,39 +14027,39 @@
       <c r="AQ66" s="86"/>
       <c r="AR66" s="209"/>
       <c r="AS66" s="209"/>
-      <c r="AT66" s="455" t="s">
+      <c r="AT66" s="458" t="s">
         <v>11</v>
       </c>
-      <c r="AU66" s="522"/>
-      <c r="AV66" s="522"/>
-      <c r="AW66" s="456"/>
+      <c r="AU66" s="525"/>
+      <c r="AV66" s="525"/>
+      <c r="AW66" s="459"/>
       <c r="AX66" s="210"/>
       <c r="AY66" s="210"/>
       <c r="AZ66" s="210"/>
       <c r="BA66" s="210"/>
       <c r="BO66" s="21" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="BP66" s="21" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="BQ66" s="21" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="BR66" s="21" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="BS66" s="21" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="BT66" s="21" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="BU66" s="21" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="BV66" s="21" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
     </row>
     <row r="67" spans="1:85" ht="137.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -14075,23 +14075,23 @@
       <c r="L67" s="79"/>
       <c r="M67" s="79"/>
       <c r="N67" s="81"/>
-      <c r="O67" s="579"/>
-      <c r="P67" s="518"/>
-      <c r="Q67" s="518"/>
-      <c r="R67" s="518"/>
-      <c r="S67" s="518"/>
-      <c r="T67" s="518"/>
-      <c r="U67" s="519"/>
+      <c r="O67" s="582"/>
+      <c r="P67" s="521"/>
+      <c r="Q67" s="521"/>
+      <c r="R67" s="521"/>
+      <c r="S67" s="521"/>
+      <c r="T67" s="521"/>
+      <c r="U67" s="522"/>
       <c r="V67" s="85"/>
       <c r="W67" s="53"/>
       <c r="X67" s="53"/>
       <c r="Y67" s="53"/>
       <c r="Z67" s="83"/>
-      <c r="AA67" s="581" t="s">
+      <c r="AA67" s="584" t="s">
         <v>48</v>
       </c>
-      <c r="AB67" s="582"/>
-      <c r="AC67" s="583"/>
+      <c r="AB67" s="585"/>
+      <c r="AC67" s="586"/>
       <c r="AD67" s="95"/>
       <c r="AE67" s="95"/>
       <c r="AF67" s="95"/>
@@ -14182,10 +14182,10 @@
         <v>22</v>
       </c>
       <c r="BW67" s="309" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="CG67" s="6" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
     </row>
     <row r="68" spans="1:85" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -14201,21 +14201,21 @@
       <c r="L68" s="79"/>
       <c r="M68" s="79"/>
       <c r="N68" s="81"/>
-      <c r="O68" s="579"/>
-      <c r="P68" s="518"/>
-      <c r="Q68" s="518"/>
-      <c r="R68" s="518"/>
-      <c r="S68" s="518"/>
-      <c r="T68" s="518"/>
-      <c r="U68" s="519"/>
+      <c r="O68" s="582"/>
+      <c r="P68" s="521"/>
+      <c r="Q68" s="521"/>
+      <c r="R68" s="521"/>
+      <c r="S68" s="521"/>
+      <c r="T68" s="521"/>
+      <c r="U68" s="522"/>
       <c r="V68" s="85"/>
       <c r="W68" s="53"/>
       <c r="X68" s="53"/>
       <c r="Y68" s="53"/>
       <c r="Z68" s="83"/>
-      <c r="AA68" s="584"/>
-      <c r="AB68" s="585"/>
-      <c r="AC68" s="586"/>
+      <c r="AA68" s="587"/>
+      <c r="AB68" s="588"/>
+      <c r="AC68" s="589"/>
       <c r="AD68" s="95"/>
       <c r="AE68" s="95"/>
       <c r="AF68" s="95"/>
@@ -14262,11 +14262,11 @@
       </c>
       <c r="BF68" s="355">
         <f>COUNTIF($AK$11:$BL$63,"*401-6-*") + COUNTIF($BO$11:$BV$65,"*401-6-*")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BG68" s="355">
         <f>COUNTIF($AK$11:$BL$63,"*401-7-*") + COUNTIF($BO$11:$BV$65,"*401-7-*")</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BH68" s="355">
         <f>COUNTIF($AK$11:$BL$63,"*401-8-*") + COUNTIF($BO$11:$BV$65,"*401-8-*")</f>
@@ -14330,7 +14330,7 @@
       </c>
       <c r="BW68" s="310">
         <f>SUM(BA68:BV68)/(14*18)</f>
-        <v>0.67460317460317465</v>
+        <v>0.65873015873015872</v>
       </c>
     </row>
     <row r="69" spans="1:85" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -14346,21 +14346,21 @@
       <c r="L69" s="79"/>
       <c r="M69" s="79"/>
       <c r="N69" s="81"/>
-      <c r="O69" s="579"/>
-      <c r="P69" s="518"/>
-      <c r="Q69" s="518"/>
-      <c r="R69" s="518"/>
-      <c r="S69" s="518"/>
-      <c r="T69" s="518"/>
-      <c r="U69" s="519"/>
+      <c r="O69" s="582"/>
+      <c r="P69" s="521"/>
+      <c r="Q69" s="521"/>
+      <c r="R69" s="521"/>
+      <c r="S69" s="521"/>
+      <c r="T69" s="521"/>
+      <c r="U69" s="522"/>
       <c r="V69" s="85"/>
       <c r="W69" s="53"/>
       <c r="X69" s="53"/>
       <c r="Y69" s="53"/>
       <c r="Z69" s="83"/>
-      <c r="AA69" s="584"/>
-      <c r="AB69" s="585"/>
-      <c r="AC69" s="586"/>
+      <c r="AA69" s="587"/>
+      <c r="AB69" s="588"/>
+      <c r="AC69" s="589"/>
       <c r="AD69" s="95"/>
       <c r="AE69" s="95"/>
       <c r="AF69" s="95"/>
@@ -14375,12 +14375,12 @@
       <c r="AQ69" s="198"/>
       <c r="AR69" s="213"/>
       <c r="AS69" s="271"/>
-      <c r="AT69" s="560" t="s">
+      <c r="AT69" s="563" t="s">
         <v>12</v>
       </c>
-      <c r="AU69" s="561"/>
-      <c r="AV69" s="561"/>
-      <c r="AW69" s="562"/>
+      <c r="AU69" s="564"/>
+      <c r="AV69" s="564"/>
+      <c r="AW69" s="565"/>
       <c r="AX69" s="210"/>
       <c r="AY69" s="210"/>
       <c r="AZ69" s="306">
@@ -14388,7 +14388,7 @@
       </c>
       <c r="BA69" s="337">
         <f>COUNTIF($AK$11:$BL$63,"*402-1-*") + COUNTIF($BO$11:$BV$65,"*402-1-*")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB69" s="337">
         <f>COUNTIF($AK$11:$BL$63,"*402-2-*") + COUNTIF($BO$11:$BV$65,"*402-2-*")</f>
@@ -14432,7 +14432,7 @@
       </c>
       <c r="BL69" s="337">
         <f>COUNTIF($AK$11:$BL$63,"*402-12-*") + COUNTIF($BO$11:$BV$65,"*402-12-*")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM69" s="337">
         <f>COUNTIF($AK$11:$BL$63,"*402-13-*") + COUNTIF($BO$11:$BV$65,"*402-13-*")</f>
@@ -14476,7 +14476,7 @@
       </c>
       <c r="BW69" s="310">
         <f>SUM(BA69:BV69)/(14*22)</f>
-        <v>0.27272727272727271</v>
+        <v>0.2792207792207792</v>
       </c>
     </row>
     <row r="70" spans="1:85" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -14492,21 +14492,21 @@
       <c r="L70" s="79"/>
       <c r="M70" s="79"/>
       <c r="N70" s="81"/>
-      <c r="O70" s="579"/>
-      <c r="P70" s="518"/>
-      <c r="Q70" s="518"/>
-      <c r="R70" s="518"/>
-      <c r="S70" s="518"/>
-      <c r="T70" s="518"/>
-      <c r="U70" s="519"/>
+      <c r="O70" s="582"/>
+      <c r="P70" s="521"/>
+      <c r="Q70" s="521"/>
+      <c r="R70" s="521"/>
+      <c r="S70" s="521"/>
+      <c r="T70" s="521"/>
+      <c r="U70" s="522"/>
       <c r="V70" s="189"/>
       <c r="W70" s="53"/>
       <c r="X70" s="53"/>
       <c r="Y70" s="53"/>
       <c r="Z70" s="83"/>
-      <c r="AA70" s="584"/>
-      <c r="AB70" s="585"/>
-      <c r="AC70" s="586"/>
+      <c r="AA70" s="587"/>
+      <c r="AB70" s="588"/>
+      <c r="AC70" s="589"/>
       <c r="AD70" s="95"/>
       <c r="AE70" s="95"/>
       <c r="AF70" s="95"/>
@@ -14517,10 +14517,10 @@
       <c r="AQ70" s="198"/>
       <c r="AR70" s="213"/>
       <c r="AS70" s="271"/>
-      <c r="AT70" s="563"/>
-      <c r="AU70" s="564"/>
-      <c r="AV70" s="564"/>
-      <c r="AW70" s="565"/>
+      <c r="AT70" s="566"/>
+      <c r="AU70" s="567"/>
+      <c r="AV70" s="567"/>
+      <c r="AW70" s="568"/>
       <c r="AX70" s="210"/>
       <c r="AY70" s="210"/>
       <c r="AZ70" s="307">
@@ -14588,7 +14588,7 @@
       </c>
       <c r="BP70" s="336">
         <f>COUNTIF($AK$11:$BL$63,"*403-16-*") + COUNTIF($BO$11:$BV$65,"*403-16-*")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BQ70" s="356">
         <f>COUNTIF($AK$11:$BL$63,"*403-17-*") + COUNTIF($BO$11:$BV$65,"*403-17-*")</f>
@@ -14616,7 +14616,7 @@
       </c>
       <c r="BW70" s="310">
         <f>SUM(BA70:BV70)/(14*16)</f>
-        <v>0.9553571428571429</v>
+        <v>0.9598214285714286</v>
       </c>
     </row>
     <row r="71" spans="1:85" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -14632,21 +14632,21 @@
       <c r="L71" s="79"/>
       <c r="M71" s="79"/>
       <c r="N71" s="81"/>
-      <c r="O71" s="579"/>
-      <c r="P71" s="518"/>
-      <c r="Q71" s="518"/>
-      <c r="R71" s="518"/>
-      <c r="S71" s="518"/>
-      <c r="T71" s="518"/>
-      <c r="U71" s="519"/>
+      <c r="O71" s="582"/>
+      <c r="P71" s="521"/>
+      <c r="Q71" s="521"/>
+      <c r="R71" s="521"/>
+      <c r="S71" s="521"/>
+      <c r="T71" s="521"/>
+      <c r="U71" s="522"/>
       <c r="V71" s="189"/>
       <c r="W71" s="53"/>
       <c r="X71" s="53"/>
       <c r="Y71" s="53"/>
       <c r="Z71" s="83"/>
-      <c r="AA71" s="587"/>
-      <c r="AB71" s="588"/>
-      <c r="AC71" s="589"/>
+      <c r="AA71" s="590"/>
+      <c r="AB71" s="591"/>
+      <c r="AC71" s="592"/>
       <c r="AD71" s="95"/>
       <c r="AE71" s="95"/>
       <c r="AF71" s="95"/>
@@ -14657,10 +14657,10 @@
       <c r="AQ71" s="198"/>
       <c r="AR71" s="213"/>
       <c r="AS71" s="271"/>
-      <c r="AT71" s="566"/>
-      <c r="AU71" s="567"/>
-      <c r="AV71" s="567"/>
-      <c r="AW71" s="568"/>
+      <c r="AT71" s="569"/>
+      <c r="AU71" s="570"/>
+      <c r="AV71" s="570"/>
+      <c r="AW71" s="571"/>
       <c r="AX71" s="210"/>
       <c r="AY71" s="210"/>
       <c r="AZ71" s="210"/>
@@ -14681,13 +14681,13 @@
       <c r="L72" s="79"/>
       <c r="M72" s="79"/>
       <c r="N72" s="81"/>
-      <c r="O72" s="579"/>
-      <c r="P72" s="518"/>
-      <c r="Q72" s="518"/>
-      <c r="R72" s="518"/>
-      <c r="S72" s="518"/>
-      <c r="T72" s="518"/>
-      <c r="U72" s="519"/>
+      <c r="O72" s="582"/>
+      <c r="P72" s="521"/>
+      <c r="Q72" s="521"/>
+      <c r="R72" s="521"/>
+      <c r="S72" s="521"/>
+      <c r="T72" s="521"/>
+      <c r="U72" s="522"/>
       <c r="V72" s="189"/>
       <c r="W72" s="53"/>
       <c r="X72" s="53"/>
@@ -14744,13 +14744,13 @@
       <c r="L73" s="79"/>
       <c r="M73" s="79"/>
       <c r="N73" s="81"/>
-      <c r="O73" s="579"/>
-      <c r="P73" s="518"/>
-      <c r="Q73" s="518"/>
-      <c r="R73" s="518"/>
-      <c r="S73" s="518"/>
-      <c r="T73" s="518"/>
-      <c r="U73" s="519"/>
+      <c r="O73" s="582"/>
+      <c r="P73" s="521"/>
+      <c r="Q73" s="521"/>
+      <c r="R73" s="521"/>
+      <c r="S73" s="521"/>
+      <c r="T73" s="521"/>
+      <c r="U73" s="522"/>
       <c r="V73" s="189"/>
       <c r="W73" s="53"/>
       <c r="X73" s="53"/>
@@ -14807,22 +14807,22 @@
       <c r="L74" s="79"/>
       <c r="M74" s="79"/>
       <c r="N74" s="81"/>
-      <c r="O74" s="579"/>
-      <c r="P74" s="518"/>
-      <c r="Q74" s="518"/>
-      <c r="R74" s="518"/>
-      <c r="S74" s="518"/>
-      <c r="T74" s="518"/>
-      <c r="U74" s="519"/>
+      <c r="O74" s="582"/>
+      <c r="P74" s="521"/>
+      <c r="Q74" s="521"/>
+      <c r="R74" s="521"/>
+      <c r="S74" s="521"/>
+      <c r="T74" s="521"/>
+      <c r="U74" s="522"/>
       <c r="V74" s="207"/>
       <c r="W74" s="208"/>
       <c r="X74" s="53"/>
       <c r="Y74" s="53"/>
       <c r="Z74" s="53"/>
-      <c r="AB74" s="509" t="s">
+      <c r="AB74" s="512" t="s">
         <v>49</v>
       </c>
-      <c r="AC74" s="510"/>
+      <c r="AC74" s="513"/>
       <c r="AG74" s="90"/>
       <c r="AH74" s="121"/>
       <c r="AI74" s="90"/>
@@ -14831,21 +14831,21 @@
       <c r="AQ74" s="198"/>
       <c r="AR74" s="198"/>
       <c r="AS74" s="198"/>
-      <c r="AT74" s="569" t="s">
+      <c r="AT74" s="572" t="s">
         <v>13</v>
       </c>
-      <c r="AU74" s="570"/>
-      <c r="AV74" s="570"/>
-      <c r="AW74" s="570"/>
-      <c r="AX74" s="570"/>
-      <c r="AY74" s="571"/>
+      <c r="AU74" s="573"/>
+      <c r="AV74" s="573"/>
+      <c r="AW74" s="573"/>
+      <c r="AX74" s="573"/>
+      <c r="AY74" s="574"/>
       <c r="AZ74" s="210"/>
       <c r="BA74" s="90"/>
-      <c r="BB74" s="513" t="s">
+      <c r="BB74" s="516" t="s">
         <v>0</v>
       </c>
       <c r="BC74" s="297"/>
-      <c r="BD74" s="513" t="s">
+      <c r="BD74" s="516" t="s">
         <v>1</v>
       </c>
       <c r="BF74" s="294"/>
@@ -14879,19 +14879,19 @@
       <c r="L75" s="79"/>
       <c r="M75" s="79"/>
       <c r="N75" s="81"/>
-      <c r="O75" s="579"/>
-      <c r="P75" s="518"/>
-      <c r="Q75" s="518"/>
-      <c r="R75" s="518"/>
-      <c r="S75" s="518"/>
-      <c r="T75" s="518"/>
-      <c r="U75" s="519"/>
+      <c r="O75" s="582"/>
+      <c r="P75" s="521"/>
+      <c r="Q75" s="521"/>
+      <c r="R75" s="521"/>
+      <c r="S75" s="521"/>
+      <c r="T75" s="521"/>
+      <c r="U75" s="522"/>
       <c r="V75" s="189"/>
       <c r="W75" s="208"/>
       <c r="X75" s="53"/>
       <c r="Z75" s="53"/>
-      <c r="AB75" s="509"/>
-      <c r="AC75" s="510"/>
+      <c r="AB75" s="512"/>
+      <c r="AC75" s="513"/>
       <c r="AD75" s="92"/>
       <c r="AE75" s="92"/>
       <c r="AG75" s="90"/>
@@ -14902,17 +14902,17 @@
       <c r="AQ75" s="42"/>
       <c r="AR75" s="198"/>
       <c r="AS75" s="198"/>
-      <c r="AT75" s="572"/>
-      <c r="AU75" s="573"/>
-      <c r="AV75" s="573"/>
-      <c r="AW75" s="573"/>
-      <c r="AX75" s="573"/>
-      <c r="AY75" s="574"/>
+      <c r="AT75" s="575"/>
+      <c r="AU75" s="576"/>
+      <c r="AV75" s="576"/>
+      <c r="AW75" s="576"/>
+      <c r="AX75" s="576"/>
+      <c r="AY75" s="577"/>
       <c r="AZ75" s="97"/>
       <c r="BA75" s="97"/>
-      <c r="BB75" s="514"/>
+      <c r="BB75" s="517"/>
       <c r="BC75" s="298"/>
-      <c r="BD75" s="514"/>
+      <c r="BD75" s="517"/>
       <c r="BL75" s="88"/>
       <c r="BN75" s="6"/>
       <c r="BO75" s="6"/>
@@ -14937,13 +14937,13 @@
       <c r="L76" s="79"/>
       <c r="M76" s="79"/>
       <c r="N76" s="81"/>
-      <c r="O76" s="579"/>
-      <c r="P76" s="518"/>
-      <c r="Q76" s="518"/>
-      <c r="R76" s="518"/>
-      <c r="S76" s="518"/>
-      <c r="T76" s="518"/>
-      <c r="U76" s="519"/>
+      <c r="O76" s="582"/>
+      <c r="P76" s="521"/>
+      <c r="Q76" s="521"/>
+      <c r="R76" s="521"/>
+      <c r="S76" s="521"/>
+      <c r="T76" s="521"/>
+      <c r="U76" s="522"/>
       <c r="V76" s="189"/>
       <c r="W76" s="208"/>
       <c r="X76" s="53"/>
@@ -14966,17 +14966,17 @@
       <c r="AQ76" s="234"/>
       <c r="AR76" s="206"/>
       <c r="AS76" s="206"/>
-      <c r="AT76" s="575"/>
-      <c r="AU76" s="576"/>
-      <c r="AV76" s="576"/>
-      <c r="AW76" s="576"/>
-      <c r="AX76" s="576"/>
-      <c r="AY76" s="577"/>
+      <c r="AT76" s="578"/>
+      <c r="AU76" s="579"/>
+      <c r="AV76" s="579"/>
+      <c r="AW76" s="579"/>
+      <c r="AX76" s="579"/>
+      <c r="AY76" s="580"/>
       <c r="AZ76" s="206"/>
       <c r="BA76" s="206"/>
-      <c r="BB76" s="515"/>
+      <c r="BB76" s="518"/>
       <c r="BC76" s="299"/>
-      <c r="BD76" s="515"/>
+      <c r="BD76" s="518"/>
       <c r="BE76" s="235"/>
       <c r="BF76" s="235"/>
       <c r="BG76" s="235"/>
@@ -14998,13 +14998,13 @@
       <c r="L77" s="79"/>
       <c r="M77" s="79"/>
       <c r="N77" s="81"/>
-      <c r="O77" s="579"/>
-      <c r="P77" s="518"/>
-      <c r="Q77" s="518"/>
-      <c r="R77" s="518"/>
-      <c r="S77" s="518"/>
-      <c r="T77" s="518"/>
-      <c r="U77" s="519"/>
+      <c r="O77" s="582"/>
+      <c r="P77" s="521"/>
+      <c r="Q77" s="521"/>
+      <c r="R77" s="521"/>
+      <c r="S77" s="521"/>
+      <c r="T77" s="521"/>
+      <c r="U77" s="522"/>
       <c r="V77" s="189"/>
       <c r="W77" s="208"/>
       <c r="X77" s="53"/>
@@ -15019,13 +15019,13 @@
       <c r="AJ77" s="186"/>
       <c r="AK77" s="226"/>
       <c r="AL77" s="226"/>
-      <c r="AM77" s="554" t="s">
+      <c r="AM77" s="557" t="s">
         <v>3</v>
       </c>
-      <c r="AN77" s="555"/>
-      <c r="AO77" s="555"/>
-      <c r="AP77" s="555"/>
-      <c r="AQ77" s="556"/>
+      <c r="AN77" s="558"/>
+      <c r="AO77" s="558"/>
+      <c r="AP77" s="558"/>
+      <c r="AQ77" s="559"/>
       <c r="AR77" s="240"/>
       <c r="BI77" s="241"/>
     </row>
@@ -15042,13 +15042,13 @@
       <c r="L78" s="107"/>
       <c r="M78" s="107"/>
       <c r="N78" s="215"/>
-      <c r="O78" s="580"/>
-      <c r="P78" s="520"/>
-      <c r="Q78" s="520"/>
-      <c r="R78" s="520"/>
-      <c r="S78" s="520"/>
-      <c r="T78" s="520"/>
-      <c r="U78" s="521"/>
+      <c r="O78" s="583"/>
+      <c r="P78" s="523"/>
+      <c r="Q78" s="523"/>
+      <c r="R78" s="523"/>
+      <c r="S78" s="523"/>
+      <c r="T78" s="523"/>
+      <c r="U78" s="524"/>
       <c r="V78" s="189"/>
       <c r="W78" s="208"/>
       <c r="X78" s="53"/>
@@ -15060,11 +15060,11 @@
       <c r="AH78" s="92"/>
       <c r="AK78" s="226"/>
       <c r="AL78" s="226"/>
-      <c r="AM78" s="557"/>
-      <c r="AN78" s="558"/>
-      <c r="AO78" s="558"/>
-      <c r="AP78" s="558"/>
-      <c r="AQ78" s="559"/>
+      <c r="AM78" s="560"/>
+      <c r="AN78" s="561"/>
+      <c r="AO78" s="561"/>
+      <c r="AP78" s="561"/>
+      <c r="AQ78" s="562"/>
       <c r="AU78" s="248"/>
       <c r="AV78" s="248"/>
       <c r="AW78" s="248"/>
@@ -15339,13 +15339,13 @@
       <c r="H83" s="229"/>
       <c r="I83" s="230"/>
       <c r="J83" s="231"/>
-      <c r="K83" s="527" t="s">
+      <c r="K83" s="530" t="s">
         <v>50</v>
       </c>
-      <c r="L83" s="528"/>
-      <c r="M83" s="528"/>
-      <c r="N83" s="528"/>
-      <c r="O83" s="529"/>
+      <c r="L83" s="531"/>
+      <c r="M83" s="531"/>
+      <c r="N83" s="531"/>
+      <c r="O83" s="532"/>
       <c r="P83" s="224"/>
       <c r="Q83" s="224"/>
       <c r="R83" s="224"/>
@@ -15402,28 +15402,28 @@
     </row>
     <row r="84" spans="1:74" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="42"/>
-      <c r="B84" s="472" t="s">
+      <c r="B84" s="475" t="s">
         <v>51</v>
       </c>
-      <c r="C84" s="536"/>
-      <c r="D84" s="537"/>
-      <c r="E84" s="525" t="s">
+      <c r="C84" s="539"/>
+      <c r="D84" s="540"/>
+      <c r="E84" s="528" t="s">
         <v>52</v>
       </c>
-      <c r="F84" s="526"/>
-      <c r="G84" s="474" t="s">
+      <c r="F84" s="529"/>
+      <c r="G84" s="477" t="s">
         <v>52</v>
       </c>
-      <c r="H84" s="487"/>
-      <c r="I84" s="542" t="s">
+      <c r="H84" s="490"/>
+      <c r="I84" s="545" t="s">
         <v>53</v>
       </c>
-      <c r="J84" s="543"/>
-      <c r="K84" s="530"/>
-      <c r="L84" s="531"/>
-      <c r="M84" s="531"/>
-      <c r="N84" s="531"/>
-      <c r="O84" s="532"/>
+      <c r="J84" s="546"/>
+      <c r="K84" s="533"/>
+      <c r="L84" s="534"/>
+      <c r="M84" s="534"/>
+      <c r="N84" s="534"/>
+      <c r="O84" s="535"/>
       <c r="P84" s="224"/>
       <c r="Q84" s="224"/>
       <c r="R84" s="224"/>
@@ -15477,27 +15477,27 @@
       <c r="BS84" s="259"/>
       <c r="BT84" s="259"/>
       <c r="BU84" s="259"/>
-      <c r="BV84" s="508"/>
+      <c r="BV84" s="511"/>
     </row>
     <row r="85" spans="1:74" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="538"/>
-      <c r="C85" s="536"/>
-      <c r="D85" s="537"/>
-      <c r="E85" s="525" t="s">
+      <c r="B85" s="541"/>
+      <c r="C85" s="539"/>
+      <c r="D85" s="540"/>
+      <c r="E85" s="528" t="s">
         <v>52</v>
       </c>
-      <c r="F85" s="546"/>
-      <c r="G85" s="525" t="s">
+      <c r="F85" s="549"/>
+      <c r="G85" s="528" t="s">
         <v>52</v>
       </c>
-      <c r="H85" s="546"/>
-      <c r="I85" s="542"/>
-      <c r="J85" s="543"/>
-      <c r="K85" s="530"/>
-      <c r="L85" s="531"/>
-      <c r="M85" s="531"/>
-      <c r="N85" s="531"/>
-      <c r="O85" s="532"/>
+      <c r="H85" s="549"/>
+      <c r="I85" s="545"/>
+      <c r="J85" s="546"/>
+      <c r="K85" s="533"/>
+      <c r="L85" s="534"/>
+      <c r="M85" s="534"/>
+      <c r="N85" s="534"/>
+      <c r="O85" s="535"/>
       <c r="P85" s="224"/>
       <c r="Q85" s="224"/>
       <c r="R85" s="224"/>
@@ -15551,28 +15551,28 @@
       <c r="BS85" s="259"/>
       <c r="BT85" s="259"/>
       <c r="BU85" s="259"/>
-      <c r="BV85" s="508"/>
+      <c r="BV85" s="511"/>
     </row>
     <row r="86" spans="1:74" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="42"/>
-      <c r="B86" s="539"/>
-      <c r="C86" s="540"/>
-      <c r="D86" s="541"/>
-      <c r="E86" s="525" t="s">
+      <c r="B86" s="542"/>
+      <c r="C86" s="543"/>
+      <c r="D86" s="544"/>
+      <c r="E86" s="528" t="s">
         <v>54</v>
       </c>
-      <c r="F86" s="526"/>
-      <c r="G86" s="525" t="s">
+      <c r="F86" s="529"/>
+      <c r="G86" s="528" t="s">
         <v>55</v>
       </c>
-      <c r="H86" s="526"/>
-      <c r="I86" s="544"/>
-      <c r="J86" s="545"/>
-      <c r="K86" s="533"/>
-      <c r="L86" s="534"/>
-      <c r="M86" s="534"/>
-      <c r="N86" s="534"/>
-      <c r="O86" s="535"/>
+      <c r="H86" s="529"/>
+      <c r="I86" s="547"/>
+      <c r="J86" s="548"/>
+      <c r="K86" s="536"/>
+      <c r="L86" s="537"/>
+      <c r="M86" s="537"/>
+      <c r="N86" s="537"/>
+      <c r="O86" s="538"/>
       <c r="P86" s="242"/>
       <c r="Q86" s="242"/>
       <c r="R86" s="242"/>
@@ -15626,7 +15626,7 @@
       <c r="BS86" s="259"/>
       <c r="BT86" s="259"/>
       <c r="BU86" s="259"/>
-      <c r="BV86" s="508"/>
+      <c r="BV86" s="511"/>
     </row>
     <row r="87" spans="1:74" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="249"/>
@@ -15698,7 +15698,7 @@
       <c r="BU87" s="259"/>
     </row>
     <row r="88" spans="1:74" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="501"/>
+      <c r="A88" s="504"/>
       <c r="B88" s="42"/>
       <c r="C88" s="42"/>
       <c r="D88" s="42"/>
@@ -15706,20 +15706,20 @@
       <c r="F88" s="42"/>
       <c r="G88" s="96"/>
       <c r="K88" s="92"/>
-      <c r="R88" s="552"/>
-      <c r="S88" s="552"/>
-      <c r="T88" s="552"/>
-      <c r="U88" s="552"/>
-      <c r="V88" s="552"/>
-      <c r="W88" s="552"/>
-      <c r="X88" s="552"/>
-      <c r="Y88" s="552"/>
-      <c r="Z88" s="552"/>
-      <c r="AA88" s="552"/>
-      <c r="AB88" s="552"/>
-      <c r="AC88" s="552"/>
-      <c r="AD88" s="590"/>
-      <c r="AE88" s="591"/>
+      <c r="R88" s="555"/>
+      <c r="S88" s="555"/>
+      <c r="T88" s="555"/>
+      <c r="U88" s="555"/>
+      <c r="V88" s="555"/>
+      <c r="W88" s="555"/>
+      <c r="X88" s="555"/>
+      <c r="Y88" s="555"/>
+      <c r="Z88" s="555"/>
+      <c r="AA88" s="555"/>
+      <c r="AB88" s="555"/>
+      <c r="AC88" s="555"/>
+      <c r="AD88" s="593"/>
+      <c r="AE88" s="594"/>
       <c r="AG88" s="260"/>
       <c r="AK88" s="206"/>
       <c r="AL88" s="206"/>
@@ -15756,7 +15756,7 @@
       <c r="BU88" s="259"/>
     </row>
     <row r="89" spans="1:74" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="501"/>
+      <c r="A89" s="504"/>
       <c r="B89" s="42"/>
       <c r="C89" s="42"/>
       <c r="D89" s="42"/>
@@ -15764,20 +15764,20 @@
       <c r="F89" s="42"/>
       <c r="G89" s="96"/>
       <c r="K89" s="92"/>
-      <c r="R89" s="553"/>
-      <c r="S89" s="553"/>
-      <c r="T89" s="553"/>
-      <c r="U89" s="553"/>
-      <c r="V89" s="553"/>
-      <c r="W89" s="553"/>
-      <c r="X89" s="553"/>
-      <c r="Y89" s="553"/>
-      <c r="Z89" s="553"/>
-      <c r="AA89" s="553"/>
-      <c r="AB89" s="553"/>
-      <c r="AC89" s="553"/>
-      <c r="AD89" s="590"/>
-      <c r="AE89" s="591"/>
+      <c r="R89" s="556"/>
+      <c r="S89" s="556"/>
+      <c r="T89" s="556"/>
+      <c r="U89" s="556"/>
+      <c r="V89" s="556"/>
+      <c r="W89" s="556"/>
+      <c r="X89" s="556"/>
+      <c r="Y89" s="556"/>
+      <c r="Z89" s="556"/>
+      <c r="AA89" s="556"/>
+      <c r="AB89" s="556"/>
+      <c r="AC89" s="556"/>
+      <c r="AD89" s="593"/>
+      <c r="AE89" s="594"/>
       <c r="AG89" s="264"/>
       <c r="AK89" s="285"/>
       <c r="AL89" s="281"/>
@@ -15818,18 +15818,18 @@
       <c r="BU89" s="259"/>
     </row>
     <row r="90" spans="1:74" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="501"/>
+      <c r="A90" s="504"/>
       <c r="H90" s="265"/>
       <c r="I90" s="265"/>
       <c r="J90" s="265"/>
       <c r="K90" s="179"/>
       <c r="L90" s="179"/>
-      <c r="R90" s="548"/>
-      <c r="S90" s="549"/>
-      <c r="T90" s="550"/>
-      <c r="U90" s="551"/>
-      <c r="V90" s="550"/>
-      <c r="W90" s="551"/>
+      <c r="R90" s="551"/>
+      <c r="S90" s="552"/>
+      <c r="T90" s="553"/>
+      <c r="U90" s="554"/>
+      <c r="V90" s="553"/>
+      <c r="W90" s="554"/>
       <c r="AD90" s="70"/>
       <c r="AE90" s="70"/>
       <c r="AF90" s="70"/>
@@ -15885,12 +15885,12 @@
       <c r="J91" s="179"/>
       <c r="K91" s="70"/>
       <c r="L91" s="70"/>
-      <c r="R91" s="523"/>
-      <c r="S91" s="524"/>
-      <c r="T91" s="523"/>
-      <c r="U91" s="524"/>
-      <c r="V91" s="547"/>
-      <c r="W91" s="592"/>
+      <c r="R91" s="526"/>
+      <c r="S91" s="527"/>
+      <c r="T91" s="526"/>
+      <c r="U91" s="527"/>
+      <c r="V91" s="550"/>
+      <c r="W91" s="595"/>
       <c r="X91" s="5"/>
       <c r="AB91" s="267"/>
       <c r="AC91" s="5"/>
@@ -15900,7 +15900,7 @@
       <c r="AH91" s="70"/>
     </row>
     <row r="92" spans="1:74" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="501"/>
+      <c r="A92" s="504"/>
       <c r="B92" s="179"/>
       <c r="C92" s="179"/>
       <c r="D92" s="179"/>
@@ -15917,15 +15917,15 @@
       <c r="O92" s="269"/>
       <c r="P92" s="224"/>
       <c r="Q92" s="70"/>
-      <c r="R92" s="523"/>
-      <c r="S92" s="524"/>
-      <c r="T92" s="523"/>
-      <c r="U92" s="524"/>
-      <c r="V92" s="523"/>
-      <c r="W92" s="524"/>
+      <c r="R92" s="526"/>
+      <c r="S92" s="527"/>
+      <c r="T92" s="526"/>
+      <c r="U92" s="527"/>
+      <c r="V92" s="526"/>
+      <c r="W92" s="527"/>
       <c r="X92" s="46"/>
-      <c r="Y92" s="523"/>
-      <c r="Z92" s="524"/>
+      <c r="Y92" s="526"/>
+      <c r="Z92" s="527"/>
       <c r="AA92" s="270"/>
       <c r="AB92" s="271"/>
       <c r="AC92" s="5"/>
@@ -15935,7 +15935,7 @@
       <c r="AH92" s="70"/>
     </row>
     <row r="93" spans="1:74" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="501"/>
+      <c r="A93" s="504"/>
       <c r="B93" s="97"/>
       <c r="C93" s="97"/>
       <c r="D93" s="97"/>
@@ -15953,13 +15953,13 @@
       <c r="P93" s="70"/>
       <c r="Q93" s="70"/>
       <c r="R93" s="272"/>
-      <c r="S93" s="523"/>
-      <c r="T93" s="524"/>
+      <c r="S93" s="526"/>
+      <c r="T93" s="527"/>
       <c r="U93" s="273"/>
-      <c r="V93" s="547"/>
-      <c r="W93" s="547"/>
-      <c r="X93" s="547"/>
-      <c r="Y93" s="547"/>
+      <c r="V93" s="550"/>
+      <c r="W93" s="550"/>
+      <c r="X93" s="550"/>
+      <c r="Y93" s="550"/>
       <c r="Z93" s="274"/>
       <c r="AA93" s="275"/>
       <c r="AB93" s="267"/>
@@ -15971,7 +15971,7 @@
       <c r="AH93" s="70"/>
     </row>
     <row r="94" spans="1:74" ht="186" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="501"/>
+      <c r="A94" s="504"/>
       <c r="B94" s="97"/>
       <c r="C94" s="97"/>
       <c r="D94" s="97"/>
@@ -16023,11 +16023,11 @@
       <c r="W95" s="199"/>
     </row>
     <row r="96" spans="1:74" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E96" s="501"/>
+      <c r="E96" s="504"/>
       <c r="F96" s="159"/>
-      <c r="G96" s="501"/>
-      <c r="H96" s="501"/>
-      <c r="I96" s="501"/>
+      <c r="G96" s="504"/>
+      <c r="H96" s="504"/>
+      <c r="I96" s="504"/>
       <c r="J96" s="199"/>
       <c r="K96" s="199"/>
       <c r="L96" s="199"/>
@@ -16044,11 +16044,11 @@
       <c r="W96" s="199"/>
     </row>
     <row r="97" spans="5:36" ht="186" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E97" s="501"/>
+      <c r="E97" s="504"/>
       <c r="F97" s="159"/>
-      <c r="G97" s="501"/>
-      <c r="H97" s="501"/>
-      <c r="I97" s="501"/>
+      <c r="G97" s="504"/>
+      <c r="H97" s="504"/>
+      <c r="I97" s="504"/>
       <c r="J97" s="199"/>
       <c r="K97" s="199"/>
       <c r="L97" s="199"/>
@@ -16078,11 +16078,11 @@
       <c r="AJ97" s="284"/>
     </row>
     <row r="98" spans="5:36" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E98" s="501"/>
+      <c r="E98" s="504"/>
       <c r="F98" s="159"/>
-      <c r="G98" s="501"/>
-      <c r="H98" s="501"/>
-      <c r="I98" s="501"/>
+      <c r="G98" s="504"/>
+      <c r="H98" s="504"/>
+      <c r="I98" s="504"/>
       <c r="J98" s="199"/>
       <c r="K98" s="199"/>
       <c r="L98" s="199"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\모듈러사업2실\★ 300. 제1공장_마감관리팀\350. 마감진행현황\BH(수정)\2026년 10월 BH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8649C2E-A625-4FAA-876A-0C2FF7F94D4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D85AFCF-B37C-43DC-90B8-81B85CD4816C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="788" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="672">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="673">
   <si>
     <t>공업화 주택 샘플</t>
   </si>
@@ -4029,12 +4029,6 @@
     <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
-    <t>402-8-9/
-36SB05
-2026-10-13</t>
-    <phoneticPr fontId="21" type="noConversion"/>
-  </si>
-  <si>
     <t>403-15-9/
 46SA75
 NONE
@@ -4226,11 +4220,6 @@
     <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
-    <t>402-6-2/
-2026-10-19</t>
-    <phoneticPr fontId="21" type="noConversion"/>
-  </si>
-  <si>
     <t>403-15-4/
 26SB68
 2026-10-19</t>
@@ -4246,6 +4235,24 @@
     <t>403-13-4/
 26SB68
 2026-10-19</t>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <t>403-12-5/
+26HB01
+2026-10-13</t>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <t>402-12-12/
+26SA02
+2026-10-20</t>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <t>402-6-8/
+36SB02
+2026-10-20</t>
     <phoneticPr fontId="21" type="noConversion"/>
   </si>
 </sst>
@@ -5453,7 +5460,7 @@
     </xf>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="430">
+  <cellXfs count="429">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6236,9 +6243,6 @@
     </xf>
     <xf numFmtId="0" fontId="48" fillId="16" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="13" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="18" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -7217,52 +7221,52 @@
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
       <c r="AA2" s="230"/>
-      <c r="AB2" s="407" t="s">
+      <c r="AB2" s="406" t="s">
         <v>4</v>
       </c>
-      <c r="AC2" s="408"/>
-      <c r="AD2" s="408"/>
-      <c r="AE2" s="408"/>
-      <c r="AF2" s="408"/>
-      <c r="AG2" s="408"/>
-      <c r="AH2" s="408"/>
-      <c r="AI2" s="409"/>
+      <c r="AC2" s="407"/>
+      <c r="AD2" s="407"/>
+      <c r="AE2" s="407"/>
+      <c r="AF2" s="407"/>
+      <c r="AG2" s="407"/>
+      <c r="AH2" s="407"/>
+      <c r="AI2" s="408"/>
       <c r="AJ2" s="2"/>
       <c r="AK2" s="230"/>
       <c r="AL2" s="200"/>
       <c r="AM2" s="201"/>
       <c r="AN2" s="201"/>
-      <c r="AO2" s="408" t="s">
+      <c r="AO2" s="407" t="s">
         <v>5</v>
       </c>
-      <c r="AP2" s="408"/>
+      <c r="AP2" s="407"/>
       <c r="AQ2" s="201"/>
       <c r="AR2" s="201"/>
       <c r="AS2" s="202"/>
       <c r="AT2" s="2"/>
       <c r="AU2" s="226"/>
-      <c r="AV2" s="410" t="s">
+      <c r="AV2" s="409" t="s">
         <v>6</v>
       </c>
-      <c r="AW2" s="411"/>
-      <c r="AX2" s="411"/>
-      <c r="AY2" s="411"/>
-      <c r="AZ2" s="411"/>
-      <c r="BA2" s="411"/>
-      <c r="BB2" s="411"/>
-      <c r="BC2" s="412"/>
+      <c r="AW2" s="410"/>
+      <c r="AX2" s="410"/>
+      <c r="AY2" s="410"/>
+      <c r="AZ2" s="410"/>
+      <c r="BA2" s="410"/>
+      <c r="BB2" s="410"/>
+      <c r="BC2" s="411"/>
       <c r="BD2" s="190"/>
       <c r="BE2" s="220"/>
-      <c r="BF2" s="410" t="s">
+      <c r="BF2" s="409" t="s">
         <v>7</v>
       </c>
-      <c r="BG2" s="411"/>
-      <c r="BH2" s="411"/>
-      <c r="BI2" s="411"/>
-      <c r="BJ2" s="411"/>
-      <c r="BK2" s="411"/>
-      <c r="BL2" s="411"/>
-      <c r="BM2" s="412"/>
+      <c r="BG2" s="410"/>
+      <c r="BH2" s="410"/>
+      <c r="BI2" s="410"/>
+      <c r="BJ2" s="410"/>
+      <c r="BK2" s="410"/>
+      <c r="BL2" s="410"/>
+      <c r="BM2" s="411"/>
       <c r="BO2" s="224"/>
     </row>
     <row r="3" spans="1:67" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -7275,28 +7279,28 @@
       </c>
       <c r="F3" s="25"/>
       <c r="G3" s="25"/>
-      <c r="H3" s="413" t="s">
+      <c r="H3" s="412" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="414"/>
-      <c r="J3" s="413" t="s">
+      <c r="I3" s="413"/>
+      <c r="J3" s="412" t="s">
         <v>15</v>
       </c>
-      <c r="K3" s="414"/>
-      <c r="L3" s="415" t="s">
+      <c r="K3" s="413"/>
+      <c r="L3" s="414" t="s">
         <v>16</v>
       </c>
-      <c r="M3" s="415"/>
+      <c r="M3" s="414"/>
       <c r="N3" s="26"/>
-      <c r="O3" s="416" t="s">
+      <c r="O3" s="415" t="s">
         <v>17</v>
       </c>
-      <c r="P3" s="417"/>
-      <c r="Q3" s="417"/>
-      <c r="R3" s="417"/>
-      <c r="S3" s="417"/>
-      <c r="T3" s="417"/>
-      <c r="U3" s="417"/>
+      <c r="P3" s="416"/>
+      <c r="Q3" s="416"/>
+      <c r="R3" s="416"/>
+      <c r="S3" s="416"/>
+      <c r="T3" s="416"/>
+      <c r="U3" s="416"/>
       <c r="V3" s="27"/>
       <c r="W3" s="28"/>
       <c r="X3" s="28"/>
@@ -7305,10 +7309,10 @@
       <c r="AA3" s="227" t="s">
         <v>275</v>
       </c>
-      <c r="AB3" s="266" t="s">
+      <c r="AB3" s="265" t="s">
         <v>585</v>
       </c>
-      <c r="AC3" s="266" t="s">
+      <c r="AC3" s="265" t="s">
         <v>605</v>
       </c>
       <c r="AD3" s="188"/>
@@ -7319,7 +7323,7 @@
       </c>
       <c r="AH3" s="188"/>
       <c r="AI3" s="188"/>
-      <c r="AJ3" s="271" t="s">
+      <c r="AJ3" s="270" t="s">
         <v>506</v>
       </c>
       <c r="AK3" s="227" t="s">
@@ -7333,7 +7337,7 @@
       <c r="AQ3" s="188"/>
       <c r="AR3" s="188"/>
       <c r="AS3" s="188"/>
-      <c r="AT3" s="271" t="s">
+      <c r="AT3" s="270" t="s">
         <v>330</v>
       </c>
       <c r="AU3" s="227" t="s">
@@ -7347,7 +7351,7 @@
       <c r="BA3" s="188"/>
       <c r="BB3" s="188"/>
       <c r="BC3" s="188"/>
-      <c r="BD3" s="271" t="s">
+      <c r="BD3" s="270" t="s">
         <v>304</v>
       </c>
       <c r="BE3" s="221" t="s">
@@ -7361,7 +7365,7 @@
       <c r="BK3" s="188"/>
       <c r="BL3" s="188"/>
       <c r="BM3" s="188"/>
-      <c r="BN3" s="271" t="s">
+      <c r="BN3" s="270" t="s">
         <v>276</v>
       </c>
       <c r="BO3" s="224"/>
@@ -7372,20 +7376,20 @@
       <c r="E4" s="30"/>
       <c r="F4" s="31"/>
       <c r="G4" s="31"/>
-      <c r="H4" s="344"/>
-      <c r="I4" s="346"/>
-      <c r="J4" s="344"/>
-      <c r="K4" s="346"/>
-      <c r="L4" s="345"/>
-      <c r="M4" s="345"/>
+      <c r="H4" s="343"/>
+      <c r="I4" s="345"/>
+      <c r="J4" s="343"/>
+      <c r="K4" s="345"/>
+      <c r="L4" s="344"/>
+      <c r="M4" s="344"/>
       <c r="N4" s="33"/>
-      <c r="O4" s="418"/>
-      <c r="P4" s="419"/>
-      <c r="Q4" s="419"/>
-      <c r="R4" s="419"/>
-      <c r="S4" s="419"/>
-      <c r="T4" s="419"/>
-      <c r="U4" s="419"/>
+      <c r="O4" s="417"/>
+      <c r="P4" s="418"/>
+      <c r="Q4" s="418"/>
+      <c r="R4" s="418"/>
+      <c r="S4" s="418"/>
+      <c r="T4" s="418"/>
+      <c r="U4" s="418"/>
       <c r="V4" s="34"/>
       <c r="W4" s="14"/>
       <c r="X4" s="14"/>
@@ -7410,7 +7414,7 @@
       <c r="AI4" s="235" t="s">
         <v>539</v>
       </c>
-      <c r="AJ4" s="271"/>
+      <c r="AJ4" s="270"/>
       <c r="AK4" s="227"/>
       <c r="AL4" s="189"/>
       <c r="AM4" s="189"/>
@@ -7420,7 +7424,7 @@
       <c r="AQ4" s="189"/>
       <c r="AR4" s="189"/>
       <c r="AS4" s="189"/>
-      <c r="AT4" s="271"/>
+      <c r="AT4" s="270"/>
       <c r="AU4" s="227"/>
       <c r="AV4" s="189"/>
       <c r="AW4" s="189"/>
@@ -7430,7 +7434,7 @@
       <c r="BA4" s="189"/>
       <c r="BB4" s="189"/>
       <c r="BC4" s="189"/>
-      <c r="BD4" s="271"/>
+      <c r="BD4" s="270"/>
       <c r="BE4" s="221"/>
       <c r="BF4" s="238" t="s">
         <v>154</v>
@@ -7444,7 +7448,7 @@
       <c r="BK4" s="189"/>
       <c r="BL4" s="189"/>
       <c r="BM4" s="189"/>
-      <c r="BN4" s="271"/>
+      <c r="BN4" s="270"/>
       <c r="BO4" s="224"/>
     </row>
     <row r="5" spans="1:67" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -7453,20 +7457,20 @@
       <c r="E5" s="30"/>
       <c r="F5" s="31"/>
       <c r="G5" s="31"/>
-      <c r="H5" s="344"/>
-      <c r="I5" s="346"/>
-      <c r="J5" s="344"/>
-      <c r="K5" s="346"/>
-      <c r="L5" s="345"/>
-      <c r="M5" s="345"/>
+      <c r="H5" s="343"/>
+      <c r="I5" s="345"/>
+      <c r="J5" s="343"/>
+      <c r="K5" s="345"/>
+      <c r="L5" s="344"/>
+      <c r="M5" s="344"/>
       <c r="N5" s="33"/>
-      <c r="O5" s="418"/>
-      <c r="P5" s="419"/>
-      <c r="Q5" s="419"/>
-      <c r="R5" s="419"/>
-      <c r="S5" s="419"/>
-      <c r="T5" s="419"/>
-      <c r="U5" s="419"/>
+      <c r="O5" s="417"/>
+      <c r="P5" s="418"/>
+      <c r="Q5" s="418"/>
+      <c r="R5" s="418"/>
+      <c r="S5" s="418"/>
+      <c r="T5" s="418"/>
+      <c r="U5" s="418"/>
       <c r="V5" s="34"/>
       <c r="W5" s="14"/>
       <c r="X5" s="14"/>
@@ -7475,10 +7479,10 @@
       <c r="AA5" s="228" t="s">
         <v>275</v>
       </c>
-      <c r="AB5" s="266" t="s">
+      <c r="AB5" s="265" t="s">
         <v>606</v>
       </c>
-      <c r="AC5" s="266" t="s">
+      <c r="AC5" s="265" t="s">
         <v>612</v>
       </c>
       <c r="AD5" s="204"/>
@@ -7489,7 +7493,7 @@
       </c>
       <c r="AH5" s="204"/>
       <c r="AI5" s="204"/>
-      <c r="AJ5" s="270" t="s">
+      <c r="AJ5" s="269" t="s">
         <v>507</v>
       </c>
       <c r="AK5" s="228" t="s">
@@ -7503,7 +7507,7 @@
       <c r="AQ5" s="204"/>
       <c r="AR5" s="204"/>
       <c r="AS5" s="204"/>
-      <c r="AT5" s="270" t="s">
+      <c r="AT5" s="269" t="s">
         <v>331</v>
       </c>
       <c r="AU5" s="228" t="s">
@@ -7517,7 +7521,7 @@
       <c r="BA5" s="204"/>
       <c r="BB5" s="204"/>
       <c r="BC5" s="204"/>
-      <c r="BD5" s="270" t="s">
+      <c r="BD5" s="269" t="s">
         <v>305</v>
       </c>
       <c r="BE5" s="222" t="s">
@@ -7531,7 +7535,7 @@
       <c r="BK5" s="204"/>
       <c r="BL5" s="204"/>
       <c r="BM5" s="204"/>
-      <c r="BN5" s="270" t="s">
+      <c r="BN5" s="269" t="s">
         <v>277</v>
       </c>
       <c r="BO5" s="224"/>
@@ -7542,20 +7546,20 @@
       <c r="E6" s="30"/>
       <c r="F6" s="31"/>
       <c r="G6" s="31"/>
-      <c r="H6" s="344"/>
-      <c r="I6" s="346"/>
-      <c r="J6" s="344"/>
-      <c r="K6" s="346"/>
-      <c r="L6" s="345"/>
-      <c r="M6" s="345"/>
+      <c r="H6" s="343"/>
+      <c r="I6" s="345"/>
+      <c r="J6" s="343"/>
+      <c r="K6" s="345"/>
+      <c r="L6" s="344"/>
+      <c r="M6" s="344"/>
       <c r="N6" s="33"/>
-      <c r="O6" s="418"/>
-      <c r="P6" s="419"/>
-      <c r="Q6" s="419"/>
-      <c r="R6" s="419"/>
-      <c r="S6" s="419"/>
-      <c r="T6" s="419"/>
-      <c r="U6" s="419"/>
+      <c r="O6" s="417"/>
+      <c r="P6" s="418"/>
+      <c r="Q6" s="418"/>
+      <c r="R6" s="418"/>
+      <c r="S6" s="418"/>
+      <c r="T6" s="418"/>
+      <c r="U6" s="418"/>
       <c r="V6" s="34"/>
       <c r="W6" s="14"/>
       <c r="X6" s="14"/>
@@ -7576,7 +7580,7 @@
         <v>587</v>
       </c>
       <c r="AG6" s="235" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="AH6" s="235" t="s">
         <v>581</v>
@@ -7584,7 +7588,7 @@
       <c r="AI6" s="235" t="s">
         <v>582</v>
       </c>
-      <c r="AJ6" s="270"/>
+      <c r="AJ6" s="269"/>
       <c r="AK6" s="228"/>
       <c r="AL6" s="203"/>
       <c r="AM6" s="203"/>
@@ -7594,7 +7598,7 @@
       <c r="AQ6" s="203"/>
       <c r="AR6" s="203"/>
       <c r="AS6" s="203"/>
-      <c r="AT6" s="270"/>
+      <c r="AT6" s="269"/>
       <c r="AU6" s="228"/>
       <c r="AV6" s="203"/>
       <c r="AW6" s="203"/>
@@ -7604,7 +7608,7 @@
       <c r="BA6" s="203"/>
       <c r="BB6" s="203"/>
       <c r="BC6" s="203"/>
-      <c r="BD6" s="270"/>
+      <c r="BD6" s="269"/>
       <c r="BE6" s="222"/>
       <c r="BF6" s="211" t="s">
         <v>409</v>
@@ -7618,7 +7622,7 @@
       <c r="BK6" s="203"/>
       <c r="BL6" s="203"/>
       <c r="BM6" s="203"/>
-      <c r="BN6" s="270"/>
+      <c r="BN6" s="269"/>
       <c r="BO6" s="224"/>
     </row>
     <row r="7" spans="1:67" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -7630,20 +7634,20 @@
       <c r="E7" s="30"/>
       <c r="F7" s="31"/>
       <c r="G7" s="31"/>
-      <c r="H7" s="344"/>
-      <c r="I7" s="346"/>
-      <c r="J7" s="344"/>
-      <c r="K7" s="346"/>
-      <c r="L7" s="345"/>
-      <c r="M7" s="345"/>
+      <c r="H7" s="343"/>
+      <c r="I7" s="345"/>
+      <c r="J7" s="343"/>
+      <c r="K7" s="345"/>
+      <c r="L7" s="344"/>
+      <c r="M7" s="344"/>
       <c r="N7" s="33"/>
-      <c r="O7" s="420"/>
-      <c r="P7" s="421"/>
-      <c r="Q7" s="421"/>
-      <c r="R7" s="421"/>
-      <c r="S7" s="421"/>
-      <c r="T7" s="421"/>
-      <c r="U7" s="421"/>
+      <c r="O7" s="419"/>
+      <c r="P7" s="420"/>
+      <c r="Q7" s="420"/>
+      <c r="R7" s="420"/>
+      <c r="S7" s="420"/>
+      <c r="T7" s="420"/>
+      <c r="U7" s="420"/>
       <c r="V7" s="34"/>
       <c r="W7" s="14"/>
       <c r="X7" s="14"/>
@@ -7652,10 +7656,10 @@
       <c r="AA7" s="227" t="s">
         <v>275</v>
       </c>
-      <c r="AB7" s="266" t="s">
+      <c r="AB7" s="265" t="s">
         <v>613</v>
       </c>
-      <c r="AC7" s="266" t="s">
+      <c r="AC7" s="265" t="s">
         <v>614</v>
       </c>
       <c r="AD7" s="188"/>
@@ -7664,7 +7668,7 @@
       <c r="AG7" s="188"/>
       <c r="AH7" s="188"/>
       <c r="AI7" s="188"/>
-      <c r="AJ7" s="271" t="s">
+      <c r="AJ7" s="270" t="s">
         <v>508</v>
       </c>
       <c r="AK7" s="227" t="s">
@@ -7678,7 +7682,7 @@
       <c r="AQ7" s="188"/>
       <c r="AR7" s="188"/>
       <c r="AS7" s="188"/>
-      <c r="AT7" s="271" t="s">
+      <c r="AT7" s="270" t="s">
         <v>332</v>
       </c>
       <c r="AU7" s="227" t="s">
@@ -7692,7 +7696,7 @@
       <c r="BA7" s="188"/>
       <c r="BB7" s="188"/>
       <c r="BC7" s="188"/>
-      <c r="BD7" s="271" t="s">
+      <c r="BD7" s="270" t="s">
         <v>306</v>
       </c>
       <c r="BE7" s="221" t="s">
@@ -7708,7 +7712,7 @@
       <c r="BK7" s="188"/>
       <c r="BL7" s="188"/>
       <c r="BM7" s="188"/>
-      <c r="BN7" s="271" t="s">
+      <c r="BN7" s="270" t="s">
         <v>278</v>
       </c>
       <c r="BO7" s="224"/>
@@ -7719,22 +7723,22 @@
       <c r="E8" s="30"/>
       <c r="F8" s="31"/>
       <c r="G8" s="31"/>
-      <c r="H8" s="344"/>
-      <c r="I8" s="346"/>
-      <c r="J8" s="344"/>
-      <c r="K8" s="346"/>
-      <c r="L8" s="345"/>
-      <c r="M8" s="345"/>
+      <c r="H8" s="343"/>
+      <c r="I8" s="345"/>
+      <c r="J8" s="343"/>
+      <c r="K8" s="345"/>
+      <c r="L8" s="344"/>
+      <c r="M8" s="344"/>
       <c r="N8" s="33"/>
-      <c r="O8" s="416" t="s">
+      <c r="O8" s="415" t="s">
         <v>18</v>
       </c>
-      <c r="P8" s="417"/>
-      <c r="Q8" s="417"/>
-      <c r="R8" s="417"/>
-      <c r="S8" s="417"/>
-      <c r="T8" s="417"/>
-      <c r="U8" s="417"/>
+      <c r="P8" s="416"/>
+      <c r="Q8" s="416"/>
+      <c r="R8" s="416"/>
+      <c r="S8" s="416"/>
+      <c r="T8" s="416"/>
+      <c r="U8" s="416"/>
       <c r="V8" s="34"/>
       <c r="W8" s="14"/>
       <c r="X8" s="14"/>
@@ -7765,7 +7769,7 @@
       <c r="AI8" s="209" t="s">
         <v>611</v>
       </c>
-      <c r="AJ8" s="271"/>
+      <c r="AJ8" s="270"/>
       <c r="AK8" s="227"/>
       <c r="AL8" s="189"/>
       <c r="AM8" s="189"/>
@@ -7775,7 +7779,7 @@
       <c r="AQ8" s="189"/>
       <c r="AR8" s="189"/>
       <c r="AS8" s="189"/>
-      <c r="AT8" s="271"/>
+      <c r="AT8" s="270"/>
       <c r="AU8" s="227"/>
       <c r="AV8" s="189"/>
       <c r="AW8" s="189"/>
@@ -7785,7 +7789,7 @@
       <c r="BA8" s="189"/>
       <c r="BB8" s="189"/>
       <c r="BC8" s="189"/>
-      <c r="BD8" s="271"/>
+      <c r="BD8" s="270"/>
       <c r="BE8" s="221"/>
       <c r="BF8" s="238" t="s">
         <v>158</v>
@@ -7797,7 +7801,7 @@
       <c r="BK8" s="189"/>
       <c r="BL8" s="189"/>
       <c r="BM8" s="189"/>
-      <c r="BN8" s="271"/>
+      <c r="BN8" s="270"/>
       <c r="BO8" s="224"/>
     </row>
     <row r="9" spans="1:67" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -7807,20 +7811,20 @@
       <c r="E9" s="30"/>
       <c r="F9" s="31"/>
       <c r="G9" s="31"/>
-      <c r="H9" s="344"/>
-      <c r="I9" s="346"/>
-      <c r="J9" s="344"/>
-      <c r="K9" s="346"/>
-      <c r="L9" s="345"/>
-      <c r="M9" s="345"/>
+      <c r="H9" s="343"/>
+      <c r="I9" s="345"/>
+      <c r="J9" s="343"/>
+      <c r="K9" s="345"/>
+      <c r="L9" s="344"/>
+      <c r="M9" s="344"/>
       <c r="N9" s="33"/>
-      <c r="O9" s="418"/>
-      <c r="P9" s="419"/>
-      <c r="Q9" s="419"/>
-      <c r="R9" s="419"/>
-      <c r="S9" s="419"/>
-      <c r="T9" s="419"/>
-      <c r="U9" s="419"/>
+      <c r="O9" s="417"/>
+      <c r="P9" s="418"/>
+      <c r="Q9" s="418"/>
+      <c r="R9" s="418"/>
+      <c r="S9" s="418"/>
+      <c r="T9" s="418"/>
+      <c r="U9" s="418"/>
       <c r="V9" s="34"/>
       <c r="W9" s="14"/>
       <c r="X9" s="14"/>
@@ -7832,7 +7836,7 @@
       <c r="AB9" s="245" t="s">
         <v>594</v>
       </c>
-      <c r="AC9" s="266" t="s">
+      <c r="AC9" s="265" t="s">
         <v>595</v>
       </c>
       <c r="AD9" s="204"/>
@@ -7841,7 +7845,7 @@
       <c r="AG9" s="204"/>
       <c r="AH9" s="204"/>
       <c r="AI9" s="204"/>
-      <c r="AJ9" s="270" t="s">
+      <c r="AJ9" s="269" t="s">
         <v>509</v>
       </c>
       <c r="AK9" s="228" t="s">
@@ -7855,7 +7859,7 @@
       <c r="AQ9" s="204"/>
       <c r="AR9" s="204"/>
       <c r="AS9" s="204"/>
-      <c r="AT9" s="270" t="s">
+      <c r="AT9" s="269" t="s">
         <v>333</v>
       </c>
       <c r="AU9" s="228" t="s">
@@ -7870,10 +7874,10 @@
       <c r="BB9" s="197" t="s">
         <v>95</v>
       </c>
-      <c r="BC9" s="267" t="s">
+      <c r="BC9" s="266" t="s">
         <v>96</v>
       </c>
-      <c r="BD9" s="270" t="s">
+      <c r="BD9" s="269" t="s">
         <v>307</v>
       </c>
       <c r="BE9" s="222" t="s">
@@ -7891,7 +7895,7 @@
       <c r="BM9" s="197" t="s">
         <v>52</v>
       </c>
-      <c r="BN9" s="426" t="s">
+      <c r="BN9" s="425" t="s">
         <v>279</v>
       </c>
       <c r="BO9" s="224"/>
@@ -7902,24 +7906,24 @@
       </c>
       <c r="B10" s="16"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="352" t="s">
+      <c r="F10" s="351" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="354"/>
-      <c r="H10" s="345"/>
-      <c r="I10" s="346"/>
-      <c r="J10" s="344"/>
-      <c r="K10" s="346"/>
-      <c r="L10" s="345"/>
-      <c r="M10" s="345"/>
+      <c r="G10" s="353"/>
+      <c r="H10" s="344"/>
+      <c r="I10" s="345"/>
+      <c r="J10" s="343"/>
+      <c r="K10" s="345"/>
+      <c r="L10" s="344"/>
+      <c r="M10" s="344"/>
       <c r="N10" s="33"/>
-      <c r="O10" s="418"/>
-      <c r="P10" s="419"/>
-      <c r="Q10" s="419"/>
-      <c r="R10" s="419"/>
-      <c r="S10" s="419"/>
-      <c r="T10" s="419"/>
-      <c r="U10" s="419"/>
+      <c r="O10" s="417"/>
+      <c r="P10" s="418"/>
+      <c r="Q10" s="418"/>
+      <c r="R10" s="418"/>
+      <c r="S10" s="418"/>
+      <c r="T10" s="418"/>
+      <c r="U10" s="418"/>
       <c r="V10" s="34"/>
       <c r="W10" s="14"/>
       <c r="X10" s="14"/>
@@ -7946,7 +7950,7 @@
       </c>
       <c r="AH10" s="203"/>
       <c r="AI10" s="203"/>
-      <c r="AJ10" s="270"/>
+      <c r="AJ10" s="269"/>
       <c r="AK10" s="228"/>
       <c r="AL10" s="203"/>
       <c r="AM10" s="203"/>
@@ -7956,7 +7960,7 @@
       <c r="AQ10" s="203"/>
       <c r="AR10" s="203"/>
       <c r="AS10" s="203"/>
-      <c r="AT10" s="270"/>
+      <c r="AT10" s="269"/>
       <c r="AU10" s="228"/>
       <c r="AV10" s="249"/>
       <c r="AW10" s="196" t="s">
@@ -7973,10 +7977,10 @@
       <c r="BB10" s="196" t="s">
         <v>97</v>
       </c>
-      <c r="BC10" s="268" t="s">
+      <c r="BC10" s="267" t="s">
         <v>98</v>
       </c>
-      <c r="BD10" s="270"/>
+      <c r="BD10" s="269"/>
       <c r="BE10" s="222"/>
       <c r="BF10" s="238" t="s">
         <v>161</v>
@@ -7996,31 +8000,31 @@
       <c r="BM10" s="238" t="s">
         <v>164</v>
       </c>
-      <c r="BN10" s="426"/>
+      <c r="BN10" s="425"/>
       <c r="BO10" s="224"/>
     </row>
     <row r="11" spans="1:67" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6"/>
       <c r="B11" s="18"/>
       <c r="E11" s="30"/>
-      <c r="F11" s="422"/>
-      <c r="G11" s="423"/>
-      <c r="H11" s="345"/>
-      <c r="I11" s="346"/>
-      <c r="J11" s="344"/>
-      <c r="K11" s="346"/>
-      <c r="L11" s="345"/>
-      <c r="M11" s="345"/>
+      <c r="F11" s="421"/>
+      <c r="G11" s="422"/>
+      <c r="H11" s="344"/>
+      <c r="I11" s="345"/>
+      <c r="J11" s="343"/>
+      <c r="K11" s="345"/>
+      <c r="L11" s="344"/>
+      <c r="M11" s="344"/>
       <c r="N11" s="33"/>
-      <c r="O11" s="367" t="s">
+      <c r="O11" s="366" t="s">
         <v>20</v>
       </c>
-      <c r="P11" s="368"/>
-      <c r="Q11" s="368"/>
-      <c r="R11" s="368"/>
-      <c r="S11" s="368"/>
-      <c r="T11" s="368"/>
-      <c r="U11" s="369"/>
+      <c r="P11" s="367"/>
+      <c r="Q11" s="367"/>
+      <c r="R11" s="367"/>
+      <c r="S11" s="367"/>
+      <c r="T11" s="367"/>
+      <c r="U11" s="368"/>
       <c r="V11" s="34"/>
       <c r="W11" s="14"/>
       <c r="X11" s="14"/>
@@ -8030,7 +8034,7 @@
         <v>275</v>
       </c>
       <c r="AB11" s="188"/>
-      <c r="AC11" s="266" t="s">
+      <c r="AC11" s="265" t="s">
         <v>626</v>
       </c>
       <c r="AD11" s="188"/>
@@ -8039,7 +8043,7 @@
       <c r="AG11" s="188"/>
       <c r="AH11" s="188"/>
       <c r="AI11" s="188"/>
-      <c r="AJ11" s="271" t="s">
+      <c r="AJ11" s="270" t="s">
         <v>510</v>
       </c>
       <c r="AK11" s="227" t="s">
@@ -8053,7 +8057,7 @@
       <c r="AQ11" s="188"/>
       <c r="AR11" s="188"/>
       <c r="AS11" s="188"/>
-      <c r="AT11" s="271" t="s">
+      <c r="AT11" s="270" t="s">
         <v>334</v>
       </c>
       <c r="AU11" s="227" t="s">
@@ -8077,7 +8081,7 @@
       <c r="BC11" s="197" t="s">
         <v>167</v>
       </c>
-      <c r="BD11" s="271" t="s">
+      <c r="BD11" s="270" t="s">
         <v>308</v>
       </c>
       <c r="BE11" s="221" t="s">
@@ -8095,33 +8099,33 @@
       <c r="BM11" s="197" t="s">
         <v>180</v>
       </c>
-      <c r="BN11" s="350" t="s">
+      <c r="BN11" s="349" t="s">
         <v>280</v>
       </c>
       <c r="BO11" s="224"/>
     </row>
     <row r="12" spans="1:67" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="376" t="s">
+      <c r="A12" s="375" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="377"/>
+      <c r="B12" s="376"/>
       <c r="E12" s="46"/>
-      <c r="F12" s="424"/>
-      <c r="G12" s="425"/>
-      <c r="H12" s="345"/>
-      <c r="I12" s="346"/>
-      <c r="J12" s="344"/>
-      <c r="K12" s="346"/>
-      <c r="L12" s="345"/>
-      <c r="M12" s="345"/>
+      <c r="F12" s="423"/>
+      <c r="G12" s="424"/>
+      <c r="H12" s="344"/>
+      <c r="I12" s="345"/>
+      <c r="J12" s="343"/>
+      <c r="K12" s="345"/>
+      <c r="L12" s="344"/>
+      <c r="M12" s="344"/>
       <c r="N12" s="33"/>
-      <c r="O12" s="370"/>
-      <c r="P12" s="371"/>
-      <c r="Q12" s="371"/>
-      <c r="R12" s="371"/>
-      <c r="S12" s="371"/>
-      <c r="T12" s="371"/>
-      <c r="U12" s="372"/>
+      <c r="O12" s="369"/>
+      <c r="P12" s="370"/>
+      <c r="Q12" s="370"/>
+      <c r="R12" s="370"/>
+      <c r="S12" s="370"/>
+      <c r="T12" s="370"/>
+      <c r="U12" s="371"/>
       <c r="V12" s="34"/>
       <c r="W12" s="14"/>
       <c r="X12" s="14"/>
@@ -8138,7 +8142,7 @@
       <c r="AG12" s="189"/>
       <c r="AH12" s="189"/>
       <c r="AI12" s="189"/>
-      <c r="AJ12" s="271"/>
+      <c r="AJ12" s="270"/>
       <c r="AK12" s="227"/>
       <c r="AL12" s="189"/>
       <c r="AM12" s="189"/>
@@ -8148,10 +8152,10 @@
       <c r="AQ12" s="189"/>
       <c r="AR12" s="189"/>
       <c r="AS12" s="189"/>
-      <c r="AT12" s="271"/>
+      <c r="AT12" s="270"/>
       <c r="AU12" s="227"/>
       <c r="AV12" s="244" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="AW12" s="211" t="s">
         <v>551</v>
@@ -8172,7 +8176,7 @@
       <c r="BC12" s="196" t="s">
         <v>171</v>
       </c>
-      <c r="BD12" s="271"/>
+      <c r="BD12" s="270"/>
       <c r="BE12" s="221"/>
       <c r="BF12" s="238" t="s">
         <v>50</v>
@@ -8182,7 +8186,7 @@
       </c>
       <c r="BH12" s="189"/>
       <c r="BI12" s="244" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="BJ12" s="211" t="s">
         <v>635</v>
@@ -8196,29 +8200,29 @@
       <c r="BM12" s="238" t="s">
         <v>173</v>
       </c>
-      <c r="BN12" s="350"/>
+      <c r="BN12" s="349"/>
       <c r="BO12" s="224"/>
     </row>
     <row r="13" spans="1:67" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="326"/>
-      <c r="B13" s="378"/>
+      <c r="A13" s="325"/>
+      <c r="B13" s="377"/>
       <c r="E13" s="48"/>
       <c r="F13" s="49"/>
       <c r="G13" s="49"/>
-      <c r="H13" s="344"/>
-      <c r="I13" s="346"/>
-      <c r="J13" s="344"/>
-      <c r="K13" s="346"/>
-      <c r="L13" s="345"/>
-      <c r="M13" s="345"/>
+      <c r="H13" s="343"/>
+      <c r="I13" s="345"/>
+      <c r="J13" s="343"/>
+      <c r="K13" s="345"/>
+      <c r="L13" s="344"/>
+      <c r="M13" s="344"/>
       <c r="N13" s="33"/>
-      <c r="O13" s="370"/>
-      <c r="P13" s="371"/>
-      <c r="Q13" s="371"/>
-      <c r="R13" s="371"/>
-      <c r="S13" s="371"/>
-      <c r="T13" s="371"/>
-      <c r="U13" s="372"/>
+      <c r="O13" s="369"/>
+      <c r="P13" s="370"/>
+      <c r="Q13" s="370"/>
+      <c r="R13" s="370"/>
+      <c r="S13" s="370"/>
+      <c r="T13" s="370"/>
+      <c r="U13" s="371"/>
       <c r="V13" s="34"/>
       <c r="W13" s="14"/>
       <c r="X13" s="14"/>
@@ -8235,7 +8239,7 @@
       <c r="AG13" s="204"/>
       <c r="AH13" s="204"/>
       <c r="AI13" s="204"/>
-      <c r="AJ13" s="270" t="s">
+      <c r="AJ13" s="269" t="s">
         <v>511</v>
       </c>
       <c r="AK13" s="228" t="s">
@@ -8249,7 +8253,7 @@
       <c r="AQ13" s="204"/>
       <c r="AR13" s="204"/>
       <c r="AS13" s="204"/>
-      <c r="AT13" s="270" t="s">
+      <c r="AT13" s="269" t="s">
         <v>335</v>
       </c>
       <c r="AU13" s="228" t="s">
@@ -8265,7 +8269,7 @@
       <c r="BC13" s="197" t="s">
         <v>112</v>
       </c>
-      <c r="BD13" s="270" t="s">
+      <c r="BD13" s="269" t="s">
         <v>309</v>
       </c>
       <c r="BE13" s="222" t="s">
@@ -8283,35 +8287,35 @@
       <c r="BK13" s="204"/>
       <c r="BL13" s="204"/>
       <c r="BM13" s="204"/>
-      <c r="BN13" s="406" t="s">
+      <c r="BN13" s="405" t="s">
         <v>281</v>
       </c>
       <c r="BO13" s="224"/>
     </row>
     <row r="14" spans="1:67" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="333"/>
-      <c r="B14" s="379"/>
+      <c r="A14" s="332"/>
+      <c r="B14" s="378"/>
       <c r="C14" s="50"/>
       <c r="D14" s="42"/>
-      <c r="E14" s="380" t="s">
+      <c r="E14" s="379" t="s">
         <v>22</v>
       </c>
-      <c r="F14" s="380"/>
-      <c r="G14" s="381"/>
-      <c r="H14" s="344"/>
-      <c r="I14" s="346"/>
-      <c r="J14" s="344"/>
-      <c r="K14" s="346"/>
-      <c r="L14" s="345"/>
-      <c r="M14" s="345"/>
+      <c r="F14" s="379"/>
+      <c r="G14" s="380"/>
+      <c r="H14" s="343"/>
+      <c r="I14" s="345"/>
+      <c r="J14" s="343"/>
+      <c r="K14" s="345"/>
+      <c r="L14" s="344"/>
+      <c r="M14" s="344"/>
       <c r="N14" s="33"/>
-      <c r="O14" s="373"/>
-      <c r="P14" s="374"/>
-      <c r="Q14" s="374"/>
-      <c r="R14" s="374"/>
-      <c r="S14" s="374"/>
-      <c r="T14" s="374"/>
-      <c r="U14" s="375"/>
+      <c r="O14" s="372"/>
+      <c r="P14" s="373"/>
+      <c r="Q14" s="373"/>
+      <c r="R14" s="373"/>
+      <c r="S14" s="373"/>
+      <c r="T14" s="373"/>
+      <c r="U14" s="374"/>
       <c r="V14" s="34"/>
       <c r="W14" s="14"/>
       <c r="X14" s="14"/>
@@ -8328,7 +8332,7 @@
       <c r="AG14" s="203"/>
       <c r="AH14" s="203"/>
       <c r="AI14" s="203"/>
-      <c r="AJ14" s="270"/>
+      <c r="AJ14" s="269"/>
       <c r="AK14" s="228"/>
       <c r="AL14" s="203"/>
       <c r="AM14" s="203"/>
@@ -8338,7 +8342,7 @@
       <c r="AQ14" s="203"/>
       <c r="AR14" s="203"/>
       <c r="AS14" s="203"/>
-      <c r="AT14" s="270"/>
+      <c r="AT14" s="269"/>
       <c r="AU14" s="228"/>
       <c r="AV14" s="196" t="s">
         <v>168</v>
@@ -8360,7 +8364,7 @@
       <c r="BC14" s="196" t="s">
         <v>101</v>
       </c>
-      <c r="BD14" s="270"/>
+      <c r="BD14" s="269"/>
       <c r="BE14" s="222"/>
       <c r="BF14" s="196" t="s">
         <v>175</v>
@@ -8380,33 +8384,33 @@
         <v>395</v>
       </c>
       <c r="BM14" s="203"/>
-      <c r="BN14" s="406"/>
+      <c r="BN14" s="405"/>
       <c r="BO14" s="224"/>
     </row>
     <row r="15" spans="1:67" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="376" t="s">
+      <c r="A15" s="375" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="384"/>
+      <c r="B15" s="383"/>
       <c r="C15" s="50"/>
       <c r="D15" s="52"/>
-      <c r="E15" s="382"/>
-      <c r="F15" s="382"/>
-      <c r="G15" s="383"/>
-      <c r="H15" s="344"/>
-      <c r="I15" s="346"/>
-      <c r="J15" s="344"/>
-      <c r="K15" s="346"/>
-      <c r="L15" s="345"/>
-      <c r="M15" s="345"/>
+      <c r="E15" s="381"/>
+      <c r="F15" s="381"/>
+      <c r="G15" s="382"/>
+      <c r="H15" s="343"/>
+      <c r="I15" s="345"/>
+      <c r="J15" s="343"/>
+      <c r="K15" s="345"/>
+      <c r="L15" s="344"/>
+      <c r="M15" s="344"/>
       <c r="N15" s="33"/>
-      <c r="O15" s="386"/>
-      <c r="P15" s="387"/>
-      <c r="Q15" s="387"/>
-      <c r="R15" s="387"/>
-      <c r="S15" s="387"/>
-      <c r="T15" s="387"/>
-      <c r="U15" s="388"/>
+      <c r="O15" s="385"/>
+      <c r="P15" s="386"/>
+      <c r="Q15" s="386"/>
+      <c r="R15" s="386"/>
+      <c r="S15" s="386"/>
+      <c r="T15" s="386"/>
+      <c r="U15" s="387"/>
       <c r="V15" s="27"/>
       <c r="W15" s="28"/>
       <c r="X15" s="28"/>
@@ -8423,7 +8427,7 @@
       <c r="AG15" s="188"/>
       <c r="AH15" s="188"/>
       <c r="AI15" s="188"/>
-      <c r="AJ15" s="271" t="s">
+      <c r="AJ15" s="270" t="s">
         <v>512</v>
       </c>
       <c r="AK15" s="227" t="s">
@@ -8437,7 +8441,7 @@
       <c r="AQ15" s="188"/>
       <c r="AR15" s="188"/>
       <c r="AS15" s="188"/>
-      <c r="AT15" s="271" t="s">
+      <c r="AT15" s="270" t="s">
         <v>336</v>
       </c>
       <c r="AU15" s="227" t="s">
@@ -8453,7 +8457,7 @@
       <c r="BC15" s="210" t="s">
         <v>181</v>
       </c>
-      <c r="BD15" s="271" t="s">
+      <c r="BD15" s="270" t="s">
         <v>310</v>
       </c>
       <c r="BE15" s="221" t="s">
@@ -8469,35 +8473,35 @@
       <c r="BK15" s="188"/>
       <c r="BL15" s="188"/>
       <c r="BM15" s="188"/>
-      <c r="BN15" s="350" t="s">
+      <c r="BN15" s="349" t="s">
         <v>282</v>
       </c>
       <c r="BO15" s="224"/>
     </row>
     <row r="16" spans="1:67" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="326"/>
-      <c r="B16" s="385"/>
+      <c r="A16" s="325"/>
+      <c r="B16" s="384"/>
       <c r="C16" s="53"/>
       <c r="D16" s="52"/>
-      <c r="E16" s="380" t="s">
+      <c r="E16" s="379" t="s">
         <v>22</v>
       </c>
-      <c r="F16" s="380"/>
-      <c r="G16" s="381"/>
-      <c r="H16" s="344"/>
-      <c r="I16" s="346"/>
-      <c r="J16" s="344"/>
-      <c r="K16" s="346"/>
-      <c r="L16" s="345"/>
-      <c r="M16" s="345"/>
+      <c r="F16" s="379"/>
+      <c r="G16" s="380"/>
+      <c r="H16" s="343"/>
+      <c r="I16" s="345"/>
+      <c r="J16" s="343"/>
+      <c r="K16" s="345"/>
+      <c r="L16" s="344"/>
+      <c r="M16" s="344"/>
       <c r="N16" s="33"/>
-      <c r="O16" s="389"/>
-      <c r="P16" s="390"/>
-      <c r="Q16" s="390"/>
-      <c r="R16" s="390"/>
-      <c r="S16" s="390"/>
-      <c r="T16" s="390"/>
-      <c r="U16" s="391"/>
+      <c r="O16" s="388"/>
+      <c r="P16" s="389"/>
+      <c r="Q16" s="389"/>
+      <c r="R16" s="389"/>
+      <c r="S16" s="389"/>
+      <c r="T16" s="389"/>
+      <c r="U16" s="390"/>
       <c r="V16" s="34"/>
       <c r="W16" s="14"/>
       <c r="X16" s="40"/>
@@ -8512,7 +8516,7 @@
       <c r="AG16" s="189"/>
       <c r="AH16" s="189"/>
       <c r="AI16" s="189"/>
-      <c r="AJ16" s="271"/>
+      <c r="AJ16" s="270"/>
       <c r="AK16" s="227"/>
       <c r="AL16" s="189"/>
       <c r="AM16" s="189"/>
@@ -8522,7 +8526,7 @@
       <c r="AQ16" s="189"/>
       <c r="AR16" s="189"/>
       <c r="AS16" s="189"/>
-      <c r="AT16" s="271"/>
+      <c r="AT16" s="270"/>
       <c r="AU16" s="227"/>
       <c r="AV16" s="235" t="s">
         <v>556</v>
@@ -8541,18 +8545,18 @@
         <v>105</v>
       </c>
       <c r="BB16" s="244" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="BC16" s="235" t="s">
         <v>106</v>
       </c>
-      <c r="BD16" s="271"/>
+      <c r="BD16" s="270"/>
       <c r="BE16" s="221"/>
       <c r="BF16" s="196" t="s">
         <v>53</v>
       </c>
       <c r="BG16" s="243" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="BH16" s="189"/>
       <c r="BI16" s="235" t="s">
@@ -8566,31 +8570,31 @@
         <v>396</v>
       </c>
       <c r="BM16" s="189"/>
-      <c r="BN16" s="350"/>
+      <c r="BN16" s="349"/>
       <c r="BO16" s="224"/>
     </row>
     <row r="17" spans="1:70" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="333"/>
-      <c r="B17" s="379"/>
+      <c r="A17" s="332"/>
+      <c r="B17" s="378"/>
       <c r="C17" s="50"/>
       <c r="D17" s="55"/>
-      <c r="E17" s="395"/>
-      <c r="F17" s="395"/>
-      <c r="G17" s="396"/>
-      <c r="H17" s="344"/>
-      <c r="I17" s="346"/>
-      <c r="J17" s="344"/>
-      <c r="K17" s="346"/>
-      <c r="L17" s="345"/>
-      <c r="M17" s="345"/>
+      <c r="E17" s="394"/>
+      <c r="F17" s="394"/>
+      <c r="G17" s="395"/>
+      <c r="H17" s="343"/>
+      <c r="I17" s="345"/>
+      <c r="J17" s="343"/>
+      <c r="K17" s="345"/>
+      <c r="L17" s="344"/>
+      <c r="M17" s="344"/>
       <c r="N17" s="33"/>
-      <c r="O17" s="389"/>
-      <c r="P17" s="390"/>
-      <c r="Q17" s="390"/>
-      <c r="R17" s="390"/>
-      <c r="S17" s="390"/>
-      <c r="T17" s="390"/>
-      <c r="U17" s="391"/>
+      <c r="O17" s="388"/>
+      <c r="P17" s="389"/>
+      <c r="Q17" s="389"/>
+      <c r="R17" s="389"/>
+      <c r="S17" s="389"/>
+      <c r="T17" s="389"/>
+      <c r="U17" s="390"/>
       <c r="V17" s="47"/>
       <c r="W17" s="44"/>
       <c r="X17" s="44"/>
@@ -8607,7 +8611,7 @@
       <c r="AG17" s="204"/>
       <c r="AH17" s="204"/>
       <c r="AI17" s="204"/>
-      <c r="AJ17" s="270" t="s">
+      <c r="AJ17" s="269" t="s">
         <v>513</v>
       </c>
       <c r="AK17" s="228" t="s">
@@ -8621,7 +8625,7 @@
       <c r="AQ17" s="204"/>
       <c r="AR17" s="204"/>
       <c r="AS17" s="204"/>
-      <c r="AT17" s="270" t="s">
+      <c r="AT17" s="269" t="s">
         <v>337</v>
       </c>
       <c r="AU17" s="228" t="s">
@@ -8641,7 +8645,7 @@
       </c>
       <c r="BB17" s="248"/>
       <c r="BC17" s="204"/>
-      <c r="BD17" s="270" t="s">
+      <c r="BD17" s="269" t="s">
         <v>311</v>
       </c>
       <c r="BE17" s="222" t="s">
@@ -8661,37 +8665,37 @@
         <v>179</v>
       </c>
       <c r="BM17" s="245" t="s">
-        <v>662</v>
-      </c>
-      <c r="BN17" s="406" t="s">
+        <v>661</v>
+      </c>
+      <c r="BN17" s="405" t="s">
         <v>283</v>
       </c>
       <c r="BO17" s="224"/>
     </row>
     <row r="18" spans="1:70" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="376" t="s">
+      <c r="A18" s="375" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="377"/>
+      <c r="B18" s="376"/>
       <c r="C18" s="19"/>
       <c r="D18" s="19"/>
-      <c r="E18" s="397"/>
-      <c r="F18" s="395"/>
-      <c r="G18" s="396"/>
-      <c r="H18" s="344"/>
-      <c r="I18" s="346"/>
-      <c r="J18" s="344"/>
-      <c r="K18" s="346"/>
-      <c r="L18" s="345"/>
-      <c r="M18" s="345"/>
+      <c r="E18" s="396"/>
+      <c r="F18" s="394"/>
+      <c r="G18" s="395"/>
+      <c r="H18" s="343"/>
+      <c r="I18" s="345"/>
+      <c r="J18" s="343"/>
+      <c r="K18" s="345"/>
+      <c r="L18" s="344"/>
+      <c r="M18" s="344"/>
       <c r="N18" s="33"/>
-      <c r="O18" s="392"/>
-      <c r="P18" s="393"/>
-      <c r="Q18" s="393"/>
-      <c r="R18" s="393"/>
-      <c r="S18" s="393"/>
-      <c r="T18" s="393"/>
-      <c r="U18" s="394"/>
+      <c r="O18" s="391"/>
+      <c r="P18" s="392"/>
+      <c r="Q18" s="392"/>
+      <c r="R18" s="392"/>
+      <c r="S18" s="392"/>
+      <c r="T18" s="392"/>
+      <c r="U18" s="393"/>
       <c r="V18" s="47"/>
       <c r="Z18" s="42"/>
       <c r="AA18" s="228"/>
@@ -8705,7 +8709,7 @@
       <c r="AG18" s="203"/>
       <c r="AH18" s="203"/>
       <c r="AI18" s="203"/>
-      <c r="AJ18" s="270"/>
+      <c r="AJ18" s="269"/>
       <c r="AK18" s="228"/>
       <c r="AL18" s="203"/>
       <c r="AM18" s="203"/>
@@ -8715,7 +8719,7 @@
       <c r="AQ18" s="203"/>
       <c r="AR18" s="203"/>
       <c r="AS18" s="203"/>
-      <c r="AT18" s="270"/>
+      <c r="AT18" s="269"/>
       <c r="AU18" s="228"/>
       <c r="AV18" s="211" t="s">
         <v>554</v>
@@ -8739,7 +8743,7 @@
       <c r="BC18" s="235" t="s">
         <v>107</v>
       </c>
-      <c r="BD18" s="270"/>
+      <c r="BD18" s="269"/>
       <c r="BE18" s="222"/>
       <c r="BF18" s="235" t="s">
         <v>406</v>
@@ -8748,7 +8752,9 @@
         <v>413</v>
       </c>
       <c r="BH18" s="203"/>
-      <c r="BI18" s="203"/>
+      <c r="BI18" s="244" t="s">
+        <v>672</v>
+      </c>
       <c r="BJ18" s="235" t="s">
         <v>405</v>
       </c>
@@ -8759,35 +8765,35 @@
         <v>55</v>
       </c>
       <c r="BM18" s="244" t="s">
-        <v>661</v>
-      </c>
-      <c r="BN18" s="406"/>
+        <v>660</v>
+      </c>
+      <c r="BN18" s="405"/>
       <c r="BO18" s="224"/>
     </row>
     <row r="19" spans="1:70" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="326"/>
-      <c r="B19" s="378"/>
+      <c r="A19" s="325"/>
+      <c r="B19" s="377"/>
       <c r="C19" s="19"/>
       <c r="D19" s="56"/>
       <c r="E19" s="57"/>
       <c r="F19" s="58"/>
       <c r="G19" s="58"/>
-      <c r="H19" s="344"/>
-      <c r="I19" s="346"/>
-      <c r="J19" s="344"/>
-      <c r="K19" s="346"/>
-      <c r="L19" s="345"/>
-      <c r="M19" s="345"/>
+      <c r="H19" s="343"/>
+      <c r="I19" s="345"/>
+      <c r="J19" s="343"/>
+      <c r="K19" s="345"/>
+      <c r="L19" s="344"/>
+      <c r="M19" s="344"/>
       <c r="N19" s="33"/>
-      <c r="O19" s="398" t="s">
+      <c r="O19" s="397" t="s">
         <v>25</v>
       </c>
-      <c r="P19" s="399"/>
-      <c r="Q19" s="399"/>
-      <c r="R19" s="399"/>
-      <c r="S19" s="399"/>
-      <c r="T19" s="399"/>
-      <c r="U19" s="400"/>
+      <c r="P19" s="398"/>
+      <c r="Q19" s="398"/>
+      <c r="R19" s="398"/>
+      <c r="S19" s="398"/>
+      <c r="T19" s="398"/>
+      <c r="U19" s="399"/>
       <c r="Z19" s="42"/>
       <c r="AA19" s="227" t="s">
         <v>275</v>
@@ -8800,7 +8806,7 @@
       <c r="AG19" s="188"/>
       <c r="AH19" s="188"/>
       <c r="AI19" s="188"/>
-      <c r="AJ19" s="271" t="s">
+      <c r="AJ19" s="270" t="s">
         <v>514</v>
       </c>
       <c r="AK19" s="227" t="s">
@@ -8814,7 +8820,7 @@
       <c r="AQ19" s="188"/>
       <c r="AR19" s="188"/>
       <c r="AS19" s="188"/>
-      <c r="AT19" s="271" t="s">
+      <c r="AT19" s="270" t="s">
         <v>338</v>
       </c>
       <c r="AU19" s="227" t="s">
@@ -8836,7 +8842,7 @@
       <c r="BC19" s="246" t="s">
         <v>188</v>
       </c>
-      <c r="BD19" s="271" t="s">
+      <c r="BD19" s="270" t="s">
         <v>312</v>
       </c>
       <c r="BE19" s="221" t="s">
@@ -8852,33 +8858,33 @@
       <c r="BM19" s="197" t="s">
         <v>57</v>
       </c>
-      <c r="BN19" s="350" t="s">
+      <c r="BN19" s="349" t="s">
         <v>284</v>
       </c>
       <c r="BO19" s="224"/>
     </row>
     <row r="20" spans="1:70" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="333"/>
-      <c r="B20" s="334"/>
-      <c r="E20" s="404" t="s">
+      <c r="A20" s="332"/>
+      <c r="B20" s="333"/>
+      <c r="E20" s="403" t="s">
         <v>26</v>
       </c>
-      <c r="F20" s="380"/>
-      <c r="G20" s="381"/>
-      <c r="H20" s="344"/>
-      <c r="I20" s="346"/>
-      <c r="J20" s="344"/>
-      <c r="K20" s="346"/>
-      <c r="L20" s="345"/>
-      <c r="M20" s="345"/>
+      <c r="F20" s="379"/>
+      <c r="G20" s="380"/>
+      <c r="H20" s="343"/>
+      <c r="I20" s="345"/>
+      <c r="J20" s="343"/>
+      <c r="K20" s="345"/>
+      <c r="L20" s="344"/>
+      <c r="M20" s="344"/>
       <c r="N20" s="33"/>
-      <c r="O20" s="401"/>
-      <c r="P20" s="402"/>
-      <c r="Q20" s="402"/>
-      <c r="R20" s="402"/>
-      <c r="S20" s="402"/>
-      <c r="T20" s="402"/>
-      <c r="U20" s="403"/>
+      <c r="O20" s="400"/>
+      <c r="P20" s="401"/>
+      <c r="Q20" s="401"/>
+      <c r="R20" s="401"/>
+      <c r="S20" s="401"/>
+      <c r="T20" s="401"/>
+      <c r="U20" s="402"/>
       <c r="V20" s="59"/>
       <c r="X20" s="41"/>
       <c r="Z20" s="42"/>
@@ -8893,7 +8899,7 @@
       <c r="AG20" s="189"/>
       <c r="AH20" s="189"/>
       <c r="AI20" s="189"/>
-      <c r="AJ20" s="271"/>
+      <c r="AJ20" s="270"/>
       <c r="AK20" s="227"/>
       <c r="AL20" s="189"/>
       <c r="AM20" s="189"/>
@@ -8903,7 +8909,7 @@
       <c r="AQ20" s="189"/>
       <c r="AR20" s="189"/>
       <c r="AS20" s="189"/>
-      <c r="AT20" s="271"/>
+      <c r="AT20" s="270"/>
       <c r="AU20" s="227"/>
       <c r="AV20" s="235" t="s">
         <v>186</v>
@@ -8927,7 +8933,7 @@
       <c r="BC20" s="235" t="s">
         <v>189</v>
       </c>
-      <c r="BD20" s="271"/>
+      <c r="BD20" s="270"/>
       <c r="BE20" s="221"/>
       <c r="BF20" s="196" t="s">
         <v>56</v>
@@ -8939,10 +8945,10 @@
         <v>615</v>
       </c>
       <c r="BJ20" s="244" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="BK20" s="235" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="BL20" s="238" t="s">
         <v>190</v>
@@ -8950,29 +8956,29 @@
       <c r="BM20" s="238" t="s">
         <v>58</v>
       </c>
-      <c r="BN20" s="350"/>
+      <c r="BN20" s="349"/>
       <c r="BO20" s="224"/>
     </row>
     <row r="21" spans="1:70" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="40"/>
       <c r="B21" s="40"/>
-      <c r="E21" s="397"/>
-      <c r="F21" s="395"/>
-      <c r="G21" s="396"/>
-      <c r="H21" s="344"/>
-      <c r="I21" s="346"/>
-      <c r="J21" s="344"/>
-      <c r="K21" s="346"/>
-      <c r="L21" s="345"/>
-      <c r="M21" s="345"/>
+      <c r="E21" s="396"/>
+      <c r="F21" s="394"/>
+      <c r="G21" s="395"/>
+      <c r="H21" s="343"/>
+      <c r="I21" s="345"/>
+      <c r="J21" s="343"/>
+      <c r="K21" s="345"/>
+      <c r="L21" s="344"/>
+      <c r="M21" s="344"/>
       <c r="N21" s="33"/>
-      <c r="O21" s="401"/>
-      <c r="P21" s="402"/>
-      <c r="Q21" s="402"/>
-      <c r="R21" s="402"/>
-      <c r="S21" s="402"/>
-      <c r="T21" s="402"/>
-      <c r="U21" s="403"/>
+      <c r="O21" s="400"/>
+      <c r="P21" s="401"/>
+      <c r="Q21" s="401"/>
+      <c r="R21" s="401"/>
+      <c r="S21" s="401"/>
+      <c r="T21" s="401"/>
+      <c r="U21" s="402"/>
       <c r="V21" s="37"/>
       <c r="W21" s="60"/>
       <c r="X21" s="41"/>
@@ -8988,7 +8994,7 @@
       <c r="AG21" s="204"/>
       <c r="AH21" s="204"/>
       <c r="AI21" s="204"/>
-      <c r="AJ21" s="270" t="s">
+      <c r="AJ21" s="269" t="s">
         <v>515</v>
       </c>
       <c r="AK21" s="228" t="s">
@@ -9002,7 +9008,7 @@
       <c r="AQ21" s="204"/>
       <c r="AR21" s="204"/>
       <c r="AS21" s="204"/>
-      <c r="AT21" s="270" t="s">
+      <c r="AT21" s="269" t="s">
         <v>339</v>
       </c>
       <c r="AU21" s="228" t="s">
@@ -9018,7 +9024,7 @@
       <c r="BA21" s="204"/>
       <c r="BB21" s="204"/>
       <c r="BC21" s="204"/>
-      <c r="BD21" s="270" t="s">
+      <c r="BD21" s="269" t="s">
         <v>313</v>
       </c>
       <c r="BE21" s="222" t="s">
@@ -9029,14 +9035,14 @@
       <c r="BH21" s="204"/>
       <c r="BI21" s="204"/>
       <c r="BJ21" s="245" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="BK21" s="204"/>
       <c r="BL21" s="204"/>
       <c r="BM21" s="197" t="s">
         <v>103</v>
       </c>
-      <c r="BN21" s="406" t="s">
+      <c r="BN21" s="405" t="s">
         <v>285</v>
       </c>
       <c r="BO21" s="224"/>
@@ -9044,23 +9050,23 @@
     <row r="22" spans="1:70" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="40"/>
       <c r="B22" s="40"/>
-      <c r="E22" s="397"/>
-      <c r="F22" s="395"/>
-      <c r="G22" s="396"/>
-      <c r="H22" s="344"/>
-      <c r="I22" s="346"/>
-      <c r="J22" s="344"/>
-      <c r="K22" s="346"/>
-      <c r="L22" s="345"/>
-      <c r="M22" s="345"/>
+      <c r="E22" s="396"/>
+      <c r="F22" s="394"/>
+      <c r="G22" s="395"/>
+      <c r="H22" s="343"/>
+      <c r="I22" s="345"/>
+      <c r="J22" s="343"/>
+      <c r="K22" s="345"/>
+      <c r="L22" s="344"/>
+      <c r="M22" s="344"/>
       <c r="N22" s="33"/>
-      <c r="O22" s="401"/>
-      <c r="P22" s="402"/>
-      <c r="Q22" s="402"/>
-      <c r="R22" s="402"/>
-      <c r="S22" s="402"/>
-      <c r="T22" s="402"/>
-      <c r="U22" s="403"/>
+      <c r="O22" s="400"/>
+      <c r="P22" s="401"/>
+      <c r="Q22" s="401"/>
+      <c r="R22" s="401"/>
+      <c r="S22" s="401"/>
+      <c r="T22" s="401"/>
+      <c r="U22" s="402"/>
       <c r="V22" s="45"/>
       <c r="X22" s="9"/>
       <c r="Y22" s="23"/>
@@ -9074,7 +9080,7 @@
       <c r="AG22" s="203"/>
       <c r="AH22" s="203"/>
       <c r="AI22" s="203"/>
-      <c r="AJ22" s="270"/>
+      <c r="AJ22" s="269"/>
       <c r="AK22" s="228"/>
       <c r="AL22" s="203"/>
       <c r="AM22" s="203"/>
@@ -9084,13 +9090,13 @@
       <c r="AQ22" s="203"/>
       <c r="AR22" s="203"/>
       <c r="AS22" s="203"/>
-      <c r="AT22" s="270"/>
+      <c r="AT22" s="269"/>
       <c r="AU22" s="228"/>
       <c r="AV22" s="235" t="s">
         <v>400</v>
       </c>
       <c r="AW22" s="244" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="AX22" s="203"/>
       <c r="AY22" s="196" t="s">
@@ -9106,9 +9112,9 @@
         <v>558</v>
       </c>
       <c r="BC22" s="244" t="s">
-        <v>641</v>
-      </c>
-      <c r="BD22" s="270"/>
+        <v>640</v>
+      </c>
+      <c r="BD22" s="269"/>
       <c r="BE22" s="222"/>
       <c r="BF22" s="196" t="s">
         <v>59</v>
@@ -9121,36 +9127,36 @@
         <v>616</v>
       </c>
       <c r="BJ22" s="244" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="BK22" s="203"/>
       <c r="BL22" s="203"/>
       <c r="BM22" s="196" t="s">
         <v>193</v>
       </c>
-      <c r="BN22" s="406"/>
+      <c r="BN22" s="405"/>
       <c r="BO22" s="224"/>
     </row>
     <row r="23" spans="1:70" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="40"/>
       <c r="B23" s="40"/>
-      <c r="E23" s="397"/>
-      <c r="F23" s="395"/>
-      <c r="G23" s="396"/>
-      <c r="H23" s="344"/>
-      <c r="I23" s="346"/>
-      <c r="J23" s="344"/>
-      <c r="K23" s="346"/>
-      <c r="L23" s="345"/>
-      <c r="M23" s="345"/>
+      <c r="E23" s="396"/>
+      <c r="F23" s="394"/>
+      <c r="G23" s="395"/>
+      <c r="H23" s="343"/>
+      <c r="I23" s="345"/>
+      <c r="J23" s="343"/>
+      <c r="K23" s="345"/>
+      <c r="L23" s="344"/>
+      <c r="M23" s="344"/>
       <c r="N23" s="33"/>
-      <c r="O23" s="401"/>
-      <c r="P23" s="402"/>
-      <c r="Q23" s="402"/>
-      <c r="R23" s="402"/>
-      <c r="S23" s="402"/>
-      <c r="T23" s="402"/>
-      <c r="U23" s="403"/>
+      <c r="O23" s="400"/>
+      <c r="P23" s="401"/>
+      <c r="Q23" s="401"/>
+      <c r="R23" s="401"/>
+      <c r="S23" s="401"/>
+      <c r="T23" s="401"/>
+      <c r="U23" s="402"/>
       <c r="V23" s="61"/>
       <c r="Z23" s="42"/>
       <c r="AA23" s="227" t="s">
@@ -9164,7 +9170,7 @@
       <c r="AG23" s="188"/>
       <c r="AH23" s="188"/>
       <c r="AI23" s="188"/>
-      <c r="AJ23" s="271" t="s">
+      <c r="AJ23" s="270" t="s">
         <v>516</v>
       </c>
       <c r="AK23" s="227" t="s">
@@ -9178,7 +9184,7 @@
       <c r="AQ23" s="188"/>
       <c r="AR23" s="188"/>
       <c r="AS23" s="188"/>
-      <c r="AT23" s="271" t="s">
+      <c r="AT23" s="270" t="s">
         <v>340</v>
       </c>
       <c r="AU23" s="227" t="s">
@@ -9200,7 +9206,7 @@
       <c r="BC23" s="210" t="s">
         <v>116</v>
       </c>
-      <c r="BD23" s="271" t="s">
+      <c r="BD23" s="270" t="s">
         <v>314</v>
       </c>
       <c r="BE23" s="221" t="s">
@@ -9217,9 +9223,9 @@
       </c>
       <c r="BL23" s="188"/>
       <c r="BM23" s="245" t="s">
-        <v>658</v>
-      </c>
-      <c r="BN23" s="350" t="s">
+        <v>657</v>
+      </c>
+      <c r="BN23" s="349" t="s">
         <v>286</v>
       </c>
       <c r="BO23" s="224"/>
@@ -9227,23 +9233,23 @@
     <row r="24" spans="1:70" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="40"/>
       <c r="B24" s="40"/>
-      <c r="E24" s="405"/>
-      <c r="F24" s="382"/>
-      <c r="G24" s="383"/>
-      <c r="H24" s="344"/>
-      <c r="I24" s="346"/>
-      <c r="J24" s="344"/>
-      <c r="K24" s="346"/>
-      <c r="L24" s="345"/>
-      <c r="M24" s="345"/>
+      <c r="E24" s="404"/>
+      <c r="F24" s="381"/>
+      <c r="G24" s="382"/>
+      <c r="H24" s="343"/>
+      <c r="I24" s="345"/>
+      <c r="J24" s="343"/>
+      <c r="K24" s="345"/>
+      <c r="L24" s="344"/>
+      <c r="M24" s="344"/>
       <c r="N24" s="33"/>
-      <c r="O24" s="401"/>
-      <c r="P24" s="402"/>
-      <c r="Q24" s="402"/>
-      <c r="R24" s="402"/>
-      <c r="S24" s="402"/>
-      <c r="T24" s="402"/>
-      <c r="U24" s="403"/>
+      <c r="O24" s="400"/>
+      <c r="P24" s="401"/>
+      <c r="Q24" s="401"/>
+      <c r="R24" s="401"/>
+      <c r="S24" s="401"/>
+      <c r="T24" s="401"/>
+      <c r="U24" s="402"/>
       <c r="V24" s="61"/>
       <c r="Z24" s="42"/>
       <c r="AA24" s="227"/>
@@ -9255,7 +9261,7 @@
       <c r="AG24" s="189"/>
       <c r="AH24" s="189"/>
       <c r="AI24" s="189"/>
-      <c r="AJ24" s="271"/>
+      <c r="AJ24" s="270"/>
       <c r="AK24" s="227"/>
       <c r="AL24" s="189"/>
       <c r="AM24" s="189"/>
@@ -9265,7 +9271,7 @@
       <c r="AQ24" s="189"/>
       <c r="AR24" s="189"/>
       <c r="AS24" s="189"/>
-      <c r="AT24" s="271"/>
+      <c r="AT24" s="270"/>
       <c r="AU24" s="227"/>
       <c r="AV24" s="238" t="s">
         <v>194</v>
@@ -9289,7 +9295,7 @@
       <c r="BC24" s="235" t="s">
         <v>412</v>
       </c>
-      <c r="BD24" s="271"/>
+      <c r="BD24" s="270"/>
       <c r="BE24" s="227"/>
       <c r="BF24" s="189"/>
       <c r="BG24" s="235" t="s">
@@ -9309,33 +9315,33 @@
         <v>618</v>
       </c>
       <c r="BM24" s="244" t="s">
-        <v>651</v>
-      </c>
-      <c r="BN24" s="350"/>
+        <v>650</v>
+      </c>
+      <c r="BN24" s="349"/>
       <c r="BO24" s="224"/>
     </row>
     <row r="25" spans="1:70" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="40"/>
       <c r="B25" s="40"/>
-      <c r="E25" s="397" t="s">
+      <c r="E25" s="396" t="s">
         <v>27</v>
       </c>
-      <c r="F25" s="395"/>
-      <c r="G25" s="396"/>
-      <c r="H25" s="344"/>
-      <c r="I25" s="346"/>
-      <c r="J25" s="344"/>
-      <c r="K25" s="346"/>
-      <c r="L25" s="345"/>
-      <c r="M25" s="345"/>
+      <c r="F25" s="394"/>
+      <c r="G25" s="395"/>
+      <c r="H25" s="343"/>
+      <c r="I25" s="345"/>
+      <c r="J25" s="343"/>
+      <c r="K25" s="345"/>
+      <c r="L25" s="344"/>
+      <c r="M25" s="344"/>
       <c r="N25" s="33"/>
-      <c r="O25" s="401"/>
-      <c r="P25" s="402"/>
-      <c r="Q25" s="402"/>
-      <c r="R25" s="402"/>
-      <c r="S25" s="402"/>
-      <c r="T25" s="402"/>
-      <c r="U25" s="403"/>
+      <c r="O25" s="400"/>
+      <c r="P25" s="401"/>
+      <c r="Q25" s="401"/>
+      <c r="R25" s="401"/>
+      <c r="S25" s="401"/>
+      <c r="T25" s="401"/>
+      <c r="U25" s="402"/>
       <c r="V25" s="61"/>
       <c r="W25" s="38"/>
       <c r="X25" s="9"/>
@@ -9352,7 +9358,7 @@
       <c r="AG25" s="204"/>
       <c r="AH25" s="204"/>
       <c r="AI25" s="204"/>
-      <c r="AJ25" s="270" t="s">
+      <c r="AJ25" s="269" t="s">
         <v>517</v>
       </c>
       <c r="AK25" s="228" t="s">
@@ -9366,7 +9372,7 @@
       <c r="AQ25" s="204"/>
       <c r="AR25" s="204"/>
       <c r="AS25" s="204"/>
-      <c r="AT25" s="270" t="s">
+      <c r="AT25" s="269" t="s">
         <v>341</v>
       </c>
       <c r="AU25" s="228" t="s">
@@ -9382,7 +9388,7 @@
       <c r="BC25" s="236" t="s">
         <v>382</v>
       </c>
-      <c r="BD25" s="270" t="s">
+      <c r="BD25" s="269" t="s">
         <v>315</v>
       </c>
       <c r="BE25" s="222" t="s">
@@ -9392,13 +9398,13 @@
       <c r="BG25" s="204"/>
       <c r="BH25" s="204"/>
       <c r="BI25" s="204"/>
-      <c r="BJ25" s="267" t="s">
+      <c r="BJ25" s="266" t="s">
         <v>200</v>
       </c>
       <c r="BK25" s="204"/>
       <c r="BL25" s="204"/>
       <c r="BM25" s="204"/>
-      <c r="BN25" s="406" t="s">
+      <c r="BN25" s="405" t="s">
         <v>287</v>
       </c>
       <c r="BO25" s="224"/>
@@ -9406,23 +9412,23 @@
     <row r="26" spans="1:70" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="40"/>
       <c r="B26" s="40"/>
-      <c r="E26" s="397"/>
-      <c r="F26" s="395"/>
-      <c r="G26" s="396"/>
-      <c r="H26" s="344"/>
-      <c r="I26" s="346"/>
-      <c r="J26" s="344"/>
-      <c r="K26" s="346"/>
-      <c r="L26" s="345"/>
-      <c r="M26" s="345"/>
+      <c r="E26" s="396"/>
+      <c r="F26" s="394"/>
+      <c r="G26" s="395"/>
+      <c r="H26" s="343"/>
+      <c r="I26" s="345"/>
+      <c r="J26" s="343"/>
+      <c r="K26" s="345"/>
+      <c r="L26" s="344"/>
+      <c r="M26" s="344"/>
       <c r="N26" s="33"/>
-      <c r="O26" s="401"/>
-      <c r="P26" s="402"/>
-      <c r="Q26" s="402"/>
-      <c r="R26" s="402"/>
-      <c r="S26" s="402"/>
-      <c r="T26" s="402"/>
-      <c r="U26" s="403"/>
+      <c r="O26" s="400"/>
+      <c r="P26" s="401"/>
+      <c r="Q26" s="401"/>
+      <c r="R26" s="401"/>
+      <c r="S26" s="401"/>
+      <c r="T26" s="401"/>
+      <c r="U26" s="402"/>
       <c r="V26" s="62"/>
       <c r="W26" s="38"/>
       <c r="X26" s="9"/>
@@ -9437,7 +9443,7 @@
       <c r="AG26" s="203"/>
       <c r="AH26" s="203"/>
       <c r="AI26" s="203"/>
-      <c r="AJ26" s="270"/>
+      <c r="AJ26" s="269"/>
       <c r="AK26" s="228"/>
       <c r="AL26" s="203"/>
       <c r="AM26" s="203"/>
@@ -9449,7 +9455,7 @@
       <c r="AS26" s="211" t="s">
         <v>468</v>
       </c>
-      <c r="AT26" s="270"/>
+      <c r="AT26" s="269"/>
       <c r="AU26" s="228"/>
       <c r="AV26" s="211" t="s">
         <v>423</v>
@@ -9473,7 +9479,7 @@
       <c r="BC26" s="235" t="s">
         <v>117</v>
       </c>
-      <c r="BD26" s="270"/>
+      <c r="BD26" s="269"/>
       <c r="BE26" s="222"/>
       <c r="BF26" s="196" t="s">
         <v>65</v>
@@ -9490,32 +9496,32 @@
       </c>
       <c r="BK26" s="203"/>
       <c r="BL26" s="244" t="s">
-        <v>668</v>
+        <v>627</v>
       </c>
       <c r="BM26" s="203"/>
-      <c r="BN26" s="406"/>
+      <c r="BN26" s="405"/>
       <c r="BO26" s="224"/>
     </row>
     <row r="27" spans="1:70" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="40"/>
       <c r="B27" s="40"/>
-      <c r="E27" s="397"/>
-      <c r="F27" s="395"/>
-      <c r="G27" s="396"/>
-      <c r="H27" s="344"/>
-      <c r="I27" s="346"/>
-      <c r="J27" s="344"/>
-      <c r="K27" s="346"/>
-      <c r="L27" s="345"/>
-      <c r="M27" s="345"/>
+      <c r="E27" s="396"/>
+      <c r="F27" s="394"/>
+      <c r="G27" s="395"/>
+      <c r="H27" s="343"/>
+      <c r="I27" s="345"/>
+      <c r="J27" s="343"/>
+      <c r="K27" s="345"/>
+      <c r="L27" s="344"/>
+      <c r="M27" s="344"/>
       <c r="N27" s="33"/>
-      <c r="O27" s="401"/>
-      <c r="P27" s="402"/>
-      <c r="Q27" s="402"/>
-      <c r="R27" s="402"/>
-      <c r="S27" s="402"/>
-      <c r="T27" s="402"/>
-      <c r="U27" s="403"/>
+      <c r="O27" s="400"/>
+      <c r="P27" s="401"/>
+      <c r="Q27" s="401"/>
+      <c r="R27" s="401"/>
+      <c r="S27" s="401"/>
+      <c r="T27" s="401"/>
+      <c r="U27" s="402"/>
       <c r="V27" s="62"/>
       <c r="W27" s="38"/>
       <c r="X27" s="9"/>
@@ -9532,7 +9538,7 @@
       <c r="AG27" s="188"/>
       <c r="AH27" s="188"/>
       <c r="AI27" s="188"/>
-      <c r="AJ27" s="271" t="s">
+      <c r="AJ27" s="270" t="s">
         <v>518</v>
       </c>
       <c r="AK27" s="227" t="s">
@@ -9546,7 +9552,7 @@
       <c r="AQ27" s="188"/>
       <c r="AR27" s="188"/>
       <c r="AS27" s="188"/>
-      <c r="AT27" s="271" t="s">
+      <c r="AT27" s="270" t="s">
         <v>342</v>
       </c>
       <c r="AU27" s="227" t="s">
@@ -9561,7 +9567,7 @@
         <v>123</v>
       </c>
       <c r="BC27" s="188"/>
-      <c r="BD27" s="271" t="s">
+      <c r="BD27" s="270" t="s">
         <v>316</v>
       </c>
       <c r="BE27" s="221" t="s">
@@ -9576,10 +9582,10 @@
       <c r="BL27" s="197" t="s">
         <v>206</v>
       </c>
-      <c r="BM27" s="267" t="s">
+      <c r="BM27" s="266" t="s">
         <v>69</v>
       </c>
-      <c r="BN27" s="350" t="s">
+      <c r="BN27" s="349" t="s">
         <v>288</v>
       </c>
       <c r="BO27" s="224"/>
@@ -9587,23 +9593,23 @@
     <row r="28" spans="1:70" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="9"/>
       <c r="B28" s="44"/>
-      <c r="E28" s="397"/>
-      <c r="F28" s="395"/>
-      <c r="G28" s="396"/>
-      <c r="H28" s="344"/>
-      <c r="I28" s="346"/>
-      <c r="J28" s="344"/>
-      <c r="K28" s="346"/>
-      <c r="L28" s="345"/>
-      <c r="M28" s="345"/>
+      <c r="E28" s="396"/>
+      <c r="F28" s="394"/>
+      <c r="G28" s="395"/>
+      <c r="H28" s="343"/>
+      <c r="I28" s="345"/>
+      <c r="J28" s="343"/>
+      <c r="K28" s="345"/>
+      <c r="L28" s="344"/>
+      <c r="M28" s="344"/>
       <c r="N28" s="33"/>
-      <c r="O28" s="401"/>
-      <c r="P28" s="402"/>
-      <c r="Q28" s="402"/>
-      <c r="R28" s="402"/>
-      <c r="S28" s="402"/>
-      <c r="T28" s="402"/>
-      <c r="U28" s="403"/>
+      <c r="O28" s="400"/>
+      <c r="P28" s="401"/>
+      <c r="Q28" s="401"/>
+      <c r="R28" s="401"/>
+      <c r="S28" s="401"/>
+      <c r="T28" s="401"/>
+      <c r="U28" s="402"/>
       <c r="V28" s="62"/>
       <c r="W28" s="37"/>
       <c r="X28" s="37"/>
@@ -9617,7 +9623,7 @@
       <c r="AG28" s="189"/>
       <c r="AH28" s="189"/>
       <c r="AI28" s="189"/>
-      <c r="AJ28" s="271"/>
+      <c r="AJ28" s="270"/>
       <c r="AK28" s="227"/>
       <c r="AL28" s="189"/>
       <c r="AM28" s="189"/>
@@ -9629,7 +9635,7 @@
       <c r="AS28" s="211" t="s">
         <v>429</v>
       </c>
-      <c r="AT28" s="271"/>
+      <c r="AT28" s="270"/>
       <c r="AU28" s="227"/>
       <c r="AV28" s="235" t="s">
         <v>430</v>
@@ -9652,7 +9658,7 @@
       <c r="BC28" s="196" t="s">
         <v>125</v>
       </c>
-      <c r="BD28" s="271"/>
+      <c r="BD28" s="270"/>
       <c r="BE28" s="221"/>
       <c r="BF28" s="238" t="s">
         <v>68</v>
@@ -9672,7 +9678,7 @@
       <c r="BM28" s="238" t="s">
         <v>70</v>
       </c>
-      <c r="BN28" s="350"/>
+      <c r="BN28" s="349"/>
       <c r="BO28" s="224"/>
       <c r="BR28" s="4" t="s">
         <v>11</v>
@@ -9681,23 +9687,23 @@
     <row r="29" spans="1:70" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="9"/>
       <c r="B29" s="44"/>
-      <c r="E29" s="397"/>
-      <c r="F29" s="395"/>
-      <c r="G29" s="396"/>
-      <c r="H29" s="344"/>
-      <c r="I29" s="346"/>
-      <c r="J29" s="344"/>
-      <c r="K29" s="346"/>
-      <c r="L29" s="345"/>
-      <c r="M29" s="345"/>
+      <c r="E29" s="396"/>
+      <c r="F29" s="394"/>
+      <c r="G29" s="395"/>
+      <c r="H29" s="343"/>
+      <c r="I29" s="345"/>
+      <c r="J29" s="343"/>
+      <c r="K29" s="345"/>
+      <c r="L29" s="344"/>
+      <c r="M29" s="344"/>
       <c r="N29" s="33"/>
-      <c r="O29" s="401"/>
-      <c r="P29" s="402"/>
-      <c r="Q29" s="402"/>
-      <c r="R29" s="402"/>
-      <c r="S29" s="402"/>
-      <c r="T29" s="402"/>
-      <c r="U29" s="403"/>
+      <c r="O29" s="400"/>
+      <c r="P29" s="401"/>
+      <c r="Q29" s="401"/>
+      <c r="R29" s="401"/>
+      <c r="S29" s="401"/>
+      <c r="T29" s="401"/>
+      <c r="U29" s="402"/>
       <c r="V29" s="44"/>
       <c r="W29" s="37"/>
       <c r="X29" s="37"/>
@@ -9731,30 +9737,30 @@
         <v>343</v>
       </c>
       <c r="AU29" s="229"/>
-      <c r="AV29" s="427" t="s">
+      <c r="AV29" s="426" t="s">
         <v>48</v>
       </c>
-      <c r="AW29" s="428"/>
-      <c r="AX29" s="428"/>
-      <c r="AY29" s="428"/>
-      <c r="AZ29" s="428"/>
-      <c r="BA29" s="428"/>
-      <c r="BB29" s="428"/>
-      <c r="BC29" s="429"/>
+      <c r="AW29" s="427"/>
+      <c r="AX29" s="427"/>
+      <c r="AY29" s="427"/>
+      <c r="AZ29" s="427"/>
+      <c r="BA29" s="427"/>
+      <c r="BB29" s="427"/>
+      <c r="BC29" s="428"/>
       <c r="BD29" s="208" t="s">
         <v>317</v>
       </c>
       <c r="BE29" s="223"/>
-      <c r="BF29" s="427" t="s">
+      <c r="BF29" s="426" t="s">
         <v>49</v>
       </c>
-      <c r="BG29" s="428"/>
-      <c r="BH29" s="428"/>
-      <c r="BI29" s="428"/>
-      <c r="BJ29" s="428"/>
-      <c r="BK29" s="428"/>
-      <c r="BL29" s="428"/>
-      <c r="BM29" s="429"/>
+      <c r="BG29" s="427"/>
+      <c r="BH29" s="427"/>
+      <c r="BI29" s="427"/>
+      <c r="BJ29" s="427"/>
+      <c r="BK29" s="427"/>
+      <c r="BL29" s="427"/>
+      <c r="BM29" s="428"/>
       <c r="BN29" s="219" t="s">
         <v>289</v>
       </c>
@@ -9763,23 +9769,23 @@
     <row r="30" spans="1:70" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="9"/>
       <c r="B30" s="44"/>
-      <c r="E30" s="405"/>
-      <c r="F30" s="382"/>
-      <c r="G30" s="383"/>
-      <c r="H30" s="344"/>
-      <c r="I30" s="346"/>
-      <c r="J30" s="344"/>
-      <c r="K30" s="346"/>
-      <c r="L30" s="345"/>
-      <c r="M30" s="345"/>
+      <c r="E30" s="404"/>
+      <c r="F30" s="381"/>
+      <c r="G30" s="382"/>
+      <c r="H30" s="343"/>
+      <c r="I30" s="345"/>
+      <c r="J30" s="343"/>
+      <c r="K30" s="345"/>
+      <c r="L30" s="344"/>
+      <c r="M30" s="344"/>
       <c r="N30" s="33"/>
-      <c r="O30" s="401"/>
-      <c r="P30" s="402"/>
-      <c r="Q30" s="402"/>
-      <c r="R30" s="402"/>
-      <c r="S30" s="402"/>
-      <c r="T30" s="402"/>
-      <c r="U30" s="403"/>
+      <c r="O30" s="400"/>
+      <c r="P30" s="401"/>
+      <c r="Q30" s="401"/>
+      <c r="R30" s="401"/>
+      <c r="S30" s="401"/>
+      <c r="T30" s="401"/>
+      <c r="U30" s="402"/>
       <c r="V30" s="44"/>
       <c r="W30" s="37"/>
       <c r="X30" s="37"/>
@@ -9796,7 +9802,7 @@
       <c r="AG30" s="188"/>
       <c r="AH30" s="188"/>
       <c r="AI30" s="188"/>
-      <c r="AJ30" s="271" t="s">
+      <c r="AJ30" s="270" t="s">
         <v>528</v>
       </c>
       <c r="AK30" s="227" t="s">
@@ -9810,7 +9816,7 @@
       <c r="AQ30" s="188"/>
       <c r="AR30" s="188"/>
       <c r="AS30" s="188"/>
-      <c r="AT30" s="271" t="s">
+      <c r="AT30" s="270" t="s">
         <v>344</v>
       </c>
       <c r="AU30" s="227" t="s">
@@ -9828,7 +9834,7 @@
       </c>
       <c r="BB30" s="188"/>
       <c r="BC30" s="188"/>
-      <c r="BD30" s="271" t="s">
+      <c r="BD30" s="270" t="s">
         <v>318</v>
       </c>
       <c r="BE30" s="221" t="s">
@@ -9842,9 +9848,9 @@
       <c r="BK30" s="188"/>
       <c r="BL30" s="188"/>
       <c r="BM30" s="245" t="s">
-        <v>656</v>
-      </c>
-      <c r="BN30" s="350" t="s">
+        <v>655</v>
+      </c>
+      <c r="BN30" s="349" t="s">
         <v>290</v>
       </c>
       <c r="BO30" s="224"/>
@@ -9852,25 +9858,25 @@
     <row r="31" spans="1:70" ht="279.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="9"/>
       <c r="B31" s="44"/>
-      <c r="E31" s="404" t="s">
+      <c r="E31" s="403" t="s">
         <v>28</v>
       </c>
-      <c r="F31" s="380"/>
-      <c r="G31" s="381"/>
-      <c r="H31" s="344"/>
-      <c r="I31" s="346"/>
-      <c r="J31" s="344"/>
-      <c r="K31" s="346"/>
-      <c r="L31" s="345"/>
-      <c r="M31" s="345"/>
+      <c r="F31" s="379"/>
+      <c r="G31" s="380"/>
+      <c r="H31" s="343"/>
+      <c r="I31" s="345"/>
+      <c r="J31" s="343"/>
+      <c r="K31" s="345"/>
+      <c r="L31" s="344"/>
+      <c r="M31" s="344"/>
       <c r="N31" s="67"/>
-      <c r="O31" s="401"/>
-      <c r="P31" s="402"/>
-      <c r="Q31" s="402"/>
-      <c r="R31" s="402"/>
-      <c r="S31" s="402"/>
-      <c r="T31" s="402"/>
-      <c r="U31" s="403"/>
+      <c r="O31" s="400"/>
+      <c r="P31" s="401"/>
+      <c r="Q31" s="401"/>
+      <c r="R31" s="401"/>
+      <c r="S31" s="401"/>
+      <c r="T31" s="401"/>
+      <c r="U31" s="402"/>
       <c r="V31" s="44"/>
       <c r="W31" s="37"/>
       <c r="X31" s="37"/>
@@ -9885,7 +9891,7 @@
       <c r="AG31" s="189"/>
       <c r="AH31" s="189"/>
       <c r="AI31" s="189"/>
-      <c r="AJ31" s="271"/>
+      <c r="AJ31" s="270"/>
       <c r="AK31" s="227"/>
       <c r="AL31" s="189"/>
       <c r="AM31" s="211" t="s">
@@ -9899,7 +9905,7 @@
         <v>631</v>
       </c>
       <c r="AS31" s="189"/>
-      <c r="AT31" s="271"/>
+      <c r="AT31" s="270"/>
       <c r="AU31" s="227"/>
       <c r="AV31" s="211" t="s">
         <v>418</v>
@@ -9923,7 +9929,7 @@
       <c r="BC31" s="211" t="s">
         <v>438</v>
       </c>
-      <c r="BD31" s="271"/>
+      <c r="BD31" s="270"/>
       <c r="BE31" s="221"/>
       <c r="BF31" s="196" t="s">
         <v>73</v>
@@ -9945,31 +9951,31 @@
         <v>72</v>
       </c>
       <c r="BM31" s="244" t="s">
-        <v>657</v>
-      </c>
-      <c r="BN31" s="350"/>
+        <v>656</v>
+      </c>
+      <c r="BN31" s="349"/>
       <c r="BO31" s="224"/>
     </row>
     <row r="32" spans="1:70" ht="279.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A32" s="9"/>
       <c r="B32" s="44"/>
-      <c r="E32" s="397"/>
-      <c r="F32" s="395"/>
-      <c r="G32" s="396"/>
-      <c r="H32" s="344"/>
-      <c r="I32" s="346"/>
-      <c r="J32" s="344"/>
-      <c r="K32" s="346"/>
-      <c r="L32" s="345"/>
-      <c r="M32" s="345"/>
+      <c r="E32" s="396"/>
+      <c r="F32" s="394"/>
+      <c r="G32" s="395"/>
+      <c r="H32" s="343"/>
+      <c r="I32" s="345"/>
+      <c r="J32" s="343"/>
+      <c r="K32" s="345"/>
+      <c r="L32" s="344"/>
+      <c r="M32" s="344"/>
       <c r="N32" s="33"/>
-      <c r="O32" s="401"/>
-      <c r="P32" s="402"/>
-      <c r="Q32" s="402"/>
-      <c r="R32" s="402"/>
-      <c r="S32" s="402"/>
-      <c r="T32" s="402"/>
-      <c r="U32" s="403"/>
+      <c r="O32" s="400"/>
+      <c r="P32" s="401"/>
+      <c r="Q32" s="401"/>
+      <c r="R32" s="401"/>
+      <c r="S32" s="401"/>
+      <c r="T32" s="401"/>
+      <c r="U32" s="402"/>
       <c r="W32" s="37"/>
       <c r="X32" s="37"/>
       <c r="Y32" s="66"/>
@@ -9985,7 +9991,7 @@
       <c r="AG32" s="204"/>
       <c r="AH32" s="204"/>
       <c r="AI32" s="204"/>
-      <c r="AJ32" s="270" t="s">
+      <c r="AJ32" s="269" t="s">
         <v>529</v>
       </c>
       <c r="AK32" s="228" t="s">
@@ -9999,7 +10005,7 @@
       <c r="AQ32" s="204"/>
       <c r="AR32" s="204"/>
       <c r="AS32" s="204"/>
-      <c r="AT32" s="270" t="s">
+      <c r="AT32" s="269" t="s">
         <v>345</v>
       </c>
       <c r="AU32" s="228" t="s">
@@ -10015,7 +10021,7 @@
       <c r="BA32" s="204"/>
       <c r="BB32" s="204"/>
       <c r="BC32" s="204"/>
-      <c r="BD32" s="270" t="s">
+      <c r="BD32" s="269" t="s">
         <v>319</v>
       </c>
       <c r="BE32" s="222" t="s">
@@ -10031,7 +10037,7 @@
       <c r="BK32" s="204"/>
       <c r="BL32" s="204"/>
       <c r="BM32" s="204"/>
-      <c r="BN32" s="406" t="s">
+      <c r="BN32" s="405" t="s">
         <v>291</v>
       </c>
       <c r="BO32" s="224"/>
@@ -10039,23 +10045,23 @@
     <row r="33" spans="1:67" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="9"/>
       <c r="B33" s="44"/>
-      <c r="E33" s="405"/>
-      <c r="F33" s="382"/>
-      <c r="G33" s="383"/>
-      <c r="H33" s="344"/>
-      <c r="I33" s="346"/>
-      <c r="J33" s="344"/>
-      <c r="K33" s="346"/>
-      <c r="L33" s="345"/>
-      <c r="M33" s="345"/>
+      <c r="E33" s="404"/>
+      <c r="F33" s="381"/>
+      <c r="G33" s="382"/>
+      <c r="H33" s="343"/>
+      <c r="I33" s="345"/>
+      <c r="J33" s="343"/>
+      <c r="K33" s="345"/>
+      <c r="L33" s="344"/>
+      <c r="M33" s="344"/>
       <c r="N33" s="33"/>
-      <c r="O33" s="401"/>
-      <c r="P33" s="402"/>
-      <c r="Q33" s="402"/>
-      <c r="R33" s="402"/>
-      <c r="S33" s="402"/>
-      <c r="T33" s="402"/>
-      <c r="U33" s="403"/>
+      <c r="O33" s="400"/>
+      <c r="P33" s="401"/>
+      <c r="Q33" s="401"/>
+      <c r="R33" s="401"/>
+      <c r="S33" s="401"/>
+      <c r="T33" s="401"/>
+      <c r="U33" s="402"/>
       <c r="W33" s="37"/>
       <c r="X33" s="37"/>
       <c r="Z33" s="69"/>
@@ -10068,7 +10074,7 @@
       <c r="AG33" s="203"/>
       <c r="AH33" s="203"/>
       <c r="AI33" s="203"/>
-      <c r="AJ33" s="270"/>
+      <c r="AJ33" s="269"/>
       <c r="AK33" s="228"/>
       <c r="AL33" s="209" t="s">
         <v>469</v>
@@ -10092,7 +10098,7 @@
       <c r="AS33" s="237" t="s">
         <v>433</v>
       </c>
-      <c r="AT33" s="270"/>
+      <c r="AT33" s="269"/>
       <c r="AU33" s="228"/>
       <c r="AV33" s="235" t="s">
         <v>440</v>
@@ -10116,7 +10122,7 @@
       <c r="BC33" s="211" t="s">
         <v>211</v>
       </c>
-      <c r="BD33" s="270"/>
+      <c r="BD33" s="269"/>
       <c r="BE33" s="222"/>
       <c r="BF33" s="196" t="s">
         <v>547</v>
@@ -10126,12 +10132,12 @@
       </c>
       <c r="BH33" s="203"/>
       <c r="BI33" s="243" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="BJ33" s="235" t="s">
         <v>209</v>
       </c>
-      <c r="BK33" s="262" t="s">
+      <c r="BK33" s="261" t="s">
         <v>563</v>
       </c>
       <c r="BL33" s="211" t="s">
@@ -10140,31 +10146,31 @@
       <c r="BM33" s="243" t="s">
         <v>625</v>
       </c>
-      <c r="BN33" s="406"/>
+      <c r="BN33" s="405"/>
       <c r="BO33" s="224"/>
     </row>
     <row r="34" spans="1:67" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="9"/>
       <c r="B34" s="44"/>
-      <c r="E34" s="404" t="s">
+      <c r="E34" s="403" t="s">
         <v>29</v>
       </c>
-      <c r="F34" s="380"/>
-      <c r="G34" s="381"/>
-      <c r="H34" s="344"/>
-      <c r="I34" s="346"/>
-      <c r="J34" s="344"/>
-      <c r="K34" s="346"/>
-      <c r="L34" s="345"/>
-      <c r="M34" s="345"/>
+      <c r="F34" s="379"/>
+      <c r="G34" s="380"/>
+      <c r="H34" s="343"/>
+      <c r="I34" s="345"/>
+      <c r="J34" s="343"/>
+      <c r="K34" s="345"/>
+      <c r="L34" s="344"/>
+      <c r="M34" s="344"/>
       <c r="N34" s="33"/>
-      <c r="O34" s="401"/>
-      <c r="P34" s="402"/>
-      <c r="Q34" s="402"/>
-      <c r="R34" s="402"/>
-      <c r="S34" s="402"/>
-      <c r="T34" s="402"/>
-      <c r="U34" s="403"/>
+      <c r="O34" s="400"/>
+      <c r="P34" s="401"/>
+      <c r="Q34" s="401"/>
+      <c r="R34" s="401"/>
+      <c r="S34" s="401"/>
+      <c r="T34" s="401"/>
+      <c r="U34" s="402"/>
       <c r="V34" s="41"/>
       <c r="W34" s="37"/>
       <c r="X34" s="37"/>
@@ -10180,7 +10186,7 @@
       <c r="AG34" s="188"/>
       <c r="AH34" s="188"/>
       <c r="AI34" s="188"/>
-      <c r="AJ34" s="271" t="s">
+      <c r="AJ34" s="270" t="s">
         <v>530</v>
       </c>
       <c r="AK34" s="227" t="s">
@@ -10194,7 +10200,7 @@
       <c r="AQ34" s="188"/>
       <c r="AR34" s="188"/>
       <c r="AS34" s="188"/>
-      <c r="AT34" s="271" t="s">
+      <c r="AT34" s="270" t="s">
         <v>346</v>
       </c>
       <c r="AU34" s="227" t="s">
@@ -10210,7 +10216,7 @@
         <v>201</v>
       </c>
       <c r="BC34" s="188"/>
-      <c r="BD34" s="271" t="s">
+      <c r="BD34" s="270" t="s">
         <v>320</v>
       </c>
       <c r="BE34" s="221" t="s">
@@ -10226,7 +10232,7 @@
       <c r="BK34" s="188"/>
       <c r="BL34" s="188"/>
       <c r="BM34" s="188"/>
-      <c r="BN34" s="350" t="s">
+      <c r="BN34" s="349" t="s">
         <v>292</v>
       </c>
       <c r="BO34" s="224"/>
@@ -10236,23 +10242,23 @@
       <c r="B35" s="44"/>
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
-      <c r="E35" s="405"/>
-      <c r="F35" s="382"/>
-      <c r="G35" s="383"/>
-      <c r="H35" s="344"/>
-      <c r="I35" s="346"/>
-      <c r="J35" s="344"/>
-      <c r="K35" s="346"/>
-      <c r="L35" s="345"/>
-      <c r="M35" s="345"/>
+      <c r="E35" s="404"/>
+      <c r="F35" s="381"/>
+      <c r="G35" s="382"/>
+      <c r="H35" s="343"/>
+      <c r="I35" s="345"/>
+      <c r="J35" s="343"/>
+      <c r="K35" s="345"/>
+      <c r="L35" s="344"/>
+      <c r="M35" s="344"/>
       <c r="N35" s="33"/>
-      <c r="O35" s="401"/>
-      <c r="P35" s="402"/>
-      <c r="Q35" s="402"/>
-      <c r="R35" s="402"/>
-      <c r="S35" s="402"/>
-      <c r="T35" s="402"/>
-      <c r="U35" s="403"/>
+      <c r="O35" s="400"/>
+      <c r="P35" s="401"/>
+      <c r="Q35" s="401"/>
+      <c r="R35" s="401"/>
+      <c r="S35" s="401"/>
+      <c r="T35" s="401"/>
+      <c r="U35" s="402"/>
       <c r="V35" s="70"/>
       <c r="W35" s="37"/>
       <c r="X35" s="37"/>
@@ -10267,7 +10273,7 @@
       <c r="AG35" s="189"/>
       <c r="AH35" s="189"/>
       <c r="AI35" s="189"/>
-      <c r="AJ35" s="271"/>
+      <c r="AJ35" s="270"/>
       <c r="AK35" s="227"/>
       <c r="AL35" s="209" t="s">
         <v>474</v>
@@ -10291,7 +10297,7 @@
       <c r="AS35" s="237" t="s">
         <v>480</v>
       </c>
-      <c r="AT35" s="271"/>
+      <c r="AT35" s="270"/>
       <c r="AU35" s="227"/>
       <c r="AV35" s="235" t="s">
         <v>445</v>
@@ -10315,7 +10321,7 @@
       <c r="BC35" s="211" t="s">
         <v>143</v>
       </c>
-      <c r="BD35" s="271"/>
+      <c r="BD35" s="270"/>
       <c r="BE35" s="221"/>
       <c r="BF35" s="196" t="s">
         <v>76</v>
@@ -10339,7 +10345,7 @@
       <c r="BM35" s="243" t="s">
         <v>565</v>
       </c>
-      <c r="BN35" s="350"/>
+      <c r="BN35" s="349"/>
       <c r="BO35" s="225"/>
     </row>
     <row r="36" spans="1:67" s="73" customFormat="1" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10347,25 +10353,25 @@
       <c r="B36" s="40"/>
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
-      <c r="E36" s="405" t="s">
+      <c r="E36" s="404" t="s">
         <v>30</v>
       </c>
-      <c r="F36" s="382"/>
-      <c r="G36" s="383"/>
-      <c r="H36" s="347"/>
-      <c r="I36" s="349"/>
-      <c r="J36" s="347"/>
-      <c r="K36" s="349"/>
-      <c r="L36" s="348"/>
-      <c r="M36" s="348"/>
+      <c r="F36" s="381"/>
+      <c r="G36" s="382"/>
+      <c r="H36" s="346"/>
+      <c r="I36" s="348"/>
+      <c r="J36" s="346"/>
+      <c r="K36" s="348"/>
+      <c r="L36" s="347"/>
+      <c r="M36" s="347"/>
       <c r="N36" s="33"/>
-      <c r="O36" s="401"/>
-      <c r="P36" s="402"/>
-      <c r="Q36" s="402"/>
-      <c r="R36" s="402"/>
-      <c r="S36" s="402"/>
-      <c r="T36" s="402"/>
-      <c r="U36" s="403"/>
+      <c r="O36" s="400"/>
+      <c r="P36" s="401"/>
+      <c r="Q36" s="401"/>
+      <c r="R36" s="401"/>
+      <c r="S36" s="401"/>
+      <c r="T36" s="401"/>
+      <c r="U36" s="402"/>
       <c r="V36" s="9"/>
       <c r="W36" s="4"/>
       <c r="X36" s="71"/>
@@ -10382,7 +10388,7 @@
       <c r="AG36" s="204"/>
       <c r="AH36" s="204"/>
       <c r="AI36" s="204"/>
-      <c r="AJ36" s="270" t="s">
+      <c r="AJ36" s="269" t="s">
         <v>531</v>
       </c>
       <c r="AK36" s="228" t="s">
@@ -10396,7 +10402,7 @@
       <c r="AQ36" s="204"/>
       <c r="AR36" s="204"/>
       <c r="AS36" s="204"/>
-      <c r="AT36" s="270" t="s">
+      <c r="AT36" s="269" t="s">
         <v>347</v>
       </c>
       <c r="AU36" s="228" t="s">
@@ -10407,10 +10413,16 @@
       <c r="AX36" s="204"/>
       <c r="AY36" s="204"/>
       <c r="AZ36" s="204"/>
-      <c r="BA36" s="204"/>
-      <c r="BB36" s="204"/>
-      <c r="BC36" s="204"/>
-      <c r="BD36" s="270" t="s">
+      <c r="BA36" s="210" t="s">
+        <v>216</v>
+      </c>
+      <c r="BB36" s="210" t="s">
+        <v>137</v>
+      </c>
+      <c r="BC36" s="210" t="s">
+        <v>147</v>
+      </c>
+      <c r="BD36" s="269" t="s">
         <v>321</v>
       </c>
       <c r="BE36" s="222" t="s">
@@ -10424,7 +10436,7 @@
       <c r="BK36" s="204"/>
       <c r="BL36" s="204"/>
       <c r="BM36" s="204"/>
-      <c r="BN36" s="406" t="s">
+      <c r="BN36" s="405" t="s">
         <v>293</v>
       </c>
       <c r="BO36" s="225"/>
@@ -10432,27 +10444,27 @@
     <row r="37" spans="1:67" s="73" customFormat="1" ht="279.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="9"/>
       <c r="B37" s="40"/>
-      <c r="E37" s="357" t="s">
+      <c r="E37" s="356" t="s">
         <v>31</v>
       </c>
-      <c r="F37" s="357"/>
-      <c r="G37" s="357"/>
-      <c r="H37" s="357"/>
-      <c r="I37" s="357"/>
-      <c r="J37" s="357"/>
-      <c r="K37" s="357"/>
-      <c r="L37" s="357"/>
-      <c r="M37" s="357"/>
+      <c r="F37" s="356"/>
+      <c r="G37" s="356"/>
+      <c r="H37" s="356"/>
+      <c r="I37" s="356"/>
+      <c r="J37" s="356"/>
+      <c r="K37" s="356"/>
+      <c r="L37" s="356"/>
+      <c r="M37" s="356"/>
       <c r="N37" s="74"/>
-      <c r="O37" s="358" t="s">
+      <c r="O37" s="357" t="s">
         <v>31</v>
       </c>
-      <c r="P37" s="359"/>
-      <c r="Q37" s="359"/>
-      <c r="R37" s="359"/>
-      <c r="S37" s="359"/>
-      <c r="T37" s="359"/>
-      <c r="U37" s="359"/>
+      <c r="P37" s="358"/>
+      <c r="Q37" s="358"/>
+      <c r="R37" s="358"/>
+      <c r="S37" s="358"/>
+      <c r="T37" s="358"/>
+      <c r="U37" s="358"/>
       <c r="V37" s="75"/>
       <c r="W37" s="76"/>
       <c r="X37" s="76"/>
@@ -10467,7 +10479,7 @@
       <c r="AG37" s="203"/>
       <c r="AH37" s="203"/>
       <c r="AI37" s="203"/>
-      <c r="AJ37" s="270"/>
+      <c r="AJ37" s="269"/>
       <c r="AK37" s="228"/>
       <c r="AL37" s="209" t="s">
         <v>481</v>
@@ -10491,23 +10503,17 @@
       <c r="AS37" s="209" t="s">
         <v>487</v>
       </c>
-      <c r="AT37" s="270"/>
+      <c r="AT37" s="269"/>
       <c r="AU37" s="228"/>
-      <c r="AV37" s="211" t="s">
-        <v>216</v>
-      </c>
+      <c r="AV37" s="203"/>
       <c r="AW37" s="211" t="s">
         <v>132</v>
       </c>
       <c r="AX37" s="260"/>
-      <c r="AY37" s="211" t="s">
+      <c r="AY37" s="203"/>
+      <c r="AZ37" s="203"/>
+      <c r="BA37" s="211" t="s">
         <v>128</v>
-      </c>
-      <c r="AZ37" s="211" t="s">
-        <v>137</v>
-      </c>
-      <c r="BA37" s="211" t="s">
-        <v>147</v>
       </c>
       <c r="BB37" s="211" t="s">
         <v>142</v>
@@ -10515,7 +10521,7 @@
       <c r="BC37" s="211" t="s">
         <v>133</v>
       </c>
-      <c r="BD37" s="270"/>
+      <c r="BD37" s="269"/>
       <c r="BE37" s="222"/>
       <c r="BF37" s="211" t="s">
         <v>449</v>
@@ -10537,7 +10543,7 @@
         <v>566</v>
       </c>
       <c r="BM37" s="250"/>
-      <c r="BN37" s="406"/>
+      <c r="BN37" s="405"/>
       <c r="BO37" s="225"/>
     </row>
     <row r="38" spans="1:67" s="73" customFormat="1" ht="279.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
@@ -10560,7 +10566,7 @@
       </c>
       <c r="M38" s="25"/>
       <c r="N38" s="81"/>
-      <c r="O38" s="360"/>
+      <c r="O38" s="359"/>
       <c r="P38" s="14"/>
       <c r="Q38" s="14"/>
       <c r="R38" s="14"/>
@@ -10581,7 +10587,7 @@
       <c r="AG38" s="188"/>
       <c r="AH38" s="188"/>
       <c r="AI38" s="188"/>
-      <c r="AJ38" s="271" t="s">
+      <c r="AJ38" s="270" t="s">
         <v>532</v>
       </c>
       <c r="AK38" s="227" t="s">
@@ -10595,7 +10601,7 @@
       <c r="AQ38" s="188"/>
       <c r="AR38" s="188"/>
       <c r="AS38" s="188"/>
-      <c r="AT38" s="271" t="s">
+      <c r="AT38" s="270" t="s">
         <v>348</v>
       </c>
       <c r="AU38" s="227" t="s">
@@ -10611,7 +10617,7 @@
       <c r="BC38" s="197" t="s">
         <v>503</v>
       </c>
-      <c r="BD38" s="271" t="s">
+      <c r="BD38" s="270" t="s">
         <v>322</v>
       </c>
       <c r="BE38" s="221" t="s">
@@ -10629,7 +10635,7 @@
       <c r="BM38" s="246" t="s">
         <v>378</v>
       </c>
-      <c r="BN38" s="350" t="s">
+      <c r="BN38" s="349" t="s">
         <v>294</v>
       </c>
       <c r="BO38" s="225"/>
@@ -10648,7 +10654,7 @@
       <c r="L39" s="31"/>
       <c r="M39" s="31"/>
       <c r="N39" s="81"/>
-      <c r="O39" s="272"/>
+      <c r="O39" s="271"/>
       <c r="P39" s="14"/>
       <c r="Q39" s="14"/>
       <c r="R39" s="14"/>
@@ -10668,7 +10674,7 @@
       <c r="AG39" s="189"/>
       <c r="AH39" s="189"/>
       <c r="AI39" s="189"/>
-      <c r="AJ39" s="271"/>
+      <c r="AJ39" s="270"/>
       <c r="AK39" s="227"/>
       <c r="AL39" s="196" t="s">
         <v>254</v>
@@ -10692,7 +10698,7 @@
       <c r="AS39" s="209" t="s">
         <v>492</v>
       </c>
-      <c r="AT39" s="271"/>
+      <c r="AT39" s="270"/>
       <c r="AU39" s="227"/>
       <c r="AV39" s="211" t="s">
         <v>135</v>
@@ -10710,12 +10716,12 @@
         <v>425</v>
       </c>
       <c r="BB39" s="243" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="BC39" s="196" t="s">
         <v>220</v>
       </c>
-      <c r="BD39" s="271"/>
+      <c r="BD39" s="270"/>
       <c r="BE39" s="221"/>
       <c r="BF39" s="211" t="s">
         <v>455</v>
@@ -10725,7 +10731,7 @@
       </c>
       <c r="BH39" s="189"/>
       <c r="BI39" s="211" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="BJ39" s="211" t="s">
         <v>448</v>
@@ -10739,7 +10745,7 @@
       <c r="BM39" s="235" t="s">
         <v>265</v>
       </c>
-      <c r="BN39" s="350"/>
+      <c r="BN39" s="349"/>
       <c r="BO39" s="225"/>
     </row>
     <row r="40" spans="1:67" s="73" customFormat="1" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10777,7 +10783,7 @@
       <c r="AG40" s="204"/>
       <c r="AH40" s="204"/>
       <c r="AI40" s="204"/>
-      <c r="AJ40" s="270" t="s">
+      <c r="AJ40" s="269" t="s">
         <v>533</v>
       </c>
       <c r="AK40" s="228" t="s">
@@ -10791,13 +10797,15 @@
       <c r="AQ40" s="204"/>
       <c r="AR40" s="204"/>
       <c r="AS40" s="204"/>
-      <c r="AT40" s="270" t="s">
+      <c r="AT40" s="269" t="s">
         <v>349</v>
       </c>
       <c r="AU40" s="228" t="s">
         <v>275</v>
       </c>
-      <c r="AV40" s="204"/>
+      <c r="AV40" s="245" t="s">
+        <v>671</v>
+      </c>
       <c r="AW40" s="204"/>
       <c r="AX40" s="204"/>
       <c r="AY40" s="204"/>
@@ -10807,7 +10815,7 @@
       </c>
       <c r="BB40" s="204"/>
       <c r="BC40" s="204"/>
-      <c r="BD40" s="270" t="s">
+      <c r="BD40" s="269" t="s">
         <v>323</v>
       </c>
       <c r="BE40" s="222" t="s">
@@ -10827,7 +10835,7 @@
       <c r="BM40" s="197" t="s">
         <v>222</v>
       </c>
-      <c r="BN40" s="406" t="s">
+      <c r="BN40" s="405" t="s">
         <v>295</v>
       </c>
       <c r="BO40" s="225"/>
@@ -10864,7 +10872,7 @@
       <c r="AG41" s="203"/>
       <c r="AH41" s="203"/>
       <c r="AI41" s="203"/>
-      <c r="AJ41" s="270"/>
+      <c r="AJ41" s="269"/>
       <c r="AK41" s="228"/>
       <c r="AL41" s="237" t="s">
         <v>493</v>
@@ -10886,7 +10894,7 @@
         <v>578</v>
       </c>
       <c r="AS41" s="203"/>
-      <c r="AT41" s="270"/>
+      <c r="AT41" s="269"/>
       <c r="AU41" s="228"/>
       <c r="AV41" s="211" t="s">
         <v>453</v>
@@ -10910,7 +10918,7 @@
       <c r="BC41" s="235" t="s">
         <v>426</v>
       </c>
-      <c r="BD41" s="270"/>
+      <c r="BD41" s="269"/>
       <c r="BE41" s="222"/>
       <c r="BF41" s="211" t="s">
         <v>454</v>
@@ -10934,7 +10942,7 @@
       <c r="BM41" s="196" t="s">
         <v>263</v>
       </c>
-      <c r="BN41" s="406"/>
+      <c r="BN41" s="405"/>
       <c r="BO41" s="225"/>
     </row>
     <row r="42" spans="1:67" s="73" customFormat="1" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10950,8 +10958,8 @@
       <c r="L42" s="31"/>
       <c r="M42" s="31"/>
       <c r="N42" s="81"/>
-      <c r="O42" s="356"/>
-      <c r="P42" s="272"/>
+      <c r="O42" s="355"/>
+      <c r="P42" s="271"/>
       <c r="Q42" s="89"/>
       <c r="R42" s="89"/>
       <c r="S42" s="89"/>
@@ -10971,7 +10979,7 @@
       <c r="AG42" s="188"/>
       <c r="AH42" s="188"/>
       <c r="AI42" s="188"/>
-      <c r="AJ42" s="271" t="s">
+      <c r="AJ42" s="270" t="s">
         <v>534</v>
       </c>
       <c r="AK42" s="227" t="s">
@@ -10985,7 +10993,7 @@
       <c r="AQ42" s="188"/>
       <c r="AR42" s="188"/>
       <c r="AS42" s="188"/>
-      <c r="AT42" s="271" t="s">
+      <c r="AT42" s="270" t="s">
         <v>350</v>
       </c>
       <c r="AU42" s="227" t="s">
@@ -10995,7 +11003,7 @@
         <v>230</v>
       </c>
       <c r="AW42" s="245" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="AX42" s="188"/>
       <c r="AY42" s="188"/>
@@ -11003,7 +11011,7 @@
       <c r="BA42" s="188"/>
       <c r="BB42" s="239"/>
       <c r="BC42" s="188"/>
-      <c r="BD42" s="271" t="s">
+      <c r="BD42" s="270" t="s">
         <v>324</v>
       </c>
       <c r="BE42" s="221" t="s">
@@ -11019,7 +11027,7 @@
       <c r="BM42" s="197" t="s">
         <v>90</v>
       </c>
-      <c r="BN42" s="350" t="s">
+      <c r="BN42" s="349" t="s">
         <v>296</v>
       </c>
       <c r="BO42" s="225"/>
@@ -11037,8 +11045,8 @@
       <c r="L43" s="31"/>
       <c r="M43" s="31"/>
       <c r="N43" s="81"/>
-      <c r="O43" s="356"/>
-      <c r="P43" s="272"/>
+      <c r="O43" s="355"/>
+      <c r="P43" s="271"/>
       <c r="Q43" s="89"/>
       <c r="R43" s="89"/>
       <c r="S43" s="89"/>
@@ -11056,7 +11064,7 @@
       <c r="AG43" s="189"/>
       <c r="AH43" s="189"/>
       <c r="AI43" s="189"/>
-      <c r="AJ43" s="271"/>
+      <c r="AJ43" s="270"/>
       <c r="AK43" s="227"/>
       <c r="AL43" s="237" t="s">
         <v>575</v>
@@ -11065,7 +11073,7 @@
         <v>576</v>
       </c>
       <c r="AN43" s="243" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="AO43" s="189"/>
       <c r="AP43" s="237" t="s">
@@ -11080,7 +11088,7 @@
       <c r="AS43" s="237" t="s">
         <v>500</v>
       </c>
-      <c r="AT43" s="271"/>
+      <c r="AT43" s="270"/>
       <c r="AU43" s="227"/>
       <c r="AV43" s="211" t="s">
         <v>141</v>
@@ -11089,22 +11097,22 @@
         <v>227</v>
       </c>
       <c r="AX43" s="189"/>
-      <c r="AY43" s="244" t="s">
-        <v>636</v>
+      <c r="AY43" s="243" t="s">
+        <v>670</v>
       </c>
       <c r="AZ43" s="196" t="s">
         <v>214</v>
       </c>
       <c r="BA43" s="244" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="BB43" s="196" t="s">
         <v>208</v>
       </c>
       <c r="BC43" s="243" t="s">
-        <v>653</v>
-      </c>
-      <c r="BD43" s="271"/>
+        <v>652</v>
+      </c>
+      <c r="BD43" s="270"/>
       <c r="BE43" s="221"/>
       <c r="BF43" s="211" t="s">
         <v>459</v>
@@ -11128,17 +11136,17 @@
       <c r="BM43" s="196" t="s">
         <v>82</v>
       </c>
-      <c r="BN43" s="350"/>
+      <c r="BN43" s="349"/>
       <c r="BO43" s="225"/>
     </row>
     <row r="44" spans="1:67" s="73" customFormat="1" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="78"/>
       <c r="B44" s="78"/>
-      <c r="E44" s="361" t="s">
+      <c r="E44" s="360" t="s">
         <v>35</v>
       </c>
-      <c r="F44" s="362"/>
-      <c r="G44" s="365" t="s">
+      <c r="F44" s="361"/>
+      <c r="G44" s="364" t="s">
         <v>36</v>
       </c>
       <c r="H44" s="31"/>
@@ -11148,8 +11156,8 @@
       <c r="L44" s="31"/>
       <c r="M44" s="31"/>
       <c r="N44" s="81"/>
-      <c r="O44" s="356"/>
-      <c r="P44" s="272"/>
+      <c r="O44" s="355"/>
+      <c r="P44" s="271"/>
       <c r="Q44" s="89"/>
       <c r="R44" s="89"/>
       <c r="S44" s="89"/>
@@ -11170,7 +11178,7 @@
       <c r="AG44" s="204"/>
       <c r="AH44" s="204"/>
       <c r="AI44" s="204"/>
-      <c r="AJ44" s="270" t="s">
+      <c r="AJ44" s="269" t="s">
         <v>535</v>
       </c>
       <c r="AK44" s="228" t="s">
@@ -11184,7 +11192,7 @@
       <c r="AQ44" s="204"/>
       <c r="AR44" s="204"/>
       <c r="AS44" s="204"/>
-      <c r="AT44" s="270" t="s">
+      <c r="AT44" s="269" t="s">
         <v>351</v>
       </c>
       <c r="AU44" s="228" t="s">
@@ -11200,7 +11208,7 @@
       <c r="BA44" s="204"/>
       <c r="BB44" s="204"/>
       <c r="BC44" s="204"/>
-      <c r="BD44" s="270" t="s">
+      <c r="BD44" s="269" t="s">
         <v>325</v>
       </c>
       <c r="BE44" s="222" t="s">
@@ -11222,7 +11230,7 @@
       <c r="BM44" s="197" t="s">
         <v>390</v>
       </c>
-      <c r="BN44" s="406" t="s">
+      <c r="BN44" s="405" t="s">
         <v>297</v>
       </c>
       <c r="BO44" s="225"/>
@@ -11230,9 +11238,9 @@
     <row r="45" spans="1:67" s="73" customFormat="1" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="78"/>
       <c r="B45" s="78"/>
-      <c r="E45" s="363"/>
-      <c r="F45" s="364"/>
-      <c r="G45" s="366"/>
+      <c r="E45" s="362"/>
+      <c r="F45" s="363"/>
+      <c r="G45" s="365"/>
       <c r="H45" s="31"/>
       <c r="I45" s="31"/>
       <c r="J45" s="30"/>
@@ -11259,7 +11267,7 @@
       <c r="AG45" s="203"/>
       <c r="AH45" s="203"/>
       <c r="AI45" s="203"/>
-      <c r="AJ45" s="270"/>
+      <c r="AJ45" s="269"/>
       <c r="AK45" s="228"/>
       <c r="AL45" s="237" t="s">
         <v>572</v>
@@ -11281,7 +11289,7 @@
         <v>502</v>
       </c>
       <c r="AS45" s="203"/>
-      <c r="AT45" s="270"/>
+      <c r="AT45" s="269"/>
       <c r="AU45" s="228"/>
       <c r="AV45" s="211" t="s">
         <v>567</v>
@@ -11300,12 +11308,12 @@
         <v>145</v>
       </c>
       <c r="BB45" s="243" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="BC45" s="243" t="s">
-        <v>671</v>
-      </c>
-      <c r="BD45" s="270"/>
+        <v>669</v>
+      </c>
+      <c r="BD45" s="269"/>
       <c r="BE45" s="222"/>
       <c r="BF45" s="243" t="s">
         <v>465</v>
@@ -11329,10 +11337,10 @@
       <c r="BM45" s="196" t="s">
         <v>389</v>
       </c>
-      <c r="BN45" s="406"/>
+      <c r="BN45" s="405"/>
       <c r="BO45" s="225"/>
     </row>
-    <row r="46" spans="1:67" s="73" customFormat="1" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:67" s="73" customFormat="1" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="78"/>
       <c r="B46" s="78"/>
       <c r="E46" s="30"/>
@@ -11368,7 +11376,7 @@
       <c r="AG46" s="188"/>
       <c r="AH46" s="188"/>
       <c r="AI46" s="188"/>
-      <c r="AJ46" s="271" t="s">
+      <c r="AJ46" s="270" t="s">
         <v>536</v>
       </c>
       <c r="AK46" s="227" t="s">
@@ -11382,7 +11390,7 @@
       <c r="AQ46" s="188"/>
       <c r="AR46" s="188"/>
       <c r="AS46" s="188"/>
-      <c r="AT46" s="271" t="s">
+      <c r="AT46" s="270" t="s">
         <v>352</v>
       </c>
       <c r="AU46" s="227" t="s">
@@ -11400,7 +11408,7 @@
       <c r="BC46" s="197" t="s">
         <v>146</v>
       </c>
-      <c r="BD46" s="271" t="s">
+      <c r="BD46" s="270" t="s">
         <v>326</v>
       </c>
       <c r="BE46" s="221" t="s">
@@ -11413,7 +11421,7 @@
       <c r="BK46" s="188"/>
       <c r="BL46" s="188"/>
       <c r="BM46" s="188"/>
-      <c r="BN46" s="350" t="s">
+      <c r="BN46" s="349" t="s">
         <v>298</v>
       </c>
       <c r="BO46" s="225"/>
@@ -11454,7 +11462,7 @@
       <c r="AG47" s="189"/>
       <c r="AH47" s="189"/>
       <c r="AI47" s="189"/>
-      <c r="AJ47" s="271"/>
+      <c r="AJ47" s="270"/>
       <c r="AK47" s="227"/>
       <c r="AL47" s="189"/>
       <c r="AM47" s="237" t="s">
@@ -11466,12 +11474,12 @@
       <c r="AQ47" s="189"/>
       <c r="AR47" s="189"/>
       <c r="AS47" s="189"/>
-      <c r="AT47" s="271"/>
+      <c r="AT47" s="270"/>
       <c r="AU47" s="227"/>
-      <c r="AV47" s="236" t="s">
+      <c r="AV47" s="243" t="s">
         <v>424</v>
       </c>
-      <c r="AW47" s="210" t="s">
+      <c r="AW47" s="211" t="s">
         <v>417</v>
       </c>
       <c r="AX47" s="189"/>
@@ -11490,7 +11498,7 @@
       <c r="BC47" s="196" t="s">
         <v>149</v>
       </c>
-      <c r="BD47" s="271"/>
+      <c r="BD47" s="270"/>
       <c r="BE47" s="221"/>
       <c r="BF47" s="211" t="s">
         <v>460</v>
@@ -11514,7 +11522,7 @@
       <c r="BM47" s="238" t="s">
         <v>260</v>
       </c>
-      <c r="BN47" s="350"/>
+      <c r="BN47" s="349"/>
       <c r="BO47" s="224"/>
     </row>
     <row r="48" spans="1:67" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -11532,15 +11540,15 @@
       <c r="L48" s="31"/>
       <c r="M48" s="31"/>
       <c r="N48" s="81"/>
-      <c r="O48" s="303" t="s">
+      <c r="O48" s="302" t="s">
         <v>37</v>
       </c>
-      <c r="P48" s="303"/>
-      <c r="Q48" s="303"/>
-      <c r="R48" s="303"/>
-      <c r="S48" s="303"/>
-      <c r="T48" s="303"/>
-      <c r="U48" s="304"/>
+      <c r="P48" s="302"/>
+      <c r="Q48" s="302"/>
+      <c r="R48" s="302"/>
+      <c r="S48" s="302"/>
+      <c r="T48" s="302"/>
+      <c r="U48" s="303"/>
       <c r="V48" s="36"/>
       <c r="W48" s="51"/>
       <c r="X48" s="14"/>
@@ -11557,7 +11565,7 @@
       <c r="AG48" s="204"/>
       <c r="AH48" s="204"/>
       <c r="AI48" s="204"/>
-      <c r="AJ48" s="270" t="s">
+      <c r="AJ48" s="269" t="s">
         <v>537</v>
       </c>
       <c r="AK48" s="228" t="s">
@@ -11571,7 +11579,7 @@
       <c r="AQ48" s="204"/>
       <c r="AR48" s="204"/>
       <c r="AS48" s="204"/>
-      <c r="AT48" s="270" t="s">
+      <c r="AT48" s="269" t="s">
         <v>353</v>
       </c>
       <c r="AU48" s="228" t="s">
@@ -11591,7 +11599,7 @@
         <v>234</v>
       </c>
       <c r="BC48" s="204"/>
-      <c r="BD48" s="270" t="s">
+      <c r="BD48" s="269" t="s">
         <v>327</v>
       </c>
       <c r="BE48" s="222" t="s">
@@ -11609,7 +11617,7 @@
       <c r="BM48" s="197" t="s">
         <v>387</v>
       </c>
-      <c r="BN48" s="406" t="s">
+      <c r="BN48" s="405" t="s">
         <v>299</v>
       </c>
       <c r="BO48" s="224"/>
@@ -11627,13 +11635,13 @@
       <c r="L49" s="31"/>
       <c r="M49" s="31"/>
       <c r="N49" s="33"/>
-      <c r="O49" s="306"/>
-      <c r="P49" s="306"/>
-      <c r="Q49" s="306"/>
-      <c r="R49" s="306"/>
-      <c r="S49" s="306"/>
-      <c r="T49" s="306"/>
-      <c r="U49" s="307"/>
+      <c r="O49" s="305"/>
+      <c r="P49" s="305"/>
+      <c r="Q49" s="305"/>
+      <c r="R49" s="305"/>
+      <c r="S49" s="305"/>
+      <c r="T49" s="305"/>
+      <c r="U49" s="306"/>
       <c r="V49" s="36"/>
       <c r="W49" s="14"/>
       <c r="X49" s="14"/>
@@ -11648,7 +11656,7 @@
       <c r="AG49" s="203"/>
       <c r="AH49" s="203"/>
       <c r="AI49" s="203"/>
-      <c r="AJ49" s="270"/>
+      <c r="AJ49" s="269"/>
       <c r="AK49" s="228"/>
       <c r="AL49" s="203"/>
       <c r="AM49" s="237" t="s">
@@ -11660,7 +11668,7 @@
       <c r="AQ49" s="203"/>
       <c r="AR49" s="203"/>
       <c r="AS49" s="203"/>
-      <c r="AT49" s="270"/>
+      <c r="AT49" s="269"/>
       <c r="AU49" s="228"/>
       <c r="AV49" s="196" t="s">
         <v>505</v>
@@ -11684,20 +11692,20 @@
       <c r="BC49" s="196" t="s">
         <v>239</v>
       </c>
-      <c r="BD49" s="270"/>
+      <c r="BD49" s="269"/>
       <c r="BE49" s="222"/>
       <c r="BF49" s="243" t="s">
+        <v>638</v>
+      </c>
+      <c r="BG49" s="243" t="s">
         <v>639</v>
-      </c>
-      <c r="BG49" s="243" t="s">
-        <v>640</v>
       </c>
       <c r="BH49" s="203"/>
       <c r="BI49" s="211" t="s">
         <v>247</v>
       </c>
       <c r="BJ49" s="244" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="BK49" s="196" t="s">
         <v>87</v>
@@ -11708,17 +11716,17 @@
       <c r="BM49" s="238" t="s">
         <v>259</v>
       </c>
-      <c r="BN49" s="406"/>
+      <c r="BN49" s="405"/>
       <c r="BO49" s="224"/>
     </row>
     <row r="50" spans="1:77" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="79"/>
       <c r="B50" s="79"/>
-      <c r="E50" s="344" t="s">
+      <c r="E50" s="343" t="s">
         <v>38</v>
       </c>
-      <c r="F50" s="345"/>
-      <c r="G50" s="346"/>
+      <c r="F50" s="344"/>
+      <c r="G50" s="345"/>
       <c r="H50" s="31"/>
       <c r="I50" s="31"/>
       <c r="J50" s="30"/>
@@ -11726,13 +11734,13 @@
       <c r="L50" s="31"/>
       <c r="M50" s="31"/>
       <c r="N50" s="33"/>
-      <c r="O50" s="306"/>
-      <c r="P50" s="306"/>
-      <c r="Q50" s="306"/>
-      <c r="R50" s="306"/>
-      <c r="S50" s="306"/>
-      <c r="T50" s="306"/>
-      <c r="U50" s="307"/>
+      <c r="O50" s="305"/>
+      <c r="P50" s="305"/>
+      <c r="Q50" s="305"/>
+      <c r="R50" s="305"/>
+      <c r="S50" s="305"/>
+      <c r="T50" s="305"/>
+      <c r="U50" s="306"/>
       <c r="V50" s="36"/>
       <c r="W50" s="14"/>
       <c r="X50" s="14"/>
@@ -11775,7 +11783,7 @@
       <c r="AQ50" s="188"/>
       <c r="AR50" s="188"/>
       <c r="AS50" s="188"/>
-      <c r="AT50" s="271" t="s">
+      <c r="AT50" s="270" t="s">
         <v>628</v>
       </c>
       <c r="AU50" s="227" t="s">
@@ -11785,7 +11793,7 @@
       <c r="AW50" s="188"/>
       <c r="AX50" s="188"/>
       <c r="AY50" s="197" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="AZ50" s="188"/>
       <c r="BA50" s="188"/>
@@ -11793,7 +11801,7 @@
         <v>151</v>
       </c>
       <c r="BC50" s="188"/>
-      <c r="BD50" s="271" t="s">
+      <c r="BD50" s="270" t="s">
         <v>328</v>
       </c>
       <c r="BE50" s="221" t="s">
@@ -11809,7 +11817,7 @@
         <v>91</v>
       </c>
       <c r="BM50" s="188"/>
-      <c r="BN50" s="350" t="s">
+      <c r="BN50" s="349" t="s">
         <v>300</v>
       </c>
       <c r="BO50" s="224"/>
@@ -11817,9 +11825,9 @@
     <row r="51" spans="1:77" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="79"/>
       <c r="B51" s="79"/>
-      <c r="E51" s="344"/>
-      <c r="F51" s="345"/>
-      <c r="G51" s="346"/>
+      <c r="E51" s="343"/>
+      <c r="F51" s="344"/>
+      <c r="G51" s="345"/>
       <c r="H51" s="31"/>
       <c r="I51" s="31"/>
       <c r="J51" s="30"/>
@@ -11827,19 +11835,19 @@
       <c r="L51" s="31"/>
       <c r="M51" s="31"/>
       <c r="N51" s="33"/>
-      <c r="O51" s="306"/>
-      <c r="P51" s="306"/>
-      <c r="Q51" s="306"/>
-      <c r="R51" s="306"/>
-      <c r="S51" s="306"/>
-      <c r="T51" s="306"/>
-      <c r="U51" s="307"/>
+      <c r="O51" s="305"/>
+      <c r="P51" s="305"/>
+      <c r="Q51" s="305"/>
+      <c r="R51" s="305"/>
+      <c r="S51" s="305"/>
+      <c r="T51" s="305"/>
+      <c r="U51" s="306"/>
       <c r="V51" s="95"/>
       <c r="W51" s="14"/>
       <c r="X51" s="14"/>
       <c r="Y51" s="14"/>
       <c r="Z51" s="60"/>
-      <c r="AA51" s="263" t="s">
+      <c r="AA51" s="262" t="s">
         <v>270</v>
       </c>
       <c r="AB51" s="198" t="s">
@@ -11854,7 +11862,7 @@
       <c r="AE51" s="198" t="s">
         <v>273</v>
       </c>
-      <c r="AF51" s="264" t="s">
+      <c r="AF51" s="263" t="s">
         <v>269</v>
       </c>
       <c r="AG51" s="256" t="s">
@@ -11872,7 +11880,7 @@
       <c r="AK51" s="227"/>
       <c r="AL51" s="189"/>
       <c r="AM51" s="244" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="AN51" s="211" t="s">
         <v>633</v>
@@ -11884,7 +11892,7 @@
       <c r="AQ51" s="189"/>
       <c r="AR51" s="189"/>
       <c r="AS51" s="189"/>
-      <c r="AT51" s="271"/>
+      <c r="AT51" s="270"/>
       <c r="AU51" s="240"/>
       <c r="AV51" s="196" t="s">
         <v>233</v>
@@ -11904,13 +11912,13 @@
       <c r="BC51" s="196" t="s">
         <v>240</v>
       </c>
-      <c r="BD51" s="271"/>
+      <c r="BD51" s="270"/>
       <c r="BE51" s="221"/>
       <c r="BF51" s="243" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="BG51" s="243" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="BH51" s="189"/>
       <c r="BI51" s="211" t="s">
@@ -11928,15 +11936,15 @@
       <c r="BM51" s="196" t="s">
         <v>258</v>
       </c>
-      <c r="BN51" s="350"/>
+      <c r="BN51" s="349"/>
       <c r="BO51" s="224"/>
     </row>
     <row r="52" spans="1:77" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="79"/>
       <c r="B52" s="79"/>
-      <c r="E52" s="344"/>
-      <c r="F52" s="345"/>
-      <c r="G52" s="346"/>
+      <c r="E52" s="343"/>
+      <c r="F52" s="344"/>
+      <c r="G52" s="345"/>
       <c r="H52" s="31"/>
       <c r="I52" s="31"/>
       <c r="J52" s="30"/>
@@ -11944,21 +11952,21 @@
       <c r="L52" s="31"/>
       <c r="M52" s="31"/>
       <c r="N52" s="33"/>
-      <c r="O52" s="306"/>
-      <c r="P52" s="306"/>
-      <c r="Q52" s="306"/>
-      <c r="R52" s="306"/>
-      <c r="S52" s="306"/>
-      <c r="T52" s="306"/>
-      <c r="U52" s="307"/>
+      <c r="O52" s="305"/>
+      <c r="P52" s="305"/>
+      <c r="Q52" s="305"/>
+      <c r="R52" s="305"/>
+      <c r="S52" s="305"/>
+      <c r="T52" s="305"/>
+      <c r="U52" s="306"/>
       <c r="V52" s="36"/>
       <c r="W52" s="14"/>
       <c r="X52" s="14"/>
       <c r="Y52" s="14"/>
       <c r="Z52" s="51"/>
-      <c r="AA52" s="265">
+      <c r="AA52" s="264">
         <f>COUNTA(AV55:BE55)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB52" s="195">
         <f>COUNTA(AB30:AI49,AB3:AI28)</f>
@@ -11970,15 +11978,15 @@
       </c>
       <c r="AD52" s="195">
         <f>COUNTA(AV30:BC53,AV3:BC28)</f>
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AE52" s="195">
         <f>COUNTA(BF30:BM57,BF3:BM28)</f>
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AF52" s="242">
         <f>SUM(AA52:AE52)+AJ52</f>
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG52" s="255">
         <f>COUNTIF( $AV$3:$BC$53,"*401*") + COUNTIF($AB$3:$AS$51,"*401*")+ COUNTIF($AV$55:$BD$55,"*401*") +COUNTIF($BF$3:$BM$57,"*401*") -1</f>
@@ -11990,7 +11998,7 @@
       </c>
       <c r="AI52" s="253">
         <f>COUNTIF( $AV$3:$BC$53,"*403*") + COUNTIF($AB$3:$AS$51,"*403*")+ COUNTIF($AV$55:$BD$55,"*403*") +COUNTIF($BF$3:$BM$57,"*403*") -1</f>
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AJ52" s="242">
         <f>14*7</f>
@@ -12031,7 +12039,7 @@
       <c r="BA52" s="204"/>
       <c r="BB52" s="204"/>
       <c r="BC52" s="204"/>
-      <c r="BD52" s="270" t="s">
+      <c r="BD52" s="269" t="s">
         <v>329</v>
       </c>
       <c r="BE52" s="222" t="s">
@@ -12045,7 +12053,7 @@
       <c r="BK52" s="204"/>
       <c r="BL52" s="204"/>
       <c r="BM52" s="204"/>
-      <c r="BN52" s="406" t="s">
+      <c r="BN52" s="405" t="s">
         <v>301</v>
       </c>
       <c r="BO52" s="224"/>
@@ -12053,9 +12061,9 @@
     <row r="53" spans="1:77" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="96"/>
       <c r="B53" s="96"/>
-      <c r="E53" s="344"/>
-      <c r="F53" s="345"/>
-      <c r="G53" s="346"/>
+      <c r="E53" s="343"/>
+      <c r="F53" s="344"/>
+      <c r="G53" s="345"/>
       <c r="H53" s="31"/>
       <c r="I53" s="31"/>
       <c r="J53" s="30"/>
@@ -12063,13 +12071,13 @@
       <c r="L53" s="31"/>
       <c r="M53" s="31"/>
       <c r="N53" s="33"/>
-      <c r="O53" s="306"/>
-      <c r="P53" s="306"/>
-      <c r="Q53" s="306"/>
-      <c r="R53" s="306"/>
-      <c r="S53" s="306"/>
-      <c r="T53" s="306"/>
-      <c r="U53" s="307"/>
+      <c r="O53" s="305"/>
+      <c r="P53" s="305"/>
+      <c r="Q53" s="305"/>
+      <c r="R53" s="305"/>
+      <c r="S53" s="305"/>
+      <c r="T53" s="305"/>
+      <c r="U53" s="306"/>
       <c r="V53" s="36"/>
       <c r="W53" s="14"/>
       <c r="X53" s="14"/>
@@ -12090,7 +12098,7 @@
       <c r="BC53" s="196" t="s">
         <v>245</v>
       </c>
-      <c r="BD53" s="270"/>
+      <c r="BD53" s="269"/>
       <c r="BE53" s="222"/>
       <c r="BF53" s="211" t="s">
         <v>241</v>
@@ -12114,15 +12122,15 @@
       <c r="BM53" s="196" t="s">
         <v>93</v>
       </c>
-      <c r="BN53" s="406"/>
+      <c r="BN53" s="405"/>
       <c r="BO53" s="224"/>
     </row>
     <row r="54" spans="1:77" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="96"/>
       <c r="B54" s="96"/>
-      <c r="E54" s="344"/>
-      <c r="F54" s="345"/>
-      <c r="G54" s="346"/>
+      <c r="E54" s="343"/>
+      <c r="F54" s="344"/>
+      <c r="G54" s="345"/>
       <c r="H54" s="31"/>
       <c r="I54" s="31"/>
       <c r="J54" s="30"/>
@@ -12130,13 +12138,13 @@
       <c r="L54" s="31"/>
       <c r="M54" s="31"/>
       <c r="N54" s="33"/>
-      <c r="O54" s="306"/>
-      <c r="P54" s="306"/>
-      <c r="Q54" s="306"/>
-      <c r="R54" s="306"/>
-      <c r="S54" s="306"/>
-      <c r="T54" s="306"/>
-      <c r="U54" s="307"/>
+      <c r="O54" s="305"/>
+      <c r="P54" s="305"/>
+      <c r="Q54" s="305"/>
+      <c r="R54" s="305"/>
+      <c r="S54" s="305"/>
+      <c r="T54" s="305"/>
+      <c r="U54" s="306"/>
       <c r="V54" s="36"/>
       <c r="W54" s="14"/>
       <c r="X54" s="14"/>
@@ -12188,7 +12196,7 @@
       <c r="BK54" s="188"/>
       <c r="BL54" s="188"/>
       <c r="BM54" s="188"/>
-      <c r="BN54" s="350" t="s">
+      <c r="BN54" s="349" t="s">
         <v>302</v>
       </c>
       <c r="BO54" s="225"/>
@@ -12206,9 +12214,9 @@
     <row r="55" spans="1:77" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="96"/>
       <c r="B55" s="96"/>
-      <c r="E55" s="344"/>
-      <c r="F55" s="345"/>
-      <c r="G55" s="346"/>
+      <c r="E55" s="343"/>
+      <c r="F55" s="344"/>
+      <c r="G55" s="345"/>
       <c r="H55" s="31"/>
       <c r="I55" s="31"/>
       <c r="J55" s="30"/>
@@ -12216,13 +12224,13 @@
       <c r="L55" s="31"/>
       <c r="M55" s="31"/>
       <c r="N55" s="33"/>
-      <c r="O55" s="306"/>
-      <c r="P55" s="306"/>
-      <c r="Q55" s="306"/>
-      <c r="R55" s="306"/>
-      <c r="S55" s="306"/>
-      <c r="T55" s="306"/>
-      <c r="U55" s="307"/>
+      <c r="O55" s="305"/>
+      <c r="P55" s="305"/>
+      <c r="Q55" s="305"/>
+      <c r="R55" s="305"/>
+      <c r="S55" s="305"/>
+      <c r="T55" s="305"/>
+      <c r="U55" s="306"/>
       <c r="V55" s="36"/>
       <c r="W55" s="14"/>
       <c r="X55" s="14"/>
@@ -12235,14 +12243,12 @@
       <c r="AU55" s="192" t="s">
         <v>274</v>
       </c>
-      <c r="AV55" s="261" t="s">
-        <v>627</v>
-      </c>
+      <c r="AV55" s="193"/>
       <c r="AW55" s="252" t="s">
         <v>253</v>
       </c>
-      <c r="AX55" s="269" t="s">
-        <v>649</v>
+      <c r="AX55" s="268" t="s">
+        <v>648</v>
       </c>
       <c r="AY55" s="193"/>
       <c r="AZ55" s="193"/>
@@ -12265,15 +12271,15 @@
       <c r="BK55" s="189"/>
       <c r="BL55" s="189"/>
       <c r="BM55" s="189"/>
-      <c r="BN55" s="350"/>
+      <c r="BN55" s="349"/>
       <c r="BO55" s="224"/>
     </row>
     <row r="56" spans="1:77" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="96"/>
       <c r="B56" s="96"/>
-      <c r="E56" s="344"/>
-      <c r="F56" s="345"/>
-      <c r="G56" s="346"/>
+      <c r="E56" s="343"/>
+      <c r="F56" s="344"/>
+      <c r="G56" s="345"/>
       <c r="H56" s="31"/>
       <c r="I56" s="31"/>
       <c r="J56" s="30"/>
@@ -12281,13 +12287,13 @@
       <c r="L56" s="31"/>
       <c r="M56" s="31"/>
       <c r="N56" s="33"/>
-      <c r="O56" s="306"/>
-      <c r="P56" s="306"/>
-      <c r="Q56" s="306"/>
-      <c r="R56" s="306"/>
-      <c r="S56" s="306"/>
-      <c r="T56" s="306"/>
-      <c r="U56" s="307"/>
+      <c r="O56" s="305"/>
+      <c r="P56" s="305"/>
+      <c r="Q56" s="305"/>
+      <c r="R56" s="305"/>
+      <c r="S56" s="305"/>
+      <c r="T56" s="305"/>
+      <c r="U56" s="306"/>
       <c r="V56" s="36"/>
       <c r="W56" s="14"/>
       <c r="X56" s="14"/>
@@ -12306,7 +12312,7 @@
       <c r="BK56" s="204"/>
       <c r="BL56" s="204"/>
       <c r="BM56" s="204"/>
-      <c r="BN56" s="351" t="s">
+      <c r="BN56" s="350" t="s">
         <v>303</v>
       </c>
       <c r="BO56" s="224"/>
@@ -12314,9 +12320,9 @@
     <row r="57" spans="1:77" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="96"/>
       <c r="B57" s="96"/>
-      <c r="E57" s="347"/>
-      <c r="F57" s="348"/>
-      <c r="G57" s="349"/>
+      <c r="E57" s="346"/>
+      <c r="F57" s="347"/>
+      <c r="G57" s="348"/>
       <c r="H57" s="31"/>
       <c r="I57" s="31"/>
       <c r="J57" s="30"/>
@@ -12324,13 +12330,13 @@
       <c r="L57" s="31"/>
       <c r="M57" s="31"/>
       <c r="N57" s="33"/>
-      <c r="O57" s="309"/>
-      <c r="P57" s="309"/>
-      <c r="Q57" s="309"/>
-      <c r="R57" s="309"/>
-      <c r="S57" s="309"/>
-      <c r="T57" s="309"/>
-      <c r="U57" s="310"/>
+      <c r="O57" s="308"/>
+      <c r="P57" s="308"/>
+      <c r="Q57" s="308"/>
+      <c r="R57" s="308"/>
+      <c r="S57" s="308"/>
+      <c r="T57" s="308"/>
+      <c r="U57" s="309"/>
       <c r="V57" s="36"/>
       <c r="W57" s="14"/>
       <c r="X57" s="14"/>
@@ -12353,7 +12359,7 @@
       <c r="BK57" s="203"/>
       <c r="BL57" s="203"/>
       <c r="BM57" s="203"/>
-      <c r="BN57" s="351"/>
+      <c r="BN57" s="350"/>
       <c r="BO57" s="224"/>
     </row>
     <row r="58" spans="1:77" ht="279.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -12371,15 +12377,15 @@
       <c r="L58" s="31"/>
       <c r="M58" s="31"/>
       <c r="N58" s="33"/>
-      <c r="O58" s="302" t="s">
+      <c r="O58" s="301" t="s">
         <v>40</v>
       </c>
-      <c r="P58" s="303"/>
-      <c r="Q58" s="303"/>
-      <c r="R58" s="303"/>
-      <c r="S58" s="303"/>
-      <c r="T58" s="303"/>
-      <c r="U58" s="304"/>
+      <c r="P58" s="302"/>
+      <c r="Q58" s="302"/>
+      <c r="R58" s="302"/>
+      <c r="S58" s="302"/>
+      <c r="T58" s="302"/>
+      <c r="U58" s="303"/>
       <c r="V58" s="36"/>
       <c r="W58" s="14"/>
       <c r="X58" s="14"/>
@@ -12394,12 +12400,12 @@
       <c r="AH58" s="37"/>
       <c r="AI58" s="104"/>
       <c r="AJ58" s="104"/>
-      <c r="AK58" s="352" t="s">
+      <c r="AK58" s="351" t="s">
         <v>8</v>
       </c>
-      <c r="AL58" s="353"/>
-      <c r="AM58" s="353"/>
-      <c r="AN58" s="354"/>
+      <c r="AL58" s="352"/>
+      <c r="AM58" s="352"/>
+      <c r="AN58" s="353"/>
       <c r="AO58" s="105"/>
       <c r="AP58" s="105"/>
       <c r="AQ58" s="105"/>
@@ -12442,13 +12448,13 @@
       <c r="L59" s="31"/>
       <c r="M59" s="31"/>
       <c r="N59" s="33"/>
-      <c r="O59" s="305"/>
-      <c r="P59" s="306"/>
-      <c r="Q59" s="306"/>
-      <c r="R59" s="306"/>
-      <c r="S59" s="306"/>
-      <c r="T59" s="306"/>
-      <c r="U59" s="307"/>
+      <c r="O59" s="304"/>
+      <c r="P59" s="305"/>
+      <c r="Q59" s="305"/>
+      <c r="R59" s="305"/>
+      <c r="S59" s="305"/>
+      <c r="T59" s="305"/>
+      <c r="U59" s="306"/>
       <c r="V59" s="36"/>
       <c r="W59" s="14"/>
       <c r="X59" s="14"/>
@@ -12557,13 +12563,13 @@
       <c r="L60" s="31"/>
       <c r="M60" s="31"/>
       <c r="N60" s="33"/>
-      <c r="O60" s="305"/>
-      <c r="P60" s="306"/>
-      <c r="Q60" s="306"/>
-      <c r="R60" s="306"/>
-      <c r="S60" s="306"/>
-      <c r="T60" s="306"/>
-      <c r="U60" s="307"/>
+      <c r="O60" s="304"/>
+      <c r="P60" s="305"/>
+      <c r="Q60" s="305"/>
+      <c r="R60" s="305"/>
+      <c r="S60" s="305"/>
+      <c r="T60" s="305"/>
+      <c r="U60" s="306"/>
       <c r="V60" s="36"/>
       <c r="W60" s="14"/>
       <c r="X60" s="14"/>
@@ -12694,13 +12700,13 @@
       <c r="L61" s="31"/>
       <c r="M61" s="31"/>
       <c r="N61" s="33"/>
-      <c r="O61" s="305"/>
-      <c r="P61" s="306"/>
-      <c r="Q61" s="306"/>
-      <c r="R61" s="306"/>
-      <c r="S61" s="306"/>
-      <c r="T61" s="306"/>
-      <c r="U61" s="307"/>
+      <c r="O61" s="304"/>
+      <c r="P61" s="305"/>
+      <c r="Q61" s="305"/>
+      <c r="R61" s="305"/>
+      <c r="S61" s="305"/>
+      <c r="T61" s="305"/>
+      <c r="U61" s="306"/>
       <c r="V61" s="36"/>
       <c r="W61" s="14"/>
       <c r="X61" s="14"/>
@@ -12716,12 +12722,12 @@
       <c r="AH61" s="98"/>
       <c r="AI61" s="107"/>
       <c r="AJ61" s="152"/>
-      <c r="AK61" s="281" t="s">
+      <c r="AK61" s="280" t="s">
         <v>9</v>
       </c>
-      <c r="AL61" s="282"/>
-      <c r="AM61" s="282"/>
-      <c r="AN61" s="283"/>
+      <c r="AL61" s="281"/>
+      <c r="AM61" s="281"/>
+      <c r="AN61" s="282"/>
       <c r="AO61" s="105"/>
       <c r="AP61" s="105"/>
       <c r="AQ61" s="182">
@@ -12757,7 +12763,7 @@
       </c>
       <c r="AY61" s="213">
         <f>COUNTIF($AB$3:$BC$55,"*402-8-*") + COUNTIF($BF$3:$BM$57,"*402-8-*")</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ61" s="213">
         <f>COUNTIF($AB$3:$BC$55,"*402-9-*") + COUNTIF($BF$3:$BM$57,"*402-9-*")</f>
@@ -12773,7 +12779,7 @@
       </c>
       <c r="BC61" s="213">
         <f>COUNTIF($AB$3:$BC$55,"*402-12-*") + COUNTIF($BF$3:$BM$57,"*402-12-*")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD61" s="213">
         <f>COUNTIF($AB$3:$BC$55,"*402-13-*") + COUNTIF($BF$3:$BM$57,"*402-13-*")</f>
@@ -12833,13 +12839,13 @@
       <c r="L62" s="31"/>
       <c r="M62" s="31"/>
       <c r="N62" s="33"/>
-      <c r="O62" s="305"/>
-      <c r="P62" s="306"/>
-      <c r="Q62" s="306"/>
-      <c r="R62" s="306"/>
-      <c r="S62" s="306"/>
-      <c r="T62" s="306"/>
-      <c r="U62" s="307"/>
+      <c r="O62" s="304"/>
+      <c r="P62" s="305"/>
+      <c r="Q62" s="305"/>
+      <c r="R62" s="305"/>
+      <c r="S62" s="305"/>
+      <c r="T62" s="305"/>
+      <c r="U62" s="306"/>
       <c r="V62" s="95"/>
       <c r="W62" s="14"/>
       <c r="X62" s="14"/>
@@ -12850,10 +12856,10 @@
       <c r="AH62" s="98"/>
       <c r="AI62" s="107"/>
       <c r="AJ62" s="152"/>
-      <c r="AK62" s="284"/>
-      <c r="AL62" s="285"/>
-      <c r="AM62" s="285"/>
-      <c r="AN62" s="286"/>
+      <c r="AK62" s="283"/>
+      <c r="AL62" s="284"/>
+      <c r="AM62" s="284"/>
+      <c r="AN62" s="285"/>
       <c r="AO62" s="105"/>
       <c r="AP62" s="105"/>
       <c r="AQ62" s="183">
@@ -12905,7 +12911,7 @@
       </c>
       <c r="BC62" s="212">
         <f>COUNTIF($AB$3:$BC$55,"*403-12-*") + COUNTIF($BF$3:$BM$57,"*403-12-*")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD62" s="212">
         <f>COUNTIF($AB$3:$BC$55,"*403-13-*") + COUNTIF($BF$3:$BM$57,"*403-13-*")</f>
@@ -12949,7 +12955,7 @@
       </c>
       <c r="BN62" s="186">
         <f>SUM(AR62:BM62)/(14*16)</f>
-        <v>0.9866071428571429</v>
+        <v>0.9910714285714286</v>
       </c>
     </row>
     <row r="63" spans="1:77" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -12965,13 +12971,13 @@
       <c r="L63" s="31"/>
       <c r="M63" s="31"/>
       <c r="N63" s="33"/>
-      <c r="O63" s="305"/>
-      <c r="P63" s="306"/>
-      <c r="Q63" s="306"/>
-      <c r="R63" s="306"/>
-      <c r="S63" s="306"/>
-      <c r="T63" s="306"/>
-      <c r="U63" s="307"/>
+      <c r="O63" s="304"/>
+      <c r="P63" s="305"/>
+      <c r="Q63" s="305"/>
+      <c r="R63" s="305"/>
+      <c r="S63" s="305"/>
+      <c r="T63" s="305"/>
+      <c r="U63" s="306"/>
       <c r="V63" s="95"/>
       <c r="W63" s="14"/>
       <c r="X63" s="14"/>
@@ -12982,10 +12988,10 @@
       <c r="AH63" s="98"/>
       <c r="AI63" s="107"/>
       <c r="AJ63" s="152"/>
-      <c r="AK63" s="287"/>
-      <c r="AL63" s="288"/>
-      <c r="AM63" s="288"/>
-      <c r="AN63" s="289"/>
+      <c r="AK63" s="286"/>
+      <c r="AL63" s="287"/>
+      <c r="AM63" s="287"/>
+      <c r="AN63" s="288"/>
       <c r="AO63" s="105"/>
       <c r="AP63" s="105"/>
       <c r="AQ63" s="105"/>
@@ -13006,13 +13012,13 @@
       <c r="L64" s="31"/>
       <c r="M64" s="31"/>
       <c r="N64" s="33"/>
-      <c r="O64" s="305"/>
-      <c r="P64" s="306"/>
-      <c r="Q64" s="306"/>
-      <c r="R64" s="306"/>
-      <c r="S64" s="306"/>
-      <c r="T64" s="306"/>
-      <c r="U64" s="307"/>
+      <c r="O64" s="304"/>
+      <c r="P64" s="305"/>
+      <c r="Q64" s="305"/>
+      <c r="R64" s="305"/>
+      <c r="S64" s="305"/>
+      <c r="T64" s="305"/>
+      <c r="U64" s="306"/>
       <c r="V64" s="95"/>
       <c r="W64" s="14"/>
       <c r="X64" s="14"/>
@@ -13062,13 +13068,13 @@
       <c r="L65" s="31"/>
       <c r="M65" s="31"/>
       <c r="N65" s="33"/>
-      <c r="O65" s="305"/>
-      <c r="P65" s="306"/>
-      <c r="Q65" s="306"/>
-      <c r="R65" s="306"/>
-      <c r="S65" s="306"/>
-      <c r="T65" s="306"/>
-      <c r="U65" s="307"/>
+      <c r="O65" s="304"/>
+      <c r="P65" s="305"/>
+      <c r="Q65" s="305"/>
+      <c r="R65" s="305"/>
+      <c r="S65" s="305"/>
+      <c r="T65" s="305"/>
+      <c r="U65" s="306"/>
       <c r="V65" s="95"/>
       <c r="W65" s="14"/>
       <c r="X65" s="14"/>
@@ -13117,13 +13123,13 @@
       <c r="L66" s="31"/>
       <c r="M66" s="31"/>
       <c r="N66" s="33"/>
-      <c r="O66" s="305"/>
-      <c r="P66" s="306"/>
-      <c r="Q66" s="306"/>
-      <c r="R66" s="306"/>
-      <c r="S66" s="306"/>
-      <c r="T66" s="306"/>
-      <c r="U66" s="307"/>
+      <c r="O66" s="304"/>
+      <c r="P66" s="305"/>
+      <c r="Q66" s="305"/>
+      <c r="R66" s="305"/>
+      <c r="S66" s="305"/>
+      <c r="T66" s="305"/>
+      <c r="U66" s="306"/>
       <c r="V66" s="102"/>
       <c r="W66" s="103"/>
       <c r="X66" s="14"/>
@@ -13134,21 +13140,21 @@
       <c r="AH66" s="98"/>
       <c r="AI66" s="98"/>
       <c r="AJ66" s="98"/>
-      <c r="AK66" s="290" t="s">
+      <c r="AK66" s="289" t="s">
         <v>10</v>
       </c>
-      <c r="AL66" s="291"/>
-      <c r="AM66" s="291"/>
-      <c r="AN66" s="291"/>
-      <c r="AO66" s="291"/>
-      <c r="AP66" s="292"/>
+      <c r="AL66" s="290"/>
+      <c r="AM66" s="290"/>
+      <c r="AN66" s="290"/>
+      <c r="AO66" s="290"/>
+      <c r="AP66" s="291"/>
       <c r="AQ66" s="105"/>
       <c r="AR66" s="40"/>
-      <c r="AS66" s="299" t="s">
+      <c r="AS66" s="298" t="s">
         <v>0</v>
       </c>
       <c r="AT66" s="173"/>
-      <c r="AU66" s="299" t="s">
+      <c r="AU66" s="298" t="s">
         <v>1</v>
       </c>
       <c r="AW66" s="170"/>
@@ -13182,13 +13188,13 @@
       <c r="L67" s="31"/>
       <c r="M67" s="31"/>
       <c r="N67" s="33"/>
-      <c r="O67" s="305"/>
-      <c r="P67" s="306"/>
-      <c r="Q67" s="306"/>
-      <c r="R67" s="306"/>
-      <c r="S67" s="306"/>
-      <c r="T67" s="306"/>
-      <c r="U67" s="307"/>
+      <c r="O67" s="304"/>
+      <c r="P67" s="305"/>
+      <c r="Q67" s="305"/>
+      <c r="R67" s="305"/>
+      <c r="S67" s="305"/>
+      <c r="T67" s="305"/>
+      <c r="U67" s="306"/>
       <c r="V67" s="95"/>
       <c r="W67" s="103"/>
       <c r="X67" s="14"/>
@@ -13198,17 +13204,17 @@
       <c r="AH67" s="9"/>
       <c r="AI67" s="98"/>
       <c r="AJ67" s="98"/>
-      <c r="AK67" s="293"/>
-      <c r="AL67" s="294"/>
-      <c r="AM67" s="294"/>
-      <c r="AN67" s="294"/>
-      <c r="AO67" s="294"/>
-      <c r="AP67" s="295"/>
+      <c r="AK67" s="292"/>
+      <c r="AL67" s="293"/>
+      <c r="AM67" s="293"/>
+      <c r="AN67" s="293"/>
+      <c r="AO67" s="293"/>
+      <c r="AP67" s="294"/>
       <c r="AQ67" s="44"/>
       <c r="AR67" s="44"/>
-      <c r="AS67" s="300"/>
+      <c r="AS67" s="299"/>
       <c r="AT67" s="174"/>
-      <c r="AU67" s="300"/>
+      <c r="AU67" s="299"/>
       <c r="BC67" s="39"/>
       <c r="BE67" s="4"/>
       <c r="BF67" s="4"/>
@@ -13233,13 +13239,13 @@
       <c r="L68" s="31"/>
       <c r="M68" s="31"/>
       <c r="N68" s="33"/>
-      <c r="O68" s="305"/>
-      <c r="P68" s="306"/>
-      <c r="Q68" s="306"/>
-      <c r="R68" s="306"/>
-      <c r="S68" s="306"/>
-      <c r="T68" s="306"/>
-      <c r="U68" s="307"/>
+      <c r="O68" s="304"/>
+      <c r="P68" s="305"/>
+      <c r="Q68" s="305"/>
+      <c r="R68" s="305"/>
+      <c r="S68" s="305"/>
+      <c r="T68" s="305"/>
+      <c r="U68" s="306"/>
       <c r="V68" s="95"/>
       <c r="W68" s="103"/>
       <c r="X68" s="14"/>
@@ -13254,17 +13260,17 @@
       <c r="AH68" s="124"/>
       <c r="AI68" s="101"/>
       <c r="AJ68" s="101"/>
-      <c r="AK68" s="296"/>
-      <c r="AL68" s="297"/>
-      <c r="AM68" s="297"/>
-      <c r="AN68" s="297"/>
-      <c r="AO68" s="297"/>
-      <c r="AP68" s="298"/>
+      <c r="AK68" s="295"/>
+      <c r="AL68" s="296"/>
+      <c r="AM68" s="296"/>
+      <c r="AN68" s="296"/>
+      <c r="AO68" s="296"/>
+      <c r="AP68" s="297"/>
       <c r="AQ68" s="101"/>
       <c r="AR68" s="101"/>
-      <c r="AS68" s="301"/>
+      <c r="AS68" s="300"/>
       <c r="AT68" s="175"/>
-      <c r="AU68" s="301"/>
+      <c r="AU68" s="300"/>
       <c r="AV68" s="125"/>
       <c r="AW68" s="125"/>
       <c r="AX68" s="125"/>
@@ -13286,13 +13292,13 @@
       <c r="L69" s="31"/>
       <c r="M69" s="31"/>
       <c r="N69" s="33"/>
-      <c r="O69" s="305"/>
-      <c r="P69" s="306"/>
-      <c r="Q69" s="306"/>
-      <c r="R69" s="306"/>
-      <c r="S69" s="306"/>
-      <c r="T69" s="306"/>
-      <c r="U69" s="307"/>
+      <c r="O69" s="304"/>
+      <c r="P69" s="305"/>
+      <c r="Q69" s="305"/>
+      <c r="R69" s="305"/>
+      <c r="S69" s="305"/>
+      <c r="T69" s="305"/>
+      <c r="U69" s="306"/>
       <c r="V69" s="95"/>
       <c r="W69" s="103"/>
       <c r="X69" s="14"/>
@@ -13301,13 +13307,13 @@
       <c r="AA69" s="94"/>
       <c r="AB69" s="117"/>
       <c r="AC69" s="117"/>
-      <c r="AD69" s="273" t="s">
+      <c r="AD69" s="272" t="s">
         <v>3</v>
       </c>
-      <c r="AE69" s="274"/>
-      <c r="AF69" s="274"/>
-      <c r="AG69" s="274"/>
-      <c r="AH69" s="275"/>
+      <c r="AE69" s="273"/>
+      <c r="AF69" s="273"/>
+      <c r="AG69" s="273"/>
+      <c r="AH69" s="274"/>
       <c r="AI69" s="129"/>
       <c r="AZ69" s="130"/>
     </row>
@@ -13324,23 +13330,23 @@
       <c r="L70" s="49"/>
       <c r="M70" s="49"/>
       <c r="N70" s="109"/>
-      <c r="O70" s="308"/>
-      <c r="P70" s="309"/>
-      <c r="Q70" s="309"/>
-      <c r="R70" s="309"/>
-      <c r="S70" s="309"/>
-      <c r="T70" s="309"/>
-      <c r="U70" s="310"/>
+      <c r="O70" s="307"/>
+      <c r="P70" s="308"/>
+      <c r="Q70" s="308"/>
+      <c r="R70" s="308"/>
+      <c r="S70" s="308"/>
+      <c r="T70" s="308"/>
+      <c r="U70" s="309"/>
       <c r="V70" s="95"/>
       <c r="W70" s="103"/>
       <c r="X70" s="14"/>
       <c r="AB70" s="117"/>
       <c r="AC70" s="117"/>
-      <c r="AD70" s="276"/>
-      <c r="AE70" s="277"/>
-      <c r="AF70" s="277"/>
-      <c r="AG70" s="277"/>
-      <c r="AH70" s="278"/>
+      <c r="AD70" s="275"/>
+      <c r="AE70" s="276"/>
+      <c r="AF70" s="276"/>
+      <c r="AG70" s="276"/>
+      <c r="AH70" s="277"/>
       <c r="AL70" s="134"/>
       <c r="AM70" s="134"/>
       <c r="AN70" s="134"/>
@@ -13591,13 +13597,13 @@
       <c r="H75" s="120"/>
       <c r="I75" s="121"/>
       <c r="J75" s="122"/>
-      <c r="K75" s="317" t="s">
+      <c r="K75" s="316" t="s">
         <v>41</v>
       </c>
-      <c r="L75" s="318"/>
-      <c r="M75" s="318"/>
-      <c r="N75" s="318"/>
-      <c r="O75" s="319"/>
+      <c r="L75" s="317"/>
+      <c r="M75" s="317"/>
+      <c r="N75" s="317"/>
+      <c r="O75" s="318"/>
       <c r="P75" s="115"/>
       <c r="Q75" s="115"/>
       <c r="R75" s="115"/>
@@ -13645,28 +13651,28 @@
     </row>
     <row r="76" spans="1:65" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="9"/>
-      <c r="B76" s="326" t="s">
+      <c r="B76" s="325" t="s">
         <v>42</v>
       </c>
-      <c r="C76" s="327"/>
-      <c r="D76" s="328"/>
-      <c r="E76" s="279" t="s">
+      <c r="C76" s="326"/>
+      <c r="D76" s="327"/>
+      <c r="E76" s="278" t="s">
         <v>43</v>
       </c>
-      <c r="F76" s="280"/>
-      <c r="G76" s="333" t="s">
+      <c r="F76" s="279"/>
+      <c r="G76" s="332" t="s">
         <v>43</v>
       </c>
-      <c r="H76" s="334"/>
-      <c r="I76" s="335" t="s">
+      <c r="H76" s="333"/>
+      <c r="I76" s="334" t="s">
         <v>44</v>
       </c>
-      <c r="J76" s="336"/>
-      <c r="K76" s="320"/>
-      <c r="L76" s="321"/>
-      <c r="M76" s="321"/>
-      <c r="N76" s="321"/>
-      <c r="O76" s="322"/>
+      <c r="J76" s="335"/>
+      <c r="K76" s="319"/>
+      <c r="L76" s="320"/>
+      <c r="M76" s="320"/>
+      <c r="N76" s="320"/>
+      <c r="O76" s="321"/>
       <c r="P76" s="115"/>
       <c r="Q76" s="115"/>
       <c r="R76" s="115"/>
@@ -13711,27 +13717,27 @@
       <c r="BJ76" s="144"/>
       <c r="BK76" s="144"/>
       <c r="BL76" s="144"/>
-      <c r="BM76" s="355"/>
+      <c r="BM76" s="354"/>
     </row>
     <row r="77" spans="1:65" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B77" s="329"/>
-      <c r="C77" s="327"/>
-      <c r="D77" s="328"/>
-      <c r="E77" s="279" t="s">
+      <c r="B77" s="328"/>
+      <c r="C77" s="326"/>
+      <c r="D77" s="327"/>
+      <c r="E77" s="278" t="s">
         <v>43</v>
       </c>
-      <c r="F77" s="339"/>
-      <c r="G77" s="279" t="s">
+      <c r="F77" s="338"/>
+      <c r="G77" s="278" t="s">
         <v>43</v>
       </c>
-      <c r="H77" s="339"/>
-      <c r="I77" s="335"/>
-      <c r="J77" s="336"/>
-      <c r="K77" s="320"/>
-      <c r="L77" s="321"/>
-      <c r="M77" s="321"/>
-      <c r="N77" s="321"/>
-      <c r="O77" s="322"/>
+      <c r="H77" s="338"/>
+      <c r="I77" s="334"/>
+      <c r="J77" s="335"/>
+      <c r="K77" s="319"/>
+      <c r="L77" s="320"/>
+      <c r="M77" s="320"/>
+      <c r="N77" s="320"/>
+      <c r="O77" s="321"/>
       <c r="P77" s="115"/>
       <c r="Q77" s="115"/>
       <c r="R77" s="115"/>
@@ -13776,28 +13782,28 @@
       <c r="BJ77" s="144"/>
       <c r="BK77" s="144"/>
       <c r="BL77" s="144"/>
-      <c r="BM77" s="355"/>
+      <c r="BM77" s="354"/>
     </row>
     <row r="78" spans="1:65" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="9"/>
-      <c r="B78" s="330"/>
-      <c r="C78" s="331"/>
-      <c r="D78" s="332"/>
-      <c r="E78" s="279" t="s">
+      <c r="B78" s="329"/>
+      <c r="C78" s="330"/>
+      <c r="D78" s="331"/>
+      <c r="E78" s="278" t="s">
         <v>45</v>
       </c>
-      <c r="F78" s="280"/>
-      <c r="G78" s="279" t="s">
+      <c r="F78" s="279"/>
+      <c r="G78" s="278" t="s">
         <v>46</v>
       </c>
-      <c r="H78" s="280"/>
-      <c r="I78" s="337"/>
-      <c r="J78" s="338"/>
-      <c r="K78" s="323"/>
-      <c r="L78" s="324"/>
-      <c r="M78" s="324"/>
-      <c r="N78" s="324"/>
-      <c r="O78" s="325"/>
+      <c r="H78" s="279"/>
+      <c r="I78" s="336"/>
+      <c r="J78" s="337"/>
+      <c r="K78" s="322"/>
+      <c r="L78" s="323"/>
+      <c r="M78" s="323"/>
+      <c r="N78" s="323"/>
+      <c r="O78" s="324"/>
       <c r="P78" s="131"/>
       <c r="Q78" s="131"/>
       <c r="R78" s="131"/>
@@ -13842,7 +13848,7 @@
       <c r="BJ78" s="144"/>
       <c r="BK78" s="144"/>
       <c r="BL78" s="144"/>
-      <c r="BM78" s="355"/>
+      <c r="BM78" s="354"/>
     </row>
     <row r="79" spans="1:65" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="135"/>
@@ -13905,7 +13911,7 @@
       <c r="BL79" s="144"/>
     </row>
     <row r="80" spans="1:65" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="272"/>
+      <c r="A80" s="271"/>
       <c r="B80" s="9"/>
       <c r="C80" s="9"/>
       <c r="D80" s="9"/>
@@ -13913,15 +13919,15 @@
       <c r="F80" s="9"/>
       <c r="G80" s="43"/>
       <c r="K80" s="41"/>
-      <c r="R80" s="315"/>
-      <c r="S80" s="315"/>
-      <c r="T80" s="315"/>
-      <c r="U80" s="315"/>
-      <c r="V80" s="315"/>
-      <c r="W80" s="315"/>
-      <c r="X80" s="315"/>
-      <c r="Y80" s="315"/>
-      <c r="Z80" s="315"/>
+      <c r="R80" s="314"/>
+      <c r="S80" s="314"/>
+      <c r="T80" s="314"/>
+      <c r="U80" s="314"/>
+      <c r="V80" s="314"/>
+      <c r="W80" s="314"/>
+      <c r="X80" s="314"/>
+      <c r="Y80" s="314"/>
+      <c r="Z80" s="314"/>
       <c r="AB80" s="101"/>
       <c r="AC80" s="101"/>
       <c r="AH80" s="145"/>
@@ -13957,7 +13963,7 @@
       <c r="BL80" s="144"/>
     </row>
     <row r="81" spans="1:64" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="272"/>
+      <c r="A81" s="271"/>
       <c r="B81" s="9"/>
       <c r="C81" s="9"/>
       <c r="D81" s="9"/>
@@ -13965,15 +13971,15 @@
       <c r="F81" s="9"/>
       <c r="G81" s="43"/>
       <c r="K81" s="41"/>
-      <c r="R81" s="316"/>
-      <c r="S81" s="316"/>
-      <c r="T81" s="316"/>
-      <c r="U81" s="316"/>
-      <c r="V81" s="316"/>
-      <c r="W81" s="316"/>
-      <c r="X81" s="316"/>
-      <c r="Y81" s="316"/>
-      <c r="Z81" s="316"/>
+      <c r="R81" s="315"/>
+      <c r="S81" s="315"/>
+      <c r="T81" s="315"/>
+      <c r="U81" s="315"/>
+      <c r="V81" s="315"/>
+      <c r="W81" s="315"/>
+      <c r="X81" s="315"/>
+      <c r="Y81" s="315"/>
+      <c r="Z81" s="315"/>
       <c r="AB81" s="163"/>
       <c r="AC81" s="161"/>
       <c r="AD81" s="161"/>
@@ -14013,18 +14019,18 @@
       <c r="BL81" s="144"/>
     </row>
     <row r="82" spans="1:64" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="272"/>
+      <c r="A82" s="271"/>
       <c r="H82" s="148"/>
       <c r="I82" s="148"/>
       <c r="J82" s="148"/>
       <c r="K82" s="92"/>
       <c r="L82" s="92"/>
-      <c r="R82" s="340"/>
-      <c r="S82" s="341"/>
-      <c r="T82" s="342"/>
-      <c r="U82" s="343"/>
-      <c r="V82" s="342"/>
-      <c r="W82" s="343"/>
+      <c r="R82" s="339"/>
+      <c r="S82" s="340"/>
+      <c r="T82" s="341"/>
+      <c r="U82" s="342"/>
+      <c r="V82" s="341"/>
+      <c r="W82" s="342"/>
       <c r="AB82" s="167"/>
       <c r="AC82" s="165"/>
       <c r="AD82" s="165"/>
@@ -14075,16 +14081,16 @@
       <c r="J83" s="92"/>
       <c r="K83" s="23"/>
       <c r="L83" s="23"/>
-      <c r="R83" s="311"/>
-      <c r="S83" s="312"/>
-      <c r="T83" s="311"/>
-      <c r="U83" s="312"/>
-      <c r="V83" s="313"/>
-      <c r="W83" s="314"/>
+      <c r="R83" s="310"/>
+      <c r="S83" s="311"/>
+      <c r="T83" s="310"/>
+      <c r="U83" s="311"/>
+      <c r="V83" s="312"/>
+      <c r="W83" s="313"/>
       <c r="X83" s="3"/>
     </row>
     <row r="84" spans="1:64" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="272"/>
+      <c r="A84" s="271"/>
       <c r="B84" s="92"/>
       <c r="C84" s="92"/>
       <c r="D84" s="92"/>
@@ -14101,18 +14107,18 @@
       <c r="O84" s="151"/>
       <c r="P84" s="115"/>
       <c r="Q84" s="23"/>
-      <c r="R84" s="311"/>
-      <c r="S84" s="312"/>
-      <c r="T84" s="311"/>
-      <c r="U84" s="312"/>
-      <c r="V84" s="311"/>
-      <c r="W84" s="312"/>
+      <c r="R84" s="310"/>
+      <c r="S84" s="311"/>
+      <c r="T84" s="310"/>
+      <c r="U84" s="311"/>
+      <c r="V84" s="310"/>
+      <c r="W84" s="311"/>
       <c r="X84" s="11"/>
-      <c r="Y84" s="311"/>
-      <c r="Z84" s="312"/>
+      <c r="Y84" s="310"/>
+      <c r="Z84" s="311"/>
     </row>
     <row r="85" spans="1:64" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="272"/>
+      <c r="A85" s="271"/>
       <c r="B85" s="44"/>
       <c r="C85" s="44"/>
       <c r="D85" s="44"/>
@@ -14130,17 +14136,17 @@
       <c r="P85" s="23"/>
       <c r="Q85" s="23"/>
       <c r="R85" s="153"/>
-      <c r="S85" s="311"/>
-      <c r="T85" s="312"/>
+      <c r="S85" s="310"/>
+      <c r="T85" s="311"/>
       <c r="U85" s="154"/>
-      <c r="V85" s="313"/>
-      <c r="W85" s="313"/>
-      <c r="X85" s="313"/>
-      <c r="Y85" s="313"/>
+      <c r="V85" s="312"/>
+      <c r="W85" s="312"/>
+      <c r="X85" s="312"/>
+      <c r="Y85" s="312"/>
       <c r="Z85" s="155"/>
     </row>
     <row r="86" spans="1:64" ht="186" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="272"/>
+      <c r="A86" s="271"/>
       <c r="B86" s="44"/>
       <c r="C86" s="44"/>
       <c r="D86" s="44"/>
@@ -14184,11 +14190,11 @@
       <c r="W87" s="99"/>
     </row>
     <row r="88" spans="1:64" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E88" s="272"/>
+      <c r="E88" s="271"/>
       <c r="F88" s="83"/>
-      <c r="G88" s="272"/>
-      <c r="H88" s="272"/>
-      <c r="I88" s="272"/>
+      <c r="G88" s="271"/>
+      <c r="H88" s="271"/>
+      <c r="I88" s="271"/>
       <c r="J88" s="99"/>
       <c r="K88" s="99"/>
       <c r="L88" s="99"/>
@@ -14205,11 +14211,11 @@
       <c r="W88" s="99"/>
     </row>
     <row r="89" spans="1:64" ht="186" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E89" s="272"/>
+      <c r="E89" s="271"/>
       <c r="F89" s="83"/>
-      <c r="G89" s="272"/>
-      <c r="H89" s="272"/>
-      <c r="I89" s="272"/>
+      <c r="G89" s="271"/>
+      <c r="H89" s="271"/>
+      <c r="I89" s="271"/>
       <c r="J89" s="99"/>
       <c r="K89" s="99"/>
       <c r="L89" s="99"/>
@@ -14230,11 +14236,11 @@
       <c r="AA89" s="162"/>
     </row>
     <row r="90" spans="1:64" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E90" s="272"/>
+      <c r="E90" s="271"/>
       <c r="F90" s="83"/>
-      <c r="G90" s="272"/>
-      <c r="H90" s="272"/>
-      <c r="I90" s="272"/>
+      <c r="G90" s="271"/>
+      <c r="H90" s="271"/>
+      <c r="I90" s="271"/>
       <c r="J90" s="99"/>
       <c r="K90" s="99"/>
       <c r="L90" s="99"/>
@@ -14447,6 +14453,6 @@
   <phoneticPr fontId="21" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="12" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="8" scale="18" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\모듈러사업2실\★ 300. 제1공장_마감관리팀\350. 마감진행현황\BH(수정)\2026년 10월 BH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B6BF2EF-9FB4-43F3-8DED-A7FD8FD04C79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69B8E688-9204-4517-A9C3-88B6792EEC56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="788" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="679">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="682">
   <si>
     <t>공업화 주택 샘플</t>
   </si>
@@ -4289,6 +4289,24 @@
     <t>402-7-5/
 36SB01
 2026-10-20</t>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <t>402-10-12/
+26SA02
+2026-10-21</t>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <t>402-9-6/
+36SB02
+2026-10-21</t>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <t>402-9-4/
+36SB42
+2026-10-21</t>
     <phoneticPr fontId="21" type="noConversion"/>
   </si>
 </sst>
@@ -6280,9 +6298,6 @@
     <xf numFmtId="0" fontId="48" fillId="16" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="18" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="16" borderId="37" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6304,13 +6319,478 @@
     <xf numFmtId="0" fontId="42" fillId="22" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="48" fillId="16" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="16" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="20" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="21" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="22" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="23" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="19" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="24" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="16" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="14" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="18" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="15" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="17" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="16" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="14" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="18" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="17" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="8" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="3" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="12" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="4" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="14" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="16" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="14" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="3" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="7" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="49" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="6" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="11" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="12" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="4" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="18" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="17" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="16" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="14" borderId="13" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="14" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="16" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="14" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="14" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="14" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="6" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="17" borderId="8" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6320,468 +6800,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="17" borderId="3" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="16" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="14" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="14" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="14" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="14" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="6" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="3" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="7" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="6" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="11" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="12" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="4" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="18" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="17" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="49" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="18" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="15" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="17" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="16" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="14" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="16" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="14" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="8" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="3" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="12" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="4" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="14" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="16" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="14" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="18" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="17" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="20" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="21" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="22" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="23" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="19" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="24" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -7257,52 +7275,52 @@
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
       <c r="AA2" s="230"/>
-      <c r="AB2" s="278" t="s">
+      <c r="AB2" s="406" t="s">
         <v>4</v>
       </c>
-      <c r="AC2" s="269"/>
-      <c r="AD2" s="269"/>
-      <c r="AE2" s="269"/>
-      <c r="AF2" s="269"/>
-      <c r="AG2" s="269"/>
-      <c r="AH2" s="269"/>
-      <c r="AI2" s="279"/>
+      <c r="AC2" s="407"/>
+      <c r="AD2" s="407"/>
+      <c r="AE2" s="407"/>
+      <c r="AF2" s="407"/>
+      <c r="AG2" s="407"/>
+      <c r="AH2" s="407"/>
+      <c r="AI2" s="408"/>
       <c r="AJ2" s="2"/>
       <c r="AK2" s="230"/>
       <c r="AL2" s="200"/>
       <c r="AM2" s="201"/>
       <c r="AN2" s="201"/>
-      <c r="AO2" s="269" t="s">
+      <c r="AO2" s="407" t="s">
         <v>5</v>
       </c>
-      <c r="AP2" s="269"/>
+      <c r="AP2" s="407"/>
       <c r="AQ2" s="201"/>
       <c r="AR2" s="201"/>
       <c r="AS2" s="202"/>
       <c r="AT2" s="2"/>
       <c r="AU2" s="226"/>
-      <c r="AV2" s="280" t="s">
+      <c r="AV2" s="409" t="s">
         <v>6</v>
       </c>
-      <c r="AW2" s="281"/>
-      <c r="AX2" s="281"/>
-      <c r="AY2" s="281"/>
-      <c r="AZ2" s="281"/>
-      <c r="BA2" s="281"/>
-      <c r="BB2" s="281"/>
-      <c r="BC2" s="282"/>
+      <c r="AW2" s="410"/>
+      <c r="AX2" s="410"/>
+      <c r="AY2" s="410"/>
+      <c r="AZ2" s="410"/>
+      <c r="BA2" s="410"/>
+      <c r="BB2" s="410"/>
+      <c r="BC2" s="411"/>
       <c r="BD2" s="190"/>
       <c r="BE2" s="220"/>
-      <c r="BF2" s="280" t="s">
+      <c r="BF2" s="409" t="s">
         <v>7</v>
       </c>
-      <c r="BG2" s="281"/>
-      <c r="BH2" s="281"/>
-      <c r="BI2" s="281"/>
-      <c r="BJ2" s="281"/>
-      <c r="BK2" s="281"/>
-      <c r="BL2" s="281"/>
-      <c r="BM2" s="282"/>
+      <c r="BG2" s="410"/>
+      <c r="BH2" s="410"/>
+      <c r="BI2" s="410"/>
+      <c r="BJ2" s="410"/>
+      <c r="BK2" s="410"/>
+      <c r="BL2" s="410"/>
+      <c r="BM2" s="411"/>
       <c r="BO2" s="224"/>
     </row>
     <row r="3" spans="1:67" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -7315,28 +7333,28 @@
       </c>
       <c r="F3" s="25"/>
       <c r="G3" s="25"/>
-      <c r="H3" s="283" t="s">
+      <c r="H3" s="412" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="284"/>
-      <c r="J3" s="283" t="s">
+      <c r="I3" s="413"/>
+      <c r="J3" s="412" t="s">
         <v>15</v>
       </c>
-      <c r="K3" s="284"/>
-      <c r="L3" s="290" t="s">
+      <c r="K3" s="413"/>
+      <c r="L3" s="414" t="s">
         <v>16</v>
       </c>
-      <c r="M3" s="290"/>
+      <c r="M3" s="414"/>
       <c r="N3" s="26"/>
-      <c r="O3" s="292" t="s">
+      <c r="O3" s="415" t="s">
         <v>17</v>
       </c>
-      <c r="P3" s="293"/>
-      <c r="Q3" s="293"/>
-      <c r="R3" s="293"/>
-      <c r="S3" s="293"/>
-      <c r="T3" s="293"/>
-      <c r="U3" s="293"/>
+      <c r="P3" s="416"/>
+      <c r="Q3" s="416"/>
+      <c r="R3" s="416"/>
+      <c r="S3" s="416"/>
+      <c r="T3" s="416"/>
+      <c r="U3" s="416"/>
       <c r="V3" s="27"/>
       <c r="W3" s="28"/>
       <c r="X3" s="28"/>
@@ -7345,10 +7363,10 @@
       <c r="AA3" s="227" t="s">
         <v>275</v>
       </c>
-      <c r="AB3" s="265" t="s">
+      <c r="AB3" s="264" t="s">
         <v>585</v>
       </c>
-      <c r="AC3" s="265" t="s">
+      <c r="AC3" s="264" t="s">
         <v>605</v>
       </c>
       <c r="AD3" s="188"/>
@@ -7412,20 +7430,20 @@
       <c r="E4" s="30"/>
       <c r="F4" s="31"/>
       <c r="G4" s="31"/>
-      <c r="H4" s="285"/>
-      <c r="I4" s="286"/>
-      <c r="J4" s="285"/>
-      <c r="K4" s="286"/>
-      <c r="L4" s="287"/>
-      <c r="M4" s="287"/>
+      <c r="H4" s="343"/>
+      <c r="I4" s="345"/>
+      <c r="J4" s="343"/>
+      <c r="K4" s="345"/>
+      <c r="L4" s="344"/>
+      <c r="M4" s="344"/>
       <c r="N4" s="33"/>
-      <c r="O4" s="294"/>
-      <c r="P4" s="295"/>
-      <c r="Q4" s="295"/>
-      <c r="R4" s="295"/>
-      <c r="S4" s="295"/>
-      <c r="T4" s="295"/>
-      <c r="U4" s="295"/>
+      <c r="O4" s="417"/>
+      <c r="P4" s="418"/>
+      <c r="Q4" s="418"/>
+      <c r="R4" s="418"/>
+      <c r="S4" s="418"/>
+      <c r="T4" s="418"/>
+      <c r="U4" s="418"/>
       <c r="V4" s="34"/>
       <c r="W4" s="14"/>
       <c r="X4" s="14"/>
@@ -7493,20 +7511,20 @@
       <c r="E5" s="30"/>
       <c r="F5" s="31"/>
       <c r="G5" s="31"/>
-      <c r="H5" s="285"/>
-      <c r="I5" s="286"/>
-      <c r="J5" s="285"/>
-      <c r="K5" s="286"/>
-      <c r="L5" s="287"/>
-      <c r="M5" s="287"/>
+      <c r="H5" s="343"/>
+      <c r="I5" s="345"/>
+      <c r="J5" s="343"/>
+      <c r="K5" s="345"/>
+      <c r="L5" s="344"/>
+      <c r="M5" s="344"/>
       <c r="N5" s="33"/>
-      <c r="O5" s="294"/>
-      <c r="P5" s="295"/>
-      <c r="Q5" s="295"/>
-      <c r="R5" s="295"/>
-      <c r="S5" s="295"/>
-      <c r="T5" s="295"/>
-      <c r="U5" s="295"/>
+      <c r="O5" s="417"/>
+      <c r="P5" s="418"/>
+      <c r="Q5" s="418"/>
+      <c r="R5" s="418"/>
+      <c r="S5" s="418"/>
+      <c r="T5" s="418"/>
+      <c r="U5" s="418"/>
       <c r="V5" s="34"/>
       <c r="W5" s="14"/>
       <c r="X5" s="14"/>
@@ -7515,10 +7533,10 @@
       <c r="AA5" s="228" t="s">
         <v>275</v>
       </c>
-      <c r="AB5" s="265" t="s">
+      <c r="AB5" s="264" t="s">
         <v>606</v>
       </c>
-      <c r="AC5" s="265" t="s">
+      <c r="AC5" s="264" t="s">
         <v>612</v>
       </c>
       <c r="AD5" s="204"/>
@@ -7529,7 +7547,7 @@
       </c>
       <c r="AH5" s="204"/>
       <c r="AI5" s="204"/>
-      <c r="AJ5" s="271" t="s">
+      <c r="AJ5" s="269" t="s">
         <v>507</v>
       </c>
       <c r="AK5" s="228" t="s">
@@ -7543,7 +7561,7 @@
       <c r="AQ5" s="204"/>
       <c r="AR5" s="204"/>
       <c r="AS5" s="204"/>
-      <c r="AT5" s="271" t="s">
+      <c r="AT5" s="269" t="s">
         <v>331</v>
       </c>
       <c r="AU5" s="228" t="s">
@@ -7557,7 +7575,7 @@
       <c r="BA5" s="204"/>
       <c r="BB5" s="204"/>
       <c r="BC5" s="204"/>
-      <c r="BD5" s="271" t="s">
+      <c r="BD5" s="269" t="s">
         <v>305</v>
       </c>
       <c r="BE5" s="222" t="s">
@@ -7571,7 +7589,7 @@
       <c r="BK5" s="204"/>
       <c r="BL5" s="204"/>
       <c r="BM5" s="204"/>
-      <c r="BN5" s="271" t="s">
+      <c r="BN5" s="269" t="s">
         <v>277</v>
       </c>
       <c r="BO5" s="224"/>
@@ -7582,20 +7600,20 @@
       <c r="E6" s="30"/>
       <c r="F6" s="31"/>
       <c r="G6" s="31"/>
-      <c r="H6" s="285"/>
-      <c r="I6" s="286"/>
-      <c r="J6" s="285"/>
-      <c r="K6" s="286"/>
-      <c r="L6" s="287"/>
-      <c r="M6" s="287"/>
+      <c r="H6" s="343"/>
+      <c r="I6" s="345"/>
+      <c r="J6" s="343"/>
+      <c r="K6" s="345"/>
+      <c r="L6" s="344"/>
+      <c r="M6" s="344"/>
       <c r="N6" s="33"/>
-      <c r="O6" s="294"/>
-      <c r="P6" s="295"/>
-      <c r="Q6" s="295"/>
-      <c r="R6" s="295"/>
-      <c r="S6" s="295"/>
-      <c r="T6" s="295"/>
-      <c r="U6" s="295"/>
+      <c r="O6" s="417"/>
+      <c r="P6" s="418"/>
+      <c r="Q6" s="418"/>
+      <c r="R6" s="418"/>
+      <c r="S6" s="418"/>
+      <c r="T6" s="418"/>
+      <c r="U6" s="418"/>
       <c r="V6" s="34"/>
       <c r="W6" s="14"/>
       <c r="X6" s="14"/>
@@ -7624,7 +7642,7 @@
       <c r="AI6" s="235" t="s">
         <v>582</v>
       </c>
-      <c r="AJ6" s="271"/>
+      <c r="AJ6" s="269"/>
       <c r="AK6" s="228"/>
       <c r="AL6" s="203"/>
       <c r="AM6" s="203"/>
@@ -7634,7 +7652,7 @@
       <c r="AQ6" s="203"/>
       <c r="AR6" s="203"/>
       <c r="AS6" s="203"/>
-      <c r="AT6" s="271"/>
+      <c r="AT6" s="269"/>
       <c r="AU6" s="228"/>
       <c r="AV6" s="203"/>
       <c r="AW6" s="203"/>
@@ -7644,7 +7662,7 @@
       <c r="BA6" s="203"/>
       <c r="BB6" s="203"/>
       <c r="BC6" s="203"/>
-      <c r="BD6" s="271"/>
+      <c r="BD6" s="269"/>
       <c r="BE6" s="222"/>
       <c r="BF6" s="211" t="s">
         <v>409</v>
@@ -7658,7 +7676,7 @@
       <c r="BK6" s="203"/>
       <c r="BL6" s="203"/>
       <c r="BM6" s="203"/>
-      <c r="BN6" s="271"/>
+      <c r="BN6" s="269"/>
       <c r="BO6" s="224"/>
     </row>
     <row r="7" spans="1:67" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -7670,20 +7688,20 @@
       <c r="E7" s="30"/>
       <c r="F7" s="31"/>
       <c r="G7" s="31"/>
-      <c r="H7" s="285"/>
-      <c r="I7" s="286"/>
-      <c r="J7" s="285"/>
-      <c r="K7" s="286"/>
-      <c r="L7" s="287"/>
-      <c r="M7" s="287"/>
+      <c r="H7" s="343"/>
+      <c r="I7" s="345"/>
+      <c r="J7" s="343"/>
+      <c r="K7" s="345"/>
+      <c r="L7" s="344"/>
+      <c r="M7" s="344"/>
       <c r="N7" s="33"/>
-      <c r="O7" s="296"/>
-      <c r="P7" s="297"/>
-      <c r="Q7" s="297"/>
-      <c r="R7" s="297"/>
-      <c r="S7" s="297"/>
-      <c r="T7" s="297"/>
-      <c r="U7" s="297"/>
+      <c r="O7" s="419"/>
+      <c r="P7" s="420"/>
+      <c r="Q7" s="420"/>
+      <c r="R7" s="420"/>
+      <c r="S7" s="420"/>
+      <c r="T7" s="420"/>
+      <c r="U7" s="420"/>
       <c r="V7" s="34"/>
       <c r="W7" s="14"/>
       <c r="X7" s="14"/>
@@ -7692,10 +7710,10 @@
       <c r="AA7" s="227" t="s">
         <v>275</v>
       </c>
-      <c r="AB7" s="265" t="s">
+      <c r="AB7" s="264" t="s">
         <v>613</v>
       </c>
-      <c r="AC7" s="265" t="s">
+      <c r="AC7" s="264" t="s">
         <v>614</v>
       </c>
       <c r="AD7" s="188"/>
@@ -7759,22 +7777,22 @@
       <c r="E8" s="30"/>
       <c r="F8" s="31"/>
       <c r="G8" s="31"/>
-      <c r="H8" s="285"/>
-      <c r="I8" s="286"/>
-      <c r="J8" s="285"/>
-      <c r="K8" s="286"/>
-      <c r="L8" s="287"/>
-      <c r="M8" s="287"/>
+      <c r="H8" s="343"/>
+      <c r="I8" s="345"/>
+      <c r="J8" s="343"/>
+      <c r="K8" s="345"/>
+      <c r="L8" s="344"/>
+      <c r="M8" s="344"/>
       <c r="N8" s="33"/>
-      <c r="O8" s="292" t="s">
+      <c r="O8" s="415" t="s">
         <v>18</v>
       </c>
-      <c r="P8" s="293"/>
-      <c r="Q8" s="293"/>
-      <c r="R8" s="293"/>
-      <c r="S8" s="293"/>
-      <c r="T8" s="293"/>
-      <c r="U8" s="293"/>
+      <c r="P8" s="416"/>
+      <c r="Q8" s="416"/>
+      <c r="R8" s="416"/>
+      <c r="S8" s="416"/>
+      <c r="T8" s="416"/>
+      <c r="U8" s="416"/>
       <c r="V8" s="34"/>
       <c r="W8" s="14"/>
       <c r="X8" s="14"/>
@@ -7849,20 +7867,20 @@
       <c r="E9" s="30"/>
       <c r="F9" s="31"/>
       <c r="G9" s="31"/>
-      <c r="H9" s="285"/>
-      <c r="I9" s="286"/>
-      <c r="J9" s="285"/>
-      <c r="K9" s="286"/>
-      <c r="L9" s="287"/>
-      <c r="M9" s="287"/>
+      <c r="H9" s="343"/>
+      <c r="I9" s="345"/>
+      <c r="J9" s="343"/>
+      <c r="K9" s="345"/>
+      <c r="L9" s="344"/>
+      <c r="M9" s="344"/>
       <c r="N9" s="33"/>
-      <c r="O9" s="294"/>
-      <c r="P9" s="295"/>
-      <c r="Q9" s="295"/>
-      <c r="R9" s="295"/>
-      <c r="S9" s="295"/>
-      <c r="T9" s="295"/>
-      <c r="U9" s="295"/>
+      <c r="O9" s="417"/>
+      <c r="P9" s="418"/>
+      <c r="Q9" s="418"/>
+      <c r="R9" s="418"/>
+      <c r="S9" s="418"/>
+      <c r="T9" s="418"/>
+      <c r="U9" s="418"/>
       <c r="V9" s="34"/>
       <c r="W9" s="14"/>
       <c r="X9" s="14"/>
@@ -7874,7 +7892,7 @@
       <c r="AB9" s="245" t="s">
         <v>594</v>
       </c>
-      <c r="AC9" s="265" t="s">
+      <c r="AC9" s="264" t="s">
         <v>595</v>
       </c>
       <c r="AD9" s="204"/>
@@ -7883,7 +7901,7 @@
       <c r="AG9" s="204"/>
       <c r="AH9" s="204"/>
       <c r="AI9" s="204"/>
-      <c r="AJ9" s="271" t="s">
+      <c r="AJ9" s="269" t="s">
         <v>509</v>
       </c>
       <c r="AK9" s="228" t="s">
@@ -7897,7 +7915,7 @@
       <c r="AQ9" s="204"/>
       <c r="AR9" s="204"/>
       <c r="AS9" s="204"/>
-      <c r="AT9" s="271" t="s">
+      <c r="AT9" s="269" t="s">
         <v>333</v>
       </c>
       <c r="AU9" s="228" t="s">
@@ -7912,10 +7930,10 @@
       <c r="BB9" s="197" t="s">
         <v>95</v>
       </c>
-      <c r="BC9" s="266" t="s">
+      <c r="BC9" s="265" t="s">
         <v>96</v>
       </c>
-      <c r="BD9" s="271" t="s">
+      <c r="BD9" s="269" t="s">
         <v>307</v>
       </c>
       <c r="BE9" s="222" t="s">
@@ -7933,7 +7951,7 @@
       <c r="BM9" s="197" t="s">
         <v>52</v>
       </c>
-      <c r="BN9" s="275" t="s">
+      <c r="BN9" s="425" t="s">
         <v>279</v>
       </c>
       <c r="BO9" s="224"/>
@@ -7944,24 +7962,24 @@
       </c>
       <c r="B10" s="16"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="307" t="s">
+      <c r="F10" s="351" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="308"/>
-      <c r="H10" s="287"/>
-      <c r="I10" s="286"/>
-      <c r="J10" s="285"/>
-      <c r="K10" s="286"/>
-      <c r="L10" s="287"/>
-      <c r="M10" s="287"/>
+      <c r="G10" s="353"/>
+      <c r="H10" s="344"/>
+      <c r="I10" s="345"/>
+      <c r="J10" s="343"/>
+      <c r="K10" s="345"/>
+      <c r="L10" s="344"/>
+      <c r="M10" s="344"/>
       <c r="N10" s="33"/>
-      <c r="O10" s="294"/>
-      <c r="P10" s="295"/>
-      <c r="Q10" s="295"/>
-      <c r="R10" s="295"/>
-      <c r="S10" s="295"/>
-      <c r="T10" s="295"/>
-      <c r="U10" s="295"/>
+      <c r="O10" s="417"/>
+      <c r="P10" s="418"/>
+      <c r="Q10" s="418"/>
+      <c r="R10" s="418"/>
+      <c r="S10" s="418"/>
+      <c r="T10" s="418"/>
+      <c r="U10" s="418"/>
       <c r="V10" s="34"/>
       <c r="W10" s="14"/>
       <c r="X10" s="14"/>
@@ -7988,7 +8006,7 @@
       </c>
       <c r="AH10" s="203"/>
       <c r="AI10" s="203"/>
-      <c r="AJ10" s="271"/>
+      <c r="AJ10" s="269"/>
       <c r="AK10" s="228"/>
       <c r="AL10" s="203"/>
       <c r="AM10" s="203"/>
@@ -7998,7 +8016,7 @@
       <c r="AQ10" s="203"/>
       <c r="AR10" s="203"/>
       <c r="AS10" s="203"/>
-      <c r="AT10" s="271"/>
+      <c r="AT10" s="269"/>
       <c r="AU10" s="228"/>
       <c r="AV10" s="249"/>
       <c r="AW10" s="196" t="s">
@@ -8015,10 +8033,10 @@
       <c r="BB10" s="196" t="s">
         <v>97</v>
       </c>
-      <c r="BC10" s="267" t="s">
+      <c r="BC10" s="266" t="s">
         <v>98</v>
       </c>
-      <c r="BD10" s="271"/>
+      <c r="BD10" s="269"/>
       <c r="BE10" s="222"/>
       <c r="BF10" s="238" t="s">
         <v>161</v>
@@ -8038,31 +8056,31 @@
       <c r="BM10" s="238" t="s">
         <v>164</v>
       </c>
-      <c r="BN10" s="275"/>
+      <c r="BN10" s="425"/>
       <c r="BO10" s="224"/>
     </row>
     <row r="11" spans="1:67" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6"/>
       <c r="B11" s="18"/>
       <c r="E11" s="30"/>
-      <c r="F11" s="309"/>
-      <c r="G11" s="310"/>
-      <c r="H11" s="287"/>
-      <c r="I11" s="286"/>
-      <c r="J11" s="285"/>
-      <c r="K11" s="286"/>
-      <c r="L11" s="287"/>
-      <c r="M11" s="287"/>
+      <c r="F11" s="421"/>
+      <c r="G11" s="422"/>
+      <c r="H11" s="344"/>
+      <c r="I11" s="345"/>
+      <c r="J11" s="343"/>
+      <c r="K11" s="345"/>
+      <c r="L11" s="344"/>
+      <c r="M11" s="344"/>
       <c r="N11" s="33"/>
-      <c r="O11" s="313" t="s">
+      <c r="O11" s="366" t="s">
         <v>20</v>
       </c>
-      <c r="P11" s="314"/>
-      <c r="Q11" s="314"/>
-      <c r="R11" s="314"/>
-      <c r="S11" s="314"/>
-      <c r="T11" s="314"/>
-      <c r="U11" s="315"/>
+      <c r="P11" s="367"/>
+      <c r="Q11" s="367"/>
+      <c r="R11" s="367"/>
+      <c r="S11" s="367"/>
+      <c r="T11" s="367"/>
+      <c r="U11" s="368"/>
       <c r="V11" s="34"/>
       <c r="W11" s="14"/>
       <c r="X11" s="14"/>
@@ -8072,7 +8090,7 @@
         <v>275</v>
       </c>
       <c r="AB11" s="188"/>
-      <c r="AC11" s="265" t="s">
+      <c r="AC11" s="264" t="s">
         <v>626</v>
       </c>
       <c r="AD11" s="188"/>
@@ -8137,33 +8155,33 @@
       <c r="BM11" s="197" t="s">
         <v>180</v>
       </c>
-      <c r="BN11" s="276" t="s">
+      <c r="BN11" s="349" t="s">
         <v>280</v>
       </c>
       <c r="BO11" s="224"/>
     </row>
     <row r="12" spans="1:67" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="322" t="s">
+      <c r="A12" s="375" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="323"/>
+      <c r="B12" s="376"/>
       <c r="E12" s="46"/>
-      <c r="F12" s="311"/>
-      <c r="G12" s="312"/>
-      <c r="H12" s="287"/>
-      <c r="I12" s="286"/>
-      <c r="J12" s="285"/>
-      <c r="K12" s="286"/>
-      <c r="L12" s="287"/>
-      <c r="M12" s="287"/>
+      <c r="F12" s="423"/>
+      <c r="G12" s="424"/>
+      <c r="H12" s="344"/>
+      <c r="I12" s="345"/>
+      <c r="J12" s="343"/>
+      <c r="K12" s="345"/>
+      <c r="L12" s="344"/>
+      <c r="M12" s="344"/>
       <c r="N12" s="33"/>
-      <c r="O12" s="316"/>
-      <c r="P12" s="317"/>
-      <c r="Q12" s="317"/>
-      <c r="R12" s="317"/>
-      <c r="S12" s="317"/>
-      <c r="T12" s="317"/>
-      <c r="U12" s="318"/>
+      <c r="O12" s="369"/>
+      <c r="P12" s="370"/>
+      <c r="Q12" s="370"/>
+      <c r="R12" s="370"/>
+      <c r="S12" s="370"/>
+      <c r="T12" s="370"/>
+      <c r="U12" s="371"/>
       <c r="V12" s="34"/>
       <c r="W12" s="14"/>
       <c r="X12" s="14"/>
@@ -8238,29 +8256,29 @@
       <c r="BM12" s="238" t="s">
         <v>173</v>
       </c>
-      <c r="BN12" s="276"/>
+      <c r="BN12" s="349"/>
       <c r="BO12" s="224"/>
     </row>
     <row r="13" spans="1:67" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="324"/>
-      <c r="B13" s="325"/>
+      <c r="A13" s="325"/>
+      <c r="B13" s="377"/>
       <c r="E13" s="48"/>
       <c r="F13" s="49"/>
       <c r="G13" s="49"/>
-      <c r="H13" s="285"/>
-      <c r="I13" s="286"/>
-      <c r="J13" s="285"/>
-      <c r="K13" s="286"/>
-      <c r="L13" s="287"/>
-      <c r="M13" s="287"/>
+      <c r="H13" s="343"/>
+      <c r="I13" s="345"/>
+      <c r="J13" s="343"/>
+      <c r="K13" s="345"/>
+      <c r="L13" s="344"/>
+      <c r="M13" s="344"/>
       <c r="N13" s="33"/>
-      <c r="O13" s="316"/>
-      <c r="P13" s="317"/>
-      <c r="Q13" s="317"/>
-      <c r="R13" s="317"/>
-      <c r="S13" s="317"/>
-      <c r="T13" s="317"/>
-      <c r="U13" s="318"/>
+      <c r="O13" s="369"/>
+      <c r="P13" s="370"/>
+      <c r="Q13" s="370"/>
+      <c r="R13" s="370"/>
+      <c r="S13" s="370"/>
+      <c r="T13" s="370"/>
+      <c r="U13" s="371"/>
       <c r="V13" s="34"/>
       <c r="W13" s="14"/>
       <c r="X13" s="14"/>
@@ -8277,7 +8295,7 @@
       <c r="AG13" s="204"/>
       <c r="AH13" s="204"/>
       <c r="AI13" s="204"/>
-      <c r="AJ13" s="271" t="s">
+      <c r="AJ13" s="269" t="s">
         <v>511</v>
       </c>
       <c r="AK13" s="228" t="s">
@@ -8291,7 +8309,7 @@
       <c r="AQ13" s="204"/>
       <c r="AR13" s="204"/>
       <c r="AS13" s="204"/>
-      <c r="AT13" s="271" t="s">
+      <c r="AT13" s="269" t="s">
         <v>335</v>
       </c>
       <c r="AU13" s="228" t="s">
@@ -8307,7 +8325,7 @@
       <c r="BC13" s="197" t="s">
         <v>112</v>
       </c>
-      <c r="BD13" s="271" t="s">
+      <c r="BD13" s="269" t="s">
         <v>309</v>
       </c>
       <c r="BE13" s="222" t="s">
@@ -8325,35 +8343,35 @@
       <c r="BK13" s="204"/>
       <c r="BL13" s="204"/>
       <c r="BM13" s="204"/>
-      <c r="BN13" s="277" t="s">
+      <c r="BN13" s="405" t="s">
         <v>281</v>
       </c>
       <c r="BO13" s="224"/>
     </row>
     <row r="14" spans="1:67" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="326"/>
-      <c r="B14" s="327"/>
+      <c r="A14" s="332"/>
+      <c r="B14" s="378"/>
       <c r="C14" s="50"/>
       <c r="D14" s="42"/>
-      <c r="E14" s="305" t="s">
+      <c r="E14" s="379" t="s">
         <v>22</v>
       </c>
-      <c r="F14" s="305"/>
-      <c r="G14" s="306"/>
-      <c r="H14" s="285"/>
-      <c r="I14" s="286"/>
-      <c r="J14" s="285"/>
-      <c r="K14" s="286"/>
-      <c r="L14" s="287"/>
-      <c r="M14" s="287"/>
+      <c r="F14" s="379"/>
+      <c r="G14" s="380"/>
+      <c r="H14" s="343"/>
+      <c r="I14" s="345"/>
+      <c r="J14" s="343"/>
+      <c r="K14" s="345"/>
+      <c r="L14" s="344"/>
+      <c r="M14" s="344"/>
       <c r="N14" s="33"/>
-      <c r="O14" s="319"/>
-      <c r="P14" s="320"/>
-      <c r="Q14" s="320"/>
-      <c r="R14" s="320"/>
-      <c r="S14" s="320"/>
-      <c r="T14" s="320"/>
-      <c r="U14" s="321"/>
+      <c r="O14" s="372"/>
+      <c r="P14" s="373"/>
+      <c r="Q14" s="373"/>
+      <c r="R14" s="373"/>
+      <c r="S14" s="373"/>
+      <c r="T14" s="373"/>
+      <c r="U14" s="374"/>
       <c r="V14" s="34"/>
       <c r="W14" s="14"/>
       <c r="X14" s="14"/>
@@ -8370,7 +8388,7 @@
       <c r="AG14" s="203"/>
       <c r="AH14" s="203"/>
       <c r="AI14" s="203"/>
-      <c r="AJ14" s="271"/>
+      <c r="AJ14" s="269"/>
       <c r="AK14" s="228"/>
       <c r="AL14" s="203"/>
       <c r="AM14" s="203"/>
@@ -8380,7 +8398,7 @@
       <c r="AQ14" s="203"/>
       <c r="AR14" s="203"/>
       <c r="AS14" s="203"/>
-      <c r="AT14" s="271"/>
+      <c r="AT14" s="269"/>
       <c r="AU14" s="228"/>
       <c r="AV14" s="196" t="s">
         <v>168</v>
@@ -8402,7 +8420,7 @@
       <c r="BC14" s="196" t="s">
         <v>101</v>
       </c>
-      <c r="BD14" s="271"/>
+      <c r="BD14" s="269"/>
       <c r="BE14" s="222"/>
       <c r="BF14" s="196" t="s">
         <v>175</v>
@@ -8422,33 +8440,33 @@
         <v>395</v>
       </c>
       <c r="BM14" s="203"/>
-      <c r="BN14" s="277"/>
+      <c r="BN14" s="405"/>
       <c r="BO14" s="224"/>
     </row>
     <row r="15" spans="1:67" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="322" t="s">
+      <c r="A15" s="375" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="328"/>
+      <c r="B15" s="383"/>
       <c r="C15" s="50"/>
       <c r="D15" s="52"/>
-      <c r="E15" s="302"/>
-      <c r="F15" s="302"/>
-      <c r="G15" s="303"/>
-      <c r="H15" s="285"/>
-      <c r="I15" s="286"/>
-      <c r="J15" s="285"/>
-      <c r="K15" s="286"/>
-      <c r="L15" s="287"/>
-      <c r="M15" s="287"/>
+      <c r="E15" s="381"/>
+      <c r="F15" s="381"/>
+      <c r="G15" s="382"/>
+      <c r="H15" s="343"/>
+      <c r="I15" s="345"/>
+      <c r="J15" s="343"/>
+      <c r="K15" s="345"/>
+      <c r="L15" s="344"/>
+      <c r="M15" s="344"/>
       <c r="N15" s="33"/>
-      <c r="O15" s="330"/>
-      <c r="P15" s="331"/>
-      <c r="Q15" s="331"/>
-      <c r="R15" s="331"/>
-      <c r="S15" s="331"/>
-      <c r="T15" s="331"/>
-      <c r="U15" s="332"/>
+      <c r="O15" s="385"/>
+      <c r="P15" s="386"/>
+      <c r="Q15" s="386"/>
+      <c r="R15" s="386"/>
+      <c r="S15" s="386"/>
+      <c r="T15" s="386"/>
+      <c r="U15" s="387"/>
       <c r="V15" s="27"/>
       <c r="W15" s="28"/>
       <c r="X15" s="28"/>
@@ -8511,35 +8529,35 @@
       <c r="BK15" s="188"/>
       <c r="BL15" s="188"/>
       <c r="BM15" s="188"/>
-      <c r="BN15" s="276" t="s">
+      <c r="BN15" s="349" t="s">
         <v>282</v>
       </c>
       <c r="BO15" s="224"/>
     </row>
     <row r="16" spans="1:67" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="324"/>
-      <c r="B16" s="329"/>
+      <c r="A16" s="325"/>
+      <c r="B16" s="384"/>
       <c r="C16" s="53"/>
       <c r="D16" s="52"/>
-      <c r="E16" s="305" t="s">
+      <c r="E16" s="379" t="s">
         <v>22</v>
       </c>
-      <c r="F16" s="305"/>
-      <c r="G16" s="306"/>
-      <c r="H16" s="285"/>
-      <c r="I16" s="286"/>
-      <c r="J16" s="285"/>
-      <c r="K16" s="286"/>
-      <c r="L16" s="287"/>
-      <c r="M16" s="287"/>
+      <c r="F16" s="379"/>
+      <c r="G16" s="380"/>
+      <c r="H16" s="343"/>
+      <c r="I16" s="345"/>
+      <c r="J16" s="343"/>
+      <c r="K16" s="345"/>
+      <c r="L16" s="344"/>
+      <c r="M16" s="344"/>
       <c r="N16" s="33"/>
-      <c r="O16" s="333"/>
-      <c r="P16" s="334"/>
-      <c r="Q16" s="334"/>
-      <c r="R16" s="334"/>
-      <c r="S16" s="334"/>
-      <c r="T16" s="334"/>
-      <c r="U16" s="335"/>
+      <c r="O16" s="388"/>
+      <c r="P16" s="389"/>
+      <c r="Q16" s="389"/>
+      <c r="R16" s="389"/>
+      <c r="S16" s="389"/>
+      <c r="T16" s="389"/>
+      <c r="U16" s="390"/>
       <c r="V16" s="34"/>
       <c r="W16" s="14"/>
       <c r="X16" s="40"/>
@@ -8608,31 +8626,31 @@
         <v>396</v>
       </c>
       <c r="BM16" s="189"/>
-      <c r="BN16" s="276"/>
+      <c r="BN16" s="349"/>
       <c r="BO16" s="224"/>
     </row>
     <row r="17" spans="1:70" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="326"/>
-      <c r="B17" s="327"/>
+      <c r="A17" s="332"/>
+      <c r="B17" s="378"/>
       <c r="C17" s="50"/>
       <c r="D17" s="55"/>
-      <c r="E17" s="299"/>
-      <c r="F17" s="299"/>
-      <c r="G17" s="300"/>
-      <c r="H17" s="285"/>
-      <c r="I17" s="286"/>
-      <c r="J17" s="285"/>
-      <c r="K17" s="286"/>
-      <c r="L17" s="287"/>
-      <c r="M17" s="287"/>
+      <c r="E17" s="394"/>
+      <c r="F17" s="394"/>
+      <c r="G17" s="395"/>
+      <c r="H17" s="343"/>
+      <c r="I17" s="345"/>
+      <c r="J17" s="343"/>
+      <c r="K17" s="345"/>
+      <c r="L17" s="344"/>
+      <c r="M17" s="344"/>
       <c r="N17" s="33"/>
-      <c r="O17" s="333"/>
-      <c r="P17" s="334"/>
-      <c r="Q17" s="334"/>
-      <c r="R17" s="334"/>
-      <c r="S17" s="334"/>
-      <c r="T17" s="334"/>
-      <c r="U17" s="335"/>
+      <c r="O17" s="388"/>
+      <c r="P17" s="389"/>
+      <c r="Q17" s="389"/>
+      <c r="R17" s="389"/>
+      <c r="S17" s="389"/>
+      <c r="T17" s="389"/>
+      <c r="U17" s="390"/>
       <c r="V17" s="47"/>
       <c r="W17" s="44"/>
       <c r="X17" s="44"/>
@@ -8649,7 +8667,7 @@
       <c r="AG17" s="204"/>
       <c r="AH17" s="204"/>
       <c r="AI17" s="204"/>
-      <c r="AJ17" s="271" t="s">
+      <c r="AJ17" s="269" t="s">
         <v>513</v>
       </c>
       <c r="AK17" s="228" t="s">
@@ -8663,7 +8681,7 @@
       <c r="AQ17" s="204"/>
       <c r="AR17" s="204"/>
       <c r="AS17" s="204"/>
-      <c r="AT17" s="271" t="s">
+      <c r="AT17" s="269" t="s">
         <v>337</v>
       </c>
       <c r="AU17" s="228" t="s">
@@ -8683,7 +8701,7 @@
       </c>
       <c r="BB17" s="248"/>
       <c r="BC17" s="204"/>
-      <c r="BD17" s="271" t="s">
+      <c r="BD17" s="269" t="s">
         <v>311</v>
       </c>
       <c r="BE17" s="222" t="s">
@@ -8705,35 +8723,35 @@
       <c r="BM17" s="245" t="s">
         <v>660</v>
       </c>
-      <c r="BN17" s="277" t="s">
+      <c r="BN17" s="405" t="s">
         <v>283</v>
       </c>
       <c r="BO17" s="224"/>
     </row>
     <row r="18" spans="1:70" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="322" t="s">
+      <c r="A18" s="375" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="323"/>
+      <c r="B18" s="376"/>
       <c r="C18" s="19"/>
       <c r="D18" s="19"/>
-      <c r="E18" s="298"/>
-      <c r="F18" s="299"/>
-      <c r="G18" s="300"/>
-      <c r="H18" s="285"/>
-      <c r="I18" s="286"/>
-      <c r="J18" s="285"/>
-      <c r="K18" s="286"/>
-      <c r="L18" s="287"/>
-      <c r="M18" s="287"/>
+      <c r="E18" s="396"/>
+      <c r="F18" s="394"/>
+      <c r="G18" s="395"/>
+      <c r="H18" s="343"/>
+      <c r="I18" s="345"/>
+      <c r="J18" s="343"/>
+      <c r="K18" s="345"/>
+      <c r="L18" s="344"/>
+      <c r="M18" s="344"/>
       <c r="N18" s="33"/>
-      <c r="O18" s="336"/>
-      <c r="P18" s="337"/>
-      <c r="Q18" s="337"/>
-      <c r="R18" s="337"/>
-      <c r="S18" s="337"/>
-      <c r="T18" s="337"/>
-      <c r="U18" s="338"/>
+      <c r="O18" s="391"/>
+      <c r="P18" s="392"/>
+      <c r="Q18" s="392"/>
+      <c r="R18" s="392"/>
+      <c r="S18" s="392"/>
+      <c r="T18" s="392"/>
+      <c r="U18" s="393"/>
       <c r="V18" s="47"/>
       <c r="Z18" s="42"/>
       <c r="AA18" s="228"/>
@@ -8747,7 +8765,7 @@
       <c r="AG18" s="203"/>
       <c r="AH18" s="203"/>
       <c r="AI18" s="203"/>
-      <c r="AJ18" s="271"/>
+      <c r="AJ18" s="269"/>
       <c r="AK18" s="228"/>
       <c r="AL18" s="203"/>
       <c r="AM18" s="203"/>
@@ -8757,7 +8775,7 @@
       <c r="AQ18" s="203"/>
       <c r="AR18" s="203"/>
       <c r="AS18" s="203"/>
-      <c r="AT18" s="271"/>
+      <c r="AT18" s="269"/>
       <c r="AU18" s="228"/>
       <c r="AV18" s="211" t="s">
         <v>554</v>
@@ -8781,7 +8799,7 @@
       <c r="BC18" s="235" t="s">
         <v>107</v>
       </c>
-      <c r="BD18" s="271"/>
+      <c r="BD18" s="269"/>
       <c r="BE18" s="222"/>
       <c r="BF18" s="235" t="s">
         <v>406</v>
@@ -8805,33 +8823,33 @@
       <c r="BM18" s="244" t="s">
         <v>659</v>
       </c>
-      <c r="BN18" s="277"/>
+      <c r="BN18" s="405"/>
       <c r="BO18" s="224"/>
     </row>
     <row r="19" spans="1:70" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="324"/>
-      <c r="B19" s="325"/>
+      <c r="A19" s="325"/>
+      <c r="B19" s="377"/>
       <c r="C19" s="19"/>
       <c r="D19" s="56"/>
       <c r="E19" s="57"/>
       <c r="F19" s="58"/>
       <c r="G19" s="58"/>
-      <c r="H19" s="285"/>
-      <c r="I19" s="286"/>
-      <c r="J19" s="285"/>
-      <c r="K19" s="286"/>
-      <c r="L19" s="287"/>
-      <c r="M19" s="287"/>
+      <c r="H19" s="343"/>
+      <c r="I19" s="345"/>
+      <c r="J19" s="343"/>
+      <c r="K19" s="345"/>
+      <c r="L19" s="344"/>
+      <c r="M19" s="344"/>
       <c r="N19" s="33"/>
-      <c r="O19" s="340" t="s">
+      <c r="O19" s="397" t="s">
         <v>25</v>
       </c>
-      <c r="P19" s="341"/>
-      <c r="Q19" s="341"/>
-      <c r="R19" s="341"/>
-      <c r="S19" s="341"/>
-      <c r="T19" s="341"/>
-      <c r="U19" s="342"/>
+      <c r="P19" s="398"/>
+      <c r="Q19" s="398"/>
+      <c r="R19" s="398"/>
+      <c r="S19" s="398"/>
+      <c r="T19" s="398"/>
+      <c r="U19" s="399"/>
       <c r="Z19" s="42"/>
       <c r="AA19" s="227" t="s">
         <v>275</v>
@@ -8896,33 +8914,33 @@
       <c r="BM19" s="197" t="s">
         <v>57</v>
       </c>
-      <c r="BN19" s="276" t="s">
+      <c r="BN19" s="349" t="s">
         <v>284</v>
       </c>
       <c r="BO19" s="224"/>
     </row>
     <row r="20" spans="1:70" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="326"/>
-      <c r="B20" s="339"/>
-      <c r="E20" s="304" t="s">
+      <c r="A20" s="332"/>
+      <c r="B20" s="333"/>
+      <c r="E20" s="403" t="s">
         <v>26</v>
       </c>
-      <c r="F20" s="305"/>
-      <c r="G20" s="306"/>
-      <c r="H20" s="285"/>
-      <c r="I20" s="286"/>
-      <c r="J20" s="285"/>
-      <c r="K20" s="286"/>
-      <c r="L20" s="287"/>
-      <c r="M20" s="287"/>
+      <c r="F20" s="379"/>
+      <c r="G20" s="380"/>
+      <c r="H20" s="343"/>
+      <c r="I20" s="345"/>
+      <c r="J20" s="343"/>
+      <c r="K20" s="345"/>
+      <c r="L20" s="344"/>
+      <c r="M20" s="344"/>
       <c r="N20" s="33"/>
-      <c r="O20" s="343"/>
-      <c r="P20" s="344"/>
-      <c r="Q20" s="344"/>
-      <c r="R20" s="344"/>
-      <c r="S20" s="344"/>
-      <c r="T20" s="344"/>
-      <c r="U20" s="345"/>
+      <c r="O20" s="400"/>
+      <c r="P20" s="401"/>
+      <c r="Q20" s="401"/>
+      <c r="R20" s="401"/>
+      <c r="S20" s="401"/>
+      <c r="T20" s="401"/>
+      <c r="U20" s="402"/>
       <c r="V20" s="59"/>
       <c r="X20" s="41"/>
       <c r="Z20" s="42"/>
@@ -8994,29 +9012,29 @@
       <c r="BM20" s="238" t="s">
         <v>58</v>
       </c>
-      <c r="BN20" s="276"/>
+      <c r="BN20" s="349"/>
       <c r="BO20" s="224"/>
     </row>
     <row r="21" spans="1:70" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="40"/>
       <c r="B21" s="40"/>
-      <c r="E21" s="298"/>
-      <c r="F21" s="299"/>
-      <c r="G21" s="300"/>
-      <c r="H21" s="285"/>
-      <c r="I21" s="286"/>
-      <c r="J21" s="285"/>
-      <c r="K21" s="286"/>
-      <c r="L21" s="287"/>
-      <c r="M21" s="287"/>
+      <c r="E21" s="396"/>
+      <c r="F21" s="394"/>
+      <c r="G21" s="395"/>
+      <c r="H21" s="343"/>
+      <c r="I21" s="345"/>
+      <c r="J21" s="343"/>
+      <c r="K21" s="345"/>
+      <c r="L21" s="344"/>
+      <c r="M21" s="344"/>
       <c r="N21" s="33"/>
-      <c r="O21" s="343"/>
-      <c r="P21" s="344"/>
-      <c r="Q21" s="344"/>
-      <c r="R21" s="344"/>
-      <c r="S21" s="344"/>
-      <c r="T21" s="344"/>
-      <c r="U21" s="345"/>
+      <c r="O21" s="400"/>
+      <c r="P21" s="401"/>
+      <c r="Q21" s="401"/>
+      <c r="R21" s="401"/>
+      <c r="S21" s="401"/>
+      <c r="T21" s="401"/>
+      <c r="U21" s="402"/>
       <c r="V21" s="37"/>
       <c r="W21" s="60"/>
       <c r="X21" s="41"/>
@@ -9032,7 +9050,7 @@
       <c r="AG21" s="204"/>
       <c r="AH21" s="204"/>
       <c r="AI21" s="204"/>
-      <c r="AJ21" s="271" t="s">
+      <c r="AJ21" s="269" t="s">
         <v>515</v>
       </c>
       <c r="AK21" s="228" t="s">
@@ -9046,7 +9064,7 @@
       <c r="AQ21" s="204"/>
       <c r="AR21" s="204"/>
       <c r="AS21" s="204"/>
-      <c r="AT21" s="271" t="s">
+      <c r="AT21" s="269" t="s">
         <v>339</v>
       </c>
       <c r="AU21" s="228" t="s">
@@ -9062,7 +9080,7 @@
       <c r="BA21" s="204"/>
       <c r="BB21" s="204"/>
       <c r="BC21" s="204"/>
-      <c r="BD21" s="271" t="s">
+      <c r="BD21" s="269" t="s">
         <v>313</v>
       </c>
       <c r="BE21" s="222" t="s">
@@ -9080,7 +9098,7 @@
       <c r="BM21" s="197" t="s">
         <v>103</v>
       </c>
-      <c r="BN21" s="277" t="s">
+      <c r="BN21" s="405" t="s">
         <v>285</v>
       </c>
       <c r="BO21" s="224"/>
@@ -9088,23 +9106,23 @@
     <row r="22" spans="1:70" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="40"/>
       <c r="B22" s="40"/>
-      <c r="E22" s="298"/>
-      <c r="F22" s="299"/>
-      <c r="G22" s="300"/>
-      <c r="H22" s="285"/>
-      <c r="I22" s="286"/>
-      <c r="J22" s="285"/>
-      <c r="K22" s="286"/>
-      <c r="L22" s="287"/>
-      <c r="M22" s="287"/>
+      <c r="E22" s="396"/>
+      <c r="F22" s="394"/>
+      <c r="G22" s="395"/>
+      <c r="H22" s="343"/>
+      <c r="I22" s="345"/>
+      <c r="J22" s="343"/>
+      <c r="K22" s="345"/>
+      <c r="L22" s="344"/>
+      <c r="M22" s="344"/>
       <c r="N22" s="33"/>
-      <c r="O22" s="343"/>
-      <c r="P22" s="344"/>
-      <c r="Q22" s="344"/>
-      <c r="R22" s="344"/>
-      <c r="S22" s="344"/>
-      <c r="T22" s="344"/>
-      <c r="U22" s="345"/>
+      <c r="O22" s="400"/>
+      <c r="P22" s="401"/>
+      <c r="Q22" s="401"/>
+      <c r="R22" s="401"/>
+      <c r="S22" s="401"/>
+      <c r="T22" s="401"/>
+      <c r="U22" s="402"/>
       <c r="V22" s="45"/>
       <c r="X22" s="9"/>
       <c r="Y22" s="23"/>
@@ -9118,7 +9136,7 @@
       <c r="AG22" s="203"/>
       <c r="AH22" s="203"/>
       <c r="AI22" s="203"/>
-      <c r="AJ22" s="271"/>
+      <c r="AJ22" s="269"/>
       <c r="AK22" s="228"/>
       <c r="AL22" s="203"/>
       <c r="AM22" s="203"/>
@@ -9128,7 +9146,7 @@
       <c r="AQ22" s="203"/>
       <c r="AR22" s="203"/>
       <c r="AS22" s="203"/>
-      <c r="AT22" s="271"/>
+      <c r="AT22" s="269"/>
       <c r="AU22" s="228"/>
       <c r="AV22" s="235" t="s">
         <v>400</v>
@@ -9152,7 +9170,7 @@
       <c r="BC22" s="244" t="s">
         <v>640</v>
       </c>
-      <c r="BD22" s="271"/>
+      <c r="BD22" s="269"/>
       <c r="BE22" s="222"/>
       <c r="BF22" s="196" t="s">
         <v>59</v>
@@ -9167,34 +9185,38 @@
       <c r="BJ22" s="244" t="s">
         <v>657</v>
       </c>
-      <c r="BK22" s="203"/>
-      <c r="BL22" s="203"/>
+      <c r="BK22" s="244" t="s">
+        <v>680</v>
+      </c>
+      <c r="BL22" s="244" t="s">
+        <v>681</v>
+      </c>
       <c r="BM22" s="196" t="s">
         <v>193</v>
       </c>
-      <c r="BN22" s="277"/>
+      <c r="BN22" s="405"/>
       <c r="BO22" s="224"/>
     </row>
     <row r="23" spans="1:70" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="40"/>
       <c r="B23" s="40"/>
-      <c r="E23" s="298"/>
-      <c r="F23" s="299"/>
-      <c r="G23" s="300"/>
-      <c r="H23" s="285"/>
-      <c r="I23" s="286"/>
-      <c r="J23" s="285"/>
-      <c r="K23" s="286"/>
-      <c r="L23" s="287"/>
-      <c r="M23" s="287"/>
+      <c r="E23" s="396"/>
+      <c r="F23" s="394"/>
+      <c r="G23" s="395"/>
+      <c r="H23" s="343"/>
+      <c r="I23" s="345"/>
+      <c r="J23" s="343"/>
+      <c r="K23" s="345"/>
+      <c r="L23" s="344"/>
+      <c r="M23" s="344"/>
       <c r="N23" s="33"/>
-      <c r="O23" s="343"/>
-      <c r="P23" s="344"/>
-      <c r="Q23" s="344"/>
-      <c r="R23" s="344"/>
-      <c r="S23" s="344"/>
-      <c r="T23" s="344"/>
-      <c r="U23" s="345"/>
+      <c r="O23" s="400"/>
+      <c r="P23" s="401"/>
+      <c r="Q23" s="401"/>
+      <c r="R23" s="401"/>
+      <c r="S23" s="401"/>
+      <c r="T23" s="401"/>
+      <c r="U23" s="402"/>
       <c r="V23" s="61"/>
       <c r="Z23" s="42"/>
       <c r="AA23" s="227" t="s">
@@ -9263,7 +9285,7 @@
       <c r="BM23" s="245" t="s">
         <v>656</v>
       </c>
-      <c r="BN23" s="276" t="s">
+      <c r="BN23" s="349" t="s">
         <v>286</v>
       </c>
       <c r="BO23" s="224"/>
@@ -9271,23 +9293,23 @@
     <row r="24" spans="1:70" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="40"/>
       <c r="B24" s="40"/>
-      <c r="E24" s="301"/>
-      <c r="F24" s="302"/>
-      <c r="G24" s="303"/>
-      <c r="H24" s="285"/>
-      <c r="I24" s="286"/>
-      <c r="J24" s="285"/>
-      <c r="K24" s="286"/>
-      <c r="L24" s="287"/>
-      <c r="M24" s="287"/>
+      <c r="E24" s="404"/>
+      <c r="F24" s="381"/>
+      <c r="G24" s="382"/>
+      <c r="H24" s="343"/>
+      <c r="I24" s="345"/>
+      <c r="J24" s="343"/>
+      <c r="K24" s="345"/>
+      <c r="L24" s="344"/>
+      <c r="M24" s="344"/>
       <c r="N24" s="33"/>
-      <c r="O24" s="343"/>
-      <c r="P24" s="344"/>
-      <c r="Q24" s="344"/>
-      <c r="R24" s="344"/>
-      <c r="S24" s="344"/>
-      <c r="T24" s="344"/>
-      <c r="U24" s="345"/>
+      <c r="O24" s="400"/>
+      <c r="P24" s="401"/>
+      <c r="Q24" s="401"/>
+      <c r="R24" s="401"/>
+      <c r="S24" s="401"/>
+      <c r="T24" s="401"/>
+      <c r="U24" s="402"/>
       <c r="V24" s="61"/>
       <c r="Z24" s="42"/>
       <c r="AA24" s="227"/>
@@ -9357,31 +9379,31 @@
       <c r="BM24" s="244" t="s">
         <v>650</v>
       </c>
-      <c r="BN24" s="276"/>
+      <c r="BN24" s="349"/>
       <c r="BO24" s="224"/>
     </row>
     <row r="25" spans="1:70" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="40"/>
       <c r="B25" s="40"/>
-      <c r="E25" s="298" t="s">
+      <c r="E25" s="396" t="s">
         <v>27</v>
       </c>
-      <c r="F25" s="299"/>
-      <c r="G25" s="300"/>
-      <c r="H25" s="285"/>
-      <c r="I25" s="286"/>
-      <c r="J25" s="285"/>
-      <c r="K25" s="286"/>
-      <c r="L25" s="287"/>
-      <c r="M25" s="287"/>
+      <c r="F25" s="394"/>
+      <c r="G25" s="395"/>
+      <c r="H25" s="343"/>
+      <c r="I25" s="345"/>
+      <c r="J25" s="343"/>
+      <c r="K25" s="345"/>
+      <c r="L25" s="344"/>
+      <c r="M25" s="344"/>
       <c r="N25" s="33"/>
-      <c r="O25" s="343"/>
-      <c r="P25" s="344"/>
-      <c r="Q25" s="344"/>
-      <c r="R25" s="344"/>
-      <c r="S25" s="344"/>
-      <c r="T25" s="344"/>
-      <c r="U25" s="345"/>
+      <c r="O25" s="400"/>
+      <c r="P25" s="401"/>
+      <c r="Q25" s="401"/>
+      <c r="R25" s="401"/>
+      <c r="S25" s="401"/>
+      <c r="T25" s="401"/>
+      <c r="U25" s="402"/>
       <c r="V25" s="61"/>
       <c r="W25" s="38"/>
       <c r="X25" s="9"/>
@@ -9398,7 +9420,7 @@
       <c r="AG25" s="204"/>
       <c r="AH25" s="204"/>
       <c r="AI25" s="204"/>
-      <c r="AJ25" s="271" t="s">
+      <c r="AJ25" s="269" t="s">
         <v>517</v>
       </c>
       <c r="AK25" s="228" t="s">
@@ -9412,7 +9434,7 @@
       <c r="AQ25" s="204"/>
       <c r="AR25" s="204"/>
       <c r="AS25" s="204"/>
-      <c r="AT25" s="271" t="s">
+      <c r="AT25" s="269" t="s">
         <v>341</v>
       </c>
       <c r="AU25" s="228" t="s">
@@ -9428,7 +9450,7 @@
       <c r="BC25" s="236" t="s">
         <v>382</v>
       </c>
-      <c r="BD25" s="271" t="s">
+      <c r="BD25" s="269" t="s">
         <v>315</v>
       </c>
       <c r="BE25" s="222" t="s">
@@ -9438,13 +9460,13 @@
       <c r="BG25" s="204"/>
       <c r="BH25" s="204"/>
       <c r="BI25" s="204"/>
-      <c r="BJ25" s="266" t="s">
+      <c r="BJ25" s="265" t="s">
         <v>200</v>
       </c>
       <c r="BK25" s="204"/>
       <c r="BL25" s="204"/>
       <c r="BM25" s="204"/>
-      <c r="BN25" s="277" t="s">
+      <c r="BN25" s="405" t="s">
         <v>287</v>
       </c>
       <c r="BO25" s="224"/>
@@ -9452,23 +9474,23 @@
     <row r="26" spans="1:70" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="40"/>
       <c r="B26" s="40"/>
-      <c r="E26" s="298"/>
-      <c r="F26" s="299"/>
-      <c r="G26" s="300"/>
-      <c r="H26" s="285"/>
-      <c r="I26" s="286"/>
-      <c r="J26" s="285"/>
-      <c r="K26" s="286"/>
-      <c r="L26" s="287"/>
-      <c r="M26" s="287"/>
+      <c r="E26" s="396"/>
+      <c r="F26" s="394"/>
+      <c r="G26" s="395"/>
+      <c r="H26" s="343"/>
+      <c r="I26" s="345"/>
+      <c r="J26" s="343"/>
+      <c r="K26" s="345"/>
+      <c r="L26" s="344"/>
+      <c r="M26" s="344"/>
       <c r="N26" s="33"/>
-      <c r="O26" s="343"/>
-      <c r="P26" s="344"/>
-      <c r="Q26" s="344"/>
-      <c r="R26" s="344"/>
-      <c r="S26" s="344"/>
-      <c r="T26" s="344"/>
-      <c r="U26" s="345"/>
+      <c r="O26" s="400"/>
+      <c r="P26" s="401"/>
+      <c r="Q26" s="401"/>
+      <c r="R26" s="401"/>
+      <c r="S26" s="401"/>
+      <c r="T26" s="401"/>
+      <c r="U26" s="402"/>
       <c r="V26" s="62"/>
       <c r="W26" s="38"/>
       <c r="X26" s="9"/>
@@ -9483,7 +9505,7 @@
       <c r="AG26" s="203"/>
       <c r="AH26" s="203"/>
       <c r="AI26" s="203"/>
-      <c r="AJ26" s="271"/>
+      <c r="AJ26" s="269"/>
       <c r="AK26" s="228"/>
       <c r="AL26" s="203"/>
       <c r="AM26" s="203"/>
@@ -9495,7 +9517,7 @@
       <c r="AS26" s="211" t="s">
         <v>468</v>
       </c>
-      <c r="AT26" s="271"/>
+      <c r="AT26" s="269"/>
       <c r="AU26" s="228"/>
       <c r="AV26" s="243" t="s">
         <v>423</v>
@@ -9519,7 +9541,7 @@
       <c r="BC26" s="235" t="s">
         <v>117</v>
       </c>
-      <c r="BD26" s="271"/>
+      <c r="BD26" s="269"/>
       <c r="BE26" s="222"/>
       <c r="BF26" s="196" t="s">
         <v>65</v>
@@ -9543,29 +9565,29 @@
       <c r="BM26" s="244" t="s">
         <v>674</v>
       </c>
-      <c r="BN26" s="277"/>
+      <c r="BN26" s="405"/>
       <c r="BO26" s="224"/>
     </row>
     <row r="27" spans="1:70" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="40"/>
       <c r="B27" s="40"/>
-      <c r="E27" s="298"/>
-      <c r="F27" s="299"/>
-      <c r="G27" s="300"/>
-      <c r="H27" s="285"/>
-      <c r="I27" s="286"/>
-      <c r="J27" s="285"/>
-      <c r="K27" s="286"/>
-      <c r="L27" s="287"/>
-      <c r="M27" s="287"/>
+      <c r="E27" s="396"/>
+      <c r="F27" s="394"/>
+      <c r="G27" s="395"/>
+      <c r="H27" s="343"/>
+      <c r="I27" s="345"/>
+      <c r="J27" s="343"/>
+      <c r="K27" s="345"/>
+      <c r="L27" s="344"/>
+      <c r="M27" s="344"/>
       <c r="N27" s="33"/>
-      <c r="O27" s="343"/>
-      <c r="P27" s="344"/>
-      <c r="Q27" s="344"/>
-      <c r="R27" s="344"/>
-      <c r="S27" s="344"/>
-      <c r="T27" s="344"/>
-      <c r="U27" s="345"/>
+      <c r="O27" s="400"/>
+      <c r="P27" s="401"/>
+      <c r="Q27" s="401"/>
+      <c r="R27" s="401"/>
+      <c r="S27" s="401"/>
+      <c r="T27" s="401"/>
+      <c r="U27" s="402"/>
       <c r="V27" s="62"/>
       <c r="W27" s="38"/>
       <c r="X27" s="9"/>
@@ -9626,10 +9648,10 @@
       <c r="BL27" s="197" t="s">
         <v>206</v>
       </c>
-      <c r="BM27" s="266" t="s">
+      <c r="BM27" s="265" t="s">
         <v>69</v>
       </c>
-      <c r="BN27" s="276" t="s">
+      <c r="BN27" s="349" t="s">
         <v>288</v>
       </c>
       <c r="BO27" s="224"/>
@@ -9637,23 +9659,23 @@
     <row r="28" spans="1:70" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="9"/>
       <c r="B28" s="44"/>
-      <c r="E28" s="298"/>
-      <c r="F28" s="299"/>
-      <c r="G28" s="300"/>
-      <c r="H28" s="285"/>
-      <c r="I28" s="286"/>
-      <c r="J28" s="285"/>
-      <c r="K28" s="286"/>
-      <c r="L28" s="287"/>
-      <c r="M28" s="287"/>
+      <c r="E28" s="396"/>
+      <c r="F28" s="394"/>
+      <c r="G28" s="395"/>
+      <c r="H28" s="343"/>
+      <c r="I28" s="345"/>
+      <c r="J28" s="343"/>
+      <c r="K28" s="345"/>
+      <c r="L28" s="344"/>
+      <c r="M28" s="344"/>
       <c r="N28" s="33"/>
-      <c r="O28" s="343"/>
-      <c r="P28" s="344"/>
-      <c r="Q28" s="344"/>
-      <c r="R28" s="344"/>
-      <c r="S28" s="344"/>
-      <c r="T28" s="344"/>
-      <c r="U28" s="345"/>
+      <c r="O28" s="400"/>
+      <c r="P28" s="401"/>
+      <c r="Q28" s="401"/>
+      <c r="R28" s="401"/>
+      <c r="S28" s="401"/>
+      <c r="T28" s="401"/>
+      <c r="U28" s="402"/>
       <c r="V28" s="62"/>
       <c r="W28" s="37"/>
       <c r="X28" s="37"/>
@@ -9726,7 +9748,7 @@
       <c r="BM28" s="238" t="s">
         <v>70</v>
       </c>
-      <c r="BN28" s="276"/>
+      <c r="BN28" s="349"/>
       <c r="BO28" s="224"/>
       <c r="BR28" s="4" t="s">
         <v>11</v>
@@ -9735,23 +9757,23 @@
     <row r="29" spans="1:70" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="9"/>
       <c r="B29" s="44"/>
-      <c r="E29" s="298"/>
-      <c r="F29" s="299"/>
-      <c r="G29" s="300"/>
-      <c r="H29" s="285"/>
-      <c r="I29" s="286"/>
-      <c r="J29" s="285"/>
-      <c r="K29" s="286"/>
-      <c r="L29" s="287"/>
-      <c r="M29" s="287"/>
+      <c r="E29" s="396"/>
+      <c r="F29" s="394"/>
+      <c r="G29" s="395"/>
+      <c r="H29" s="343"/>
+      <c r="I29" s="345"/>
+      <c r="J29" s="343"/>
+      <c r="K29" s="345"/>
+      <c r="L29" s="344"/>
+      <c r="M29" s="344"/>
       <c r="N29" s="33"/>
-      <c r="O29" s="343"/>
-      <c r="P29" s="344"/>
-      <c r="Q29" s="344"/>
-      <c r="R29" s="344"/>
-      <c r="S29" s="344"/>
-      <c r="T29" s="344"/>
-      <c r="U29" s="345"/>
+      <c r="O29" s="400"/>
+      <c r="P29" s="401"/>
+      <c r="Q29" s="401"/>
+      <c r="R29" s="401"/>
+      <c r="S29" s="401"/>
+      <c r="T29" s="401"/>
+      <c r="U29" s="402"/>
       <c r="V29" s="44"/>
       <c r="W29" s="37"/>
       <c r="X29" s="37"/>
@@ -9785,30 +9807,30 @@
         <v>343</v>
       </c>
       <c r="AU29" s="229"/>
-      <c r="AV29" s="272" t="s">
+      <c r="AV29" s="426" t="s">
         <v>48</v>
       </c>
-      <c r="AW29" s="273"/>
-      <c r="AX29" s="273"/>
-      <c r="AY29" s="273"/>
-      <c r="AZ29" s="273"/>
-      <c r="BA29" s="273"/>
-      <c r="BB29" s="273"/>
-      <c r="BC29" s="274"/>
+      <c r="AW29" s="427"/>
+      <c r="AX29" s="427"/>
+      <c r="AY29" s="427"/>
+      <c r="AZ29" s="427"/>
+      <c r="BA29" s="427"/>
+      <c r="BB29" s="427"/>
+      <c r="BC29" s="428"/>
       <c r="BD29" s="208" t="s">
         <v>317</v>
       </c>
       <c r="BE29" s="223"/>
-      <c r="BF29" s="272" t="s">
+      <c r="BF29" s="426" t="s">
         <v>49</v>
       </c>
-      <c r="BG29" s="273"/>
-      <c r="BH29" s="273"/>
-      <c r="BI29" s="273"/>
-      <c r="BJ29" s="273"/>
-      <c r="BK29" s="273"/>
-      <c r="BL29" s="273"/>
-      <c r="BM29" s="274"/>
+      <c r="BG29" s="427"/>
+      <c r="BH29" s="427"/>
+      <c r="BI29" s="427"/>
+      <c r="BJ29" s="427"/>
+      <c r="BK29" s="427"/>
+      <c r="BL29" s="427"/>
+      <c r="BM29" s="428"/>
       <c r="BN29" s="219" t="s">
         <v>289</v>
       </c>
@@ -9817,23 +9839,23 @@
     <row r="30" spans="1:70" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="9"/>
       <c r="B30" s="44"/>
-      <c r="E30" s="301"/>
-      <c r="F30" s="302"/>
-      <c r="G30" s="303"/>
-      <c r="H30" s="285"/>
-      <c r="I30" s="286"/>
-      <c r="J30" s="285"/>
-      <c r="K30" s="286"/>
-      <c r="L30" s="287"/>
-      <c r="M30" s="287"/>
+      <c r="E30" s="404"/>
+      <c r="F30" s="381"/>
+      <c r="G30" s="382"/>
+      <c r="H30" s="343"/>
+      <c r="I30" s="345"/>
+      <c r="J30" s="343"/>
+      <c r="K30" s="345"/>
+      <c r="L30" s="344"/>
+      <c r="M30" s="344"/>
       <c r="N30" s="33"/>
-      <c r="O30" s="343"/>
-      <c r="P30" s="344"/>
-      <c r="Q30" s="344"/>
-      <c r="R30" s="344"/>
-      <c r="S30" s="344"/>
-      <c r="T30" s="344"/>
-      <c r="U30" s="345"/>
+      <c r="O30" s="400"/>
+      <c r="P30" s="401"/>
+      <c r="Q30" s="401"/>
+      <c r="R30" s="401"/>
+      <c r="S30" s="401"/>
+      <c r="T30" s="401"/>
+      <c r="U30" s="402"/>
       <c r="V30" s="44"/>
       <c r="W30" s="37"/>
       <c r="X30" s="37"/>
@@ -9898,7 +9920,7 @@
       <c r="BM30" s="245" t="s">
         <v>655</v>
       </c>
-      <c r="BN30" s="276" t="s">
+      <c r="BN30" s="349" t="s">
         <v>290</v>
       </c>
       <c r="BO30" s="224"/>
@@ -9906,25 +9928,25 @@
     <row r="31" spans="1:70" ht="279.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="9"/>
       <c r="B31" s="44"/>
-      <c r="E31" s="304" t="s">
+      <c r="E31" s="403" t="s">
         <v>28</v>
       </c>
-      <c r="F31" s="305"/>
-      <c r="G31" s="306"/>
-      <c r="H31" s="285"/>
-      <c r="I31" s="286"/>
-      <c r="J31" s="285"/>
-      <c r="K31" s="286"/>
-      <c r="L31" s="287"/>
-      <c r="M31" s="287"/>
+      <c r="F31" s="379"/>
+      <c r="G31" s="380"/>
+      <c r="H31" s="343"/>
+      <c r="I31" s="345"/>
+      <c r="J31" s="343"/>
+      <c r="K31" s="345"/>
+      <c r="L31" s="344"/>
+      <c r="M31" s="344"/>
       <c r="N31" s="67"/>
-      <c r="O31" s="343"/>
-      <c r="P31" s="344"/>
-      <c r="Q31" s="344"/>
-      <c r="R31" s="344"/>
-      <c r="S31" s="344"/>
-      <c r="T31" s="344"/>
-      <c r="U31" s="345"/>
+      <c r="O31" s="400"/>
+      <c r="P31" s="401"/>
+      <c r="Q31" s="401"/>
+      <c r="R31" s="401"/>
+      <c r="S31" s="401"/>
+      <c r="T31" s="401"/>
+      <c r="U31" s="402"/>
       <c r="V31" s="44"/>
       <c r="W31" s="37"/>
       <c r="X31" s="37"/>
@@ -9997,29 +10019,29 @@
       <c r="BM31" s="244" t="s">
         <v>672</v>
       </c>
-      <c r="BN31" s="276"/>
+      <c r="BN31" s="349"/>
       <c r="BO31" s="224"/>
     </row>
     <row r="32" spans="1:70" ht="279.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A32" s="9"/>
       <c r="B32" s="44"/>
-      <c r="E32" s="298"/>
-      <c r="F32" s="299"/>
-      <c r="G32" s="300"/>
-      <c r="H32" s="285"/>
-      <c r="I32" s="286"/>
-      <c r="J32" s="285"/>
-      <c r="K32" s="286"/>
-      <c r="L32" s="287"/>
-      <c r="M32" s="287"/>
+      <c r="E32" s="396"/>
+      <c r="F32" s="394"/>
+      <c r="G32" s="395"/>
+      <c r="H32" s="343"/>
+      <c r="I32" s="345"/>
+      <c r="J32" s="343"/>
+      <c r="K32" s="345"/>
+      <c r="L32" s="344"/>
+      <c r="M32" s="344"/>
       <c r="N32" s="33"/>
-      <c r="O32" s="343"/>
-      <c r="P32" s="344"/>
-      <c r="Q32" s="344"/>
-      <c r="R32" s="344"/>
-      <c r="S32" s="344"/>
-      <c r="T32" s="344"/>
-      <c r="U32" s="345"/>
+      <c r="O32" s="400"/>
+      <c r="P32" s="401"/>
+      <c r="Q32" s="401"/>
+      <c r="R32" s="401"/>
+      <c r="S32" s="401"/>
+      <c r="T32" s="401"/>
+      <c r="U32" s="402"/>
       <c r="W32" s="37"/>
       <c r="X32" s="37"/>
       <c r="Y32" s="66"/>
@@ -10035,7 +10057,7 @@
       <c r="AG32" s="204"/>
       <c r="AH32" s="204"/>
       <c r="AI32" s="204"/>
-      <c r="AJ32" s="271" t="s">
+      <c r="AJ32" s="269" t="s">
         <v>529</v>
       </c>
       <c r="AK32" s="228" t="s">
@@ -10049,7 +10071,7 @@
       <c r="AQ32" s="204"/>
       <c r="AR32" s="204"/>
       <c r="AS32" s="204"/>
-      <c r="AT32" s="271" t="s">
+      <c r="AT32" s="269" t="s">
         <v>345</v>
       </c>
       <c r="AU32" s="228" t="s">
@@ -10060,8 +10082,12 @@
       </c>
       <c r="AW32" s="204"/>
       <c r="AX32" s="204"/>
-      <c r="AY32" s="204"/>
-      <c r="AZ32" s="204"/>
+      <c r="AY32" s="246" t="s">
+        <v>441</v>
+      </c>
+      <c r="AZ32" s="210" t="s">
+        <v>236</v>
+      </c>
       <c r="BA32" s="210" t="s">
         <v>136</v>
       </c>
@@ -10071,7 +10097,7 @@
       <c r="BC32" s="210" t="s">
         <v>435</v>
       </c>
-      <c r="BD32" s="271" t="s">
+      <c r="BD32" s="269" t="s">
         <v>319</v>
       </c>
       <c r="BE32" s="222" t="s">
@@ -10087,7 +10113,7 @@
       <c r="BK32" s="204"/>
       <c r="BL32" s="204"/>
       <c r="BM32" s="204"/>
-      <c r="BN32" s="277" t="s">
+      <c r="BN32" s="405" t="s">
         <v>291</v>
       </c>
       <c r="BO32" s="224"/>
@@ -10095,23 +10121,23 @@
     <row r="33" spans="1:67" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="9"/>
       <c r="B33" s="44"/>
-      <c r="E33" s="301"/>
-      <c r="F33" s="302"/>
-      <c r="G33" s="303"/>
-      <c r="H33" s="285"/>
-      <c r="I33" s="286"/>
-      <c r="J33" s="285"/>
-      <c r="K33" s="286"/>
-      <c r="L33" s="287"/>
-      <c r="M33" s="287"/>
+      <c r="E33" s="404"/>
+      <c r="F33" s="381"/>
+      <c r="G33" s="382"/>
+      <c r="H33" s="343"/>
+      <c r="I33" s="345"/>
+      <c r="J33" s="343"/>
+      <c r="K33" s="345"/>
+      <c r="L33" s="344"/>
+      <c r="M33" s="344"/>
       <c r="N33" s="33"/>
-      <c r="O33" s="343"/>
-      <c r="P33" s="344"/>
-      <c r="Q33" s="344"/>
-      <c r="R33" s="344"/>
-      <c r="S33" s="344"/>
-      <c r="T33" s="344"/>
-      <c r="U33" s="345"/>
+      <c r="O33" s="400"/>
+      <c r="P33" s="401"/>
+      <c r="Q33" s="401"/>
+      <c r="R33" s="401"/>
+      <c r="S33" s="401"/>
+      <c r="T33" s="401"/>
+      <c r="U33" s="402"/>
       <c r="W33" s="37"/>
       <c r="X33" s="37"/>
       <c r="Z33" s="69"/>
@@ -10124,7 +10150,7 @@
       <c r="AG33" s="203"/>
       <c r="AH33" s="203"/>
       <c r="AI33" s="203"/>
-      <c r="AJ33" s="271"/>
+      <c r="AJ33" s="269"/>
       <c r="AK33" s="228"/>
       <c r="AL33" s="209" t="s">
         <v>469</v>
@@ -10148,14 +10174,12 @@
       <c r="AS33" s="237" t="s">
         <v>433</v>
       </c>
-      <c r="AT33" s="271"/>
+      <c r="AT33" s="269"/>
       <c r="AU33" s="228"/>
       <c r="AV33" s="235" t="s">
         <v>440</v>
       </c>
-      <c r="AW33" s="235" t="s">
-        <v>441</v>
-      </c>
+      <c r="AW33" s="203"/>
       <c r="AX33" s="203"/>
       <c r="AY33" s="235" t="s">
         <v>442</v>
@@ -10172,7 +10196,7 @@
       <c r="BC33" s="211" t="s">
         <v>211</v>
       </c>
-      <c r="BD33" s="271"/>
+      <c r="BD33" s="269"/>
       <c r="BE33" s="222"/>
       <c r="BF33" s="196" t="s">
         <v>547</v>
@@ -10187,40 +10211,38 @@
       <c r="BJ33" s="235" t="s">
         <v>209</v>
       </c>
-      <c r="BK33" s="261" t="s">
-        <v>563</v>
-      </c>
+      <c r="BK33" s="268"/>
       <c r="BL33" s="211" t="s">
         <v>624</v>
       </c>
       <c r="BM33" s="243" t="s">
         <v>625</v>
       </c>
-      <c r="BN33" s="277"/>
+      <c r="BN33" s="405"/>
       <c r="BO33" s="224"/>
     </row>
     <row r="34" spans="1:67" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="9"/>
       <c r="B34" s="44"/>
-      <c r="E34" s="304" t="s">
+      <c r="E34" s="403" t="s">
         <v>29</v>
       </c>
-      <c r="F34" s="305"/>
-      <c r="G34" s="306"/>
-      <c r="H34" s="285"/>
-      <c r="I34" s="286"/>
-      <c r="J34" s="285"/>
-      <c r="K34" s="286"/>
-      <c r="L34" s="287"/>
-      <c r="M34" s="287"/>
+      <c r="F34" s="379"/>
+      <c r="G34" s="380"/>
+      <c r="H34" s="343"/>
+      <c r="I34" s="345"/>
+      <c r="J34" s="343"/>
+      <c r="K34" s="345"/>
+      <c r="L34" s="344"/>
+      <c r="M34" s="344"/>
       <c r="N34" s="33"/>
-      <c r="O34" s="343"/>
-      <c r="P34" s="344"/>
-      <c r="Q34" s="344"/>
-      <c r="R34" s="344"/>
-      <c r="S34" s="344"/>
-      <c r="T34" s="344"/>
-      <c r="U34" s="345"/>
+      <c r="O34" s="400"/>
+      <c r="P34" s="401"/>
+      <c r="Q34" s="401"/>
+      <c r="R34" s="401"/>
+      <c r="S34" s="401"/>
+      <c r="T34" s="401"/>
+      <c r="U34" s="402"/>
       <c r="V34" s="41"/>
       <c r="W34" s="37"/>
       <c r="X34" s="37"/>
@@ -10260,7 +10282,7 @@
       <c r="AW34" s="188"/>
       <c r="AX34" s="188"/>
       <c r="AY34" s="210" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AZ34" s="210" t="s">
         <v>213</v>
@@ -10287,10 +10309,16 @@
       <c r="BH34" s="188"/>
       <c r="BI34" s="188"/>
       <c r="BJ34" s="188"/>
-      <c r="BK34" s="188"/>
-      <c r="BL34" s="188"/>
-      <c r="BM34" s="188"/>
-      <c r="BN34" s="276" t="s">
+      <c r="BK34" s="210" t="s">
+        <v>566</v>
+      </c>
+      <c r="BL34" s="210" t="s">
+        <v>447</v>
+      </c>
+      <c r="BM34" s="210" t="s">
+        <v>563</v>
+      </c>
+      <c r="BN34" s="349" t="s">
         <v>292</v>
       </c>
       <c r="BO34" s="224"/>
@@ -10300,23 +10328,23 @@
       <c r="B35" s="44"/>
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
-      <c r="E35" s="301"/>
-      <c r="F35" s="302"/>
-      <c r="G35" s="303"/>
-      <c r="H35" s="285"/>
-      <c r="I35" s="286"/>
-      <c r="J35" s="285"/>
-      <c r="K35" s="286"/>
-      <c r="L35" s="287"/>
-      <c r="M35" s="287"/>
+      <c r="E35" s="404"/>
+      <c r="F35" s="381"/>
+      <c r="G35" s="382"/>
+      <c r="H35" s="343"/>
+      <c r="I35" s="345"/>
+      <c r="J35" s="343"/>
+      <c r="K35" s="345"/>
+      <c r="L35" s="344"/>
+      <c r="M35" s="344"/>
       <c r="N35" s="33"/>
-      <c r="O35" s="343"/>
-      <c r="P35" s="344"/>
-      <c r="Q35" s="344"/>
-      <c r="R35" s="344"/>
-      <c r="S35" s="344"/>
-      <c r="T35" s="344"/>
-      <c r="U35" s="345"/>
+      <c r="O35" s="400"/>
+      <c r="P35" s="401"/>
+      <c r="Q35" s="401"/>
+      <c r="R35" s="401"/>
+      <c r="S35" s="401"/>
+      <c r="T35" s="401"/>
+      <c r="U35" s="402"/>
       <c r="V35" s="70"/>
       <c r="W35" s="37"/>
       <c r="X35" s="37"/>
@@ -10399,7 +10427,7 @@
       <c r="BM35" s="243" t="s">
         <v>565</v>
       </c>
-      <c r="BN35" s="276"/>
+      <c r="BN35" s="349"/>
       <c r="BO35" s="225"/>
     </row>
     <row r="36" spans="1:67" s="73" customFormat="1" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10407,25 +10435,25 @@
       <c r="B36" s="40"/>
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
-      <c r="E36" s="301" t="s">
+      <c r="E36" s="404" t="s">
         <v>30</v>
       </c>
-      <c r="F36" s="302"/>
-      <c r="G36" s="303"/>
-      <c r="H36" s="288"/>
-      <c r="I36" s="289"/>
-      <c r="J36" s="288"/>
-      <c r="K36" s="289"/>
-      <c r="L36" s="291"/>
-      <c r="M36" s="291"/>
+      <c r="F36" s="381"/>
+      <c r="G36" s="382"/>
+      <c r="H36" s="346"/>
+      <c r="I36" s="348"/>
+      <c r="J36" s="346"/>
+      <c r="K36" s="348"/>
+      <c r="L36" s="347"/>
+      <c r="M36" s="347"/>
       <c r="N36" s="33"/>
-      <c r="O36" s="343"/>
-      <c r="P36" s="344"/>
-      <c r="Q36" s="344"/>
-      <c r="R36" s="344"/>
-      <c r="S36" s="344"/>
-      <c r="T36" s="344"/>
-      <c r="U36" s="345"/>
+      <c r="O36" s="400"/>
+      <c r="P36" s="401"/>
+      <c r="Q36" s="401"/>
+      <c r="R36" s="401"/>
+      <c r="S36" s="401"/>
+      <c r="T36" s="401"/>
+      <c r="U36" s="402"/>
       <c r="V36" s="9"/>
       <c r="W36" s="4"/>
       <c r="X36" s="71"/>
@@ -10442,7 +10470,7 @@
       <c r="AG36" s="204"/>
       <c r="AH36" s="204"/>
       <c r="AI36" s="204"/>
-      <c r="AJ36" s="271" t="s">
+      <c r="AJ36" s="269" t="s">
         <v>531</v>
       </c>
       <c r="AK36" s="228" t="s">
@@ -10456,7 +10484,7 @@
       <c r="AQ36" s="204"/>
       <c r="AR36" s="204"/>
       <c r="AS36" s="204"/>
-      <c r="AT36" s="271" t="s">
+      <c r="AT36" s="269" t="s">
         <v>347</v>
       </c>
       <c r="AU36" s="228" t="s">
@@ -10465,7 +10493,9 @@
       <c r="AV36" s="204"/>
       <c r="AW36" s="204"/>
       <c r="AX36" s="204"/>
-      <c r="AY36" s="204"/>
+      <c r="AY36" s="210" t="s">
+        <v>227</v>
+      </c>
       <c r="AZ36" s="210" t="s">
         <v>216</v>
       </c>
@@ -10478,13 +10508,15 @@
       <c r="BC36" s="210" t="s">
         <v>147</v>
       </c>
-      <c r="BD36" s="271" t="s">
+      <c r="BD36" s="269" t="s">
         <v>321</v>
       </c>
       <c r="BE36" s="222" t="s">
         <v>275</v>
       </c>
-      <c r="BF36" s="204"/>
+      <c r="BF36" s="210" t="s">
+        <v>94</v>
+      </c>
       <c r="BG36" s="204"/>
       <c r="BH36" s="204"/>
       <c r="BI36" s="204"/>
@@ -10492,7 +10524,7 @@
       <c r="BK36" s="204"/>
       <c r="BL36" s="204"/>
       <c r="BM36" s="204"/>
-      <c r="BN36" s="277" t="s">
+      <c r="BN36" s="405" t="s">
         <v>293</v>
       </c>
       <c r="BO36" s="225"/>
@@ -10500,27 +10532,27 @@
     <row r="37" spans="1:67" s="73" customFormat="1" ht="279.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="9"/>
       <c r="B37" s="40"/>
-      <c r="E37" s="346" t="s">
+      <c r="E37" s="356" t="s">
         <v>31</v>
       </c>
-      <c r="F37" s="346"/>
-      <c r="G37" s="346"/>
-      <c r="H37" s="346"/>
-      <c r="I37" s="346"/>
-      <c r="J37" s="346"/>
-      <c r="K37" s="346"/>
-      <c r="L37" s="346"/>
-      <c r="M37" s="346"/>
+      <c r="F37" s="356"/>
+      <c r="G37" s="356"/>
+      <c r="H37" s="356"/>
+      <c r="I37" s="356"/>
+      <c r="J37" s="356"/>
+      <c r="K37" s="356"/>
+      <c r="L37" s="356"/>
+      <c r="M37" s="356"/>
       <c r="N37" s="74"/>
-      <c r="O37" s="347" t="s">
+      <c r="O37" s="357" t="s">
         <v>31</v>
       </c>
-      <c r="P37" s="348"/>
-      <c r="Q37" s="348"/>
-      <c r="R37" s="348"/>
-      <c r="S37" s="348"/>
-      <c r="T37" s="348"/>
-      <c r="U37" s="348"/>
+      <c r="P37" s="358"/>
+      <c r="Q37" s="358"/>
+      <c r="R37" s="358"/>
+      <c r="S37" s="358"/>
+      <c r="T37" s="358"/>
+      <c r="U37" s="358"/>
       <c r="V37" s="75"/>
       <c r="W37" s="76"/>
       <c r="X37" s="76"/>
@@ -10535,7 +10567,7 @@
       <c r="AG37" s="203"/>
       <c r="AH37" s="203"/>
       <c r="AI37" s="203"/>
-      <c r="AJ37" s="271"/>
+      <c r="AJ37" s="269"/>
       <c r="AK37" s="228"/>
       <c r="AL37" s="209" t="s">
         <v>481</v>
@@ -10559,7 +10591,7 @@
       <c r="AS37" s="209" t="s">
         <v>487</v>
       </c>
-      <c r="AT37" s="271"/>
+      <c r="AT37" s="269"/>
       <c r="AU37" s="228"/>
       <c r="AV37" s="244" t="s">
         <v>670</v>
@@ -10583,7 +10615,7 @@
       <c r="BC37" s="211" t="s">
         <v>133</v>
       </c>
-      <c r="BD37" s="271"/>
+      <c r="BD37" s="269"/>
       <c r="BE37" s="222"/>
       <c r="BF37" s="211" t="s">
         <v>449</v>
@@ -10598,14 +10630,10 @@
       <c r="BJ37" s="235" t="s">
         <v>215</v>
       </c>
-      <c r="BK37" s="211" t="s">
-        <v>447</v>
-      </c>
-      <c r="BL37" s="211" t="s">
-        <v>566</v>
-      </c>
+      <c r="BK37" s="203"/>
+      <c r="BL37" s="203"/>
       <c r="BM37" s="250"/>
-      <c r="BN37" s="277"/>
+      <c r="BN37" s="405"/>
       <c r="BO37" s="225"/>
     </row>
     <row r="38" spans="1:67" s="73" customFormat="1" ht="279.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
@@ -10628,7 +10656,7 @@
       </c>
       <c r="M38" s="25"/>
       <c r="N38" s="81"/>
-      <c r="O38" s="349"/>
+      <c r="O38" s="359"/>
       <c r="P38" s="14"/>
       <c r="Q38" s="14"/>
       <c r="R38" s="14"/>
@@ -10685,7 +10713,9 @@
       <c r="BE38" s="221" t="s">
         <v>275</v>
       </c>
-      <c r="BF38" s="188"/>
+      <c r="BF38" s="210" t="s">
+        <v>249</v>
+      </c>
       <c r="BG38" s="188"/>
       <c r="BH38" s="188"/>
       <c r="BI38" s="188"/>
@@ -10697,7 +10727,7 @@
       <c r="BM38" s="246" t="s">
         <v>378</v>
       </c>
-      <c r="BN38" s="276" t="s">
+      <c r="BN38" s="349" t="s">
         <v>294</v>
       </c>
       <c r="BO38" s="225"/>
@@ -10716,7 +10746,7 @@
       <c r="L39" s="31"/>
       <c r="M39" s="31"/>
       <c r="N39" s="81"/>
-      <c r="O39" s="350"/>
+      <c r="O39" s="271"/>
       <c r="P39" s="14"/>
       <c r="Q39" s="14"/>
       <c r="R39" s="14"/>
@@ -10803,7 +10833,7 @@
       <c r="BM39" s="235" t="s">
         <v>265</v>
       </c>
-      <c r="BN39" s="276"/>
+      <c r="BN39" s="349"/>
       <c r="BO39" s="225"/>
     </row>
     <row r="40" spans="1:67" s="73" customFormat="1" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10841,7 +10871,7 @@
       <c r="AG40" s="204"/>
       <c r="AH40" s="204"/>
       <c r="AI40" s="204"/>
-      <c r="AJ40" s="271" t="s">
+      <c r="AJ40" s="269" t="s">
         <v>533</v>
       </c>
       <c r="AK40" s="228" t="s">
@@ -10855,7 +10885,7 @@
       <c r="AQ40" s="204"/>
       <c r="AR40" s="204"/>
       <c r="AS40" s="204"/>
-      <c r="AT40" s="271" t="s">
+      <c r="AT40" s="269" t="s">
         <v>349</v>
       </c>
       <c r="AU40" s="228" t="s">
@@ -10871,13 +10901,15 @@
       </c>
       <c r="BB40" s="204"/>
       <c r="BC40" s="204"/>
-      <c r="BD40" s="271" t="s">
+      <c r="BD40" s="269" t="s">
         <v>323</v>
       </c>
       <c r="BE40" s="222" t="s">
         <v>275</v>
       </c>
-      <c r="BF40" s="204"/>
+      <c r="BF40" s="210" t="s">
+        <v>462</v>
+      </c>
       <c r="BG40" s="204"/>
       <c r="BH40" s="204"/>
       <c r="BI40" s="204"/>
@@ -10891,7 +10923,7 @@
       <c r="BM40" s="197" t="s">
         <v>222</v>
       </c>
-      <c r="BN40" s="277" t="s">
+      <c r="BN40" s="405" t="s">
         <v>295</v>
       </c>
       <c r="BO40" s="225"/>
@@ -10928,7 +10960,7 @@
       <c r="AG41" s="203"/>
       <c r="AH41" s="203"/>
       <c r="AI41" s="203"/>
-      <c r="AJ41" s="271"/>
+      <c r="AJ41" s="269"/>
       <c r="AK41" s="228"/>
       <c r="AL41" s="237" t="s">
         <v>493</v>
@@ -10950,7 +10982,7 @@
         <v>578</v>
       </c>
       <c r="AS41" s="203"/>
-      <c r="AT41" s="271"/>
+      <c r="AT41" s="269"/>
       <c r="AU41" s="228"/>
       <c r="AV41" s="203"/>
       <c r="AW41" s="203"/>
@@ -10970,7 +11002,7 @@
       <c r="BC41" s="235" t="s">
         <v>426</v>
       </c>
-      <c r="BD41" s="271"/>
+      <c r="BD41" s="269"/>
       <c r="BE41" s="222"/>
       <c r="BF41" s="211" t="s">
         <v>454</v>
@@ -10994,7 +11026,7 @@
       <c r="BM41" s="196" t="s">
         <v>263</v>
       </c>
-      <c r="BN41" s="277"/>
+      <c r="BN41" s="405"/>
       <c r="BO41" s="225"/>
     </row>
     <row r="42" spans="1:67" s="73" customFormat="1" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -11010,8 +11042,8 @@
       <c r="L42" s="31"/>
       <c r="M42" s="31"/>
       <c r="N42" s="81"/>
-      <c r="O42" s="358"/>
-      <c r="P42" s="350"/>
+      <c r="O42" s="355"/>
+      <c r="P42" s="271"/>
       <c r="Q42" s="89"/>
       <c r="R42" s="89"/>
       <c r="S42" s="89"/>
@@ -11067,7 +11099,9 @@
       <c r="BE42" s="221" t="s">
         <v>275</v>
       </c>
-      <c r="BF42" s="188"/>
+      <c r="BF42" s="210" t="s">
+        <v>250</v>
+      </c>
       <c r="BG42" s="188"/>
       <c r="BH42" s="188"/>
       <c r="BI42" s="188"/>
@@ -11077,7 +11111,7 @@
       <c r="BM42" s="197" t="s">
         <v>90</v>
       </c>
-      <c r="BN42" s="276" t="s">
+      <c r="BN42" s="349" t="s">
         <v>296</v>
       </c>
       <c r="BO42" s="225"/>
@@ -11095,8 +11129,8 @@
       <c r="L43" s="31"/>
       <c r="M43" s="31"/>
       <c r="N43" s="81"/>
-      <c r="O43" s="358"/>
-      <c r="P43" s="350"/>
+      <c r="O43" s="355"/>
+      <c r="P43" s="271"/>
       <c r="Q43" s="89"/>
       <c r="R43" s="89"/>
       <c r="S43" s="89"/>
@@ -11184,17 +11218,17 @@
       <c r="BM43" s="196" t="s">
         <v>82</v>
       </c>
-      <c r="BN43" s="276"/>
+      <c r="BN43" s="349"/>
       <c r="BO43" s="225"/>
     </row>
     <row r="44" spans="1:67" s="73" customFormat="1" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="78"/>
       <c r="B44" s="78"/>
-      <c r="E44" s="351" t="s">
+      <c r="E44" s="360" t="s">
         <v>35</v>
       </c>
-      <c r="F44" s="352"/>
-      <c r="G44" s="355" t="s">
+      <c r="F44" s="361"/>
+      <c r="G44" s="364" t="s">
         <v>36</v>
       </c>
       <c r="H44" s="31"/>
@@ -11204,8 +11238,8 @@
       <c r="L44" s="31"/>
       <c r="M44" s="31"/>
       <c r="N44" s="81"/>
-      <c r="O44" s="358"/>
-      <c r="P44" s="350"/>
+      <c r="O44" s="355"/>
+      <c r="P44" s="271"/>
       <c r="Q44" s="89"/>
       <c r="R44" s="89"/>
       <c r="S44" s="89"/>
@@ -11226,7 +11260,7 @@
       <c r="AG44" s="204"/>
       <c r="AH44" s="204"/>
       <c r="AI44" s="204"/>
-      <c r="AJ44" s="271" t="s">
+      <c r="AJ44" s="269" t="s">
         <v>535</v>
       </c>
       <c r="AK44" s="228" t="s">
@@ -11240,7 +11274,7 @@
       <c r="AQ44" s="204"/>
       <c r="AR44" s="204"/>
       <c r="AS44" s="204"/>
-      <c r="AT44" s="271" t="s">
+      <c r="AT44" s="269" t="s">
         <v>351</v>
       </c>
       <c r="AU44" s="228" t="s">
@@ -11256,7 +11290,7 @@
       <c r="BA44" s="204"/>
       <c r="BB44" s="204"/>
       <c r="BC44" s="204"/>
-      <c r="BD44" s="271" t="s">
+      <c r="BD44" s="269" t="s">
         <v>325</v>
       </c>
       <c r="BE44" s="222" t="s">
@@ -11278,7 +11312,7 @@
       <c r="BM44" s="197" t="s">
         <v>390</v>
       </c>
-      <c r="BN44" s="277" t="s">
+      <c r="BN44" s="405" t="s">
         <v>297</v>
       </c>
       <c r="BO44" s="225"/>
@@ -11286,9 +11320,9 @@
     <row r="45" spans="1:67" s="73" customFormat="1" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="78"/>
       <c r="B45" s="78"/>
-      <c r="E45" s="353"/>
-      <c r="F45" s="354"/>
-      <c r="G45" s="356"/>
+      <c r="E45" s="362"/>
+      <c r="F45" s="363"/>
+      <c r="G45" s="365"/>
       <c r="H45" s="31"/>
       <c r="I45" s="31"/>
       <c r="J45" s="30"/>
@@ -11315,7 +11349,7 @@
       <c r="AG45" s="203"/>
       <c r="AH45" s="203"/>
       <c r="AI45" s="203"/>
-      <c r="AJ45" s="271"/>
+      <c r="AJ45" s="269"/>
       <c r="AK45" s="228"/>
       <c r="AL45" s="237" t="s">
         <v>572</v>
@@ -11337,13 +11371,13 @@
         <v>502</v>
       </c>
       <c r="AS45" s="203"/>
-      <c r="AT45" s="271"/>
+      <c r="AT45" s="269"/>
       <c r="AU45" s="228"/>
       <c r="AV45" s="211" t="s">
         <v>567</v>
       </c>
-      <c r="AW45" s="211" t="s">
-        <v>229</v>
+      <c r="AW45" s="244" t="s">
+        <v>679</v>
       </c>
       <c r="AX45" s="203"/>
       <c r="AY45" s="196" t="s">
@@ -11361,7 +11395,7 @@
       <c r="BC45" s="243" t="s">
         <v>668</v>
       </c>
-      <c r="BD45" s="271"/>
+      <c r="BD45" s="269"/>
       <c r="BE45" s="222"/>
       <c r="BF45" s="243" t="s">
         <v>465</v>
@@ -11370,9 +11404,7 @@
         <v>464</v>
       </c>
       <c r="BH45" s="203"/>
-      <c r="BI45" s="211" t="s">
-        <v>94</v>
-      </c>
+      <c r="BI45" s="203"/>
       <c r="BJ45" s="196" t="s">
         <v>544</v>
       </c>
@@ -11385,7 +11417,7 @@
       <c r="BM45" s="196" t="s">
         <v>389</v>
       </c>
-      <c r="BN45" s="277"/>
+      <c r="BN45" s="405"/>
       <c r="BO45" s="225"/>
     </row>
     <row r="46" spans="1:67" s="73" customFormat="1" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -11469,7 +11501,7 @@
       <c r="BK46" s="188"/>
       <c r="BL46" s="188"/>
       <c r="BM46" s="188"/>
-      <c r="BN46" s="276" t="s">
+      <c r="BN46" s="349" t="s">
         <v>298</v>
       </c>
       <c r="BO46" s="225"/>
@@ -11555,9 +11587,7 @@
         <v>251</v>
       </c>
       <c r="BH47" s="189"/>
-      <c r="BI47" s="211" t="s">
-        <v>249</v>
-      </c>
+      <c r="BI47" s="189"/>
       <c r="BJ47" s="238" t="s">
         <v>120</v>
       </c>
@@ -11570,7 +11600,7 @@
       <c r="BM47" s="238" t="s">
         <v>260</v>
       </c>
-      <c r="BN47" s="276"/>
+      <c r="BN47" s="349"/>
       <c r="BO47" s="224"/>
     </row>
     <row r="48" spans="1:67" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -11588,15 +11618,15 @@
       <c r="L48" s="31"/>
       <c r="M48" s="31"/>
       <c r="N48" s="81"/>
-      <c r="O48" s="363" t="s">
+      <c r="O48" s="302" t="s">
         <v>37</v>
       </c>
-      <c r="P48" s="363"/>
-      <c r="Q48" s="363"/>
-      <c r="R48" s="363"/>
-      <c r="S48" s="363"/>
-      <c r="T48" s="363"/>
-      <c r="U48" s="364"/>
+      <c r="P48" s="302"/>
+      <c r="Q48" s="302"/>
+      <c r="R48" s="302"/>
+      <c r="S48" s="302"/>
+      <c r="T48" s="302"/>
+      <c r="U48" s="303"/>
       <c r="V48" s="36"/>
       <c r="W48" s="51"/>
       <c r="X48" s="14"/>
@@ -11613,7 +11643,7 @@
       <c r="AG48" s="204"/>
       <c r="AH48" s="204"/>
       <c r="AI48" s="204"/>
-      <c r="AJ48" s="271" t="s">
+      <c r="AJ48" s="269" t="s">
         <v>537</v>
       </c>
       <c r="AK48" s="228" t="s">
@@ -11627,7 +11657,7 @@
       <c r="AQ48" s="204"/>
       <c r="AR48" s="204"/>
       <c r="AS48" s="204"/>
-      <c r="AT48" s="271" t="s">
+      <c r="AT48" s="269" t="s">
         <v>353</v>
       </c>
       <c r="AU48" s="228" t="s">
@@ -11647,7 +11677,7 @@
         <v>234</v>
       </c>
       <c r="BC48" s="204"/>
-      <c r="BD48" s="271" t="s">
+      <c r="BD48" s="269" t="s">
         <v>327</v>
       </c>
       <c r="BE48" s="222" t="s">
@@ -11665,7 +11695,7 @@
       <c r="BM48" s="197" t="s">
         <v>387</v>
       </c>
-      <c r="BN48" s="277" t="s">
+      <c r="BN48" s="405" t="s">
         <v>299</v>
       </c>
       <c r="BO48" s="224"/>
@@ -11683,13 +11713,13 @@
       <c r="L49" s="31"/>
       <c r="M49" s="31"/>
       <c r="N49" s="33"/>
-      <c r="O49" s="365"/>
-      <c r="P49" s="365"/>
-      <c r="Q49" s="365"/>
-      <c r="R49" s="365"/>
-      <c r="S49" s="365"/>
-      <c r="T49" s="365"/>
-      <c r="U49" s="366"/>
+      <c r="O49" s="305"/>
+      <c r="P49" s="305"/>
+      <c r="Q49" s="305"/>
+      <c r="R49" s="305"/>
+      <c r="S49" s="305"/>
+      <c r="T49" s="305"/>
+      <c r="U49" s="306"/>
       <c r="V49" s="36"/>
       <c r="W49" s="14"/>
       <c r="X49" s="14"/>
@@ -11704,7 +11734,7 @@
       <c r="AG49" s="203"/>
       <c r="AH49" s="203"/>
       <c r="AI49" s="203"/>
-      <c r="AJ49" s="271"/>
+      <c r="AJ49" s="269"/>
       <c r="AK49" s="228"/>
       <c r="AL49" s="203"/>
       <c r="AM49" s="237" t="s">
@@ -11716,7 +11746,7 @@
       <c r="AQ49" s="203"/>
       <c r="AR49" s="203"/>
       <c r="AS49" s="203"/>
-      <c r="AT49" s="271"/>
+      <c r="AT49" s="269"/>
       <c r="AU49" s="228"/>
       <c r="AV49" s="196" t="s">
         <v>505</v>
@@ -11725,9 +11755,7 @@
         <v>139</v>
       </c>
       <c r="AX49" s="203"/>
-      <c r="AY49" s="211" t="s">
-        <v>236</v>
-      </c>
+      <c r="AY49" s="203"/>
       <c r="AZ49" s="196" t="s">
         <v>237</v>
       </c>
@@ -11740,7 +11768,7 @@
       <c r="BC49" s="196" t="s">
         <v>239</v>
       </c>
-      <c r="BD49" s="271"/>
+      <c r="BD49" s="269"/>
       <c r="BE49" s="222"/>
       <c r="BF49" s="243" t="s">
         <v>638</v>
@@ -11749,9 +11777,7 @@
         <v>639</v>
       </c>
       <c r="BH49" s="203"/>
-      <c r="BI49" s="211" t="s">
-        <v>247</v>
-      </c>
+      <c r="BI49" s="203"/>
       <c r="BJ49" s="244" t="s">
         <v>645</v>
       </c>
@@ -11764,17 +11790,17 @@
       <c r="BM49" s="238" t="s">
         <v>259</v>
       </c>
-      <c r="BN49" s="277"/>
+      <c r="BN49" s="405"/>
       <c r="BO49" s="224"/>
     </row>
     <row r="50" spans="1:77" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="79"/>
       <c r="B50" s="79"/>
-      <c r="E50" s="285" t="s">
+      <c r="E50" s="343" t="s">
         <v>38</v>
       </c>
-      <c r="F50" s="287"/>
-      <c r="G50" s="286"/>
+      <c r="F50" s="344"/>
+      <c r="G50" s="345"/>
       <c r="H50" s="31"/>
       <c r="I50" s="31"/>
       <c r="J50" s="30"/>
@@ -11782,13 +11808,13 @@
       <c r="L50" s="31"/>
       <c r="M50" s="31"/>
       <c r="N50" s="33"/>
-      <c r="O50" s="365"/>
-      <c r="P50" s="365"/>
-      <c r="Q50" s="365"/>
-      <c r="R50" s="365"/>
-      <c r="S50" s="365"/>
-      <c r="T50" s="365"/>
-      <c r="U50" s="366"/>
+      <c r="O50" s="305"/>
+      <c r="P50" s="305"/>
+      <c r="Q50" s="305"/>
+      <c r="R50" s="305"/>
+      <c r="S50" s="305"/>
+      <c r="T50" s="305"/>
+      <c r="U50" s="306"/>
       <c r="V50" s="36"/>
       <c r="W50" s="14"/>
       <c r="X50" s="14"/>
@@ -11865,7 +11891,7 @@
         <v>91</v>
       </c>
       <c r="BM50" s="188"/>
-      <c r="BN50" s="276" t="s">
+      <c r="BN50" s="349" t="s">
         <v>300</v>
       </c>
       <c r="BO50" s="224"/>
@@ -11873,9 +11899,9 @@
     <row r="51" spans="1:77" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="79"/>
       <c r="B51" s="79"/>
-      <c r="E51" s="285"/>
-      <c r="F51" s="287"/>
-      <c r="G51" s="286"/>
+      <c r="E51" s="343"/>
+      <c r="F51" s="344"/>
+      <c r="G51" s="345"/>
       <c r="H51" s="31"/>
       <c r="I51" s="31"/>
       <c r="J51" s="30"/>
@@ -11883,19 +11909,19 @@
       <c r="L51" s="31"/>
       <c r="M51" s="31"/>
       <c r="N51" s="33"/>
-      <c r="O51" s="365"/>
-      <c r="P51" s="365"/>
-      <c r="Q51" s="365"/>
-      <c r="R51" s="365"/>
-      <c r="S51" s="365"/>
-      <c r="T51" s="365"/>
-      <c r="U51" s="366"/>
+      <c r="O51" s="305"/>
+      <c r="P51" s="305"/>
+      <c r="Q51" s="305"/>
+      <c r="R51" s="305"/>
+      <c r="S51" s="305"/>
+      <c r="T51" s="305"/>
+      <c r="U51" s="306"/>
       <c r="V51" s="95"/>
       <c r="W51" s="14"/>
       <c r="X51" s="14"/>
       <c r="Y51" s="14"/>
       <c r="Z51" s="60"/>
-      <c r="AA51" s="262" t="s">
+      <c r="AA51" s="261" t="s">
         <v>270</v>
       </c>
       <c r="AB51" s="198" t="s">
@@ -11910,7 +11936,7 @@
       <c r="AE51" s="198" t="s">
         <v>273</v>
       </c>
-      <c r="AF51" s="263" t="s">
+      <c r="AF51" s="262" t="s">
         <v>269</v>
       </c>
       <c r="AG51" s="256" t="s">
@@ -11969,12 +11995,8 @@
         <v>651</v>
       </c>
       <c r="BH51" s="189"/>
-      <c r="BI51" s="211" t="s">
-        <v>246</v>
-      </c>
-      <c r="BJ51" s="211" t="s">
-        <v>244</v>
-      </c>
+      <c r="BI51" s="189"/>
+      <c r="BJ51" s="189"/>
       <c r="BK51" s="196" t="s">
         <v>138</v>
       </c>
@@ -11984,15 +12006,15 @@
       <c r="BM51" s="196" t="s">
         <v>258</v>
       </c>
-      <c r="BN51" s="276"/>
+      <c r="BN51" s="349"/>
       <c r="BO51" s="224"/>
     </row>
     <row r="52" spans="1:77" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="79"/>
       <c r="B52" s="79"/>
-      <c r="E52" s="285"/>
-      <c r="F52" s="287"/>
-      <c r="G52" s="286"/>
+      <c r="E52" s="343"/>
+      <c r="F52" s="344"/>
+      <c r="G52" s="345"/>
       <c r="H52" s="31"/>
       <c r="I52" s="31"/>
       <c r="J52" s="30"/>
@@ -12000,19 +12022,19 @@
       <c r="L52" s="31"/>
       <c r="M52" s="31"/>
       <c r="N52" s="33"/>
-      <c r="O52" s="365"/>
-      <c r="P52" s="365"/>
-      <c r="Q52" s="365"/>
-      <c r="R52" s="365"/>
-      <c r="S52" s="365"/>
-      <c r="T52" s="365"/>
-      <c r="U52" s="366"/>
+      <c r="O52" s="305"/>
+      <c r="P52" s="305"/>
+      <c r="Q52" s="305"/>
+      <c r="R52" s="305"/>
+      <c r="S52" s="305"/>
+      <c r="T52" s="305"/>
+      <c r="U52" s="306"/>
       <c r="V52" s="36"/>
       <c r="W52" s="14"/>
       <c r="X52" s="14"/>
       <c r="Y52" s="14"/>
       <c r="Z52" s="51"/>
-      <c r="AA52" s="264">
+      <c r="AA52" s="263">
         <f>COUNTA(AV55:BE55)</f>
         <v>2</v>
       </c>
@@ -12026,15 +12048,15 @@
       </c>
       <c r="AD52" s="195">
         <f>COUNTA(AV30:BC53,AV3:BC28)</f>
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AE52" s="195">
         <f>COUNTA(BF30:BM57,BF3:BM28)</f>
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AF52" s="242">
         <f>SUM(AA52:AE52)+AJ52</f>
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="AG52" s="255">
         <f>COUNTIF( $AV$3:$BC$53,"*401*") + COUNTIF($AB$3:$AS$51,"*401*")+ COUNTIF($AV$55:$BD$55,"*401*") +COUNTIF($BF$3:$BM$57,"*401*") -1</f>
@@ -12042,7 +12064,7 @@
       </c>
       <c r="AH52" s="254">
         <f>COUNTIF( $AV$3:$BC$53,"*402*") + COUNTIF($AB$3:$AS$51,"*402*")+ COUNTIF($AV$55:$BD$55,"*402*") +COUNTIF($BF$3:$BM$57,"*402*") -1</f>
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="AI52" s="253">
         <f>COUNTIF( $AV$3:$BC$53,"*403*") + COUNTIF($AB$3:$AS$51,"*403*")+ COUNTIF($AV$55:$BD$55,"*403*") +COUNTIF($BF$3:$BM$57,"*403*") -1</f>
@@ -12087,21 +12109,25 @@
       <c r="BA52" s="204"/>
       <c r="BB52" s="204"/>
       <c r="BC52" s="204"/>
-      <c r="BD52" s="271" t="s">
+      <c r="BD52" s="269" t="s">
         <v>329</v>
       </c>
       <c r="BE52" s="222" t="s">
         <v>275</v>
       </c>
-      <c r="BF52" s="204"/>
-      <c r="BG52" s="204"/>
+      <c r="BF52" s="210" t="s">
+        <v>247</v>
+      </c>
+      <c r="BG52" s="210" t="s">
+        <v>246</v>
+      </c>
       <c r="BH52" s="204"/>
       <c r="BI52" s="204"/>
       <c r="BJ52" s="204"/>
       <c r="BK52" s="204"/>
       <c r="BL52" s="204"/>
       <c r="BM52" s="204"/>
-      <c r="BN52" s="277" t="s">
+      <c r="BN52" s="405" t="s">
         <v>301</v>
       </c>
       <c r="BO52" s="224"/>
@@ -12109,9 +12135,9 @@
     <row r="53" spans="1:77" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="96"/>
       <c r="B53" s="96"/>
-      <c r="E53" s="285"/>
-      <c r="F53" s="287"/>
-      <c r="G53" s="286"/>
+      <c r="E53" s="343"/>
+      <c r="F53" s="344"/>
+      <c r="G53" s="345"/>
       <c r="H53" s="31"/>
       <c r="I53" s="31"/>
       <c r="J53" s="30"/>
@@ -12119,13 +12145,13 @@
       <c r="L53" s="31"/>
       <c r="M53" s="31"/>
       <c r="N53" s="33"/>
-      <c r="O53" s="365"/>
-      <c r="P53" s="365"/>
-      <c r="Q53" s="365"/>
-      <c r="R53" s="365"/>
-      <c r="S53" s="365"/>
-      <c r="T53" s="365"/>
-      <c r="U53" s="366"/>
+      <c r="O53" s="305"/>
+      <c r="P53" s="305"/>
+      <c r="Q53" s="305"/>
+      <c r="R53" s="305"/>
+      <c r="S53" s="305"/>
+      <c r="T53" s="305"/>
+      <c r="U53" s="306"/>
       <c r="V53" s="36"/>
       <c r="W53" s="14"/>
       <c r="X53" s="14"/>
@@ -12146,7 +12172,7 @@
       <c r="BC53" s="196" t="s">
         <v>245</v>
       </c>
-      <c r="BD53" s="271"/>
+      <c r="BD53" s="269"/>
       <c r="BE53" s="222"/>
       <c r="BF53" s="211" t="s">
         <v>241</v>
@@ -12154,9 +12180,7 @@
       <c r="BG53" s="211" t="s">
         <v>242</v>
       </c>
-      <c r="BH53" s="211" t="s">
-        <v>243</v>
-      </c>
+      <c r="BH53" s="203"/>
       <c r="BI53" s="203"/>
       <c r="BJ53" s="196" t="s">
         <v>88</v>
@@ -12170,15 +12194,15 @@
       <c r="BM53" s="196" t="s">
         <v>93</v>
       </c>
-      <c r="BN53" s="277"/>
+      <c r="BN53" s="405"/>
       <c r="BO53" s="224"/>
     </row>
     <row r="54" spans="1:77" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="96"/>
       <c r="B54" s="96"/>
-      <c r="E54" s="285"/>
-      <c r="F54" s="287"/>
-      <c r="G54" s="286"/>
+      <c r="E54" s="343"/>
+      <c r="F54" s="344"/>
+      <c r="G54" s="345"/>
       <c r="H54" s="31"/>
       <c r="I54" s="31"/>
       <c r="J54" s="30"/>
@@ -12186,13 +12210,13 @@
       <c r="L54" s="31"/>
       <c r="M54" s="31"/>
       <c r="N54" s="33"/>
-      <c r="O54" s="365"/>
-      <c r="P54" s="365"/>
-      <c r="Q54" s="365"/>
-      <c r="R54" s="365"/>
-      <c r="S54" s="365"/>
-      <c r="T54" s="365"/>
-      <c r="U54" s="366"/>
+      <c r="O54" s="305"/>
+      <c r="P54" s="305"/>
+      <c r="Q54" s="305"/>
+      <c r="R54" s="305"/>
+      <c r="S54" s="305"/>
+      <c r="T54" s="305"/>
+      <c r="U54" s="306"/>
       <c r="V54" s="36"/>
       <c r="W54" s="14"/>
       <c r="X54" s="14"/>
@@ -12236,15 +12260,19 @@
       <c r="BE54" s="221" t="s">
         <v>47</v>
       </c>
-      <c r="BF54" s="188"/>
-      <c r="BG54" s="188"/>
+      <c r="BF54" s="210" t="s">
+        <v>243</v>
+      </c>
+      <c r="BG54" s="210" t="s">
+        <v>248</v>
+      </c>
       <c r="BH54" s="188"/>
       <c r="BI54" s="188"/>
       <c r="BJ54" s="188"/>
       <c r="BK54" s="188"/>
       <c r="BL54" s="188"/>
       <c r="BM54" s="188"/>
-      <c r="BN54" s="276" t="s">
+      <c r="BN54" s="349" t="s">
         <v>302</v>
       </c>
       <c r="BO54" s="225"/>
@@ -12262,9 +12290,9 @@
     <row r="55" spans="1:77" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="96"/>
       <c r="B55" s="96"/>
-      <c r="E55" s="285"/>
-      <c r="F55" s="287"/>
-      <c r="G55" s="286"/>
+      <c r="E55" s="343"/>
+      <c r="F55" s="344"/>
+      <c r="G55" s="345"/>
       <c r="H55" s="31"/>
       <c r="I55" s="31"/>
       <c r="J55" s="30"/>
@@ -12272,13 +12300,13 @@
       <c r="L55" s="31"/>
       <c r="M55" s="31"/>
       <c r="N55" s="33"/>
-      <c r="O55" s="365"/>
-      <c r="P55" s="365"/>
-      <c r="Q55" s="365"/>
-      <c r="R55" s="365"/>
-      <c r="S55" s="365"/>
-      <c r="T55" s="365"/>
-      <c r="U55" s="366"/>
+      <c r="O55" s="305"/>
+      <c r="P55" s="305"/>
+      <c r="Q55" s="305"/>
+      <c r="R55" s="305"/>
+      <c r="S55" s="305"/>
+      <c r="T55" s="305"/>
+      <c r="U55" s="306"/>
       <c r="V55" s="36"/>
       <c r="W55" s="14"/>
       <c r="X55" s="14"/>
@@ -12295,7 +12323,7 @@
       <c r="AW55" s="252" t="s">
         <v>253</v>
       </c>
-      <c r="AX55" s="268" t="s">
+      <c r="AX55" s="267" t="s">
         <v>648</v>
       </c>
       <c r="AY55" s="193"/>
@@ -12306,28 +12334,26 @@
       <c r="BD55" s="4"/>
       <c r="BE55" s="221"/>
       <c r="BF55" s="211" t="s">
-        <v>462</v>
+        <v>244</v>
       </c>
       <c r="BG55" s="211" t="s">
         <v>463</v>
       </c>
-      <c r="BH55" s="211" t="s">
-        <v>248</v>
-      </c>
+      <c r="BH55" s="189"/>
       <c r="BI55" s="189"/>
       <c r="BJ55" s="189"/>
       <c r="BK55" s="189"/>
       <c r="BL55" s="189"/>
       <c r="BM55" s="189"/>
-      <c r="BN55" s="276"/>
+      <c r="BN55" s="349"/>
       <c r="BO55" s="224"/>
     </row>
     <row r="56" spans="1:77" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="96"/>
       <c r="B56" s="96"/>
-      <c r="E56" s="285"/>
-      <c r="F56" s="287"/>
-      <c r="G56" s="286"/>
+      <c r="E56" s="343"/>
+      <c r="F56" s="344"/>
+      <c r="G56" s="345"/>
       <c r="H56" s="31"/>
       <c r="I56" s="31"/>
       <c r="J56" s="30"/>
@@ -12335,13 +12361,13 @@
       <c r="L56" s="31"/>
       <c r="M56" s="31"/>
       <c r="N56" s="33"/>
-      <c r="O56" s="365"/>
-      <c r="P56" s="365"/>
-      <c r="Q56" s="365"/>
-      <c r="R56" s="365"/>
-      <c r="S56" s="365"/>
-      <c r="T56" s="365"/>
-      <c r="U56" s="366"/>
+      <c r="O56" s="305"/>
+      <c r="P56" s="305"/>
+      <c r="Q56" s="305"/>
+      <c r="R56" s="305"/>
+      <c r="S56" s="305"/>
+      <c r="T56" s="305"/>
+      <c r="U56" s="306"/>
       <c r="V56" s="36"/>
       <c r="W56" s="14"/>
       <c r="X56" s="14"/>
@@ -12352,7 +12378,9 @@
       <c r="BE56" s="222" t="s">
         <v>47</v>
       </c>
-      <c r="BF56" s="204"/>
+      <c r="BF56" s="210" t="s">
+        <v>467</v>
+      </c>
       <c r="BG56" s="204"/>
       <c r="BH56" s="204"/>
       <c r="BI56" s="204"/>
@@ -12360,7 +12388,7 @@
       <c r="BK56" s="204"/>
       <c r="BL56" s="204"/>
       <c r="BM56" s="204"/>
-      <c r="BN56" s="359" t="s">
+      <c r="BN56" s="350" t="s">
         <v>303</v>
       </c>
       <c r="BO56" s="224"/>
@@ -12368,9 +12396,9 @@
     <row r="57" spans="1:77" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="96"/>
       <c r="B57" s="96"/>
-      <c r="E57" s="288"/>
-      <c r="F57" s="291"/>
-      <c r="G57" s="289"/>
+      <c r="E57" s="346"/>
+      <c r="F57" s="347"/>
+      <c r="G57" s="348"/>
       <c r="H57" s="31"/>
       <c r="I57" s="31"/>
       <c r="J57" s="30"/>
@@ -12378,13 +12406,13 @@
       <c r="L57" s="31"/>
       <c r="M57" s="31"/>
       <c r="N57" s="33"/>
-      <c r="O57" s="367"/>
-      <c r="P57" s="367"/>
-      <c r="Q57" s="367"/>
-      <c r="R57" s="367"/>
-      <c r="S57" s="367"/>
-      <c r="T57" s="367"/>
-      <c r="U57" s="368"/>
+      <c r="O57" s="308"/>
+      <c r="P57" s="308"/>
+      <c r="Q57" s="308"/>
+      <c r="R57" s="308"/>
+      <c r="S57" s="308"/>
+      <c r="T57" s="308"/>
+      <c r="U57" s="309"/>
       <c r="V57" s="36"/>
       <c r="W57" s="14"/>
       <c r="X57" s="14"/>
@@ -12396,18 +12424,14 @@
       <c r="BF57" s="243" t="s">
         <v>466</v>
       </c>
-      <c r="BG57" s="211" t="s">
-        <v>250</v>
-      </c>
-      <c r="BH57" s="211" t="s">
-        <v>467</v>
-      </c>
+      <c r="BG57" s="203"/>
+      <c r="BH57" s="203"/>
       <c r="BI57" s="203"/>
       <c r="BJ57" s="203"/>
       <c r="BK57" s="203"/>
       <c r="BL57" s="203"/>
       <c r="BM57" s="203"/>
-      <c r="BN57" s="359"/>
+      <c r="BN57" s="350"/>
       <c r="BO57" s="224"/>
     </row>
     <row r="58" spans="1:77" ht="279.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -12425,15 +12449,15 @@
       <c r="L58" s="31"/>
       <c r="M58" s="31"/>
       <c r="N58" s="33"/>
-      <c r="O58" s="425" t="s">
+      <c r="O58" s="301" t="s">
         <v>40</v>
       </c>
-      <c r="P58" s="363"/>
-      <c r="Q58" s="363"/>
-      <c r="R58" s="363"/>
-      <c r="S58" s="363"/>
-      <c r="T58" s="363"/>
-      <c r="U58" s="364"/>
+      <c r="P58" s="302"/>
+      <c r="Q58" s="302"/>
+      <c r="R58" s="302"/>
+      <c r="S58" s="302"/>
+      <c r="T58" s="302"/>
+      <c r="U58" s="303"/>
       <c r="V58" s="36"/>
       <c r="W58" s="14"/>
       <c r="X58" s="14"/>
@@ -12448,12 +12472,12 @@
       <c r="AH58" s="37"/>
       <c r="AI58" s="104"/>
       <c r="AJ58" s="104"/>
-      <c r="AK58" s="307" t="s">
+      <c r="AK58" s="351" t="s">
         <v>8</v>
       </c>
-      <c r="AL58" s="369"/>
-      <c r="AM58" s="369"/>
-      <c r="AN58" s="308"/>
+      <c r="AL58" s="352"/>
+      <c r="AM58" s="352"/>
+      <c r="AN58" s="353"/>
       <c r="AO58" s="105"/>
       <c r="AP58" s="105"/>
       <c r="AQ58" s="105"/>
@@ -12496,13 +12520,13 @@
       <c r="L59" s="31"/>
       <c r="M59" s="31"/>
       <c r="N59" s="33"/>
-      <c r="O59" s="426"/>
-      <c r="P59" s="365"/>
-      <c r="Q59" s="365"/>
-      <c r="R59" s="365"/>
-      <c r="S59" s="365"/>
-      <c r="T59" s="365"/>
-      <c r="U59" s="366"/>
+      <c r="O59" s="304"/>
+      <c r="P59" s="305"/>
+      <c r="Q59" s="305"/>
+      <c r="R59" s="305"/>
+      <c r="S59" s="305"/>
+      <c r="T59" s="305"/>
+      <c r="U59" s="306"/>
       <c r="V59" s="36"/>
       <c r="W59" s="14"/>
       <c r="X59" s="14"/>
@@ -12611,13 +12635,13 @@
       <c r="L60" s="31"/>
       <c r="M60" s="31"/>
       <c r="N60" s="33"/>
-      <c r="O60" s="426"/>
-      <c r="P60" s="365"/>
-      <c r="Q60" s="365"/>
-      <c r="R60" s="365"/>
-      <c r="S60" s="365"/>
-      <c r="T60" s="365"/>
-      <c r="U60" s="366"/>
+      <c r="O60" s="304"/>
+      <c r="P60" s="305"/>
+      <c r="Q60" s="305"/>
+      <c r="R60" s="305"/>
+      <c r="S60" s="305"/>
+      <c r="T60" s="305"/>
+      <c r="U60" s="306"/>
       <c r="V60" s="36"/>
       <c r="W60" s="14"/>
       <c r="X60" s="14"/>
@@ -12748,13 +12772,13 @@
       <c r="L61" s="31"/>
       <c r="M61" s="31"/>
       <c r="N61" s="33"/>
-      <c r="O61" s="426"/>
-      <c r="P61" s="365"/>
-      <c r="Q61" s="365"/>
-      <c r="R61" s="365"/>
-      <c r="S61" s="365"/>
-      <c r="T61" s="365"/>
-      <c r="U61" s="366"/>
+      <c r="O61" s="304"/>
+      <c r="P61" s="305"/>
+      <c r="Q61" s="305"/>
+      <c r="R61" s="305"/>
+      <c r="S61" s="305"/>
+      <c r="T61" s="305"/>
+      <c r="U61" s="306"/>
       <c r="V61" s="36"/>
       <c r="W61" s="14"/>
       <c r="X61" s="14"/>
@@ -12770,12 +12794,12 @@
       <c r="AH61" s="98"/>
       <c r="AI61" s="107"/>
       <c r="AJ61" s="152"/>
-      <c r="AK61" s="407" t="s">
+      <c r="AK61" s="280" t="s">
         <v>9</v>
       </c>
-      <c r="AL61" s="408"/>
-      <c r="AM61" s="408"/>
-      <c r="AN61" s="409"/>
+      <c r="AL61" s="281"/>
+      <c r="AM61" s="281"/>
+      <c r="AN61" s="282"/>
       <c r="AO61" s="105"/>
       <c r="AP61" s="105"/>
       <c r="AQ61" s="182">
@@ -12815,11 +12839,11 @@
       </c>
       <c r="AZ61" s="213">
         <f>COUNTIF($AB$3:$BC$55,"*402-9-*") + COUNTIF($BF$3:$BM$57,"*402-9-*")</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BA61" s="213">
         <f>COUNTIF($AB$3:$BC$55,"*402-10-*") + COUNTIF($BF$3:$BM$57,"*402-10-*")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB61" s="213">
         <f>COUNTIF($AB$3:$BC$55,"*402-11-*") + COUNTIF($BF$3:$BM$57,"*402-11-*")</f>
@@ -12871,7 +12895,7 @@
       </c>
       <c r="BN61" s="186">
         <f>SUM(AR61:BM61)/(14*22)</f>
-        <v>0.33766233766233766</v>
+        <v>0.34740259740259738</v>
       </c>
     </row>
     <row r="62" spans="1:77" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -12887,13 +12911,13 @@
       <c r="L62" s="31"/>
       <c r="M62" s="31"/>
       <c r="N62" s="33"/>
-      <c r="O62" s="426"/>
-      <c r="P62" s="365"/>
-      <c r="Q62" s="365"/>
-      <c r="R62" s="365"/>
-      <c r="S62" s="365"/>
-      <c r="T62" s="365"/>
-      <c r="U62" s="366"/>
+      <c r="O62" s="304"/>
+      <c r="P62" s="305"/>
+      <c r="Q62" s="305"/>
+      <c r="R62" s="305"/>
+      <c r="S62" s="305"/>
+      <c r="T62" s="305"/>
+      <c r="U62" s="306"/>
       <c r="V62" s="95"/>
       <c r="W62" s="14"/>
       <c r="X62" s="14"/>
@@ -12904,10 +12928,10 @@
       <c r="AH62" s="98"/>
       <c r="AI62" s="107"/>
       <c r="AJ62" s="152"/>
-      <c r="AK62" s="410"/>
-      <c r="AL62" s="411"/>
-      <c r="AM62" s="411"/>
-      <c r="AN62" s="412"/>
+      <c r="AK62" s="283"/>
+      <c r="AL62" s="284"/>
+      <c r="AM62" s="284"/>
+      <c r="AN62" s="285"/>
       <c r="AO62" s="105"/>
       <c r="AP62" s="105"/>
       <c r="AQ62" s="183">
@@ -13019,13 +13043,13 @@
       <c r="L63" s="31"/>
       <c r="M63" s="31"/>
       <c r="N63" s="33"/>
-      <c r="O63" s="426"/>
-      <c r="P63" s="365"/>
-      <c r="Q63" s="365"/>
-      <c r="R63" s="365"/>
-      <c r="S63" s="365"/>
-      <c r="T63" s="365"/>
-      <c r="U63" s="366"/>
+      <c r="O63" s="304"/>
+      <c r="P63" s="305"/>
+      <c r="Q63" s="305"/>
+      <c r="R63" s="305"/>
+      <c r="S63" s="305"/>
+      <c r="T63" s="305"/>
+      <c r="U63" s="306"/>
       <c r="V63" s="95"/>
       <c r="W63" s="14"/>
       <c r="X63" s="14"/>
@@ -13036,10 +13060,10 @@
       <c r="AH63" s="98"/>
       <c r="AI63" s="107"/>
       <c r="AJ63" s="152"/>
-      <c r="AK63" s="413"/>
-      <c r="AL63" s="414"/>
-      <c r="AM63" s="414"/>
-      <c r="AN63" s="415"/>
+      <c r="AK63" s="286"/>
+      <c r="AL63" s="287"/>
+      <c r="AM63" s="287"/>
+      <c r="AN63" s="288"/>
       <c r="AO63" s="105"/>
       <c r="AP63" s="105"/>
       <c r="AQ63" s="105"/>
@@ -13060,13 +13084,13 @@
       <c r="L64" s="31"/>
       <c r="M64" s="31"/>
       <c r="N64" s="33"/>
-      <c r="O64" s="426"/>
-      <c r="P64" s="365"/>
-      <c r="Q64" s="365"/>
-      <c r="R64" s="365"/>
-      <c r="S64" s="365"/>
-      <c r="T64" s="365"/>
-      <c r="U64" s="366"/>
+      <c r="O64" s="304"/>
+      <c r="P64" s="305"/>
+      <c r="Q64" s="305"/>
+      <c r="R64" s="305"/>
+      <c r="S64" s="305"/>
+      <c r="T64" s="305"/>
+      <c r="U64" s="306"/>
       <c r="V64" s="95"/>
       <c r="W64" s="14"/>
       <c r="X64" s="14"/>
@@ -13116,13 +13140,13 @@
       <c r="L65" s="31"/>
       <c r="M65" s="31"/>
       <c r="N65" s="33"/>
-      <c r="O65" s="426"/>
-      <c r="P65" s="365"/>
-      <c r="Q65" s="365"/>
-      <c r="R65" s="365"/>
-      <c r="S65" s="365"/>
-      <c r="T65" s="365"/>
-      <c r="U65" s="366"/>
+      <c r="O65" s="304"/>
+      <c r="P65" s="305"/>
+      <c r="Q65" s="305"/>
+      <c r="R65" s="305"/>
+      <c r="S65" s="305"/>
+      <c r="T65" s="305"/>
+      <c r="U65" s="306"/>
       <c r="V65" s="95"/>
       <c r="W65" s="14"/>
       <c r="X65" s="14"/>
@@ -13171,13 +13195,13 @@
       <c r="L66" s="31"/>
       <c r="M66" s="31"/>
       <c r="N66" s="33"/>
-      <c r="O66" s="426"/>
-      <c r="P66" s="365"/>
-      <c r="Q66" s="365"/>
-      <c r="R66" s="365"/>
-      <c r="S66" s="365"/>
-      <c r="T66" s="365"/>
-      <c r="U66" s="366"/>
+      <c r="O66" s="304"/>
+      <c r="P66" s="305"/>
+      <c r="Q66" s="305"/>
+      <c r="R66" s="305"/>
+      <c r="S66" s="305"/>
+      <c r="T66" s="305"/>
+      <c r="U66" s="306"/>
       <c r="V66" s="102"/>
       <c r="W66" s="103"/>
       <c r="X66" s="14"/>
@@ -13188,21 +13212,21 @@
       <c r="AH66" s="98"/>
       <c r="AI66" s="98"/>
       <c r="AJ66" s="98"/>
-      <c r="AK66" s="416" t="s">
+      <c r="AK66" s="289" t="s">
         <v>10</v>
       </c>
-      <c r="AL66" s="417"/>
-      <c r="AM66" s="417"/>
-      <c r="AN66" s="417"/>
-      <c r="AO66" s="417"/>
-      <c r="AP66" s="418"/>
+      <c r="AL66" s="290"/>
+      <c r="AM66" s="290"/>
+      <c r="AN66" s="290"/>
+      <c r="AO66" s="290"/>
+      <c r="AP66" s="291"/>
       <c r="AQ66" s="105"/>
       <c r="AR66" s="40"/>
-      <c r="AS66" s="360" t="s">
+      <c r="AS66" s="298" t="s">
         <v>0</v>
       </c>
       <c r="AT66" s="173"/>
-      <c r="AU66" s="360" t="s">
+      <c r="AU66" s="298" t="s">
         <v>1</v>
       </c>
       <c r="AW66" s="170"/>
@@ -13236,13 +13260,13 @@
       <c r="L67" s="31"/>
       <c r="M67" s="31"/>
       <c r="N67" s="33"/>
-      <c r="O67" s="426"/>
-      <c r="P67" s="365"/>
-      <c r="Q67" s="365"/>
-      <c r="R67" s="365"/>
-      <c r="S67" s="365"/>
-      <c r="T67" s="365"/>
-      <c r="U67" s="366"/>
+      <c r="O67" s="304"/>
+      <c r="P67" s="305"/>
+      <c r="Q67" s="305"/>
+      <c r="R67" s="305"/>
+      <c r="S67" s="305"/>
+      <c r="T67" s="305"/>
+      <c r="U67" s="306"/>
       <c r="V67" s="95"/>
       <c r="W67" s="103"/>
       <c r="X67" s="14"/>
@@ -13252,17 +13276,17 @@
       <c r="AH67" s="9"/>
       <c r="AI67" s="98"/>
       <c r="AJ67" s="98"/>
-      <c r="AK67" s="419"/>
-      <c r="AL67" s="420"/>
-      <c r="AM67" s="420"/>
-      <c r="AN67" s="420"/>
-      <c r="AO67" s="420"/>
-      <c r="AP67" s="421"/>
+      <c r="AK67" s="292"/>
+      <c r="AL67" s="293"/>
+      <c r="AM67" s="293"/>
+      <c r="AN67" s="293"/>
+      <c r="AO67" s="293"/>
+      <c r="AP67" s="294"/>
       <c r="AQ67" s="44"/>
       <c r="AR67" s="44"/>
-      <c r="AS67" s="361"/>
+      <c r="AS67" s="299"/>
       <c r="AT67" s="174"/>
-      <c r="AU67" s="361"/>
+      <c r="AU67" s="299"/>
       <c r="BC67" s="39"/>
       <c r="BE67" s="4"/>
       <c r="BF67" s="4"/>
@@ -13287,13 +13311,13 @@
       <c r="L68" s="31"/>
       <c r="M68" s="31"/>
       <c r="N68" s="33"/>
-      <c r="O68" s="426"/>
-      <c r="P68" s="365"/>
-      <c r="Q68" s="365"/>
-      <c r="R68" s="365"/>
-      <c r="S68" s="365"/>
-      <c r="T68" s="365"/>
-      <c r="U68" s="366"/>
+      <c r="O68" s="304"/>
+      <c r="P68" s="305"/>
+      <c r="Q68" s="305"/>
+      <c r="R68" s="305"/>
+      <c r="S68" s="305"/>
+      <c r="T68" s="305"/>
+      <c r="U68" s="306"/>
       <c r="V68" s="95"/>
       <c r="W68" s="103"/>
       <c r="X68" s="14"/>
@@ -13308,17 +13332,17 @@
       <c r="AH68" s="124"/>
       <c r="AI68" s="101"/>
       <c r="AJ68" s="101"/>
-      <c r="AK68" s="422"/>
-      <c r="AL68" s="423"/>
-      <c r="AM68" s="423"/>
-      <c r="AN68" s="423"/>
-      <c r="AO68" s="423"/>
-      <c r="AP68" s="424"/>
+      <c r="AK68" s="295"/>
+      <c r="AL68" s="296"/>
+      <c r="AM68" s="296"/>
+      <c r="AN68" s="296"/>
+      <c r="AO68" s="296"/>
+      <c r="AP68" s="297"/>
       <c r="AQ68" s="101"/>
       <c r="AR68" s="101"/>
-      <c r="AS68" s="362"/>
+      <c r="AS68" s="300"/>
       <c r="AT68" s="175"/>
-      <c r="AU68" s="362"/>
+      <c r="AU68" s="300"/>
       <c r="AV68" s="125"/>
       <c r="AW68" s="125"/>
       <c r="AX68" s="125"/>
@@ -13340,13 +13364,13 @@
       <c r="L69" s="31"/>
       <c r="M69" s="31"/>
       <c r="N69" s="33"/>
-      <c r="O69" s="426"/>
-      <c r="P69" s="365"/>
-      <c r="Q69" s="365"/>
-      <c r="R69" s="365"/>
-      <c r="S69" s="365"/>
-      <c r="T69" s="365"/>
-      <c r="U69" s="366"/>
+      <c r="O69" s="304"/>
+      <c r="P69" s="305"/>
+      <c r="Q69" s="305"/>
+      <c r="R69" s="305"/>
+      <c r="S69" s="305"/>
+      <c r="T69" s="305"/>
+      <c r="U69" s="306"/>
       <c r="V69" s="95"/>
       <c r="W69" s="103"/>
       <c r="X69" s="14"/>
@@ -13355,13 +13379,13 @@
       <c r="AA69" s="94"/>
       <c r="AB69" s="117"/>
       <c r="AC69" s="117"/>
-      <c r="AD69" s="401" t="s">
+      <c r="AD69" s="272" t="s">
         <v>3</v>
       </c>
-      <c r="AE69" s="402"/>
-      <c r="AF69" s="402"/>
-      <c r="AG69" s="402"/>
-      <c r="AH69" s="403"/>
+      <c r="AE69" s="273"/>
+      <c r="AF69" s="273"/>
+      <c r="AG69" s="273"/>
+      <c r="AH69" s="274"/>
       <c r="AI69" s="129"/>
       <c r="AZ69" s="130"/>
     </row>
@@ -13378,23 +13402,23 @@
       <c r="L70" s="49"/>
       <c r="M70" s="49"/>
       <c r="N70" s="109"/>
-      <c r="O70" s="427"/>
-      <c r="P70" s="367"/>
-      <c r="Q70" s="367"/>
-      <c r="R70" s="367"/>
-      <c r="S70" s="367"/>
-      <c r="T70" s="367"/>
-      <c r="U70" s="368"/>
+      <c r="O70" s="307"/>
+      <c r="P70" s="308"/>
+      <c r="Q70" s="308"/>
+      <c r="R70" s="308"/>
+      <c r="S70" s="308"/>
+      <c r="T70" s="308"/>
+      <c r="U70" s="309"/>
       <c r="V70" s="95"/>
       <c r="W70" s="103"/>
       <c r="X70" s="14"/>
       <c r="AB70" s="117"/>
       <c r="AC70" s="117"/>
-      <c r="AD70" s="404"/>
-      <c r="AE70" s="405"/>
-      <c r="AF70" s="405"/>
-      <c r="AG70" s="405"/>
-      <c r="AH70" s="406"/>
+      <c r="AD70" s="275"/>
+      <c r="AE70" s="276"/>
+      <c r="AF70" s="276"/>
+      <c r="AG70" s="276"/>
+      <c r="AH70" s="277"/>
       <c r="AL70" s="134"/>
       <c r="AM70" s="134"/>
       <c r="AN70" s="134"/>
@@ -13645,13 +13669,13 @@
       <c r="H75" s="120"/>
       <c r="I75" s="121"/>
       <c r="J75" s="122"/>
-      <c r="K75" s="374" t="s">
+      <c r="K75" s="316" t="s">
         <v>41</v>
       </c>
-      <c r="L75" s="375"/>
-      <c r="M75" s="375"/>
-      <c r="N75" s="375"/>
-      <c r="O75" s="376"/>
+      <c r="L75" s="317"/>
+      <c r="M75" s="317"/>
+      <c r="N75" s="317"/>
+      <c r="O75" s="318"/>
       <c r="P75" s="115"/>
       <c r="Q75" s="115"/>
       <c r="R75" s="115"/>
@@ -13699,28 +13723,28 @@
     </row>
     <row r="76" spans="1:65" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="9"/>
-      <c r="B76" s="324" t="s">
+      <c r="B76" s="325" t="s">
         <v>42</v>
       </c>
-      <c r="C76" s="383"/>
-      <c r="D76" s="384"/>
-      <c r="E76" s="372" t="s">
+      <c r="C76" s="326"/>
+      <c r="D76" s="327"/>
+      <c r="E76" s="278" t="s">
         <v>43</v>
       </c>
-      <c r="F76" s="373"/>
-      <c r="G76" s="326" t="s">
+      <c r="F76" s="279"/>
+      <c r="G76" s="332" t="s">
         <v>43</v>
       </c>
-      <c r="H76" s="339"/>
-      <c r="I76" s="389" t="s">
+      <c r="H76" s="333"/>
+      <c r="I76" s="334" t="s">
         <v>44</v>
       </c>
-      <c r="J76" s="390"/>
-      <c r="K76" s="377"/>
-      <c r="L76" s="378"/>
-      <c r="M76" s="378"/>
-      <c r="N76" s="378"/>
-      <c r="O76" s="379"/>
+      <c r="J76" s="335"/>
+      <c r="K76" s="319"/>
+      <c r="L76" s="320"/>
+      <c r="M76" s="320"/>
+      <c r="N76" s="320"/>
+      <c r="O76" s="321"/>
       <c r="P76" s="115"/>
       <c r="Q76" s="115"/>
       <c r="R76" s="115"/>
@@ -13765,27 +13789,27 @@
       <c r="BJ76" s="144"/>
       <c r="BK76" s="144"/>
       <c r="BL76" s="144"/>
-      <c r="BM76" s="357"/>
+      <c r="BM76" s="354"/>
     </row>
     <row r="77" spans="1:65" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B77" s="385"/>
-      <c r="C77" s="383"/>
-      <c r="D77" s="384"/>
-      <c r="E77" s="372" t="s">
+      <c r="B77" s="328"/>
+      <c r="C77" s="326"/>
+      <c r="D77" s="327"/>
+      <c r="E77" s="278" t="s">
         <v>43</v>
       </c>
-      <c r="F77" s="393"/>
-      <c r="G77" s="372" t="s">
+      <c r="F77" s="338"/>
+      <c r="G77" s="278" t="s">
         <v>43</v>
       </c>
-      <c r="H77" s="393"/>
-      <c r="I77" s="389"/>
-      <c r="J77" s="390"/>
-      <c r="K77" s="377"/>
-      <c r="L77" s="378"/>
-      <c r="M77" s="378"/>
-      <c r="N77" s="378"/>
-      <c r="O77" s="379"/>
+      <c r="H77" s="338"/>
+      <c r="I77" s="334"/>
+      <c r="J77" s="335"/>
+      <c r="K77" s="319"/>
+      <c r="L77" s="320"/>
+      <c r="M77" s="320"/>
+      <c r="N77" s="320"/>
+      <c r="O77" s="321"/>
       <c r="P77" s="115"/>
       <c r="Q77" s="115"/>
       <c r="R77" s="115"/>
@@ -13830,28 +13854,28 @@
       <c r="BJ77" s="144"/>
       <c r="BK77" s="144"/>
       <c r="BL77" s="144"/>
-      <c r="BM77" s="357"/>
+      <c r="BM77" s="354"/>
     </row>
     <row r="78" spans="1:65" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="9"/>
-      <c r="B78" s="386"/>
-      <c r="C78" s="387"/>
-      <c r="D78" s="388"/>
-      <c r="E78" s="372" t="s">
+      <c r="B78" s="329"/>
+      <c r="C78" s="330"/>
+      <c r="D78" s="331"/>
+      <c r="E78" s="278" t="s">
         <v>45</v>
       </c>
-      <c r="F78" s="373"/>
-      <c r="G78" s="372" t="s">
+      <c r="F78" s="279"/>
+      <c r="G78" s="278" t="s">
         <v>46</v>
       </c>
-      <c r="H78" s="373"/>
-      <c r="I78" s="391"/>
-      <c r="J78" s="392"/>
-      <c r="K78" s="380"/>
-      <c r="L78" s="381"/>
-      <c r="M78" s="381"/>
-      <c r="N78" s="381"/>
-      <c r="O78" s="382"/>
+      <c r="H78" s="279"/>
+      <c r="I78" s="336"/>
+      <c r="J78" s="337"/>
+      <c r="K78" s="322"/>
+      <c r="L78" s="323"/>
+      <c r="M78" s="323"/>
+      <c r="N78" s="323"/>
+      <c r="O78" s="324"/>
       <c r="P78" s="131"/>
       <c r="Q78" s="131"/>
       <c r="R78" s="131"/>
@@ -13896,7 +13920,7 @@
       <c r="BJ78" s="144"/>
       <c r="BK78" s="144"/>
       <c r="BL78" s="144"/>
-      <c r="BM78" s="357"/>
+      <c r="BM78" s="354"/>
     </row>
     <row r="79" spans="1:65" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="135"/>
@@ -13959,7 +13983,7 @@
       <c r="BL79" s="144"/>
     </row>
     <row r="80" spans="1:65" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="350"/>
+      <c r="A80" s="271"/>
       <c r="B80" s="9"/>
       <c r="C80" s="9"/>
       <c r="D80" s="9"/>
@@ -13967,15 +13991,15 @@
       <c r="F80" s="9"/>
       <c r="G80" s="43"/>
       <c r="K80" s="41"/>
-      <c r="R80" s="399"/>
-      <c r="S80" s="399"/>
-      <c r="T80" s="399"/>
-      <c r="U80" s="399"/>
-      <c r="V80" s="399"/>
-      <c r="W80" s="399"/>
-      <c r="X80" s="399"/>
-      <c r="Y80" s="399"/>
-      <c r="Z80" s="399"/>
+      <c r="R80" s="314"/>
+      <c r="S80" s="314"/>
+      <c r="T80" s="314"/>
+      <c r="U80" s="314"/>
+      <c r="V80" s="314"/>
+      <c r="W80" s="314"/>
+      <c r="X80" s="314"/>
+      <c r="Y80" s="314"/>
+      <c r="Z80" s="314"/>
       <c r="AB80" s="101"/>
       <c r="AC80" s="101"/>
       <c r="AH80" s="145"/>
@@ -14011,7 +14035,7 @@
       <c r="BL80" s="144"/>
     </row>
     <row r="81" spans="1:64" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="350"/>
+      <c r="A81" s="271"/>
       <c r="B81" s="9"/>
       <c r="C81" s="9"/>
       <c r="D81" s="9"/>
@@ -14019,15 +14043,15 @@
       <c r="F81" s="9"/>
       <c r="G81" s="43"/>
       <c r="K81" s="41"/>
-      <c r="R81" s="400"/>
-      <c r="S81" s="400"/>
-      <c r="T81" s="400"/>
-      <c r="U81" s="400"/>
-      <c r="V81" s="400"/>
-      <c r="W81" s="400"/>
-      <c r="X81" s="400"/>
-      <c r="Y81" s="400"/>
-      <c r="Z81" s="400"/>
+      <c r="R81" s="315"/>
+      <c r="S81" s="315"/>
+      <c r="T81" s="315"/>
+      <c r="U81" s="315"/>
+      <c r="V81" s="315"/>
+      <c r="W81" s="315"/>
+      <c r="X81" s="315"/>
+      <c r="Y81" s="315"/>
+      <c r="Z81" s="315"/>
       <c r="AB81" s="163"/>
       <c r="AC81" s="161"/>
       <c r="AD81" s="161"/>
@@ -14067,18 +14091,18 @@
       <c r="BL81" s="144"/>
     </row>
     <row r="82" spans="1:64" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="350"/>
+      <c r="A82" s="271"/>
       <c r="H82" s="148"/>
       <c r="I82" s="148"/>
       <c r="J82" s="148"/>
       <c r="K82" s="92"/>
       <c r="L82" s="92"/>
-      <c r="R82" s="395"/>
-      <c r="S82" s="396"/>
-      <c r="T82" s="397"/>
-      <c r="U82" s="398"/>
-      <c r="V82" s="397"/>
-      <c r="W82" s="398"/>
+      <c r="R82" s="339"/>
+      <c r="S82" s="340"/>
+      <c r="T82" s="341"/>
+      <c r="U82" s="342"/>
+      <c r="V82" s="341"/>
+      <c r="W82" s="342"/>
       <c r="AB82" s="167"/>
       <c r="AC82" s="165"/>
       <c r="AD82" s="165"/>
@@ -14129,16 +14153,16 @@
       <c r="J83" s="92"/>
       <c r="K83" s="23"/>
       <c r="L83" s="23"/>
-      <c r="R83" s="370"/>
-      <c r="S83" s="371"/>
-      <c r="T83" s="370"/>
-      <c r="U83" s="371"/>
-      <c r="V83" s="394"/>
-      <c r="W83" s="428"/>
+      <c r="R83" s="310"/>
+      <c r="S83" s="311"/>
+      <c r="T83" s="310"/>
+      <c r="U83" s="311"/>
+      <c r="V83" s="312"/>
+      <c r="W83" s="313"/>
       <c r="X83" s="3"/>
     </row>
     <row r="84" spans="1:64" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="350"/>
+      <c r="A84" s="271"/>
       <c r="B84" s="92"/>
       <c r="C84" s="92"/>
       <c r="D84" s="92"/>
@@ -14155,18 +14179,18 @@
       <c r="O84" s="151"/>
       <c r="P84" s="115"/>
       <c r="Q84" s="23"/>
-      <c r="R84" s="370"/>
-      <c r="S84" s="371"/>
-      <c r="T84" s="370"/>
-      <c r="U84" s="371"/>
-      <c r="V84" s="370"/>
-      <c r="W84" s="371"/>
+      <c r="R84" s="310"/>
+      <c r="S84" s="311"/>
+      <c r="T84" s="310"/>
+      <c r="U84" s="311"/>
+      <c r="V84" s="310"/>
+      <c r="W84" s="311"/>
       <c r="X84" s="11"/>
-      <c r="Y84" s="370"/>
-      <c r="Z84" s="371"/>
+      <c r="Y84" s="310"/>
+      <c r="Z84" s="311"/>
     </row>
     <row r="85" spans="1:64" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="350"/>
+      <c r="A85" s="271"/>
       <c r="B85" s="44"/>
       <c r="C85" s="44"/>
       <c r="D85" s="44"/>
@@ -14184,17 +14208,17 @@
       <c r="P85" s="23"/>
       <c r="Q85" s="23"/>
       <c r="R85" s="153"/>
-      <c r="S85" s="370"/>
-      <c r="T85" s="371"/>
+      <c r="S85" s="310"/>
+      <c r="T85" s="311"/>
       <c r="U85" s="154"/>
-      <c r="V85" s="394"/>
-      <c r="W85" s="394"/>
-      <c r="X85" s="394"/>
-      <c r="Y85" s="394"/>
+      <c r="V85" s="312"/>
+      <c r="W85" s="312"/>
+      <c r="X85" s="312"/>
+      <c r="Y85" s="312"/>
       <c r="Z85" s="155"/>
     </row>
     <row r="86" spans="1:64" ht="186" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="350"/>
+      <c r="A86" s="271"/>
       <c r="B86" s="44"/>
       <c r="C86" s="44"/>
       <c r="D86" s="44"/>
@@ -14238,11 +14262,11 @@
       <c r="W87" s="99"/>
     </row>
     <row r="88" spans="1:64" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E88" s="350"/>
+      <c r="E88" s="271"/>
       <c r="F88" s="83"/>
-      <c r="G88" s="350"/>
-      <c r="H88" s="350"/>
-      <c r="I88" s="350"/>
+      <c r="G88" s="271"/>
+      <c r="H88" s="271"/>
+      <c r="I88" s="271"/>
       <c r="J88" s="99"/>
       <c r="K88" s="99"/>
       <c r="L88" s="99"/>
@@ -14259,11 +14283,11 @@
       <c r="W88" s="99"/>
     </row>
     <row r="89" spans="1:64" ht="186" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E89" s="350"/>
+      <c r="E89" s="271"/>
       <c r="F89" s="83"/>
-      <c r="G89" s="350"/>
-      <c r="H89" s="350"/>
-      <c r="I89" s="350"/>
+      <c r="G89" s="271"/>
+      <c r="H89" s="271"/>
+      <c r="I89" s="271"/>
       <c r="J89" s="99"/>
       <c r="K89" s="99"/>
       <c r="L89" s="99"/>
@@ -14284,11 +14308,11 @@
       <c r="AA89" s="162"/>
     </row>
     <row r="90" spans="1:64" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E90" s="350"/>
+      <c r="E90" s="271"/>
       <c r="F90" s="83"/>
-      <c r="G90" s="350"/>
-      <c r="H90" s="350"/>
-      <c r="I90" s="350"/>
+      <c r="G90" s="271"/>
+      <c r="H90" s="271"/>
+      <c r="I90" s="271"/>
       <c r="J90" s="99"/>
       <c r="K90" s="99"/>
       <c r="L90" s="99"/>
@@ -14318,42 +14342,125 @@
     </row>
   </sheetData>
   <mergeCells count="179">
-    <mergeCell ref="AJ21:AJ22"/>
-    <mergeCell ref="AJ23:AJ24"/>
-    <mergeCell ref="AJ25:AJ26"/>
-    <mergeCell ref="AJ27:AJ28"/>
-    <mergeCell ref="AJ30:AJ31"/>
-    <mergeCell ref="AJ32:AJ33"/>
-    <mergeCell ref="AJ34:AJ35"/>
-    <mergeCell ref="AJ36:AJ37"/>
-    <mergeCell ref="AJ38:AJ39"/>
-    <mergeCell ref="AJ3:AJ4"/>
-    <mergeCell ref="AJ5:AJ6"/>
-    <mergeCell ref="AJ7:AJ8"/>
-    <mergeCell ref="AJ9:AJ10"/>
-    <mergeCell ref="AJ11:AJ12"/>
-    <mergeCell ref="AJ13:AJ14"/>
-    <mergeCell ref="AJ15:AJ16"/>
-    <mergeCell ref="AJ17:AJ18"/>
-    <mergeCell ref="AJ19:AJ20"/>
-    <mergeCell ref="E88:E90"/>
-    <mergeCell ref="G88:G90"/>
-    <mergeCell ref="H88:H90"/>
-    <mergeCell ref="I88:I90"/>
-    <mergeCell ref="AD69:AH70"/>
-    <mergeCell ref="G78:H78"/>
-    <mergeCell ref="AK61:AN63"/>
-    <mergeCell ref="AK66:AP68"/>
-    <mergeCell ref="AS66:AS68"/>
-    <mergeCell ref="O58:U70"/>
-    <mergeCell ref="R83:S83"/>
-    <mergeCell ref="T83:U83"/>
-    <mergeCell ref="V83:W83"/>
-    <mergeCell ref="X80:X81"/>
-    <mergeCell ref="Y80:Y81"/>
-    <mergeCell ref="Z80:Z81"/>
-    <mergeCell ref="R80:R81"/>
-    <mergeCell ref="S80:S81"/>
+    <mergeCell ref="AO2:AP2"/>
+    <mergeCell ref="AT19:AT20"/>
+    <mergeCell ref="AT21:AT22"/>
+    <mergeCell ref="AT23:AT24"/>
+    <mergeCell ref="AT25:AT26"/>
+    <mergeCell ref="AT27:AT28"/>
+    <mergeCell ref="AT30:AT31"/>
+    <mergeCell ref="AT32:AT33"/>
+    <mergeCell ref="AT3:AT4"/>
+    <mergeCell ref="AT5:AT6"/>
+    <mergeCell ref="AT7:AT8"/>
+    <mergeCell ref="AT9:AT10"/>
+    <mergeCell ref="AT11:AT12"/>
+    <mergeCell ref="AT13:AT14"/>
+    <mergeCell ref="AT15:AT16"/>
+    <mergeCell ref="AT17:AT18"/>
+    <mergeCell ref="AT34:AT35"/>
+    <mergeCell ref="AT36:AT37"/>
+    <mergeCell ref="AT38:AT39"/>
+    <mergeCell ref="AT40:AT41"/>
+    <mergeCell ref="BD32:BD33"/>
+    <mergeCell ref="BD34:BD35"/>
+    <mergeCell ref="BD36:BD37"/>
+    <mergeCell ref="BD38:BD39"/>
+    <mergeCell ref="BF29:BM29"/>
+    <mergeCell ref="AV29:BC29"/>
+    <mergeCell ref="BD40:BD41"/>
+    <mergeCell ref="BD13:BD14"/>
+    <mergeCell ref="BD15:BD16"/>
+    <mergeCell ref="BD17:BD18"/>
+    <mergeCell ref="BD19:BD20"/>
+    <mergeCell ref="BD21:BD22"/>
+    <mergeCell ref="BD23:BD24"/>
+    <mergeCell ref="BD25:BD26"/>
+    <mergeCell ref="BD27:BD28"/>
+    <mergeCell ref="BD30:BD31"/>
+    <mergeCell ref="BN3:BN4"/>
+    <mergeCell ref="BN5:BN6"/>
+    <mergeCell ref="BN7:BN8"/>
+    <mergeCell ref="BN9:BN10"/>
+    <mergeCell ref="BD3:BD4"/>
+    <mergeCell ref="BD5:BD6"/>
+    <mergeCell ref="BD7:BD8"/>
+    <mergeCell ref="BD9:BD10"/>
+    <mergeCell ref="BD11:BD12"/>
+    <mergeCell ref="BN11:BN12"/>
+    <mergeCell ref="BN17:BN18"/>
+    <mergeCell ref="BN19:BN20"/>
+    <mergeCell ref="BN40:BN41"/>
+    <mergeCell ref="BN42:BN43"/>
+    <mergeCell ref="BN44:BN45"/>
+    <mergeCell ref="BN46:BN47"/>
+    <mergeCell ref="BN52:BN53"/>
+    <mergeCell ref="BN21:BN22"/>
+    <mergeCell ref="BN23:BN24"/>
+    <mergeCell ref="BN25:BN26"/>
+    <mergeCell ref="BN27:BN28"/>
+    <mergeCell ref="BN30:BN31"/>
+    <mergeCell ref="BN32:BN33"/>
+    <mergeCell ref="BN34:BN35"/>
+    <mergeCell ref="BN36:BN37"/>
+    <mergeCell ref="BN38:BN39"/>
+    <mergeCell ref="BN48:BN49"/>
+    <mergeCell ref="BN13:BN14"/>
+    <mergeCell ref="AB2:AI2"/>
+    <mergeCell ref="AV2:BC2"/>
+    <mergeCell ref="BF2:BM2"/>
+    <mergeCell ref="H3:I36"/>
+    <mergeCell ref="J3:K36"/>
+    <mergeCell ref="L3:M36"/>
+    <mergeCell ref="O3:U7"/>
+    <mergeCell ref="O8:U10"/>
+    <mergeCell ref="E25:G30"/>
+    <mergeCell ref="BN15:BN16"/>
+    <mergeCell ref="E31:G33"/>
+    <mergeCell ref="E34:G35"/>
+    <mergeCell ref="E36:G36"/>
+    <mergeCell ref="F10:G12"/>
+    <mergeCell ref="O11:U14"/>
+    <mergeCell ref="A12:B14"/>
+    <mergeCell ref="E14:G15"/>
+    <mergeCell ref="A15:B17"/>
+    <mergeCell ref="O15:U18"/>
+    <mergeCell ref="E16:G18"/>
+    <mergeCell ref="A18:B20"/>
+    <mergeCell ref="O19:U36"/>
+    <mergeCell ref="E20:G24"/>
+    <mergeCell ref="AJ40:AJ41"/>
+    <mergeCell ref="AJ42:AJ43"/>
+    <mergeCell ref="AJ44:AJ45"/>
+    <mergeCell ref="AJ46:AJ47"/>
+    <mergeCell ref="AJ48:AJ49"/>
+    <mergeCell ref="E37:M37"/>
+    <mergeCell ref="O37:U37"/>
+    <mergeCell ref="O38:O39"/>
+    <mergeCell ref="E44:F45"/>
+    <mergeCell ref="G44:G45"/>
+    <mergeCell ref="BM76:BM78"/>
+    <mergeCell ref="O42:P42"/>
+    <mergeCell ref="O43:P43"/>
+    <mergeCell ref="BD42:BD43"/>
+    <mergeCell ref="BD44:BD45"/>
+    <mergeCell ref="AT42:AT43"/>
+    <mergeCell ref="AT44:AT45"/>
+    <mergeCell ref="AT46:AT47"/>
+    <mergeCell ref="BD46:BD47"/>
+    <mergeCell ref="BD48:BD49"/>
+    <mergeCell ref="BD50:BD51"/>
+    <mergeCell ref="BD52:BD53"/>
+    <mergeCell ref="O44:P44"/>
+    <mergeCell ref="E50:G57"/>
+    <mergeCell ref="BN50:BN51"/>
+    <mergeCell ref="BN54:BN55"/>
+    <mergeCell ref="BN56:BN57"/>
+    <mergeCell ref="AU66:AU68"/>
+    <mergeCell ref="AT50:AT51"/>
+    <mergeCell ref="O48:U57"/>
+    <mergeCell ref="AT48:AT49"/>
+    <mergeCell ref="AK58:AN58"/>
     <mergeCell ref="A84:A86"/>
     <mergeCell ref="R84:S84"/>
     <mergeCell ref="T84:U84"/>
@@ -14378,125 +14485,42 @@
     <mergeCell ref="U80:U81"/>
     <mergeCell ref="V80:V81"/>
     <mergeCell ref="W80:W81"/>
-    <mergeCell ref="E50:G57"/>
-    <mergeCell ref="BN50:BN51"/>
-    <mergeCell ref="BN54:BN55"/>
-    <mergeCell ref="BN56:BN57"/>
-    <mergeCell ref="AU66:AU68"/>
-    <mergeCell ref="AT50:AT51"/>
-    <mergeCell ref="O48:U57"/>
-    <mergeCell ref="AT48:AT49"/>
-    <mergeCell ref="AK58:AN58"/>
-    <mergeCell ref="BM76:BM78"/>
-    <mergeCell ref="O42:P42"/>
-    <mergeCell ref="O43:P43"/>
-    <mergeCell ref="BD42:BD43"/>
-    <mergeCell ref="BD44:BD45"/>
-    <mergeCell ref="AT42:AT43"/>
-    <mergeCell ref="AT44:AT45"/>
-    <mergeCell ref="AT46:AT47"/>
-    <mergeCell ref="BD46:BD47"/>
-    <mergeCell ref="BD48:BD49"/>
-    <mergeCell ref="BD50:BD51"/>
-    <mergeCell ref="BD52:BD53"/>
-    <mergeCell ref="O44:P44"/>
-    <mergeCell ref="AJ40:AJ41"/>
-    <mergeCell ref="AJ42:AJ43"/>
-    <mergeCell ref="AJ44:AJ45"/>
-    <mergeCell ref="AJ46:AJ47"/>
-    <mergeCell ref="AJ48:AJ49"/>
-    <mergeCell ref="E37:M37"/>
-    <mergeCell ref="O37:U37"/>
-    <mergeCell ref="O38:O39"/>
-    <mergeCell ref="E44:F45"/>
-    <mergeCell ref="G44:G45"/>
-    <mergeCell ref="O11:U14"/>
-    <mergeCell ref="A12:B14"/>
-    <mergeCell ref="E14:G15"/>
-    <mergeCell ref="A15:B17"/>
-    <mergeCell ref="O15:U18"/>
-    <mergeCell ref="E16:G18"/>
-    <mergeCell ref="A18:B20"/>
-    <mergeCell ref="O19:U36"/>
-    <mergeCell ref="E20:G24"/>
-    <mergeCell ref="BN13:BN14"/>
-    <mergeCell ref="AB2:AI2"/>
-    <mergeCell ref="AV2:BC2"/>
-    <mergeCell ref="BF2:BM2"/>
-    <mergeCell ref="H3:I36"/>
-    <mergeCell ref="J3:K36"/>
-    <mergeCell ref="L3:M36"/>
-    <mergeCell ref="O3:U7"/>
-    <mergeCell ref="O8:U10"/>
-    <mergeCell ref="E25:G30"/>
-    <mergeCell ref="BN15:BN16"/>
-    <mergeCell ref="E31:G33"/>
-    <mergeCell ref="E34:G35"/>
-    <mergeCell ref="E36:G36"/>
-    <mergeCell ref="F10:G12"/>
-    <mergeCell ref="BN17:BN18"/>
-    <mergeCell ref="BN19:BN20"/>
-    <mergeCell ref="BN40:BN41"/>
-    <mergeCell ref="BN42:BN43"/>
-    <mergeCell ref="BN44:BN45"/>
-    <mergeCell ref="BN46:BN47"/>
-    <mergeCell ref="BN52:BN53"/>
-    <mergeCell ref="BN21:BN22"/>
-    <mergeCell ref="BN23:BN24"/>
-    <mergeCell ref="BN25:BN26"/>
-    <mergeCell ref="BN27:BN28"/>
-    <mergeCell ref="BN30:BN31"/>
-    <mergeCell ref="BN32:BN33"/>
-    <mergeCell ref="BN34:BN35"/>
-    <mergeCell ref="BN36:BN37"/>
-    <mergeCell ref="BN38:BN39"/>
-    <mergeCell ref="BN48:BN49"/>
-    <mergeCell ref="BN3:BN4"/>
-    <mergeCell ref="BN5:BN6"/>
-    <mergeCell ref="BN7:BN8"/>
-    <mergeCell ref="BN9:BN10"/>
-    <mergeCell ref="BD3:BD4"/>
-    <mergeCell ref="BD5:BD6"/>
-    <mergeCell ref="BD7:BD8"/>
-    <mergeCell ref="BD9:BD10"/>
-    <mergeCell ref="BD11:BD12"/>
-    <mergeCell ref="BN11:BN12"/>
-    <mergeCell ref="BD13:BD14"/>
-    <mergeCell ref="BD15:BD16"/>
-    <mergeCell ref="BD17:BD18"/>
-    <mergeCell ref="BD19:BD20"/>
-    <mergeCell ref="BD21:BD22"/>
-    <mergeCell ref="BD23:BD24"/>
-    <mergeCell ref="BD25:BD26"/>
-    <mergeCell ref="BD27:BD28"/>
-    <mergeCell ref="BD30:BD31"/>
-    <mergeCell ref="AT34:AT35"/>
-    <mergeCell ref="AT36:AT37"/>
-    <mergeCell ref="AT38:AT39"/>
-    <mergeCell ref="AT40:AT41"/>
-    <mergeCell ref="BD32:BD33"/>
-    <mergeCell ref="BD34:BD35"/>
-    <mergeCell ref="BD36:BD37"/>
-    <mergeCell ref="BD38:BD39"/>
-    <mergeCell ref="BF29:BM29"/>
-    <mergeCell ref="AV29:BC29"/>
-    <mergeCell ref="BD40:BD41"/>
-    <mergeCell ref="AO2:AP2"/>
-    <mergeCell ref="AT19:AT20"/>
-    <mergeCell ref="AT21:AT22"/>
-    <mergeCell ref="AT23:AT24"/>
-    <mergeCell ref="AT25:AT26"/>
-    <mergeCell ref="AT27:AT28"/>
-    <mergeCell ref="AT30:AT31"/>
-    <mergeCell ref="AT32:AT33"/>
-    <mergeCell ref="AT3:AT4"/>
-    <mergeCell ref="AT5:AT6"/>
-    <mergeCell ref="AT7:AT8"/>
-    <mergeCell ref="AT9:AT10"/>
-    <mergeCell ref="AT11:AT12"/>
-    <mergeCell ref="AT13:AT14"/>
-    <mergeCell ref="AT15:AT16"/>
-    <mergeCell ref="AT17:AT18"/>
+    <mergeCell ref="E88:E90"/>
+    <mergeCell ref="G88:G90"/>
+    <mergeCell ref="H88:H90"/>
+    <mergeCell ref="I88:I90"/>
+    <mergeCell ref="AD69:AH70"/>
+    <mergeCell ref="G78:H78"/>
+    <mergeCell ref="AK61:AN63"/>
+    <mergeCell ref="AK66:AP68"/>
+    <mergeCell ref="AS66:AS68"/>
+    <mergeCell ref="O58:U70"/>
+    <mergeCell ref="R83:S83"/>
+    <mergeCell ref="T83:U83"/>
+    <mergeCell ref="V83:W83"/>
+    <mergeCell ref="X80:X81"/>
+    <mergeCell ref="Y80:Y81"/>
+    <mergeCell ref="Z80:Z81"/>
+    <mergeCell ref="R80:R81"/>
+    <mergeCell ref="S80:S81"/>
+    <mergeCell ref="AJ3:AJ4"/>
+    <mergeCell ref="AJ5:AJ6"/>
+    <mergeCell ref="AJ7:AJ8"/>
+    <mergeCell ref="AJ9:AJ10"/>
+    <mergeCell ref="AJ11:AJ12"/>
+    <mergeCell ref="AJ13:AJ14"/>
+    <mergeCell ref="AJ15:AJ16"/>
+    <mergeCell ref="AJ17:AJ18"/>
+    <mergeCell ref="AJ19:AJ20"/>
+    <mergeCell ref="AJ21:AJ22"/>
+    <mergeCell ref="AJ23:AJ24"/>
+    <mergeCell ref="AJ25:AJ26"/>
+    <mergeCell ref="AJ27:AJ28"/>
+    <mergeCell ref="AJ30:AJ31"/>
+    <mergeCell ref="AJ32:AJ33"/>
+    <mergeCell ref="AJ34:AJ35"/>
+    <mergeCell ref="AJ36:AJ37"/>
+    <mergeCell ref="AJ38:AJ39"/>
   </mergeCells>
   <phoneticPr fontId="21" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\모듈러사업2실\★ 300. 제1공장_마감관리팀\350. 마감진행현황\BH(수정)\2026년 10월 BH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69B8E688-9204-4517-A9C3-88B6792EEC56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{038C2874-713E-4051-B453-25168DFEE6D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="788" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="682">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="821" uniqueCount="683">
   <si>
     <t>공업화 주택 샘플</t>
   </si>
@@ -4306,6 +4306,12 @@
   <si>
     <t>402-9-4/
 36SB42
+2026-10-21</t>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <t>402-7-1/
+36SB73
 2026-10-21</t>
     <phoneticPr fontId="21" type="noConversion"/>
   </si>
@@ -6322,13 +6328,400 @@
     <xf numFmtId="0" fontId="48" fillId="16" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="13" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="41" fillId="16" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="17" borderId="8" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="43" fillId="17" borderId="0" xfId="18" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="17" borderId="3" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="16" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="14" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="14" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="14" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="14" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="6" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="3" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="7" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="6" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="11" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="12" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="4" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="18" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="17" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="49" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="18" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="15" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="17" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="16" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="14" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="16" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="14" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="8" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="3" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="12" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="4" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="14" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="16" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="14" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="18" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="17" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="8" borderId="20" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6349,12 +6742,6 @@
     <xf numFmtId="0" fontId="19" fillId="8" borderId="24" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="16" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="14" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6409,397 +6796,16 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="18" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="15" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="17" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="8" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="8" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="8" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="16" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="14" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="18" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="17" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="8" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="3" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="12" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="4" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="14" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="16" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="14" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="3" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="7" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="49" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="6" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="11" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="12" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="4" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="18" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="17" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="16" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="13" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="14" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="14" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="14" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="14" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="6" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="17" borderId="8" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="17" borderId="0" xfId="18" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="17" borderId="3" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -7275,52 +7281,52 @@
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
       <c r="AA2" s="230"/>
-      <c r="AB2" s="406" t="s">
+      <c r="AB2" s="278" t="s">
         <v>4</v>
       </c>
-      <c r="AC2" s="407"/>
-      <c r="AD2" s="407"/>
-      <c r="AE2" s="407"/>
-      <c r="AF2" s="407"/>
-      <c r="AG2" s="407"/>
-      <c r="AH2" s="407"/>
-      <c r="AI2" s="408"/>
+      <c r="AC2" s="269"/>
+      <c r="AD2" s="269"/>
+      <c r="AE2" s="269"/>
+      <c r="AF2" s="269"/>
+      <c r="AG2" s="269"/>
+      <c r="AH2" s="269"/>
+      <c r="AI2" s="279"/>
       <c r="AJ2" s="2"/>
       <c r="AK2" s="230"/>
       <c r="AL2" s="200"/>
       <c r="AM2" s="201"/>
       <c r="AN2" s="201"/>
-      <c r="AO2" s="407" t="s">
+      <c r="AO2" s="269" t="s">
         <v>5</v>
       </c>
-      <c r="AP2" s="407"/>
+      <c r="AP2" s="269"/>
       <c r="AQ2" s="201"/>
       <c r="AR2" s="201"/>
       <c r="AS2" s="202"/>
       <c r="AT2" s="2"/>
       <c r="AU2" s="226"/>
-      <c r="AV2" s="409" t="s">
+      <c r="AV2" s="280" t="s">
         <v>6</v>
       </c>
-      <c r="AW2" s="410"/>
-      <c r="AX2" s="410"/>
-      <c r="AY2" s="410"/>
-      <c r="AZ2" s="410"/>
-      <c r="BA2" s="410"/>
-      <c r="BB2" s="410"/>
-      <c r="BC2" s="411"/>
+      <c r="AW2" s="281"/>
+      <c r="AX2" s="281"/>
+      <c r="AY2" s="281"/>
+      <c r="AZ2" s="281"/>
+      <c r="BA2" s="281"/>
+      <c r="BB2" s="281"/>
+      <c r="BC2" s="282"/>
       <c r="BD2" s="190"/>
       <c r="BE2" s="220"/>
-      <c r="BF2" s="409" t="s">
+      <c r="BF2" s="280" t="s">
         <v>7</v>
       </c>
-      <c r="BG2" s="410"/>
-      <c r="BH2" s="410"/>
-      <c r="BI2" s="410"/>
-      <c r="BJ2" s="410"/>
-      <c r="BK2" s="410"/>
-      <c r="BL2" s="410"/>
-      <c r="BM2" s="411"/>
+      <c r="BG2" s="281"/>
+      <c r="BH2" s="281"/>
+      <c r="BI2" s="281"/>
+      <c r="BJ2" s="281"/>
+      <c r="BK2" s="281"/>
+      <c r="BL2" s="281"/>
+      <c r="BM2" s="282"/>
       <c r="BO2" s="224"/>
     </row>
     <row r="3" spans="1:67" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -7333,28 +7339,28 @@
       </c>
       <c r="F3" s="25"/>
       <c r="G3" s="25"/>
-      <c r="H3" s="412" t="s">
+      <c r="H3" s="283" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="413"/>
-      <c r="J3" s="412" t="s">
+      <c r="I3" s="284"/>
+      <c r="J3" s="283" t="s">
         <v>15</v>
       </c>
-      <c r="K3" s="413"/>
-      <c r="L3" s="414" t="s">
+      <c r="K3" s="284"/>
+      <c r="L3" s="290" t="s">
         <v>16</v>
       </c>
-      <c r="M3" s="414"/>
+      <c r="M3" s="290"/>
       <c r="N3" s="26"/>
-      <c r="O3" s="415" t="s">
+      <c r="O3" s="292" t="s">
         <v>17</v>
       </c>
-      <c r="P3" s="416"/>
-      <c r="Q3" s="416"/>
-      <c r="R3" s="416"/>
-      <c r="S3" s="416"/>
-      <c r="T3" s="416"/>
-      <c r="U3" s="416"/>
+      <c r="P3" s="293"/>
+      <c r="Q3" s="293"/>
+      <c r="R3" s="293"/>
+      <c r="S3" s="293"/>
+      <c r="T3" s="293"/>
+      <c r="U3" s="293"/>
       <c r="V3" s="27"/>
       <c r="W3" s="28"/>
       <c r="X3" s="28"/>
@@ -7430,20 +7436,20 @@
       <c r="E4" s="30"/>
       <c r="F4" s="31"/>
       <c r="G4" s="31"/>
-      <c r="H4" s="343"/>
-      <c r="I4" s="345"/>
-      <c r="J4" s="343"/>
-      <c r="K4" s="345"/>
-      <c r="L4" s="344"/>
-      <c r="M4" s="344"/>
+      <c r="H4" s="285"/>
+      <c r="I4" s="286"/>
+      <c r="J4" s="285"/>
+      <c r="K4" s="286"/>
+      <c r="L4" s="287"/>
+      <c r="M4" s="287"/>
       <c r="N4" s="33"/>
-      <c r="O4" s="417"/>
-      <c r="P4" s="418"/>
-      <c r="Q4" s="418"/>
-      <c r="R4" s="418"/>
-      <c r="S4" s="418"/>
-      <c r="T4" s="418"/>
-      <c r="U4" s="418"/>
+      <c r="O4" s="294"/>
+      <c r="P4" s="295"/>
+      <c r="Q4" s="295"/>
+      <c r="R4" s="295"/>
+      <c r="S4" s="295"/>
+      <c r="T4" s="295"/>
+      <c r="U4" s="295"/>
       <c r="V4" s="34"/>
       <c r="W4" s="14"/>
       <c r="X4" s="14"/>
@@ -7511,20 +7517,20 @@
       <c r="E5" s="30"/>
       <c r="F5" s="31"/>
       <c r="G5" s="31"/>
-      <c r="H5" s="343"/>
-      <c r="I5" s="345"/>
-      <c r="J5" s="343"/>
-      <c r="K5" s="345"/>
-      <c r="L5" s="344"/>
-      <c r="M5" s="344"/>
+      <c r="H5" s="285"/>
+      <c r="I5" s="286"/>
+      <c r="J5" s="285"/>
+      <c r="K5" s="286"/>
+      <c r="L5" s="287"/>
+      <c r="M5" s="287"/>
       <c r="N5" s="33"/>
-      <c r="O5" s="417"/>
-      <c r="P5" s="418"/>
-      <c r="Q5" s="418"/>
-      <c r="R5" s="418"/>
-      <c r="S5" s="418"/>
-      <c r="T5" s="418"/>
-      <c r="U5" s="418"/>
+      <c r="O5" s="294"/>
+      <c r="P5" s="295"/>
+      <c r="Q5" s="295"/>
+      <c r="R5" s="295"/>
+      <c r="S5" s="295"/>
+      <c r="T5" s="295"/>
+      <c r="U5" s="295"/>
       <c r="V5" s="34"/>
       <c r="W5" s="14"/>
       <c r="X5" s="14"/>
@@ -7547,7 +7553,7 @@
       </c>
       <c r="AH5" s="204"/>
       <c r="AI5" s="204"/>
-      <c r="AJ5" s="269" t="s">
+      <c r="AJ5" s="271" t="s">
         <v>507</v>
       </c>
       <c r="AK5" s="228" t="s">
@@ -7561,7 +7567,7 @@
       <c r="AQ5" s="204"/>
       <c r="AR5" s="204"/>
       <c r="AS5" s="204"/>
-      <c r="AT5" s="269" t="s">
+      <c r="AT5" s="271" t="s">
         <v>331</v>
       </c>
       <c r="AU5" s="228" t="s">
@@ -7575,7 +7581,7 @@
       <c r="BA5" s="204"/>
       <c r="BB5" s="204"/>
       <c r="BC5" s="204"/>
-      <c r="BD5" s="269" t="s">
+      <c r="BD5" s="271" t="s">
         <v>305</v>
       </c>
       <c r="BE5" s="222" t="s">
@@ -7589,7 +7595,7 @@
       <c r="BK5" s="204"/>
       <c r="BL5" s="204"/>
       <c r="BM5" s="204"/>
-      <c r="BN5" s="269" t="s">
+      <c r="BN5" s="271" t="s">
         <v>277</v>
       </c>
       <c r="BO5" s="224"/>
@@ -7600,20 +7606,20 @@
       <c r="E6" s="30"/>
       <c r="F6" s="31"/>
       <c r="G6" s="31"/>
-      <c r="H6" s="343"/>
-      <c r="I6" s="345"/>
-      <c r="J6" s="343"/>
-      <c r="K6" s="345"/>
-      <c r="L6" s="344"/>
-      <c r="M6" s="344"/>
+      <c r="H6" s="285"/>
+      <c r="I6" s="286"/>
+      <c r="J6" s="285"/>
+      <c r="K6" s="286"/>
+      <c r="L6" s="287"/>
+      <c r="M6" s="287"/>
       <c r="N6" s="33"/>
-      <c r="O6" s="417"/>
-      <c r="P6" s="418"/>
-      <c r="Q6" s="418"/>
-      <c r="R6" s="418"/>
-      <c r="S6" s="418"/>
-      <c r="T6" s="418"/>
-      <c r="U6" s="418"/>
+      <c r="O6" s="294"/>
+      <c r="P6" s="295"/>
+      <c r="Q6" s="295"/>
+      <c r="R6" s="295"/>
+      <c r="S6" s="295"/>
+      <c r="T6" s="295"/>
+      <c r="U6" s="295"/>
       <c r="V6" s="34"/>
       <c r="W6" s="14"/>
       <c r="X6" s="14"/>
@@ -7642,7 +7648,7 @@
       <c r="AI6" s="235" t="s">
         <v>582</v>
       </c>
-      <c r="AJ6" s="269"/>
+      <c r="AJ6" s="271"/>
       <c r="AK6" s="228"/>
       <c r="AL6" s="203"/>
       <c r="AM6" s="203"/>
@@ -7652,7 +7658,7 @@
       <c r="AQ6" s="203"/>
       <c r="AR6" s="203"/>
       <c r="AS6" s="203"/>
-      <c r="AT6" s="269"/>
+      <c r="AT6" s="271"/>
       <c r="AU6" s="228"/>
       <c r="AV6" s="203"/>
       <c r="AW6" s="203"/>
@@ -7662,7 +7668,7 @@
       <c r="BA6" s="203"/>
       <c r="BB6" s="203"/>
       <c r="BC6" s="203"/>
-      <c r="BD6" s="269"/>
+      <c r="BD6" s="271"/>
       <c r="BE6" s="222"/>
       <c r="BF6" s="211" t="s">
         <v>409</v>
@@ -7676,7 +7682,7 @@
       <c r="BK6" s="203"/>
       <c r="BL6" s="203"/>
       <c r="BM6" s="203"/>
-      <c r="BN6" s="269"/>
+      <c r="BN6" s="271"/>
       <c r="BO6" s="224"/>
     </row>
     <row r="7" spans="1:67" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -7688,20 +7694,20 @@
       <c r="E7" s="30"/>
       <c r="F7" s="31"/>
       <c r="G7" s="31"/>
-      <c r="H7" s="343"/>
-      <c r="I7" s="345"/>
-      <c r="J7" s="343"/>
-      <c r="K7" s="345"/>
-      <c r="L7" s="344"/>
-      <c r="M7" s="344"/>
+      <c r="H7" s="285"/>
+      <c r="I7" s="286"/>
+      <c r="J7" s="285"/>
+      <c r="K7" s="286"/>
+      <c r="L7" s="287"/>
+      <c r="M7" s="287"/>
       <c r="N7" s="33"/>
-      <c r="O7" s="419"/>
-      <c r="P7" s="420"/>
-      <c r="Q7" s="420"/>
-      <c r="R7" s="420"/>
-      <c r="S7" s="420"/>
-      <c r="T7" s="420"/>
-      <c r="U7" s="420"/>
+      <c r="O7" s="296"/>
+      <c r="P7" s="297"/>
+      <c r="Q7" s="297"/>
+      <c r="R7" s="297"/>
+      <c r="S7" s="297"/>
+      <c r="T7" s="297"/>
+      <c r="U7" s="297"/>
       <c r="V7" s="34"/>
       <c r="W7" s="14"/>
       <c r="X7" s="14"/>
@@ -7777,22 +7783,22 @@
       <c r="E8" s="30"/>
       <c r="F8" s="31"/>
       <c r="G8" s="31"/>
-      <c r="H8" s="343"/>
-      <c r="I8" s="345"/>
-      <c r="J8" s="343"/>
-      <c r="K8" s="345"/>
-      <c r="L8" s="344"/>
-      <c r="M8" s="344"/>
+      <c r="H8" s="285"/>
+      <c r="I8" s="286"/>
+      <c r="J8" s="285"/>
+      <c r="K8" s="286"/>
+      <c r="L8" s="287"/>
+      <c r="M8" s="287"/>
       <c r="N8" s="33"/>
-      <c r="O8" s="415" t="s">
+      <c r="O8" s="292" t="s">
         <v>18</v>
       </c>
-      <c r="P8" s="416"/>
-      <c r="Q8" s="416"/>
-      <c r="R8" s="416"/>
-      <c r="S8" s="416"/>
-      <c r="T8" s="416"/>
-      <c r="U8" s="416"/>
+      <c r="P8" s="293"/>
+      <c r="Q8" s="293"/>
+      <c r="R8" s="293"/>
+      <c r="S8" s="293"/>
+      <c r="T8" s="293"/>
+      <c r="U8" s="293"/>
       <c r="V8" s="34"/>
       <c r="W8" s="14"/>
       <c r="X8" s="14"/>
@@ -7867,20 +7873,20 @@
       <c r="E9" s="30"/>
       <c r="F9" s="31"/>
       <c r="G9" s="31"/>
-      <c r="H9" s="343"/>
-      <c r="I9" s="345"/>
-      <c r="J9" s="343"/>
-      <c r="K9" s="345"/>
-      <c r="L9" s="344"/>
-      <c r="M9" s="344"/>
+      <c r="H9" s="285"/>
+      <c r="I9" s="286"/>
+      <c r="J9" s="285"/>
+      <c r="K9" s="286"/>
+      <c r="L9" s="287"/>
+      <c r="M9" s="287"/>
       <c r="N9" s="33"/>
-      <c r="O9" s="417"/>
-      <c r="P9" s="418"/>
-      <c r="Q9" s="418"/>
-      <c r="R9" s="418"/>
-      <c r="S9" s="418"/>
-      <c r="T9" s="418"/>
-      <c r="U9" s="418"/>
+      <c r="O9" s="294"/>
+      <c r="P9" s="295"/>
+      <c r="Q9" s="295"/>
+      <c r="R9" s="295"/>
+      <c r="S9" s="295"/>
+      <c r="T9" s="295"/>
+      <c r="U9" s="295"/>
       <c r="V9" s="34"/>
       <c r="W9" s="14"/>
       <c r="X9" s="14"/>
@@ -7901,7 +7907,7 @@
       <c r="AG9" s="204"/>
       <c r="AH9" s="204"/>
       <c r="AI9" s="204"/>
-      <c r="AJ9" s="269" t="s">
+      <c r="AJ9" s="271" t="s">
         <v>509</v>
       </c>
       <c r="AK9" s="228" t="s">
@@ -7915,7 +7921,7 @@
       <c r="AQ9" s="204"/>
       <c r="AR9" s="204"/>
       <c r="AS9" s="204"/>
-      <c r="AT9" s="269" t="s">
+      <c r="AT9" s="271" t="s">
         <v>333</v>
       </c>
       <c r="AU9" s="228" t="s">
@@ -7933,7 +7939,7 @@
       <c r="BC9" s="265" t="s">
         <v>96</v>
       </c>
-      <c r="BD9" s="269" t="s">
+      <c r="BD9" s="271" t="s">
         <v>307</v>
       </c>
       <c r="BE9" s="222" t="s">
@@ -7951,7 +7957,7 @@
       <c r="BM9" s="197" t="s">
         <v>52</v>
       </c>
-      <c r="BN9" s="425" t="s">
+      <c r="BN9" s="275" t="s">
         <v>279</v>
       </c>
       <c r="BO9" s="224"/>
@@ -7962,24 +7968,24 @@
       </c>
       <c r="B10" s="16"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="351" t="s">
+      <c r="F10" s="307" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="353"/>
-      <c r="H10" s="344"/>
-      <c r="I10" s="345"/>
-      <c r="J10" s="343"/>
-      <c r="K10" s="345"/>
-      <c r="L10" s="344"/>
-      <c r="M10" s="344"/>
+      <c r="G10" s="308"/>
+      <c r="H10" s="287"/>
+      <c r="I10" s="286"/>
+      <c r="J10" s="285"/>
+      <c r="K10" s="286"/>
+      <c r="L10" s="287"/>
+      <c r="M10" s="287"/>
       <c r="N10" s="33"/>
-      <c r="O10" s="417"/>
-      <c r="P10" s="418"/>
-      <c r="Q10" s="418"/>
-      <c r="R10" s="418"/>
-      <c r="S10" s="418"/>
-      <c r="T10" s="418"/>
-      <c r="U10" s="418"/>
+      <c r="O10" s="294"/>
+      <c r="P10" s="295"/>
+      <c r="Q10" s="295"/>
+      <c r="R10" s="295"/>
+      <c r="S10" s="295"/>
+      <c r="T10" s="295"/>
+      <c r="U10" s="295"/>
       <c r="V10" s="34"/>
       <c r="W10" s="14"/>
       <c r="X10" s="14"/>
@@ -8006,7 +8012,7 @@
       </c>
       <c r="AH10" s="203"/>
       <c r="AI10" s="203"/>
-      <c r="AJ10" s="269"/>
+      <c r="AJ10" s="271"/>
       <c r="AK10" s="228"/>
       <c r="AL10" s="203"/>
       <c r="AM10" s="203"/>
@@ -8016,7 +8022,7 @@
       <c r="AQ10" s="203"/>
       <c r="AR10" s="203"/>
       <c r="AS10" s="203"/>
-      <c r="AT10" s="269"/>
+      <c r="AT10" s="271"/>
       <c r="AU10" s="228"/>
       <c r="AV10" s="249"/>
       <c r="AW10" s="196" t="s">
@@ -8036,7 +8042,7 @@
       <c r="BC10" s="266" t="s">
         <v>98</v>
       </c>
-      <c r="BD10" s="269"/>
+      <c r="BD10" s="271"/>
       <c r="BE10" s="222"/>
       <c r="BF10" s="238" t="s">
         <v>161</v>
@@ -8056,31 +8062,31 @@
       <c r="BM10" s="238" t="s">
         <v>164</v>
       </c>
-      <c r="BN10" s="425"/>
+      <c r="BN10" s="275"/>
       <c r="BO10" s="224"/>
     </row>
     <row r="11" spans="1:67" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6"/>
       <c r="B11" s="18"/>
       <c r="E11" s="30"/>
-      <c r="F11" s="421"/>
-      <c r="G11" s="422"/>
-      <c r="H11" s="344"/>
-      <c r="I11" s="345"/>
-      <c r="J11" s="343"/>
-      <c r="K11" s="345"/>
-      <c r="L11" s="344"/>
-      <c r="M11" s="344"/>
+      <c r="F11" s="309"/>
+      <c r="G11" s="310"/>
+      <c r="H11" s="287"/>
+      <c r="I11" s="286"/>
+      <c r="J11" s="285"/>
+      <c r="K11" s="286"/>
+      <c r="L11" s="287"/>
+      <c r="M11" s="287"/>
       <c r="N11" s="33"/>
-      <c r="O11" s="366" t="s">
+      <c r="O11" s="313" t="s">
         <v>20</v>
       </c>
-      <c r="P11" s="367"/>
-      <c r="Q11" s="367"/>
-      <c r="R11" s="367"/>
-      <c r="S11" s="367"/>
-      <c r="T11" s="367"/>
-      <c r="U11" s="368"/>
+      <c r="P11" s="314"/>
+      <c r="Q11" s="314"/>
+      <c r="R11" s="314"/>
+      <c r="S11" s="314"/>
+      <c r="T11" s="314"/>
+      <c r="U11" s="315"/>
       <c r="V11" s="34"/>
       <c r="W11" s="14"/>
       <c r="X11" s="14"/>
@@ -8155,33 +8161,33 @@
       <c r="BM11" s="197" t="s">
         <v>180</v>
       </c>
-      <c r="BN11" s="349" t="s">
+      <c r="BN11" s="276" t="s">
         <v>280</v>
       </c>
       <c r="BO11" s="224"/>
     </row>
     <row r="12" spans="1:67" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="375" t="s">
+      <c r="A12" s="322" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="376"/>
+      <c r="B12" s="323"/>
       <c r="E12" s="46"/>
-      <c r="F12" s="423"/>
-      <c r="G12" s="424"/>
-      <c r="H12" s="344"/>
-      <c r="I12" s="345"/>
-      <c r="J12" s="343"/>
-      <c r="K12" s="345"/>
-      <c r="L12" s="344"/>
-      <c r="M12" s="344"/>
+      <c r="F12" s="311"/>
+      <c r="G12" s="312"/>
+      <c r="H12" s="287"/>
+      <c r="I12" s="286"/>
+      <c r="J12" s="285"/>
+      <c r="K12" s="286"/>
+      <c r="L12" s="287"/>
+      <c r="M12" s="287"/>
       <c r="N12" s="33"/>
-      <c r="O12" s="369"/>
-      <c r="P12" s="370"/>
-      <c r="Q12" s="370"/>
-      <c r="R12" s="370"/>
-      <c r="S12" s="370"/>
-      <c r="T12" s="370"/>
-      <c r="U12" s="371"/>
+      <c r="O12" s="316"/>
+      <c r="P12" s="317"/>
+      <c r="Q12" s="317"/>
+      <c r="R12" s="317"/>
+      <c r="S12" s="317"/>
+      <c r="T12" s="317"/>
+      <c r="U12" s="318"/>
       <c r="V12" s="34"/>
       <c r="W12" s="14"/>
       <c r="X12" s="14"/>
@@ -8256,29 +8262,29 @@
       <c r="BM12" s="238" t="s">
         <v>173</v>
       </c>
-      <c r="BN12" s="349"/>
+      <c r="BN12" s="276"/>
       <c r="BO12" s="224"/>
     </row>
     <row r="13" spans="1:67" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="325"/>
-      <c r="B13" s="377"/>
+      <c r="A13" s="324"/>
+      <c r="B13" s="325"/>
       <c r="E13" s="48"/>
       <c r="F13" s="49"/>
       <c r="G13" s="49"/>
-      <c r="H13" s="343"/>
-      <c r="I13" s="345"/>
-      <c r="J13" s="343"/>
-      <c r="K13" s="345"/>
-      <c r="L13" s="344"/>
-      <c r="M13" s="344"/>
+      <c r="H13" s="285"/>
+      <c r="I13" s="286"/>
+      <c r="J13" s="285"/>
+      <c r="K13" s="286"/>
+      <c r="L13" s="287"/>
+      <c r="M13" s="287"/>
       <c r="N13" s="33"/>
-      <c r="O13" s="369"/>
-      <c r="P13" s="370"/>
-      <c r="Q13" s="370"/>
-      <c r="R13" s="370"/>
-      <c r="S13" s="370"/>
-      <c r="T13" s="370"/>
-      <c r="U13" s="371"/>
+      <c r="O13" s="316"/>
+      <c r="P13" s="317"/>
+      <c r="Q13" s="317"/>
+      <c r="R13" s="317"/>
+      <c r="S13" s="317"/>
+      <c r="T13" s="317"/>
+      <c r="U13" s="318"/>
       <c r="V13" s="34"/>
       <c r="W13" s="14"/>
       <c r="X13" s="14"/>
@@ -8295,7 +8301,7 @@
       <c r="AG13" s="204"/>
       <c r="AH13" s="204"/>
       <c r="AI13" s="204"/>
-      <c r="AJ13" s="269" t="s">
+      <c r="AJ13" s="271" t="s">
         <v>511</v>
       </c>
       <c r="AK13" s="228" t="s">
@@ -8309,7 +8315,7 @@
       <c r="AQ13" s="204"/>
       <c r="AR13" s="204"/>
       <c r="AS13" s="204"/>
-      <c r="AT13" s="269" t="s">
+      <c r="AT13" s="271" t="s">
         <v>335</v>
       </c>
       <c r="AU13" s="228" t="s">
@@ -8325,7 +8331,7 @@
       <c r="BC13" s="197" t="s">
         <v>112</v>
       </c>
-      <c r="BD13" s="269" t="s">
+      <c r="BD13" s="271" t="s">
         <v>309</v>
       </c>
       <c r="BE13" s="222" t="s">
@@ -8334,7 +8340,9 @@
       <c r="BF13" s="197" t="s">
         <v>62</v>
       </c>
-      <c r="BG13" s="204"/>
+      <c r="BG13" s="197" t="s">
+        <v>59</v>
+      </c>
       <c r="BH13" s="204"/>
       <c r="BI13" s="246" t="s">
         <v>404</v>
@@ -8343,35 +8351,35 @@
       <c r="BK13" s="204"/>
       <c r="BL13" s="204"/>
       <c r="BM13" s="204"/>
-      <c r="BN13" s="405" t="s">
+      <c r="BN13" s="277" t="s">
         <v>281</v>
       </c>
       <c r="BO13" s="224"/>
     </row>
     <row r="14" spans="1:67" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="332"/>
-      <c r="B14" s="378"/>
+      <c r="A14" s="326"/>
+      <c r="B14" s="327"/>
       <c r="C14" s="50"/>
       <c r="D14" s="42"/>
-      <c r="E14" s="379" t="s">
+      <c r="E14" s="305" t="s">
         <v>22</v>
       </c>
-      <c r="F14" s="379"/>
-      <c r="G14" s="380"/>
-      <c r="H14" s="343"/>
-      <c r="I14" s="345"/>
-      <c r="J14" s="343"/>
-      <c r="K14" s="345"/>
-      <c r="L14" s="344"/>
-      <c r="M14" s="344"/>
+      <c r="F14" s="305"/>
+      <c r="G14" s="306"/>
+      <c r="H14" s="285"/>
+      <c r="I14" s="286"/>
+      <c r="J14" s="285"/>
+      <c r="K14" s="286"/>
+      <c r="L14" s="287"/>
+      <c r="M14" s="287"/>
       <c r="N14" s="33"/>
-      <c r="O14" s="372"/>
-      <c r="P14" s="373"/>
-      <c r="Q14" s="373"/>
-      <c r="R14" s="373"/>
-      <c r="S14" s="373"/>
-      <c r="T14" s="373"/>
-      <c r="U14" s="374"/>
+      <c r="O14" s="319"/>
+      <c r="P14" s="320"/>
+      <c r="Q14" s="320"/>
+      <c r="R14" s="320"/>
+      <c r="S14" s="320"/>
+      <c r="T14" s="320"/>
+      <c r="U14" s="321"/>
       <c r="V14" s="34"/>
       <c r="W14" s="14"/>
       <c r="X14" s="14"/>
@@ -8388,7 +8396,7 @@
       <c r="AG14" s="203"/>
       <c r="AH14" s="203"/>
       <c r="AI14" s="203"/>
-      <c r="AJ14" s="269"/>
+      <c r="AJ14" s="271"/>
       <c r="AK14" s="228"/>
       <c r="AL14" s="203"/>
       <c r="AM14" s="203"/>
@@ -8398,7 +8406,7 @@
       <c r="AQ14" s="203"/>
       <c r="AR14" s="203"/>
       <c r="AS14" s="203"/>
-      <c r="AT14" s="269"/>
+      <c r="AT14" s="271"/>
       <c r="AU14" s="228"/>
       <c r="AV14" s="196" t="s">
         <v>168</v>
@@ -8420,7 +8428,7 @@
       <c r="BC14" s="196" t="s">
         <v>101</v>
       </c>
-      <c r="BD14" s="269"/>
+      <c r="BD14" s="271"/>
       <c r="BE14" s="222"/>
       <c r="BF14" s="196" t="s">
         <v>175</v>
@@ -8432,7 +8440,9 @@
       <c r="BI14" s="235" t="s">
         <v>393</v>
       </c>
-      <c r="BJ14" s="203"/>
+      <c r="BJ14" s="244" t="s">
+        <v>682</v>
+      </c>
       <c r="BK14" s="235" t="s">
         <v>392</v>
       </c>
@@ -8440,33 +8450,33 @@
         <v>395</v>
       </c>
       <c r="BM14" s="203"/>
-      <c r="BN14" s="405"/>
+      <c r="BN14" s="277"/>
       <c r="BO14" s="224"/>
     </row>
     <row r="15" spans="1:67" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="375" t="s">
+      <c r="A15" s="322" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="383"/>
+      <c r="B15" s="328"/>
       <c r="C15" s="50"/>
       <c r="D15" s="52"/>
-      <c r="E15" s="381"/>
-      <c r="F15" s="381"/>
-      <c r="G15" s="382"/>
-      <c r="H15" s="343"/>
-      <c r="I15" s="345"/>
-      <c r="J15" s="343"/>
-      <c r="K15" s="345"/>
-      <c r="L15" s="344"/>
-      <c r="M15" s="344"/>
+      <c r="E15" s="302"/>
+      <c r="F15" s="302"/>
+      <c r="G15" s="303"/>
+      <c r="H15" s="285"/>
+      <c r="I15" s="286"/>
+      <c r="J15" s="285"/>
+      <c r="K15" s="286"/>
+      <c r="L15" s="287"/>
+      <c r="M15" s="287"/>
       <c r="N15" s="33"/>
-      <c r="O15" s="385"/>
-      <c r="P15" s="386"/>
-      <c r="Q15" s="386"/>
-      <c r="R15" s="386"/>
-      <c r="S15" s="386"/>
-      <c r="T15" s="386"/>
-      <c r="U15" s="387"/>
+      <c r="O15" s="330"/>
+      <c r="P15" s="331"/>
+      <c r="Q15" s="331"/>
+      <c r="R15" s="331"/>
+      <c r="S15" s="331"/>
+      <c r="T15" s="331"/>
+      <c r="U15" s="332"/>
       <c r="V15" s="27"/>
       <c r="W15" s="28"/>
       <c r="X15" s="28"/>
@@ -8519,7 +8529,9 @@
       <c r="BE15" s="221" t="s">
         <v>275</v>
       </c>
-      <c r="BF15" s="188"/>
+      <c r="BF15" s="197" t="s">
+        <v>56</v>
+      </c>
       <c r="BG15" s="188"/>
       <c r="BH15" s="188"/>
       <c r="BI15" s="188"/>
@@ -8529,35 +8541,35 @@
       <c r="BK15" s="188"/>
       <c r="BL15" s="188"/>
       <c r="BM15" s="188"/>
-      <c r="BN15" s="349" t="s">
+      <c r="BN15" s="276" t="s">
         <v>282</v>
       </c>
       <c r="BO15" s="224"/>
     </row>
     <row r="16" spans="1:67" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="325"/>
-      <c r="B16" s="384"/>
+      <c r="A16" s="324"/>
+      <c r="B16" s="329"/>
       <c r="C16" s="53"/>
       <c r="D16" s="52"/>
-      <c r="E16" s="379" t="s">
+      <c r="E16" s="305" t="s">
         <v>22</v>
       </c>
-      <c r="F16" s="379"/>
-      <c r="G16" s="380"/>
-      <c r="H16" s="343"/>
-      <c r="I16" s="345"/>
-      <c r="J16" s="343"/>
-      <c r="K16" s="345"/>
-      <c r="L16" s="344"/>
-      <c r="M16" s="344"/>
+      <c r="F16" s="305"/>
+      <c r="G16" s="306"/>
+      <c r="H16" s="285"/>
+      <c r="I16" s="286"/>
+      <c r="J16" s="285"/>
+      <c r="K16" s="286"/>
+      <c r="L16" s="287"/>
+      <c r="M16" s="287"/>
       <c r="N16" s="33"/>
-      <c r="O16" s="388"/>
-      <c r="P16" s="389"/>
-      <c r="Q16" s="389"/>
-      <c r="R16" s="389"/>
-      <c r="S16" s="389"/>
-      <c r="T16" s="389"/>
-      <c r="U16" s="390"/>
+      <c r="O16" s="333"/>
+      <c r="P16" s="334"/>
+      <c r="Q16" s="334"/>
+      <c r="R16" s="334"/>
+      <c r="S16" s="334"/>
+      <c r="T16" s="334"/>
+      <c r="U16" s="335"/>
       <c r="V16" s="34"/>
       <c r="W16" s="14"/>
       <c r="X16" s="40"/>
@@ -8626,31 +8638,31 @@
         <v>396</v>
       </c>
       <c r="BM16" s="189"/>
-      <c r="BN16" s="349"/>
+      <c r="BN16" s="276"/>
       <c r="BO16" s="224"/>
     </row>
     <row r="17" spans="1:70" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="332"/>
-      <c r="B17" s="378"/>
+      <c r="A17" s="326"/>
+      <c r="B17" s="327"/>
       <c r="C17" s="50"/>
       <c r="D17" s="55"/>
-      <c r="E17" s="394"/>
-      <c r="F17" s="394"/>
-      <c r="G17" s="395"/>
-      <c r="H17" s="343"/>
-      <c r="I17" s="345"/>
-      <c r="J17" s="343"/>
-      <c r="K17" s="345"/>
-      <c r="L17" s="344"/>
-      <c r="M17" s="344"/>
+      <c r="E17" s="299"/>
+      <c r="F17" s="299"/>
+      <c r="G17" s="300"/>
+      <c r="H17" s="285"/>
+      <c r="I17" s="286"/>
+      <c r="J17" s="285"/>
+      <c r="K17" s="286"/>
+      <c r="L17" s="287"/>
+      <c r="M17" s="287"/>
       <c r="N17" s="33"/>
-      <c r="O17" s="388"/>
-      <c r="P17" s="389"/>
-      <c r="Q17" s="389"/>
-      <c r="R17" s="389"/>
-      <c r="S17" s="389"/>
-      <c r="T17" s="389"/>
-      <c r="U17" s="390"/>
+      <c r="O17" s="333"/>
+      <c r="P17" s="334"/>
+      <c r="Q17" s="334"/>
+      <c r="R17" s="334"/>
+      <c r="S17" s="334"/>
+      <c r="T17" s="334"/>
+      <c r="U17" s="335"/>
       <c r="V17" s="47"/>
       <c r="W17" s="44"/>
       <c r="X17" s="44"/>
@@ -8667,7 +8679,7 @@
       <c r="AG17" s="204"/>
       <c r="AH17" s="204"/>
       <c r="AI17" s="204"/>
-      <c r="AJ17" s="269" t="s">
+      <c r="AJ17" s="271" t="s">
         <v>513</v>
       </c>
       <c r="AK17" s="228" t="s">
@@ -8681,7 +8693,7 @@
       <c r="AQ17" s="204"/>
       <c r="AR17" s="204"/>
       <c r="AS17" s="204"/>
-      <c r="AT17" s="269" t="s">
+      <c r="AT17" s="271" t="s">
         <v>337</v>
       </c>
       <c r="AU17" s="228" t="s">
@@ -8701,7 +8713,7 @@
       </c>
       <c r="BB17" s="248"/>
       <c r="BC17" s="204"/>
-      <c r="BD17" s="269" t="s">
+      <c r="BD17" s="271" t="s">
         <v>311</v>
       </c>
       <c r="BE17" s="222" t="s">
@@ -8723,35 +8735,35 @@
       <c r="BM17" s="245" t="s">
         <v>660</v>
       </c>
-      <c r="BN17" s="405" t="s">
+      <c r="BN17" s="277" t="s">
         <v>283</v>
       </c>
       <c r="BO17" s="224"/>
     </row>
     <row r="18" spans="1:70" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="375" t="s">
+      <c r="A18" s="322" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="376"/>
+      <c r="B18" s="323"/>
       <c r="C18" s="19"/>
       <c r="D18" s="19"/>
-      <c r="E18" s="396"/>
-      <c r="F18" s="394"/>
-      <c r="G18" s="395"/>
-      <c r="H18" s="343"/>
-      <c r="I18" s="345"/>
-      <c r="J18" s="343"/>
-      <c r="K18" s="345"/>
-      <c r="L18" s="344"/>
-      <c r="M18" s="344"/>
+      <c r="E18" s="298"/>
+      <c r="F18" s="299"/>
+      <c r="G18" s="300"/>
+      <c r="H18" s="285"/>
+      <c r="I18" s="286"/>
+      <c r="J18" s="285"/>
+      <c r="K18" s="286"/>
+      <c r="L18" s="287"/>
+      <c r="M18" s="287"/>
       <c r="N18" s="33"/>
-      <c r="O18" s="391"/>
-      <c r="P18" s="392"/>
-      <c r="Q18" s="392"/>
-      <c r="R18" s="392"/>
-      <c r="S18" s="392"/>
-      <c r="T18" s="392"/>
-      <c r="U18" s="393"/>
+      <c r="O18" s="336"/>
+      <c r="P18" s="337"/>
+      <c r="Q18" s="337"/>
+      <c r="R18" s="337"/>
+      <c r="S18" s="337"/>
+      <c r="T18" s="337"/>
+      <c r="U18" s="338"/>
       <c r="V18" s="47"/>
       <c r="Z18" s="42"/>
       <c r="AA18" s="228"/>
@@ -8765,7 +8777,7 @@
       <c r="AG18" s="203"/>
       <c r="AH18" s="203"/>
       <c r="AI18" s="203"/>
-      <c r="AJ18" s="269"/>
+      <c r="AJ18" s="271"/>
       <c r="AK18" s="228"/>
       <c r="AL18" s="203"/>
       <c r="AM18" s="203"/>
@@ -8775,7 +8787,7 @@
       <c r="AQ18" s="203"/>
       <c r="AR18" s="203"/>
       <c r="AS18" s="203"/>
-      <c r="AT18" s="269"/>
+      <c r="AT18" s="271"/>
       <c r="AU18" s="228"/>
       <c r="AV18" s="211" t="s">
         <v>554</v>
@@ -8799,7 +8811,7 @@
       <c r="BC18" s="235" t="s">
         <v>107</v>
       </c>
-      <c r="BD18" s="269"/>
+      <c r="BD18" s="271"/>
       <c r="BE18" s="222"/>
       <c r="BF18" s="235" t="s">
         <v>406</v>
@@ -8823,33 +8835,33 @@
       <c r="BM18" s="244" t="s">
         <v>659</v>
       </c>
-      <c r="BN18" s="405"/>
+      <c r="BN18" s="277"/>
       <c r="BO18" s="224"/>
     </row>
     <row r="19" spans="1:70" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="325"/>
-      <c r="B19" s="377"/>
+      <c r="A19" s="324"/>
+      <c r="B19" s="325"/>
       <c r="C19" s="19"/>
       <c r="D19" s="56"/>
       <c r="E19" s="57"/>
       <c r="F19" s="58"/>
       <c r="G19" s="58"/>
-      <c r="H19" s="343"/>
-      <c r="I19" s="345"/>
-      <c r="J19" s="343"/>
-      <c r="K19" s="345"/>
-      <c r="L19" s="344"/>
-      <c r="M19" s="344"/>
+      <c r="H19" s="285"/>
+      <c r="I19" s="286"/>
+      <c r="J19" s="285"/>
+      <c r="K19" s="286"/>
+      <c r="L19" s="287"/>
+      <c r="M19" s="287"/>
       <c r="N19" s="33"/>
-      <c r="O19" s="397" t="s">
+      <c r="O19" s="340" t="s">
         <v>25</v>
       </c>
-      <c r="P19" s="398"/>
-      <c r="Q19" s="398"/>
-      <c r="R19" s="398"/>
-      <c r="S19" s="398"/>
-      <c r="T19" s="398"/>
-      <c r="U19" s="399"/>
+      <c r="P19" s="341"/>
+      <c r="Q19" s="341"/>
+      <c r="R19" s="341"/>
+      <c r="S19" s="341"/>
+      <c r="T19" s="341"/>
+      <c r="U19" s="342"/>
       <c r="Z19" s="42"/>
       <c r="AA19" s="227" t="s">
         <v>275</v>
@@ -8914,33 +8926,33 @@
       <c r="BM19" s="197" t="s">
         <v>57</v>
       </c>
-      <c r="BN19" s="349" t="s">
+      <c r="BN19" s="276" t="s">
         <v>284</v>
       </c>
       <c r="BO19" s="224"/>
     </row>
     <row r="20" spans="1:70" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="332"/>
-      <c r="B20" s="333"/>
-      <c r="E20" s="403" t="s">
+      <c r="A20" s="326"/>
+      <c r="B20" s="339"/>
+      <c r="E20" s="304" t="s">
         <v>26</v>
       </c>
-      <c r="F20" s="379"/>
-      <c r="G20" s="380"/>
-      <c r="H20" s="343"/>
-      <c r="I20" s="345"/>
-      <c r="J20" s="343"/>
-      <c r="K20" s="345"/>
-      <c r="L20" s="344"/>
-      <c r="M20" s="344"/>
+      <c r="F20" s="305"/>
+      <c r="G20" s="306"/>
+      <c r="H20" s="285"/>
+      <c r="I20" s="286"/>
+      <c r="J20" s="285"/>
+      <c r="K20" s="286"/>
+      <c r="L20" s="287"/>
+      <c r="M20" s="287"/>
       <c r="N20" s="33"/>
-      <c r="O20" s="400"/>
-      <c r="P20" s="401"/>
-      <c r="Q20" s="401"/>
-      <c r="R20" s="401"/>
-      <c r="S20" s="401"/>
-      <c r="T20" s="401"/>
-      <c r="U20" s="402"/>
+      <c r="O20" s="343"/>
+      <c r="P20" s="344"/>
+      <c r="Q20" s="344"/>
+      <c r="R20" s="344"/>
+      <c r="S20" s="344"/>
+      <c r="T20" s="344"/>
+      <c r="U20" s="345"/>
       <c r="V20" s="59"/>
       <c r="X20" s="41"/>
       <c r="Z20" s="42"/>
@@ -8991,12 +9003,9 @@
       </c>
       <c r="BD20" s="270"/>
       <c r="BE20" s="221"/>
-      <c r="BF20" s="196" t="s">
-        <v>56</v>
-      </c>
-      <c r="BG20" s="235" t="s">
-        <v>407</v>
-      </c>
+      <c r="BF20" s="189"/>
+      <c r="BG20" s="189"/>
+      <c r="BH20" s="189"/>
       <c r="BI20" s="209" t="s">
         <v>615</v>
       </c>
@@ -9012,29 +9021,29 @@
       <c r="BM20" s="238" t="s">
         <v>58</v>
       </c>
-      <c r="BN20" s="349"/>
+      <c r="BN20" s="276"/>
       <c r="BO20" s="224"/>
     </row>
     <row r="21" spans="1:70" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="40"/>
       <c r="B21" s="40"/>
-      <c r="E21" s="396"/>
-      <c r="F21" s="394"/>
-      <c r="G21" s="395"/>
-      <c r="H21" s="343"/>
-      <c r="I21" s="345"/>
-      <c r="J21" s="343"/>
-      <c r="K21" s="345"/>
-      <c r="L21" s="344"/>
-      <c r="M21" s="344"/>
+      <c r="E21" s="298"/>
+      <c r="F21" s="299"/>
+      <c r="G21" s="300"/>
+      <c r="H21" s="285"/>
+      <c r="I21" s="286"/>
+      <c r="J21" s="285"/>
+      <c r="K21" s="286"/>
+      <c r="L21" s="287"/>
+      <c r="M21" s="287"/>
       <c r="N21" s="33"/>
-      <c r="O21" s="400"/>
-      <c r="P21" s="401"/>
-      <c r="Q21" s="401"/>
-      <c r="R21" s="401"/>
-      <c r="S21" s="401"/>
-      <c r="T21" s="401"/>
-      <c r="U21" s="402"/>
+      <c r="O21" s="343"/>
+      <c r="P21" s="344"/>
+      <c r="Q21" s="344"/>
+      <c r="R21" s="344"/>
+      <c r="S21" s="344"/>
+      <c r="T21" s="344"/>
+      <c r="U21" s="345"/>
       <c r="V21" s="37"/>
       <c r="W21" s="60"/>
       <c r="X21" s="41"/>
@@ -9050,7 +9059,7 @@
       <c r="AG21" s="204"/>
       <c r="AH21" s="204"/>
       <c r="AI21" s="204"/>
-      <c r="AJ21" s="269" t="s">
+      <c r="AJ21" s="271" t="s">
         <v>515</v>
       </c>
       <c r="AK21" s="228" t="s">
@@ -9064,7 +9073,7 @@
       <c r="AQ21" s="204"/>
       <c r="AR21" s="204"/>
       <c r="AS21" s="204"/>
-      <c r="AT21" s="269" t="s">
+      <c r="AT21" s="271" t="s">
         <v>339</v>
       </c>
       <c r="AU21" s="228" t="s">
@@ -9080,7 +9089,7 @@
       <c r="BA21" s="204"/>
       <c r="BB21" s="204"/>
       <c r="BC21" s="204"/>
-      <c r="BD21" s="269" t="s">
+      <c r="BD21" s="271" t="s">
         <v>313</v>
       </c>
       <c r="BE21" s="222" t="s">
@@ -9098,7 +9107,7 @@
       <c r="BM21" s="197" t="s">
         <v>103</v>
       </c>
-      <c r="BN21" s="405" t="s">
+      <c r="BN21" s="277" t="s">
         <v>285</v>
       </c>
       <c r="BO21" s="224"/>
@@ -9106,23 +9115,23 @@
     <row r="22" spans="1:70" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="40"/>
       <c r="B22" s="40"/>
-      <c r="E22" s="396"/>
-      <c r="F22" s="394"/>
-      <c r="G22" s="395"/>
-      <c r="H22" s="343"/>
-      <c r="I22" s="345"/>
-      <c r="J22" s="343"/>
-      <c r="K22" s="345"/>
-      <c r="L22" s="344"/>
-      <c r="M22" s="344"/>
+      <c r="E22" s="298"/>
+      <c r="F22" s="299"/>
+      <c r="G22" s="300"/>
+      <c r="H22" s="285"/>
+      <c r="I22" s="286"/>
+      <c r="J22" s="285"/>
+      <c r="K22" s="286"/>
+      <c r="L22" s="287"/>
+      <c r="M22" s="287"/>
       <c r="N22" s="33"/>
-      <c r="O22" s="400"/>
-      <c r="P22" s="401"/>
-      <c r="Q22" s="401"/>
-      <c r="R22" s="401"/>
-      <c r="S22" s="401"/>
-      <c r="T22" s="401"/>
-      <c r="U22" s="402"/>
+      <c r="O22" s="343"/>
+      <c r="P22" s="344"/>
+      <c r="Q22" s="344"/>
+      <c r="R22" s="344"/>
+      <c r="S22" s="344"/>
+      <c r="T22" s="344"/>
+      <c r="U22" s="345"/>
       <c r="V22" s="45"/>
       <c r="X22" s="9"/>
       <c r="Y22" s="23"/>
@@ -9136,7 +9145,7 @@
       <c r="AG22" s="203"/>
       <c r="AH22" s="203"/>
       <c r="AI22" s="203"/>
-      <c r="AJ22" s="269"/>
+      <c r="AJ22" s="271"/>
       <c r="AK22" s="228"/>
       <c r="AL22" s="203"/>
       <c r="AM22" s="203"/>
@@ -9146,7 +9155,7 @@
       <c r="AQ22" s="203"/>
       <c r="AR22" s="203"/>
       <c r="AS22" s="203"/>
-      <c r="AT22" s="269"/>
+      <c r="AT22" s="271"/>
       <c r="AU22" s="228"/>
       <c r="AV22" s="235" t="s">
         <v>400</v>
@@ -9170,11 +9179,9 @@
       <c r="BC22" s="244" t="s">
         <v>640</v>
       </c>
-      <c r="BD22" s="269"/>
+      <c r="BD22" s="271"/>
       <c r="BE22" s="222"/>
-      <c r="BF22" s="196" t="s">
-        <v>59</v>
-      </c>
+      <c r="BF22" s="203"/>
       <c r="BG22" s="235" t="s">
         <v>410</v>
       </c>
@@ -9194,29 +9201,29 @@
       <c r="BM22" s="196" t="s">
         <v>193</v>
       </c>
-      <c r="BN22" s="405"/>
+      <c r="BN22" s="277"/>
       <c r="BO22" s="224"/>
     </row>
     <row r="23" spans="1:70" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="40"/>
       <c r="B23" s="40"/>
-      <c r="E23" s="396"/>
-      <c r="F23" s="394"/>
-      <c r="G23" s="395"/>
-      <c r="H23" s="343"/>
-      <c r="I23" s="345"/>
-      <c r="J23" s="343"/>
-      <c r="K23" s="345"/>
-      <c r="L23" s="344"/>
-      <c r="M23" s="344"/>
+      <c r="E23" s="298"/>
+      <c r="F23" s="299"/>
+      <c r="G23" s="300"/>
+      <c r="H23" s="285"/>
+      <c r="I23" s="286"/>
+      <c r="J23" s="285"/>
+      <c r="K23" s="286"/>
+      <c r="L23" s="287"/>
+      <c r="M23" s="287"/>
       <c r="N23" s="33"/>
-      <c r="O23" s="400"/>
-      <c r="P23" s="401"/>
-      <c r="Q23" s="401"/>
-      <c r="R23" s="401"/>
-      <c r="S23" s="401"/>
-      <c r="T23" s="401"/>
-      <c r="U23" s="402"/>
+      <c r="O23" s="343"/>
+      <c r="P23" s="344"/>
+      <c r="Q23" s="344"/>
+      <c r="R23" s="344"/>
+      <c r="S23" s="344"/>
+      <c r="T23" s="344"/>
+      <c r="U23" s="345"/>
       <c r="V23" s="61"/>
       <c r="Z23" s="42"/>
       <c r="AA23" s="227" t="s">
@@ -9285,7 +9292,7 @@
       <c r="BM23" s="245" t="s">
         <v>656</v>
       </c>
-      <c r="BN23" s="349" t="s">
+      <c r="BN23" s="276" t="s">
         <v>286</v>
       </c>
       <c r="BO23" s="224"/>
@@ -9293,23 +9300,23 @@
     <row r="24" spans="1:70" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="40"/>
       <c r="B24" s="40"/>
-      <c r="E24" s="404"/>
-      <c r="F24" s="381"/>
-      <c r="G24" s="382"/>
-      <c r="H24" s="343"/>
-      <c r="I24" s="345"/>
-      <c r="J24" s="343"/>
-      <c r="K24" s="345"/>
-      <c r="L24" s="344"/>
-      <c r="M24" s="344"/>
+      <c r="E24" s="301"/>
+      <c r="F24" s="302"/>
+      <c r="G24" s="303"/>
+      <c r="H24" s="285"/>
+      <c r="I24" s="286"/>
+      <c r="J24" s="285"/>
+      <c r="K24" s="286"/>
+      <c r="L24" s="287"/>
+      <c r="M24" s="287"/>
       <c r="N24" s="33"/>
-      <c r="O24" s="400"/>
-      <c r="P24" s="401"/>
-      <c r="Q24" s="401"/>
-      <c r="R24" s="401"/>
-      <c r="S24" s="401"/>
-      <c r="T24" s="401"/>
-      <c r="U24" s="402"/>
+      <c r="O24" s="343"/>
+      <c r="P24" s="344"/>
+      <c r="Q24" s="344"/>
+      <c r="R24" s="344"/>
+      <c r="S24" s="344"/>
+      <c r="T24" s="344"/>
+      <c r="U24" s="345"/>
       <c r="V24" s="61"/>
       <c r="Z24" s="42"/>
       <c r="AA24" s="227"/>
@@ -9379,31 +9386,31 @@
       <c r="BM24" s="244" t="s">
         <v>650</v>
       </c>
-      <c r="BN24" s="349"/>
+      <c r="BN24" s="276"/>
       <c r="BO24" s="224"/>
     </row>
     <row r="25" spans="1:70" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="40"/>
       <c r="B25" s="40"/>
-      <c r="E25" s="396" t="s">
+      <c r="E25" s="298" t="s">
         <v>27</v>
       </c>
-      <c r="F25" s="394"/>
-      <c r="G25" s="395"/>
-      <c r="H25" s="343"/>
-      <c r="I25" s="345"/>
-      <c r="J25" s="343"/>
-      <c r="K25" s="345"/>
-      <c r="L25" s="344"/>
-      <c r="M25" s="344"/>
+      <c r="F25" s="299"/>
+      <c r="G25" s="300"/>
+      <c r="H25" s="285"/>
+      <c r="I25" s="286"/>
+      <c r="J25" s="285"/>
+      <c r="K25" s="286"/>
+      <c r="L25" s="287"/>
+      <c r="M25" s="287"/>
       <c r="N25" s="33"/>
-      <c r="O25" s="400"/>
-      <c r="P25" s="401"/>
-      <c r="Q25" s="401"/>
-      <c r="R25" s="401"/>
-      <c r="S25" s="401"/>
-      <c r="T25" s="401"/>
-      <c r="U25" s="402"/>
+      <c r="O25" s="343"/>
+      <c r="P25" s="344"/>
+      <c r="Q25" s="344"/>
+      <c r="R25" s="344"/>
+      <c r="S25" s="344"/>
+      <c r="T25" s="344"/>
+      <c r="U25" s="345"/>
       <c r="V25" s="61"/>
       <c r="W25" s="38"/>
       <c r="X25" s="9"/>
@@ -9420,7 +9427,7 @@
       <c r="AG25" s="204"/>
       <c r="AH25" s="204"/>
       <c r="AI25" s="204"/>
-      <c r="AJ25" s="269" t="s">
+      <c r="AJ25" s="271" t="s">
         <v>517</v>
       </c>
       <c r="AK25" s="228" t="s">
@@ -9434,7 +9441,7 @@
       <c r="AQ25" s="204"/>
       <c r="AR25" s="204"/>
       <c r="AS25" s="204"/>
-      <c r="AT25" s="269" t="s">
+      <c r="AT25" s="271" t="s">
         <v>341</v>
       </c>
       <c r="AU25" s="228" t="s">
@@ -9450,7 +9457,7 @@
       <c r="BC25" s="236" t="s">
         <v>382</v>
       </c>
-      <c r="BD25" s="269" t="s">
+      <c r="BD25" s="271" t="s">
         <v>315</v>
       </c>
       <c r="BE25" s="222" t="s">
@@ -9466,7 +9473,7 @@
       <c r="BK25" s="204"/>
       <c r="BL25" s="204"/>
       <c r="BM25" s="204"/>
-      <c r="BN25" s="405" t="s">
+      <c r="BN25" s="277" t="s">
         <v>287</v>
       </c>
       <c r="BO25" s="224"/>
@@ -9474,23 +9481,23 @@
     <row r="26" spans="1:70" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="40"/>
       <c r="B26" s="40"/>
-      <c r="E26" s="396"/>
-      <c r="F26" s="394"/>
-      <c r="G26" s="395"/>
-      <c r="H26" s="343"/>
-      <c r="I26" s="345"/>
-      <c r="J26" s="343"/>
-      <c r="K26" s="345"/>
-      <c r="L26" s="344"/>
-      <c r="M26" s="344"/>
+      <c r="E26" s="298"/>
+      <c r="F26" s="299"/>
+      <c r="G26" s="300"/>
+      <c r="H26" s="285"/>
+      <c r="I26" s="286"/>
+      <c r="J26" s="285"/>
+      <c r="K26" s="286"/>
+      <c r="L26" s="287"/>
+      <c r="M26" s="287"/>
       <c r="N26" s="33"/>
-      <c r="O26" s="400"/>
-      <c r="P26" s="401"/>
-      <c r="Q26" s="401"/>
-      <c r="R26" s="401"/>
-      <c r="S26" s="401"/>
-      <c r="T26" s="401"/>
-      <c r="U26" s="402"/>
+      <c r="O26" s="343"/>
+      <c r="P26" s="344"/>
+      <c r="Q26" s="344"/>
+      <c r="R26" s="344"/>
+      <c r="S26" s="344"/>
+      <c r="T26" s="344"/>
+      <c r="U26" s="345"/>
       <c r="V26" s="62"/>
       <c r="W26" s="38"/>
       <c r="X26" s="9"/>
@@ -9505,7 +9512,7 @@
       <c r="AG26" s="203"/>
       <c r="AH26" s="203"/>
       <c r="AI26" s="203"/>
-      <c r="AJ26" s="269"/>
+      <c r="AJ26" s="271"/>
       <c r="AK26" s="228"/>
       <c r="AL26" s="203"/>
       <c r="AM26" s="203"/>
@@ -9517,7 +9524,7 @@
       <c r="AS26" s="211" t="s">
         <v>468</v>
       </c>
-      <c r="AT26" s="269"/>
+      <c r="AT26" s="271"/>
       <c r="AU26" s="228"/>
       <c r="AV26" s="243" t="s">
         <v>423</v>
@@ -9541,7 +9548,7 @@
       <c r="BC26" s="235" t="s">
         <v>117</v>
       </c>
-      <c r="BD26" s="269"/>
+      <c r="BD26" s="271"/>
       <c r="BE26" s="222"/>
       <c r="BF26" s="196" t="s">
         <v>65</v>
@@ -9565,29 +9572,29 @@
       <c r="BM26" s="244" t="s">
         <v>674</v>
       </c>
-      <c r="BN26" s="405"/>
+      <c r="BN26" s="277"/>
       <c r="BO26" s="224"/>
     </row>
     <row r="27" spans="1:70" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="40"/>
       <c r="B27" s="40"/>
-      <c r="E27" s="396"/>
-      <c r="F27" s="394"/>
-      <c r="G27" s="395"/>
-      <c r="H27" s="343"/>
-      <c r="I27" s="345"/>
-      <c r="J27" s="343"/>
-      <c r="K27" s="345"/>
-      <c r="L27" s="344"/>
-      <c r="M27" s="344"/>
+      <c r="E27" s="298"/>
+      <c r="F27" s="299"/>
+      <c r="G27" s="300"/>
+      <c r="H27" s="285"/>
+      <c r="I27" s="286"/>
+      <c r="J27" s="285"/>
+      <c r="K27" s="286"/>
+      <c r="L27" s="287"/>
+      <c r="M27" s="287"/>
       <c r="N27" s="33"/>
-      <c r="O27" s="400"/>
-      <c r="P27" s="401"/>
-      <c r="Q27" s="401"/>
-      <c r="R27" s="401"/>
-      <c r="S27" s="401"/>
-      <c r="T27" s="401"/>
-      <c r="U27" s="402"/>
+      <c r="O27" s="343"/>
+      <c r="P27" s="344"/>
+      <c r="Q27" s="344"/>
+      <c r="R27" s="344"/>
+      <c r="S27" s="344"/>
+      <c r="T27" s="344"/>
+      <c r="U27" s="345"/>
       <c r="V27" s="62"/>
       <c r="W27" s="38"/>
       <c r="X27" s="9"/>
@@ -9651,7 +9658,7 @@
       <c r="BM27" s="265" t="s">
         <v>69</v>
       </c>
-      <c r="BN27" s="349" t="s">
+      <c r="BN27" s="276" t="s">
         <v>288</v>
       </c>
       <c r="BO27" s="224"/>
@@ -9659,23 +9666,23 @@
     <row r="28" spans="1:70" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="9"/>
       <c r="B28" s="44"/>
-      <c r="E28" s="396"/>
-      <c r="F28" s="394"/>
-      <c r="G28" s="395"/>
-      <c r="H28" s="343"/>
-      <c r="I28" s="345"/>
-      <c r="J28" s="343"/>
-      <c r="K28" s="345"/>
-      <c r="L28" s="344"/>
-      <c r="M28" s="344"/>
+      <c r="E28" s="298"/>
+      <c r="F28" s="299"/>
+      <c r="G28" s="300"/>
+      <c r="H28" s="285"/>
+      <c r="I28" s="286"/>
+      <c r="J28" s="285"/>
+      <c r="K28" s="286"/>
+      <c r="L28" s="287"/>
+      <c r="M28" s="287"/>
       <c r="N28" s="33"/>
-      <c r="O28" s="400"/>
-      <c r="P28" s="401"/>
-      <c r="Q28" s="401"/>
-      <c r="R28" s="401"/>
-      <c r="S28" s="401"/>
-      <c r="T28" s="401"/>
-      <c r="U28" s="402"/>
+      <c r="O28" s="343"/>
+      <c r="P28" s="344"/>
+      <c r="Q28" s="344"/>
+      <c r="R28" s="344"/>
+      <c r="S28" s="344"/>
+      <c r="T28" s="344"/>
+      <c r="U28" s="345"/>
       <c r="V28" s="62"/>
       <c r="W28" s="37"/>
       <c r="X28" s="37"/>
@@ -9748,7 +9755,7 @@
       <c r="BM28" s="238" t="s">
         <v>70</v>
       </c>
-      <c r="BN28" s="349"/>
+      <c r="BN28" s="276"/>
       <c r="BO28" s="224"/>
       <c r="BR28" s="4" t="s">
         <v>11</v>
@@ -9757,23 +9764,23 @@
     <row r="29" spans="1:70" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="9"/>
       <c r="B29" s="44"/>
-      <c r="E29" s="396"/>
-      <c r="F29" s="394"/>
-      <c r="G29" s="395"/>
-      <c r="H29" s="343"/>
-      <c r="I29" s="345"/>
-      <c r="J29" s="343"/>
-      <c r="K29" s="345"/>
-      <c r="L29" s="344"/>
-      <c r="M29" s="344"/>
+      <c r="E29" s="298"/>
+      <c r="F29" s="299"/>
+      <c r="G29" s="300"/>
+      <c r="H29" s="285"/>
+      <c r="I29" s="286"/>
+      <c r="J29" s="285"/>
+      <c r="K29" s="286"/>
+      <c r="L29" s="287"/>
+      <c r="M29" s="287"/>
       <c r="N29" s="33"/>
-      <c r="O29" s="400"/>
-      <c r="P29" s="401"/>
-      <c r="Q29" s="401"/>
-      <c r="R29" s="401"/>
-      <c r="S29" s="401"/>
-      <c r="T29" s="401"/>
-      <c r="U29" s="402"/>
+      <c r="O29" s="343"/>
+      <c r="P29" s="344"/>
+      <c r="Q29" s="344"/>
+      <c r="R29" s="344"/>
+      <c r="S29" s="344"/>
+      <c r="T29" s="344"/>
+      <c r="U29" s="345"/>
       <c r="V29" s="44"/>
       <c r="W29" s="37"/>
       <c r="X29" s="37"/>
@@ -9807,30 +9814,30 @@
         <v>343</v>
       </c>
       <c r="AU29" s="229"/>
-      <c r="AV29" s="426" t="s">
+      <c r="AV29" s="272" t="s">
         <v>48</v>
       </c>
-      <c r="AW29" s="427"/>
-      <c r="AX29" s="427"/>
-      <c r="AY29" s="427"/>
-      <c r="AZ29" s="427"/>
-      <c r="BA29" s="427"/>
-      <c r="BB29" s="427"/>
-      <c r="BC29" s="428"/>
+      <c r="AW29" s="273"/>
+      <c r="AX29" s="273"/>
+      <c r="AY29" s="273"/>
+      <c r="AZ29" s="273"/>
+      <c r="BA29" s="273"/>
+      <c r="BB29" s="273"/>
+      <c r="BC29" s="274"/>
       <c r="BD29" s="208" t="s">
         <v>317</v>
       </c>
       <c r="BE29" s="223"/>
-      <c r="BF29" s="426" t="s">
+      <c r="BF29" s="272" t="s">
         <v>49</v>
       </c>
-      <c r="BG29" s="427"/>
-      <c r="BH29" s="427"/>
-      <c r="BI29" s="427"/>
-      <c r="BJ29" s="427"/>
-      <c r="BK29" s="427"/>
-      <c r="BL29" s="427"/>
-      <c r="BM29" s="428"/>
+      <c r="BG29" s="273"/>
+      <c r="BH29" s="273"/>
+      <c r="BI29" s="273"/>
+      <c r="BJ29" s="273"/>
+      <c r="BK29" s="273"/>
+      <c r="BL29" s="273"/>
+      <c r="BM29" s="274"/>
       <c r="BN29" s="219" t="s">
         <v>289</v>
       </c>
@@ -9839,23 +9846,23 @@
     <row r="30" spans="1:70" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="9"/>
       <c r="B30" s="44"/>
-      <c r="E30" s="404"/>
-      <c r="F30" s="381"/>
-      <c r="G30" s="382"/>
-      <c r="H30" s="343"/>
-      <c r="I30" s="345"/>
-      <c r="J30" s="343"/>
-      <c r="K30" s="345"/>
-      <c r="L30" s="344"/>
-      <c r="M30" s="344"/>
+      <c r="E30" s="301"/>
+      <c r="F30" s="302"/>
+      <c r="G30" s="303"/>
+      <c r="H30" s="285"/>
+      <c r="I30" s="286"/>
+      <c r="J30" s="285"/>
+      <c r="K30" s="286"/>
+      <c r="L30" s="287"/>
+      <c r="M30" s="287"/>
       <c r="N30" s="33"/>
-      <c r="O30" s="400"/>
-      <c r="P30" s="401"/>
-      <c r="Q30" s="401"/>
-      <c r="R30" s="401"/>
-      <c r="S30" s="401"/>
-      <c r="T30" s="401"/>
-      <c r="U30" s="402"/>
+      <c r="O30" s="343"/>
+      <c r="P30" s="344"/>
+      <c r="Q30" s="344"/>
+      <c r="R30" s="344"/>
+      <c r="S30" s="344"/>
+      <c r="T30" s="344"/>
+      <c r="U30" s="345"/>
       <c r="V30" s="44"/>
       <c r="W30" s="37"/>
       <c r="X30" s="37"/>
@@ -9920,7 +9927,7 @@
       <c r="BM30" s="245" t="s">
         <v>655</v>
       </c>
-      <c r="BN30" s="349" t="s">
+      <c r="BN30" s="276" t="s">
         <v>290</v>
       </c>
       <c r="BO30" s="224"/>
@@ -9928,25 +9935,25 @@
     <row r="31" spans="1:70" ht="279.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="9"/>
       <c r="B31" s="44"/>
-      <c r="E31" s="403" t="s">
+      <c r="E31" s="304" t="s">
         <v>28</v>
       </c>
-      <c r="F31" s="379"/>
-      <c r="G31" s="380"/>
-      <c r="H31" s="343"/>
-      <c r="I31" s="345"/>
-      <c r="J31" s="343"/>
-      <c r="K31" s="345"/>
-      <c r="L31" s="344"/>
-      <c r="M31" s="344"/>
+      <c r="F31" s="305"/>
+      <c r="G31" s="306"/>
+      <c r="H31" s="285"/>
+      <c r="I31" s="286"/>
+      <c r="J31" s="285"/>
+      <c r="K31" s="286"/>
+      <c r="L31" s="287"/>
+      <c r="M31" s="287"/>
       <c r="N31" s="67"/>
-      <c r="O31" s="400"/>
-      <c r="P31" s="401"/>
-      <c r="Q31" s="401"/>
-      <c r="R31" s="401"/>
-      <c r="S31" s="401"/>
-      <c r="T31" s="401"/>
-      <c r="U31" s="402"/>
+      <c r="O31" s="343"/>
+      <c r="P31" s="344"/>
+      <c r="Q31" s="344"/>
+      <c r="R31" s="344"/>
+      <c r="S31" s="344"/>
+      <c r="T31" s="344"/>
+      <c r="U31" s="345"/>
       <c r="V31" s="44"/>
       <c r="W31" s="37"/>
       <c r="X31" s="37"/>
@@ -10019,29 +10026,29 @@
       <c r="BM31" s="244" t="s">
         <v>672</v>
       </c>
-      <c r="BN31" s="349"/>
+      <c r="BN31" s="276"/>
       <c r="BO31" s="224"/>
     </row>
     <row r="32" spans="1:70" ht="279.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A32" s="9"/>
       <c r="B32" s="44"/>
-      <c r="E32" s="396"/>
-      <c r="F32" s="394"/>
-      <c r="G32" s="395"/>
-      <c r="H32" s="343"/>
-      <c r="I32" s="345"/>
-      <c r="J32" s="343"/>
-      <c r="K32" s="345"/>
-      <c r="L32" s="344"/>
-      <c r="M32" s="344"/>
+      <c r="E32" s="298"/>
+      <c r="F32" s="299"/>
+      <c r="G32" s="300"/>
+      <c r="H32" s="285"/>
+      <c r="I32" s="286"/>
+      <c r="J32" s="285"/>
+      <c r="K32" s="286"/>
+      <c r="L32" s="287"/>
+      <c r="M32" s="287"/>
       <c r="N32" s="33"/>
-      <c r="O32" s="400"/>
-      <c r="P32" s="401"/>
-      <c r="Q32" s="401"/>
-      <c r="R32" s="401"/>
-      <c r="S32" s="401"/>
-      <c r="T32" s="401"/>
-      <c r="U32" s="402"/>
+      <c r="O32" s="343"/>
+      <c r="P32" s="344"/>
+      <c r="Q32" s="344"/>
+      <c r="R32" s="344"/>
+      <c r="S32" s="344"/>
+      <c r="T32" s="344"/>
+      <c r="U32" s="345"/>
       <c r="W32" s="37"/>
       <c r="X32" s="37"/>
       <c r="Y32" s="66"/>
@@ -10057,7 +10064,7 @@
       <c r="AG32" s="204"/>
       <c r="AH32" s="204"/>
       <c r="AI32" s="204"/>
-      <c r="AJ32" s="269" t="s">
+      <c r="AJ32" s="271" t="s">
         <v>529</v>
       </c>
       <c r="AK32" s="228" t="s">
@@ -10071,7 +10078,7 @@
       <c r="AQ32" s="204"/>
       <c r="AR32" s="204"/>
       <c r="AS32" s="204"/>
-      <c r="AT32" s="269" t="s">
+      <c r="AT32" s="271" t="s">
         <v>345</v>
       </c>
       <c r="AU32" s="228" t="s">
@@ -10097,7 +10104,7 @@
       <c r="BC32" s="210" t="s">
         <v>435</v>
       </c>
-      <c r="BD32" s="269" t="s">
+      <c r="BD32" s="271" t="s">
         <v>319</v>
       </c>
       <c r="BE32" s="222" t="s">
@@ -10113,7 +10120,7 @@
       <c r="BK32" s="204"/>
       <c r="BL32" s="204"/>
       <c r="BM32" s="204"/>
-      <c r="BN32" s="405" t="s">
+      <c r="BN32" s="277" t="s">
         <v>291</v>
       </c>
       <c r="BO32" s="224"/>
@@ -10121,23 +10128,23 @@
     <row r="33" spans="1:67" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="9"/>
       <c r="B33" s="44"/>
-      <c r="E33" s="404"/>
-      <c r="F33" s="381"/>
-      <c r="G33" s="382"/>
-      <c r="H33" s="343"/>
-      <c r="I33" s="345"/>
-      <c r="J33" s="343"/>
-      <c r="K33" s="345"/>
-      <c r="L33" s="344"/>
-      <c r="M33" s="344"/>
+      <c r="E33" s="301"/>
+      <c r="F33" s="302"/>
+      <c r="G33" s="303"/>
+      <c r="H33" s="285"/>
+      <c r="I33" s="286"/>
+      <c r="J33" s="285"/>
+      <c r="K33" s="286"/>
+      <c r="L33" s="287"/>
+      <c r="M33" s="287"/>
       <c r="N33" s="33"/>
-      <c r="O33" s="400"/>
-      <c r="P33" s="401"/>
-      <c r="Q33" s="401"/>
-      <c r="R33" s="401"/>
-      <c r="S33" s="401"/>
-      <c r="T33" s="401"/>
-      <c r="U33" s="402"/>
+      <c r="O33" s="343"/>
+      <c r="P33" s="344"/>
+      <c r="Q33" s="344"/>
+      <c r="R33" s="344"/>
+      <c r="S33" s="344"/>
+      <c r="T33" s="344"/>
+      <c r="U33" s="345"/>
       <c r="W33" s="37"/>
       <c r="X33" s="37"/>
       <c r="Z33" s="69"/>
@@ -10150,7 +10157,7 @@
       <c r="AG33" s="203"/>
       <c r="AH33" s="203"/>
       <c r="AI33" s="203"/>
-      <c r="AJ33" s="269"/>
+      <c r="AJ33" s="271"/>
       <c r="AK33" s="228"/>
       <c r="AL33" s="209" t="s">
         <v>469</v>
@@ -10174,7 +10181,7 @@
       <c r="AS33" s="237" t="s">
         <v>433</v>
       </c>
-      <c r="AT33" s="269"/>
+      <c r="AT33" s="271"/>
       <c r="AU33" s="228"/>
       <c r="AV33" s="235" t="s">
         <v>440</v>
@@ -10196,7 +10203,7 @@
       <c r="BC33" s="211" t="s">
         <v>211</v>
       </c>
-      <c r="BD33" s="269"/>
+      <c r="BD33" s="271"/>
       <c r="BE33" s="222"/>
       <c r="BF33" s="196" t="s">
         <v>547</v>
@@ -10218,31 +10225,31 @@
       <c r="BM33" s="243" t="s">
         <v>625</v>
       </c>
-      <c r="BN33" s="405"/>
+      <c r="BN33" s="277"/>
       <c r="BO33" s="224"/>
     </row>
     <row r="34" spans="1:67" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="9"/>
       <c r="B34" s="44"/>
-      <c r="E34" s="403" t="s">
+      <c r="E34" s="304" t="s">
         <v>29</v>
       </c>
-      <c r="F34" s="379"/>
-      <c r="G34" s="380"/>
-      <c r="H34" s="343"/>
-      <c r="I34" s="345"/>
-      <c r="J34" s="343"/>
-      <c r="K34" s="345"/>
-      <c r="L34" s="344"/>
-      <c r="M34" s="344"/>
+      <c r="F34" s="305"/>
+      <c r="G34" s="306"/>
+      <c r="H34" s="285"/>
+      <c r="I34" s="286"/>
+      <c r="J34" s="285"/>
+      <c r="K34" s="286"/>
+      <c r="L34" s="287"/>
+      <c r="M34" s="287"/>
       <c r="N34" s="33"/>
-      <c r="O34" s="400"/>
-      <c r="P34" s="401"/>
-      <c r="Q34" s="401"/>
-      <c r="R34" s="401"/>
-      <c r="S34" s="401"/>
-      <c r="T34" s="401"/>
-      <c r="U34" s="402"/>
+      <c r="O34" s="343"/>
+      <c r="P34" s="344"/>
+      <c r="Q34" s="344"/>
+      <c r="R34" s="344"/>
+      <c r="S34" s="344"/>
+      <c r="T34" s="344"/>
+      <c r="U34" s="345"/>
       <c r="V34" s="41"/>
       <c r="W34" s="37"/>
       <c r="X34" s="37"/>
@@ -10318,7 +10325,7 @@
       <c r="BM34" s="210" t="s">
         <v>563</v>
       </c>
-      <c r="BN34" s="349" t="s">
+      <c r="BN34" s="276" t="s">
         <v>292</v>
       </c>
       <c r="BO34" s="224"/>
@@ -10328,23 +10335,23 @@
       <c r="B35" s="44"/>
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
-      <c r="E35" s="404"/>
-      <c r="F35" s="381"/>
-      <c r="G35" s="382"/>
-      <c r="H35" s="343"/>
-      <c r="I35" s="345"/>
-      <c r="J35" s="343"/>
-      <c r="K35" s="345"/>
-      <c r="L35" s="344"/>
-      <c r="M35" s="344"/>
+      <c r="E35" s="301"/>
+      <c r="F35" s="302"/>
+      <c r="G35" s="303"/>
+      <c r="H35" s="285"/>
+      <c r="I35" s="286"/>
+      <c r="J35" s="285"/>
+      <c r="K35" s="286"/>
+      <c r="L35" s="287"/>
+      <c r="M35" s="287"/>
       <c r="N35" s="33"/>
-      <c r="O35" s="400"/>
-      <c r="P35" s="401"/>
-      <c r="Q35" s="401"/>
-      <c r="R35" s="401"/>
-      <c r="S35" s="401"/>
-      <c r="T35" s="401"/>
-      <c r="U35" s="402"/>
+      <c r="O35" s="343"/>
+      <c r="P35" s="344"/>
+      <c r="Q35" s="344"/>
+      <c r="R35" s="344"/>
+      <c r="S35" s="344"/>
+      <c r="T35" s="344"/>
+      <c r="U35" s="345"/>
       <c r="V35" s="70"/>
       <c r="W35" s="37"/>
       <c r="X35" s="37"/>
@@ -10427,7 +10434,7 @@
       <c r="BM35" s="243" t="s">
         <v>565</v>
       </c>
-      <c r="BN35" s="349"/>
+      <c r="BN35" s="276"/>
       <c r="BO35" s="225"/>
     </row>
     <row r="36" spans="1:67" s="73" customFormat="1" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10435,25 +10442,25 @@
       <c r="B36" s="40"/>
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
-      <c r="E36" s="404" t="s">
+      <c r="E36" s="301" t="s">
         <v>30</v>
       </c>
-      <c r="F36" s="381"/>
-      <c r="G36" s="382"/>
-      <c r="H36" s="346"/>
-      <c r="I36" s="348"/>
-      <c r="J36" s="346"/>
-      <c r="K36" s="348"/>
-      <c r="L36" s="347"/>
-      <c r="M36" s="347"/>
+      <c r="F36" s="302"/>
+      <c r="G36" s="303"/>
+      <c r="H36" s="288"/>
+      <c r="I36" s="289"/>
+      <c r="J36" s="288"/>
+      <c r="K36" s="289"/>
+      <c r="L36" s="291"/>
+      <c r="M36" s="291"/>
       <c r="N36" s="33"/>
-      <c r="O36" s="400"/>
-      <c r="P36" s="401"/>
-      <c r="Q36" s="401"/>
-      <c r="R36" s="401"/>
-      <c r="S36" s="401"/>
-      <c r="T36" s="401"/>
-      <c r="U36" s="402"/>
+      <c r="O36" s="343"/>
+      <c r="P36" s="344"/>
+      <c r="Q36" s="344"/>
+      <c r="R36" s="344"/>
+      <c r="S36" s="344"/>
+      <c r="T36" s="344"/>
+      <c r="U36" s="345"/>
       <c r="V36" s="9"/>
       <c r="W36" s="4"/>
       <c r="X36" s="71"/>
@@ -10470,7 +10477,7 @@
       <c r="AG36" s="204"/>
       <c r="AH36" s="204"/>
       <c r="AI36" s="204"/>
-      <c r="AJ36" s="269" t="s">
+      <c r="AJ36" s="271" t="s">
         <v>531</v>
       </c>
       <c r="AK36" s="228" t="s">
@@ -10484,7 +10491,7 @@
       <c r="AQ36" s="204"/>
       <c r="AR36" s="204"/>
       <c r="AS36" s="204"/>
-      <c r="AT36" s="269" t="s">
+      <c r="AT36" s="271" t="s">
         <v>347</v>
       </c>
       <c r="AU36" s="228" t="s">
@@ -10508,7 +10515,7 @@
       <c r="BC36" s="210" t="s">
         <v>147</v>
       </c>
-      <c r="BD36" s="269" t="s">
+      <c r="BD36" s="271" t="s">
         <v>321</v>
       </c>
       <c r="BE36" s="222" t="s">
@@ -10524,7 +10531,7 @@
       <c r="BK36" s="204"/>
       <c r="BL36" s="204"/>
       <c r="BM36" s="204"/>
-      <c r="BN36" s="405" t="s">
+      <c r="BN36" s="277" t="s">
         <v>293</v>
       </c>
       <c r="BO36" s="225"/>
@@ -10532,27 +10539,27 @@
     <row r="37" spans="1:67" s="73" customFormat="1" ht="279.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="9"/>
       <c r="B37" s="40"/>
-      <c r="E37" s="356" t="s">
+      <c r="E37" s="346" t="s">
         <v>31</v>
       </c>
-      <c r="F37" s="356"/>
-      <c r="G37" s="356"/>
-      <c r="H37" s="356"/>
-      <c r="I37" s="356"/>
-      <c r="J37" s="356"/>
-      <c r="K37" s="356"/>
-      <c r="L37" s="356"/>
-      <c r="M37" s="356"/>
+      <c r="F37" s="346"/>
+      <c r="G37" s="346"/>
+      <c r="H37" s="346"/>
+      <c r="I37" s="346"/>
+      <c r="J37" s="346"/>
+      <c r="K37" s="346"/>
+      <c r="L37" s="346"/>
+      <c r="M37" s="346"/>
       <c r="N37" s="74"/>
-      <c r="O37" s="357" t="s">
+      <c r="O37" s="347" t="s">
         <v>31</v>
       </c>
-      <c r="P37" s="358"/>
-      <c r="Q37" s="358"/>
-      <c r="R37" s="358"/>
-      <c r="S37" s="358"/>
-      <c r="T37" s="358"/>
-      <c r="U37" s="358"/>
+      <c r="P37" s="348"/>
+      <c r="Q37" s="348"/>
+      <c r="R37" s="348"/>
+      <c r="S37" s="348"/>
+      <c r="T37" s="348"/>
+      <c r="U37" s="348"/>
       <c r="V37" s="75"/>
       <c r="W37" s="76"/>
       <c r="X37" s="76"/>
@@ -10567,7 +10574,7 @@
       <c r="AG37" s="203"/>
       <c r="AH37" s="203"/>
       <c r="AI37" s="203"/>
-      <c r="AJ37" s="269"/>
+      <c r="AJ37" s="271"/>
       <c r="AK37" s="228"/>
       <c r="AL37" s="209" t="s">
         <v>481</v>
@@ -10591,7 +10598,7 @@
       <c r="AS37" s="209" t="s">
         <v>487</v>
       </c>
-      <c r="AT37" s="269"/>
+      <c r="AT37" s="271"/>
       <c r="AU37" s="228"/>
       <c r="AV37" s="244" t="s">
         <v>670</v>
@@ -10615,7 +10622,7 @@
       <c r="BC37" s="211" t="s">
         <v>133</v>
       </c>
-      <c r="BD37" s="269"/>
+      <c r="BD37" s="271"/>
       <c r="BE37" s="222"/>
       <c r="BF37" s="211" t="s">
         <v>449</v>
@@ -10633,7 +10640,7 @@
       <c r="BK37" s="203"/>
       <c r="BL37" s="203"/>
       <c r="BM37" s="250"/>
-      <c r="BN37" s="405"/>
+      <c r="BN37" s="277"/>
       <c r="BO37" s="225"/>
     </row>
     <row r="38" spans="1:67" s="73" customFormat="1" ht="279.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
@@ -10656,7 +10663,7 @@
       </c>
       <c r="M38" s="25"/>
       <c r="N38" s="81"/>
-      <c r="O38" s="359"/>
+      <c r="O38" s="349"/>
       <c r="P38" s="14"/>
       <c r="Q38" s="14"/>
       <c r="R38" s="14"/>
@@ -10716,7 +10723,9 @@
       <c r="BF38" s="210" t="s">
         <v>249</v>
       </c>
-      <c r="BG38" s="188"/>
+      <c r="BG38" s="246" t="s">
+        <v>407</v>
+      </c>
       <c r="BH38" s="188"/>
       <c r="BI38" s="188"/>
       <c r="BJ38" s="188"/>
@@ -10727,7 +10736,7 @@
       <c r="BM38" s="246" t="s">
         <v>378</v>
       </c>
-      <c r="BN38" s="349" t="s">
+      <c r="BN38" s="276" t="s">
         <v>294</v>
       </c>
       <c r="BO38" s="225"/>
@@ -10746,7 +10755,7 @@
       <c r="L39" s="31"/>
       <c r="M39" s="31"/>
       <c r="N39" s="81"/>
-      <c r="O39" s="271"/>
+      <c r="O39" s="350"/>
       <c r="P39" s="14"/>
       <c r="Q39" s="14"/>
       <c r="R39" s="14"/>
@@ -10833,7 +10842,7 @@
       <c r="BM39" s="235" t="s">
         <v>265</v>
       </c>
-      <c r="BN39" s="349"/>
+      <c r="BN39" s="276"/>
       <c r="BO39" s="225"/>
     </row>
     <row r="40" spans="1:67" s="73" customFormat="1" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10871,7 +10880,7 @@
       <c r="AG40" s="204"/>
       <c r="AH40" s="204"/>
       <c r="AI40" s="204"/>
-      <c r="AJ40" s="269" t="s">
+      <c r="AJ40" s="271" t="s">
         <v>533</v>
       </c>
       <c r="AK40" s="228" t="s">
@@ -10885,7 +10894,7 @@
       <c r="AQ40" s="204"/>
       <c r="AR40" s="204"/>
       <c r="AS40" s="204"/>
-      <c r="AT40" s="269" t="s">
+      <c r="AT40" s="271" t="s">
         <v>349</v>
       </c>
       <c r="AU40" s="228" t="s">
@@ -10901,7 +10910,7 @@
       </c>
       <c r="BB40" s="204"/>
       <c r="BC40" s="204"/>
-      <c r="BD40" s="269" t="s">
+      <c r="BD40" s="271" t="s">
         <v>323</v>
       </c>
       <c r="BE40" s="222" t="s">
@@ -10923,7 +10932,7 @@
       <c r="BM40" s="197" t="s">
         <v>222</v>
       </c>
-      <c r="BN40" s="405" t="s">
+      <c r="BN40" s="277" t="s">
         <v>295</v>
       </c>
       <c r="BO40" s="225"/>
@@ -10960,7 +10969,7 @@
       <c r="AG41" s="203"/>
       <c r="AH41" s="203"/>
       <c r="AI41" s="203"/>
-      <c r="AJ41" s="269"/>
+      <c r="AJ41" s="271"/>
       <c r="AK41" s="228"/>
       <c r="AL41" s="237" t="s">
         <v>493</v>
@@ -10982,7 +10991,7 @@
         <v>578</v>
       </c>
       <c r="AS41" s="203"/>
-      <c r="AT41" s="269"/>
+      <c r="AT41" s="271"/>
       <c r="AU41" s="228"/>
       <c r="AV41" s="203"/>
       <c r="AW41" s="203"/>
@@ -11002,7 +11011,7 @@
       <c r="BC41" s="235" t="s">
         <v>426</v>
       </c>
-      <c r="BD41" s="269"/>
+      <c r="BD41" s="271"/>
       <c r="BE41" s="222"/>
       <c r="BF41" s="211" t="s">
         <v>454</v>
@@ -11026,7 +11035,7 @@
       <c r="BM41" s="196" t="s">
         <v>263</v>
       </c>
-      <c r="BN41" s="405"/>
+      <c r="BN41" s="277"/>
       <c r="BO41" s="225"/>
     </row>
     <row r="42" spans="1:67" s="73" customFormat="1" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -11042,8 +11051,8 @@
       <c r="L42" s="31"/>
       <c r="M42" s="31"/>
       <c r="N42" s="81"/>
-      <c r="O42" s="355"/>
-      <c r="P42" s="271"/>
+      <c r="O42" s="358"/>
+      <c r="P42" s="350"/>
       <c r="Q42" s="89"/>
       <c r="R42" s="89"/>
       <c r="S42" s="89"/>
@@ -11111,7 +11120,7 @@
       <c r="BM42" s="197" t="s">
         <v>90</v>
       </c>
-      <c r="BN42" s="349" t="s">
+      <c r="BN42" s="276" t="s">
         <v>296</v>
       </c>
       <c r="BO42" s="225"/>
@@ -11129,8 +11138,8 @@
       <c r="L43" s="31"/>
       <c r="M43" s="31"/>
       <c r="N43" s="81"/>
-      <c r="O43" s="355"/>
-      <c r="P43" s="271"/>
+      <c r="O43" s="358"/>
+      <c r="P43" s="350"/>
       <c r="Q43" s="89"/>
       <c r="R43" s="89"/>
       <c r="S43" s="89"/>
@@ -11218,17 +11227,17 @@
       <c r="BM43" s="196" t="s">
         <v>82</v>
       </c>
-      <c r="BN43" s="349"/>
+      <c r="BN43" s="276"/>
       <c r="BO43" s="225"/>
     </row>
     <row r="44" spans="1:67" s="73" customFormat="1" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="78"/>
       <c r="B44" s="78"/>
-      <c r="E44" s="360" t="s">
+      <c r="E44" s="351" t="s">
         <v>35</v>
       </c>
-      <c r="F44" s="361"/>
-      <c r="G44" s="364" t="s">
+      <c r="F44" s="352"/>
+      <c r="G44" s="355" t="s">
         <v>36</v>
       </c>
       <c r="H44" s="31"/>
@@ -11238,8 +11247,8 @@
       <c r="L44" s="31"/>
       <c r="M44" s="31"/>
       <c r="N44" s="81"/>
-      <c r="O44" s="355"/>
-      <c r="P44" s="271"/>
+      <c r="O44" s="358"/>
+      <c r="P44" s="350"/>
       <c r="Q44" s="89"/>
       <c r="R44" s="89"/>
       <c r="S44" s="89"/>
@@ -11260,7 +11269,7 @@
       <c r="AG44" s="204"/>
       <c r="AH44" s="204"/>
       <c r="AI44" s="204"/>
-      <c r="AJ44" s="269" t="s">
+      <c r="AJ44" s="271" t="s">
         <v>535</v>
       </c>
       <c r="AK44" s="228" t="s">
@@ -11274,7 +11283,7 @@
       <c r="AQ44" s="204"/>
       <c r="AR44" s="204"/>
       <c r="AS44" s="204"/>
-      <c r="AT44" s="269" t="s">
+      <c r="AT44" s="271" t="s">
         <v>351</v>
       </c>
       <c r="AU44" s="228" t="s">
@@ -11290,7 +11299,7 @@
       <c r="BA44" s="204"/>
       <c r="BB44" s="204"/>
       <c r="BC44" s="204"/>
-      <c r="BD44" s="269" t="s">
+      <c r="BD44" s="271" t="s">
         <v>325</v>
       </c>
       <c r="BE44" s="222" t="s">
@@ -11312,7 +11321,7 @@
       <c r="BM44" s="197" t="s">
         <v>390</v>
       </c>
-      <c r="BN44" s="405" t="s">
+      <c r="BN44" s="277" t="s">
         <v>297</v>
       </c>
       <c r="BO44" s="225"/>
@@ -11320,9 +11329,9 @@
     <row r="45" spans="1:67" s="73" customFormat="1" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="78"/>
       <c r="B45" s="78"/>
-      <c r="E45" s="362"/>
-      <c r="F45" s="363"/>
-      <c r="G45" s="365"/>
+      <c r="E45" s="353"/>
+      <c r="F45" s="354"/>
+      <c r="G45" s="356"/>
       <c r="H45" s="31"/>
       <c r="I45" s="31"/>
       <c r="J45" s="30"/>
@@ -11349,7 +11358,7 @@
       <c r="AG45" s="203"/>
       <c r="AH45" s="203"/>
       <c r="AI45" s="203"/>
-      <c r="AJ45" s="269"/>
+      <c r="AJ45" s="271"/>
       <c r="AK45" s="228"/>
       <c r="AL45" s="237" t="s">
         <v>572</v>
@@ -11371,7 +11380,7 @@
         <v>502</v>
       </c>
       <c r="AS45" s="203"/>
-      <c r="AT45" s="269"/>
+      <c r="AT45" s="271"/>
       <c r="AU45" s="228"/>
       <c r="AV45" s="211" t="s">
         <v>567</v>
@@ -11395,7 +11404,7 @@
       <c r="BC45" s="243" t="s">
         <v>668</v>
       </c>
-      <c r="BD45" s="269"/>
+      <c r="BD45" s="271"/>
       <c r="BE45" s="222"/>
       <c r="BF45" s="243" t="s">
         <v>465</v>
@@ -11417,7 +11426,7 @@
       <c r="BM45" s="196" t="s">
         <v>389</v>
       </c>
-      <c r="BN45" s="405"/>
+      <c r="BN45" s="277"/>
       <c r="BO45" s="225"/>
     </row>
     <row r="46" spans="1:67" s="73" customFormat="1" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -11501,7 +11510,7 @@
       <c r="BK46" s="188"/>
       <c r="BL46" s="188"/>
       <c r="BM46" s="188"/>
-      <c r="BN46" s="349" t="s">
+      <c r="BN46" s="276" t="s">
         <v>298</v>
       </c>
       <c r="BO46" s="225"/>
@@ -11600,7 +11609,7 @@
       <c r="BM47" s="238" t="s">
         <v>260</v>
       </c>
-      <c r="BN47" s="349"/>
+      <c r="BN47" s="276"/>
       <c r="BO47" s="224"/>
     </row>
     <row r="48" spans="1:67" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -11618,15 +11627,15 @@
       <c r="L48" s="31"/>
       <c r="M48" s="31"/>
       <c r="N48" s="81"/>
-      <c r="O48" s="302" t="s">
+      <c r="O48" s="363" t="s">
         <v>37</v>
       </c>
-      <c r="P48" s="302"/>
-      <c r="Q48" s="302"/>
-      <c r="R48" s="302"/>
-      <c r="S48" s="302"/>
-      <c r="T48" s="302"/>
-      <c r="U48" s="303"/>
+      <c r="P48" s="363"/>
+      <c r="Q48" s="363"/>
+      <c r="R48" s="363"/>
+      <c r="S48" s="363"/>
+      <c r="T48" s="363"/>
+      <c r="U48" s="364"/>
       <c r="V48" s="36"/>
       <c r="W48" s="51"/>
       <c r="X48" s="14"/>
@@ -11643,7 +11652,7 @@
       <c r="AG48" s="204"/>
       <c r="AH48" s="204"/>
       <c r="AI48" s="204"/>
-      <c r="AJ48" s="269" t="s">
+      <c r="AJ48" s="271" t="s">
         <v>537</v>
       </c>
       <c r="AK48" s="228" t="s">
@@ -11657,7 +11666,7 @@
       <c r="AQ48" s="204"/>
       <c r="AR48" s="204"/>
       <c r="AS48" s="204"/>
-      <c r="AT48" s="269" t="s">
+      <c r="AT48" s="271" t="s">
         <v>353</v>
       </c>
       <c r="AU48" s="228" t="s">
@@ -11677,7 +11686,7 @@
         <v>234</v>
       </c>
       <c r="BC48" s="204"/>
-      <c r="BD48" s="269" t="s">
+      <c r="BD48" s="271" t="s">
         <v>327</v>
       </c>
       <c r="BE48" s="222" t="s">
@@ -11695,7 +11704,7 @@
       <c r="BM48" s="197" t="s">
         <v>387</v>
       </c>
-      <c r="BN48" s="405" t="s">
+      <c r="BN48" s="277" t="s">
         <v>299</v>
       </c>
       <c r="BO48" s="224"/>
@@ -11713,13 +11722,13 @@
       <c r="L49" s="31"/>
       <c r="M49" s="31"/>
       <c r="N49" s="33"/>
-      <c r="O49" s="305"/>
-      <c r="P49" s="305"/>
-      <c r="Q49" s="305"/>
-      <c r="R49" s="305"/>
-      <c r="S49" s="305"/>
-      <c r="T49" s="305"/>
-      <c r="U49" s="306"/>
+      <c r="O49" s="365"/>
+      <c r="P49" s="365"/>
+      <c r="Q49" s="365"/>
+      <c r="R49" s="365"/>
+      <c r="S49" s="365"/>
+      <c r="T49" s="365"/>
+      <c r="U49" s="366"/>
       <c r="V49" s="36"/>
       <c r="W49" s="14"/>
       <c r="X49" s="14"/>
@@ -11734,7 +11743,7 @@
       <c r="AG49" s="203"/>
       <c r="AH49" s="203"/>
       <c r="AI49" s="203"/>
-      <c r="AJ49" s="269"/>
+      <c r="AJ49" s="271"/>
       <c r="AK49" s="228"/>
       <c r="AL49" s="203"/>
       <c r="AM49" s="237" t="s">
@@ -11746,7 +11755,7 @@
       <c r="AQ49" s="203"/>
       <c r="AR49" s="203"/>
       <c r="AS49" s="203"/>
-      <c r="AT49" s="269"/>
+      <c r="AT49" s="271"/>
       <c r="AU49" s="228"/>
       <c r="AV49" s="196" t="s">
         <v>505</v>
@@ -11768,7 +11777,7 @@
       <c r="BC49" s="196" t="s">
         <v>239</v>
       </c>
-      <c r="BD49" s="269"/>
+      <c r="BD49" s="271"/>
       <c r="BE49" s="222"/>
       <c r="BF49" s="243" t="s">
         <v>638</v>
@@ -11790,17 +11799,17 @@
       <c r="BM49" s="238" t="s">
         <v>259</v>
       </c>
-      <c r="BN49" s="405"/>
+      <c r="BN49" s="277"/>
       <c r="BO49" s="224"/>
     </row>
     <row r="50" spans="1:77" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="79"/>
       <c r="B50" s="79"/>
-      <c r="E50" s="343" t="s">
+      <c r="E50" s="285" t="s">
         <v>38</v>
       </c>
-      <c r="F50" s="344"/>
-      <c r="G50" s="345"/>
+      <c r="F50" s="287"/>
+      <c r="G50" s="286"/>
       <c r="H50" s="31"/>
       <c r="I50" s="31"/>
       <c r="J50" s="30"/>
@@ -11808,13 +11817,13 @@
       <c r="L50" s="31"/>
       <c r="M50" s="31"/>
       <c r="N50" s="33"/>
-      <c r="O50" s="305"/>
-      <c r="P50" s="305"/>
-      <c r="Q50" s="305"/>
-      <c r="R50" s="305"/>
-      <c r="S50" s="305"/>
-      <c r="T50" s="305"/>
-      <c r="U50" s="306"/>
+      <c r="O50" s="365"/>
+      <c r="P50" s="365"/>
+      <c r="Q50" s="365"/>
+      <c r="R50" s="365"/>
+      <c r="S50" s="365"/>
+      <c r="T50" s="365"/>
+      <c r="U50" s="366"/>
       <c r="V50" s="36"/>
       <c r="W50" s="14"/>
       <c r="X50" s="14"/>
@@ -11891,7 +11900,7 @@
         <v>91</v>
       </c>
       <c r="BM50" s="188"/>
-      <c r="BN50" s="349" t="s">
+      <c r="BN50" s="276" t="s">
         <v>300</v>
       </c>
       <c r="BO50" s="224"/>
@@ -11899,9 +11908,9 @@
     <row r="51" spans="1:77" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="79"/>
       <c r="B51" s="79"/>
-      <c r="E51" s="343"/>
-      <c r="F51" s="344"/>
-      <c r="G51" s="345"/>
+      <c r="E51" s="285"/>
+      <c r="F51" s="287"/>
+      <c r="G51" s="286"/>
       <c r="H51" s="31"/>
       <c r="I51" s="31"/>
       <c r="J51" s="30"/>
@@ -11909,13 +11918,13 @@
       <c r="L51" s="31"/>
       <c r="M51" s="31"/>
       <c r="N51" s="33"/>
-      <c r="O51" s="305"/>
-      <c r="P51" s="305"/>
-      <c r="Q51" s="305"/>
-      <c r="R51" s="305"/>
-      <c r="S51" s="305"/>
-      <c r="T51" s="305"/>
-      <c r="U51" s="306"/>
+      <c r="O51" s="365"/>
+      <c r="P51" s="365"/>
+      <c r="Q51" s="365"/>
+      <c r="R51" s="365"/>
+      <c r="S51" s="365"/>
+      <c r="T51" s="365"/>
+      <c r="U51" s="366"/>
       <c r="V51" s="95"/>
       <c r="W51" s="14"/>
       <c r="X51" s="14"/>
@@ -12006,15 +12015,15 @@
       <c r="BM51" s="196" t="s">
         <v>258</v>
       </c>
-      <c r="BN51" s="349"/>
+      <c r="BN51" s="276"/>
       <c r="BO51" s="224"/>
     </row>
     <row r="52" spans="1:77" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="79"/>
       <c r="B52" s="79"/>
-      <c r="E52" s="343"/>
-      <c r="F52" s="344"/>
-      <c r="G52" s="345"/>
+      <c r="E52" s="285"/>
+      <c r="F52" s="287"/>
+      <c r="G52" s="286"/>
       <c r="H52" s="31"/>
       <c r="I52" s="31"/>
       <c r="J52" s="30"/>
@@ -12022,13 +12031,13 @@
       <c r="L52" s="31"/>
       <c r="M52" s="31"/>
       <c r="N52" s="33"/>
-      <c r="O52" s="305"/>
-      <c r="P52" s="305"/>
-      <c r="Q52" s="305"/>
-      <c r="R52" s="305"/>
-      <c r="S52" s="305"/>
-      <c r="T52" s="305"/>
-      <c r="U52" s="306"/>
+      <c r="O52" s="365"/>
+      <c r="P52" s="365"/>
+      <c r="Q52" s="365"/>
+      <c r="R52" s="365"/>
+      <c r="S52" s="365"/>
+      <c r="T52" s="365"/>
+      <c r="U52" s="366"/>
       <c r="V52" s="36"/>
       <c r="W52" s="14"/>
       <c r="X52" s="14"/>
@@ -12052,11 +12061,11 @@
       </c>
       <c r="AE52" s="195">
         <f>COUNTA(BF30:BM57,BF3:BM28)</f>
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AF52" s="242">
         <f>SUM(AA52:AE52)+AJ52</f>
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG52" s="255">
         <f>COUNTIF( $AV$3:$BC$53,"*401*") + COUNTIF($AB$3:$AS$51,"*401*")+ COUNTIF($AV$55:$BD$55,"*401*") +COUNTIF($BF$3:$BM$57,"*401*") -1</f>
@@ -12064,7 +12073,7 @@
       </c>
       <c r="AH52" s="254">
         <f>COUNTIF( $AV$3:$BC$53,"*402*") + COUNTIF($AB$3:$AS$51,"*402*")+ COUNTIF($AV$55:$BD$55,"*402*") +COUNTIF($BF$3:$BM$57,"*402*") -1</f>
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AI52" s="253">
         <f>COUNTIF( $AV$3:$BC$53,"*403*") + COUNTIF($AB$3:$AS$51,"*403*")+ COUNTIF($AV$55:$BD$55,"*403*") +COUNTIF($BF$3:$BM$57,"*403*") -1</f>
@@ -12109,7 +12118,7 @@
       <c r="BA52" s="204"/>
       <c r="BB52" s="204"/>
       <c r="BC52" s="204"/>
-      <c r="BD52" s="269" t="s">
+      <c r="BD52" s="271" t="s">
         <v>329</v>
       </c>
       <c r="BE52" s="222" t="s">
@@ -12127,7 +12136,7 @@
       <c r="BK52" s="204"/>
       <c r="BL52" s="204"/>
       <c r="BM52" s="204"/>
-      <c r="BN52" s="405" t="s">
+      <c r="BN52" s="277" t="s">
         <v>301</v>
       </c>
       <c r="BO52" s="224"/>
@@ -12135,9 +12144,9 @@
     <row r="53" spans="1:77" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="96"/>
       <c r="B53" s="96"/>
-      <c r="E53" s="343"/>
-      <c r="F53" s="344"/>
-      <c r="G53" s="345"/>
+      <c r="E53" s="285"/>
+      <c r="F53" s="287"/>
+      <c r="G53" s="286"/>
       <c r="H53" s="31"/>
       <c r="I53" s="31"/>
       <c r="J53" s="30"/>
@@ -12145,13 +12154,13 @@
       <c r="L53" s="31"/>
       <c r="M53" s="31"/>
       <c r="N53" s="33"/>
-      <c r="O53" s="305"/>
-      <c r="P53" s="305"/>
-      <c r="Q53" s="305"/>
-      <c r="R53" s="305"/>
-      <c r="S53" s="305"/>
-      <c r="T53" s="305"/>
-      <c r="U53" s="306"/>
+      <c r="O53" s="365"/>
+      <c r="P53" s="365"/>
+      <c r="Q53" s="365"/>
+      <c r="R53" s="365"/>
+      <c r="S53" s="365"/>
+      <c r="T53" s="365"/>
+      <c r="U53" s="366"/>
       <c r="V53" s="36"/>
       <c r="W53" s="14"/>
       <c r="X53" s="14"/>
@@ -12172,7 +12181,7 @@
       <c r="BC53" s="196" t="s">
         <v>245</v>
       </c>
-      <c r="BD53" s="269"/>
+      <c r="BD53" s="271"/>
       <c r="BE53" s="222"/>
       <c r="BF53" s="211" t="s">
         <v>241</v>
@@ -12194,15 +12203,15 @@
       <c r="BM53" s="196" t="s">
         <v>93</v>
       </c>
-      <c r="BN53" s="405"/>
+      <c r="BN53" s="277"/>
       <c r="BO53" s="224"/>
     </row>
     <row r="54" spans="1:77" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="96"/>
       <c r="B54" s="96"/>
-      <c r="E54" s="343"/>
-      <c r="F54" s="344"/>
-      <c r="G54" s="345"/>
+      <c r="E54" s="285"/>
+      <c r="F54" s="287"/>
+      <c r="G54" s="286"/>
       <c r="H54" s="31"/>
       <c r="I54" s="31"/>
       <c r="J54" s="30"/>
@@ -12210,13 +12219,13 @@
       <c r="L54" s="31"/>
       <c r="M54" s="31"/>
       <c r="N54" s="33"/>
-      <c r="O54" s="305"/>
-      <c r="P54" s="305"/>
-      <c r="Q54" s="305"/>
-      <c r="R54" s="305"/>
-      <c r="S54" s="305"/>
-      <c r="T54" s="305"/>
-      <c r="U54" s="306"/>
+      <c r="O54" s="365"/>
+      <c r="P54" s="365"/>
+      <c r="Q54" s="365"/>
+      <c r="R54" s="365"/>
+      <c r="S54" s="365"/>
+      <c r="T54" s="365"/>
+      <c r="U54" s="366"/>
       <c r="V54" s="36"/>
       <c r="W54" s="14"/>
       <c r="X54" s="14"/>
@@ -12272,7 +12281,7 @@
       <c r="BK54" s="188"/>
       <c r="BL54" s="188"/>
       <c r="BM54" s="188"/>
-      <c r="BN54" s="349" t="s">
+      <c r="BN54" s="276" t="s">
         <v>302</v>
       </c>
       <c r="BO54" s="225"/>
@@ -12290,9 +12299,9 @@
     <row r="55" spans="1:77" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="96"/>
       <c r="B55" s="96"/>
-      <c r="E55" s="343"/>
-      <c r="F55" s="344"/>
-      <c r="G55" s="345"/>
+      <c r="E55" s="285"/>
+      <c r="F55" s="287"/>
+      <c r="G55" s="286"/>
       <c r="H55" s="31"/>
       <c r="I55" s="31"/>
       <c r="J55" s="30"/>
@@ -12300,13 +12309,13 @@
       <c r="L55" s="31"/>
       <c r="M55" s="31"/>
       <c r="N55" s="33"/>
-      <c r="O55" s="305"/>
-      <c r="P55" s="305"/>
-      <c r="Q55" s="305"/>
-      <c r="R55" s="305"/>
-      <c r="S55" s="305"/>
-      <c r="T55" s="305"/>
-      <c r="U55" s="306"/>
+      <c r="O55" s="365"/>
+      <c r="P55" s="365"/>
+      <c r="Q55" s="365"/>
+      <c r="R55" s="365"/>
+      <c r="S55" s="365"/>
+      <c r="T55" s="365"/>
+      <c r="U55" s="366"/>
       <c r="V55" s="36"/>
       <c r="W55" s="14"/>
       <c r="X55" s="14"/>
@@ -12345,15 +12354,15 @@
       <c r="BK55" s="189"/>
       <c r="BL55" s="189"/>
       <c r="BM55" s="189"/>
-      <c r="BN55" s="349"/>
+      <c r="BN55" s="276"/>
       <c r="BO55" s="224"/>
     </row>
     <row r="56" spans="1:77" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="96"/>
       <c r="B56" s="96"/>
-      <c r="E56" s="343"/>
-      <c r="F56" s="344"/>
-      <c r="G56" s="345"/>
+      <c r="E56" s="285"/>
+      <c r="F56" s="287"/>
+      <c r="G56" s="286"/>
       <c r="H56" s="31"/>
       <c r="I56" s="31"/>
       <c r="J56" s="30"/>
@@ -12361,13 +12370,13 @@
       <c r="L56" s="31"/>
       <c r="M56" s="31"/>
       <c r="N56" s="33"/>
-      <c r="O56" s="305"/>
-      <c r="P56" s="305"/>
-      <c r="Q56" s="305"/>
-      <c r="R56" s="305"/>
-      <c r="S56" s="305"/>
-      <c r="T56" s="305"/>
-      <c r="U56" s="306"/>
+      <c r="O56" s="365"/>
+      <c r="P56" s="365"/>
+      <c r="Q56" s="365"/>
+      <c r="R56" s="365"/>
+      <c r="S56" s="365"/>
+      <c r="T56" s="365"/>
+      <c r="U56" s="366"/>
       <c r="V56" s="36"/>
       <c r="W56" s="14"/>
       <c r="X56" s="14"/>
@@ -12388,7 +12397,7 @@
       <c r="BK56" s="204"/>
       <c r="BL56" s="204"/>
       <c r="BM56" s="204"/>
-      <c r="BN56" s="350" t="s">
+      <c r="BN56" s="359" t="s">
         <v>303</v>
       </c>
       <c r="BO56" s="224"/>
@@ -12396,9 +12405,9 @@
     <row r="57" spans="1:77" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="96"/>
       <c r="B57" s="96"/>
-      <c r="E57" s="346"/>
-      <c r="F57" s="347"/>
-      <c r="G57" s="348"/>
+      <c r="E57" s="288"/>
+      <c r="F57" s="291"/>
+      <c r="G57" s="289"/>
       <c r="H57" s="31"/>
       <c r="I57" s="31"/>
       <c r="J57" s="30"/>
@@ -12406,13 +12415,13 @@
       <c r="L57" s="31"/>
       <c r="M57" s="31"/>
       <c r="N57" s="33"/>
-      <c r="O57" s="308"/>
-      <c r="P57" s="308"/>
-      <c r="Q57" s="308"/>
-      <c r="R57" s="308"/>
-      <c r="S57" s="308"/>
-      <c r="T57" s="308"/>
-      <c r="U57" s="309"/>
+      <c r="O57" s="367"/>
+      <c r="P57" s="367"/>
+      <c r="Q57" s="367"/>
+      <c r="R57" s="367"/>
+      <c r="S57" s="367"/>
+      <c r="T57" s="367"/>
+      <c r="U57" s="368"/>
       <c r="V57" s="36"/>
       <c r="W57" s="14"/>
       <c r="X57" s="14"/>
@@ -12431,7 +12440,7 @@
       <c r="BK57" s="203"/>
       <c r="BL57" s="203"/>
       <c r="BM57" s="203"/>
-      <c r="BN57" s="350"/>
+      <c r="BN57" s="359"/>
       <c r="BO57" s="224"/>
     </row>
     <row r="58" spans="1:77" ht="279.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -12449,15 +12458,15 @@
       <c r="L58" s="31"/>
       <c r="M58" s="31"/>
       <c r="N58" s="33"/>
-      <c r="O58" s="301" t="s">
+      <c r="O58" s="425" t="s">
         <v>40</v>
       </c>
-      <c r="P58" s="302"/>
-      <c r="Q58" s="302"/>
-      <c r="R58" s="302"/>
-      <c r="S58" s="302"/>
-      <c r="T58" s="302"/>
-      <c r="U58" s="303"/>
+      <c r="P58" s="363"/>
+      <c r="Q58" s="363"/>
+      <c r="R58" s="363"/>
+      <c r="S58" s="363"/>
+      <c r="T58" s="363"/>
+      <c r="U58" s="364"/>
       <c r="V58" s="36"/>
       <c r="W58" s="14"/>
       <c r="X58" s="14"/>
@@ -12472,12 +12481,12 @@
       <c r="AH58" s="37"/>
       <c r="AI58" s="104"/>
       <c r="AJ58" s="104"/>
-      <c r="AK58" s="351" t="s">
+      <c r="AK58" s="307" t="s">
         <v>8</v>
       </c>
-      <c r="AL58" s="352"/>
-      <c r="AM58" s="352"/>
-      <c r="AN58" s="353"/>
+      <c r="AL58" s="369"/>
+      <c r="AM58" s="369"/>
+      <c r="AN58" s="308"/>
       <c r="AO58" s="105"/>
       <c r="AP58" s="105"/>
       <c r="AQ58" s="105"/>
@@ -12520,13 +12529,13 @@
       <c r="L59" s="31"/>
       <c r="M59" s="31"/>
       <c r="N59" s="33"/>
-      <c r="O59" s="304"/>
-      <c r="P59" s="305"/>
-      <c r="Q59" s="305"/>
-      <c r="R59" s="305"/>
-      <c r="S59" s="305"/>
-      <c r="T59" s="305"/>
-      <c r="U59" s="306"/>
+      <c r="O59" s="426"/>
+      <c r="P59" s="365"/>
+      <c r="Q59" s="365"/>
+      <c r="R59" s="365"/>
+      <c r="S59" s="365"/>
+      <c r="T59" s="365"/>
+      <c r="U59" s="366"/>
       <c r="V59" s="36"/>
       <c r="W59" s="14"/>
       <c r="X59" s="14"/>
@@ -12635,13 +12644,13 @@
       <c r="L60" s="31"/>
       <c r="M60" s="31"/>
       <c r="N60" s="33"/>
-      <c r="O60" s="304"/>
-      <c r="P60" s="305"/>
-      <c r="Q60" s="305"/>
-      <c r="R60" s="305"/>
-      <c r="S60" s="305"/>
-      <c r="T60" s="305"/>
-      <c r="U60" s="306"/>
+      <c r="O60" s="426"/>
+      <c r="P60" s="365"/>
+      <c r="Q60" s="365"/>
+      <c r="R60" s="365"/>
+      <c r="S60" s="365"/>
+      <c r="T60" s="365"/>
+      <c r="U60" s="366"/>
       <c r="V60" s="36"/>
       <c r="W60" s="14"/>
       <c r="X60" s="14"/>
@@ -12772,13 +12781,13 @@
       <c r="L61" s="31"/>
       <c r="M61" s="31"/>
       <c r="N61" s="33"/>
-      <c r="O61" s="304"/>
-      <c r="P61" s="305"/>
-      <c r="Q61" s="305"/>
-      <c r="R61" s="305"/>
-      <c r="S61" s="305"/>
-      <c r="T61" s="305"/>
-      <c r="U61" s="306"/>
+      <c r="O61" s="426"/>
+      <c r="P61" s="365"/>
+      <c r="Q61" s="365"/>
+      <c r="R61" s="365"/>
+      <c r="S61" s="365"/>
+      <c r="T61" s="365"/>
+      <c r="U61" s="366"/>
       <c r="V61" s="36"/>
       <c r="W61" s="14"/>
       <c r="X61" s="14"/>
@@ -12794,12 +12803,12 @@
       <c r="AH61" s="98"/>
       <c r="AI61" s="107"/>
       <c r="AJ61" s="152"/>
-      <c r="AK61" s="280" t="s">
+      <c r="AK61" s="407" t="s">
         <v>9</v>
       </c>
-      <c r="AL61" s="281"/>
-      <c r="AM61" s="281"/>
-      <c r="AN61" s="282"/>
+      <c r="AL61" s="408"/>
+      <c r="AM61" s="408"/>
+      <c r="AN61" s="409"/>
       <c r="AO61" s="105"/>
       <c r="AP61" s="105"/>
       <c r="AQ61" s="182">
@@ -12831,7 +12840,7 @@
       </c>
       <c r="AX61" s="213">
         <f>COUNTIF($AB$3:$BC$55,"*402-7-*") + COUNTIF($BF$3:$BM$57,"*402-7-*")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY61" s="213">
         <f>COUNTIF($AB$3:$BC$55,"*402-8-*") + COUNTIF($BF$3:$BM$57,"*402-8-*")</f>
@@ -12895,7 +12904,7 @@
       </c>
       <c r="BN61" s="186">
         <f>SUM(AR61:BM61)/(14*22)</f>
-        <v>0.34740259740259738</v>
+        <v>0.35064935064935066</v>
       </c>
     </row>
     <row r="62" spans="1:77" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -12911,13 +12920,13 @@
       <c r="L62" s="31"/>
       <c r="M62" s="31"/>
       <c r="N62" s="33"/>
-      <c r="O62" s="304"/>
-      <c r="P62" s="305"/>
-      <c r="Q62" s="305"/>
-      <c r="R62" s="305"/>
-      <c r="S62" s="305"/>
-      <c r="T62" s="305"/>
-      <c r="U62" s="306"/>
+      <c r="O62" s="426"/>
+      <c r="P62" s="365"/>
+      <c r="Q62" s="365"/>
+      <c r="R62" s="365"/>
+      <c r="S62" s="365"/>
+      <c r="T62" s="365"/>
+      <c r="U62" s="366"/>
       <c r="V62" s="95"/>
       <c r="W62" s="14"/>
       <c r="X62" s="14"/>
@@ -12928,10 +12937,10 @@
       <c r="AH62" s="98"/>
       <c r="AI62" s="107"/>
       <c r="AJ62" s="152"/>
-      <c r="AK62" s="283"/>
-      <c r="AL62" s="284"/>
-      <c r="AM62" s="284"/>
-      <c r="AN62" s="285"/>
+      <c r="AK62" s="410"/>
+      <c r="AL62" s="411"/>
+      <c r="AM62" s="411"/>
+      <c r="AN62" s="412"/>
       <c r="AO62" s="105"/>
       <c r="AP62" s="105"/>
       <c r="AQ62" s="183">
@@ -13043,13 +13052,13 @@
       <c r="L63" s="31"/>
       <c r="M63" s="31"/>
       <c r="N63" s="33"/>
-      <c r="O63" s="304"/>
-      <c r="P63" s="305"/>
-      <c r="Q63" s="305"/>
-      <c r="R63" s="305"/>
-      <c r="S63" s="305"/>
-      <c r="T63" s="305"/>
-      <c r="U63" s="306"/>
+      <c r="O63" s="426"/>
+      <c r="P63" s="365"/>
+      <c r="Q63" s="365"/>
+      <c r="R63" s="365"/>
+      <c r="S63" s="365"/>
+      <c r="T63" s="365"/>
+      <c r="U63" s="366"/>
       <c r="V63" s="95"/>
       <c r="W63" s="14"/>
       <c r="X63" s="14"/>
@@ -13060,10 +13069,10 @@
       <c r="AH63" s="98"/>
       <c r="AI63" s="107"/>
       <c r="AJ63" s="152"/>
-      <c r="AK63" s="286"/>
-      <c r="AL63" s="287"/>
-      <c r="AM63" s="287"/>
-      <c r="AN63" s="288"/>
+      <c r="AK63" s="413"/>
+      <c r="AL63" s="414"/>
+      <c r="AM63" s="414"/>
+      <c r="AN63" s="415"/>
       <c r="AO63" s="105"/>
       <c r="AP63" s="105"/>
       <c r="AQ63" s="105"/>
@@ -13084,13 +13093,13 @@
       <c r="L64" s="31"/>
       <c r="M64" s="31"/>
       <c r="N64" s="33"/>
-      <c r="O64" s="304"/>
-      <c r="P64" s="305"/>
-      <c r="Q64" s="305"/>
-      <c r="R64" s="305"/>
-      <c r="S64" s="305"/>
-      <c r="T64" s="305"/>
-      <c r="U64" s="306"/>
+      <c r="O64" s="426"/>
+      <c r="P64" s="365"/>
+      <c r="Q64" s="365"/>
+      <c r="R64" s="365"/>
+      <c r="S64" s="365"/>
+      <c r="T64" s="365"/>
+      <c r="U64" s="366"/>
       <c r="V64" s="95"/>
       <c r="W64" s="14"/>
       <c r="X64" s="14"/>
@@ -13140,13 +13149,13 @@
       <c r="L65" s="31"/>
       <c r="M65" s="31"/>
       <c r="N65" s="33"/>
-      <c r="O65" s="304"/>
-      <c r="P65" s="305"/>
-      <c r="Q65" s="305"/>
-      <c r="R65" s="305"/>
-      <c r="S65" s="305"/>
-      <c r="T65" s="305"/>
-      <c r="U65" s="306"/>
+      <c r="O65" s="426"/>
+      <c r="P65" s="365"/>
+      <c r="Q65" s="365"/>
+      <c r="R65" s="365"/>
+      <c r="S65" s="365"/>
+      <c r="T65" s="365"/>
+      <c r="U65" s="366"/>
       <c r="V65" s="95"/>
       <c r="W65" s="14"/>
       <c r="X65" s="14"/>
@@ -13195,13 +13204,13 @@
       <c r="L66" s="31"/>
       <c r="M66" s="31"/>
       <c r="N66" s="33"/>
-      <c r="O66" s="304"/>
-      <c r="P66" s="305"/>
-      <c r="Q66" s="305"/>
-      <c r="R66" s="305"/>
-      <c r="S66" s="305"/>
-      <c r="T66" s="305"/>
-      <c r="U66" s="306"/>
+      <c r="O66" s="426"/>
+      <c r="P66" s="365"/>
+      <c r="Q66" s="365"/>
+      <c r="R66" s="365"/>
+      <c r="S66" s="365"/>
+      <c r="T66" s="365"/>
+      <c r="U66" s="366"/>
       <c r="V66" s="102"/>
       <c r="W66" s="103"/>
       <c r="X66" s="14"/>
@@ -13212,21 +13221,21 @@
       <c r="AH66" s="98"/>
       <c r="AI66" s="98"/>
       <c r="AJ66" s="98"/>
-      <c r="AK66" s="289" t="s">
+      <c r="AK66" s="416" t="s">
         <v>10</v>
       </c>
-      <c r="AL66" s="290"/>
-      <c r="AM66" s="290"/>
-      <c r="AN66" s="290"/>
-      <c r="AO66" s="290"/>
-      <c r="AP66" s="291"/>
+      <c r="AL66" s="417"/>
+      <c r="AM66" s="417"/>
+      <c r="AN66" s="417"/>
+      <c r="AO66" s="417"/>
+      <c r="AP66" s="418"/>
       <c r="AQ66" s="105"/>
       <c r="AR66" s="40"/>
-      <c r="AS66" s="298" t="s">
+      <c r="AS66" s="360" t="s">
         <v>0</v>
       </c>
       <c r="AT66" s="173"/>
-      <c r="AU66" s="298" t="s">
+      <c r="AU66" s="360" t="s">
         <v>1</v>
       </c>
       <c r="AW66" s="170"/>
@@ -13260,13 +13269,13 @@
       <c r="L67" s="31"/>
       <c r="M67" s="31"/>
       <c r="N67" s="33"/>
-      <c r="O67" s="304"/>
-      <c r="P67" s="305"/>
-      <c r="Q67" s="305"/>
-      <c r="R67" s="305"/>
-      <c r="S67" s="305"/>
-      <c r="T67" s="305"/>
-      <c r="U67" s="306"/>
+      <c r="O67" s="426"/>
+      <c r="P67" s="365"/>
+      <c r="Q67" s="365"/>
+      <c r="R67" s="365"/>
+      <c r="S67" s="365"/>
+      <c r="T67" s="365"/>
+      <c r="U67" s="366"/>
       <c r="V67" s="95"/>
       <c r="W67" s="103"/>
       <c r="X67" s="14"/>
@@ -13276,17 +13285,17 @@
       <c r="AH67" s="9"/>
       <c r="AI67" s="98"/>
       <c r="AJ67" s="98"/>
-      <c r="AK67" s="292"/>
-      <c r="AL67" s="293"/>
-      <c r="AM67" s="293"/>
-      <c r="AN67" s="293"/>
-      <c r="AO67" s="293"/>
-      <c r="AP67" s="294"/>
+      <c r="AK67" s="419"/>
+      <c r="AL67" s="420"/>
+      <c r="AM67" s="420"/>
+      <c r="AN67" s="420"/>
+      <c r="AO67" s="420"/>
+      <c r="AP67" s="421"/>
       <c r="AQ67" s="44"/>
       <c r="AR67" s="44"/>
-      <c r="AS67" s="299"/>
+      <c r="AS67" s="361"/>
       <c r="AT67" s="174"/>
-      <c r="AU67" s="299"/>
+      <c r="AU67" s="361"/>
       <c r="BC67" s="39"/>
       <c r="BE67" s="4"/>
       <c r="BF67" s="4"/>
@@ -13311,13 +13320,13 @@
       <c r="L68" s="31"/>
       <c r="M68" s="31"/>
       <c r="N68" s="33"/>
-      <c r="O68" s="304"/>
-      <c r="P68" s="305"/>
-      <c r="Q68" s="305"/>
-      <c r="R68" s="305"/>
-      <c r="S68" s="305"/>
-      <c r="T68" s="305"/>
-      <c r="U68" s="306"/>
+      <c r="O68" s="426"/>
+      <c r="P68" s="365"/>
+      <c r="Q68" s="365"/>
+      <c r="R68" s="365"/>
+      <c r="S68" s="365"/>
+      <c r="T68" s="365"/>
+      <c r="U68" s="366"/>
       <c r="V68" s="95"/>
       <c r="W68" s="103"/>
       <c r="X68" s="14"/>
@@ -13332,17 +13341,17 @@
       <c r="AH68" s="124"/>
       <c r="AI68" s="101"/>
       <c r="AJ68" s="101"/>
-      <c r="AK68" s="295"/>
-      <c r="AL68" s="296"/>
-      <c r="AM68" s="296"/>
-      <c r="AN68" s="296"/>
-      <c r="AO68" s="296"/>
-      <c r="AP68" s="297"/>
+      <c r="AK68" s="422"/>
+      <c r="AL68" s="423"/>
+      <c r="AM68" s="423"/>
+      <c r="AN68" s="423"/>
+      <c r="AO68" s="423"/>
+      <c r="AP68" s="424"/>
       <c r="AQ68" s="101"/>
       <c r="AR68" s="101"/>
-      <c r="AS68" s="300"/>
+      <c r="AS68" s="362"/>
       <c r="AT68" s="175"/>
-      <c r="AU68" s="300"/>
+      <c r="AU68" s="362"/>
       <c r="AV68" s="125"/>
       <c r="AW68" s="125"/>
       <c r="AX68" s="125"/>
@@ -13364,13 +13373,13 @@
       <c r="L69" s="31"/>
       <c r="M69" s="31"/>
       <c r="N69" s="33"/>
-      <c r="O69" s="304"/>
-      <c r="P69" s="305"/>
-      <c r="Q69" s="305"/>
-      <c r="R69" s="305"/>
-      <c r="S69" s="305"/>
-      <c r="T69" s="305"/>
-      <c r="U69" s="306"/>
+      <c r="O69" s="426"/>
+      <c r="P69" s="365"/>
+      <c r="Q69" s="365"/>
+      <c r="R69" s="365"/>
+      <c r="S69" s="365"/>
+      <c r="T69" s="365"/>
+      <c r="U69" s="366"/>
       <c r="V69" s="95"/>
       <c r="W69" s="103"/>
       <c r="X69" s="14"/>
@@ -13379,13 +13388,13 @@
       <c r="AA69" s="94"/>
       <c r="AB69" s="117"/>
       <c r="AC69" s="117"/>
-      <c r="AD69" s="272" t="s">
+      <c r="AD69" s="401" t="s">
         <v>3</v>
       </c>
-      <c r="AE69" s="273"/>
-      <c r="AF69" s="273"/>
-      <c r="AG69" s="273"/>
-      <c r="AH69" s="274"/>
+      <c r="AE69" s="402"/>
+      <c r="AF69" s="402"/>
+      <c r="AG69" s="402"/>
+      <c r="AH69" s="403"/>
       <c r="AI69" s="129"/>
       <c r="AZ69" s="130"/>
     </row>
@@ -13402,23 +13411,23 @@
       <c r="L70" s="49"/>
       <c r="M70" s="49"/>
       <c r="N70" s="109"/>
-      <c r="O70" s="307"/>
-      <c r="P70" s="308"/>
-      <c r="Q70" s="308"/>
-      <c r="R70" s="308"/>
-      <c r="S70" s="308"/>
-      <c r="T70" s="308"/>
-      <c r="U70" s="309"/>
+      <c r="O70" s="427"/>
+      <c r="P70" s="367"/>
+      <c r="Q70" s="367"/>
+      <c r="R70" s="367"/>
+      <c r="S70" s="367"/>
+      <c r="T70" s="367"/>
+      <c r="U70" s="368"/>
       <c r="V70" s="95"/>
       <c r="W70" s="103"/>
       <c r="X70" s="14"/>
       <c r="AB70" s="117"/>
       <c r="AC70" s="117"/>
-      <c r="AD70" s="275"/>
-      <c r="AE70" s="276"/>
-      <c r="AF70" s="276"/>
-      <c r="AG70" s="276"/>
-      <c r="AH70" s="277"/>
+      <c r="AD70" s="404"/>
+      <c r="AE70" s="405"/>
+      <c r="AF70" s="405"/>
+      <c r="AG70" s="405"/>
+      <c r="AH70" s="406"/>
       <c r="AL70" s="134"/>
       <c r="AM70" s="134"/>
       <c r="AN70" s="134"/>
@@ -13669,13 +13678,13 @@
       <c r="H75" s="120"/>
       <c r="I75" s="121"/>
       <c r="J75" s="122"/>
-      <c r="K75" s="316" t="s">
+      <c r="K75" s="374" t="s">
         <v>41</v>
       </c>
-      <c r="L75" s="317"/>
-      <c r="M75" s="317"/>
-      <c r="N75" s="317"/>
-      <c r="O75" s="318"/>
+      <c r="L75" s="375"/>
+      <c r="M75" s="375"/>
+      <c r="N75" s="375"/>
+      <c r="O75" s="376"/>
       <c r="P75" s="115"/>
       <c r="Q75" s="115"/>
       <c r="R75" s="115"/>
@@ -13723,28 +13732,28 @@
     </row>
     <row r="76" spans="1:65" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="9"/>
-      <c r="B76" s="325" t="s">
+      <c r="B76" s="324" t="s">
         <v>42</v>
       </c>
-      <c r="C76" s="326"/>
-      <c r="D76" s="327"/>
-      <c r="E76" s="278" t="s">
+      <c r="C76" s="383"/>
+      <c r="D76" s="384"/>
+      <c r="E76" s="372" t="s">
         <v>43</v>
       </c>
-      <c r="F76" s="279"/>
-      <c r="G76" s="332" t="s">
+      <c r="F76" s="373"/>
+      <c r="G76" s="326" t="s">
         <v>43</v>
       </c>
-      <c r="H76" s="333"/>
-      <c r="I76" s="334" t="s">
+      <c r="H76" s="339"/>
+      <c r="I76" s="389" t="s">
         <v>44</v>
       </c>
-      <c r="J76" s="335"/>
-      <c r="K76" s="319"/>
-      <c r="L76" s="320"/>
-      <c r="M76" s="320"/>
-      <c r="N76" s="320"/>
-      <c r="O76" s="321"/>
+      <c r="J76" s="390"/>
+      <c r="K76" s="377"/>
+      <c r="L76" s="378"/>
+      <c r="M76" s="378"/>
+      <c r="N76" s="378"/>
+      <c r="O76" s="379"/>
       <c r="P76" s="115"/>
       <c r="Q76" s="115"/>
       <c r="R76" s="115"/>
@@ -13789,27 +13798,27 @@
       <c r="BJ76" s="144"/>
       <c r="BK76" s="144"/>
       <c r="BL76" s="144"/>
-      <c r="BM76" s="354"/>
+      <c r="BM76" s="357"/>
     </row>
     <row r="77" spans="1:65" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B77" s="328"/>
-      <c r="C77" s="326"/>
-      <c r="D77" s="327"/>
-      <c r="E77" s="278" t="s">
+      <c r="B77" s="385"/>
+      <c r="C77" s="383"/>
+      <c r="D77" s="384"/>
+      <c r="E77" s="372" t="s">
         <v>43</v>
       </c>
-      <c r="F77" s="338"/>
-      <c r="G77" s="278" t="s">
+      <c r="F77" s="393"/>
+      <c r="G77" s="372" t="s">
         <v>43</v>
       </c>
-      <c r="H77" s="338"/>
-      <c r="I77" s="334"/>
-      <c r="J77" s="335"/>
-      <c r="K77" s="319"/>
-      <c r="L77" s="320"/>
-      <c r="M77" s="320"/>
-      <c r="N77" s="320"/>
-      <c r="O77" s="321"/>
+      <c r="H77" s="393"/>
+      <c r="I77" s="389"/>
+      <c r="J77" s="390"/>
+      <c r="K77" s="377"/>
+      <c r="L77" s="378"/>
+      <c r="M77" s="378"/>
+      <c r="N77" s="378"/>
+      <c r="O77" s="379"/>
       <c r="P77" s="115"/>
       <c r="Q77" s="115"/>
       <c r="R77" s="115"/>
@@ -13854,28 +13863,28 @@
       <c r="BJ77" s="144"/>
       <c r="BK77" s="144"/>
       <c r="BL77" s="144"/>
-      <c r="BM77" s="354"/>
+      <c r="BM77" s="357"/>
     </row>
     <row r="78" spans="1:65" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="9"/>
-      <c r="B78" s="329"/>
-      <c r="C78" s="330"/>
-      <c r="D78" s="331"/>
-      <c r="E78" s="278" t="s">
+      <c r="B78" s="386"/>
+      <c r="C78" s="387"/>
+      <c r="D78" s="388"/>
+      <c r="E78" s="372" t="s">
         <v>45</v>
       </c>
-      <c r="F78" s="279"/>
-      <c r="G78" s="278" t="s">
+      <c r="F78" s="373"/>
+      <c r="G78" s="372" t="s">
         <v>46</v>
       </c>
-      <c r="H78" s="279"/>
-      <c r="I78" s="336"/>
-      <c r="J78" s="337"/>
-      <c r="K78" s="322"/>
-      <c r="L78" s="323"/>
-      <c r="M78" s="323"/>
-      <c r="N78" s="323"/>
-      <c r="O78" s="324"/>
+      <c r="H78" s="373"/>
+      <c r="I78" s="391"/>
+      <c r="J78" s="392"/>
+      <c r="K78" s="380"/>
+      <c r="L78" s="381"/>
+      <c r="M78" s="381"/>
+      <c r="N78" s="381"/>
+      <c r="O78" s="382"/>
       <c r="P78" s="131"/>
       <c r="Q78" s="131"/>
       <c r="R78" s="131"/>
@@ -13920,7 +13929,7 @@
       <c r="BJ78" s="144"/>
       <c r="BK78" s="144"/>
       <c r="BL78" s="144"/>
-      <c r="BM78" s="354"/>
+      <c r="BM78" s="357"/>
     </row>
     <row r="79" spans="1:65" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="135"/>
@@ -13983,7 +13992,7 @@
       <c r="BL79" s="144"/>
     </row>
     <row r="80" spans="1:65" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="271"/>
+      <c r="A80" s="350"/>
       <c r="B80" s="9"/>
       <c r="C80" s="9"/>
       <c r="D80" s="9"/>
@@ -13991,15 +14000,15 @@
       <c r="F80" s="9"/>
       <c r="G80" s="43"/>
       <c r="K80" s="41"/>
-      <c r="R80" s="314"/>
-      <c r="S80" s="314"/>
-      <c r="T80" s="314"/>
-      <c r="U80" s="314"/>
-      <c r="V80" s="314"/>
-      <c r="W80" s="314"/>
-      <c r="X80" s="314"/>
-      <c r="Y80" s="314"/>
-      <c r="Z80" s="314"/>
+      <c r="R80" s="399"/>
+      <c r="S80" s="399"/>
+      <c r="T80" s="399"/>
+      <c r="U80" s="399"/>
+      <c r="V80" s="399"/>
+      <c r="W80" s="399"/>
+      <c r="X80" s="399"/>
+      <c r="Y80" s="399"/>
+      <c r="Z80" s="399"/>
       <c r="AB80" s="101"/>
       <c r="AC80" s="101"/>
       <c r="AH80" s="145"/>
@@ -14035,7 +14044,7 @@
       <c r="BL80" s="144"/>
     </row>
     <row r="81" spans="1:64" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="271"/>
+      <c r="A81" s="350"/>
       <c r="B81" s="9"/>
       <c r="C81" s="9"/>
       <c r="D81" s="9"/>
@@ -14043,15 +14052,15 @@
       <c r="F81" s="9"/>
       <c r="G81" s="43"/>
       <c r="K81" s="41"/>
-      <c r="R81" s="315"/>
-      <c r="S81" s="315"/>
-      <c r="T81" s="315"/>
-      <c r="U81" s="315"/>
-      <c r="V81" s="315"/>
-      <c r="W81" s="315"/>
-      <c r="X81" s="315"/>
-      <c r="Y81" s="315"/>
-      <c r="Z81" s="315"/>
+      <c r="R81" s="400"/>
+      <c r="S81" s="400"/>
+      <c r="T81" s="400"/>
+      <c r="U81" s="400"/>
+      <c r="V81" s="400"/>
+      <c r="W81" s="400"/>
+      <c r="X81" s="400"/>
+      <c r="Y81" s="400"/>
+      <c r="Z81" s="400"/>
       <c r="AB81" s="163"/>
       <c r="AC81" s="161"/>
       <c r="AD81" s="161"/>
@@ -14091,18 +14100,18 @@
       <c r="BL81" s="144"/>
     </row>
     <row r="82" spans="1:64" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="271"/>
+      <c r="A82" s="350"/>
       <c r="H82" s="148"/>
       <c r="I82" s="148"/>
       <c r="J82" s="148"/>
       <c r="K82" s="92"/>
       <c r="L82" s="92"/>
-      <c r="R82" s="339"/>
-      <c r="S82" s="340"/>
-      <c r="T82" s="341"/>
-      <c r="U82" s="342"/>
-      <c r="V82" s="341"/>
-      <c r="W82" s="342"/>
+      <c r="R82" s="395"/>
+      <c r="S82" s="396"/>
+      <c r="T82" s="397"/>
+      <c r="U82" s="398"/>
+      <c r="V82" s="397"/>
+      <c r="W82" s="398"/>
       <c r="AB82" s="167"/>
       <c r="AC82" s="165"/>
       <c r="AD82" s="165"/>
@@ -14153,16 +14162,16 @@
       <c r="J83" s="92"/>
       <c r="K83" s="23"/>
       <c r="L83" s="23"/>
-      <c r="R83" s="310"/>
-      <c r="S83" s="311"/>
-      <c r="T83" s="310"/>
-      <c r="U83" s="311"/>
-      <c r="V83" s="312"/>
-      <c r="W83" s="313"/>
+      <c r="R83" s="370"/>
+      <c r="S83" s="371"/>
+      <c r="T83" s="370"/>
+      <c r="U83" s="371"/>
+      <c r="V83" s="394"/>
+      <c r="W83" s="428"/>
       <c r="X83" s="3"/>
     </row>
     <row r="84" spans="1:64" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="271"/>
+      <c r="A84" s="350"/>
       <c r="B84" s="92"/>
       <c r="C84" s="92"/>
       <c r="D84" s="92"/>
@@ -14179,18 +14188,18 @@
       <c r="O84" s="151"/>
       <c r="P84" s="115"/>
       <c r="Q84" s="23"/>
-      <c r="R84" s="310"/>
-      <c r="S84" s="311"/>
-      <c r="T84" s="310"/>
-      <c r="U84" s="311"/>
-      <c r="V84" s="310"/>
-      <c r="W84" s="311"/>
+      <c r="R84" s="370"/>
+      <c r="S84" s="371"/>
+      <c r="T84" s="370"/>
+      <c r="U84" s="371"/>
+      <c r="V84" s="370"/>
+      <c r="W84" s="371"/>
       <c r="X84" s="11"/>
-      <c r="Y84" s="310"/>
-      <c r="Z84" s="311"/>
+      <c r="Y84" s="370"/>
+      <c r="Z84" s="371"/>
     </row>
     <row r="85" spans="1:64" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="271"/>
+      <c r="A85" s="350"/>
       <c r="B85" s="44"/>
       <c r="C85" s="44"/>
       <c r="D85" s="44"/>
@@ -14208,17 +14217,17 @@
       <c r="P85" s="23"/>
       <c r="Q85" s="23"/>
       <c r="R85" s="153"/>
-      <c r="S85" s="310"/>
-      <c r="T85" s="311"/>
+      <c r="S85" s="370"/>
+      <c r="T85" s="371"/>
       <c r="U85" s="154"/>
-      <c r="V85" s="312"/>
-      <c r="W85" s="312"/>
-      <c r="X85" s="312"/>
-      <c r="Y85" s="312"/>
+      <c r="V85" s="394"/>
+      <c r="W85" s="394"/>
+      <c r="X85" s="394"/>
+      <c r="Y85" s="394"/>
       <c r="Z85" s="155"/>
     </row>
     <row r="86" spans="1:64" ht="186" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="271"/>
+      <c r="A86" s="350"/>
       <c r="B86" s="44"/>
       <c r="C86" s="44"/>
       <c r="D86" s="44"/>
@@ -14262,11 +14271,11 @@
       <c r="W87" s="99"/>
     </row>
     <row r="88" spans="1:64" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E88" s="271"/>
+      <c r="E88" s="350"/>
       <c r="F88" s="83"/>
-      <c r="G88" s="271"/>
-      <c r="H88" s="271"/>
-      <c r="I88" s="271"/>
+      <c r="G88" s="350"/>
+      <c r="H88" s="350"/>
+      <c r="I88" s="350"/>
       <c r="J88" s="99"/>
       <c r="K88" s="99"/>
       <c r="L88" s="99"/>
@@ -14283,11 +14292,11 @@
       <c r="W88" s="99"/>
     </row>
     <row r="89" spans="1:64" ht="186" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E89" s="271"/>
+      <c r="E89" s="350"/>
       <c r="F89" s="83"/>
-      <c r="G89" s="271"/>
-      <c r="H89" s="271"/>
-      <c r="I89" s="271"/>
+      <c r="G89" s="350"/>
+      <c r="H89" s="350"/>
+      <c r="I89" s="350"/>
       <c r="J89" s="99"/>
       <c r="K89" s="99"/>
       <c r="L89" s="99"/>
@@ -14308,11 +14317,11 @@
       <c r="AA89" s="162"/>
     </row>
     <row r="90" spans="1:64" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E90" s="271"/>
+      <c r="E90" s="350"/>
       <c r="F90" s="83"/>
-      <c r="G90" s="271"/>
-      <c r="H90" s="271"/>
-      <c r="I90" s="271"/>
+      <c r="G90" s="350"/>
+      <c r="H90" s="350"/>
+      <c r="I90" s="350"/>
       <c r="J90" s="99"/>
       <c r="K90" s="99"/>
       <c r="L90" s="99"/>
@@ -14342,125 +14351,42 @@
     </row>
   </sheetData>
   <mergeCells count="179">
-    <mergeCell ref="AO2:AP2"/>
-    <mergeCell ref="AT19:AT20"/>
-    <mergeCell ref="AT21:AT22"/>
-    <mergeCell ref="AT23:AT24"/>
-    <mergeCell ref="AT25:AT26"/>
-    <mergeCell ref="AT27:AT28"/>
-    <mergeCell ref="AT30:AT31"/>
-    <mergeCell ref="AT32:AT33"/>
-    <mergeCell ref="AT3:AT4"/>
-    <mergeCell ref="AT5:AT6"/>
-    <mergeCell ref="AT7:AT8"/>
-    <mergeCell ref="AT9:AT10"/>
-    <mergeCell ref="AT11:AT12"/>
-    <mergeCell ref="AT13:AT14"/>
-    <mergeCell ref="AT15:AT16"/>
-    <mergeCell ref="AT17:AT18"/>
-    <mergeCell ref="AT34:AT35"/>
-    <mergeCell ref="AT36:AT37"/>
-    <mergeCell ref="AT38:AT39"/>
-    <mergeCell ref="AT40:AT41"/>
-    <mergeCell ref="BD32:BD33"/>
-    <mergeCell ref="BD34:BD35"/>
-    <mergeCell ref="BD36:BD37"/>
-    <mergeCell ref="BD38:BD39"/>
-    <mergeCell ref="BF29:BM29"/>
-    <mergeCell ref="AV29:BC29"/>
-    <mergeCell ref="BD40:BD41"/>
-    <mergeCell ref="BD13:BD14"/>
-    <mergeCell ref="BD15:BD16"/>
-    <mergeCell ref="BD17:BD18"/>
-    <mergeCell ref="BD19:BD20"/>
-    <mergeCell ref="BD21:BD22"/>
-    <mergeCell ref="BD23:BD24"/>
-    <mergeCell ref="BD25:BD26"/>
-    <mergeCell ref="BD27:BD28"/>
-    <mergeCell ref="BD30:BD31"/>
-    <mergeCell ref="BN3:BN4"/>
-    <mergeCell ref="BN5:BN6"/>
-    <mergeCell ref="BN7:BN8"/>
-    <mergeCell ref="BN9:BN10"/>
-    <mergeCell ref="BD3:BD4"/>
-    <mergeCell ref="BD5:BD6"/>
-    <mergeCell ref="BD7:BD8"/>
-    <mergeCell ref="BD9:BD10"/>
-    <mergeCell ref="BD11:BD12"/>
-    <mergeCell ref="BN11:BN12"/>
-    <mergeCell ref="BN17:BN18"/>
-    <mergeCell ref="BN19:BN20"/>
-    <mergeCell ref="BN40:BN41"/>
-    <mergeCell ref="BN42:BN43"/>
-    <mergeCell ref="BN44:BN45"/>
-    <mergeCell ref="BN46:BN47"/>
-    <mergeCell ref="BN52:BN53"/>
-    <mergeCell ref="BN21:BN22"/>
-    <mergeCell ref="BN23:BN24"/>
-    <mergeCell ref="BN25:BN26"/>
-    <mergeCell ref="BN27:BN28"/>
-    <mergeCell ref="BN30:BN31"/>
-    <mergeCell ref="BN32:BN33"/>
-    <mergeCell ref="BN34:BN35"/>
-    <mergeCell ref="BN36:BN37"/>
-    <mergeCell ref="BN38:BN39"/>
-    <mergeCell ref="BN48:BN49"/>
-    <mergeCell ref="BN13:BN14"/>
-    <mergeCell ref="AB2:AI2"/>
-    <mergeCell ref="AV2:BC2"/>
-    <mergeCell ref="BF2:BM2"/>
-    <mergeCell ref="H3:I36"/>
-    <mergeCell ref="J3:K36"/>
-    <mergeCell ref="L3:M36"/>
-    <mergeCell ref="O3:U7"/>
-    <mergeCell ref="O8:U10"/>
-    <mergeCell ref="E25:G30"/>
-    <mergeCell ref="BN15:BN16"/>
-    <mergeCell ref="E31:G33"/>
-    <mergeCell ref="E34:G35"/>
-    <mergeCell ref="E36:G36"/>
-    <mergeCell ref="F10:G12"/>
-    <mergeCell ref="O11:U14"/>
-    <mergeCell ref="A12:B14"/>
-    <mergeCell ref="E14:G15"/>
-    <mergeCell ref="A15:B17"/>
-    <mergeCell ref="O15:U18"/>
-    <mergeCell ref="E16:G18"/>
-    <mergeCell ref="A18:B20"/>
-    <mergeCell ref="O19:U36"/>
-    <mergeCell ref="E20:G24"/>
-    <mergeCell ref="AJ40:AJ41"/>
-    <mergeCell ref="AJ42:AJ43"/>
-    <mergeCell ref="AJ44:AJ45"/>
-    <mergeCell ref="AJ46:AJ47"/>
-    <mergeCell ref="AJ48:AJ49"/>
-    <mergeCell ref="E37:M37"/>
-    <mergeCell ref="O37:U37"/>
-    <mergeCell ref="O38:O39"/>
-    <mergeCell ref="E44:F45"/>
-    <mergeCell ref="G44:G45"/>
-    <mergeCell ref="BM76:BM78"/>
-    <mergeCell ref="O42:P42"/>
-    <mergeCell ref="O43:P43"/>
-    <mergeCell ref="BD42:BD43"/>
-    <mergeCell ref="BD44:BD45"/>
-    <mergeCell ref="AT42:AT43"/>
-    <mergeCell ref="AT44:AT45"/>
-    <mergeCell ref="AT46:AT47"/>
-    <mergeCell ref="BD46:BD47"/>
-    <mergeCell ref="BD48:BD49"/>
-    <mergeCell ref="BD50:BD51"/>
-    <mergeCell ref="BD52:BD53"/>
-    <mergeCell ref="O44:P44"/>
-    <mergeCell ref="E50:G57"/>
-    <mergeCell ref="BN50:BN51"/>
-    <mergeCell ref="BN54:BN55"/>
-    <mergeCell ref="BN56:BN57"/>
-    <mergeCell ref="AU66:AU68"/>
-    <mergeCell ref="AT50:AT51"/>
-    <mergeCell ref="O48:U57"/>
-    <mergeCell ref="AT48:AT49"/>
-    <mergeCell ref="AK58:AN58"/>
+    <mergeCell ref="AJ21:AJ22"/>
+    <mergeCell ref="AJ23:AJ24"/>
+    <mergeCell ref="AJ25:AJ26"/>
+    <mergeCell ref="AJ27:AJ28"/>
+    <mergeCell ref="AJ30:AJ31"/>
+    <mergeCell ref="AJ32:AJ33"/>
+    <mergeCell ref="AJ34:AJ35"/>
+    <mergeCell ref="AJ36:AJ37"/>
+    <mergeCell ref="AJ38:AJ39"/>
+    <mergeCell ref="AJ3:AJ4"/>
+    <mergeCell ref="AJ5:AJ6"/>
+    <mergeCell ref="AJ7:AJ8"/>
+    <mergeCell ref="AJ9:AJ10"/>
+    <mergeCell ref="AJ11:AJ12"/>
+    <mergeCell ref="AJ13:AJ14"/>
+    <mergeCell ref="AJ15:AJ16"/>
+    <mergeCell ref="AJ17:AJ18"/>
+    <mergeCell ref="AJ19:AJ20"/>
+    <mergeCell ref="E88:E90"/>
+    <mergeCell ref="G88:G90"/>
+    <mergeCell ref="H88:H90"/>
+    <mergeCell ref="I88:I90"/>
+    <mergeCell ref="AD69:AH70"/>
+    <mergeCell ref="G78:H78"/>
+    <mergeCell ref="AK61:AN63"/>
+    <mergeCell ref="AK66:AP68"/>
+    <mergeCell ref="AS66:AS68"/>
+    <mergeCell ref="O58:U70"/>
+    <mergeCell ref="R83:S83"/>
+    <mergeCell ref="T83:U83"/>
+    <mergeCell ref="V83:W83"/>
+    <mergeCell ref="X80:X81"/>
+    <mergeCell ref="Y80:Y81"/>
+    <mergeCell ref="Z80:Z81"/>
+    <mergeCell ref="R80:R81"/>
+    <mergeCell ref="S80:S81"/>
     <mergeCell ref="A84:A86"/>
     <mergeCell ref="R84:S84"/>
     <mergeCell ref="T84:U84"/>
@@ -14485,42 +14411,125 @@
     <mergeCell ref="U80:U81"/>
     <mergeCell ref="V80:V81"/>
     <mergeCell ref="W80:W81"/>
-    <mergeCell ref="E88:E90"/>
-    <mergeCell ref="G88:G90"/>
-    <mergeCell ref="H88:H90"/>
-    <mergeCell ref="I88:I90"/>
-    <mergeCell ref="AD69:AH70"/>
-    <mergeCell ref="G78:H78"/>
-    <mergeCell ref="AK61:AN63"/>
-    <mergeCell ref="AK66:AP68"/>
-    <mergeCell ref="AS66:AS68"/>
-    <mergeCell ref="O58:U70"/>
-    <mergeCell ref="R83:S83"/>
-    <mergeCell ref="T83:U83"/>
-    <mergeCell ref="V83:W83"/>
-    <mergeCell ref="X80:X81"/>
-    <mergeCell ref="Y80:Y81"/>
-    <mergeCell ref="Z80:Z81"/>
-    <mergeCell ref="R80:R81"/>
-    <mergeCell ref="S80:S81"/>
-    <mergeCell ref="AJ3:AJ4"/>
-    <mergeCell ref="AJ5:AJ6"/>
-    <mergeCell ref="AJ7:AJ8"/>
-    <mergeCell ref="AJ9:AJ10"/>
-    <mergeCell ref="AJ11:AJ12"/>
-    <mergeCell ref="AJ13:AJ14"/>
-    <mergeCell ref="AJ15:AJ16"/>
-    <mergeCell ref="AJ17:AJ18"/>
-    <mergeCell ref="AJ19:AJ20"/>
-    <mergeCell ref="AJ21:AJ22"/>
-    <mergeCell ref="AJ23:AJ24"/>
-    <mergeCell ref="AJ25:AJ26"/>
-    <mergeCell ref="AJ27:AJ28"/>
-    <mergeCell ref="AJ30:AJ31"/>
-    <mergeCell ref="AJ32:AJ33"/>
-    <mergeCell ref="AJ34:AJ35"/>
-    <mergeCell ref="AJ36:AJ37"/>
-    <mergeCell ref="AJ38:AJ39"/>
+    <mergeCell ref="E50:G57"/>
+    <mergeCell ref="BN50:BN51"/>
+    <mergeCell ref="BN54:BN55"/>
+    <mergeCell ref="BN56:BN57"/>
+    <mergeCell ref="AU66:AU68"/>
+    <mergeCell ref="AT50:AT51"/>
+    <mergeCell ref="O48:U57"/>
+    <mergeCell ref="AT48:AT49"/>
+    <mergeCell ref="AK58:AN58"/>
+    <mergeCell ref="BM76:BM78"/>
+    <mergeCell ref="O42:P42"/>
+    <mergeCell ref="O43:P43"/>
+    <mergeCell ref="BD42:BD43"/>
+    <mergeCell ref="BD44:BD45"/>
+    <mergeCell ref="AT42:AT43"/>
+    <mergeCell ref="AT44:AT45"/>
+    <mergeCell ref="AT46:AT47"/>
+    <mergeCell ref="BD46:BD47"/>
+    <mergeCell ref="BD48:BD49"/>
+    <mergeCell ref="BD50:BD51"/>
+    <mergeCell ref="BD52:BD53"/>
+    <mergeCell ref="O44:P44"/>
+    <mergeCell ref="AJ40:AJ41"/>
+    <mergeCell ref="AJ42:AJ43"/>
+    <mergeCell ref="AJ44:AJ45"/>
+    <mergeCell ref="AJ46:AJ47"/>
+    <mergeCell ref="AJ48:AJ49"/>
+    <mergeCell ref="E37:M37"/>
+    <mergeCell ref="O37:U37"/>
+    <mergeCell ref="O38:O39"/>
+    <mergeCell ref="E44:F45"/>
+    <mergeCell ref="G44:G45"/>
+    <mergeCell ref="O11:U14"/>
+    <mergeCell ref="A12:B14"/>
+    <mergeCell ref="E14:G15"/>
+    <mergeCell ref="A15:B17"/>
+    <mergeCell ref="O15:U18"/>
+    <mergeCell ref="E16:G18"/>
+    <mergeCell ref="A18:B20"/>
+    <mergeCell ref="O19:U36"/>
+    <mergeCell ref="E20:G24"/>
+    <mergeCell ref="BN13:BN14"/>
+    <mergeCell ref="AB2:AI2"/>
+    <mergeCell ref="AV2:BC2"/>
+    <mergeCell ref="BF2:BM2"/>
+    <mergeCell ref="H3:I36"/>
+    <mergeCell ref="J3:K36"/>
+    <mergeCell ref="L3:M36"/>
+    <mergeCell ref="O3:U7"/>
+    <mergeCell ref="O8:U10"/>
+    <mergeCell ref="E25:G30"/>
+    <mergeCell ref="BN15:BN16"/>
+    <mergeCell ref="E31:G33"/>
+    <mergeCell ref="E34:G35"/>
+    <mergeCell ref="E36:G36"/>
+    <mergeCell ref="F10:G12"/>
+    <mergeCell ref="BN17:BN18"/>
+    <mergeCell ref="BN19:BN20"/>
+    <mergeCell ref="BN40:BN41"/>
+    <mergeCell ref="BN42:BN43"/>
+    <mergeCell ref="BN44:BN45"/>
+    <mergeCell ref="BN46:BN47"/>
+    <mergeCell ref="BN52:BN53"/>
+    <mergeCell ref="BN21:BN22"/>
+    <mergeCell ref="BN23:BN24"/>
+    <mergeCell ref="BN25:BN26"/>
+    <mergeCell ref="BN27:BN28"/>
+    <mergeCell ref="BN30:BN31"/>
+    <mergeCell ref="BN32:BN33"/>
+    <mergeCell ref="BN34:BN35"/>
+    <mergeCell ref="BN36:BN37"/>
+    <mergeCell ref="BN38:BN39"/>
+    <mergeCell ref="BN48:BN49"/>
+    <mergeCell ref="BN3:BN4"/>
+    <mergeCell ref="BN5:BN6"/>
+    <mergeCell ref="BN7:BN8"/>
+    <mergeCell ref="BN9:BN10"/>
+    <mergeCell ref="BD3:BD4"/>
+    <mergeCell ref="BD5:BD6"/>
+    <mergeCell ref="BD7:BD8"/>
+    <mergeCell ref="BD9:BD10"/>
+    <mergeCell ref="BD11:BD12"/>
+    <mergeCell ref="BN11:BN12"/>
+    <mergeCell ref="BD13:BD14"/>
+    <mergeCell ref="BD15:BD16"/>
+    <mergeCell ref="BD17:BD18"/>
+    <mergeCell ref="BD19:BD20"/>
+    <mergeCell ref="BD21:BD22"/>
+    <mergeCell ref="BD23:BD24"/>
+    <mergeCell ref="BD25:BD26"/>
+    <mergeCell ref="BD27:BD28"/>
+    <mergeCell ref="BD30:BD31"/>
+    <mergeCell ref="AT34:AT35"/>
+    <mergeCell ref="AT36:AT37"/>
+    <mergeCell ref="AT38:AT39"/>
+    <mergeCell ref="AT40:AT41"/>
+    <mergeCell ref="BD32:BD33"/>
+    <mergeCell ref="BD34:BD35"/>
+    <mergeCell ref="BD36:BD37"/>
+    <mergeCell ref="BD38:BD39"/>
+    <mergeCell ref="BF29:BM29"/>
+    <mergeCell ref="AV29:BC29"/>
+    <mergeCell ref="BD40:BD41"/>
+    <mergeCell ref="AO2:AP2"/>
+    <mergeCell ref="AT19:AT20"/>
+    <mergeCell ref="AT21:AT22"/>
+    <mergeCell ref="AT23:AT24"/>
+    <mergeCell ref="AT25:AT26"/>
+    <mergeCell ref="AT27:AT28"/>
+    <mergeCell ref="AT30:AT31"/>
+    <mergeCell ref="AT32:AT33"/>
+    <mergeCell ref="AT3:AT4"/>
+    <mergeCell ref="AT5:AT6"/>
+    <mergeCell ref="AT7:AT8"/>
+    <mergeCell ref="AT9:AT10"/>
+    <mergeCell ref="AT11:AT12"/>
+    <mergeCell ref="AT13:AT14"/>
+    <mergeCell ref="AT15:AT16"/>
+    <mergeCell ref="AT17:AT18"/>
   </mergeCells>
   <phoneticPr fontId="21" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\모듈러사업2실\★ 300. 제1공장_마감관리팀\350. 마감진행현황\BH(수정)\2026년 10월 BH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{038C2874-713E-4051-B453-25168DFEE6D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5442B3E3-5725-4ED3-8EA4-0375B2CC1F2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="788" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="821" uniqueCount="683">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="685">
   <si>
     <t>공업화 주택 샘플</t>
   </si>
@@ -4313,6 +4313,18 @@
     <t>402-7-1/
 36SB73
 2026-10-21</t>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <t>402-10-13/
+26SA43
+2026-10-22</t>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <t>402-11-12/
+26SA02
+2026-10-22</t>
     <phoneticPr fontId="21" type="noConversion"/>
   </si>
 </sst>
@@ -6328,13 +6340,475 @@
     <xf numFmtId="0" fontId="48" fillId="16" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="41" fillId="16" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="20" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="21" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="22" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="23" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="19" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="24" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="16" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="14" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="18" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="15" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="17" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="16" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="14" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="18" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="17" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="8" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="3" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="12" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="4" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="14" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="16" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="14" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="3" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="7" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="49" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="6" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="11" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="12" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="4" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="18" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="17" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="16" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="14" borderId="13" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="14" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="16" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="14" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="14" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="14" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="6" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="17" borderId="8" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6344,468 +6818,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="17" borderId="3" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="16" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="14" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="14" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="14" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="14" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="6" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="3" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="7" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="6" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="11" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="12" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="4" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="18" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="17" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="49" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="18" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="15" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="17" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="16" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="14" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="16" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="14" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="8" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="3" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="12" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="4" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="14" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="16" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="14" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="18" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="17" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="20" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="21" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="22" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="23" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="19" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="24" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -7281,52 +7293,52 @@
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
       <c r="AA2" s="230"/>
-      <c r="AB2" s="278" t="s">
+      <c r="AB2" s="406" t="s">
         <v>4</v>
       </c>
-      <c r="AC2" s="269"/>
-      <c r="AD2" s="269"/>
-      <c r="AE2" s="269"/>
-      <c r="AF2" s="269"/>
-      <c r="AG2" s="269"/>
-      <c r="AH2" s="269"/>
-      <c r="AI2" s="279"/>
+      <c r="AC2" s="407"/>
+      <c r="AD2" s="407"/>
+      <c r="AE2" s="407"/>
+      <c r="AF2" s="407"/>
+      <c r="AG2" s="407"/>
+      <c r="AH2" s="407"/>
+      <c r="AI2" s="408"/>
       <c r="AJ2" s="2"/>
       <c r="AK2" s="230"/>
       <c r="AL2" s="200"/>
       <c r="AM2" s="201"/>
       <c r="AN2" s="201"/>
-      <c r="AO2" s="269" t="s">
+      <c r="AO2" s="407" t="s">
         <v>5</v>
       </c>
-      <c r="AP2" s="269"/>
+      <c r="AP2" s="407"/>
       <c r="AQ2" s="201"/>
       <c r="AR2" s="201"/>
       <c r="AS2" s="202"/>
       <c r="AT2" s="2"/>
       <c r="AU2" s="226"/>
-      <c r="AV2" s="280" t="s">
+      <c r="AV2" s="409" t="s">
         <v>6</v>
       </c>
-      <c r="AW2" s="281"/>
-      <c r="AX2" s="281"/>
-      <c r="AY2" s="281"/>
-      <c r="AZ2" s="281"/>
-      <c r="BA2" s="281"/>
-      <c r="BB2" s="281"/>
-      <c r="BC2" s="282"/>
+      <c r="AW2" s="410"/>
+      <c r="AX2" s="410"/>
+      <c r="AY2" s="410"/>
+      <c r="AZ2" s="410"/>
+      <c r="BA2" s="410"/>
+      <c r="BB2" s="410"/>
+      <c r="BC2" s="411"/>
       <c r="BD2" s="190"/>
       <c r="BE2" s="220"/>
-      <c r="BF2" s="280" t="s">
+      <c r="BF2" s="409" t="s">
         <v>7</v>
       </c>
-      <c r="BG2" s="281"/>
-      <c r="BH2" s="281"/>
-      <c r="BI2" s="281"/>
-      <c r="BJ2" s="281"/>
-      <c r="BK2" s="281"/>
-      <c r="BL2" s="281"/>
-      <c r="BM2" s="282"/>
+      <c r="BG2" s="410"/>
+      <c r="BH2" s="410"/>
+      <c r="BI2" s="410"/>
+      <c r="BJ2" s="410"/>
+      <c r="BK2" s="410"/>
+      <c r="BL2" s="410"/>
+      <c r="BM2" s="411"/>
       <c r="BO2" s="224"/>
     </row>
     <row r="3" spans="1:67" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -7339,28 +7351,28 @@
       </c>
       <c r="F3" s="25"/>
       <c r="G3" s="25"/>
-      <c r="H3" s="283" t="s">
+      <c r="H3" s="412" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="284"/>
-      <c r="J3" s="283" t="s">
+      <c r="I3" s="413"/>
+      <c r="J3" s="412" t="s">
         <v>15</v>
       </c>
-      <c r="K3" s="284"/>
-      <c r="L3" s="290" t="s">
+      <c r="K3" s="413"/>
+      <c r="L3" s="414" t="s">
         <v>16</v>
       </c>
-      <c r="M3" s="290"/>
+      <c r="M3" s="414"/>
       <c r="N3" s="26"/>
-      <c r="O3" s="292" t="s">
+      <c r="O3" s="415" t="s">
         <v>17</v>
       </c>
-      <c r="P3" s="293"/>
-      <c r="Q3" s="293"/>
-      <c r="R3" s="293"/>
-      <c r="S3" s="293"/>
-      <c r="T3" s="293"/>
-      <c r="U3" s="293"/>
+      <c r="P3" s="416"/>
+      <c r="Q3" s="416"/>
+      <c r="R3" s="416"/>
+      <c r="S3" s="416"/>
+      <c r="T3" s="416"/>
+      <c r="U3" s="416"/>
       <c r="V3" s="27"/>
       <c r="W3" s="28"/>
       <c r="X3" s="28"/>
@@ -7378,9 +7390,7 @@
       <c r="AD3" s="188"/>
       <c r="AE3" s="188"/>
       <c r="AF3" s="188"/>
-      <c r="AG3" s="246" t="s">
-        <v>609</v>
-      </c>
+      <c r="AG3" s="188"/>
       <c r="AH3" s="188"/>
       <c r="AI3" s="188"/>
       <c r="AJ3" s="270" t="s">
@@ -7436,20 +7446,20 @@
       <c r="E4" s="30"/>
       <c r="F4" s="31"/>
       <c r="G4" s="31"/>
-      <c r="H4" s="285"/>
-      <c r="I4" s="286"/>
-      <c r="J4" s="285"/>
-      <c r="K4" s="286"/>
-      <c r="L4" s="287"/>
-      <c r="M4" s="287"/>
+      <c r="H4" s="343"/>
+      <c r="I4" s="345"/>
+      <c r="J4" s="343"/>
+      <c r="K4" s="345"/>
+      <c r="L4" s="344"/>
+      <c r="M4" s="344"/>
       <c r="N4" s="33"/>
-      <c r="O4" s="294"/>
-      <c r="P4" s="295"/>
-      <c r="Q4" s="295"/>
-      <c r="R4" s="295"/>
-      <c r="S4" s="295"/>
-      <c r="T4" s="295"/>
-      <c r="U4" s="295"/>
+      <c r="O4" s="417"/>
+      <c r="P4" s="418"/>
+      <c r="Q4" s="418"/>
+      <c r="R4" s="418"/>
+      <c r="S4" s="418"/>
+      <c r="T4" s="418"/>
+      <c r="U4" s="418"/>
       <c r="V4" s="34"/>
       <c r="W4" s="14"/>
       <c r="X4" s="14"/>
@@ -7462,9 +7472,13 @@
       <c r="AC4" s="237" t="s">
         <v>541</v>
       </c>
-      <c r="AD4" s="189"/>
+      <c r="AD4" s="243" t="s">
+        <v>610</v>
+      </c>
       <c r="AE4" s="189"/>
-      <c r="AF4" s="189"/>
+      <c r="AF4" s="243" t="s">
+        <v>609</v>
+      </c>
       <c r="AG4" s="235" t="s">
         <v>588</v>
       </c>
@@ -7517,20 +7531,20 @@
       <c r="E5" s="30"/>
       <c r="F5" s="31"/>
       <c r="G5" s="31"/>
-      <c r="H5" s="285"/>
-      <c r="I5" s="286"/>
-      <c r="J5" s="285"/>
-      <c r="K5" s="286"/>
-      <c r="L5" s="287"/>
-      <c r="M5" s="287"/>
+      <c r="H5" s="343"/>
+      <c r="I5" s="345"/>
+      <c r="J5" s="343"/>
+      <c r="K5" s="345"/>
+      <c r="L5" s="344"/>
+      <c r="M5" s="344"/>
       <c r="N5" s="33"/>
-      <c r="O5" s="294"/>
-      <c r="P5" s="295"/>
-      <c r="Q5" s="295"/>
-      <c r="R5" s="295"/>
-      <c r="S5" s="295"/>
-      <c r="T5" s="295"/>
-      <c r="U5" s="295"/>
+      <c r="O5" s="417"/>
+      <c r="P5" s="418"/>
+      <c r="Q5" s="418"/>
+      <c r="R5" s="418"/>
+      <c r="S5" s="418"/>
+      <c r="T5" s="418"/>
+      <c r="U5" s="418"/>
       <c r="V5" s="34"/>
       <c r="W5" s="14"/>
       <c r="X5" s="14"/>
@@ -7548,12 +7562,10 @@
       <c r="AD5" s="204"/>
       <c r="AE5" s="204"/>
       <c r="AF5" s="204"/>
-      <c r="AG5" s="246" t="s">
-        <v>610</v>
-      </c>
+      <c r="AG5" s="204"/>
       <c r="AH5" s="204"/>
       <c r="AI5" s="204"/>
-      <c r="AJ5" s="271" t="s">
+      <c r="AJ5" s="269" t="s">
         <v>507</v>
       </c>
       <c r="AK5" s="228" t="s">
@@ -7567,7 +7579,7 @@
       <c r="AQ5" s="204"/>
       <c r="AR5" s="204"/>
       <c r="AS5" s="204"/>
-      <c r="AT5" s="271" t="s">
+      <c r="AT5" s="269" t="s">
         <v>331</v>
       </c>
       <c r="AU5" s="228" t="s">
@@ -7581,7 +7593,7 @@
       <c r="BA5" s="204"/>
       <c r="BB5" s="204"/>
       <c r="BC5" s="204"/>
-      <c r="BD5" s="271" t="s">
+      <c r="BD5" s="269" t="s">
         <v>305</v>
       </c>
       <c r="BE5" s="222" t="s">
@@ -7595,7 +7607,7 @@
       <c r="BK5" s="204"/>
       <c r="BL5" s="204"/>
       <c r="BM5" s="204"/>
-      <c r="BN5" s="271" t="s">
+      <c r="BN5" s="269" t="s">
         <v>277</v>
       </c>
       <c r="BO5" s="224"/>
@@ -7606,20 +7618,20 @@
       <c r="E6" s="30"/>
       <c r="F6" s="31"/>
       <c r="G6" s="31"/>
-      <c r="H6" s="285"/>
-      <c r="I6" s="286"/>
-      <c r="J6" s="285"/>
-      <c r="K6" s="286"/>
-      <c r="L6" s="287"/>
-      <c r="M6" s="287"/>
+      <c r="H6" s="343"/>
+      <c r="I6" s="345"/>
+      <c r="J6" s="343"/>
+      <c r="K6" s="345"/>
+      <c r="L6" s="344"/>
+      <c r="M6" s="344"/>
       <c r="N6" s="33"/>
-      <c r="O6" s="294"/>
-      <c r="P6" s="295"/>
-      <c r="Q6" s="295"/>
-      <c r="R6" s="295"/>
-      <c r="S6" s="295"/>
-      <c r="T6" s="295"/>
-      <c r="U6" s="295"/>
+      <c r="O6" s="417"/>
+      <c r="P6" s="418"/>
+      <c r="Q6" s="418"/>
+      <c r="R6" s="418"/>
+      <c r="S6" s="418"/>
+      <c r="T6" s="418"/>
+      <c r="U6" s="418"/>
       <c r="V6" s="34"/>
       <c r="W6" s="14"/>
       <c r="X6" s="14"/>
@@ -7648,7 +7660,7 @@
       <c r="AI6" s="235" t="s">
         <v>582</v>
       </c>
-      <c r="AJ6" s="271"/>
+      <c r="AJ6" s="269"/>
       <c r="AK6" s="228"/>
       <c r="AL6" s="203"/>
       <c r="AM6" s="203"/>
@@ -7658,7 +7670,7 @@
       <c r="AQ6" s="203"/>
       <c r="AR6" s="203"/>
       <c r="AS6" s="203"/>
-      <c r="AT6" s="271"/>
+      <c r="AT6" s="269"/>
       <c r="AU6" s="228"/>
       <c r="AV6" s="203"/>
       <c r="AW6" s="203"/>
@@ -7668,7 +7680,7 @@
       <c r="BA6" s="203"/>
       <c r="BB6" s="203"/>
       <c r="BC6" s="203"/>
-      <c r="BD6" s="271"/>
+      <c r="BD6" s="269"/>
       <c r="BE6" s="222"/>
       <c r="BF6" s="211" t="s">
         <v>409</v>
@@ -7682,7 +7694,7 @@
       <c r="BK6" s="203"/>
       <c r="BL6" s="203"/>
       <c r="BM6" s="203"/>
-      <c r="BN6" s="271"/>
+      <c r="BN6" s="269"/>
       <c r="BO6" s="224"/>
     </row>
     <row r="7" spans="1:67" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -7694,20 +7706,20 @@
       <c r="E7" s="30"/>
       <c r="F7" s="31"/>
       <c r="G7" s="31"/>
-      <c r="H7" s="285"/>
-      <c r="I7" s="286"/>
-      <c r="J7" s="285"/>
-      <c r="K7" s="286"/>
-      <c r="L7" s="287"/>
-      <c r="M7" s="287"/>
+      <c r="H7" s="343"/>
+      <c r="I7" s="345"/>
+      <c r="J7" s="343"/>
+      <c r="K7" s="345"/>
+      <c r="L7" s="344"/>
+      <c r="M7" s="344"/>
       <c r="N7" s="33"/>
-      <c r="O7" s="296"/>
-      <c r="P7" s="297"/>
-      <c r="Q7" s="297"/>
-      <c r="R7" s="297"/>
-      <c r="S7" s="297"/>
-      <c r="T7" s="297"/>
-      <c r="U7" s="297"/>
+      <c r="O7" s="419"/>
+      <c r="P7" s="420"/>
+      <c r="Q7" s="420"/>
+      <c r="R7" s="420"/>
+      <c r="S7" s="420"/>
+      <c r="T7" s="420"/>
+      <c r="U7" s="420"/>
       <c r="V7" s="34"/>
       <c r="W7" s="14"/>
       <c r="X7" s="14"/>
@@ -7783,22 +7795,22 @@
       <c r="E8" s="30"/>
       <c r="F8" s="31"/>
       <c r="G8" s="31"/>
-      <c r="H8" s="285"/>
-      <c r="I8" s="286"/>
-      <c r="J8" s="285"/>
-      <c r="K8" s="286"/>
-      <c r="L8" s="287"/>
-      <c r="M8" s="287"/>
+      <c r="H8" s="343"/>
+      <c r="I8" s="345"/>
+      <c r="J8" s="343"/>
+      <c r="K8" s="345"/>
+      <c r="L8" s="344"/>
+      <c r="M8" s="344"/>
       <c r="N8" s="33"/>
-      <c r="O8" s="292" t="s">
+      <c r="O8" s="415" t="s">
         <v>18</v>
       </c>
-      <c r="P8" s="293"/>
-      <c r="Q8" s="293"/>
-      <c r="R8" s="293"/>
-      <c r="S8" s="293"/>
-      <c r="T8" s="293"/>
-      <c r="U8" s="293"/>
+      <c r="P8" s="416"/>
+      <c r="Q8" s="416"/>
+      <c r="R8" s="416"/>
+      <c r="S8" s="416"/>
+      <c r="T8" s="416"/>
+      <c r="U8" s="416"/>
       <c r="V8" s="34"/>
       <c r="W8" s="14"/>
       <c r="X8" s="14"/>
@@ -7873,20 +7885,20 @@
       <c r="E9" s="30"/>
       <c r="F9" s="31"/>
       <c r="G9" s="31"/>
-      <c r="H9" s="285"/>
-      <c r="I9" s="286"/>
-      <c r="J9" s="285"/>
-      <c r="K9" s="286"/>
-      <c r="L9" s="287"/>
-      <c r="M9" s="287"/>
+      <c r="H9" s="343"/>
+      <c r="I9" s="345"/>
+      <c r="J9" s="343"/>
+      <c r="K9" s="345"/>
+      <c r="L9" s="344"/>
+      <c r="M9" s="344"/>
       <c r="N9" s="33"/>
-      <c r="O9" s="294"/>
-      <c r="P9" s="295"/>
-      <c r="Q9" s="295"/>
-      <c r="R9" s="295"/>
-      <c r="S9" s="295"/>
-      <c r="T9" s="295"/>
-      <c r="U9" s="295"/>
+      <c r="O9" s="417"/>
+      <c r="P9" s="418"/>
+      <c r="Q9" s="418"/>
+      <c r="R9" s="418"/>
+      <c r="S9" s="418"/>
+      <c r="T9" s="418"/>
+      <c r="U9" s="418"/>
       <c r="V9" s="34"/>
       <c r="W9" s="14"/>
       <c r="X9" s="14"/>
@@ -7907,7 +7919,7 @@
       <c r="AG9" s="204"/>
       <c r="AH9" s="204"/>
       <c r="AI9" s="204"/>
-      <c r="AJ9" s="271" t="s">
+      <c r="AJ9" s="269" t="s">
         <v>509</v>
       </c>
       <c r="AK9" s="228" t="s">
@@ -7921,7 +7933,7 @@
       <c r="AQ9" s="204"/>
       <c r="AR9" s="204"/>
       <c r="AS9" s="204"/>
-      <c r="AT9" s="271" t="s">
+      <c r="AT9" s="269" t="s">
         <v>333</v>
       </c>
       <c r="AU9" s="228" t="s">
@@ -7939,7 +7951,7 @@
       <c r="BC9" s="265" t="s">
         <v>96</v>
       </c>
-      <c r="BD9" s="271" t="s">
+      <c r="BD9" s="269" t="s">
         <v>307</v>
       </c>
       <c r="BE9" s="222" t="s">
@@ -7957,7 +7969,7 @@
       <c r="BM9" s="197" t="s">
         <v>52</v>
       </c>
-      <c r="BN9" s="275" t="s">
+      <c r="BN9" s="425" t="s">
         <v>279</v>
       </c>
       <c r="BO9" s="224"/>
@@ -7968,24 +7980,24 @@
       </c>
       <c r="B10" s="16"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="307" t="s">
+      <c r="F10" s="351" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="308"/>
-      <c r="H10" s="287"/>
-      <c r="I10" s="286"/>
-      <c r="J10" s="285"/>
-      <c r="K10" s="286"/>
-      <c r="L10" s="287"/>
-      <c r="M10" s="287"/>
+      <c r="G10" s="353"/>
+      <c r="H10" s="344"/>
+      <c r="I10" s="345"/>
+      <c r="J10" s="343"/>
+      <c r="K10" s="345"/>
+      <c r="L10" s="344"/>
+      <c r="M10" s="344"/>
       <c r="N10" s="33"/>
-      <c r="O10" s="294"/>
-      <c r="P10" s="295"/>
-      <c r="Q10" s="295"/>
-      <c r="R10" s="295"/>
-      <c r="S10" s="295"/>
-      <c r="T10" s="295"/>
-      <c r="U10" s="295"/>
+      <c r="O10" s="417"/>
+      <c r="P10" s="418"/>
+      <c r="Q10" s="418"/>
+      <c r="R10" s="418"/>
+      <c r="S10" s="418"/>
+      <c r="T10" s="418"/>
+      <c r="U10" s="418"/>
       <c r="V10" s="34"/>
       <c r="W10" s="14"/>
       <c r="X10" s="14"/>
@@ -8012,7 +8024,7 @@
       </c>
       <c r="AH10" s="203"/>
       <c r="AI10" s="203"/>
-      <c r="AJ10" s="271"/>
+      <c r="AJ10" s="269"/>
       <c r="AK10" s="228"/>
       <c r="AL10" s="203"/>
       <c r="AM10" s="203"/>
@@ -8022,7 +8034,7 @@
       <c r="AQ10" s="203"/>
       <c r="AR10" s="203"/>
       <c r="AS10" s="203"/>
-      <c r="AT10" s="271"/>
+      <c r="AT10" s="269"/>
       <c r="AU10" s="228"/>
       <c r="AV10" s="249"/>
       <c r="AW10" s="196" t="s">
@@ -8042,7 +8054,7 @@
       <c r="BC10" s="266" t="s">
         <v>98</v>
       </c>
-      <c r="BD10" s="271"/>
+      <c r="BD10" s="269"/>
       <c r="BE10" s="222"/>
       <c r="BF10" s="238" t="s">
         <v>161</v>
@@ -8062,31 +8074,31 @@
       <c r="BM10" s="238" t="s">
         <v>164</v>
       </c>
-      <c r="BN10" s="275"/>
+      <c r="BN10" s="425"/>
       <c r="BO10" s="224"/>
     </row>
     <row r="11" spans="1:67" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6"/>
       <c r="B11" s="18"/>
       <c r="E11" s="30"/>
-      <c r="F11" s="309"/>
-      <c r="G11" s="310"/>
-      <c r="H11" s="287"/>
-      <c r="I11" s="286"/>
-      <c r="J11" s="285"/>
-      <c r="K11" s="286"/>
-      <c r="L11" s="287"/>
-      <c r="M11" s="287"/>
+      <c r="F11" s="421"/>
+      <c r="G11" s="422"/>
+      <c r="H11" s="344"/>
+      <c r="I11" s="345"/>
+      <c r="J11" s="343"/>
+      <c r="K11" s="345"/>
+      <c r="L11" s="344"/>
+      <c r="M11" s="344"/>
       <c r="N11" s="33"/>
-      <c r="O11" s="313" t="s">
+      <c r="O11" s="366" t="s">
         <v>20</v>
       </c>
-      <c r="P11" s="314"/>
-      <c r="Q11" s="314"/>
-      <c r="R11" s="314"/>
-      <c r="S11" s="314"/>
-      <c r="T11" s="314"/>
-      <c r="U11" s="315"/>
+      <c r="P11" s="367"/>
+      <c r="Q11" s="367"/>
+      <c r="R11" s="367"/>
+      <c r="S11" s="367"/>
+      <c r="T11" s="367"/>
+      <c r="U11" s="368"/>
       <c r="V11" s="34"/>
       <c r="W11" s="14"/>
       <c r="X11" s="14"/>
@@ -8161,33 +8173,33 @@
       <c r="BM11" s="197" t="s">
         <v>180</v>
       </c>
-      <c r="BN11" s="276" t="s">
+      <c r="BN11" s="349" t="s">
         <v>280</v>
       </c>
       <c r="BO11" s="224"/>
     </row>
     <row r="12" spans="1:67" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="322" t="s">
+      <c r="A12" s="375" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="323"/>
+      <c r="B12" s="376"/>
       <c r="E12" s="46"/>
-      <c r="F12" s="311"/>
-      <c r="G12" s="312"/>
-      <c r="H12" s="287"/>
-      <c r="I12" s="286"/>
-      <c r="J12" s="285"/>
-      <c r="K12" s="286"/>
-      <c r="L12" s="287"/>
-      <c r="M12" s="287"/>
+      <c r="F12" s="423"/>
+      <c r="G12" s="424"/>
+      <c r="H12" s="344"/>
+      <c r="I12" s="345"/>
+      <c r="J12" s="343"/>
+      <c r="K12" s="345"/>
+      <c r="L12" s="344"/>
+      <c r="M12" s="344"/>
       <c r="N12" s="33"/>
-      <c r="O12" s="316"/>
-      <c r="P12" s="317"/>
-      <c r="Q12" s="317"/>
-      <c r="R12" s="317"/>
-      <c r="S12" s="317"/>
-      <c r="T12" s="317"/>
-      <c r="U12" s="318"/>
+      <c r="O12" s="369"/>
+      <c r="P12" s="370"/>
+      <c r="Q12" s="370"/>
+      <c r="R12" s="370"/>
+      <c r="S12" s="370"/>
+      <c r="T12" s="370"/>
+      <c r="U12" s="371"/>
       <c r="V12" s="34"/>
       <c r="W12" s="14"/>
       <c r="X12" s="14"/>
@@ -8262,29 +8274,29 @@
       <c r="BM12" s="238" t="s">
         <v>173</v>
       </c>
-      <c r="BN12" s="276"/>
+      <c r="BN12" s="349"/>
       <c r="BO12" s="224"/>
     </row>
     <row r="13" spans="1:67" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="324"/>
-      <c r="B13" s="325"/>
+      <c r="A13" s="325"/>
+      <c r="B13" s="377"/>
       <c r="E13" s="48"/>
       <c r="F13" s="49"/>
       <c r="G13" s="49"/>
-      <c r="H13" s="285"/>
-      <c r="I13" s="286"/>
-      <c r="J13" s="285"/>
-      <c r="K13" s="286"/>
-      <c r="L13" s="287"/>
-      <c r="M13" s="287"/>
+      <c r="H13" s="343"/>
+      <c r="I13" s="345"/>
+      <c r="J13" s="343"/>
+      <c r="K13" s="345"/>
+      <c r="L13" s="344"/>
+      <c r="M13" s="344"/>
       <c r="N13" s="33"/>
-      <c r="O13" s="316"/>
-      <c r="P13" s="317"/>
-      <c r="Q13" s="317"/>
-      <c r="R13" s="317"/>
-      <c r="S13" s="317"/>
-      <c r="T13" s="317"/>
-      <c r="U13" s="318"/>
+      <c r="O13" s="369"/>
+      <c r="P13" s="370"/>
+      <c r="Q13" s="370"/>
+      <c r="R13" s="370"/>
+      <c r="S13" s="370"/>
+      <c r="T13" s="370"/>
+      <c r="U13" s="371"/>
       <c r="V13" s="34"/>
       <c r="W13" s="14"/>
       <c r="X13" s="14"/>
@@ -8301,7 +8313,7 @@
       <c r="AG13" s="204"/>
       <c r="AH13" s="204"/>
       <c r="AI13" s="204"/>
-      <c r="AJ13" s="271" t="s">
+      <c r="AJ13" s="269" t="s">
         <v>511</v>
       </c>
       <c r="AK13" s="228" t="s">
@@ -8315,7 +8327,7 @@
       <c r="AQ13" s="204"/>
       <c r="AR13" s="204"/>
       <c r="AS13" s="204"/>
-      <c r="AT13" s="271" t="s">
+      <c r="AT13" s="269" t="s">
         <v>335</v>
       </c>
       <c r="AU13" s="228" t="s">
@@ -8331,7 +8343,7 @@
       <c r="BC13" s="197" t="s">
         <v>112</v>
       </c>
-      <c r="BD13" s="271" t="s">
+      <c r="BD13" s="269" t="s">
         <v>309</v>
       </c>
       <c r="BE13" s="222" t="s">
@@ -8351,35 +8363,35 @@
       <c r="BK13" s="204"/>
       <c r="BL13" s="204"/>
       <c r="BM13" s="204"/>
-      <c r="BN13" s="277" t="s">
+      <c r="BN13" s="405" t="s">
         <v>281</v>
       </c>
       <c r="BO13" s="224"/>
     </row>
     <row r="14" spans="1:67" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="326"/>
-      <c r="B14" s="327"/>
+      <c r="A14" s="332"/>
+      <c r="B14" s="378"/>
       <c r="C14" s="50"/>
       <c r="D14" s="42"/>
-      <c r="E14" s="305" t="s">
+      <c r="E14" s="379" t="s">
         <v>22</v>
       </c>
-      <c r="F14" s="305"/>
-      <c r="G14" s="306"/>
-      <c r="H14" s="285"/>
-      <c r="I14" s="286"/>
-      <c r="J14" s="285"/>
-      <c r="K14" s="286"/>
-      <c r="L14" s="287"/>
-      <c r="M14" s="287"/>
+      <c r="F14" s="379"/>
+      <c r="G14" s="380"/>
+      <c r="H14" s="343"/>
+      <c r="I14" s="345"/>
+      <c r="J14" s="343"/>
+      <c r="K14" s="345"/>
+      <c r="L14" s="344"/>
+      <c r="M14" s="344"/>
       <c r="N14" s="33"/>
-      <c r="O14" s="319"/>
-      <c r="P14" s="320"/>
-      <c r="Q14" s="320"/>
-      <c r="R14" s="320"/>
-      <c r="S14" s="320"/>
-      <c r="T14" s="320"/>
-      <c r="U14" s="321"/>
+      <c r="O14" s="372"/>
+      <c r="P14" s="373"/>
+      <c r="Q14" s="373"/>
+      <c r="R14" s="373"/>
+      <c r="S14" s="373"/>
+      <c r="T14" s="373"/>
+      <c r="U14" s="374"/>
       <c r="V14" s="34"/>
       <c r="W14" s="14"/>
       <c r="X14" s="14"/>
@@ -8396,7 +8408,7 @@
       <c r="AG14" s="203"/>
       <c r="AH14" s="203"/>
       <c r="AI14" s="203"/>
-      <c r="AJ14" s="271"/>
+      <c r="AJ14" s="269"/>
       <c r="AK14" s="228"/>
       <c r="AL14" s="203"/>
       <c r="AM14" s="203"/>
@@ -8406,7 +8418,7 @@
       <c r="AQ14" s="203"/>
       <c r="AR14" s="203"/>
       <c r="AS14" s="203"/>
-      <c r="AT14" s="271"/>
+      <c r="AT14" s="269"/>
       <c r="AU14" s="228"/>
       <c r="AV14" s="196" t="s">
         <v>168</v>
@@ -8428,7 +8440,7 @@
       <c r="BC14" s="196" t="s">
         <v>101</v>
       </c>
-      <c r="BD14" s="271"/>
+      <c r="BD14" s="269"/>
       <c r="BE14" s="222"/>
       <c r="BF14" s="196" t="s">
         <v>175</v>
@@ -8450,33 +8462,33 @@
         <v>395</v>
       </c>
       <c r="BM14" s="203"/>
-      <c r="BN14" s="277"/>
+      <c r="BN14" s="405"/>
       <c r="BO14" s="224"/>
     </row>
     <row r="15" spans="1:67" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="322" t="s">
+      <c r="A15" s="375" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="328"/>
+      <c r="B15" s="383"/>
       <c r="C15" s="50"/>
       <c r="D15" s="52"/>
-      <c r="E15" s="302"/>
-      <c r="F15" s="302"/>
-      <c r="G15" s="303"/>
-      <c r="H15" s="285"/>
-      <c r="I15" s="286"/>
-      <c r="J15" s="285"/>
-      <c r="K15" s="286"/>
-      <c r="L15" s="287"/>
-      <c r="M15" s="287"/>
+      <c r="E15" s="381"/>
+      <c r="F15" s="381"/>
+      <c r="G15" s="382"/>
+      <c r="H15" s="343"/>
+      <c r="I15" s="345"/>
+      <c r="J15" s="343"/>
+      <c r="K15" s="345"/>
+      <c r="L15" s="344"/>
+      <c r="M15" s="344"/>
       <c r="N15" s="33"/>
-      <c r="O15" s="330"/>
-      <c r="P15" s="331"/>
-      <c r="Q15" s="331"/>
-      <c r="R15" s="331"/>
-      <c r="S15" s="331"/>
-      <c r="T15" s="331"/>
-      <c r="U15" s="332"/>
+      <c r="O15" s="385"/>
+      <c r="P15" s="386"/>
+      <c r="Q15" s="386"/>
+      <c r="R15" s="386"/>
+      <c r="S15" s="386"/>
+      <c r="T15" s="386"/>
+      <c r="U15" s="387"/>
       <c r="V15" s="27"/>
       <c r="W15" s="28"/>
       <c r="X15" s="28"/>
@@ -8541,35 +8553,35 @@
       <c r="BK15" s="188"/>
       <c r="BL15" s="188"/>
       <c r="BM15" s="188"/>
-      <c r="BN15" s="276" t="s">
+      <c r="BN15" s="349" t="s">
         <v>282</v>
       </c>
       <c r="BO15" s="224"/>
     </row>
     <row r="16" spans="1:67" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="324"/>
-      <c r="B16" s="329"/>
+      <c r="A16" s="325"/>
+      <c r="B16" s="384"/>
       <c r="C16" s="53"/>
       <c r="D16" s="52"/>
-      <c r="E16" s="305" t="s">
+      <c r="E16" s="379" t="s">
         <v>22</v>
       </c>
-      <c r="F16" s="305"/>
-      <c r="G16" s="306"/>
-      <c r="H16" s="285"/>
-      <c r="I16" s="286"/>
-      <c r="J16" s="285"/>
-      <c r="K16" s="286"/>
-      <c r="L16" s="287"/>
-      <c r="M16" s="287"/>
+      <c r="F16" s="379"/>
+      <c r="G16" s="380"/>
+      <c r="H16" s="343"/>
+      <c r="I16" s="345"/>
+      <c r="J16" s="343"/>
+      <c r="K16" s="345"/>
+      <c r="L16" s="344"/>
+      <c r="M16" s="344"/>
       <c r="N16" s="33"/>
-      <c r="O16" s="333"/>
-      <c r="P16" s="334"/>
-      <c r="Q16" s="334"/>
-      <c r="R16" s="334"/>
-      <c r="S16" s="334"/>
-      <c r="T16" s="334"/>
-      <c r="U16" s="335"/>
+      <c r="O16" s="388"/>
+      <c r="P16" s="389"/>
+      <c r="Q16" s="389"/>
+      <c r="R16" s="389"/>
+      <c r="S16" s="389"/>
+      <c r="T16" s="389"/>
+      <c r="U16" s="390"/>
       <c r="V16" s="34"/>
       <c r="W16" s="14"/>
       <c r="X16" s="40"/>
@@ -8638,31 +8650,31 @@
         <v>396</v>
       </c>
       <c r="BM16" s="189"/>
-      <c r="BN16" s="276"/>
+      <c r="BN16" s="349"/>
       <c r="BO16" s="224"/>
     </row>
     <row r="17" spans="1:70" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="326"/>
-      <c r="B17" s="327"/>
+      <c r="A17" s="332"/>
+      <c r="B17" s="378"/>
       <c r="C17" s="50"/>
       <c r="D17" s="55"/>
-      <c r="E17" s="299"/>
-      <c r="F17" s="299"/>
-      <c r="G17" s="300"/>
-      <c r="H17" s="285"/>
-      <c r="I17" s="286"/>
-      <c r="J17" s="285"/>
-      <c r="K17" s="286"/>
-      <c r="L17" s="287"/>
-      <c r="M17" s="287"/>
+      <c r="E17" s="394"/>
+      <c r="F17" s="394"/>
+      <c r="G17" s="395"/>
+      <c r="H17" s="343"/>
+      <c r="I17" s="345"/>
+      <c r="J17" s="343"/>
+      <c r="K17" s="345"/>
+      <c r="L17" s="344"/>
+      <c r="M17" s="344"/>
       <c r="N17" s="33"/>
-      <c r="O17" s="333"/>
-      <c r="P17" s="334"/>
-      <c r="Q17" s="334"/>
-      <c r="R17" s="334"/>
-      <c r="S17" s="334"/>
-      <c r="T17" s="334"/>
-      <c r="U17" s="335"/>
+      <c r="O17" s="388"/>
+      <c r="P17" s="389"/>
+      <c r="Q17" s="389"/>
+      <c r="R17" s="389"/>
+      <c r="S17" s="389"/>
+      <c r="T17" s="389"/>
+      <c r="U17" s="390"/>
       <c r="V17" s="47"/>
       <c r="W17" s="44"/>
       <c r="X17" s="44"/>
@@ -8679,7 +8691,7 @@
       <c r="AG17" s="204"/>
       <c r="AH17" s="204"/>
       <c r="AI17" s="204"/>
-      <c r="AJ17" s="271" t="s">
+      <c r="AJ17" s="269" t="s">
         <v>513</v>
       </c>
       <c r="AK17" s="228" t="s">
@@ -8693,7 +8705,7 @@
       <c r="AQ17" s="204"/>
       <c r="AR17" s="204"/>
       <c r="AS17" s="204"/>
-      <c r="AT17" s="271" t="s">
+      <c r="AT17" s="269" t="s">
         <v>337</v>
       </c>
       <c r="AU17" s="228" t="s">
@@ -8713,7 +8725,7 @@
       </c>
       <c r="BB17" s="248"/>
       <c r="BC17" s="204"/>
-      <c r="BD17" s="271" t="s">
+      <c r="BD17" s="269" t="s">
         <v>311</v>
       </c>
       <c r="BE17" s="222" t="s">
@@ -8735,35 +8747,35 @@
       <c r="BM17" s="245" t="s">
         <v>660</v>
       </c>
-      <c r="BN17" s="277" t="s">
+      <c r="BN17" s="405" t="s">
         <v>283</v>
       </c>
       <c r="BO17" s="224"/>
     </row>
     <row r="18" spans="1:70" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="322" t="s">
+      <c r="A18" s="375" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="323"/>
+      <c r="B18" s="376"/>
       <c r="C18" s="19"/>
       <c r="D18" s="19"/>
-      <c r="E18" s="298"/>
-      <c r="F18" s="299"/>
-      <c r="G18" s="300"/>
-      <c r="H18" s="285"/>
-      <c r="I18" s="286"/>
-      <c r="J18" s="285"/>
-      <c r="K18" s="286"/>
-      <c r="L18" s="287"/>
-      <c r="M18" s="287"/>
+      <c r="E18" s="396"/>
+      <c r="F18" s="394"/>
+      <c r="G18" s="395"/>
+      <c r="H18" s="343"/>
+      <c r="I18" s="345"/>
+      <c r="J18" s="343"/>
+      <c r="K18" s="345"/>
+      <c r="L18" s="344"/>
+      <c r="M18" s="344"/>
       <c r="N18" s="33"/>
-      <c r="O18" s="336"/>
-      <c r="P18" s="337"/>
-      <c r="Q18" s="337"/>
-      <c r="R18" s="337"/>
-      <c r="S18" s="337"/>
-      <c r="T18" s="337"/>
-      <c r="U18" s="338"/>
+      <c r="O18" s="391"/>
+      <c r="P18" s="392"/>
+      <c r="Q18" s="392"/>
+      <c r="R18" s="392"/>
+      <c r="S18" s="392"/>
+      <c r="T18" s="392"/>
+      <c r="U18" s="393"/>
       <c r="V18" s="47"/>
       <c r="Z18" s="42"/>
       <c r="AA18" s="228"/>
@@ -8777,7 +8789,7 @@
       <c r="AG18" s="203"/>
       <c r="AH18" s="203"/>
       <c r="AI18" s="203"/>
-      <c r="AJ18" s="271"/>
+      <c r="AJ18" s="269"/>
       <c r="AK18" s="228"/>
       <c r="AL18" s="203"/>
       <c r="AM18" s="203"/>
@@ -8787,7 +8799,7 @@
       <c r="AQ18" s="203"/>
       <c r="AR18" s="203"/>
       <c r="AS18" s="203"/>
-      <c r="AT18" s="271"/>
+      <c r="AT18" s="269"/>
       <c r="AU18" s="228"/>
       <c r="AV18" s="211" t="s">
         <v>554</v>
@@ -8811,7 +8823,7 @@
       <c r="BC18" s="235" t="s">
         <v>107</v>
       </c>
-      <c r="BD18" s="271"/>
+      <c r="BD18" s="269"/>
       <c r="BE18" s="222"/>
       <c r="BF18" s="235" t="s">
         <v>406</v>
@@ -8835,33 +8847,33 @@
       <c r="BM18" s="244" t="s">
         <v>659</v>
       </c>
-      <c r="BN18" s="277"/>
+      <c r="BN18" s="405"/>
       <c r="BO18" s="224"/>
     </row>
     <row r="19" spans="1:70" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="324"/>
-      <c r="B19" s="325"/>
+      <c r="A19" s="325"/>
+      <c r="B19" s="377"/>
       <c r="C19" s="19"/>
       <c r="D19" s="56"/>
       <c r="E19" s="57"/>
       <c r="F19" s="58"/>
       <c r="G19" s="58"/>
-      <c r="H19" s="285"/>
-      <c r="I19" s="286"/>
-      <c r="J19" s="285"/>
-      <c r="K19" s="286"/>
-      <c r="L19" s="287"/>
-      <c r="M19" s="287"/>
+      <c r="H19" s="343"/>
+      <c r="I19" s="345"/>
+      <c r="J19" s="343"/>
+      <c r="K19" s="345"/>
+      <c r="L19" s="344"/>
+      <c r="M19" s="344"/>
       <c r="N19" s="33"/>
-      <c r="O19" s="340" t="s">
+      <c r="O19" s="397" t="s">
         <v>25</v>
       </c>
-      <c r="P19" s="341"/>
-      <c r="Q19" s="341"/>
-      <c r="R19" s="341"/>
-      <c r="S19" s="341"/>
-      <c r="T19" s="341"/>
-      <c r="U19" s="342"/>
+      <c r="P19" s="398"/>
+      <c r="Q19" s="398"/>
+      <c r="R19" s="398"/>
+      <c r="S19" s="398"/>
+      <c r="T19" s="398"/>
+      <c r="U19" s="399"/>
       <c r="Z19" s="42"/>
       <c r="AA19" s="227" t="s">
         <v>275</v>
@@ -8926,33 +8938,33 @@
       <c r="BM19" s="197" t="s">
         <v>57</v>
       </c>
-      <c r="BN19" s="276" t="s">
+      <c r="BN19" s="349" t="s">
         <v>284</v>
       </c>
       <c r="BO19" s="224"/>
     </row>
     <row r="20" spans="1:70" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="326"/>
-      <c r="B20" s="339"/>
-      <c r="E20" s="304" t="s">
+      <c r="A20" s="332"/>
+      <c r="B20" s="333"/>
+      <c r="E20" s="403" t="s">
         <v>26</v>
       </c>
-      <c r="F20" s="305"/>
-      <c r="G20" s="306"/>
-      <c r="H20" s="285"/>
-      <c r="I20" s="286"/>
-      <c r="J20" s="285"/>
-      <c r="K20" s="286"/>
-      <c r="L20" s="287"/>
-      <c r="M20" s="287"/>
+      <c r="F20" s="379"/>
+      <c r="G20" s="380"/>
+      <c r="H20" s="343"/>
+      <c r="I20" s="345"/>
+      <c r="J20" s="343"/>
+      <c r="K20" s="345"/>
+      <c r="L20" s="344"/>
+      <c r="M20" s="344"/>
       <c r="N20" s="33"/>
-      <c r="O20" s="343"/>
-      <c r="P20" s="344"/>
-      <c r="Q20" s="344"/>
-      <c r="R20" s="344"/>
-      <c r="S20" s="344"/>
-      <c r="T20" s="344"/>
-      <c r="U20" s="345"/>
+      <c r="O20" s="400"/>
+      <c r="P20" s="401"/>
+      <c r="Q20" s="401"/>
+      <c r="R20" s="401"/>
+      <c r="S20" s="401"/>
+      <c r="T20" s="401"/>
+      <c r="U20" s="402"/>
       <c r="V20" s="59"/>
       <c r="X20" s="41"/>
       <c r="Z20" s="42"/>
@@ -9021,29 +9033,29 @@
       <c r="BM20" s="238" t="s">
         <v>58</v>
       </c>
-      <c r="BN20" s="276"/>
+      <c r="BN20" s="349"/>
       <c r="BO20" s="224"/>
     </row>
     <row r="21" spans="1:70" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="40"/>
       <c r="B21" s="40"/>
-      <c r="E21" s="298"/>
-      <c r="F21" s="299"/>
-      <c r="G21" s="300"/>
-      <c r="H21" s="285"/>
-      <c r="I21" s="286"/>
-      <c r="J21" s="285"/>
-      <c r="K21" s="286"/>
-      <c r="L21" s="287"/>
-      <c r="M21" s="287"/>
+      <c r="E21" s="396"/>
+      <c r="F21" s="394"/>
+      <c r="G21" s="395"/>
+      <c r="H21" s="343"/>
+      <c r="I21" s="345"/>
+      <c r="J21" s="343"/>
+      <c r="K21" s="345"/>
+      <c r="L21" s="344"/>
+      <c r="M21" s="344"/>
       <c r="N21" s="33"/>
-      <c r="O21" s="343"/>
-      <c r="P21" s="344"/>
-      <c r="Q21" s="344"/>
-      <c r="R21" s="344"/>
-      <c r="S21" s="344"/>
-      <c r="T21" s="344"/>
-      <c r="U21" s="345"/>
+      <c r="O21" s="400"/>
+      <c r="P21" s="401"/>
+      <c r="Q21" s="401"/>
+      <c r="R21" s="401"/>
+      <c r="S21" s="401"/>
+      <c r="T21" s="401"/>
+      <c r="U21" s="402"/>
       <c r="V21" s="37"/>
       <c r="W21" s="60"/>
       <c r="X21" s="41"/>
@@ -9059,7 +9071,7 @@
       <c r="AG21" s="204"/>
       <c r="AH21" s="204"/>
       <c r="AI21" s="204"/>
-      <c r="AJ21" s="271" t="s">
+      <c r="AJ21" s="269" t="s">
         <v>515</v>
       </c>
       <c r="AK21" s="228" t="s">
@@ -9073,7 +9085,7 @@
       <c r="AQ21" s="204"/>
       <c r="AR21" s="204"/>
       <c r="AS21" s="204"/>
-      <c r="AT21" s="271" t="s">
+      <c r="AT21" s="269" t="s">
         <v>339</v>
       </c>
       <c r="AU21" s="228" t="s">
@@ -9089,7 +9101,7 @@
       <c r="BA21" s="204"/>
       <c r="BB21" s="204"/>
       <c r="BC21" s="204"/>
-      <c r="BD21" s="271" t="s">
+      <c r="BD21" s="269" t="s">
         <v>313</v>
       </c>
       <c r="BE21" s="222" t="s">
@@ -9107,7 +9119,7 @@
       <c r="BM21" s="197" t="s">
         <v>103</v>
       </c>
-      <c r="BN21" s="277" t="s">
+      <c r="BN21" s="405" t="s">
         <v>285</v>
       </c>
       <c r="BO21" s="224"/>
@@ -9115,23 +9127,23 @@
     <row r="22" spans="1:70" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="40"/>
       <c r="B22" s="40"/>
-      <c r="E22" s="298"/>
-      <c r="F22" s="299"/>
-      <c r="G22" s="300"/>
-      <c r="H22" s="285"/>
-      <c r="I22" s="286"/>
-      <c r="J22" s="285"/>
-      <c r="K22" s="286"/>
-      <c r="L22" s="287"/>
-      <c r="M22" s="287"/>
+      <c r="E22" s="396"/>
+      <c r="F22" s="394"/>
+      <c r="G22" s="395"/>
+      <c r="H22" s="343"/>
+      <c r="I22" s="345"/>
+      <c r="J22" s="343"/>
+      <c r="K22" s="345"/>
+      <c r="L22" s="344"/>
+      <c r="M22" s="344"/>
       <c r="N22" s="33"/>
-      <c r="O22" s="343"/>
-      <c r="P22" s="344"/>
-      <c r="Q22" s="344"/>
-      <c r="R22" s="344"/>
-      <c r="S22" s="344"/>
-      <c r="T22" s="344"/>
-      <c r="U22" s="345"/>
+      <c r="O22" s="400"/>
+      <c r="P22" s="401"/>
+      <c r="Q22" s="401"/>
+      <c r="R22" s="401"/>
+      <c r="S22" s="401"/>
+      <c r="T22" s="401"/>
+      <c r="U22" s="402"/>
       <c r="V22" s="45"/>
       <c r="X22" s="9"/>
       <c r="Y22" s="23"/>
@@ -9145,7 +9157,7 @@
       <c r="AG22" s="203"/>
       <c r="AH22" s="203"/>
       <c r="AI22" s="203"/>
-      <c r="AJ22" s="271"/>
+      <c r="AJ22" s="269"/>
       <c r="AK22" s="228"/>
       <c r="AL22" s="203"/>
       <c r="AM22" s="203"/>
@@ -9155,7 +9167,7 @@
       <c r="AQ22" s="203"/>
       <c r="AR22" s="203"/>
       <c r="AS22" s="203"/>
-      <c r="AT22" s="271"/>
+      <c r="AT22" s="269"/>
       <c r="AU22" s="228"/>
       <c r="AV22" s="235" t="s">
         <v>400</v>
@@ -9179,7 +9191,7 @@
       <c r="BC22" s="244" t="s">
         <v>640</v>
       </c>
-      <c r="BD22" s="271"/>
+      <c r="BD22" s="269"/>
       <c r="BE22" s="222"/>
       <c r="BF22" s="203"/>
       <c r="BG22" s="235" t="s">
@@ -9201,29 +9213,29 @@
       <c r="BM22" s="196" t="s">
         <v>193</v>
       </c>
-      <c r="BN22" s="277"/>
+      <c r="BN22" s="405"/>
       <c r="BO22" s="224"/>
     </row>
     <row r="23" spans="1:70" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="40"/>
       <c r="B23" s="40"/>
-      <c r="E23" s="298"/>
-      <c r="F23" s="299"/>
-      <c r="G23" s="300"/>
-      <c r="H23" s="285"/>
-      <c r="I23" s="286"/>
-      <c r="J23" s="285"/>
-      <c r="K23" s="286"/>
-      <c r="L23" s="287"/>
-      <c r="M23" s="287"/>
+      <c r="E23" s="396"/>
+      <c r="F23" s="394"/>
+      <c r="G23" s="395"/>
+      <c r="H23" s="343"/>
+      <c r="I23" s="345"/>
+      <c r="J23" s="343"/>
+      <c r="K23" s="345"/>
+      <c r="L23" s="344"/>
+      <c r="M23" s="344"/>
       <c r="N23" s="33"/>
-      <c r="O23" s="343"/>
-      <c r="P23" s="344"/>
-      <c r="Q23" s="344"/>
-      <c r="R23" s="344"/>
-      <c r="S23" s="344"/>
-      <c r="T23" s="344"/>
-      <c r="U23" s="345"/>
+      <c r="O23" s="400"/>
+      <c r="P23" s="401"/>
+      <c r="Q23" s="401"/>
+      <c r="R23" s="401"/>
+      <c r="S23" s="401"/>
+      <c r="T23" s="401"/>
+      <c r="U23" s="402"/>
       <c r="V23" s="61"/>
       <c r="Z23" s="42"/>
       <c r="AA23" s="227" t="s">
@@ -9292,7 +9304,7 @@
       <c r="BM23" s="245" t="s">
         <v>656</v>
       </c>
-      <c r="BN23" s="276" t="s">
+      <c r="BN23" s="349" t="s">
         <v>286</v>
       </c>
       <c r="BO23" s="224"/>
@@ -9300,23 +9312,23 @@
     <row r="24" spans="1:70" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="40"/>
       <c r="B24" s="40"/>
-      <c r="E24" s="301"/>
-      <c r="F24" s="302"/>
-      <c r="G24" s="303"/>
-      <c r="H24" s="285"/>
-      <c r="I24" s="286"/>
-      <c r="J24" s="285"/>
-      <c r="K24" s="286"/>
-      <c r="L24" s="287"/>
-      <c r="M24" s="287"/>
+      <c r="E24" s="404"/>
+      <c r="F24" s="381"/>
+      <c r="G24" s="382"/>
+      <c r="H24" s="343"/>
+      <c r="I24" s="345"/>
+      <c r="J24" s="343"/>
+      <c r="K24" s="345"/>
+      <c r="L24" s="344"/>
+      <c r="M24" s="344"/>
       <c r="N24" s="33"/>
-      <c r="O24" s="343"/>
-      <c r="P24" s="344"/>
-      <c r="Q24" s="344"/>
-      <c r="R24" s="344"/>
-      <c r="S24" s="344"/>
-      <c r="T24" s="344"/>
-      <c r="U24" s="345"/>
+      <c r="O24" s="400"/>
+      <c r="P24" s="401"/>
+      <c r="Q24" s="401"/>
+      <c r="R24" s="401"/>
+      <c r="S24" s="401"/>
+      <c r="T24" s="401"/>
+      <c r="U24" s="402"/>
       <c r="V24" s="61"/>
       <c r="Z24" s="42"/>
       <c r="AA24" s="227"/>
@@ -9386,31 +9398,31 @@
       <c r="BM24" s="244" t="s">
         <v>650</v>
       </c>
-      <c r="BN24" s="276"/>
+      <c r="BN24" s="349"/>
       <c r="BO24" s="224"/>
     </row>
     <row r="25" spans="1:70" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="40"/>
       <c r="B25" s="40"/>
-      <c r="E25" s="298" t="s">
+      <c r="E25" s="396" t="s">
         <v>27</v>
       </c>
-      <c r="F25" s="299"/>
-      <c r="G25" s="300"/>
-      <c r="H25" s="285"/>
-      <c r="I25" s="286"/>
-      <c r="J25" s="285"/>
-      <c r="K25" s="286"/>
-      <c r="L25" s="287"/>
-      <c r="M25" s="287"/>
+      <c r="F25" s="394"/>
+      <c r="G25" s="395"/>
+      <c r="H25" s="343"/>
+      <c r="I25" s="345"/>
+      <c r="J25" s="343"/>
+      <c r="K25" s="345"/>
+      <c r="L25" s="344"/>
+      <c r="M25" s="344"/>
       <c r="N25" s="33"/>
-      <c r="O25" s="343"/>
-      <c r="P25" s="344"/>
-      <c r="Q25" s="344"/>
-      <c r="R25" s="344"/>
-      <c r="S25" s="344"/>
-      <c r="T25" s="344"/>
-      <c r="U25" s="345"/>
+      <c r="O25" s="400"/>
+      <c r="P25" s="401"/>
+      <c r="Q25" s="401"/>
+      <c r="R25" s="401"/>
+      <c r="S25" s="401"/>
+      <c r="T25" s="401"/>
+      <c r="U25" s="402"/>
       <c r="V25" s="61"/>
       <c r="W25" s="38"/>
       <c r="X25" s="9"/>
@@ -9427,7 +9439,7 @@
       <c r="AG25" s="204"/>
       <c r="AH25" s="204"/>
       <c r="AI25" s="204"/>
-      <c r="AJ25" s="271" t="s">
+      <c r="AJ25" s="269" t="s">
         <v>517</v>
       </c>
       <c r="AK25" s="228" t="s">
@@ -9441,7 +9453,7 @@
       <c r="AQ25" s="204"/>
       <c r="AR25" s="204"/>
       <c r="AS25" s="204"/>
-      <c r="AT25" s="271" t="s">
+      <c r="AT25" s="269" t="s">
         <v>341</v>
       </c>
       <c r="AU25" s="228" t="s">
@@ -9457,7 +9469,7 @@
       <c r="BC25" s="236" t="s">
         <v>382</v>
       </c>
-      <c r="BD25" s="271" t="s">
+      <c r="BD25" s="269" t="s">
         <v>315</v>
       </c>
       <c r="BE25" s="222" t="s">
@@ -9473,7 +9485,7 @@
       <c r="BK25" s="204"/>
       <c r="BL25" s="204"/>
       <c r="BM25" s="204"/>
-      <c r="BN25" s="277" t="s">
+      <c r="BN25" s="405" t="s">
         <v>287</v>
       </c>
       <c r="BO25" s="224"/>
@@ -9481,23 +9493,23 @@
     <row r="26" spans="1:70" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="40"/>
       <c r="B26" s="40"/>
-      <c r="E26" s="298"/>
-      <c r="F26" s="299"/>
-      <c r="G26" s="300"/>
-      <c r="H26" s="285"/>
-      <c r="I26" s="286"/>
-      <c r="J26" s="285"/>
-      <c r="K26" s="286"/>
-      <c r="L26" s="287"/>
-      <c r="M26" s="287"/>
+      <c r="E26" s="396"/>
+      <c r="F26" s="394"/>
+      <c r="G26" s="395"/>
+      <c r="H26" s="343"/>
+      <c r="I26" s="345"/>
+      <c r="J26" s="343"/>
+      <c r="K26" s="345"/>
+      <c r="L26" s="344"/>
+      <c r="M26" s="344"/>
       <c r="N26" s="33"/>
-      <c r="O26" s="343"/>
-      <c r="P26" s="344"/>
-      <c r="Q26" s="344"/>
-      <c r="R26" s="344"/>
-      <c r="S26" s="344"/>
-      <c r="T26" s="344"/>
-      <c r="U26" s="345"/>
+      <c r="O26" s="400"/>
+      <c r="P26" s="401"/>
+      <c r="Q26" s="401"/>
+      <c r="R26" s="401"/>
+      <c r="S26" s="401"/>
+      <c r="T26" s="401"/>
+      <c r="U26" s="402"/>
       <c r="V26" s="62"/>
       <c r="W26" s="38"/>
       <c r="X26" s="9"/>
@@ -9512,7 +9524,7 @@
       <c r="AG26" s="203"/>
       <c r="AH26" s="203"/>
       <c r="AI26" s="203"/>
-      <c r="AJ26" s="271"/>
+      <c r="AJ26" s="269"/>
       <c r="AK26" s="228"/>
       <c r="AL26" s="203"/>
       <c r="AM26" s="203"/>
@@ -9524,7 +9536,7 @@
       <c r="AS26" s="211" t="s">
         <v>468</v>
       </c>
-      <c r="AT26" s="271"/>
+      <c r="AT26" s="269"/>
       <c r="AU26" s="228"/>
       <c r="AV26" s="243" t="s">
         <v>423</v>
@@ -9548,7 +9560,7 @@
       <c r="BC26" s="235" t="s">
         <v>117</v>
       </c>
-      <c r="BD26" s="271"/>
+      <c r="BD26" s="269"/>
       <c r="BE26" s="222"/>
       <c r="BF26" s="196" t="s">
         <v>65</v>
@@ -9572,29 +9584,29 @@
       <c r="BM26" s="244" t="s">
         <v>674</v>
       </c>
-      <c r="BN26" s="277"/>
+      <c r="BN26" s="405"/>
       <c r="BO26" s="224"/>
     </row>
     <row r="27" spans="1:70" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="40"/>
       <c r="B27" s="40"/>
-      <c r="E27" s="298"/>
-      <c r="F27" s="299"/>
-      <c r="G27" s="300"/>
-      <c r="H27" s="285"/>
-      <c r="I27" s="286"/>
-      <c r="J27" s="285"/>
-      <c r="K27" s="286"/>
-      <c r="L27" s="287"/>
-      <c r="M27" s="287"/>
+      <c r="E27" s="396"/>
+      <c r="F27" s="394"/>
+      <c r="G27" s="395"/>
+      <c r="H27" s="343"/>
+      <c r="I27" s="345"/>
+      <c r="J27" s="343"/>
+      <c r="K27" s="345"/>
+      <c r="L27" s="344"/>
+      <c r="M27" s="344"/>
       <c r="N27" s="33"/>
-      <c r="O27" s="343"/>
-      <c r="P27" s="344"/>
-      <c r="Q27" s="344"/>
-      <c r="R27" s="344"/>
-      <c r="S27" s="344"/>
-      <c r="T27" s="344"/>
-      <c r="U27" s="345"/>
+      <c r="O27" s="400"/>
+      <c r="P27" s="401"/>
+      <c r="Q27" s="401"/>
+      <c r="R27" s="401"/>
+      <c r="S27" s="401"/>
+      <c r="T27" s="401"/>
+      <c r="U27" s="402"/>
       <c r="V27" s="62"/>
       <c r="W27" s="38"/>
       <c r="X27" s="9"/>
@@ -9658,7 +9670,7 @@
       <c r="BM27" s="265" t="s">
         <v>69</v>
       </c>
-      <c r="BN27" s="276" t="s">
+      <c r="BN27" s="349" t="s">
         <v>288</v>
       </c>
       <c r="BO27" s="224"/>
@@ -9666,23 +9678,23 @@
     <row r="28" spans="1:70" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="9"/>
       <c r="B28" s="44"/>
-      <c r="E28" s="298"/>
-      <c r="F28" s="299"/>
-      <c r="G28" s="300"/>
-      <c r="H28" s="285"/>
-      <c r="I28" s="286"/>
-      <c r="J28" s="285"/>
-      <c r="K28" s="286"/>
-      <c r="L28" s="287"/>
-      <c r="M28" s="287"/>
+      <c r="E28" s="396"/>
+      <c r="F28" s="394"/>
+      <c r="G28" s="395"/>
+      <c r="H28" s="343"/>
+      <c r="I28" s="345"/>
+      <c r="J28" s="343"/>
+      <c r="K28" s="345"/>
+      <c r="L28" s="344"/>
+      <c r="M28" s="344"/>
       <c r="N28" s="33"/>
-      <c r="O28" s="343"/>
-      <c r="P28" s="344"/>
-      <c r="Q28" s="344"/>
-      <c r="R28" s="344"/>
-      <c r="S28" s="344"/>
-      <c r="T28" s="344"/>
-      <c r="U28" s="345"/>
+      <c r="O28" s="400"/>
+      <c r="P28" s="401"/>
+      <c r="Q28" s="401"/>
+      <c r="R28" s="401"/>
+      <c r="S28" s="401"/>
+      <c r="T28" s="401"/>
+      <c r="U28" s="402"/>
       <c r="V28" s="62"/>
       <c r="W28" s="37"/>
       <c r="X28" s="37"/>
@@ -9755,7 +9767,7 @@
       <c r="BM28" s="238" t="s">
         <v>70</v>
       </c>
-      <c r="BN28" s="276"/>
+      <c r="BN28" s="349"/>
       <c r="BO28" s="224"/>
       <c r="BR28" s="4" t="s">
         <v>11</v>
@@ -9764,23 +9776,23 @@
     <row r="29" spans="1:70" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="9"/>
       <c r="B29" s="44"/>
-      <c r="E29" s="298"/>
-      <c r="F29" s="299"/>
-      <c r="G29" s="300"/>
-      <c r="H29" s="285"/>
-      <c r="I29" s="286"/>
-      <c r="J29" s="285"/>
-      <c r="K29" s="286"/>
-      <c r="L29" s="287"/>
-      <c r="M29" s="287"/>
+      <c r="E29" s="396"/>
+      <c r="F29" s="394"/>
+      <c r="G29" s="395"/>
+      <c r="H29" s="343"/>
+      <c r="I29" s="345"/>
+      <c r="J29" s="343"/>
+      <c r="K29" s="345"/>
+      <c r="L29" s="344"/>
+      <c r="M29" s="344"/>
       <c r="N29" s="33"/>
-      <c r="O29" s="343"/>
-      <c r="P29" s="344"/>
-      <c r="Q29" s="344"/>
-      <c r="R29" s="344"/>
-      <c r="S29" s="344"/>
-      <c r="T29" s="344"/>
-      <c r="U29" s="345"/>
+      <c r="O29" s="400"/>
+      <c r="P29" s="401"/>
+      <c r="Q29" s="401"/>
+      <c r="R29" s="401"/>
+      <c r="S29" s="401"/>
+      <c r="T29" s="401"/>
+      <c r="U29" s="402"/>
       <c r="V29" s="44"/>
       <c r="W29" s="37"/>
       <c r="X29" s="37"/>
@@ -9814,30 +9826,30 @@
         <v>343</v>
       </c>
       <c r="AU29" s="229"/>
-      <c r="AV29" s="272" t="s">
+      <c r="AV29" s="426" t="s">
         <v>48</v>
       </c>
-      <c r="AW29" s="273"/>
-      <c r="AX29" s="273"/>
-      <c r="AY29" s="273"/>
-      <c r="AZ29" s="273"/>
-      <c r="BA29" s="273"/>
-      <c r="BB29" s="273"/>
-      <c r="BC29" s="274"/>
+      <c r="AW29" s="427"/>
+      <c r="AX29" s="427"/>
+      <c r="AY29" s="427"/>
+      <c r="AZ29" s="427"/>
+      <c r="BA29" s="427"/>
+      <c r="BB29" s="427"/>
+      <c r="BC29" s="428"/>
       <c r="BD29" s="208" t="s">
         <v>317</v>
       </c>
       <c r="BE29" s="223"/>
-      <c r="BF29" s="272" t="s">
+      <c r="BF29" s="426" t="s">
         <v>49</v>
       </c>
-      <c r="BG29" s="273"/>
-      <c r="BH29" s="273"/>
-      <c r="BI29" s="273"/>
-      <c r="BJ29" s="273"/>
-      <c r="BK29" s="273"/>
-      <c r="BL29" s="273"/>
-      <c r="BM29" s="274"/>
+      <c r="BG29" s="427"/>
+      <c r="BH29" s="427"/>
+      <c r="BI29" s="427"/>
+      <c r="BJ29" s="427"/>
+      <c r="BK29" s="427"/>
+      <c r="BL29" s="427"/>
+      <c r="BM29" s="428"/>
       <c r="BN29" s="219" t="s">
         <v>289</v>
       </c>
@@ -9846,23 +9858,23 @@
     <row r="30" spans="1:70" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="9"/>
       <c r="B30" s="44"/>
-      <c r="E30" s="301"/>
-      <c r="F30" s="302"/>
-      <c r="G30" s="303"/>
-      <c r="H30" s="285"/>
-      <c r="I30" s="286"/>
-      <c r="J30" s="285"/>
-      <c r="K30" s="286"/>
-      <c r="L30" s="287"/>
-      <c r="M30" s="287"/>
+      <c r="E30" s="404"/>
+      <c r="F30" s="381"/>
+      <c r="G30" s="382"/>
+      <c r="H30" s="343"/>
+      <c r="I30" s="345"/>
+      <c r="J30" s="343"/>
+      <c r="K30" s="345"/>
+      <c r="L30" s="344"/>
+      <c r="M30" s="344"/>
       <c r="N30" s="33"/>
-      <c r="O30" s="343"/>
-      <c r="P30" s="344"/>
-      <c r="Q30" s="344"/>
-      <c r="R30" s="344"/>
-      <c r="S30" s="344"/>
-      <c r="T30" s="344"/>
-      <c r="U30" s="345"/>
+      <c r="O30" s="400"/>
+      <c r="P30" s="401"/>
+      <c r="Q30" s="401"/>
+      <c r="R30" s="401"/>
+      <c r="S30" s="401"/>
+      <c r="T30" s="401"/>
+      <c r="U30" s="402"/>
       <c r="V30" s="44"/>
       <c r="W30" s="37"/>
       <c r="X30" s="37"/>
@@ -9917,7 +9929,9 @@
       <c r="BE30" s="221" t="s">
         <v>275</v>
       </c>
-      <c r="BF30" s="188"/>
+      <c r="BF30" s="197" t="s">
+        <v>77</v>
+      </c>
       <c r="BG30" s="188"/>
       <c r="BH30" s="188"/>
       <c r="BI30" s="188"/>
@@ -9927,7 +9941,7 @@
       <c r="BM30" s="245" t="s">
         <v>655</v>
       </c>
-      <c r="BN30" s="276" t="s">
+      <c r="BN30" s="349" t="s">
         <v>290</v>
       </c>
       <c r="BO30" s="224"/>
@@ -9935,25 +9949,25 @@
     <row r="31" spans="1:70" ht="279.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="9"/>
       <c r="B31" s="44"/>
-      <c r="E31" s="304" t="s">
+      <c r="E31" s="403" t="s">
         <v>28</v>
       </c>
-      <c r="F31" s="305"/>
-      <c r="G31" s="306"/>
-      <c r="H31" s="285"/>
-      <c r="I31" s="286"/>
-      <c r="J31" s="285"/>
-      <c r="K31" s="286"/>
-      <c r="L31" s="287"/>
-      <c r="M31" s="287"/>
+      <c r="F31" s="379"/>
+      <c r="G31" s="380"/>
+      <c r="H31" s="343"/>
+      <c r="I31" s="345"/>
+      <c r="J31" s="343"/>
+      <c r="K31" s="345"/>
+      <c r="L31" s="344"/>
+      <c r="M31" s="344"/>
       <c r="N31" s="67"/>
-      <c r="O31" s="343"/>
-      <c r="P31" s="344"/>
-      <c r="Q31" s="344"/>
-      <c r="R31" s="344"/>
-      <c r="S31" s="344"/>
-      <c r="T31" s="344"/>
-      <c r="U31" s="345"/>
+      <c r="O31" s="400"/>
+      <c r="P31" s="401"/>
+      <c r="Q31" s="401"/>
+      <c r="R31" s="401"/>
+      <c r="S31" s="401"/>
+      <c r="T31" s="401"/>
+      <c r="U31" s="402"/>
       <c r="V31" s="44"/>
       <c r="W31" s="37"/>
       <c r="X31" s="37"/>
@@ -10026,29 +10040,29 @@
       <c r="BM31" s="244" t="s">
         <v>672</v>
       </c>
-      <c r="BN31" s="276"/>
+      <c r="BN31" s="349"/>
       <c r="BO31" s="224"/>
     </row>
     <row r="32" spans="1:70" ht="279.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A32" s="9"/>
       <c r="B32" s="44"/>
-      <c r="E32" s="298"/>
-      <c r="F32" s="299"/>
-      <c r="G32" s="300"/>
-      <c r="H32" s="285"/>
-      <c r="I32" s="286"/>
-      <c r="J32" s="285"/>
-      <c r="K32" s="286"/>
-      <c r="L32" s="287"/>
-      <c r="M32" s="287"/>
+      <c r="E32" s="396"/>
+      <c r="F32" s="394"/>
+      <c r="G32" s="395"/>
+      <c r="H32" s="343"/>
+      <c r="I32" s="345"/>
+      <c r="J32" s="343"/>
+      <c r="K32" s="345"/>
+      <c r="L32" s="344"/>
+      <c r="M32" s="344"/>
       <c r="N32" s="33"/>
-      <c r="O32" s="343"/>
-      <c r="P32" s="344"/>
-      <c r="Q32" s="344"/>
-      <c r="R32" s="344"/>
-      <c r="S32" s="344"/>
-      <c r="T32" s="344"/>
-      <c r="U32" s="345"/>
+      <c r="O32" s="400"/>
+      <c r="P32" s="401"/>
+      <c r="Q32" s="401"/>
+      <c r="R32" s="401"/>
+      <c r="S32" s="401"/>
+      <c r="T32" s="401"/>
+      <c r="U32" s="402"/>
       <c r="W32" s="37"/>
       <c r="X32" s="37"/>
       <c r="Y32" s="66"/>
@@ -10064,7 +10078,7 @@
       <c r="AG32" s="204"/>
       <c r="AH32" s="204"/>
       <c r="AI32" s="204"/>
-      <c r="AJ32" s="271" t="s">
+      <c r="AJ32" s="269" t="s">
         <v>529</v>
       </c>
       <c r="AK32" s="228" t="s">
@@ -10078,7 +10092,7 @@
       <c r="AQ32" s="204"/>
       <c r="AR32" s="204"/>
       <c r="AS32" s="204"/>
-      <c r="AT32" s="271" t="s">
+      <c r="AT32" s="269" t="s">
         <v>345</v>
       </c>
       <c r="AU32" s="228" t="s">
@@ -10104,7 +10118,7 @@
       <c r="BC32" s="210" t="s">
         <v>435</v>
       </c>
-      <c r="BD32" s="271" t="s">
+      <c r="BD32" s="269" t="s">
         <v>319</v>
       </c>
       <c r="BE32" s="222" t="s">
@@ -10120,7 +10134,7 @@
       <c r="BK32" s="204"/>
       <c r="BL32" s="204"/>
       <c r="BM32" s="204"/>
-      <c r="BN32" s="277" t="s">
+      <c r="BN32" s="405" t="s">
         <v>291</v>
       </c>
       <c r="BO32" s="224"/>
@@ -10128,23 +10142,23 @@
     <row r="33" spans="1:67" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="9"/>
       <c r="B33" s="44"/>
-      <c r="E33" s="301"/>
-      <c r="F33" s="302"/>
-      <c r="G33" s="303"/>
-      <c r="H33" s="285"/>
-      <c r="I33" s="286"/>
-      <c r="J33" s="285"/>
-      <c r="K33" s="286"/>
-      <c r="L33" s="287"/>
-      <c r="M33" s="287"/>
+      <c r="E33" s="404"/>
+      <c r="F33" s="381"/>
+      <c r="G33" s="382"/>
+      <c r="H33" s="343"/>
+      <c r="I33" s="345"/>
+      <c r="J33" s="343"/>
+      <c r="K33" s="345"/>
+      <c r="L33" s="344"/>
+      <c r="M33" s="344"/>
       <c r="N33" s="33"/>
-      <c r="O33" s="343"/>
-      <c r="P33" s="344"/>
-      <c r="Q33" s="344"/>
-      <c r="R33" s="344"/>
-      <c r="S33" s="344"/>
-      <c r="T33" s="344"/>
-      <c r="U33" s="345"/>
+      <c r="O33" s="400"/>
+      <c r="P33" s="401"/>
+      <c r="Q33" s="401"/>
+      <c r="R33" s="401"/>
+      <c r="S33" s="401"/>
+      <c r="T33" s="401"/>
+      <c r="U33" s="402"/>
       <c r="W33" s="37"/>
       <c r="X33" s="37"/>
       <c r="Z33" s="69"/>
@@ -10157,7 +10171,7 @@
       <c r="AG33" s="203"/>
       <c r="AH33" s="203"/>
       <c r="AI33" s="203"/>
-      <c r="AJ33" s="271"/>
+      <c r="AJ33" s="269"/>
       <c r="AK33" s="228"/>
       <c r="AL33" s="209" t="s">
         <v>469</v>
@@ -10181,7 +10195,7 @@
       <c r="AS33" s="237" t="s">
         <v>433</v>
       </c>
-      <c r="AT33" s="271"/>
+      <c r="AT33" s="269"/>
       <c r="AU33" s="228"/>
       <c r="AV33" s="235" t="s">
         <v>440</v>
@@ -10203,7 +10217,7 @@
       <c r="BC33" s="211" t="s">
         <v>211</v>
       </c>
-      <c r="BD33" s="271"/>
+      <c r="BD33" s="269"/>
       <c r="BE33" s="222"/>
       <c r="BF33" s="196" t="s">
         <v>547</v>
@@ -10225,31 +10239,31 @@
       <c r="BM33" s="243" t="s">
         <v>625</v>
       </c>
-      <c r="BN33" s="277"/>
+      <c r="BN33" s="405"/>
       <c r="BO33" s="224"/>
     </row>
     <row r="34" spans="1:67" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="9"/>
       <c r="B34" s="44"/>
-      <c r="E34" s="304" t="s">
+      <c r="E34" s="403" t="s">
         <v>29</v>
       </c>
-      <c r="F34" s="305"/>
-      <c r="G34" s="306"/>
-      <c r="H34" s="285"/>
-      <c r="I34" s="286"/>
-      <c r="J34" s="285"/>
-      <c r="K34" s="286"/>
-      <c r="L34" s="287"/>
-      <c r="M34" s="287"/>
+      <c r="F34" s="379"/>
+      <c r="G34" s="380"/>
+      <c r="H34" s="343"/>
+      <c r="I34" s="345"/>
+      <c r="J34" s="343"/>
+      <c r="K34" s="345"/>
+      <c r="L34" s="344"/>
+      <c r="M34" s="344"/>
       <c r="N34" s="33"/>
-      <c r="O34" s="343"/>
-      <c r="P34" s="344"/>
-      <c r="Q34" s="344"/>
-      <c r="R34" s="344"/>
-      <c r="S34" s="344"/>
-      <c r="T34" s="344"/>
-      <c r="U34" s="345"/>
+      <c r="O34" s="400"/>
+      <c r="P34" s="401"/>
+      <c r="Q34" s="401"/>
+      <c r="R34" s="401"/>
+      <c r="S34" s="401"/>
+      <c r="T34" s="401"/>
+      <c r="U34" s="402"/>
       <c r="V34" s="41"/>
       <c r="W34" s="37"/>
       <c r="X34" s="37"/>
@@ -10325,7 +10339,7 @@
       <c r="BM34" s="210" t="s">
         <v>563</v>
       </c>
-      <c r="BN34" s="276" t="s">
+      <c r="BN34" s="349" t="s">
         <v>292</v>
       </c>
       <c r="BO34" s="224"/>
@@ -10335,23 +10349,23 @@
       <c r="B35" s="44"/>
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
-      <c r="E35" s="301"/>
-      <c r="F35" s="302"/>
-      <c r="G35" s="303"/>
-      <c r="H35" s="285"/>
-      <c r="I35" s="286"/>
-      <c r="J35" s="285"/>
-      <c r="K35" s="286"/>
-      <c r="L35" s="287"/>
-      <c r="M35" s="287"/>
+      <c r="E35" s="404"/>
+      <c r="F35" s="381"/>
+      <c r="G35" s="382"/>
+      <c r="H35" s="343"/>
+      <c r="I35" s="345"/>
+      <c r="J35" s="343"/>
+      <c r="K35" s="345"/>
+      <c r="L35" s="344"/>
+      <c r="M35" s="344"/>
       <c r="N35" s="33"/>
-      <c r="O35" s="343"/>
-      <c r="P35" s="344"/>
-      <c r="Q35" s="344"/>
-      <c r="R35" s="344"/>
-      <c r="S35" s="344"/>
-      <c r="T35" s="344"/>
-      <c r="U35" s="345"/>
+      <c r="O35" s="400"/>
+      <c r="P35" s="401"/>
+      <c r="Q35" s="401"/>
+      <c r="R35" s="401"/>
+      <c r="S35" s="401"/>
+      <c r="T35" s="401"/>
+      <c r="U35" s="402"/>
       <c r="V35" s="70"/>
       <c r="W35" s="37"/>
       <c r="X35" s="37"/>
@@ -10434,7 +10448,7 @@
       <c r="BM35" s="243" t="s">
         <v>565</v>
       </c>
-      <c r="BN35" s="276"/>
+      <c r="BN35" s="349"/>
       <c r="BO35" s="225"/>
     </row>
     <row r="36" spans="1:67" s="73" customFormat="1" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10442,25 +10456,25 @@
       <c r="B36" s="40"/>
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
-      <c r="E36" s="301" t="s">
+      <c r="E36" s="404" t="s">
         <v>30</v>
       </c>
-      <c r="F36" s="302"/>
-      <c r="G36" s="303"/>
-      <c r="H36" s="288"/>
-      <c r="I36" s="289"/>
-      <c r="J36" s="288"/>
-      <c r="K36" s="289"/>
-      <c r="L36" s="291"/>
-      <c r="M36" s="291"/>
+      <c r="F36" s="381"/>
+      <c r="G36" s="382"/>
+      <c r="H36" s="346"/>
+      <c r="I36" s="348"/>
+      <c r="J36" s="346"/>
+      <c r="K36" s="348"/>
+      <c r="L36" s="347"/>
+      <c r="M36" s="347"/>
       <c r="N36" s="33"/>
-      <c r="O36" s="343"/>
-      <c r="P36" s="344"/>
-      <c r="Q36" s="344"/>
-      <c r="R36" s="344"/>
-      <c r="S36" s="344"/>
-      <c r="T36" s="344"/>
-      <c r="U36" s="345"/>
+      <c r="O36" s="400"/>
+      <c r="P36" s="401"/>
+      <c r="Q36" s="401"/>
+      <c r="R36" s="401"/>
+      <c r="S36" s="401"/>
+      <c r="T36" s="401"/>
+      <c r="U36" s="402"/>
       <c r="V36" s="9"/>
       <c r="W36" s="4"/>
       <c r="X36" s="71"/>
@@ -10477,7 +10491,7 @@
       <c r="AG36" s="204"/>
       <c r="AH36" s="204"/>
       <c r="AI36" s="204"/>
-      <c r="AJ36" s="271" t="s">
+      <c r="AJ36" s="269" t="s">
         <v>531</v>
       </c>
       <c r="AK36" s="228" t="s">
@@ -10491,7 +10505,7 @@
       <c r="AQ36" s="204"/>
       <c r="AR36" s="204"/>
       <c r="AS36" s="204"/>
-      <c r="AT36" s="271" t="s">
+      <c r="AT36" s="269" t="s">
         <v>347</v>
       </c>
       <c r="AU36" s="228" t="s">
@@ -10515,7 +10529,7 @@
       <c r="BC36" s="210" t="s">
         <v>147</v>
       </c>
-      <c r="BD36" s="271" t="s">
+      <c r="BD36" s="269" t="s">
         <v>321</v>
       </c>
       <c r="BE36" s="222" t="s">
@@ -10531,7 +10545,7 @@
       <c r="BK36" s="204"/>
       <c r="BL36" s="204"/>
       <c r="BM36" s="204"/>
-      <c r="BN36" s="277" t="s">
+      <c r="BN36" s="405" t="s">
         <v>293</v>
       </c>
       <c r="BO36" s="225"/>
@@ -10539,27 +10553,27 @@
     <row r="37" spans="1:67" s="73" customFormat="1" ht="279.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="9"/>
       <c r="B37" s="40"/>
-      <c r="E37" s="346" t="s">
+      <c r="E37" s="356" t="s">
         <v>31</v>
       </c>
-      <c r="F37" s="346"/>
-      <c r="G37" s="346"/>
-      <c r="H37" s="346"/>
-      <c r="I37" s="346"/>
-      <c r="J37" s="346"/>
-      <c r="K37" s="346"/>
-      <c r="L37" s="346"/>
-      <c r="M37" s="346"/>
+      <c r="F37" s="356"/>
+      <c r="G37" s="356"/>
+      <c r="H37" s="356"/>
+      <c r="I37" s="356"/>
+      <c r="J37" s="356"/>
+      <c r="K37" s="356"/>
+      <c r="L37" s="356"/>
+      <c r="M37" s="356"/>
       <c r="N37" s="74"/>
-      <c r="O37" s="347" t="s">
+      <c r="O37" s="357" t="s">
         <v>31</v>
       </c>
-      <c r="P37" s="348"/>
-      <c r="Q37" s="348"/>
-      <c r="R37" s="348"/>
-      <c r="S37" s="348"/>
-      <c r="T37" s="348"/>
-      <c r="U37" s="348"/>
+      <c r="P37" s="358"/>
+      <c r="Q37" s="358"/>
+      <c r="R37" s="358"/>
+      <c r="S37" s="358"/>
+      <c r="T37" s="358"/>
+      <c r="U37" s="358"/>
       <c r="V37" s="75"/>
       <c r="W37" s="76"/>
       <c r="X37" s="76"/>
@@ -10574,7 +10588,7 @@
       <c r="AG37" s="203"/>
       <c r="AH37" s="203"/>
       <c r="AI37" s="203"/>
-      <c r="AJ37" s="271"/>
+      <c r="AJ37" s="269"/>
       <c r="AK37" s="228"/>
       <c r="AL37" s="209" t="s">
         <v>481</v>
@@ -10598,7 +10612,7 @@
       <c r="AS37" s="209" t="s">
         <v>487</v>
       </c>
-      <c r="AT37" s="271"/>
+      <c r="AT37" s="269"/>
       <c r="AU37" s="228"/>
       <c r="AV37" s="244" t="s">
         <v>670</v>
@@ -10622,14 +10636,12 @@
       <c r="BC37" s="211" t="s">
         <v>133</v>
       </c>
-      <c r="BD37" s="271"/>
+      <c r="BD37" s="269"/>
       <c r="BE37" s="222"/>
       <c r="BF37" s="211" t="s">
         <v>449</v>
       </c>
-      <c r="BG37" s="196" t="s">
-        <v>77</v>
-      </c>
+      <c r="BG37" s="203"/>
       <c r="BH37" s="203"/>
       <c r="BI37" s="243" t="s">
         <v>604</v>
@@ -10640,7 +10652,7 @@
       <c r="BK37" s="203"/>
       <c r="BL37" s="203"/>
       <c r="BM37" s="250"/>
-      <c r="BN37" s="277"/>
+      <c r="BN37" s="405"/>
       <c r="BO37" s="225"/>
     </row>
     <row r="38" spans="1:67" s="73" customFormat="1" ht="279.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
@@ -10663,7 +10675,7 @@
       </c>
       <c r="M38" s="25"/>
       <c r="N38" s="81"/>
-      <c r="O38" s="349"/>
+      <c r="O38" s="359"/>
       <c r="P38" s="14"/>
       <c r="Q38" s="14"/>
       <c r="R38" s="14"/>
@@ -10736,7 +10748,7 @@
       <c r="BM38" s="246" t="s">
         <v>378</v>
       </c>
-      <c r="BN38" s="276" t="s">
+      <c r="BN38" s="349" t="s">
         <v>294</v>
       </c>
       <c r="BO38" s="225"/>
@@ -10755,7 +10767,7 @@
       <c r="L39" s="31"/>
       <c r="M39" s="31"/>
       <c r="N39" s="81"/>
-      <c r="O39" s="350"/>
+      <c r="O39" s="271"/>
       <c r="P39" s="14"/>
       <c r="Q39" s="14"/>
       <c r="R39" s="14"/>
@@ -10842,7 +10854,7 @@
       <c r="BM39" s="235" t="s">
         <v>265</v>
       </c>
-      <c r="BN39" s="276"/>
+      <c r="BN39" s="349"/>
       <c r="BO39" s="225"/>
     </row>
     <row r="40" spans="1:67" s="73" customFormat="1" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10880,7 +10892,7 @@
       <c r="AG40" s="204"/>
       <c r="AH40" s="204"/>
       <c r="AI40" s="204"/>
-      <c r="AJ40" s="271" t="s">
+      <c r="AJ40" s="269" t="s">
         <v>533</v>
       </c>
       <c r="AK40" s="228" t="s">
@@ -10894,7 +10906,7 @@
       <c r="AQ40" s="204"/>
       <c r="AR40" s="204"/>
       <c r="AS40" s="204"/>
-      <c r="AT40" s="271" t="s">
+      <c r="AT40" s="269" t="s">
         <v>349</v>
       </c>
       <c r="AU40" s="228" t="s">
@@ -10910,7 +10922,7 @@
       </c>
       <c r="BB40" s="204"/>
       <c r="BC40" s="204"/>
-      <c r="BD40" s="271" t="s">
+      <c r="BD40" s="269" t="s">
         <v>323</v>
       </c>
       <c r="BE40" s="222" t="s">
@@ -10932,7 +10944,7 @@
       <c r="BM40" s="197" t="s">
         <v>222</v>
       </c>
-      <c r="BN40" s="277" t="s">
+      <c r="BN40" s="405" t="s">
         <v>295</v>
       </c>
       <c r="BO40" s="225"/>
@@ -10969,7 +10981,7 @@
       <c r="AG41" s="203"/>
       <c r="AH41" s="203"/>
       <c r="AI41" s="203"/>
-      <c r="AJ41" s="271"/>
+      <c r="AJ41" s="269"/>
       <c r="AK41" s="228"/>
       <c r="AL41" s="237" t="s">
         <v>493</v>
@@ -10991,7 +11003,7 @@
         <v>578</v>
       </c>
       <c r="AS41" s="203"/>
-      <c r="AT41" s="271"/>
+      <c r="AT41" s="269"/>
       <c r="AU41" s="228"/>
       <c r="AV41" s="203"/>
       <c r="AW41" s="203"/>
@@ -11011,7 +11023,7 @@
       <c r="BC41" s="235" t="s">
         <v>426</v>
       </c>
-      <c r="BD41" s="271"/>
+      <c r="BD41" s="269"/>
       <c r="BE41" s="222"/>
       <c r="BF41" s="211" t="s">
         <v>454</v>
@@ -11035,7 +11047,7 @@
       <c r="BM41" s="196" t="s">
         <v>263</v>
       </c>
-      <c r="BN41" s="277"/>
+      <c r="BN41" s="405"/>
       <c r="BO41" s="225"/>
     </row>
     <row r="42" spans="1:67" s="73" customFormat="1" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -11051,8 +11063,8 @@
       <c r="L42" s="31"/>
       <c r="M42" s="31"/>
       <c r="N42" s="81"/>
-      <c r="O42" s="358"/>
-      <c r="P42" s="350"/>
+      <c r="O42" s="355"/>
+      <c r="P42" s="271"/>
       <c r="Q42" s="89"/>
       <c r="R42" s="89"/>
       <c r="S42" s="89"/>
@@ -11120,7 +11132,7 @@
       <c r="BM42" s="197" t="s">
         <v>90</v>
       </c>
-      <c r="BN42" s="276" t="s">
+      <c r="BN42" s="349" t="s">
         <v>296</v>
       </c>
       <c r="BO42" s="225"/>
@@ -11138,8 +11150,8 @@
       <c r="L43" s="31"/>
       <c r="M43" s="31"/>
       <c r="N43" s="81"/>
-      <c r="O43" s="358"/>
-      <c r="P43" s="350"/>
+      <c r="O43" s="355"/>
+      <c r="P43" s="271"/>
       <c r="Q43" s="89"/>
       <c r="R43" s="89"/>
       <c r="S43" s="89"/>
@@ -11186,7 +11198,9 @@
       <c r="AV43" s="211" t="s">
         <v>141</v>
       </c>
-      <c r="AW43" s="189"/>
+      <c r="AW43" s="244" t="s">
+        <v>683</v>
+      </c>
       <c r="AX43" s="189"/>
       <c r="AY43" s="243" t="s">
         <v>669</v>
@@ -11227,17 +11241,17 @@
       <c r="BM43" s="196" t="s">
         <v>82</v>
       </c>
-      <c r="BN43" s="276"/>
+      <c r="BN43" s="349"/>
       <c r="BO43" s="225"/>
     </row>
     <row r="44" spans="1:67" s="73" customFormat="1" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="78"/>
       <c r="B44" s="78"/>
-      <c r="E44" s="351" t="s">
+      <c r="E44" s="360" t="s">
         <v>35</v>
       </c>
-      <c r="F44" s="352"/>
-      <c r="G44" s="355" t="s">
+      <c r="F44" s="361"/>
+      <c r="G44" s="364" t="s">
         <v>36</v>
       </c>
       <c r="H44" s="31"/>
@@ -11247,8 +11261,8 @@
       <c r="L44" s="31"/>
       <c r="M44" s="31"/>
       <c r="N44" s="81"/>
-      <c r="O44" s="358"/>
-      <c r="P44" s="350"/>
+      <c r="O44" s="355"/>
+      <c r="P44" s="271"/>
       <c r="Q44" s="89"/>
       <c r="R44" s="89"/>
       <c r="S44" s="89"/>
@@ -11269,7 +11283,7 @@
       <c r="AG44" s="204"/>
       <c r="AH44" s="204"/>
       <c r="AI44" s="204"/>
-      <c r="AJ44" s="271" t="s">
+      <c r="AJ44" s="269" t="s">
         <v>535</v>
       </c>
       <c r="AK44" s="228" t="s">
@@ -11283,7 +11297,7 @@
       <c r="AQ44" s="204"/>
       <c r="AR44" s="204"/>
       <c r="AS44" s="204"/>
-      <c r="AT44" s="271" t="s">
+      <c r="AT44" s="269" t="s">
         <v>351</v>
       </c>
       <c r="AU44" s="228" t="s">
@@ -11299,7 +11313,7 @@
       <c r="BA44" s="204"/>
       <c r="BB44" s="204"/>
       <c r="BC44" s="204"/>
-      <c r="BD44" s="271" t="s">
+      <c r="BD44" s="269" t="s">
         <v>325</v>
       </c>
       <c r="BE44" s="222" t="s">
@@ -11321,7 +11335,7 @@
       <c r="BM44" s="197" t="s">
         <v>390</v>
       </c>
-      <c r="BN44" s="277" t="s">
+      <c r="BN44" s="405" t="s">
         <v>297</v>
       </c>
       <c r="BO44" s="225"/>
@@ -11329,9 +11343,9 @@
     <row r="45" spans="1:67" s="73" customFormat="1" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="78"/>
       <c r="B45" s="78"/>
-      <c r="E45" s="353"/>
-      <c r="F45" s="354"/>
-      <c r="G45" s="356"/>
+      <c r="E45" s="362"/>
+      <c r="F45" s="363"/>
+      <c r="G45" s="365"/>
       <c r="H45" s="31"/>
       <c r="I45" s="31"/>
       <c r="J45" s="30"/>
@@ -11358,7 +11372,7 @@
       <c r="AG45" s="203"/>
       <c r="AH45" s="203"/>
       <c r="AI45" s="203"/>
-      <c r="AJ45" s="271"/>
+      <c r="AJ45" s="269"/>
       <c r="AK45" s="228"/>
       <c r="AL45" s="237" t="s">
         <v>572</v>
@@ -11380,7 +11394,7 @@
         <v>502</v>
       </c>
       <c r="AS45" s="203"/>
-      <c r="AT45" s="271"/>
+      <c r="AT45" s="269"/>
       <c r="AU45" s="228"/>
       <c r="AV45" s="211" t="s">
         <v>567</v>
@@ -11404,7 +11418,7 @@
       <c r="BC45" s="243" t="s">
         <v>668</v>
       </c>
-      <c r="BD45" s="271"/>
+      <c r="BD45" s="269"/>
       <c r="BE45" s="222"/>
       <c r="BF45" s="243" t="s">
         <v>465</v>
@@ -11426,7 +11440,7 @@
       <c r="BM45" s="196" t="s">
         <v>389</v>
       </c>
-      <c r="BN45" s="277"/>
+      <c r="BN45" s="405"/>
       <c r="BO45" s="225"/>
     </row>
     <row r="46" spans="1:67" s="73" customFormat="1" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -11510,7 +11524,7 @@
       <c r="BK46" s="188"/>
       <c r="BL46" s="188"/>
       <c r="BM46" s="188"/>
-      <c r="BN46" s="276" t="s">
+      <c r="BN46" s="349" t="s">
         <v>298</v>
       </c>
       <c r="BO46" s="225"/>
@@ -11609,7 +11623,7 @@
       <c r="BM47" s="238" t="s">
         <v>260</v>
       </c>
-      <c r="BN47" s="276"/>
+      <c r="BN47" s="349"/>
       <c r="BO47" s="224"/>
     </row>
     <row r="48" spans="1:67" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -11627,15 +11641,15 @@
       <c r="L48" s="31"/>
       <c r="M48" s="31"/>
       <c r="N48" s="81"/>
-      <c r="O48" s="363" t="s">
+      <c r="O48" s="302" t="s">
         <v>37</v>
       </c>
-      <c r="P48" s="363"/>
-      <c r="Q48" s="363"/>
-      <c r="R48" s="363"/>
-      <c r="S48" s="363"/>
-      <c r="T48" s="363"/>
-      <c r="U48" s="364"/>
+      <c r="P48" s="302"/>
+      <c r="Q48" s="302"/>
+      <c r="R48" s="302"/>
+      <c r="S48" s="302"/>
+      <c r="T48" s="302"/>
+      <c r="U48" s="303"/>
       <c r="V48" s="36"/>
       <c r="W48" s="51"/>
       <c r="X48" s="14"/>
@@ -11652,7 +11666,7 @@
       <c r="AG48" s="204"/>
       <c r="AH48" s="204"/>
       <c r="AI48" s="204"/>
-      <c r="AJ48" s="271" t="s">
+      <c r="AJ48" s="269" t="s">
         <v>537</v>
       </c>
       <c r="AK48" s="228" t="s">
@@ -11666,7 +11680,7 @@
       <c r="AQ48" s="204"/>
       <c r="AR48" s="204"/>
       <c r="AS48" s="204"/>
-      <c r="AT48" s="271" t="s">
+      <c r="AT48" s="269" t="s">
         <v>353</v>
       </c>
       <c r="AU48" s="228" t="s">
@@ -11686,7 +11700,7 @@
         <v>234</v>
       </c>
       <c r="BC48" s="204"/>
-      <c r="BD48" s="271" t="s">
+      <c r="BD48" s="269" t="s">
         <v>327</v>
       </c>
       <c r="BE48" s="222" t="s">
@@ -11704,7 +11718,7 @@
       <c r="BM48" s="197" t="s">
         <v>387</v>
       </c>
-      <c r="BN48" s="277" t="s">
+      <c r="BN48" s="405" t="s">
         <v>299</v>
       </c>
       <c r="BO48" s="224"/>
@@ -11722,13 +11736,13 @@
       <c r="L49" s="31"/>
       <c r="M49" s="31"/>
       <c r="N49" s="33"/>
-      <c r="O49" s="365"/>
-      <c r="P49" s="365"/>
-      <c r="Q49" s="365"/>
-      <c r="R49" s="365"/>
-      <c r="S49" s="365"/>
-      <c r="T49" s="365"/>
-      <c r="U49" s="366"/>
+      <c r="O49" s="305"/>
+      <c r="P49" s="305"/>
+      <c r="Q49" s="305"/>
+      <c r="R49" s="305"/>
+      <c r="S49" s="305"/>
+      <c r="T49" s="305"/>
+      <c r="U49" s="306"/>
       <c r="V49" s="36"/>
       <c r="W49" s="14"/>
       <c r="X49" s="14"/>
@@ -11743,7 +11757,7 @@
       <c r="AG49" s="203"/>
       <c r="AH49" s="203"/>
       <c r="AI49" s="203"/>
-      <c r="AJ49" s="271"/>
+      <c r="AJ49" s="269"/>
       <c r="AK49" s="228"/>
       <c r="AL49" s="203"/>
       <c r="AM49" s="237" t="s">
@@ -11755,7 +11769,7 @@
       <c r="AQ49" s="203"/>
       <c r="AR49" s="203"/>
       <c r="AS49" s="203"/>
-      <c r="AT49" s="271"/>
+      <c r="AT49" s="269"/>
       <c r="AU49" s="228"/>
       <c r="AV49" s="196" t="s">
         <v>505</v>
@@ -11764,7 +11778,9 @@
         <v>139</v>
       </c>
       <c r="AX49" s="203"/>
-      <c r="AY49" s="203"/>
+      <c r="AY49" s="244" t="s">
+        <v>684</v>
+      </c>
       <c r="AZ49" s="196" t="s">
         <v>237</v>
       </c>
@@ -11777,7 +11793,7 @@
       <c r="BC49" s="196" t="s">
         <v>239</v>
       </c>
-      <c r="BD49" s="271"/>
+      <c r="BD49" s="269"/>
       <c r="BE49" s="222"/>
       <c r="BF49" s="243" t="s">
         <v>638</v>
@@ -11799,17 +11815,17 @@
       <c r="BM49" s="238" t="s">
         <v>259</v>
       </c>
-      <c r="BN49" s="277"/>
+      <c r="BN49" s="405"/>
       <c r="BO49" s="224"/>
     </row>
     <row r="50" spans="1:77" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="79"/>
       <c r="B50" s="79"/>
-      <c r="E50" s="285" t="s">
+      <c r="E50" s="343" t="s">
         <v>38</v>
       </c>
-      <c r="F50" s="287"/>
-      <c r="G50" s="286"/>
+      <c r="F50" s="344"/>
+      <c r="G50" s="345"/>
       <c r="H50" s="31"/>
       <c r="I50" s="31"/>
       <c r="J50" s="30"/>
@@ -11817,13 +11833,13 @@
       <c r="L50" s="31"/>
       <c r="M50" s="31"/>
       <c r="N50" s="33"/>
-      <c r="O50" s="365"/>
-      <c r="P50" s="365"/>
-      <c r="Q50" s="365"/>
-      <c r="R50" s="365"/>
-      <c r="S50" s="365"/>
-      <c r="T50" s="365"/>
-      <c r="U50" s="366"/>
+      <c r="O50" s="305"/>
+      <c r="P50" s="305"/>
+      <c r="Q50" s="305"/>
+      <c r="R50" s="305"/>
+      <c r="S50" s="305"/>
+      <c r="T50" s="305"/>
+      <c r="U50" s="306"/>
       <c r="V50" s="36"/>
       <c r="W50" s="14"/>
       <c r="X50" s="14"/>
@@ -11900,7 +11916,7 @@
         <v>91</v>
       </c>
       <c r="BM50" s="188"/>
-      <c r="BN50" s="276" t="s">
+      <c r="BN50" s="349" t="s">
         <v>300</v>
       </c>
       <c r="BO50" s="224"/>
@@ -11908,9 +11924,9 @@
     <row r="51" spans="1:77" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="79"/>
       <c r="B51" s="79"/>
-      <c r="E51" s="285"/>
-      <c r="F51" s="287"/>
-      <c r="G51" s="286"/>
+      <c r="E51" s="343"/>
+      <c r="F51" s="344"/>
+      <c r="G51" s="345"/>
       <c r="H51" s="31"/>
       <c r="I51" s="31"/>
       <c r="J51" s="30"/>
@@ -11918,13 +11934,13 @@
       <c r="L51" s="31"/>
       <c r="M51" s="31"/>
       <c r="N51" s="33"/>
-      <c r="O51" s="365"/>
-      <c r="P51" s="365"/>
-      <c r="Q51" s="365"/>
-      <c r="R51" s="365"/>
-      <c r="S51" s="365"/>
-      <c r="T51" s="365"/>
-      <c r="U51" s="366"/>
+      <c r="O51" s="305"/>
+      <c r="P51" s="305"/>
+      <c r="Q51" s="305"/>
+      <c r="R51" s="305"/>
+      <c r="S51" s="305"/>
+      <c r="T51" s="305"/>
+      <c r="U51" s="306"/>
       <c r="V51" s="95"/>
       <c r="W51" s="14"/>
       <c r="X51" s="14"/>
@@ -12015,15 +12031,15 @@
       <c r="BM51" s="196" t="s">
         <v>258</v>
       </c>
-      <c r="BN51" s="276"/>
+      <c r="BN51" s="349"/>
       <c r="BO51" s="224"/>
     </row>
     <row r="52" spans="1:77" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="79"/>
       <c r="B52" s="79"/>
-      <c r="E52" s="285"/>
-      <c r="F52" s="287"/>
-      <c r="G52" s="286"/>
+      <c r="E52" s="343"/>
+      <c r="F52" s="344"/>
+      <c r="G52" s="345"/>
       <c r="H52" s="31"/>
       <c r="I52" s="31"/>
       <c r="J52" s="30"/>
@@ -12031,13 +12047,13 @@
       <c r="L52" s="31"/>
       <c r="M52" s="31"/>
       <c r="N52" s="33"/>
-      <c r="O52" s="365"/>
-      <c r="P52" s="365"/>
-      <c r="Q52" s="365"/>
-      <c r="R52" s="365"/>
-      <c r="S52" s="365"/>
-      <c r="T52" s="365"/>
-      <c r="U52" s="366"/>
+      <c r="O52" s="305"/>
+      <c r="P52" s="305"/>
+      <c r="Q52" s="305"/>
+      <c r="R52" s="305"/>
+      <c r="S52" s="305"/>
+      <c r="T52" s="305"/>
+      <c r="U52" s="306"/>
       <c r="V52" s="36"/>
       <c r="W52" s="14"/>
       <c r="X52" s="14"/>
@@ -12057,7 +12073,7 @@
       </c>
       <c r="AD52" s="195">
         <f>COUNTA(AV30:BC53,AV3:BC28)</f>
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AE52" s="195">
         <f>COUNTA(BF30:BM57,BF3:BM28)</f>
@@ -12065,7 +12081,7 @@
       </c>
       <c r="AF52" s="242">
         <f>SUM(AA52:AE52)+AJ52</f>
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AG52" s="255">
         <f>COUNTIF( $AV$3:$BC$53,"*401*") + COUNTIF($AB$3:$AS$51,"*401*")+ COUNTIF($AV$55:$BD$55,"*401*") +COUNTIF($BF$3:$BM$57,"*401*") -1</f>
@@ -12073,7 +12089,7 @@
       </c>
       <c r="AH52" s="254">
         <f>COUNTIF( $AV$3:$BC$53,"*402*") + COUNTIF($AB$3:$AS$51,"*402*")+ COUNTIF($AV$55:$BD$55,"*402*") +COUNTIF($BF$3:$BM$57,"*402*") -1</f>
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AI52" s="253">
         <f>COUNTIF( $AV$3:$BC$53,"*403*") + COUNTIF($AB$3:$AS$51,"*403*")+ COUNTIF($AV$55:$BD$55,"*403*") +COUNTIF($BF$3:$BM$57,"*403*") -1</f>
@@ -12118,7 +12134,7 @@
       <c r="BA52" s="204"/>
       <c r="BB52" s="204"/>
       <c r="BC52" s="204"/>
-      <c r="BD52" s="271" t="s">
+      <c r="BD52" s="269" t="s">
         <v>329</v>
       </c>
       <c r="BE52" s="222" t="s">
@@ -12136,7 +12152,7 @@
       <c r="BK52" s="204"/>
       <c r="BL52" s="204"/>
       <c r="BM52" s="204"/>
-      <c r="BN52" s="277" t="s">
+      <c r="BN52" s="405" t="s">
         <v>301</v>
       </c>
       <c r="BO52" s="224"/>
@@ -12144,9 +12160,9 @@
     <row r="53" spans="1:77" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="96"/>
       <c r="B53" s="96"/>
-      <c r="E53" s="285"/>
-      <c r="F53" s="287"/>
-      <c r="G53" s="286"/>
+      <c r="E53" s="343"/>
+      <c r="F53" s="344"/>
+      <c r="G53" s="345"/>
       <c r="H53" s="31"/>
       <c r="I53" s="31"/>
       <c r="J53" s="30"/>
@@ -12154,13 +12170,13 @@
       <c r="L53" s="31"/>
       <c r="M53" s="31"/>
       <c r="N53" s="33"/>
-      <c r="O53" s="365"/>
-      <c r="P53" s="365"/>
-      <c r="Q53" s="365"/>
-      <c r="R53" s="365"/>
-      <c r="S53" s="365"/>
-      <c r="T53" s="365"/>
-      <c r="U53" s="366"/>
+      <c r="O53" s="305"/>
+      <c r="P53" s="305"/>
+      <c r="Q53" s="305"/>
+      <c r="R53" s="305"/>
+      <c r="S53" s="305"/>
+      <c r="T53" s="305"/>
+      <c r="U53" s="306"/>
       <c r="V53" s="36"/>
       <c r="W53" s="14"/>
       <c r="X53" s="14"/>
@@ -12181,7 +12197,7 @@
       <c r="BC53" s="196" t="s">
         <v>245</v>
       </c>
-      <c r="BD53" s="271"/>
+      <c r="BD53" s="269"/>
       <c r="BE53" s="222"/>
       <c r="BF53" s="211" t="s">
         <v>241</v>
@@ -12203,15 +12219,15 @@
       <c r="BM53" s="196" t="s">
         <v>93</v>
       </c>
-      <c r="BN53" s="277"/>
+      <c r="BN53" s="405"/>
       <c r="BO53" s="224"/>
     </row>
     <row r="54" spans="1:77" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="96"/>
       <c r="B54" s="96"/>
-      <c r="E54" s="285"/>
-      <c r="F54" s="287"/>
-      <c r="G54" s="286"/>
+      <c r="E54" s="343"/>
+      <c r="F54" s="344"/>
+      <c r="G54" s="345"/>
       <c r="H54" s="31"/>
       <c r="I54" s="31"/>
       <c r="J54" s="30"/>
@@ -12219,13 +12235,13 @@
       <c r="L54" s="31"/>
       <c r="M54" s="31"/>
       <c r="N54" s="33"/>
-      <c r="O54" s="365"/>
-      <c r="P54" s="365"/>
-      <c r="Q54" s="365"/>
-      <c r="R54" s="365"/>
-      <c r="S54" s="365"/>
-      <c r="T54" s="365"/>
-      <c r="U54" s="366"/>
+      <c r="O54" s="305"/>
+      <c r="P54" s="305"/>
+      <c r="Q54" s="305"/>
+      <c r="R54" s="305"/>
+      <c r="S54" s="305"/>
+      <c r="T54" s="305"/>
+      <c r="U54" s="306"/>
       <c r="V54" s="36"/>
       <c r="W54" s="14"/>
       <c r="X54" s="14"/>
@@ -12281,7 +12297,7 @@
       <c r="BK54" s="188"/>
       <c r="BL54" s="188"/>
       <c r="BM54" s="188"/>
-      <c r="BN54" s="276" t="s">
+      <c r="BN54" s="349" t="s">
         <v>302</v>
       </c>
       <c r="BO54" s="225"/>
@@ -12299,9 +12315,9 @@
     <row r="55" spans="1:77" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="96"/>
       <c r="B55" s="96"/>
-      <c r="E55" s="285"/>
-      <c r="F55" s="287"/>
-      <c r="G55" s="286"/>
+      <c r="E55" s="343"/>
+      <c r="F55" s="344"/>
+      <c r="G55" s="345"/>
       <c r="H55" s="31"/>
       <c r="I55" s="31"/>
       <c r="J55" s="30"/>
@@ -12309,13 +12325,13 @@
       <c r="L55" s="31"/>
       <c r="M55" s="31"/>
       <c r="N55" s="33"/>
-      <c r="O55" s="365"/>
-      <c r="P55" s="365"/>
-      <c r="Q55" s="365"/>
-      <c r="R55" s="365"/>
-      <c r="S55" s="365"/>
-      <c r="T55" s="365"/>
-      <c r="U55" s="366"/>
+      <c r="O55" s="305"/>
+      <c r="P55" s="305"/>
+      <c r="Q55" s="305"/>
+      <c r="R55" s="305"/>
+      <c r="S55" s="305"/>
+      <c r="T55" s="305"/>
+      <c r="U55" s="306"/>
       <c r="V55" s="36"/>
       <c r="W55" s="14"/>
       <c r="X55" s="14"/>
@@ -12354,15 +12370,15 @@
       <c r="BK55" s="189"/>
       <c r="BL55" s="189"/>
       <c r="BM55" s="189"/>
-      <c r="BN55" s="276"/>
+      <c r="BN55" s="349"/>
       <c r="BO55" s="224"/>
     </row>
     <row r="56" spans="1:77" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="96"/>
       <c r="B56" s="96"/>
-      <c r="E56" s="285"/>
-      <c r="F56" s="287"/>
-      <c r="G56" s="286"/>
+      <c r="E56" s="343"/>
+      <c r="F56" s="344"/>
+      <c r="G56" s="345"/>
       <c r="H56" s="31"/>
       <c r="I56" s="31"/>
       <c r="J56" s="30"/>
@@ -12370,13 +12386,13 @@
       <c r="L56" s="31"/>
       <c r="M56" s="31"/>
       <c r="N56" s="33"/>
-      <c r="O56" s="365"/>
-      <c r="P56" s="365"/>
-      <c r="Q56" s="365"/>
-      <c r="R56" s="365"/>
-      <c r="S56" s="365"/>
-      <c r="T56" s="365"/>
-      <c r="U56" s="366"/>
+      <c r="O56" s="305"/>
+      <c r="P56" s="305"/>
+      <c r="Q56" s="305"/>
+      <c r="R56" s="305"/>
+      <c r="S56" s="305"/>
+      <c r="T56" s="305"/>
+      <c r="U56" s="306"/>
       <c r="V56" s="36"/>
       <c r="W56" s="14"/>
       <c r="X56" s="14"/>
@@ -12397,7 +12413,7 @@
       <c r="BK56" s="204"/>
       <c r="BL56" s="204"/>
       <c r="BM56" s="204"/>
-      <c r="BN56" s="359" t="s">
+      <c r="BN56" s="350" t="s">
         <v>303</v>
       </c>
       <c r="BO56" s="224"/>
@@ -12405,9 +12421,9 @@
     <row r="57" spans="1:77" ht="279.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="96"/>
       <c r="B57" s="96"/>
-      <c r="E57" s="288"/>
-      <c r="F57" s="291"/>
-      <c r="G57" s="289"/>
+      <c r="E57" s="346"/>
+      <c r="F57" s="347"/>
+      <c r="G57" s="348"/>
       <c r="H57" s="31"/>
       <c r="I57" s="31"/>
       <c r="J57" s="30"/>
@@ -12415,13 +12431,13 @@
       <c r="L57" s="31"/>
       <c r="M57" s="31"/>
       <c r="N57" s="33"/>
-      <c r="O57" s="367"/>
-      <c r="P57" s="367"/>
-      <c r="Q57" s="367"/>
-      <c r="R57" s="367"/>
-      <c r="S57" s="367"/>
-      <c r="T57" s="367"/>
-      <c r="U57" s="368"/>
+      <c r="O57" s="308"/>
+      <c r="P57" s="308"/>
+      <c r="Q57" s="308"/>
+      <c r="R57" s="308"/>
+      <c r="S57" s="308"/>
+      <c r="T57" s="308"/>
+      <c r="U57" s="309"/>
       <c r="V57" s="36"/>
       <c r="W57" s="14"/>
       <c r="X57" s="14"/>
@@ -12440,7 +12456,7 @@
       <c r="BK57" s="203"/>
       <c r="BL57" s="203"/>
       <c r="BM57" s="203"/>
-      <c r="BN57" s="359"/>
+      <c r="BN57" s="350"/>
       <c r="BO57" s="224"/>
     </row>
     <row r="58" spans="1:77" ht="279.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -12458,15 +12474,15 @@
       <c r="L58" s="31"/>
       <c r="M58" s="31"/>
       <c r="N58" s="33"/>
-      <c r="O58" s="425" t="s">
+      <c r="O58" s="301" t="s">
         <v>40</v>
       </c>
-      <c r="P58" s="363"/>
-      <c r="Q58" s="363"/>
-      <c r="R58" s="363"/>
-      <c r="S58" s="363"/>
-      <c r="T58" s="363"/>
-      <c r="U58" s="364"/>
+      <c r="P58" s="302"/>
+      <c r="Q58" s="302"/>
+      <c r="R58" s="302"/>
+      <c r="S58" s="302"/>
+      <c r="T58" s="302"/>
+      <c r="U58" s="303"/>
       <c r="V58" s="36"/>
       <c r="W58" s="14"/>
       <c r="X58" s="14"/>
@@ -12481,12 +12497,12 @@
       <c r="AH58" s="37"/>
       <c r="AI58" s="104"/>
       <c r="AJ58" s="104"/>
-      <c r="AK58" s="307" t="s">
+      <c r="AK58" s="351" t="s">
         <v>8</v>
       </c>
-      <c r="AL58" s="369"/>
-      <c r="AM58" s="369"/>
-      <c r="AN58" s="308"/>
+      <c r="AL58" s="352"/>
+      <c r="AM58" s="352"/>
+      <c r="AN58" s="353"/>
       <c r="AO58" s="105"/>
       <c r="AP58" s="105"/>
       <c r="AQ58" s="105"/>
@@ -12529,13 +12545,13 @@
       <c r="L59" s="31"/>
       <c r="M59" s="31"/>
       <c r="N59" s="33"/>
-      <c r="O59" s="426"/>
-      <c r="P59" s="365"/>
-      <c r="Q59" s="365"/>
-      <c r="R59" s="365"/>
-      <c r="S59" s="365"/>
-      <c r="T59" s="365"/>
-      <c r="U59" s="366"/>
+      <c r="O59" s="304"/>
+      <c r="P59" s="305"/>
+      <c r="Q59" s="305"/>
+      <c r="R59" s="305"/>
+      <c r="S59" s="305"/>
+      <c r="T59" s="305"/>
+      <c r="U59" s="306"/>
       <c r="V59" s="36"/>
       <c r="W59" s="14"/>
       <c r="X59" s="14"/>
@@ -12644,13 +12660,13 @@
       <c r="L60" s="31"/>
       <c r="M60" s="31"/>
       <c r="N60" s="33"/>
-      <c r="O60" s="426"/>
-      <c r="P60" s="365"/>
-      <c r="Q60" s="365"/>
-      <c r="R60" s="365"/>
-      <c r="S60" s="365"/>
-      <c r="T60" s="365"/>
-      <c r="U60" s="366"/>
+      <c r="O60" s="304"/>
+      <c r="P60" s="305"/>
+      <c r="Q60" s="305"/>
+      <c r="R60" s="305"/>
+      <c r="S60" s="305"/>
+      <c r="T60" s="305"/>
+      <c r="U60" s="306"/>
       <c r="V60" s="36"/>
       <c r="W60" s="14"/>
       <c r="X60" s="14"/>
@@ -12781,13 +12797,13 @@
       <c r="L61" s="31"/>
       <c r="M61" s="31"/>
       <c r="N61" s="33"/>
-      <c r="O61" s="426"/>
-      <c r="P61" s="365"/>
-      <c r="Q61" s="365"/>
-      <c r="R61" s="365"/>
-      <c r="S61" s="365"/>
-      <c r="T61" s="365"/>
-      <c r="U61" s="366"/>
+      <c r="O61" s="304"/>
+      <c r="P61" s="305"/>
+      <c r="Q61" s="305"/>
+      <c r="R61" s="305"/>
+      <c r="S61" s="305"/>
+      <c r="T61" s="305"/>
+      <c r="U61" s="306"/>
       <c r="V61" s="36"/>
       <c r="W61" s="14"/>
       <c r="X61" s="14"/>
@@ -12803,12 +12819,12 @@
       <c r="AH61" s="98"/>
       <c r="AI61" s="107"/>
       <c r="AJ61" s="152"/>
-      <c r="AK61" s="407" t="s">
+      <c r="AK61" s="280" t="s">
         <v>9</v>
       </c>
-      <c r="AL61" s="408"/>
-      <c r="AM61" s="408"/>
-      <c r="AN61" s="409"/>
+      <c r="AL61" s="281"/>
+      <c r="AM61" s="281"/>
+      <c r="AN61" s="282"/>
       <c r="AO61" s="105"/>
       <c r="AP61" s="105"/>
       <c r="AQ61" s="182">
@@ -12852,11 +12868,11 @@
       </c>
       <c r="BA61" s="213">
         <f>COUNTIF($AB$3:$BC$55,"*402-10-*") + COUNTIF($BF$3:$BM$57,"*402-10-*")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB61" s="213">
         <f>COUNTIF($AB$3:$BC$55,"*402-11-*") + COUNTIF($BF$3:$BM$57,"*402-11-*")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC61" s="213">
         <f>COUNTIF($AB$3:$BC$55,"*402-12-*") + COUNTIF($BF$3:$BM$57,"*402-12-*")</f>
@@ -12904,7 +12920,7 @@
       </c>
       <c r="BN61" s="186">
         <f>SUM(AR61:BM61)/(14*22)</f>
-        <v>0.35064935064935066</v>
+        <v>0.35714285714285715</v>
       </c>
     </row>
     <row r="62" spans="1:77" ht="279.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -12920,13 +12936,13 @@
       <c r="L62" s="31"/>
       <c r="M62" s="31"/>
       <c r="N62" s="33"/>
-      <c r="O62" s="426"/>
-      <c r="P62" s="365"/>
-      <c r="Q62" s="365"/>
-      <c r="R62" s="365"/>
-      <c r="S62" s="365"/>
-      <c r="T62" s="365"/>
-      <c r="U62" s="366"/>
+      <c r="O62" s="304"/>
+      <c r="P62" s="305"/>
+      <c r="Q62" s="305"/>
+      <c r="R62" s="305"/>
+      <c r="S62" s="305"/>
+      <c r="T62" s="305"/>
+      <c r="U62" s="306"/>
       <c r="V62" s="95"/>
       <c r="W62" s="14"/>
       <c r="X62" s="14"/>
@@ -12937,10 +12953,10 @@
       <c r="AH62" s="98"/>
       <c r="AI62" s="107"/>
       <c r="AJ62" s="152"/>
-      <c r="AK62" s="410"/>
-      <c r="AL62" s="411"/>
-      <c r="AM62" s="411"/>
-      <c r="AN62" s="412"/>
+      <c r="AK62" s="283"/>
+      <c r="AL62" s="284"/>
+      <c r="AM62" s="284"/>
+      <c r="AN62" s="285"/>
       <c r="AO62" s="105"/>
       <c r="AP62" s="105"/>
       <c r="AQ62" s="183">
@@ -13052,13 +13068,13 @@
       <c r="L63" s="31"/>
       <c r="M63" s="31"/>
       <c r="N63" s="33"/>
-      <c r="O63" s="426"/>
-      <c r="P63" s="365"/>
-      <c r="Q63" s="365"/>
-      <c r="R63" s="365"/>
-      <c r="S63" s="365"/>
-      <c r="T63" s="365"/>
-      <c r="U63" s="366"/>
+      <c r="O63" s="304"/>
+      <c r="P63" s="305"/>
+      <c r="Q63" s="305"/>
+      <c r="R63" s="305"/>
+      <c r="S63" s="305"/>
+      <c r="T63" s="305"/>
+      <c r="U63" s="306"/>
       <c r="V63" s="95"/>
       <c r="W63" s="14"/>
       <c r="X63" s="14"/>
@@ -13069,10 +13085,10 @@
       <c r="AH63" s="98"/>
       <c r="AI63" s="107"/>
       <c r="AJ63" s="152"/>
-      <c r="AK63" s="413"/>
-      <c r="AL63" s="414"/>
-      <c r="AM63" s="414"/>
-      <c r="AN63" s="415"/>
+      <c r="AK63" s="286"/>
+      <c r="AL63" s="287"/>
+      <c r="AM63" s="287"/>
+      <c r="AN63" s="288"/>
       <c r="AO63" s="105"/>
       <c r="AP63" s="105"/>
       <c r="AQ63" s="105"/>
@@ -13093,13 +13109,13 @@
       <c r="L64" s="31"/>
       <c r="M64" s="31"/>
       <c r="N64" s="33"/>
-      <c r="O64" s="426"/>
-      <c r="P64" s="365"/>
-      <c r="Q64" s="365"/>
-      <c r="R64" s="365"/>
-      <c r="S64" s="365"/>
-      <c r="T64" s="365"/>
-      <c r="U64" s="366"/>
+      <c r="O64" s="304"/>
+      <c r="P64" s="305"/>
+      <c r="Q64" s="305"/>
+      <c r="R64" s="305"/>
+      <c r="S64" s="305"/>
+      <c r="T64" s="305"/>
+      <c r="U64" s="306"/>
       <c r="V64" s="95"/>
       <c r="W64" s="14"/>
       <c r="X64" s="14"/>
@@ -13149,13 +13165,13 @@
       <c r="L65" s="31"/>
       <c r="M65" s="31"/>
       <c r="N65" s="33"/>
-      <c r="O65" s="426"/>
-      <c r="P65" s="365"/>
-      <c r="Q65" s="365"/>
-      <c r="R65" s="365"/>
-      <c r="S65" s="365"/>
-      <c r="T65" s="365"/>
-      <c r="U65" s="366"/>
+      <c r="O65" s="304"/>
+      <c r="P65" s="305"/>
+      <c r="Q65" s="305"/>
+      <c r="R65" s="305"/>
+      <c r="S65" s="305"/>
+      <c r="T65" s="305"/>
+      <c r="U65" s="306"/>
       <c r="V65" s="95"/>
       <c r="W65" s="14"/>
       <c r="X65" s="14"/>
@@ -13204,13 +13220,13 @@
       <c r="L66" s="31"/>
       <c r="M66" s="31"/>
       <c r="N66" s="33"/>
-      <c r="O66" s="426"/>
-      <c r="P66" s="365"/>
-      <c r="Q66" s="365"/>
-      <c r="R66" s="365"/>
-      <c r="S66" s="365"/>
-      <c r="T66" s="365"/>
-      <c r="U66" s="366"/>
+      <c r="O66" s="304"/>
+      <c r="P66" s="305"/>
+      <c r="Q66" s="305"/>
+      <c r="R66" s="305"/>
+      <c r="S66" s="305"/>
+      <c r="T66" s="305"/>
+      <c r="U66" s="306"/>
       <c r="V66" s="102"/>
       <c r="W66" s="103"/>
       <c r="X66" s="14"/>
@@ -13221,21 +13237,21 @@
       <c r="AH66" s="98"/>
       <c r="AI66" s="98"/>
       <c r="AJ66" s="98"/>
-      <c r="AK66" s="416" t="s">
+      <c r="AK66" s="289" t="s">
         <v>10</v>
       </c>
-      <c r="AL66" s="417"/>
-      <c r="AM66" s="417"/>
-      <c r="AN66" s="417"/>
-      <c r="AO66" s="417"/>
-      <c r="AP66" s="418"/>
+      <c r="AL66" s="290"/>
+      <c r="AM66" s="290"/>
+      <c r="AN66" s="290"/>
+      <c r="AO66" s="290"/>
+      <c r="AP66" s="291"/>
       <c r="AQ66" s="105"/>
       <c r="AR66" s="40"/>
-      <c r="AS66" s="360" t="s">
+      <c r="AS66" s="298" t="s">
         <v>0</v>
       </c>
       <c r="AT66" s="173"/>
-      <c r="AU66" s="360" t="s">
+      <c r="AU66" s="298" t="s">
         <v>1</v>
       </c>
       <c r="AW66" s="170"/>
@@ -13269,13 +13285,13 @@
       <c r="L67" s="31"/>
       <c r="M67" s="31"/>
       <c r="N67" s="33"/>
-      <c r="O67" s="426"/>
-      <c r="P67" s="365"/>
-      <c r="Q67" s="365"/>
-      <c r="R67" s="365"/>
-      <c r="S67" s="365"/>
-      <c r="T67" s="365"/>
-      <c r="U67" s="366"/>
+      <c r="O67" s="304"/>
+      <c r="P67" s="305"/>
+      <c r="Q67" s="305"/>
+      <c r="R67" s="305"/>
+      <c r="S67" s="305"/>
+      <c r="T67" s="305"/>
+      <c r="U67" s="306"/>
       <c r="V67" s="95"/>
       <c r="W67" s="103"/>
       <c r="X67" s="14"/>
@@ -13285,17 +13301,17 @@
       <c r="AH67" s="9"/>
       <c r="AI67" s="98"/>
       <c r="AJ67" s="98"/>
-      <c r="AK67" s="419"/>
-      <c r="AL67" s="420"/>
-      <c r="AM67" s="420"/>
-      <c r="AN67" s="420"/>
-      <c r="AO67" s="420"/>
-      <c r="AP67" s="421"/>
+      <c r="AK67" s="292"/>
+      <c r="AL67" s="293"/>
+      <c r="AM67" s="293"/>
+      <c r="AN67" s="293"/>
+      <c r="AO67" s="293"/>
+      <c r="AP67" s="294"/>
       <c r="AQ67" s="44"/>
       <c r="AR67" s="44"/>
-      <c r="AS67" s="361"/>
+      <c r="AS67" s="299"/>
       <c r="AT67" s="174"/>
-      <c r="AU67" s="361"/>
+      <c r="AU67" s="299"/>
       <c r="BC67" s="39"/>
       <c r="BE67" s="4"/>
       <c r="BF67" s="4"/>
@@ -13320,13 +13336,13 @@
       <c r="L68" s="31"/>
       <c r="M68" s="31"/>
       <c r="N68" s="33"/>
-      <c r="O68" s="426"/>
-      <c r="P68" s="365"/>
-      <c r="Q68" s="365"/>
-      <c r="R68" s="365"/>
-      <c r="S68" s="365"/>
-      <c r="T68" s="365"/>
-      <c r="U68" s="366"/>
+      <c r="O68" s="304"/>
+      <c r="P68" s="305"/>
+      <c r="Q68" s="305"/>
+      <c r="R68" s="305"/>
+      <c r="S68" s="305"/>
+      <c r="T68" s="305"/>
+      <c r="U68" s="306"/>
       <c r="V68" s="95"/>
       <c r="W68" s="103"/>
       <c r="X68" s="14"/>
@@ -13341,17 +13357,17 @@
       <c r="AH68" s="124"/>
       <c r="AI68" s="101"/>
       <c r="AJ68" s="101"/>
-      <c r="AK68" s="422"/>
-      <c r="AL68" s="423"/>
-      <c r="AM68" s="423"/>
-      <c r="AN68" s="423"/>
-      <c r="AO68" s="423"/>
-      <c r="AP68" s="424"/>
+      <c r="AK68" s="295"/>
+      <c r="AL68" s="296"/>
+      <c r="AM68" s="296"/>
+      <c r="AN68" s="296"/>
+      <c r="AO68" s="296"/>
+      <c r="AP68" s="297"/>
       <c r="AQ68" s="101"/>
       <c r="AR68" s="101"/>
-      <c r="AS68" s="362"/>
+      <c r="AS68" s="300"/>
       <c r="AT68" s="175"/>
-      <c r="AU68" s="362"/>
+      <c r="AU68" s="300"/>
       <c r="AV68" s="125"/>
       <c r="AW68" s="125"/>
       <c r="AX68" s="125"/>
@@ -13373,13 +13389,13 @@
       <c r="L69" s="31"/>
       <c r="M69" s="31"/>
       <c r="N69" s="33"/>
-      <c r="O69" s="426"/>
-      <c r="P69" s="365"/>
-      <c r="Q69" s="365"/>
-      <c r="R69" s="365"/>
-      <c r="S69" s="365"/>
-      <c r="T69" s="365"/>
-      <c r="U69" s="366"/>
+      <c r="O69" s="304"/>
+      <c r="P69" s="305"/>
+      <c r="Q69" s="305"/>
+      <c r="R69" s="305"/>
+      <c r="S69" s="305"/>
+      <c r="T69" s="305"/>
+      <c r="U69" s="306"/>
       <c r="V69" s="95"/>
       <c r="W69" s="103"/>
       <c r="X69" s="14"/>
@@ -13388,13 +13404,13 @@
       <c r="AA69" s="94"/>
       <c r="AB69" s="117"/>
       <c r="AC69" s="117"/>
-      <c r="AD69" s="401" t="s">
+      <c r="AD69" s="272" t="s">
         <v>3</v>
       </c>
-      <c r="AE69" s="402"/>
-      <c r="AF69" s="402"/>
-      <c r="AG69" s="402"/>
-      <c r="AH69" s="403"/>
+      <c r="AE69" s="273"/>
+      <c r="AF69" s="273"/>
+      <c r="AG69" s="273"/>
+      <c r="AH69" s="274"/>
       <c r="AI69" s="129"/>
       <c r="AZ69" s="130"/>
     </row>
@@ -13411,23 +13427,23 @@
       <c r="L70" s="49"/>
       <c r="M70" s="49"/>
       <c r="N70" s="109"/>
-      <c r="O70" s="427"/>
-      <c r="P70" s="367"/>
-      <c r="Q70" s="367"/>
-      <c r="R70" s="367"/>
-      <c r="S70" s="367"/>
-      <c r="T70" s="367"/>
-      <c r="U70" s="368"/>
+      <c r="O70" s="307"/>
+      <c r="P70" s="308"/>
+      <c r="Q70" s="308"/>
+      <c r="R70" s="308"/>
+      <c r="S70" s="308"/>
+      <c r="T70" s="308"/>
+      <c r="U70" s="309"/>
       <c r="V70" s="95"/>
       <c r="W70" s="103"/>
       <c r="X70" s="14"/>
       <c r="AB70" s="117"/>
       <c r="AC70" s="117"/>
-      <c r="AD70" s="404"/>
-      <c r="AE70" s="405"/>
-      <c r="AF70" s="405"/>
-      <c r="AG70" s="405"/>
-      <c r="AH70" s="406"/>
+      <c r="AD70" s="275"/>
+      <c r="AE70" s="276"/>
+      <c r="AF70" s="276"/>
+      <c r="AG70" s="276"/>
+      <c r="AH70" s="277"/>
       <c r="AL70" s="134"/>
       <c r="AM70" s="134"/>
       <c r="AN70" s="134"/>
@@ -13678,13 +13694,13 @@
       <c r="H75" s="120"/>
       <c r="I75" s="121"/>
       <c r="J75" s="122"/>
-      <c r="K75" s="374" t="s">
+      <c r="K75" s="316" t="s">
         <v>41</v>
       </c>
-      <c r="L75" s="375"/>
-      <c r="M75" s="375"/>
-      <c r="N75" s="375"/>
-      <c r="O75" s="376"/>
+      <c r="L75" s="317"/>
+      <c r="M75" s="317"/>
+      <c r="N75" s="317"/>
+      <c r="O75" s="318"/>
       <c r="P75" s="115"/>
       <c r="Q75" s="115"/>
       <c r="R75" s="115"/>
@@ -13732,28 +13748,28 @@
     </row>
     <row r="76" spans="1:65" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="9"/>
-      <c r="B76" s="324" t="s">
+      <c r="B76" s="325" t="s">
         <v>42</v>
       </c>
-      <c r="C76" s="383"/>
-      <c r="D76" s="384"/>
-      <c r="E76" s="372" t="s">
+      <c r="C76" s="326"/>
+      <c r="D76" s="327"/>
+      <c r="E76" s="278" t="s">
         <v>43</v>
       </c>
-      <c r="F76" s="373"/>
-      <c r="G76" s="326" t="s">
+      <c r="F76" s="279"/>
+      <c r="G76" s="332" t="s">
         <v>43</v>
       </c>
-      <c r="H76" s="339"/>
-      <c r="I76" s="389" t="s">
+      <c r="H76" s="333"/>
+      <c r="I76" s="334" t="s">
         <v>44</v>
       </c>
-      <c r="J76" s="390"/>
-      <c r="K76" s="377"/>
-      <c r="L76" s="378"/>
-      <c r="M76" s="378"/>
-      <c r="N76" s="378"/>
-      <c r="O76" s="379"/>
+      <c r="J76" s="335"/>
+      <c r="K76" s="319"/>
+      <c r="L76" s="320"/>
+      <c r="M76" s="320"/>
+      <c r="N76" s="320"/>
+      <c r="O76" s="321"/>
       <c r="P76" s="115"/>
       <c r="Q76" s="115"/>
       <c r="R76" s="115"/>
@@ -13798,27 +13814,27 @@
       <c r="BJ76" s="144"/>
       <c r="BK76" s="144"/>
       <c r="BL76" s="144"/>
-      <c r="BM76" s="357"/>
+      <c r="BM76" s="354"/>
     </row>
     <row r="77" spans="1:65" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B77" s="385"/>
-      <c r="C77" s="383"/>
-      <c r="D77" s="384"/>
-      <c r="E77" s="372" t="s">
+      <c r="B77" s="328"/>
+      <c r="C77" s="326"/>
+      <c r="D77" s="327"/>
+      <c r="E77" s="278" t="s">
         <v>43</v>
       </c>
-      <c r="F77" s="393"/>
-      <c r="G77" s="372" t="s">
+      <c r="F77" s="338"/>
+      <c r="G77" s="278" t="s">
         <v>43</v>
       </c>
-      <c r="H77" s="393"/>
-      <c r="I77" s="389"/>
-      <c r="J77" s="390"/>
-      <c r="K77" s="377"/>
-      <c r="L77" s="378"/>
-      <c r="M77" s="378"/>
-      <c r="N77" s="378"/>
-      <c r="O77" s="379"/>
+      <c r="H77" s="338"/>
+      <c r="I77" s="334"/>
+      <c r="J77" s="335"/>
+      <c r="K77" s="319"/>
+      <c r="L77" s="320"/>
+      <c r="M77" s="320"/>
+      <c r="N77" s="320"/>
+      <c r="O77" s="321"/>
       <c r="P77" s="115"/>
       <c r="Q77" s="115"/>
       <c r="R77" s="115"/>
@@ -13863,28 +13879,28 @@
       <c r="BJ77" s="144"/>
       <c r="BK77" s="144"/>
       <c r="BL77" s="144"/>
-      <c r="BM77" s="357"/>
+      <c r="BM77" s="354"/>
     </row>
     <row r="78" spans="1:65" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="9"/>
-      <c r="B78" s="386"/>
-      <c r="C78" s="387"/>
-      <c r="D78" s="388"/>
-      <c r="E78" s="372" t="s">
+      <c r="B78" s="329"/>
+      <c r="C78" s="330"/>
+      <c r="D78" s="331"/>
+      <c r="E78" s="278" t="s">
         <v>45</v>
       </c>
-      <c r="F78" s="373"/>
-      <c r="G78" s="372" t="s">
+      <c r="F78" s="279"/>
+      <c r="G78" s="278" t="s">
         <v>46</v>
       </c>
-      <c r="H78" s="373"/>
-      <c r="I78" s="391"/>
-      <c r="J78" s="392"/>
-      <c r="K78" s="380"/>
-      <c r="L78" s="381"/>
-      <c r="M78" s="381"/>
-      <c r="N78" s="381"/>
-      <c r="O78" s="382"/>
+      <c r="H78" s="279"/>
+      <c r="I78" s="336"/>
+      <c r="J78" s="337"/>
+      <c r="K78" s="322"/>
+      <c r="L78" s="323"/>
+      <c r="M78" s="323"/>
+      <c r="N78" s="323"/>
+      <c r="O78" s="324"/>
       <c r="P78" s="131"/>
       <c r="Q78" s="131"/>
       <c r="R78" s="131"/>
@@ -13929,7 +13945,7 @@
       <c r="BJ78" s="144"/>
       <c r="BK78" s="144"/>
       <c r="BL78" s="144"/>
-      <c r="BM78" s="357"/>
+      <c r="BM78" s="354"/>
     </row>
     <row r="79" spans="1:65" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="135"/>
@@ -13992,7 +14008,7 @@
       <c r="BL79" s="144"/>
     </row>
     <row r="80" spans="1:65" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="350"/>
+      <c r="A80" s="271"/>
       <c r="B80" s="9"/>
       <c r="C80" s="9"/>
       <c r="D80" s="9"/>
@@ -14000,15 +14016,15 @@
       <c r="F80" s="9"/>
       <c r="G80" s="43"/>
       <c r="K80" s="41"/>
-      <c r="R80" s="399"/>
-      <c r="S80" s="399"/>
-      <c r="T80" s="399"/>
-      <c r="U80" s="399"/>
-      <c r="V80" s="399"/>
-      <c r="W80" s="399"/>
-      <c r="X80" s="399"/>
-      <c r="Y80" s="399"/>
-      <c r="Z80" s="399"/>
+      <c r="R80" s="314"/>
+      <c r="S80" s="314"/>
+      <c r="T80" s="314"/>
+      <c r="U80" s="314"/>
+      <c r="V80" s="314"/>
+      <c r="W80" s="314"/>
+      <c r="X80" s="314"/>
+      <c r="Y80" s="314"/>
+      <c r="Z80" s="314"/>
       <c r="AB80" s="101"/>
       <c r="AC80" s="101"/>
       <c r="AH80" s="145"/>
@@ -14044,7 +14060,7 @@
       <c r="BL80" s="144"/>
     </row>
     <row r="81" spans="1:64" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="350"/>
+      <c r="A81" s="271"/>
       <c r="B81" s="9"/>
       <c r="C81" s="9"/>
       <c r="D81" s="9"/>
@@ -14052,15 +14068,15 @@
       <c r="F81" s="9"/>
       <c r="G81" s="43"/>
       <c r="K81" s="41"/>
-      <c r="R81" s="400"/>
-      <c r="S81" s="400"/>
-      <c r="T81" s="400"/>
-      <c r="U81" s="400"/>
-      <c r="V81" s="400"/>
-      <c r="W81" s="400"/>
-      <c r="X81" s="400"/>
-      <c r="Y81" s="400"/>
-      <c r="Z81" s="400"/>
+      <c r="R81" s="315"/>
+      <c r="S81" s="315"/>
+      <c r="T81" s="315"/>
+      <c r="U81" s="315"/>
+      <c r="V81" s="315"/>
+      <c r="W81" s="315"/>
+      <c r="X81" s="315"/>
+      <c r="Y81" s="315"/>
+      <c r="Z81" s="315"/>
       <c r="AB81" s="163"/>
       <c r="AC81" s="161"/>
       <c r="AD81" s="161"/>
@@ -14100,18 +14116,18 @@
       <c r="BL81" s="144"/>
     </row>
     <row r="82" spans="1:64" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="350"/>
+      <c r="A82" s="271"/>
       <c r="H82" s="148"/>
       <c r="I82" s="148"/>
       <c r="J82" s="148"/>
       <c r="K82" s="92"/>
       <c r="L82" s="92"/>
-      <c r="R82" s="395"/>
-      <c r="S82" s="396"/>
-      <c r="T82" s="397"/>
-      <c r="U82" s="398"/>
-      <c r="V82" s="397"/>
-      <c r="W82" s="398"/>
+      <c r="R82" s="339"/>
+      <c r="S82" s="340"/>
+      <c r="T82" s="341"/>
+      <c r="U82" s="342"/>
+      <c r="V82" s="341"/>
+      <c r="W82" s="342"/>
       <c r="AB82" s="167"/>
       <c r="AC82" s="165"/>
       <c r="AD82" s="165"/>
@@ -14162,16 +14178,16 @@
       <c r="J83" s="92"/>
       <c r="K83" s="23"/>
       <c r="L83" s="23"/>
-      <c r="R83" s="370"/>
-      <c r="S83" s="371"/>
-      <c r="T83" s="370"/>
-      <c r="U83" s="371"/>
-      <c r="V83" s="394"/>
-      <c r="W83" s="428"/>
+      <c r="R83" s="310"/>
+      <c r="S83" s="311"/>
+      <c r="T83" s="310"/>
+      <c r="U83" s="311"/>
+      <c r="V83" s="312"/>
+      <c r="W83" s="313"/>
       <c r="X83" s="3"/>
     </row>
     <row r="84" spans="1:64" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="350"/>
+      <c r="A84" s="271"/>
       <c r="B84" s="92"/>
       <c r="C84" s="92"/>
       <c r="D84" s="92"/>
@@ -14188,18 +14204,18 @@
       <c r="O84" s="151"/>
       <c r="P84" s="115"/>
       <c r="Q84" s="23"/>
-      <c r="R84" s="370"/>
-      <c r="S84" s="371"/>
-      <c r="T84" s="370"/>
-      <c r="U84" s="371"/>
-      <c r="V84" s="370"/>
-      <c r="W84" s="371"/>
+      <c r="R84" s="310"/>
+      <c r="S84" s="311"/>
+      <c r="T84" s="310"/>
+      <c r="U84" s="311"/>
+      <c r="V84" s="310"/>
+      <c r="W84" s="311"/>
       <c r="X84" s="11"/>
-      <c r="Y84" s="370"/>
-      <c r="Z84" s="371"/>
+      <c r="Y84" s="310"/>
+      <c r="Z84" s="311"/>
     </row>
     <row r="85" spans="1:64" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="350"/>
+      <c r="A85" s="271"/>
       <c r="B85" s="44"/>
       <c r="C85" s="44"/>
       <c r="D85" s="44"/>
@@ -14217,17 +14233,17 @@
       <c r="P85" s="23"/>
       <c r="Q85" s="23"/>
       <c r="R85" s="153"/>
-      <c r="S85" s="370"/>
-      <c r="T85" s="371"/>
+      <c r="S85" s="310"/>
+      <c r="T85" s="311"/>
       <c r="U85" s="154"/>
-      <c r="V85" s="394"/>
-      <c r="W85" s="394"/>
-      <c r="X85" s="394"/>
-      <c r="Y85" s="394"/>
+      <c r="V85" s="312"/>
+      <c r="W85" s="312"/>
+      <c r="X85" s="312"/>
+      <c r="Y85" s="312"/>
       <c r="Z85" s="155"/>
     </row>
     <row r="86" spans="1:64" ht="186" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="350"/>
+      <c r="A86" s="271"/>
       <c r="B86" s="44"/>
       <c r="C86" s="44"/>
       <c r="D86" s="44"/>
@@ -14271,11 +14287,11 @@
       <c r="W87" s="99"/>
     </row>
     <row r="88" spans="1:64" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E88" s="350"/>
+      <c r="E88" s="271"/>
       <c r="F88" s="83"/>
-      <c r="G88" s="350"/>
-      <c r="H88" s="350"/>
-      <c r="I88" s="350"/>
+      <c r="G88" s="271"/>
+      <c r="H88" s="271"/>
+      <c r="I88" s="271"/>
       <c r="J88" s="99"/>
       <c r="K88" s="99"/>
       <c r="L88" s="99"/>
@@ -14292,11 +14308,11 @@
       <c r="W88" s="99"/>
     </row>
     <row r="89" spans="1:64" ht="186" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E89" s="350"/>
+      <c r="E89" s="271"/>
       <c r="F89" s="83"/>
-      <c r="G89" s="350"/>
-      <c r="H89" s="350"/>
-      <c r="I89" s="350"/>
+      <c r="G89" s="271"/>
+      <c r="H89" s="271"/>
+      <c r="I89" s="271"/>
       <c r="J89" s="99"/>
       <c r="K89" s="99"/>
       <c r="L89" s="99"/>
@@ -14317,11 +14333,11 @@
       <c r="AA89" s="162"/>
     </row>
     <row r="90" spans="1:64" ht="186" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E90" s="350"/>
+      <c r="E90" s="271"/>
       <c r="F90" s="83"/>
-      <c r="G90" s="350"/>
-      <c r="H90" s="350"/>
-      <c r="I90" s="350"/>
+      <c r="G90" s="271"/>
+      <c r="H90" s="271"/>
+      <c r="I90" s="271"/>
       <c r="J90" s="99"/>
       <c r="K90" s="99"/>
       <c r="L90" s="99"/>
@@ -14351,42 +14367,125 @@
     </row>
   </sheetData>
   <mergeCells count="179">
-    <mergeCell ref="AJ21:AJ22"/>
-    <mergeCell ref="AJ23:AJ24"/>
-    <mergeCell ref="AJ25:AJ26"/>
-    <mergeCell ref="AJ27:AJ28"/>
-    <mergeCell ref="AJ30:AJ31"/>
-    <mergeCell ref="AJ32:AJ33"/>
-    <mergeCell ref="AJ34:AJ35"/>
-    <mergeCell ref="AJ36:AJ37"/>
-    <mergeCell ref="AJ38:AJ39"/>
-    <mergeCell ref="AJ3:AJ4"/>
-    <mergeCell ref="AJ5:AJ6"/>
-    <mergeCell ref="AJ7:AJ8"/>
-    <mergeCell ref="AJ9:AJ10"/>
-    <mergeCell ref="AJ11:AJ12"/>
-    <mergeCell ref="AJ13:AJ14"/>
-    <mergeCell ref="AJ15:AJ16"/>
-    <mergeCell ref="AJ17:AJ18"/>
-    <mergeCell ref="AJ19:AJ20"/>
-    <mergeCell ref="E88:E90"/>
-    <mergeCell ref="G88:G90"/>
-    <mergeCell ref="H88:H90"/>
-    <mergeCell ref="I88:I90"/>
-    <mergeCell ref="AD69:AH70"/>
-    <mergeCell ref="G78:H78"/>
-    <mergeCell ref="AK61:AN63"/>
-    <mergeCell ref="AK66:AP68"/>
-    <mergeCell ref="AS66:AS68"/>
-    <mergeCell ref="O58:U70"/>
-    <mergeCell ref="R83:S83"/>
-    <mergeCell ref="T83:U83"/>
-    <mergeCell ref="V83:W83"/>
-    <mergeCell ref="X80:X81"/>
-    <mergeCell ref="Y80:Y81"/>
-    <mergeCell ref="Z80:Z81"/>
-    <mergeCell ref="R80:R81"/>
-    <mergeCell ref="S80:S81"/>
+    <mergeCell ref="AO2:AP2"/>
+    <mergeCell ref="AT19:AT20"/>
+    <mergeCell ref="AT21:AT22"/>
+    <mergeCell ref="AT23:AT24"/>
+    <mergeCell ref="AT25:AT26"/>
+    <mergeCell ref="AT27:AT28"/>
+    <mergeCell ref="AT30:AT31"/>
+    <mergeCell ref="AT32:AT33"/>
+    <mergeCell ref="AT3:AT4"/>
+    <mergeCell ref="AT5:AT6"/>
+    <mergeCell ref="AT7:AT8"/>
+    <mergeCell ref="AT9:AT10"/>
+    <mergeCell ref="AT11:AT12"/>
+    <mergeCell ref="AT13:AT14"/>
+    <mergeCell ref="AT15:AT16"/>
+    <mergeCell ref="AT17:AT18"/>
+    <mergeCell ref="AT34:AT35"/>
+    <mergeCell ref="AT36:AT37"/>
+    <mergeCell ref="AT38:AT39"/>
+    <mergeCell ref="AT40:AT41"/>
+    <mergeCell ref="BD32:BD33"/>
+    <mergeCell ref="BD34:BD35"/>
+    <mergeCell ref="BD36:BD37"/>
+    <mergeCell ref="BD38:BD39"/>
+    <mergeCell ref="BF29:BM29"/>
+    <mergeCell ref="AV29:BC29"/>
+    <mergeCell ref="BD40:BD41"/>
+    <mergeCell ref="BD13:BD14"/>
+    <mergeCell ref="BD15:BD16"/>
+    <mergeCell ref="BD17:BD18"/>
+    <mergeCell ref="BD19:BD20"/>
+    <mergeCell ref="BD21:BD22"/>
+    <mergeCell ref="BD23:BD24"/>
+    <mergeCell ref="BD25:BD26"/>
+    <mergeCell ref="BD27:BD28"/>
+    <mergeCell ref="BD30:BD31"/>
+    <mergeCell ref="BN3:BN4"/>
+    <mergeCell ref="BN5:BN6"/>
+    <mergeCell ref="BN7:BN8"/>
+    <mergeCell ref="BN9:BN10"/>
+    <mergeCell ref="BD3:BD4"/>
+    <mergeCell ref="BD5:BD6"/>
+    <mergeCell ref="BD7:BD8"/>
+    <mergeCell ref="BD9:BD10"/>
+    <mergeCell ref="BD11:BD12"/>
+    <mergeCell ref="BN11:BN12"/>
+    <mergeCell ref="BN17:BN18"/>
+    <mergeCell ref="BN19:BN20"/>
+    <mergeCell ref="BN40:BN41"/>
+    <mergeCell ref="BN42:BN43"/>
+    <mergeCell ref="BN44:BN45"/>
+    <mergeCell ref="BN46:BN47"/>
+    <mergeCell ref="BN52:BN53"/>
+    <mergeCell ref="BN21:BN22"/>
+    <mergeCell ref="BN23:BN24"/>
+    <mergeCell ref="BN25:BN26"/>
+    <mergeCell ref="BN27:BN28"/>
+    <mergeCell ref="BN30:BN31"/>
+    <mergeCell ref="BN32:BN33"/>
+    <mergeCell ref="BN34:BN35"/>
+    <mergeCell ref="BN36:BN37"/>
+    <mergeCell ref="BN38:BN39"/>
+    <mergeCell ref="BN48:BN49"/>
+    <mergeCell ref="BN13:BN14"/>
+    <mergeCell ref="AB2:AI2"/>
+    <mergeCell ref="AV2:BC2"/>
+    <mergeCell ref="BF2:BM2"/>
+    <mergeCell ref="H3:I36"/>
+    <mergeCell ref="J3:K36"/>
+    <mergeCell ref="L3:M36"/>
+    <mergeCell ref="O3:U7"/>
+    <mergeCell ref="O8:U10"/>
+    <mergeCell ref="E25:G30"/>
+    <mergeCell ref="BN15:BN16"/>
+    <mergeCell ref="E31:G33"/>
+    <mergeCell ref="E34:G35"/>
+    <mergeCell ref="E36:G36"/>
+    <mergeCell ref="F10:G12"/>
+    <mergeCell ref="O11:U14"/>
+    <mergeCell ref="A12:B14"/>
+    <mergeCell ref="E14:G15"/>
+    <mergeCell ref="A15:B17"/>
+    <mergeCell ref="O15:U18"/>
+    <mergeCell ref="E16:G18"/>
+    <mergeCell ref="A18:B20"/>
+    <mergeCell ref="O19:U36"/>
+    <mergeCell ref="E20:G24"/>
+    <mergeCell ref="AJ40:AJ41"/>
+    <mergeCell ref="AJ42:AJ43"/>
+    <mergeCell ref="AJ44:AJ45"/>
+    <mergeCell ref="AJ46:AJ47"/>
+    <mergeCell ref="AJ48:AJ49"/>
+    <mergeCell ref="E37:M37"/>
+    <mergeCell ref="O37:U37"/>
+    <mergeCell ref="O38:O39"/>
+    <mergeCell ref="E44:F45"/>
+    <mergeCell ref="G44:G45"/>
+    <mergeCell ref="BM76:BM78"/>
+    <mergeCell ref="O42:P42"/>
+    <mergeCell ref="O43:P43"/>
+    <mergeCell ref="BD42:BD43"/>
+    <mergeCell ref="BD44:BD45"/>
+    <mergeCell ref="AT42:AT43"/>
+    <mergeCell ref="AT44:AT45"/>
+    <mergeCell ref="AT46:AT47"/>
+    <mergeCell ref="BD46:BD47"/>
+    <mergeCell ref="BD48:BD49"/>
+    <mergeCell ref="BD50:BD51"/>
+    <mergeCell ref="BD52:BD53"/>
+    <mergeCell ref="O44:P44"/>
+    <mergeCell ref="E50:G57"/>
+    <mergeCell ref="BN50:BN51"/>
+    <mergeCell ref="BN54:BN55"/>
+    <mergeCell ref="BN56:BN57"/>
+    <mergeCell ref="AU66:AU68"/>
+    <mergeCell ref="AT50:AT51"/>
+    <mergeCell ref="O48:U57"/>
+    <mergeCell ref="AT48:AT49"/>
+    <mergeCell ref="AK58:AN58"/>
     <mergeCell ref="A84:A86"/>
     <mergeCell ref="R84:S84"/>
     <mergeCell ref="T84:U84"/>
@@ -14411,125 +14510,42 @@
     <mergeCell ref="U80:U81"/>
     <mergeCell ref="V80:V81"/>
     <mergeCell ref="W80:W81"/>
-    <mergeCell ref="E50:G57"/>
-    <mergeCell ref="BN50:BN51"/>
-    <mergeCell ref="BN54:BN55"/>
-    <mergeCell ref="BN56:BN57"/>
-    <mergeCell ref="AU66:AU68"/>
-    <mergeCell ref="AT50:AT51"/>
-    <mergeCell ref="O48:U57"/>
-    <mergeCell ref="AT48:AT49"/>
-    <mergeCell ref="AK58:AN58"/>
-    <mergeCell ref="BM76:BM78"/>
-    <mergeCell ref="O42:P42"/>
-    <mergeCell ref="O43:P43"/>
-    <mergeCell ref="BD42:BD43"/>
-    <mergeCell ref="BD44:BD45"/>
-    <mergeCell ref="AT42:AT43"/>
-    <mergeCell ref="AT44:AT45"/>
-    <mergeCell ref="AT46:AT47"/>
-    <mergeCell ref="BD46:BD47"/>
-    <mergeCell ref="BD48:BD49"/>
-    <mergeCell ref="BD50:BD51"/>
-    <mergeCell ref="BD52:BD53"/>
-    <mergeCell ref="O44:P44"/>
-    <mergeCell ref="AJ40:AJ41"/>
-    <mergeCell ref="AJ42:AJ43"/>
-    <mergeCell ref="AJ44:AJ45"/>
-    <mergeCell ref="AJ46:AJ47"/>
-    <mergeCell ref="AJ48:AJ49"/>
-    <mergeCell ref="E37:M37"/>
-    <mergeCell ref="O37:U37"/>
-    <mergeCell ref="O38:O39"/>
-    <mergeCell ref="E44:F45"/>
-    <mergeCell ref="G44:G45"/>
-    <mergeCell ref="O11:U14"/>
-    <mergeCell ref="A12:B14"/>
-    <mergeCell ref="E14:G15"/>
-    <mergeCell ref="A15:B17"/>
-    <mergeCell ref="O15:U18"/>
-    <mergeCell ref="E16:G18"/>
-    <mergeCell ref="A18:B20"/>
-    <mergeCell ref="O19:U36"/>
-    <mergeCell ref="E20:G24"/>
-    <mergeCell ref="BN13:BN14"/>
-    <mergeCell ref="AB2:AI2"/>
-    <mergeCell ref="AV2:BC2"/>
-    <mergeCell ref="BF2:BM2"/>
-    <mergeCell ref="H3:I36"/>
-    <mergeCell ref="J3:K36"/>
-    <mergeCell ref="L3:M36"/>
-    <mergeCell ref="O3:U7"/>
-    <mergeCell ref="O8:U10"/>
-    <mergeCell ref="E25:G30"/>
-    <mergeCell ref="BN15:BN16"/>
-    <mergeCell ref="E31:G33"/>
-    <mergeCell ref="E34:G35"/>
-    <mergeCell ref="E36:G36"/>
-    <mergeCell ref="F10:G12"/>
-    <mergeCell ref="BN17:BN18"/>
-    <mergeCell ref="BN19:BN20"/>
-    <mergeCell ref="BN40:BN41"/>
-    <mergeCell ref="BN42:BN43"/>
-    <mergeCell ref="BN44:BN45"/>
-    <mergeCell ref="BN46:BN47"/>
-    <mergeCell ref="BN52:BN53"/>
-    <mergeCell ref="BN21:BN22"/>
-    <mergeCell ref="BN23:BN24"/>
-    <mergeCell ref="BN25:BN26"/>
-    <mergeCell ref="BN27:BN28"/>
-    <mergeCell ref="BN30:BN31"/>
-    <mergeCell ref="BN32:BN33"/>
-    <mergeCell ref="BN34:BN35"/>
-    <mergeCell ref="BN36:BN37"/>
-    <mergeCell ref="BN38:BN39"/>
-    <mergeCell ref="BN48:BN49"/>
-    <mergeCell ref="BN3:BN4"/>
-    <mergeCell ref="BN5:BN6"/>
-    <mergeCell ref="BN7:BN8"/>
-    <mergeCell ref="BN9:BN10"/>
-    <mergeCell ref="BD3:BD4"/>
-    <mergeCell ref="BD5:BD6"/>
-    <mergeCell ref="BD7:BD8"/>
-    <mergeCell ref="BD9:BD10"/>
-    <mergeCell ref="BD11:BD12"/>
-    <mergeCell ref="BN11:BN12"/>
-    <mergeCell ref="BD13:BD14"/>
-    <mergeCell ref="BD15:BD16"/>
-    <mergeCell ref="BD17:BD18"/>
-    <mergeCell ref="BD19:BD20"/>
-    <mergeCell ref="BD21:BD22"/>
-    <mergeCell ref="BD23:BD24"/>
-    <mergeCell ref="BD25:BD26"/>
-    <mergeCell ref="BD27:BD28"/>
-    <mergeCell ref="BD30:BD31"/>
-    <mergeCell ref="AT34:AT35"/>
-    <mergeCell ref="AT36:AT37"/>
-    <mergeCell ref="AT38:AT39"/>
-    <mergeCell ref="AT40:AT41"/>
-    <mergeCell ref="BD32:BD33"/>
-    <mergeCell ref="BD34:BD35"/>
-    <mergeCell ref="BD36:BD37"/>
-    <mergeCell ref="BD38:BD39"/>
-    <mergeCell ref="BF29:BM29"/>
-    <mergeCell ref="AV29:BC29"/>
-    <mergeCell ref="BD40:BD41"/>
-    <mergeCell ref="AO2:AP2"/>
-    <mergeCell ref="AT19:AT20"/>
-    <mergeCell ref="AT21:AT22"/>
-    <mergeCell ref="AT23:AT24"/>
-    <mergeCell ref="AT25:AT26"/>
-    <mergeCell ref="AT27:AT28"/>
-    <mergeCell ref="AT30:AT31"/>
-    <mergeCell ref="AT32:AT33"/>
-    <mergeCell ref="AT3:AT4"/>
-    <mergeCell ref="AT5:AT6"/>
-    <mergeCell ref="AT7:AT8"/>
-    <mergeCell ref="AT9:AT10"/>
-    <mergeCell ref="AT11:AT12"/>
-    <mergeCell ref="AT13:AT14"/>
-    <mergeCell ref="AT15:AT16"/>
-    <mergeCell ref="AT17:AT18"/>
+    <mergeCell ref="E88:E90"/>
+    <mergeCell ref="G88:G90"/>
+    <mergeCell ref="H88:H90"/>
+    <mergeCell ref="I88:I90"/>
+    <mergeCell ref="AD69:AH70"/>
+    <mergeCell ref="G78:H78"/>
+    <mergeCell ref="AK61:AN63"/>
+    <mergeCell ref="AK66:AP68"/>
+    <mergeCell ref="AS66:AS68"/>
+    <mergeCell ref="O58:U70"/>
+    <mergeCell ref="R83:S83"/>
+    <mergeCell ref="T83:U83"/>
+    <mergeCell ref="V83:W83"/>
+    <mergeCell ref="X80:X81"/>
+    <mergeCell ref="Y80:Y81"/>
+    <mergeCell ref="Z80:Z81"/>
+    <mergeCell ref="R80:R81"/>
+    <mergeCell ref="S80:S81"/>
+    <mergeCell ref="AJ3:AJ4"/>
+    <mergeCell ref="AJ5:AJ6"/>
+    <mergeCell ref="AJ7:AJ8"/>
+    <mergeCell ref="AJ9:AJ10"/>
+    <mergeCell ref="AJ11:AJ12"/>
+    <mergeCell ref="AJ13:AJ14"/>
+    <mergeCell ref="AJ15:AJ16"/>
+    <mergeCell ref="AJ17:AJ18"/>
+    <mergeCell ref="AJ19:AJ20"/>
+    <mergeCell ref="AJ21:AJ22"/>
+    <mergeCell ref="AJ23:AJ24"/>
+    <mergeCell ref="AJ25:AJ26"/>
+    <mergeCell ref="AJ27:AJ28"/>
+    <mergeCell ref="AJ30:AJ31"/>
+    <mergeCell ref="AJ32:AJ33"/>
+    <mergeCell ref="AJ34:AJ35"/>
+    <mergeCell ref="AJ36:AJ37"/>
+    <mergeCell ref="AJ38:AJ39"/>
   </mergeCells>
   <phoneticPr fontId="21" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
